--- a/Guias Produccion/HU-57723.xlsx
+++ b/Guias Produccion/HU-57723.xlsx
@@ -1914,8 +1914,89 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="54" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2019,90 +2100,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="54" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2174,6 +2171,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -11021,42 +11021,42 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:15" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="94" t="s">
+      <c r="A3" s="121" t="s">
         <v>103</v>
       </c>
-      <c r="B3" s="95"/>
-      <c r="C3" s="95"/>
-      <c r="D3" s="95"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="95"/>
-      <c r="G3" s="95"/>
-      <c r="H3" s="95"/>
-      <c r="I3" s="95"/>
-      <c r="J3" s="95"/>
-      <c r="K3" s="95"/>
-      <c r="L3" s="96"/>
-      <c r="N3" s="88" t="s">
+      <c r="B3" s="122"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="122"/>
+      <c r="I3" s="122"/>
+      <c r="J3" s="122"/>
+      <c r="K3" s="122"/>
+      <c r="L3" s="123"/>
+      <c r="N3" s="115" t="s">
         <v>0</v>
       </c>
-      <c r="O3" s="89"/>
+      <c r="O3" s="116"/>
     </row>
     <row r="4" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="101" t="s">
+      <c r="B4" s="128" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="102"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="102"/>
-      <c r="F4" s="102"/>
-      <c r="G4" s="102"/>
-      <c r="H4" s="102"/>
-      <c r="I4" s="102"/>
-      <c r="J4" s="103"/>
-      <c r="K4" s="103"/>
-      <c r="L4" s="104"/>
+      <c r="C4" s="129"/>
+      <c r="D4" s="129"/>
+      <c r="E4" s="129"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="129"/>
+      <c r="H4" s="129"/>
+      <c r="I4" s="129"/>
+      <c r="J4" s="130"/>
+      <c r="K4" s="130"/>
+      <c r="L4" s="131"/>
       <c r="N4" s="21" t="s">
         <v>2</v>
       </c>
@@ -11066,19 +11066,19 @@
       <c r="A5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="105" t="s">
+      <c r="B5" s="132" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="105"/>
-      <c r="D5" s="105"/>
-      <c r="E5" s="105"/>
-      <c r="F5" s="105"/>
-      <c r="G5" s="105"/>
-      <c r="H5" s="105"/>
-      <c r="I5" s="105"/>
-      <c r="J5" s="106"/>
-      <c r="K5" s="106"/>
-      <c r="L5" s="107"/>
+      <c r="C5" s="132"/>
+      <c r="D5" s="132"/>
+      <c r="E5" s="132"/>
+      <c r="F5" s="132"/>
+      <c r="G5" s="132"/>
+      <c r="H5" s="132"/>
+      <c r="I5" s="132"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="133"/>
+      <c r="L5" s="134"/>
       <c r="N5" s="15" t="s">
         <v>4</v>
       </c>
@@ -11088,19 +11088,19 @@
       <c r="A6" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="91">
+      <c r="B6" s="118">
         <v>46073</v>
       </c>
-      <c r="C6" s="92"/>
-      <c r="D6" s="92"/>
-      <c r="E6" s="92"/>
-      <c r="F6" s="92"/>
-      <c r="G6" s="92"/>
-      <c r="H6" s="92"/>
-      <c r="I6" s="92"/>
-      <c r="J6" s="92"/>
-      <c r="K6" s="92"/>
-      <c r="L6" s="93"/>
+      <c r="C6" s="119"/>
+      <c r="D6" s="119"/>
+      <c r="E6" s="119"/>
+      <c r="F6" s="119"/>
+      <c r="G6" s="119"/>
+      <c r="H6" s="119"/>
+      <c r="I6" s="119"/>
+      <c r="J6" s="119"/>
+      <c r="K6" s="119"/>
+      <c r="L6" s="120"/>
       <c r="N6" s="14"/>
       <c r="O6" s="14"/>
     </row>
@@ -11108,17 +11108,17 @@
       <c r="A7" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="108"/>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="109"/>
-      <c r="F7" s="109"/>
-      <c r="G7" s="109"/>
-      <c r="H7" s="109"/>
-      <c r="I7" s="109"/>
-      <c r="J7" s="110"/>
-      <c r="K7" s="110"/>
-      <c r="L7" s="111"/>
+      <c r="B7" s="135"/>
+      <c r="C7" s="136"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="136"/>
+      <c r="F7" s="136"/>
+      <c r="G7" s="136"/>
+      <c r="H7" s="136"/>
+      <c r="I7" s="136"/>
+      <c r="J7" s="137"/>
+      <c r="K7" s="137"/>
+      <c r="L7" s="138"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
@@ -11135,20 +11135,20 @@
       <c r="L8" s="13"/>
     </row>
     <row r="9" spans="1:15" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="97" t="s">
+      <c r="A9" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="98"/>
-      <c r="C9" s="98"/>
-      <c r="D9" s="98"/>
-      <c r="E9" s="98"/>
-      <c r="F9" s="98"/>
-      <c r="G9" s="98"/>
-      <c r="H9" s="98"/>
-      <c r="I9" s="98"/>
-      <c r="J9" s="99"/>
-      <c r="K9" s="99"/>
-      <c r="L9" s="100"/>
+      <c r="B9" s="125"/>
+      <c r="C9" s="125"/>
+      <c r="D9" s="125"/>
+      <c r="E9" s="125"/>
+      <c r="F9" s="125"/>
+      <c r="G9" s="125"/>
+      <c r="H9" s="125"/>
+      <c r="I9" s="125"/>
+      <c r="J9" s="126"/>
+      <c r="K9" s="126"/>
+      <c r="L9" s="127"/>
     </row>
     <row r="10" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -11248,63 +11248,63 @@
       <c r="A14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="90"/>
-      <c r="C14" s="86"/>
-      <c r="D14" s="86"/>
-      <c r="E14" s="86"/>
-      <c r="F14" s="86"/>
-      <c r="G14" s="86"/>
-      <c r="H14" s="86"/>
-      <c r="I14" s="86"/>
-      <c r="J14" s="86"/>
-      <c r="K14" s="86"/>
-      <c r="L14" s="87"/>
+      <c r="B14" s="117"/>
+      <c r="C14" s="113"/>
+      <c r="D14" s="113"/>
+      <c r="E14" s="113"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="113"/>
+      <c r="H14" s="113"/>
+      <c r="I14" s="113"/>
+      <c r="J14" s="113"/>
+      <c r="K14" s="113"/>
+      <c r="L14" s="114"/>
     </row>
     <row r="15" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="85"/>
-      <c r="C15" s="86"/>
-      <c r="D15" s="86"/>
-      <c r="E15" s="86"/>
-      <c r="F15" s="86"/>
-      <c r="G15" s="86"/>
-      <c r="H15" s="86"/>
-      <c r="I15" s="86"/>
-      <c r="J15" s="86"/>
-      <c r="K15" s="86"/>
-      <c r="L15" s="87"/>
+      <c r="B15" s="112"/>
+      <c r="C15" s="113"/>
+      <c r="D15" s="113"/>
+      <c r="E15" s="113"/>
+      <c r="F15" s="113"/>
+      <c r="G15" s="113"/>
+      <c r="H15" s="113"/>
+      <c r="I15" s="113"/>
+      <c r="J15" s="113"/>
+      <c r="K15" s="113"/>
+      <c r="L15" s="114"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="78"/>
-      <c r="B16" s="79"/>
-      <c r="C16" s="79"/>
-      <c r="D16" s="79"/>
-      <c r="E16" s="79"/>
-      <c r="F16" s="79"/>
-      <c r="G16" s="79"/>
-      <c r="H16" s="79"/>
-      <c r="I16" s="79"/>
-      <c r="J16" s="79"/>
-      <c r="K16" s="79"/>
-      <c r="L16" s="80"/>
+      <c r="A16" s="105"/>
+      <c r="B16" s="106"/>
+      <c r="C16" s="106"/>
+      <c r="D16" s="106"/>
+      <c r="E16" s="106"/>
+      <c r="F16" s="106"/>
+      <c r="G16" s="106"/>
+      <c r="H16" s="106"/>
+      <c r="I16" s="106"/>
+      <c r="J16" s="106"/>
+      <c r="K16" s="106"/>
+      <c r="L16" s="107"/>
     </row>
     <row r="17" spans="1:12" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="81" t="s">
+      <c r="A17" s="108" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="82"/>
-      <c r="C17" s="82"/>
-      <c r="D17" s="82"/>
-      <c r="E17" s="82"/>
-      <c r="F17" s="82"/>
-      <c r="G17" s="82"/>
-      <c r="H17" s="82"/>
-      <c r="I17" s="82"/>
-      <c r="J17" s="83"/>
-      <c r="K17" s="83"/>
-      <c r="L17" s="84"/>
+      <c r="B17" s="109"/>
+      <c r="C17" s="109"/>
+      <c r="D17" s="109"/>
+      <c r="E17" s="109"/>
+      <c r="F17" s="109"/>
+      <c r="G17" s="109"/>
+      <c r="H17" s="109"/>
+      <c r="I17" s="109"/>
+      <c r="J17" s="110"/>
+      <c r="K17" s="110"/>
+      <c r="L17" s="111"/>
     </row>
     <row r="18" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
@@ -11314,19 +11314,19 @@
       <c r="C18" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="112" t="s">
+      <c r="D18" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="114" t="s">
+      <c r="E18" s="83" t="s">
         <v>142</v>
       </c>
-      <c r="F18" s="114"/>
-      <c r="G18" s="114"/>
-      <c r="H18" s="114"/>
-      <c r="I18" s="114"/>
-      <c r="J18" s="115"/>
-      <c r="K18" s="115"/>
-      <c r="L18" s="116"/>
+      <c r="F18" s="83"/>
+      <c r="G18" s="83"/>
+      <c r="H18" s="83"/>
+      <c r="I18" s="83"/>
+      <c r="J18" s="84"/>
+      <c r="K18" s="84"/>
+      <c r="L18" s="85"/>
     </row>
     <row r="19" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
@@ -11336,15 +11336,15 @@
         <v>30</v>
       </c>
       <c r="C19" s="44"/>
-      <c r="D19" s="113"/>
-      <c r="E19" s="117"/>
-      <c r="F19" s="117"/>
-      <c r="G19" s="117"/>
-      <c r="H19" s="117"/>
-      <c r="I19" s="117"/>
-      <c r="J19" s="118"/>
-      <c r="K19" s="118"/>
-      <c r="L19" s="119"/>
+      <c r="D19" s="82"/>
+      <c r="E19" s="86"/>
+      <c r="F19" s="86"/>
+      <c r="G19" s="86"/>
+      <c r="H19" s="86"/>
+      <c r="I19" s="86"/>
+      <c r="J19" s="87"/>
+      <c r="K19" s="87"/>
+      <c r="L19" s="88"/>
     </row>
     <row r="20" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
@@ -11354,15 +11354,15 @@
       <c r="C20" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="113"/>
-      <c r="E20" s="117"/>
-      <c r="F20" s="117"/>
-      <c r="G20" s="117"/>
-      <c r="H20" s="117"/>
-      <c r="I20" s="117"/>
-      <c r="J20" s="118"/>
-      <c r="K20" s="118"/>
-      <c r="L20" s="119"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="86"/>
+      <c r="F20" s="86"/>
+      <c r="G20" s="86"/>
+      <c r="H20" s="86"/>
+      <c r="I20" s="86"/>
+      <c r="J20" s="87"/>
+      <c r="K20" s="87"/>
+      <c r="L20" s="88"/>
     </row>
     <row r="21" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
@@ -11372,19 +11372,19 @@
       <c r="C21" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="128" t="s">
+      <c r="D21" s="97" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="130" t="s">
+      <c r="E21" s="99" t="s">
         <v>107</v>
       </c>
-      <c r="F21" s="131"/>
-      <c r="G21" s="131"/>
-      <c r="H21" s="131"/>
-      <c r="I21" s="131"/>
-      <c r="J21" s="131"/>
-      <c r="K21" s="131"/>
-      <c r="L21" s="132"/>
+      <c r="F21" s="100"/>
+      <c r="G21" s="100"/>
+      <c r="H21" s="100"/>
+      <c r="I21" s="100"/>
+      <c r="J21" s="100"/>
+      <c r="K21" s="100"/>
+      <c r="L21" s="101"/>
     </row>
     <row r="22" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
@@ -11394,45 +11394,45 @@
       <c r="C22" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="129"/>
-      <c r="E22" s="133"/>
-      <c r="F22" s="134"/>
-      <c r="G22" s="134"/>
-      <c r="H22" s="134"/>
-      <c r="I22" s="134"/>
-      <c r="J22" s="134"/>
-      <c r="K22" s="134"/>
-      <c r="L22" s="135"/>
+      <c r="D22" s="98"/>
+      <c r="E22" s="102"/>
+      <c r="F22" s="103"/>
+      <c r="G22" s="103"/>
+      <c r="H22" s="103"/>
+      <c r="I22" s="103"/>
+      <c r="J22" s="103"/>
+      <c r="K22" s="103"/>
+      <c r="L22" s="104"/>
     </row>
     <row r="23" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="121"/>
-      <c r="B23" s="122"/>
-      <c r="C23" s="122"/>
-      <c r="D23" s="123"/>
-      <c r="E23" s="123"/>
-      <c r="F23" s="123"/>
-      <c r="G23" s="123"/>
-      <c r="H23" s="123"/>
-      <c r="I23" s="123"/>
-      <c r="J23" s="123"/>
-      <c r="K23" s="123"/>
-      <c r="L23" s="124"/>
+      <c r="A23" s="90"/>
+      <c r="B23" s="91"/>
+      <c r="C23" s="91"/>
+      <c r="D23" s="92"/>
+      <c r="E23" s="92"/>
+      <c r="F23" s="92"/>
+      <c r="G23" s="92"/>
+      <c r="H23" s="92"/>
+      <c r="I23" s="92"/>
+      <c r="J23" s="92"/>
+      <c r="K23" s="92"/>
+      <c r="L23" s="93"/>
     </row>
     <row r="24" spans="1:12" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="125" t="s">
+      <c r="A24" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="126"/>
-      <c r="C24" s="126"/>
-      <c r="D24" s="126"/>
-      <c r="E24" s="126"/>
-      <c r="F24" s="126"/>
-      <c r="G24" s="126"/>
-      <c r="H24" s="126"/>
-      <c r="I24" s="126"/>
-      <c r="J24" s="126"/>
-      <c r="K24" s="126"/>
-      <c r="L24" s="127"/>
+      <c r="B24" s="95"/>
+      <c r="C24" s="95"/>
+      <c r="D24" s="95"/>
+      <c r="E24" s="95"/>
+      <c r="F24" s="95"/>
+      <c r="G24" s="95"/>
+      <c r="H24" s="95"/>
+      <c r="I24" s="95"/>
+      <c r="J24" s="95"/>
+      <c r="K24" s="95"/>
+      <c r="L24" s="96"/>
     </row>
     <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
@@ -11444,17 +11444,17 @@
       <c r="C25" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="120" t="s">
+      <c r="D25" s="89" t="s">
         <v>38</v>
       </c>
-      <c r="E25" s="120"/>
-      <c r="F25" s="120"/>
-      <c r="G25" s="120"/>
-      <c r="H25" s="120"/>
-      <c r="I25" s="120"/>
-      <c r="J25" s="120"/>
-      <c r="K25" s="120"/>
-      <c r="L25" s="120"/>
+      <c r="E25" s="89"/>
+      <c r="F25" s="89"/>
+      <c r="G25" s="89"/>
+      <c r="H25" s="89"/>
+      <c r="I25" s="89"/>
+      <c r="J25" s="89"/>
+      <c r="K25" s="89"/>
+      <c r="L25" s="89"/>
     </row>
     <row r="26" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="33">
@@ -11464,17 +11464,17 @@
         <v>115</v>
       </c>
       <c r="C26" s="34"/>
-      <c r="D26" s="136" t="s">
+      <c r="D26" s="77" t="s">
         <v>108</v>
       </c>
-      <c r="E26" s="137"/>
-      <c r="F26" s="137"/>
-      <c r="G26" s="137"/>
-      <c r="H26" s="137"/>
-      <c r="I26" s="137"/>
-      <c r="J26" s="137"/>
-      <c r="K26" s="137"/>
-      <c r="L26" s="137"/>
+      <c r="E26" s="78"/>
+      <c r="F26" s="78"/>
+      <c r="G26" s="78"/>
+      <c r="H26" s="78"/>
+      <c r="I26" s="78"/>
+      <c r="J26" s="78"/>
+      <c r="K26" s="78"/>
+      <c r="L26" s="78"/>
     </row>
     <row r="27" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
@@ -11484,15 +11484,15 @@
         <v>116</v>
       </c>
       <c r="C27" s="34"/>
-      <c r="D27" s="138"/>
-      <c r="E27" s="139"/>
-      <c r="F27" s="139"/>
-      <c r="G27" s="139"/>
-      <c r="H27" s="139"/>
-      <c r="I27" s="139"/>
-      <c r="J27" s="139"/>
-      <c r="K27" s="139"/>
-      <c r="L27" s="139"/>
+      <c r="D27" s="79"/>
+      <c r="E27" s="80"/>
+      <c r="F27" s="80"/>
+      <c r="G27" s="80"/>
+      <c r="H27" s="80"/>
+      <c r="I27" s="80"/>
+      <c r="J27" s="80"/>
+      <c r="K27" s="80"/>
+      <c r="L27" s="80"/>
     </row>
     <row r="28" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="33">
@@ -11502,15 +11502,15 @@
         <v>117</v>
       </c>
       <c r="C28" s="34"/>
-      <c r="D28" s="138"/>
-      <c r="E28" s="139"/>
-      <c r="F28" s="139"/>
-      <c r="G28" s="139"/>
-      <c r="H28" s="139"/>
-      <c r="I28" s="139"/>
-      <c r="J28" s="139"/>
-      <c r="K28" s="139"/>
-      <c r="L28" s="139"/>
+      <c r="D28" s="79"/>
+      <c r="E28" s="80"/>
+      <c r="F28" s="80"/>
+      <c r="G28" s="80"/>
+      <c r="H28" s="80"/>
+      <c r="I28" s="80"/>
+      <c r="J28" s="80"/>
+      <c r="K28" s="80"/>
+      <c r="L28" s="80"/>
     </row>
     <row r="29" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
@@ -11520,15 +11520,15 @@
         <v>118</v>
       </c>
       <c r="C29" s="34"/>
-      <c r="D29" s="138"/>
-      <c r="E29" s="139"/>
-      <c r="F29" s="139"/>
-      <c r="G29" s="139"/>
-      <c r="H29" s="139"/>
-      <c r="I29" s="139"/>
-      <c r="J29" s="139"/>
-      <c r="K29" s="139"/>
-      <c r="L29" s="139"/>
+      <c r="D29" s="79"/>
+      <c r="E29" s="80"/>
+      <c r="F29" s="80"/>
+      <c r="G29" s="80"/>
+      <c r="H29" s="80"/>
+      <c r="I29" s="80"/>
+      <c r="J29" s="80"/>
+      <c r="K29" s="80"/>
+      <c r="L29" s="80"/>
     </row>
     <row r="30" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="33">
@@ -11538,15 +11538,15 @@
         <v>119</v>
       </c>
       <c r="C30" s="34"/>
-      <c r="D30" s="138"/>
-      <c r="E30" s="139"/>
-      <c r="F30" s="139"/>
-      <c r="G30" s="139"/>
-      <c r="H30" s="139"/>
-      <c r="I30" s="139"/>
-      <c r="J30" s="139"/>
-      <c r="K30" s="139"/>
-      <c r="L30" s="139"/>
+      <c r="D30" s="79"/>
+      <c r="E30" s="80"/>
+      <c r="F30" s="80"/>
+      <c r="G30" s="80"/>
+      <c r="H30" s="80"/>
+      <c r="I30" s="80"/>
+      <c r="J30" s="80"/>
+      <c r="K30" s="80"/>
+      <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="33">
@@ -11556,15 +11556,15 @@
         <v>120</v>
       </c>
       <c r="C31" s="34"/>
-      <c r="D31" s="138"/>
-      <c r="E31" s="139"/>
-      <c r="F31" s="139"/>
-      <c r="G31" s="139"/>
-      <c r="H31" s="139"/>
-      <c r="I31" s="139"/>
-      <c r="J31" s="139"/>
-      <c r="K31" s="139"/>
-      <c r="L31" s="139"/>
+      <c r="D31" s="79"/>
+      <c r="E31" s="80"/>
+      <c r="F31" s="80"/>
+      <c r="G31" s="80"/>
+      <c r="H31" s="80"/>
+      <c r="I31" s="80"/>
+      <c r="J31" s="80"/>
+      <c r="K31" s="80"/>
+      <c r="L31" s="80"/>
     </row>
     <row r="32" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="33">
@@ -11574,15 +11574,15 @@
         <v>121</v>
       </c>
       <c r="C32" s="34"/>
-      <c r="D32" s="138"/>
-      <c r="E32" s="139"/>
-      <c r="F32" s="139"/>
-      <c r="G32" s="139"/>
-      <c r="H32" s="139"/>
-      <c r="I32" s="139"/>
-      <c r="J32" s="139"/>
-      <c r="K32" s="139"/>
-      <c r="L32" s="139"/>
+      <c r="D32" s="79"/>
+      <c r="E32" s="80"/>
+      <c r="F32" s="80"/>
+      <c r="G32" s="80"/>
+      <c r="H32" s="80"/>
+      <c r="I32" s="80"/>
+      <c r="J32" s="80"/>
+      <c r="K32" s="80"/>
+      <c r="L32" s="80"/>
     </row>
     <row r="33" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="33">
@@ -11592,15 +11592,15 @@
         <v>122</v>
       </c>
       <c r="C33" s="34"/>
-      <c r="D33" s="138"/>
-      <c r="E33" s="139"/>
-      <c r="F33" s="139"/>
-      <c r="G33" s="139"/>
-      <c r="H33" s="139"/>
-      <c r="I33" s="139"/>
-      <c r="J33" s="139"/>
-      <c r="K33" s="139"/>
-      <c r="L33" s="139"/>
+      <c r="D33" s="79"/>
+      <c r="E33" s="80"/>
+      <c r="F33" s="80"/>
+      <c r="G33" s="80"/>
+      <c r="H33" s="80"/>
+      <c r="I33" s="80"/>
+      <c r="J33" s="80"/>
+      <c r="K33" s="80"/>
+      <c r="L33" s="80"/>
     </row>
     <row r="34" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="33">
@@ -11610,15 +11610,15 @@
         <v>123</v>
       </c>
       <c r="C34" s="34"/>
-      <c r="D34" s="138"/>
-      <c r="E34" s="139"/>
-      <c r="F34" s="139"/>
-      <c r="G34" s="139"/>
-      <c r="H34" s="139"/>
-      <c r="I34" s="139"/>
-      <c r="J34" s="139"/>
-      <c r="K34" s="139"/>
-      <c r="L34" s="139"/>
+      <c r="D34" s="79"/>
+      <c r="E34" s="80"/>
+      <c r="F34" s="80"/>
+      <c r="G34" s="80"/>
+      <c r="H34" s="80"/>
+      <c r="I34" s="80"/>
+      <c r="J34" s="80"/>
+      <c r="K34" s="80"/>
+      <c r="L34" s="80"/>
     </row>
     <row r="35" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="33">
@@ -11628,15 +11628,15 @@
         <v>124</v>
       </c>
       <c r="C35" s="34"/>
-      <c r="D35" s="138"/>
-      <c r="E35" s="139"/>
-      <c r="F35" s="139"/>
-      <c r="G35" s="139"/>
-      <c r="H35" s="139"/>
-      <c r="I35" s="139"/>
-      <c r="J35" s="139"/>
-      <c r="K35" s="139"/>
-      <c r="L35" s="139"/>
+      <c r="D35" s="79"/>
+      <c r="E35" s="80"/>
+      <c r="F35" s="80"/>
+      <c r="G35" s="80"/>
+      <c r="H35" s="80"/>
+      <c r="I35" s="80"/>
+      <c r="J35" s="80"/>
+      <c r="K35" s="80"/>
+      <c r="L35" s="80"/>
     </row>
     <row r="36" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="33">
@@ -11646,15 +11646,15 @@
         <v>125</v>
       </c>
       <c r="C36" s="34"/>
-      <c r="D36" s="138"/>
-      <c r="E36" s="139"/>
-      <c r="F36" s="139"/>
-      <c r="G36" s="139"/>
-      <c r="H36" s="139"/>
-      <c r="I36" s="139"/>
-      <c r="J36" s="139"/>
-      <c r="K36" s="139"/>
-      <c r="L36" s="139"/>
+      <c r="D36" s="79"/>
+      <c r="E36" s="80"/>
+      <c r="F36" s="80"/>
+      <c r="G36" s="80"/>
+      <c r="H36" s="80"/>
+      <c r="I36" s="80"/>
+      <c r="J36" s="80"/>
+      <c r="K36" s="80"/>
+      <c r="L36" s="80"/>
     </row>
     <row r="37" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="33">
@@ -11664,15 +11664,15 @@
         <v>126</v>
       </c>
       <c r="C37" s="34"/>
-      <c r="D37" s="138"/>
-      <c r="E37" s="139"/>
-      <c r="F37" s="139"/>
-      <c r="G37" s="139"/>
-      <c r="H37" s="139"/>
-      <c r="I37" s="139"/>
-      <c r="J37" s="139"/>
-      <c r="K37" s="139"/>
-      <c r="L37" s="139"/>
+      <c r="D37" s="79"/>
+      <c r="E37" s="80"/>
+      <c r="F37" s="80"/>
+      <c r="G37" s="80"/>
+      <c r="H37" s="80"/>
+      <c r="I37" s="80"/>
+      <c r="J37" s="80"/>
+      <c r="K37" s="80"/>
+      <c r="L37" s="80"/>
     </row>
     <row r="38" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="33">
@@ -11682,15 +11682,15 @@
         <v>127</v>
       </c>
       <c r="C38" s="34"/>
-      <c r="D38" s="138"/>
-      <c r="E38" s="139"/>
-      <c r="F38" s="139"/>
-      <c r="G38" s="139"/>
-      <c r="H38" s="139"/>
-      <c r="I38" s="139"/>
-      <c r="J38" s="139"/>
-      <c r="K38" s="139"/>
-      <c r="L38" s="139"/>
+      <c r="D38" s="79"/>
+      <c r="E38" s="80"/>
+      <c r="F38" s="80"/>
+      <c r="G38" s="80"/>
+      <c r="H38" s="80"/>
+      <c r="I38" s="80"/>
+      <c r="J38" s="80"/>
+      <c r="K38" s="80"/>
+      <c r="L38" s="80"/>
     </row>
     <row r="39" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="33">
@@ -11700,15 +11700,15 @@
         <v>128</v>
       </c>
       <c r="C39" s="34"/>
-      <c r="D39" s="138"/>
-      <c r="E39" s="139"/>
-      <c r="F39" s="139"/>
-      <c r="G39" s="139"/>
-      <c r="H39" s="139"/>
-      <c r="I39" s="139"/>
-      <c r="J39" s="139"/>
-      <c r="K39" s="139"/>
-      <c r="L39" s="139"/>
+      <c r="D39" s="79"/>
+      <c r="E39" s="80"/>
+      <c r="F39" s="80"/>
+      <c r="G39" s="80"/>
+      <c r="H39" s="80"/>
+      <c r="I39" s="80"/>
+      <c r="J39" s="80"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="80"/>
     </row>
     <row r="40" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="33">
@@ -11718,15 +11718,15 @@
         <v>129</v>
       </c>
       <c r="C40" s="34"/>
-      <c r="D40" s="138"/>
-      <c r="E40" s="139"/>
-      <c r="F40" s="139"/>
-      <c r="G40" s="139"/>
-      <c r="H40" s="139"/>
-      <c r="I40" s="139"/>
-      <c r="J40" s="139"/>
-      <c r="K40" s="139"/>
-      <c r="L40" s="139"/>
+      <c r="D40" s="79"/>
+      <c r="E40" s="80"/>
+      <c r="F40" s="80"/>
+      <c r="G40" s="80"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="80"/>
+      <c r="J40" s="80"/>
+      <c r="K40" s="80"/>
+      <c r="L40" s="80"/>
     </row>
     <row r="41" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="33">
@@ -11736,15 +11736,15 @@
         <v>130</v>
       </c>
       <c r="C41" s="34"/>
-      <c r="D41" s="138"/>
-      <c r="E41" s="139"/>
-      <c r="F41" s="139"/>
-      <c r="G41" s="139"/>
-      <c r="H41" s="139"/>
-      <c r="I41" s="139"/>
-      <c r="J41" s="139"/>
-      <c r="K41" s="139"/>
-      <c r="L41" s="139"/>
+      <c r="D41" s="79"/>
+      <c r="E41" s="80"/>
+      <c r="F41" s="80"/>
+      <c r="G41" s="80"/>
+      <c r="H41" s="80"/>
+      <c r="I41" s="80"/>
+      <c r="J41" s="80"/>
+      <c r="K41" s="80"/>
+      <c r="L41" s="80"/>
     </row>
     <row r="42" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="33">
@@ -11754,15 +11754,15 @@
         <v>131</v>
       </c>
       <c r="C42" s="34"/>
-      <c r="D42" s="138"/>
-      <c r="E42" s="139"/>
-      <c r="F42" s="139"/>
-      <c r="G42" s="139"/>
-      <c r="H42" s="139"/>
-      <c r="I42" s="139"/>
-      <c r="J42" s="139"/>
-      <c r="K42" s="139"/>
-      <c r="L42" s="139"/>
+      <c r="D42" s="79"/>
+      <c r="E42" s="80"/>
+      <c r="F42" s="80"/>
+      <c r="G42" s="80"/>
+      <c r="H42" s="80"/>
+      <c r="I42" s="80"/>
+      <c r="J42" s="80"/>
+      <c r="K42" s="80"/>
+      <c r="L42" s="80"/>
     </row>
     <row r="43" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="33">
@@ -11772,15 +11772,15 @@
         <v>132</v>
       </c>
       <c r="C43" s="34"/>
-      <c r="D43" s="138"/>
-      <c r="E43" s="139"/>
-      <c r="F43" s="139"/>
-      <c r="G43" s="139"/>
-      <c r="H43" s="139"/>
-      <c r="I43" s="139"/>
-      <c r="J43" s="139"/>
-      <c r="K43" s="139"/>
-      <c r="L43" s="139"/>
+      <c r="D43" s="79"/>
+      <c r="E43" s="80"/>
+      <c r="F43" s="80"/>
+      <c r="G43" s="80"/>
+      <c r="H43" s="80"/>
+      <c r="I43" s="80"/>
+      <c r="J43" s="80"/>
+      <c r="K43" s="80"/>
+      <c r="L43" s="80"/>
     </row>
     <row r="44" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="33">
@@ -11790,15 +11790,15 @@
         <v>133</v>
       </c>
       <c r="C44" s="34"/>
-      <c r="D44" s="138"/>
-      <c r="E44" s="139"/>
-      <c r="F44" s="139"/>
-      <c r="G44" s="139"/>
-      <c r="H44" s="139"/>
-      <c r="I44" s="139"/>
-      <c r="J44" s="139"/>
-      <c r="K44" s="139"/>
-      <c r="L44" s="139"/>
+      <c r="D44" s="79"/>
+      <c r="E44" s="80"/>
+      <c r="F44" s="80"/>
+      <c r="G44" s="80"/>
+      <c r="H44" s="80"/>
+      <c r="I44" s="80"/>
+      <c r="J44" s="80"/>
+      <c r="K44" s="80"/>
+      <c r="L44" s="80"/>
     </row>
     <row r="45" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="33">
@@ -11808,15 +11808,15 @@
         <v>134</v>
       </c>
       <c r="C45" s="34"/>
-      <c r="D45" s="138"/>
-      <c r="E45" s="139"/>
-      <c r="F45" s="139"/>
-      <c r="G45" s="139"/>
-      <c r="H45" s="139"/>
-      <c r="I45" s="139"/>
-      <c r="J45" s="139"/>
-      <c r="K45" s="139"/>
-      <c r="L45" s="139"/>
+      <c r="D45" s="79"/>
+      <c r="E45" s="80"/>
+      <c r="F45" s="80"/>
+      <c r="G45" s="80"/>
+      <c r="H45" s="80"/>
+      <c r="I45" s="80"/>
+      <c r="J45" s="80"/>
+      <c r="K45" s="80"/>
+      <c r="L45" s="80"/>
     </row>
     <row r="46" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="33">
@@ -11826,15 +11826,15 @@
         <v>135</v>
       </c>
       <c r="C46" s="34"/>
-      <c r="D46" s="138"/>
-      <c r="E46" s="139"/>
-      <c r="F46" s="139"/>
-      <c r="G46" s="139"/>
-      <c r="H46" s="139"/>
-      <c r="I46" s="139"/>
-      <c r="J46" s="139"/>
-      <c r="K46" s="139"/>
-      <c r="L46" s="139"/>
+      <c r="D46" s="79"/>
+      <c r="E46" s="80"/>
+      <c r="F46" s="80"/>
+      <c r="G46" s="80"/>
+      <c r="H46" s="80"/>
+      <c r="I46" s="80"/>
+      <c r="J46" s="80"/>
+      <c r="K46" s="80"/>
+      <c r="L46" s="80"/>
     </row>
     <row r="47" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="33">
@@ -11844,15 +11844,15 @@
         <v>136</v>
       </c>
       <c r="C47" s="34"/>
-      <c r="D47" s="138"/>
-      <c r="E47" s="139"/>
-      <c r="F47" s="139"/>
-      <c r="G47" s="139"/>
-      <c r="H47" s="139"/>
-      <c r="I47" s="139"/>
-      <c r="J47" s="139"/>
-      <c r="K47" s="139"/>
-      <c r="L47" s="139"/>
+      <c r="D47" s="79"/>
+      <c r="E47" s="80"/>
+      <c r="F47" s="80"/>
+      <c r="G47" s="80"/>
+      <c r="H47" s="80"/>
+      <c r="I47" s="80"/>
+      <c r="J47" s="80"/>
+      <c r="K47" s="80"/>
+      <c r="L47" s="80"/>
     </row>
     <row r="48" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="33">
@@ -11862,15 +11862,15 @@
         <v>137</v>
       </c>
       <c r="C48" s="34"/>
-      <c r="D48" s="138"/>
-      <c r="E48" s="139"/>
-      <c r="F48" s="139"/>
-      <c r="G48" s="139"/>
-      <c r="H48" s="139"/>
-      <c r="I48" s="139"/>
-      <c r="J48" s="139"/>
-      <c r="K48" s="139"/>
-      <c r="L48" s="139"/>
+      <c r="D48" s="79"/>
+      <c r="E48" s="80"/>
+      <c r="F48" s="80"/>
+      <c r="G48" s="80"/>
+      <c r="H48" s="80"/>
+      <c r="I48" s="80"/>
+      <c r="J48" s="80"/>
+      <c r="K48" s="80"/>
+      <c r="L48" s="80"/>
     </row>
     <row r="49" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="33">
@@ -11880,15 +11880,15 @@
         <v>138</v>
       </c>
       <c r="C49" s="34"/>
-      <c r="D49" s="138"/>
-      <c r="E49" s="139"/>
-      <c r="F49" s="139"/>
-      <c r="G49" s="139"/>
-      <c r="H49" s="139"/>
-      <c r="I49" s="139"/>
-      <c r="J49" s="139"/>
-      <c r="K49" s="139"/>
-      <c r="L49" s="139"/>
+      <c r="D49" s="79"/>
+      <c r="E49" s="80"/>
+      <c r="F49" s="80"/>
+      <c r="G49" s="80"/>
+      <c r="H49" s="80"/>
+      <c r="I49" s="80"/>
+      <c r="J49" s="80"/>
+      <c r="K49" s="80"/>
+      <c r="L49" s="80"/>
     </row>
     <row r="50" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="33">
@@ -11898,15 +11898,15 @@
         <v>139</v>
       </c>
       <c r="C50" s="34"/>
-      <c r="D50" s="138"/>
-      <c r="E50" s="139"/>
-      <c r="F50" s="139"/>
-      <c r="G50" s="139"/>
-      <c r="H50" s="139"/>
-      <c r="I50" s="139"/>
-      <c r="J50" s="139"/>
-      <c r="K50" s="139"/>
-      <c r="L50" s="139"/>
+      <c r="D50" s="79"/>
+      <c r="E50" s="80"/>
+      <c r="F50" s="80"/>
+      <c r="G50" s="80"/>
+      <c r="H50" s="80"/>
+      <c r="I50" s="80"/>
+      <c r="J50" s="80"/>
+      <c r="K50" s="80"/>
+      <c r="L50" s="80"/>
     </row>
     <row r="51" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="33">
@@ -11916,15 +11916,15 @@
         <v>140</v>
       </c>
       <c r="C51" s="34"/>
-      <c r="D51" s="138"/>
-      <c r="E51" s="139"/>
-      <c r="F51" s="139"/>
-      <c r="G51" s="139"/>
-      <c r="H51" s="139"/>
-      <c r="I51" s="139"/>
-      <c r="J51" s="139"/>
-      <c r="K51" s="139"/>
-      <c r="L51" s="139"/>
+      <c r="D51" s="79"/>
+      <c r="E51" s="80"/>
+      <c r="F51" s="80"/>
+      <c r="G51" s="80"/>
+      <c r="H51" s="80"/>
+      <c r="I51" s="80"/>
+      <c r="J51" s="80"/>
+      <c r="K51" s="80"/>
+      <c r="L51" s="80"/>
     </row>
     <row r="52" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="33">
@@ -11934,26 +11934,18 @@
         <v>141</v>
       </c>
       <c r="C52" s="34"/>
-      <c r="D52" s="138"/>
-      <c r="E52" s="139"/>
-      <c r="F52" s="139"/>
-      <c r="G52" s="139"/>
-      <c r="H52" s="139"/>
-      <c r="I52" s="139"/>
-      <c r="J52" s="139"/>
-      <c r="K52" s="139"/>
-      <c r="L52" s="139"/>
+      <c r="D52" s="79"/>
+      <c r="E52" s="80"/>
+      <c r="F52" s="80"/>
+      <c r="G52" s="80"/>
+      <c r="H52" s="80"/>
+      <c r="I52" s="80"/>
+      <c r="J52" s="80"/>
+      <c r="K52" s="80"/>
+      <c r="L52" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="D26:L52"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:L20"/>
-    <mergeCell ref="D25:L25"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:L22"/>
     <mergeCell ref="A16:L16"/>
     <mergeCell ref="A17:L17"/>
     <mergeCell ref="B15:L15"/>
@@ -11965,6 +11957,14 @@
     <mergeCell ref="B4:L4"/>
     <mergeCell ref="B5:L5"/>
     <mergeCell ref="B7:L7"/>
+    <mergeCell ref="D26:L52"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:L20"/>
+    <mergeCell ref="D25:L25"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:L22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D26" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -14903,50 +14903,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="149" t="s">
+      <c r="A1" s="148" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="150"/>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="151"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="150"/>
     </row>
     <row r="2" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="151" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="153"/>
-      <c r="D2" s="153"/>
-      <c r="E2" s="153"/>
-      <c r="F2" s="153"/>
-      <c r="G2" s="153"/>
-      <c r="H2" s="153"/>
-      <c r="I2" s="153"/>
-      <c r="J2" s="153"/>
-      <c r="K2" s="153"/>
-      <c r="L2" s="154"/>
+      <c r="B2" s="152"/>
+      <c r="C2" s="152"/>
+      <c r="D2" s="152"/>
+      <c r="E2" s="152"/>
+      <c r="F2" s="152"/>
+      <c r="G2" s="152"/>
+      <c r="H2" s="152"/>
+      <c r="I2" s="152"/>
+      <c r="J2" s="152"/>
+      <c r="K2" s="152"/>
+      <c r="L2" s="153"/>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="155"/>
-      <c r="B3" s="156"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="156"/>
-      <c r="F3" s="156"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="156"/>
-      <c r="K3" s="156"/>
-      <c r="L3" s="157"/>
+      <c r="A3" s="154"/>
+      <c r="B3" s="155"/>
+      <c r="C3" s="155"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="155"/>
+      <c r="F3" s="155"/>
+      <c r="G3" s="155"/>
+      <c r="H3" s="155"/>
+      <c r="I3" s="155"/>
+      <c r="J3" s="155"/>
+      <c r="K3" s="155"/>
+      <c r="L3" s="156"/>
     </row>
     <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
@@ -15036,65 +15036,65 @@
       <c r="A8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="160"/>
-      <c r="C8" s="161"/>
-      <c r="D8" s="161"/>
-      <c r="E8" s="161"/>
-      <c r="F8" s="161"/>
-      <c r="G8" s="161"/>
-      <c r="H8" s="161"/>
-      <c r="I8" s="161"/>
-      <c r="J8" s="161"/>
-      <c r="K8" s="161"/>
-      <c r="L8" s="162"/>
+      <c r="B8" s="159"/>
+      <c r="C8" s="160"/>
+      <c r="D8" s="160"/>
+      <c r="E8" s="160"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="160"/>
+      <c r="H8" s="160"/>
+      <c r="I8" s="160"/>
+      <c r="J8" s="160"/>
+      <c r="K8" s="160"/>
+      <c r="L8" s="161"/>
     </row>
     <row r="9" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="163"/>
-      <c r="C9" s="161"/>
-      <c r="D9" s="161"/>
-      <c r="E9" s="161"/>
-      <c r="F9" s="161"/>
-      <c r="G9" s="161"/>
-      <c r="H9" s="161"/>
-      <c r="I9" s="161"/>
-      <c r="J9" s="161"/>
-      <c r="K9" s="161"/>
-      <c r="L9" s="162"/>
+      <c r="B9" s="162"/>
+      <c r="C9" s="160"/>
+      <c r="D9" s="160"/>
+      <c r="E9" s="160"/>
+      <c r="F9" s="160"/>
+      <c r="G9" s="160"/>
+      <c r="H9" s="160"/>
+      <c r="I9" s="160"/>
+      <c r="J9" s="160"/>
+      <c r="K9" s="160"/>
+      <c r="L9" s="161"/>
     </row>
     <row r="10" spans="1:12" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="158" t="s">
+      <c r="A10" s="157" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="159"/>
-      <c r="C10" s="159"/>
-      <c r="D10" s="159"/>
-      <c r="E10" s="159"/>
-      <c r="F10" s="159"/>
-      <c r="G10" s="159"/>
-      <c r="H10" s="159"/>
-      <c r="I10" s="159"/>
-      <c r="J10" s="159"/>
-      <c r="K10" s="159"/>
-      <c r="L10" s="159"/>
+      <c r="B10" s="158"/>
+      <c r="C10" s="158"/>
+      <c r="D10" s="158"/>
+      <c r="E10" s="158"/>
+      <c r="F10" s="158"/>
+      <c r="G10" s="158"/>
+      <c r="H10" s="158"/>
+      <c r="I10" s="158"/>
+      <c r="J10" s="158"/>
+      <c r="K10" s="158"/>
+      <c r="L10" s="158"/>
     </row>
     <row r="11" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="140" t="s">
+      <c r="A11" s="139" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="141"/>
-      <c r="C11" s="141"/>
-      <c r="D11" s="141"/>
-      <c r="E11" s="141"/>
-      <c r="F11" s="141"/>
-      <c r="G11" s="141"/>
-      <c r="H11" s="141"/>
-      <c r="I11" s="141"/>
-      <c r="J11" s="141"/>
-      <c r="K11" s="141"/>
-      <c r="L11" s="142"/>
+      <c r="B11" s="140"/>
+      <c r="C11" s="140"/>
+      <c r="D11" s="140"/>
+      <c r="E11" s="140"/>
+      <c r="F11" s="140"/>
+      <c r="G11" s="140"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="140"/>
+      <c r="K11" s="140"/>
+      <c r="L11" s="141"/>
     </row>
     <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
@@ -15106,101 +15106,101 @@
       <c r="C12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="120" t="s">
+      <c r="D12" s="89" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="120"/>
-      <c r="F12" s="120"/>
-      <c r="G12" s="120"/>
-      <c r="H12" s="120"/>
-      <c r="I12" s="120"/>
-      <c r="J12" s="120"/>
-      <c r="K12" s="120"/>
-      <c r="L12" s="120"/>
+      <c r="E12" s="89"/>
+      <c r="F12" s="89"/>
+      <c r="G12" s="89"/>
+      <c r="H12" s="89"/>
+      <c r="I12" s="89"/>
+      <c r="J12" s="89"/>
+      <c r="K12" s="89"/>
+      <c r="L12" s="89"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="49"/>
       <c r="B13" s="50"/>
       <c r="C13" s="50"/>
-      <c r="D13" s="143"/>
-      <c r="E13" s="144"/>
-      <c r="F13" s="144"/>
-      <c r="G13" s="144"/>
-      <c r="H13" s="144"/>
-      <c r="I13" s="144"/>
-      <c r="J13" s="144"/>
-      <c r="K13" s="144"/>
-      <c r="L13" s="145"/>
+      <c r="D13" s="142"/>
+      <c r="E13" s="143"/>
+      <c r="F13" s="143"/>
+      <c r="G13" s="143"/>
+      <c r="H13" s="143"/>
+      <c r="I13" s="143"/>
+      <c r="J13" s="143"/>
+      <c r="K13" s="143"/>
+      <c r="L13" s="144"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="49"/>
       <c r="B14" s="50"/>
       <c r="C14" s="50"/>
-      <c r="D14" s="146"/>
-      <c r="E14" s="147"/>
-      <c r="F14" s="147"/>
-      <c r="G14" s="147"/>
-      <c r="H14" s="147"/>
-      <c r="I14" s="147"/>
-      <c r="J14" s="147"/>
-      <c r="K14" s="147"/>
-      <c r="L14" s="148"/>
+      <c r="D14" s="145"/>
+      <c r="E14" s="146"/>
+      <c r="F14" s="146"/>
+      <c r="G14" s="146"/>
+      <c r="H14" s="146"/>
+      <c r="I14" s="146"/>
+      <c r="J14" s="146"/>
+      <c r="K14" s="146"/>
+      <c r="L14" s="147"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="49"/>
       <c r="B15" s="50"/>
       <c r="C15" s="50"/>
-      <c r="D15" s="146"/>
-      <c r="E15" s="147"/>
-      <c r="F15" s="147"/>
-      <c r="G15" s="147"/>
-      <c r="H15" s="147"/>
-      <c r="I15" s="147"/>
-      <c r="J15" s="147"/>
-      <c r="K15" s="147"/>
-      <c r="L15" s="148"/>
+      <c r="D15" s="145"/>
+      <c r="E15" s="146"/>
+      <c r="F15" s="146"/>
+      <c r="G15" s="146"/>
+      <c r="H15" s="146"/>
+      <c r="I15" s="146"/>
+      <c r="J15" s="146"/>
+      <c r="K15" s="146"/>
+      <c r="L15" s="147"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="49"/>
       <c r="B16" s="50"/>
       <c r="C16" s="50"/>
-      <c r="D16" s="146"/>
-      <c r="E16" s="147"/>
-      <c r="F16" s="147"/>
-      <c r="G16" s="147"/>
-      <c r="H16" s="147"/>
-      <c r="I16" s="147"/>
-      <c r="J16" s="147"/>
-      <c r="K16" s="147"/>
-      <c r="L16" s="148"/>
+      <c r="D16" s="145"/>
+      <c r="E16" s="146"/>
+      <c r="F16" s="146"/>
+      <c r="G16" s="146"/>
+      <c r="H16" s="146"/>
+      <c r="I16" s="146"/>
+      <c r="J16" s="146"/>
+      <c r="K16" s="146"/>
+      <c r="L16" s="147"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="49"/>
       <c r="B17" s="50"/>
       <c r="C17" s="50"/>
-      <c r="D17" s="146"/>
-      <c r="E17" s="147"/>
-      <c r="F17" s="147"/>
-      <c r="G17" s="147"/>
-      <c r="H17" s="147"/>
-      <c r="I17" s="147"/>
-      <c r="J17" s="147"/>
-      <c r="K17" s="147"/>
-      <c r="L17" s="148"/>
+      <c r="D17" s="145"/>
+      <c r="E17" s="146"/>
+      <c r="F17" s="146"/>
+      <c r="G17" s="146"/>
+      <c r="H17" s="146"/>
+      <c r="I17" s="146"/>
+      <c r="J17" s="146"/>
+      <c r="K17" s="146"/>
+      <c r="L17" s="147"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="49"/>
       <c r="B18" s="50"/>
       <c r="C18" s="50"/>
-      <c r="D18" s="146"/>
-      <c r="E18" s="147"/>
-      <c r="F18" s="147"/>
-      <c r="G18" s="147"/>
-      <c r="H18" s="147"/>
-      <c r="I18" s="147"/>
-      <c r="J18" s="147"/>
-      <c r="K18" s="147"/>
-      <c r="L18" s="148"/>
+      <c r="D18" s="145"/>
+      <c r="E18" s="146"/>
+      <c r="F18" s="146"/>
+      <c r="G18" s="146"/>
+      <c r="H18" s="146"/>
+      <c r="I18" s="146"/>
+      <c r="J18" s="146"/>
+      <c r="K18" s="146"/>
+      <c r="L18" s="147"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -15289,10 +15289,10 @@
       <c r="B4" s="63"/>
     </row>
     <row r="6" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="A6" s="77" t="s">
+      <c r="A6" s="163" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="77"/>
+      <c r="B6" s="163"/>
     </row>
     <row r="8" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="66" t="s">
@@ -16024,6 +16024,68 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50">
+      <UserInfo>
+        <DisplayName>Luis Campos / Logiztik Alliance</DisplayName>
+        <AccountId>265</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Jairo Gonzalez / Logiztik Alliance</DisplayName>
+        <AccountId>322</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>José Ganchozo / Logiztik Alliance</DisplayName>
+        <AccountId>304</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Edwin Casa / Logiztik Alliance</DisplayName>
+        <AccountId>299</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Cristhian Cuichan / Logiztik Alliance</DisplayName>
+        <AccountId>369</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Oscar Yunda /  Logiztik Alliance</DisplayName>
+        <AccountId>355</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Fernando Ordoñez / Logiztik Alliance</DisplayName>
+        <AccountId>321</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Alex Rivera / Logiztik Alliance</DisplayName>
+        <AccountId>370</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <TaxCatchAll xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="87481c51-c14c-4071-bf64-faa2b5708bb6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101005DA7AC6E4F4FAE42B9D9FCD9C82CAAE1" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="553e0bb76796fbad2df2b84fb95dc83d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="87481c51-c14c-4071-bf64-faa2b5708bb6" xmlns:ns3="8029d101-3d2a-47c4-b15f-619642bf5e50" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d87cd7f238c73dc12c577d08dde48736" ns2:_="" ns3:_="">
     <xsd:import namespace="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
@@ -16272,69 +16334,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD069904-634F-48DA-AA92-BAE250498BEE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8029d101-3d2a-47c4-b15f-619642bf5e50"/>
+    <ds:schemaRef ds:uri="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50">
-      <UserInfo>
-        <DisplayName>Luis Campos / Logiztik Alliance</DisplayName>
-        <AccountId>265</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Jairo Gonzalez / Logiztik Alliance</DisplayName>
-        <AccountId>322</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>José Ganchozo / Logiztik Alliance</DisplayName>
-        <AccountId>304</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Edwin Casa / Logiztik Alliance</DisplayName>
-        <AccountId>299</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Cristhian Cuichan / Logiztik Alliance</DisplayName>
-        <AccountId>369</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Oscar Yunda /  Logiztik Alliance</DisplayName>
-        <AccountId>355</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Fernando Ordoñez / Logiztik Alliance</DisplayName>
-        <AccountId>321</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Alex Rivera / Logiztik Alliance</DisplayName>
-        <AccountId>370</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <TaxCatchAll xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="87481c51-c14c-4071-bf64-faa2b5708bb6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371D8832-41B3-447B-B13D-2663C267E34F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F7F06D0-41B3-4EAF-B418-88FC726117CC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -16351,23 +16370,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371D8832-41B3-447B-B13D-2663C267E34F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD069904-634F-48DA-AA92-BAE250498BEE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8029d101-3d2a-47c4-b15f-619642bf5e50"/>
-    <ds:schemaRef ds:uri="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Guias Produccion/HU-57723.xlsx
+++ b/Guias Produccion/HU-57723.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Alliance\ScriptsEntidades\Guias Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C889C6-25A4-4CC6-9B29-D945391F7B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4F5F127-0288-4B5A-BA05-528C60EE176C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -519,9 +519,6 @@
     <t>03-f_SearchEntities.sql</t>
   </si>
   <si>
-    <t>04-pro_General_GenerateBulkInt.sql</t>
-  </si>
-  <si>
     <t>05-AC_pro_GetMachineShipments.sql</t>
   </si>
   <si>
@@ -543,9 +540,6 @@
     <t>11-AC_pro_GetLocalOrdersByEmployee.sql</t>
   </si>
   <si>
-    <t>12-AC_pro_ManageGuiasHoseDetallesEditedOrder.sql</t>
-  </si>
-  <si>
     <t>13-AC_pro_ListCarrierProgramming.sql</t>
   </si>
   <si>
@@ -556,12 +550,6 @@
   </si>
   <si>
     <t>16-AC_pro_ShippingDocumentsPODClient360.sql</t>
-  </si>
-  <si>
-    <t>17-AC_pro_module_edi_detail.sql</t>
-  </si>
-  <si>
-    <t>18-AC_pro_module_edi.sql</t>
   </si>
   <si>
     <t>19-AC_pro_ListPiecesInventory.sql</t>
@@ -579,9 +567,6 @@
     <t>23-AC_pro_GetShipmentAnalyticsReports.sql</t>
   </si>
   <si>
-    <t>24-AC_pro_GetListOFCycleCounts.sql</t>
-  </si>
-  <si>
     <t>25-AC_pro_GetCycleCountDiscrepancies.sql</t>
   </si>
   <si>
@@ -592,6 +577,21 @@
   </si>
   <si>
     <t>Es necesario que se ejecuten primero los scripts de la Hu 55188, ya que existe dependencia de algunos campos</t>
+  </si>
+  <si>
+    <t>04-AC_pro_General_GenerateBulkInt.sql</t>
+  </si>
+  <si>
+    <t>12-AC_pro_ManageGuiasHouseDetallesEditedOrder.sql</t>
+  </si>
+  <si>
+    <t>17-AC_pro_ModuleEdiDetail.sql</t>
+  </si>
+  <si>
+    <t>18-AC_pro_Module_Edi.sql</t>
+  </si>
+  <si>
+    <t>24-AC_pro_GetListOfCycleCounts.sql</t>
   </si>
 </sst>
 </file>
@@ -1914,90 +1914,6 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="54" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2099,6 +2015,90 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="54" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2270,7 +2270,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp110.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$25" noThreeD="1" sel="9" val="7"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$25" noThreeD="1" sel="8" val="7"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp111.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11021,42 +11021,42 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:15" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="121" t="s">
+      <c r="A3" s="93" t="s">
         <v>103</v>
       </c>
-      <c r="B3" s="122"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="122"/>
-      <c r="E3" s="122"/>
-      <c r="F3" s="122"/>
-      <c r="G3" s="122"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="122"/>
-      <c r="K3" s="122"/>
-      <c r="L3" s="123"/>
-      <c r="N3" s="115" t="s">
+      <c r="B3" s="94"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="94"/>
+      <c r="I3" s="94"/>
+      <c r="J3" s="94"/>
+      <c r="K3" s="94"/>
+      <c r="L3" s="95"/>
+      <c r="N3" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="O3" s="116"/>
+      <c r="O3" s="88"/>
     </row>
     <row r="4" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="128" t="s">
+      <c r="B4" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="129"/>
-      <c r="D4" s="129"/>
-      <c r="E4" s="129"/>
-      <c r="F4" s="129"/>
-      <c r="G4" s="129"/>
-      <c r="H4" s="129"/>
-      <c r="I4" s="129"/>
-      <c r="J4" s="130"/>
-      <c r="K4" s="130"/>
-      <c r="L4" s="131"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="102"/>
+      <c r="K4" s="102"/>
+      <c r="L4" s="103"/>
       <c r="N4" s="21" t="s">
         <v>2</v>
       </c>
@@ -11066,19 +11066,19 @@
       <c r="A5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="132" t="s">
+      <c r="B5" s="104" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="132"/>
-      <c r="D5" s="132"/>
-      <c r="E5" s="132"/>
-      <c r="F5" s="132"/>
-      <c r="G5" s="132"/>
-      <c r="H5" s="132"/>
-      <c r="I5" s="132"/>
-      <c r="J5" s="133"/>
-      <c r="K5" s="133"/>
-      <c r="L5" s="134"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="104"/>
+      <c r="F5" s="104"/>
+      <c r="G5" s="104"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="105"/>
+      <c r="K5" s="105"/>
+      <c r="L5" s="106"/>
       <c r="N5" s="15" t="s">
         <v>4</v>
       </c>
@@ -11088,19 +11088,19 @@
       <c r="A6" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="118">
+      <c r="B6" s="90">
         <v>46073</v>
       </c>
-      <c r="C6" s="119"/>
-      <c r="D6" s="119"/>
-      <c r="E6" s="119"/>
-      <c r="F6" s="119"/>
-      <c r="G6" s="119"/>
-      <c r="H6" s="119"/>
-      <c r="I6" s="119"/>
-      <c r="J6" s="119"/>
-      <c r="K6" s="119"/>
-      <c r="L6" s="120"/>
+      <c r="C6" s="91"/>
+      <c r="D6" s="91"/>
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
+      <c r="J6" s="91"/>
+      <c r="K6" s="91"/>
+      <c r="L6" s="92"/>
       <c r="N6" s="14"/>
       <c r="O6" s="14"/>
     </row>
@@ -11108,17 +11108,17 @@
       <c r="A7" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="135"/>
-      <c r="C7" s="136"/>
-      <c r="D7" s="136"/>
-      <c r="E7" s="136"/>
-      <c r="F7" s="136"/>
-      <c r="G7" s="136"/>
-      <c r="H7" s="136"/>
-      <c r="I7" s="136"/>
-      <c r="J7" s="137"/>
-      <c r="K7" s="137"/>
-      <c r="L7" s="138"/>
+      <c r="B7" s="107"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="108"/>
+      <c r="F7" s="108"/>
+      <c r="G7" s="108"/>
+      <c r="H7" s="108"/>
+      <c r="I7" s="108"/>
+      <c r="J7" s="109"/>
+      <c r="K7" s="109"/>
+      <c r="L7" s="110"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
@@ -11135,20 +11135,20 @@
       <c r="L8" s="13"/>
     </row>
     <row r="9" spans="1:15" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="124" t="s">
+      <c r="A9" s="96" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="125"/>
-      <c r="C9" s="125"/>
-      <c r="D9" s="125"/>
-      <c r="E9" s="125"/>
-      <c r="F9" s="125"/>
-      <c r="G9" s="125"/>
-      <c r="H9" s="125"/>
-      <c r="I9" s="125"/>
-      <c r="J9" s="126"/>
-      <c r="K9" s="126"/>
-      <c r="L9" s="127"/>
+      <c r="B9" s="97"/>
+      <c r="C9" s="97"/>
+      <c r="D9" s="97"/>
+      <c r="E9" s="97"/>
+      <c r="F9" s="97"/>
+      <c r="G9" s="97"/>
+      <c r="H9" s="97"/>
+      <c r="I9" s="97"/>
+      <c r="J9" s="98"/>
+      <c r="K9" s="98"/>
+      <c r="L9" s="99"/>
     </row>
     <row r="10" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -11248,63 +11248,63 @@
       <c r="A14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="117"/>
-      <c r="C14" s="113"/>
-      <c r="D14" s="113"/>
-      <c r="E14" s="113"/>
-      <c r="F14" s="113"/>
-      <c r="G14" s="113"/>
-      <c r="H14" s="113"/>
-      <c r="I14" s="113"/>
-      <c r="J14" s="113"/>
-      <c r="K14" s="113"/>
-      <c r="L14" s="114"/>
+      <c r="B14" s="89"/>
+      <c r="C14" s="85"/>
+      <c r="D14" s="85"/>
+      <c r="E14" s="85"/>
+      <c r="F14" s="85"/>
+      <c r="G14" s="85"/>
+      <c r="H14" s="85"/>
+      <c r="I14" s="85"/>
+      <c r="J14" s="85"/>
+      <c r="K14" s="85"/>
+      <c r="L14" s="86"/>
     </row>
     <row r="15" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="112"/>
-      <c r="C15" s="113"/>
-      <c r="D15" s="113"/>
-      <c r="E15" s="113"/>
-      <c r="F15" s="113"/>
-      <c r="G15" s="113"/>
-      <c r="H15" s="113"/>
-      <c r="I15" s="113"/>
-      <c r="J15" s="113"/>
-      <c r="K15" s="113"/>
-      <c r="L15" s="114"/>
+      <c r="B15" s="84"/>
+      <c r="C15" s="85"/>
+      <c r="D15" s="85"/>
+      <c r="E15" s="85"/>
+      <c r="F15" s="85"/>
+      <c r="G15" s="85"/>
+      <c r="H15" s="85"/>
+      <c r="I15" s="85"/>
+      <c r="J15" s="85"/>
+      <c r="K15" s="85"/>
+      <c r="L15" s="86"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="105"/>
-      <c r="B16" s="106"/>
-      <c r="C16" s="106"/>
-      <c r="D16" s="106"/>
-      <c r="E16" s="106"/>
-      <c r="F16" s="106"/>
-      <c r="G16" s="106"/>
-      <c r="H16" s="106"/>
-      <c r="I16" s="106"/>
-      <c r="J16" s="106"/>
-      <c r="K16" s="106"/>
-      <c r="L16" s="107"/>
+      <c r="A16" s="77"/>
+      <c r="B16" s="78"/>
+      <c r="C16" s="78"/>
+      <c r="D16" s="78"/>
+      <c r="E16" s="78"/>
+      <c r="F16" s="78"/>
+      <c r="G16" s="78"/>
+      <c r="H16" s="78"/>
+      <c r="I16" s="78"/>
+      <c r="J16" s="78"/>
+      <c r="K16" s="78"/>
+      <c r="L16" s="79"/>
     </row>
     <row r="17" spans="1:12" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="108" t="s">
+      <c r="A17" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="109"/>
-      <c r="C17" s="109"/>
-      <c r="D17" s="109"/>
-      <c r="E17" s="109"/>
-      <c r="F17" s="109"/>
-      <c r="G17" s="109"/>
-      <c r="H17" s="109"/>
-      <c r="I17" s="109"/>
-      <c r="J17" s="110"/>
-      <c r="K17" s="110"/>
-      <c r="L17" s="111"/>
+      <c r="B17" s="81"/>
+      <c r="C17" s="81"/>
+      <c r="D17" s="81"/>
+      <c r="E17" s="81"/>
+      <c r="F17" s="81"/>
+      <c r="G17" s="81"/>
+      <c r="H17" s="81"/>
+      <c r="I17" s="81"/>
+      <c r="J17" s="82"/>
+      <c r="K17" s="82"/>
+      <c r="L17" s="83"/>
     </row>
     <row r="18" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
@@ -11314,19 +11314,19 @@
       <c r="C18" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="81" t="s">
+      <c r="D18" s="115" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="83" t="s">
-        <v>142</v>
-      </c>
-      <c r="F18" s="83"/>
-      <c r="G18" s="83"/>
-      <c r="H18" s="83"/>
-      <c r="I18" s="83"/>
-      <c r="J18" s="84"/>
-      <c r="K18" s="84"/>
-      <c r="L18" s="85"/>
+      <c r="E18" s="117" t="s">
+        <v>137</v>
+      </c>
+      <c r="F18" s="117"/>
+      <c r="G18" s="117"/>
+      <c r="H18" s="117"/>
+      <c r="I18" s="117"/>
+      <c r="J18" s="118"/>
+      <c r="K18" s="118"/>
+      <c r="L18" s="119"/>
     </row>
     <row r="19" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
@@ -11336,15 +11336,15 @@
         <v>30</v>
       </c>
       <c r="C19" s="44"/>
-      <c r="D19" s="82"/>
-      <c r="E19" s="86"/>
-      <c r="F19" s="86"/>
-      <c r="G19" s="86"/>
-      <c r="H19" s="86"/>
-      <c r="I19" s="86"/>
-      <c r="J19" s="87"/>
-      <c r="K19" s="87"/>
-      <c r="L19" s="88"/>
+      <c r="D19" s="116"/>
+      <c r="E19" s="120"/>
+      <c r="F19" s="120"/>
+      <c r="G19" s="120"/>
+      <c r="H19" s="120"/>
+      <c r="I19" s="120"/>
+      <c r="J19" s="121"/>
+      <c r="K19" s="121"/>
+      <c r="L19" s="122"/>
     </row>
     <row r="20" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
@@ -11354,15 +11354,15 @@
       <c r="C20" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="82"/>
-      <c r="E20" s="86"/>
-      <c r="F20" s="86"/>
-      <c r="G20" s="86"/>
-      <c r="H20" s="86"/>
-      <c r="I20" s="86"/>
-      <c r="J20" s="87"/>
-      <c r="K20" s="87"/>
-      <c r="L20" s="88"/>
+      <c r="D20" s="116"/>
+      <c r="E20" s="120"/>
+      <c r="F20" s="120"/>
+      <c r="G20" s="120"/>
+      <c r="H20" s="120"/>
+      <c r="I20" s="120"/>
+      <c r="J20" s="121"/>
+      <c r="K20" s="121"/>
+      <c r="L20" s="122"/>
     </row>
     <row r="21" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
@@ -11372,19 +11372,19 @@
       <c r="C21" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="97" t="s">
+      <c r="D21" s="131" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="99" t="s">
+      <c r="E21" s="133" t="s">
         <v>107</v>
       </c>
-      <c r="F21" s="100"/>
-      <c r="G21" s="100"/>
-      <c r="H21" s="100"/>
-      <c r="I21" s="100"/>
-      <c r="J21" s="100"/>
-      <c r="K21" s="100"/>
-      <c r="L21" s="101"/>
+      <c r="F21" s="134"/>
+      <c r="G21" s="134"/>
+      <c r="H21" s="134"/>
+      <c r="I21" s="134"/>
+      <c r="J21" s="134"/>
+      <c r="K21" s="134"/>
+      <c r="L21" s="135"/>
     </row>
     <row r="22" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
@@ -11394,45 +11394,45 @@
       <c r="C22" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="98"/>
-      <c r="E22" s="102"/>
-      <c r="F22" s="103"/>
-      <c r="G22" s="103"/>
-      <c r="H22" s="103"/>
-      <c r="I22" s="103"/>
-      <c r="J22" s="103"/>
-      <c r="K22" s="103"/>
-      <c r="L22" s="104"/>
+      <c r="D22" s="132"/>
+      <c r="E22" s="136"/>
+      <c r="F22" s="137"/>
+      <c r="G22" s="137"/>
+      <c r="H22" s="137"/>
+      <c r="I22" s="137"/>
+      <c r="J22" s="137"/>
+      <c r="K22" s="137"/>
+      <c r="L22" s="138"/>
     </row>
     <row r="23" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="90"/>
-      <c r="B23" s="91"/>
-      <c r="C23" s="91"/>
-      <c r="D23" s="92"/>
-      <c r="E23" s="92"/>
-      <c r="F23" s="92"/>
-      <c r="G23" s="92"/>
-      <c r="H23" s="92"/>
-      <c r="I23" s="92"/>
-      <c r="J23" s="92"/>
-      <c r="K23" s="92"/>
-      <c r="L23" s="93"/>
+      <c r="A23" s="124"/>
+      <c r="B23" s="125"/>
+      <c r="C23" s="125"/>
+      <c r="D23" s="126"/>
+      <c r="E23" s="126"/>
+      <c r="F23" s="126"/>
+      <c r="G23" s="126"/>
+      <c r="H23" s="126"/>
+      <c r="I23" s="126"/>
+      <c r="J23" s="126"/>
+      <c r="K23" s="126"/>
+      <c r="L23" s="127"/>
     </row>
     <row r="24" spans="1:12" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="94" t="s">
+      <c r="A24" s="128" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="95"/>
-      <c r="C24" s="95"/>
-      <c r="D24" s="95"/>
-      <c r="E24" s="95"/>
-      <c r="F24" s="95"/>
-      <c r="G24" s="95"/>
-      <c r="H24" s="95"/>
-      <c r="I24" s="95"/>
-      <c r="J24" s="95"/>
-      <c r="K24" s="95"/>
-      <c r="L24" s="96"/>
+      <c r="B24" s="129"/>
+      <c r="C24" s="129"/>
+      <c r="D24" s="129"/>
+      <c r="E24" s="129"/>
+      <c r="F24" s="129"/>
+      <c r="G24" s="129"/>
+      <c r="H24" s="129"/>
+      <c r="I24" s="129"/>
+      <c r="J24" s="129"/>
+      <c r="K24" s="129"/>
+      <c r="L24" s="130"/>
     </row>
     <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
@@ -11444,17 +11444,17 @@
       <c r="C25" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="89" t="s">
+      <c r="D25" s="123" t="s">
         <v>38</v>
       </c>
-      <c r="E25" s="89"/>
-      <c r="F25" s="89"/>
-      <c r="G25" s="89"/>
-      <c r="H25" s="89"/>
-      <c r="I25" s="89"/>
-      <c r="J25" s="89"/>
-      <c r="K25" s="89"/>
-      <c r="L25" s="89"/>
+      <c r="E25" s="123"/>
+      <c r="F25" s="123"/>
+      <c r="G25" s="123"/>
+      <c r="H25" s="123"/>
+      <c r="I25" s="123"/>
+      <c r="J25" s="123"/>
+      <c r="K25" s="123"/>
+      <c r="L25" s="123"/>
     </row>
     <row r="26" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="33">
@@ -11464,17 +11464,17 @@
         <v>115</v>
       </c>
       <c r="C26" s="34"/>
-      <c r="D26" s="77" t="s">
+      <c r="D26" s="111" t="s">
         <v>108</v>
       </c>
-      <c r="E26" s="78"/>
-      <c r="F26" s="78"/>
-      <c r="G26" s="78"/>
-      <c r="H26" s="78"/>
-      <c r="I26" s="78"/>
-      <c r="J26" s="78"/>
-      <c r="K26" s="78"/>
-      <c r="L26" s="78"/>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="112"/>
+      <c r="H26" s="112"/>
+      <c r="I26" s="112"/>
+      <c r="J26" s="112"/>
+      <c r="K26" s="112"/>
+      <c r="L26" s="112"/>
     </row>
     <row r="27" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
@@ -11484,15 +11484,15 @@
         <v>116</v>
       </c>
       <c r="C27" s="34"/>
-      <c r="D27" s="79"/>
-      <c r="E27" s="80"/>
-      <c r="F27" s="80"/>
-      <c r="G27" s="80"/>
-      <c r="H27" s="80"/>
-      <c r="I27" s="80"/>
-      <c r="J27" s="80"/>
-      <c r="K27" s="80"/>
-      <c r="L27" s="80"/>
+      <c r="D27" s="113"/>
+      <c r="E27" s="114"/>
+      <c r="F27" s="114"/>
+      <c r="G27" s="114"/>
+      <c r="H27" s="114"/>
+      <c r="I27" s="114"/>
+      <c r="J27" s="114"/>
+      <c r="K27" s="114"/>
+      <c r="L27" s="114"/>
     </row>
     <row r="28" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="33">
@@ -11502,450 +11502,458 @@
         <v>117</v>
       </c>
       <c r="C28" s="34"/>
-      <c r="D28" s="79"/>
-      <c r="E28" s="80"/>
-      <c r="F28" s="80"/>
-      <c r="G28" s="80"/>
-      <c r="H28" s="80"/>
-      <c r="I28" s="80"/>
-      <c r="J28" s="80"/>
-      <c r="K28" s="80"/>
-      <c r="L28" s="80"/>
+      <c r="D28" s="113"/>
+      <c r="E28" s="114"/>
+      <c r="F28" s="114"/>
+      <c r="G28" s="114"/>
+      <c r="H28" s="114"/>
+      <c r="I28" s="114"/>
+      <c r="J28" s="114"/>
+      <c r="K28" s="114"/>
+      <c r="L28" s="114"/>
     </row>
     <row r="29" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
         <v>4</v>
       </c>
       <c r="B29" s="34" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="C29" s="34"/>
-      <c r="D29" s="79"/>
-      <c r="E29" s="80"/>
-      <c r="F29" s="80"/>
-      <c r="G29" s="80"/>
-      <c r="H29" s="80"/>
-      <c r="I29" s="80"/>
-      <c r="J29" s="80"/>
-      <c r="K29" s="80"/>
-      <c r="L29" s="80"/>
+      <c r="D29" s="113"/>
+      <c r="E29" s="114"/>
+      <c r="F29" s="114"/>
+      <c r="G29" s="114"/>
+      <c r="H29" s="114"/>
+      <c r="I29" s="114"/>
+      <c r="J29" s="114"/>
+      <c r="K29" s="114"/>
+      <c r="L29" s="114"/>
     </row>
     <row r="30" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="33">
         <v>5</v>
       </c>
       <c r="B30" s="34" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C30" s="34"/>
-      <c r="D30" s="79"/>
-      <c r="E30" s="80"/>
-      <c r="F30" s="80"/>
-      <c r="G30" s="80"/>
-      <c r="H30" s="80"/>
-      <c r="I30" s="80"/>
-      <c r="J30" s="80"/>
-      <c r="K30" s="80"/>
-      <c r="L30" s="80"/>
+      <c r="D30" s="113"/>
+      <c r="E30" s="114"/>
+      <c r="F30" s="114"/>
+      <c r="G30" s="114"/>
+      <c r="H30" s="114"/>
+      <c r="I30" s="114"/>
+      <c r="J30" s="114"/>
+      <c r="K30" s="114"/>
+      <c r="L30" s="114"/>
     </row>
     <row r="31" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="33">
         <v>6</v>
       </c>
       <c r="B31" s="34" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C31" s="34"/>
-      <c r="D31" s="79"/>
-      <c r="E31" s="80"/>
-      <c r="F31" s="80"/>
-      <c r="G31" s="80"/>
-      <c r="H31" s="80"/>
-      <c r="I31" s="80"/>
-      <c r="J31" s="80"/>
-      <c r="K31" s="80"/>
-      <c r="L31" s="80"/>
+      <c r="D31" s="113"/>
+      <c r="E31" s="114"/>
+      <c r="F31" s="114"/>
+      <c r="G31" s="114"/>
+      <c r="H31" s="114"/>
+      <c r="I31" s="114"/>
+      <c r="J31" s="114"/>
+      <c r="K31" s="114"/>
+      <c r="L31" s="114"/>
     </row>
     <row r="32" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="33">
         <v>7</v>
       </c>
       <c r="B32" s="34" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C32" s="34"/>
-      <c r="D32" s="79"/>
-      <c r="E32" s="80"/>
-      <c r="F32" s="80"/>
-      <c r="G32" s="80"/>
-      <c r="H32" s="80"/>
-      <c r="I32" s="80"/>
-      <c r="J32" s="80"/>
-      <c r="K32" s="80"/>
-      <c r="L32" s="80"/>
+      <c r="D32" s="113"/>
+      <c r="E32" s="114"/>
+      <c r="F32" s="114"/>
+      <c r="G32" s="114"/>
+      <c r="H32" s="114"/>
+      <c r="I32" s="114"/>
+      <c r="J32" s="114"/>
+      <c r="K32" s="114"/>
+      <c r="L32" s="114"/>
     </row>
     <row r="33" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="33">
         <v>8</v>
       </c>
       <c r="B33" s="34" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C33" s="34"/>
-      <c r="D33" s="79"/>
-      <c r="E33" s="80"/>
-      <c r="F33" s="80"/>
-      <c r="G33" s="80"/>
-      <c r="H33" s="80"/>
-      <c r="I33" s="80"/>
-      <c r="J33" s="80"/>
-      <c r="K33" s="80"/>
-      <c r="L33" s="80"/>
+      <c r="D33" s="113"/>
+      <c r="E33" s="114"/>
+      <c r="F33" s="114"/>
+      <c r="G33" s="114"/>
+      <c r="H33" s="114"/>
+      <c r="I33" s="114"/>
+      <c r="J33" s="114"/>
+      <c r="K33" s="114"/>
+      <c r="L33" s="114"/>
     </row>
     <row r="34" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="33">
         <v>9</v>
       </c>
       <c r="B34" s="34" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C34" s="34"/>
-      <c r="D34" s="79"/>
-      <c r="E34" s="80"/>
-      <c r="F34" s="80"/>
-      <c r="G34" s="80"/>
-      <c r="H34" s="80"/>
-      <c r="I34" s="80"/>
-      <c r="J34" s="80"/>
-      <c r="K34" s="80"/>
-      <c r="L34" s="80"/>
+      <c r="D34" s="113"/>
+      <c r="E34" s="114"/>
+      <c r="F34" s="114"/>
+      <c r="G34" s="114"/>
+      <c r="H34" s="114"/>
+      <c r="I34" s="114"/>
+      <c r="J34" s="114"/>
+      <c r="K34" s="114"/>
+      <c r="L34" s="114"/>
     </row>
     <row r="35" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="33">
         <v>10</v>
       </c>
       <c r="B35" s="34" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C35" s="34"/>
-      <c r="D35" s="79"/>
-      <c r="E35" s="80"/>
-      <c r="F35" s="80"/>
-      <c r="G35" s="80"/>
-      <c r="H35" s="80"/>
-      <c r="I35" s="80"/>
-      <c r="J35" s="80"/>
-      <c r="K35" s="80"/>
-      <c r="L35" s="80"/>
+      <c r="D35" s="113"/>
+      <c r="E35" s="114"/>
+      <c r="F35" s="114"/>
+      <c r="G35" s="114"/>
+      <c r="H35" s="114"/>
+      <c r="I35" s="114"/>
+      <c r="J35" s="114"/>
+      <c r="K35" s="114"/>
+      <c r="L35" s="114"/>
     </row>
     <row r="36" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="33">
         <v>11</v>
       </c>
       <c r="B36" s="34" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C36" s="34"/>
-      <c r="D36" s="79"/>
-      <c r="E36" s="80"/>
-      <c r="F36" s="80"/>
-      <c r="G36" s="80"/>
-      <c r="H36" s="80"/>
-      <c r="I36" s="80"/>
-      <c r="J36" s="80"/>
-      <c r="K36" s="80"/>
-      <c r="L36" s="80"/>
+      <c r="D36" s="113"/>
+      <c r="E36" s="114"/>
+      <c r="F36" s="114"/>
+      <c r="G36" s="114"/>
+      <c r="H36" s="114"/>
+      <c r="I36" s="114"/>
+      <c r="J36" s="114"/>
+      <c r="K36" s="114"/>
+      <c r="L36" s="114"/>
     </row>
     <row r="37" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="33">
         <v>12</v>
       </c>
       <c r="B37" s="34" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="C37" s="34"/>
-      <c r="D37" s="79"/>
-      <c r="E37" s="80"/>
-      <c r="F37" s="80"/>
-      <c r="G37" s="80"/>
-      <c r="H37" s="80"/>
-      <c r="I37" s="80"/>
-      <c r="J37" s="80"/>
-      <c r="K37" s="80"/>
-      <c r="L37" s="80"/>
+      <c r="D37" s="113"/>
+      <c r="E37" s="114"/>
+      <c r="F37" s="114"/>
+      <c r="G37" s="114"/>
+      <c r="H37" s="114"/>
+      <c r="I37" s="114"/>
+      <c r="J37" s="114"/>
+      <c r="K37" s="114"/>
+      <c r="L37" s="114"/>
     </row>
     <row r="38" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="33">
         <v>13</v>
       </c>
       <c r="B38" s="34" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C38" s="34"/>
-      <c r="D38" s="79"/>
-      <c r="E38" s="80"/>
-      <c r="F38" s="80"/>
-      <c r="G38" s="80"/>
-      <c r="H38" s="80"/>
-      <c r="I38" s="80"/>
-      <c r="J38" s="80"/>
-      <c r="K38" s="80"/>
-      <c r="L38" s="80"/>
+      <c r="D38" s="113"/>
+      <c r="E38" s="114"/>
+      <c r="F38" s="114"/>
+      <c r="G38" s="114"/>
+      <c r="H38" s="114"/>
+      <c r="I38" s="114"/>
+      <c r="J38" s="114"/>
+      <c r="K38" s="114"/>
+      <c r="L38" s="114"/>
     </row>
     <row r="39" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="33">
         <v>14</v>
       </c>
       <c r="B39" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C39" s="34"/>
-      <c r="D39" s="79"/>
-      <c r="E39" s="80"/>
-      <c r="F39" s="80"/>
-      <c r="G39" s="80"/>
-      <c r="H39" s="80"/>
-      <c r="I39" s="80"/>
-      <c r="J39" s="80"/>
-      <c r="K39" s="80"/>
-      <c r="L39" s="80"/>
+      <c r="D39" s="113"/>
+      <c r="E39" s="114"/>
+      <c r="F39" s="114"/>
+      <c r="G39" s="114"/>
+      <c r="H39" s="114"/>
+      <c r="I39" s="114"/>
+      <c r="J39" s="114"/>
+      <c r="K39" s="114"/>
+      <c r="L39" s="114"/>
     </row>
     <row r="40" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="33">
         <v>15</v>
       </c>
       <c r="B40" s="34" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C40" s="34"/>
-      <c r="D40" s="79"/>
-      <c r="E40" s="80"/>
-      <c r="F40" s="80"/>
-      <c r="G40" s="80"/>
-      <c r="H40" s="80"/>
-      <c r="I40" s="80"/>
-      <c r="J40" s="80"/>
-      <c r="K40" s="80"/>
-      <c r="L40" s="80"/>
+      <c r="D40" s="113"/>
+      <c r="E40" s="114"/>
+      <c r="F40" s="114"/>
+      <c r="G40" s="114"/>
+      <c r="H40" s="114"/>
+      <c r="I40" s="114"/>
+      <c r="J40" s="114"/>
+      <c r="K40" s="114"/>
+      <c r="L40" s="114"/>
     </row>
     <row r="41" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="33">
         <v>16</v>
       </c>
       <c r="B41" s="34" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C41" s="34"/>
-      <c r="D41" s="79"/>
-      <c r="E41" s="80"/>
-      <c r="F41" s="80"/>
-      <c r="G41" s="80"/>
-      <c r="H41" s="80"/>
-      <c r="I41" s="80"/>
-      <c r="J41" s="80"/>
-      <c r="K41" s="80"/>
-      <c r="L41" s="80"/>
+      <c r="D41" s="113"/>
+      <c r="E41" s="114"/>
+      <c r="F41" s="114"/>
+      <c r="G41" s="114"/>
+      <c r="H41" s="114"/>
+      <c r="I41" s="114"/>
+      <c r="J41" s="114"/>
+      <c r="K41" s="114"/>
+      <c r="L41" s="114"/>
     </row>
     <row r="42" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="33">
         <v>17</v>
       </c>
       <c r="B42" s="34" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C42" s="34"/>
-      <c r="D42" s="79"/>
-      <c r="E42" s="80"/>
-      <c r="F42" s="80"/>
-      <c r="G42" s="80"/>
-      <c r="H42" s="80"/>
-      <c r="I42" s="80"/>
-      <c r="J42" s="80"/>
-      <c r="K42" s="80"/>
-      <c r="L42" s="80"/>
+      <c r="D42" s="113"/>
+      <c r="E42" s="114"/>
+      <c r="F42" s="114"/>
+      <c r="G42" s="114"/>
+      <c r="H42" s="114"/>
+      <c r="I42" s="114"/>
+      <c r="J42" s="114"/>
+      <c r="K42" s="114"/>
+      <c r="L42" s="114"/>
     </row>
     <row r="43" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="33">
         <v>18</v>
       </c>
       <c r="B43" s="34" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="C43" s="34"/>
-      <c r="D43" s="79"/>
-      <c r="E43" s="80"/>
-      <c r="F43" s="80"/>
-      <c r="G43" s="80"/>
-      <c r="H43" s="80"/>
-      <c r="I43" s="80"/>
-      <c r="J43" s="80"/>
-      <c r="K43" s="80"/>
-      <c r="L43" s="80"/>
+      <c r="D43" s="113"/>
+      <c r="E43" s="114"/>
+      <c r="F43" s="114"/>
+      <c r="G43" s="114"/>
+      <c r="H43" s="114"/>
+      <c r="I43" s="114"/>
+      <c r="J43" s="114"/>
+      <c r="K43" s="114"/>
+      <c r="L43" s="114"/>
     </row>
     <row r="44" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="33">
         <v>19</v>
       </c>
       <c r="B44" s="34" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C44" s="34"/>
-      <c r="D44" s="79"/>
-      <c r="E44" s="80"/>
-      <c r="F44" s="80"/>
-      <c r="G44" s="80"/>
-      <c r="H44" s="80"/>
-      <c r="I44" s="80"/>
-      <c r="J44" s="80"/>
-      <c r="K44" s="80"/>
-      <c r="L44" s="80"/>
+      <c r="D44" s="113"/>
+      <c r="E44" s="114"/>
+      <c r="F44" s="114"/>
+      <c r="G44" s="114"/>
+      <c r="H44" s="114"/>
+      <c r="I44" s="114"/>
+      <c r="J44" s="114"/>
+      <c r="K44" s="114"/>
+      <c r="L44" s="114"/>
     </row>
     <row r="45" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="33">
         <v>20</v>
       </c>
       <c r="B45" s="34" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C45" s="34"/>
-      <c r="D45" s="79"/>
-      <c r="E45" s="80"/>
-      <c r="F45" s="80"/>
-      <c r="G45" s="80"/>
-      <c r="H45" s="80"/>
-      <c r="I45" s="80"/>
-      <c r="J45" s="80"/>
-      <c r="K45" s="80"/>
-      <c r="L45" s="80"/>
+      <c r="D45" s="113"/>
+      <c r="E45" s="114"/>
+      <c r="F45" s="114"/>
+      <c r="G45" s="114"/>
+      <c r="H45" s="114"/>
+      <c r="I45" s="114"/>
+      <c r="J45" s="114"/>
+      <c r="K45" s="114"/>
+      <c r="L45" s="114"/>
     </row>
     <row r="46" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="33">
         <v>21</v>
       </c>
       <c r="B46" s="34" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C46" s="34"/>
-      <c r="D46" s="79"/>
-      <c r="E46" s="80"/>
-      <c r="F46" s="80"/>
-      <c r="G46" s="80"/>
-      <c r="H46" s="80"/>
-      <c r="I46" s="80"/>
-      <c r="J46" s="80"/>
-      <c r="K46" s="80"/>
-      <c r="L46" s="80"/>
+      <c r="D46" s="113"/>
+      <c r="E46" s="114"/>
+      <c r="F46" s="114"/>
+      <c r="G46" s="114"/>
+      <c r="H46" s="114"/>
+      <c r="I46" s="114"/>
+      <c r="J46" s="114"/>
+      <c r="K46" s="114"/>
+      <c r="L46" s="114"/>
     </row>
     <row r="47" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="33">
         <v>22</v>
       </c>
       <c r="B47" s="34" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C47" s="34"/>
-      <c r="D47" s="79"/>
-      <c r="E47" s="80"/>
-      <c r="F47" s="80"/>
-      <c r="G47" s="80"/>
-      <c r="H47" s="80"/>
-      <c r="I47" s="80"/>
-      <c r="J47" s="80"/>
-      <c r="K47" s="80"/>
-      <c r="L47" s="80"/>
+      <c r="D47" s="113"/>
+      <c r="E47" s="114"/>
+      <c r="F47" s="114"/>
+      <c r="G47" s="114"/>
+      <c r="H47" s="114"/>
+      <c r="I47" s="114"/>
+      <c r="J47" s="114"/>
+      <c r="K47" s="114"/>
+      <c r="L47" s="114"/>
     </row>
     <row r="48" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="33">
         <v>23</v>
       </c>
       <c r="B48" s="34" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C48" s="34"/>
-      <c r="D48" s="79"/>
-      <c r="E48" s="80"/>
-      <c r="F48" s="80"/>
-      <c r="G48" s="80"/>
-      <c r="H48" s="80"/>
-      <c r="I48" s="80"/>
-      <c r="J48" s="80"/>
-      <c r="K48" s="80"/>
-      <c r="L48" s="80"/>
+      <c r="D48" s="113"/>
+      <c r="E48" s="114"/>
+      <c r="F48" s="114"/>
+      <c r="G48" s="114"/>
+      <c r="H48" s="114"/>
+      <c r="I48" s="114"/>
+      <c r="J48" s="114"/>
+      <c r="K48" s="114"/>
+      <c r="L48" s="114"/>
     </row>
     <row r="49" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="33">
         <v>24</v>
       </c>
       <c r="B49" s="34" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C49" s="34"/>
-      <c r="D49" s="79"/>
-      <c r="E49" s="80"/>
-      <c r="F49" s="80"/>
-      <c r="G49" s="80"/>
-      <c r="H49" s="80"/>
-      <c r="I49" s="80"/>
-      <c r="J49" s="80"/>
-      <c r="K49" s="80"/>
-      <c r="L49" s="80"/>
+      <c r="D49" s="113"/>
+      <c r="E49" s="114"/>
+      <c r="F49" s="114"/>
+      <c r="G49" s="114"/>
+      <c r="H49" s="114"/>
+      <c r="I49" s="114"/>
+      <c r="J49" s="114"/>
+      <c r="K49" s="114"/>
+      <c r="L49" s="114"/>
     </row>
     <row r="50" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="33">
         <v>25</v>
       </c>
       <c r="B50" s="34" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C50" s="34"/>
-      <c r="D50" s="79"/>
-      <c r="E50" s="80"/>
-      <c r="F50" s="80"/>
-      <c r="G50" s="80"/>
-      <c r="H50" s="80"/>
-      <c r="I50" s="80"/>
-      <c r="J50" s="80"/>
-      <c r="K50" s="80"/>
-      <c r="L50" s="80"/>
+      <c r="D50" s="113"/>
+      <c r="E50" s="114"/>
+      <c r="F50" s="114"/>
+      <c r="G50" s="114"/>
+      <c r="H50" s="114"/>
+      <c r="I50" s="114"/>
+      <c r="J50" s="114"/>
+      <c r="K50" s="114"/>
+      <c r="L50" s="114"/>
     </row>
     <row r="51" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="33">
         <v>26</v>
       </c>
       <c r="B51" s="34" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C51" s="34"/>
-      <c r="D51" s="79"/>
-      <c r="E51" s="80"/>
-      <c r="F51" s="80"/>
-      <c r="G51" s="80"/>
-      <c r="H51" s="80"/>
-      <c r="I51" s="80"/>
-      <c r="J51" s="80"/>
-      <c r="K51" s="80"/>
-      <c r="L51" s="80"/>
+      <c r="D51" s="113"/>
+      <c r="E51" s="114"/>
+      <c r="F51" s="114"/>
+      <c r="G51" s="114"/>
+      <c r="H51" s="114"/>
+      <c r="I51" s="114"/>
+      <c r="J51" s="114"/>
+      <c r="K51" s="114"/>
+      <c r="L51" s="114"/>
     </row>
     <row r="52" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="33">
         <v>27</v>
       </c>
       <c r="B52" s="34" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C52" s="34"/>
-      <c r="D52" s="79"/>
-      <c r="E52" s="80"/>
-      <c r="F52" s="80"/>
-      <c r="G52" s="80"/>
-      <c r="H52" s="80"/>
-      <c r="I52" s="80"/>
-      <c r="J52" s="80"/>
-      <c r="K52" s="80"/>
-      <c r="L52" s="80"/>
+      <c r="D52" s="113"/>
+      <c r="E52" s="114"/>
+      <c r="F52" s="114"/>
+      <c r="G52" s="114"/>
+      <c r="H52" s="114"/>
+      <c r="I52" s="114"/>
+      <c r="J52" s="114"/>
+      <c r="K52" s="114"/>
+      <c r="L52" s="114"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="D26:L52"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:L20"/>
+    <mergeCell ref="D25:L25"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:L22"/>
     <mergeCell ref="A16:L16"/>
     <mergeCell ref="A17:L17"/>
     <mergeCell ref="B15:L15"/>
@@ -11957,14 +11965,6 @@
     <mergeCell ref="B4:L4"/>
     <mergeCell ref="B5:L5"/>
     <mergeCell ref="B7:L7"/>
-    <mergeCell ref="D26:L52"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:L20"/>
-    <mergeCell ref="D25:L25"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:L22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D26" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -15106,17 +15106,17 @@
       <c r="C12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="89" t="s">
+      <c r="D12" s="123" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="89"/>
-      <c r="F12" s="89"/>
-      <c r="G12" s="89"/>
-      <c r="H12" s="89"/>
-      <c r="I12" s="89"/>
-      <c r="J12" s="89"/>
-      <c r="K12" s="89"/>
-      <c r="L12" s="89"/>
+      <c r="E12" s="123"/>
+      <c r="F12" s="123"/>
+      <c r="G12" s="123"/>
+      <c r="H12" s="123"/>
+      <c r="I12" s="123"/>
+      <c r="J12" s="123"/>
+      <c r="K12" s="123"/>
+      <c r="L12" s="123"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="49"/>
@@ -16024,6 +16024,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <SharedWithUsers xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50">
@@ -16074,15 +16083,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16335,20 +16335,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371D8832-41B3-447B-B13D-2663C267E34F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD069904-634F-48DA-AA92-BAE250498BEE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="8029d101-3d2a-47c4-b15f-619642bf5e50"/>
     <ds:schemaRef ds:uri="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371D8832-41B3-447B-B13D-2663C267E34F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Guias Produccion/HU-57723.xlsx
+++ b/Guias Produccion/HU-57723.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Alliance\ScriptsEntidades\Guias Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4F5F127-0288-4B5A-BA05-528C60EE176C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB600DDA-73EB-420C-A864-496F83D5FC9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="145">
   <si>
     <t>Guia documentación</t>
   </si>
@@ -593,6 +593,12 @@
   <si>
     <t>24-AC_pro_GetListOfCycleCounts.sql</t>
   </si>
+  <si>
+    <t>28-AC_pro_GetAccountingAnalyticsReports.sql</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29-AC_pro_GetSalesOrdes </t>
+  </si>
 </sst>
 </file>
 
@@ -811,7 +817,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="75">
+  <borders count="80">
     <border>
       <left/>
       <right/>
@@ -1759,12 +1765,69 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="177">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2016,18 +2079,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="54" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2099,6 +2150,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="54" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2198,6 +2261,15 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="75" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="76" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="77" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="78" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="79" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2370,10 +2442,18 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp133.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$18" noThreeD="1" sel="8" val="3"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp134.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$18" noThreeD="1" sel="8" val="3"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp135.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$17" noThreeD="1" sel="17" val="9"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp134.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp136.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$17" noThreeD="1" sel="17" val="9"/>
 </file>
 
@@ -10377,6 +10457,122 @@
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D2040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>52</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>1409700</xdr:colOff>
+          <xdr:row>52</xdr:row>
+          <xdr:rowOff>220980</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1235" name="Drop Down 211" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1235"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D3040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>53</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>1409700</xdr:colOff>
+          <xdr:row>53</xdr:row>
+          <xdr:rowOff>220980</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1236" name="Drop Down 212" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1236"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D2230B8-CC77-582B-CBB5-F7A67E8158B6}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -11002,7 +11198,7 @@
   <sheetPr codeName="Hoja1">
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A3:O52"/>
+  <dimension ref="A3:O54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.44140625" bestFit="1" customWidth="1"/>
@@ -11314,19 +11510,19 @@
       <c r="C18" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="115" t="s">
+      <c r="D18" s="111" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="117" t="s">
+      <c r="E18" s="113" t="s">
         <v>137</v>
       </c>
-      <c r="F18" s="117"/>
-      <c r="G18" s="117"/>
-      <c r="H18" s="117"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="118"/>
-      <c r="K18" s="118"/>
-      <c r="L18" s="119"/>
+      <c r="F18" s="113"/>
+      <c r="G18" s="113"/>
+      <c r="H18" s="113"/>
+      <c r="I18" s="113"/>
+      <c r="J18" s="114"/>
+      <c r="K18" s="114"/>
+      <c r="L18" s="115"/>
     </row>
     <row r="19" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
@@ -11336,15 +11532,15 @@
         <v>30</v>
       </c>
       <c r="C19" s="44"/>
-      <c r="D19" s="116"/>
-      <c r="E19" s="120"/>
-      <c r="F19" s="120"/>
-      <c r="G19" s="120"/>
-      <c r="H19" s="120"/>
-      <c r="I19" s="120"/>
-      <c r="J19" s="121"/>
-      <c r="K19" s="121"/>
-      <c r="L19" s="122"/>
+      <c r="D19" s="112"/>
+      <c r="E19" s="116"/>
+      <c r="F19" s="116"/>
+      <c r="G19" s="116"/>
+      <c r="H19" s="116"/>
+      <c r="I19" s="116"/>
+      <c r="J19" s="117"/>
+      <c r="K19" s="117"/>
+      <c r="L19" s="118"/>
     </row>
     <row r="20" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
@@ -11354,15 +11550,15 @@
       <c r="C20" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="116"/>
-      <c r="E20" s="120"/>
-      <c r="F20" s="120"/>
-      <c r="G20" s="120"/>
-      <c r="H20" s="120"/>
-      <c r="I20" s="120"/>
-      <c r="J20" s="121"/>
-      <c r="K20" s="121"/>
-      <c r="L20" s="122"/>
+      <c r="D20" s="112"/>
+      <c r="E20" s="116"/>
+      <c r="F20" s="116"/>
+      <c r="G20" s="116"/>
+      <c r="H20" s="116"/>
+      <c r="I20" s="116"/>
+      <c r="J20" s="117"/>
+      <c r="K20" s="117"/>
+      <c r="L20" s="118"/>
     </row>
     <row r="21" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
@@ -11372,19 +11568,19 @@
       <c r="C21" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="131" t="s">
+      <c r="D21" s="127" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="133" t="s">
+      <c r="E21" s="129" t="s">
         <v>107</v>
       </c>
-      <c r="F21" s="134"/>
-      <c r="G21" s="134"/>
-      <c r="H21" s="134"/>
-      <c r="I21" s="134"/>
-      <c r="J21" s="134"/>
-      <c r="K21" s="134"/>
-      <c r="L21" s="135"/>
+      <c r="F21" s="130"/>
+      <c r="G21" s="130"/>
+      <c r="H21" s="130"/>
+      <c r="I21" s="130"/>
+      <c r="J21" s="130"/>
+      <c r="K21" s="130"/>
+      <c r="L21" s="131"/>
     </row>
     <row r="22" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
@@ -11394,45 +11590,45 @@
       <c r="C22" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="132"/>
-      <c r="E22" s="136"/>
-      <c r="F22" s="137"/>
-      <c r="G22" s="137"/>
-      <c r="H22" s="137"/>
-      <c r="I22" s="137"/>
-      <c r="J22" s="137"/>
-      <c r="K22" s="137"/>
-      <c r="L22" s="138"/>
+      <c r="D22" s="128"/>
+      <c r="E22" s="132"/>
+      <c r="F22" s="133"/>
+      <c r="G22" s="133"/>
+      <c r="H22" s="133"/>
+      <c r="I22" s="133"/>
+      <c r="J22" s="133"/>
+      <c r="K22" s="133"/>
+      <c r="L22" s="134"/>
     </row>
     <row r="23" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="124"/>
-      <c r="B23" s="125"/>
-      <c r="C23" s="125"/>
-      <c r="D23" s="126"/>
-      <c r="E23" s="126"/>
-      <c r="F23" s="126"/>
-      <c r="G23" s="126"/>
-      <c r="H23" s="126"/>
-      <c r="I23" s="126"/>
-      <c r="J23" s="126"/>
-      <c r="K23" s="126"/>
-      <c r="L23" s="127"/>
+      <c r="A23" s="120"/>
+      <c r="B23" s="121"/>
+      <c r="C23" s="121"/>
+      <c r="D23" s="122"/>
+      <c r="E23" s="122"/>
+      <c r="F23" s="122"/>
+      <c r="G23" s="122"/>
+      <c r="H23" s="122"/>
+      <c r="I23" s="122"/>
+      <c r="J23" s="122"/>
+      <c r="K23" s="122"/>
+      <c r="L23" s="123"/>
     </row>
     <row r="24" spans="1:12" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="128" t="s">
+      <c r="A24" s="124" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="129"/>
-      <c r="C24" s="129"/>
-      <c r="D24" s="129"/>
-      <c r="E24" s="129"/>
-      <c r="F24" s="129"/>
-      <c r="G24" s="129"/>
-      <c r="H24" s="129"/>
-      <c r="I24" s="129"/>
-      <c r="J24" s="129"/>
-      <c r="K24" s="129"/>
-      <c r="L24" s="130"/>
+      <c r="B24" s="125"/>
+      <c r="C24" s="125"/>
+      <c r="D24" s="125"/>
+      <c r="E24" s="125"/>
+      <c r="F24" s="125"/>
+      <c r="G24" s="125"/>
+      <c r="H24" s="125"/>
+      <c r="I24" s="125"/>
+      <c r="J24" s="125"/>
+      <c r="K24" s="125"/>
+      <c r="L24" s="126"/>
     </row>
     <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
@@ -11444,17 +11640,17 @@
       <c r="C25" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="123" t="s">
+      <c r="D25" s="119" t="s">
         <v>38</v>
       </c>
-      <c r="E25" s="123"/>
-      <c r="F25" s="123"/>
-      <c r="G25" s="123"/>
-      <c r="H25" s="123"/>
-      <c r="I25" s="123"/>
-      <c r="J25" s="123"/>
-      <c r="K25" s="123"/>
-      <c r="L25" s="123"/>
+      <c r="E25" s="119"/>
+      <c r="F25" s="119"/>
+      <c r="G25" s="119"/>
+      <c r="H25" s="119"/>
+      <c r="I25" s="119"/>
+      <c r="J25" s="119"/>
+      <c r="K25" s="119"/>
+      <c r="L25" s="119"/>
     </row>
     <row r="26" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="33">
@@ -11464,17 +11660,17 @@
         <v>115</v>
       </c>
       <c r="C26" s="34"/>
-      <c r="D26" s="111" t="s">
+      <c r="D26" s="135" t="s">
         <v>108</v>
       </c>
-      <c r="E26" s="112"/>
-      <c r="F26" s="112"/>
-      <c r="G26" s="112"/>
-      <c r="H26" s="112"/>
-      <c r="I26" s="112"/>
-      <c r="J26" s="112"/>
-      <c r="K26" s="112"/>
-      <c r="L26" s="112"/>
+      <c r="E26" s="136"/>
+      <c r="F26" s="136"/>
+      <c r="G26" s="136"/>
+      <c r="H26" s="136"/>
+      <c r="I26" s="136"/>
+      <c r="J26" s="136"/>
+      <c r="K26" s="136"/>
+      <c r="L26" s="136"/>
     </row>
     <row r="27" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
@@ -11484,15 +11680,15 @@
         <v>116</v>
       </c>
       <c r="C27" s="34"/>
-      <c r="D27" s="113"/>
-      <c r="E27" s="114"/>
-      <c r="F27" s="114"/>
-      <c r="G27" s="114"/>
-      <c r="H27" s="114"/>
-      <c r="I27" s="114"/>
-      <c r="J27" s="114"/>
-      <c r="K27" s="114"/>
-      <c r="L27" s="114"/>
+      <c r="D27" s="137"/>
+      <c r="E27" s="138"/>
+      <c r="F27" s="138"/>
+      <c r="G27" s="138"/>
+      <c r="H27" s="138"/>
+      <c r="I27" s="138"/>
+      <c r="J27" s="138"/>
+      <c r="K27" s="138"/>
+      <c r="L27" s="138"/>
     </row>
     <row r="28" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="33">
@@ -11502,15 +11698,15 @@
         <v>117</v>
       </c>
       <c r="C28" s="34"/>
-      <c r="D28" s="113"/>
-      <c r="E28" s="114"/>
-      <c r="F28" s="114"/>
-      <c r="G28" s="114"/>
-      <c r="H28" s="114"/>
-      <c r="I28" s="114"/>
-      <c r="J28" s="114"/>
-      <c r="K28" s="114"/>
-      <c r="L28" s="114"/>
+      <c r="D28" s="137"/>
+      <c r="E28" s="138"/>
+      <c r="F28" s="138"/>
+      <c r="G28" s="138"/>
+      <c r="H28" s="138"/>
+      <c r="I28" s="138"/>
+      <c r="J28" s="138"/>
+      <c r="K28" s="138"/>
+      <c r="L28" s="138"/>
     </row>
     <row r="29" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
@@ -11520,15 +11716,15 @@
         <v>138</v>
       </c>
       <c r="C29" s="34"/>
-      <c r="D29" s="113"/>
-      <c r="E29" s="114"/>
-      <c r="F29" s="114"/>
-      <c r="G29" s="114"/>
-      <c r="H29" s="114"/>
-      <c r="I29" s="114"/>
-      <c r="J29" s="114"/>
-      <c r="K29" s="114"/>
-      <c r="L29" s="114"/>
+      <c r="D29" s="137"/>
+      <c r="E29" s="138"/>
+      <c r="F29" s="138"/>
+      <c r="G29" s="138"/>
+      <c r="H29" s="138"/>
+      <c r="I29" s="138"/>
+      <c r="J29" s="138"/>
+      <c r="K29" s="138"/>
+      <c r="L29" s="138"/>
     </row>
     <row r="30" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="33">
@@ -11538,15 +11734,15 @@
         <v>118</v>
       </c>
       <c r="C30" s="34"/>
-      <c r="D30" s="113"/>
-      <c r="E30" s="114"/>
-      <c r="F30" s="114"/>
-      <c r="G30" s="114"/>
-      <c r="H30" s="114"/>
-      <c r="I30" s="114"/>
-      <c r="J30" s="114"/>
-      <c r="K30" s="114"/>
-      <c r="L30" s="114"/>
+      <c r="D30" s="137"/>
+      <c r="E30" s="138"/>
+      <c r="F30" s="138"/>
+      <c r="G30" s="138"/>
+      <c r="H30" s="138"/>
+      <c r="I30" s="138"/>
+      <c r="J30" s="138"/>
+      <c r="K30" s="138"/>
+      <c r="L30" s="138"/>
     </row>
     <row r="31" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="33">
@@ -11556,15 +11752,15 @@
         <v>119</v>
       </c>
       <c r="C31" s="34"/>
-      <c r="D31" s="113"/>
-      <c r="E31" s="114"/>
-      <c r="F31" s="114"/>
-      <c r="G31" s="114"/>
-      <c r="H31" s="114"/>
-      <c r="I31" s="114"/>
-      <c r="J31" s="114"/>
-      <c r="K31" s="114"/>
-      <c r="L31" s="114"/>
+      <c r="D31" s="137"/>
+      <c r="E31" s="138"/>
+      <c r="F31" s="138"/>
+      <c r="G31" s="138"/>
+      <c r="H31" s="138"/>
+      <c r="I31" s="138"/>
+      <c r="J31" s="138"/>
+      <c r="K31" s="138"/>
+      <c r="L31" s="138"/>
     </row>
     <row r="32" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="33">
@@ -11574,15 +11770,15 @@
         <v>120</v>
       </c>
       <c r="C32" s="34"/>
-      <c r="D32" s="113"/>
-      <c r="E32" s="114"/>
-      <c r="F32" s="114"/>
-      <c r="G32" s="114"/>
-      <c r="H32" s="114"/>
-      <c r="I32" s="114"/>
-      <c r="J32" s="114"/>
-      <c r="K32" s="114"/>
-      <c r="L32" s="114"/>
+      <c r="D32" s="137"/>
+      <c r="E32" s="138"/>
+      <c r="F32" s="138"/>
+      <c r="G32" s="138"/>
+      <c r="H32" s="138"/>
+      <c r="I32" s="138"/>
+      <c r="J32" s="138"/>
+      <c r="K32" s="138"/>
+      <c r="L32" s="138"/>
     </row>
     <row r="33" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="33">
@@ -11592,15 +11788,15 @@
         <v>121</v>
       </c>
       <c r="C33" s="34"/>
-      <c r="D33" s="113"/>
-      <c r="E33" s="114"/>
-      <c r="F33" s="114"/>
-      <c r="G33" s="114"/>
-      <c r="H33" s="114"/>
-      <c r="I33" s="114"/>
-      <c r="J33" s="114"/>
-      <c r="K33" s="114"/>
-      <c r="L33" s="114"/>
+      <c r="D33" s="137"/>
+      <c r="E33" s="138"/>
+      <c r="F33" s="138"/>
+      <c r="G33" s="138"/>
+      <c r="H33" s="138"/>
+      <c r="I33" s="138"/>
+      <c r="J33" s="138"/>
+      <c r="K33" s="138"/>
+      <c r="L33" s="138"/>
     </row>
     <row r="34" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="33">
@@ -11610,15 +11806,15 @@
         <v>122</v>
       </c>
       <c r="C34" s="34"/>
-      <c r="D34" s="113"/>
-      <c r="E34" s="114"/>
-      <c r="F34" s="114"/>
-      <c r="G34" s="114"/>
-      <c r="H34" s="114"/>
-      <c r="I34" s="114"/>
-      <c r="J34" s="114"/>
-      <c r="K34" s="114"/>
-      <c r="L34" s="114"/>
+      <c r="D34" s="137"/>
+      <c r="E34" s="138"/>
+      <c r="F34" s="138"/>
+      <c r="G34" s="138"/>
+      <c r="H34" s="138"/>
+      <c r="I34" s="138"/>
+      <c r="J34" s="138"/>
+      <c r="K34" s="138"/>
+      <c r="L34" s="138"/>
     </row>
     <row r="35" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="33">
@@ -11628,15 +11824,15 @@
         <v>123</v>
       </c>
       <c r="C35" s="34"/>
-      <c r="D35" s="113"/>
-      <c r="E35" s="114"/>
-      <c r="F35" s="114"/>
-      <c r="G35" s="114"/>
-      <c r="H35" s="114"/>
-      <c r="I35" s="114"/>
-      <c r="J35" s="114"/>
-      <c r="K35" s="114"/>
-      <c r="L35" s="114"/>
+      <c r="D35" s="137"/>
+      <c r="E35" s="138"/>
+      <c r="F35" s="138"/>
+      <c r="G35" s="138"/>
+      <c r="H35" s="138"/>
+      <c r="I35" s="138"/>
+      <c r="J35" s="138"/>
+      <c r="K35" s="138"/>
+      <c r="L35" s="138"/>
     </row>
     <row r="36" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="33">
@@ -11646,15 +11842,15 @@
         <v>124</v>
       </c>
       <c r="C36" s="34"/>
-      <c r="D36" s="113"/>
-      <c r="E36" s="114"/>
-      <c r="F36" s="114"/>
-      <c r="G36" s="114"/>
-      <c r="H36" s="114"/>
-      <c r="I36" s="114"/>
-      <c r="J36" s="114"/>
-      <c r="K36" s="114"/>
-      <c r="L36" s="114"/>
+      <c r="D36" s="137"/>
+      <c r="E36" s="138"/>
+      <c r="F36" s="138"/>
+      <c r="G36" s="138"/>
+      <c r="H36" s="138"/>
+      <c r="I36" s="138"/>
+      <c r="J36" s="138"/>
+      <c r="K36" s="138"/>
+      <c r="L36" s="138"/>
     </row>
     <row r="37" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="33">
@@ -11664,15 +11860,15 @@
         <v>139</v>
       </c>
       <c r="C37" s="34"/>
-      <c r="D37" s="113"/>
-      <c r="E37" s="114"/>
-      <c r="F37" s="114"/>
-      <c r="G37" s="114"/>
-      <c r="H37" s="114"/>
-      <c r="I37" s="114"/>
-      <c r="J37" s="114"/>
-      <c r="K37" s="114"/>
-      <c r="L37" s="114"/>
+      <c r="D37" s="137"/>
+      <c r="E37" s="138"/>
+      <c r="F37" s="138"/>
+      <c r="G37" s="138"/>
+      <c r="H37" s="138"/>
+      <c r="I37" s="138"/>
+      <c r="J37" s="138"/>
+      <c r="K37" s="138"/>
+      <c r="L37" s="138"/>
     </row>
     <row r="38" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="33">
@@ -11682,15 +11878,15 @@
         <v>125</v>
       </c>
       <c r="C38" s="34"/>
-      <c r="D38" s="113"/>
-      <c r="E38" s="114"/>
-      <c r="F38" s="114"/>
-      <c r="G38" s="114"/>
-      <c r="H38" s="114"/>
-      <c r="I38" s="114"/>
-      <c r="J38" s="114"/>
-      <c r="K38" s="114"/>
-      <c r="L38" s="114"/>
+      <c r="D38" s="137"/>
+      <c r="E38" s="138"/>
+      <c r="F38" s="138"/>
+      <c r="G38" s="138"/>
+      <c r="H38" s="138"/>
+      <c r="I38" s="138"/>
+      <c r="J38" s="138"/>
+      <c r="K38" s="138"/>
+      <c r="L38" s="138"/>
     </row>
     <row r="39" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="33">
@@ -11700,15 +11896,15 @@
         <v>126</v>
       </c>
       <c r="C39" s="34"/>
-      <c r="D39" s="113"/>
-      <c r="E39" s="114"/>
-      <c r="F39" s="114"/>
-      <c r="G39" s="114"/>
-      <c r="H39" s="114"/>
-      <c r="I39" s="114"/>
-      <c r="J39" s="114"/>
-      <c r="K39" s="114"/>
-      <c r="L39" s="114"/>
+      <c r="D39" s="137"/>
+      <c r="E39" s="138"/>
+      <c r="F39" s="138"/>
+      <c r="G39" s="138"/>
+      <c r="H39" s="138"/>
+      <c r="I39" s="138"/>
+      <c r="J39" s="138"/>
+      <c r="K39" s="138"/>
+      <c r="L39" s="138"/>
     </row>
     <row r="40" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="33">
@@ -11718,15 +11914,15 @@
         <v>127</v>
       </c>
       <c r="C40" s="34"/>
-      <c r="D40" s="113"/>
-      <c r="E40" s="114"/>
-      <c r="F40" s="114"/>
-      <c r="G40" s="114"/>
-      <c r="H40" s="114"/>
-      <c r="I40" s="114"/>
-      <c r="J40" s="114"/>
-      <c r="K40" s="114"/>
-      <c r="L40" s="114"/>
+      <c r="D40" s="137"/>
+      <c r="E40" s="138"/>
+      <c r="F40" s="138"/>
+      <c r="G40" s="138"/>
+      <c r="H40" s="138"/>
+      <c r="I40" s="138"/>
+      <c r="J40" s="138"/>
+      <c r="K40" s="138"/>
+      <c r="L40" s="138"/>
     </row>
     <row r="41" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="33">
@@ -11736,15 +11932,15 @@
         <v>128</v>
       </c>
       <c r="C41" s="34"/>
-      <c r="D41" s="113"/>
-      <c r="E41" s="114"/>
-      <c r="F41" s="114"/>
-      <c r="G41" s="114"/>
-      <c r="H41" s="114"/>
-      <c r="I41" s="114"/>
-      <c r="J41" s="114"/>
-      <c r="K41" s="114"/>
-      <c r="L41" s="114"/>
+      <c r="D41" s="137"/>
+      <c r="E41" s="138"/>
+      <c r="F41" s="138"/>
+      <c r="G41" s="138"/>
+      <c r="H41" s="138"/>
+      <c r="I41" s="138"/>
+      <c r="J41" s="138"/>
+      <c r="K41" s="138"/>
+      <c r="L41" s="138"/>
     </row>
     <row r="42" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="33">
@@ -11754,15 +11950,15 @@
         <v>140</v>
       </c>
       <c r="C42" s="34"/>
-      <c r="D42" s="113"/>
-      <c r="E42" s="114"/>
-      <c r="F42" s="114"/>
-      <c r="G42" s="114"/>
-      <c r="H42" s="114"/>
-      <c r="I42" s="114"/>
-      <c r="J42" s="114"/>
-      <c r="K42" s="114"/>
-      <c r="L42" s="114"/>
+      <c r="D42" s="137"/>
+      <c r="E42" s="138"/>
+      <c r="F42" s="138"/>
+      <c r="G42" s="138"/>
+      <c r="H42" s="138"/>
+      <c r="I42" s="138"/>
+      <c r="J42" s="138"/>
+      <c r="K42" s="138"/>
+      <c r="L42" s="138"/>
     </row>
     <row r="43" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="33">
@@ -11772,15 +11968,15 @@
         <v>141</v>
       </c>
       <c r="C43" s="34"/>
-      <c r="D43" s="113"/>
-      <c r="E43" s="114"/>
-      <c r="F43" s="114"/>
-      <c r="G43" s="114"/>
-      <c r="H43" s="114"/>
-      <c r="I43" s="114"/>
-      <c r="J43" s="114"/>
-      <c r="K43" s="114"/>
-      <c r="L43" s="114"/>
+      <c r="D43" s="137"/>
+      <c r="E43" s="138"/>
+      <c r="F43" s="138"/>
+      <c r="G43" s="138"/>
+      <c r="H43" s="138"/>
+      <c r="I43" s="138"/>
+      <c r="J43" s="138"/>
+      <c r="K43" s="138"/>
+      <c r="L43" s="138"/>
     </row>
     <row r="44" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="33">
@@ -11790,15 +11986,15 @@
         <v>129</v>
       </c>
       <c r="C44" s="34"/>
-      <c r="D44" s="113"/>
-      <c r="E44" s="114"/>
-      <c r="F44" s="114"/>
-      <c r="G44" s="114"/>
-      <c r="H44" s="114"/>
-      <c r="I44" s="114"/>
-      <c r="J44" s="114"/>
-      <c r="K44" s="114"/>
-      <c r="L44" s="114"/>
+      <c r="D44" s="137"/>
+      <c r="E44" s="138"/>
+      <c r="F44" s="138"/>
+      <c r="G44" s="138"/>
+      <c r="H44" s="138"/>
+      <c r="I44" s="138"/>
+      <c r="J44" s="138"/>
+      <c r="K44" s="138"/>
+      <c r="L44" s="138"/>
     </row>
     <row r="45" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="33">
@@ -11808,15 +12004,15 @@
         <v>130</v>
       </c>
       <c r="C45" s="34"/>
-      <c r="D45" s="113"/>
-      <c r="E45" s="114"/>
-      <c r="F45" s="114"/>
-      <c r="G45" s="114"/>
-      <c r="H45" s="114"/>
-      <c r="I45" s="114"/>
-      <c r="J45" s="114"/>
-      <c r="K45" s="114"/>
-      <c r="L45" s="114"/>
+      <c r="D45" s="137"/>
+      <c r="E45" s="138"/>
+      <c r="F45" s="138"/>
+      <c r="G45" s="138"/>
+      <c r="H45" s="138"/>
+      <c r="I45" s="138"/>
+      <c r="J45" s="138"/>
+      <c r="K45" s="138"/>
+      <c r="L45" s="138"/>
     </row>
     <row r="46" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="33">
@@ -11826,15 +12022,15 @@
         <v>131</v>
       </c>
       <c r="C46" s="34"/>
-      <c r="D46" s="113"/>
-      <c r="E46" s="114"/>
-      <c r="F46" s="114"/>
-      <c r="G46" s="114"/>
-      <c r="H46" s="114"/>
-      <c r="I46" s="114"/>
-      <c r="J46" s="114"/>
-      <c r="K46" s="114"/>
-      <c r="L46" s="114"/>
+      <c r="D46" s="137"/>
+      <c r="E46" s="138"/>
+      <c r="F46" s="138"/>
+      <c r="G46" s="138"/>
+      <c r="H46" s="138"/>
+      <c r="I46" s="138"/>
+      <c r="J46" s="138"/>
+      <c r="K46" s="138"/>
+      <c r="L46" s="138"/>
     </row>
     <row r="47" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="33">
@@ -11844,15 +12040,15 @@
         <v>132</v>
       </c>
       <c r="C47" s="34"/>
-      <c r="D47" s="113"/>
-      <c r="E47" s="114"/>
-      <c r="F47" s="114"/>
-      <c r="G47" s="114"/>
-      <c r="H47" s="114"/>
-      <c r="I47" s="114"/>
-      <c r="J47" s="114"/>
-      <c r="K47" s="114"/>
-      <c r="L47" s="114"/>
+      <c r="D47" s="137"/>
+      <c r="E47" s="138"/>
+      <c r="F47" s="138"/>
+      <c r="G47" s="138"/>
+      <c r="H47" s="138"/>
+      <c r="I47" s="138"/>
+      <c r="J47" s="138"/>
+      <c r="K47" s="138"/>
+      <c r="L47" s="138"/>
     </row>
     <row r="48" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="33">
@@ -11862,15 +12058,15 @@
         <v>133</v>
       </c>
       <c r="C48" s="34"/>
-      <c r="D48" s="113"/>
-      <c r="E48" s="114"/>
-      <c r="F48" s="114"/>
-      <c r="G48" s="114"/>
-      <c r="H48" s="114"/>
-      <c r="I48" s="114"/>
-      <c r="J48" s="114"/>
-      <c r="K48" s="114"/>
-      <c r="L48" s="114"/>
+      <c r="D48" s="137"/>
+      <c r="E48" s="138"/>
+      <c r="F48" s="138"/>
+      <c r="G48" s="138"/>
+      <c r="H48" s="138"/>
+      <c r="I48" s="138"/>
+      <c r="J48" s="138"/>
+      <c r="K48" s="138"/>
+      <c r="L48" s="138"/>
     </row>
     <row r="49" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="33">
@@ -11880,73 +12076,109 @@
         <v>142</v>
       </c>
       <c r="C49" s="34"/>
-      <c r="D49" s="113"/>
-      <c r="E49" s="114"/>
-      <c r="F49" s="114"/>
-      <c r="G49" s="114"/>
-      <c r="H49" s="114"/>
-      <c r="I49" s="114"/>
-      <c r="J49" s="114"/>
-      <c r="K49" s="114"/>
-      <c r="L49" s="114"/>
+      <c r="D49" s="137"/>
+      <c r="E49" s="138"/>
+      <c r="F49" s="138"/>
+      <c r="G49" s="138"/>
+      <c r="H49" s="138"/>
+      <c r="I49" s="138"/>
+      <c r="J49" s="138"/>
+      <c r="K49" s="138"/>
+      <c r="L49" s="138"/>
     </row>
     <row r="50" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="33">
+      <c r="A50" s="72">
         <v>25</v>
       </c>
-      <c r="B50" s="34" t="s">
+      <c r="B50" s="172" t="s">
         <v>134</v>
       </c>
       <c r="C50" s="34"/>
-      <c r="D50" s="113"/>
-      <c r="E50" s="114"/>
-      <c r="F50" s="114"/>
-      <c r="G50" s="114"/>
-      <c r="H50" s="114"/>
-      <c r="I50" s="114"/>
-      <c r="J50" s="114"/>
-      <c r="K50" s="114"/>
-      <c r="L50" s="114"/>
+      <c r="D50" s="137"/>
+      <c r="E50" s="138"/>
+      <c r="F50" s="138"/>
+      <c r="G50" s="138"/>
+      <c r="H50" s="138"/>
+      <c r="I50" s="138"/>
+      <c r="J50" s="138"/>
+      <c r="K50" s="138"/>
+      <c r="L50" s="138"/>
     </row>
     <row r="51" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="33">
+      <c r="A51" s="72">
         <v>26</v>
       </c>
-      <c r="B51" s="34" t="s">
+      <c r="B51" s="172" t="s">
         <v>135</v>
       </c>
       <c r="C51" s="34"/>
-      <c r="D51" s="113"/>
-      <c r="E51" s="114"/>
-      <c r="F51" s="114"/>
-      <c r="G51" s="114"/>
-      <c r="H51" s="114"/>
-      <c r="I51" s="114"/>
-      <c r="J51" s="114"/>
-      <c r="K51" s="114"/>
-      <c r="L51" s="114"/>
+      <c r="D51" s="137"/>
+      <c r="E51" s="138"/>
+      <c r="F51" s="138"/>
+      <c r="G51" s="138"/>
+      <c r="H51" s="138"/>
+      <c r="I51" s="138"/>
+      <c r="J51" s="138"/>
+      <c r="K51" s="138"/>
+      <c r="L51" s="138"/>
     </row>
     <row r="52" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="33">
+      <c r="A52" s="72">
         <v>27</v>
       </c>
-      <c r="B52" s="34" t="s">
+      <c r="B52" s="172" t="s">
         <v>136</v>
       </c>
       <c r="C52" s="34"/>
-      <c r="D52" s="113"/>
-      <c r="E52" s="114"/>
-      <c r="F52" s="114"/>
-      <c r="G52" s="114"/>
-      <c r="H52" s="114"/>
-      <c r="I52" s="114"/>
-      <c r="J52" s="114"/>
-      <c r="K52" s="114"/>
-      <c r="L52" s="114"/>
+      <c r="D52" s="137"/>
+      <c r="E52" s="138"/>
+      <c r="F52" s="138"/>
+      <c r="G52" s="138"/>
+      <c r="H52" s="138"/>
+      <c r="I52" s="138"/>
+      <c r="J52" s="138"/>
+      <c r="K52" s="138"/>
+      <c r="L52" s="138"/>
+    </row>
+    <row r="53" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="72">
+        <v>28</v>
+      </c>
+      <c r="B53" s="173" t="s">
+        <v>143</v>
+      </c>
+      <c r="C53" s="174"/>
+      <c r="D53" s="137"/>
+      <c r="E53" s="138"/>
+      <c r="F53" s="138"/>
+      <c r="G53" s="138"/>
+      <c r="H53" s="138"/>
+      <c r="I53" s="138"/>
+      <c r="J53" s="138"/>
+      <c r="K53" s="138"/>
+      <c r="L53" s="138"/>
+    </row>
+    <row r="54" spans="1:12" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="72">
+        <v>29</v>
+      </c>
+      <c r="B54" s="173" t="s">
+        <v>144</v>
+      </c>
+      <c r="C54" s="72"/>
+      <c r="D54" s="175"/>
+      <c r="E54" s="176"/>
+      <c r="F54" s="176"/>
+      <c r="G54" s="176"/>
+      <c r="H54" s="176"/>
+      <c r="I54" s="176"/>
+      <c r="J54" s="176"/>
+      <c r="K54" s="176"/>
+      <c r="L54" s="176"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="D26:L52"/>
+    <mergeCell ref="D26:L54"/>
     <mergeCell ref="D18:D20"/>
     <mergeCell ref="E18:L20"/>
     <mergeCell ref="D25:L25"/>
@@ -14880,6 +15112,50 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1235" r:id="rId137" name="Drop Down 211">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>52</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>1409700</xdr:colOff>
+                    <xdr:row>52</xdr:row>
+                    <xdr:rowOff>220980</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1236" r:id="rId138" name="Drop Down 212">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>53</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>1409700</xdr:colOff>
+                    <xdr:row>53</xdr:row>
+                    <xdr:rowOff>220980</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </mc:Choice>
   </mc:AlternateContent>
@@ -15106,17 +15382,17 @@
       <c r="C12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="123" t="s">
+      <c r="D12" s="119" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="123"/>
-      <c r="F12" s="123"/>
-      <c r="G12" s="123"/>
-      <c r="H12" s="123"/>
-      <c r="I12" s="123"/>
-      <c r="J12" s="123"/>
-      <c r="K12" s="123"/>
-      <c r="L12" s="123"/>
+      <c r="E12" s="119"/>
+      <c r="F12" s="119"/>
+      <c r="G12" s="119"/>
+      <c r="H12" s="119"/>
+      <c r="I12" s="119"/>
+      <c r="J12" s="119"/>
+      <c r="K12" s="119"/>
+      <c r="L12" s="119"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="49"/>
@@ -16024,68 +16300,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50">
-      <UserInfo>
-        <DisplayName>Luis Campos / Logiztik Alliance</DisplayName>
-        <AccountId>265</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Jairo Gonzalez / Logiztik Alliance</DisplayName>
-        <AccountId>322</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>José Ganchozo / Logiztik Alliance</DisplayName>
-        <AccountId>304</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Edwin Casa / Logiztik Alliance</DisplayName>
-        <AccountId>299</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Cristhian Cuichan / Logiztik Alliance</DisplayName>
-        <AccountId>369</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Oscar Yunda /  Logiztik Alliance</DisplayName>
-        <AccountId>355</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Fernando Ordoñez / Logiztik Alliance</DisplayName>
-        <AccountId>321</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Alex Rivera / Logiztik Alliance</DisplayName>
-        <AccountId>370</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <TaxCatchAll xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="87481c51-c14c-4071-bf64-faa2b5708bb6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101005DA7AC6E4F4FAE42B9D9FCD9C82CAAE1" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="553e0bb76796fbad2df2b84fb95dc83d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="87481c51-c14c-4071-bf64-faa2b5708bb6" xmlns:ns3="8029d101-3d2a-47c4-b15f-619642bf5e50" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d87cd7f238c73dc12c577d08dde48736" ns2:_="" ns3:_="">
     <xsd:import namespace="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
@@ -16334,26 +16548,69 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371D8832-41B3-447B-B13D-2663C267E34F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD069904-634F-48DA-AA92-BAE250498BEE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8029d101-3d2a-47c4-b15f-619642bf5e50"/>
-    <ds:schemaRef ds:uri="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50">
+      <UserInfo>
+        <DisplayName>Luis Campos / Logiztik Alliance</DisplayName>
+        <AccountId>265</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Jairo Gonzalez / Logiztik Alliance</DisplayName>
+        <AccountId>322</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>José Ganchozo / Logiztik Alliance</DisplayName>
+        <AccountId>304</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Edwin Casa / Logiztik Alliance</DisplayName>
+        <AccountId>299</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Cristhian Cuichan / Logiztik Alliance</DisplayName>
+        <AccountId>369</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Oscar Yunda /  Logiztik Alliance</DisplayName>
+        <AccountId>355</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Fernando Ordoñez / Logiztik Alliance</DisplayName>
+        <AccountId>321</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Alex Rivera / Logiztik Alliance</DisplayName>
+        <AccountId>370</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <TaxCatchAll xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="87481c51-c14c-4071-bf64-faa2b5708bb6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F7F06D0-41B3-4EAF-B418-88FC726117CC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -16370,4 +16627,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371D8832-41B3-447B-B13D-2663C267E34F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD069904-634F-48DA-AA92-BAE250498BEE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8029d101-3d2a-47c4-b15f-619642bf5e50"/>
+    <ds:schemaRef ds:uri="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Guias Produccion/HU-57723.xlsx
+++ b/Guias Produccion/HU-57723.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Alliance\ScriptsEntidades\Guias Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB600DDA-73EB-420C-A864-496F83D5FC9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B69ABD94-2576-45C3-B8BE-8F3AF5470FE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guia de implementación" sheetId="1" r:id="rId1"/>
@@ -591,13 +591,13 @@
     <t>18-AC_pro_Module_Edi.sql</t>
   </si>
   <si>
-    <t>24-AC_pro_GetListOfCycleCounts.sql</t>
-  </si>
-  <si>
     <t>28-AC_pro_GetAccountingAnalyticsReports.sql</t>
   </si>
   <si>
-    <t xml:space="preserve">29-AC_pro_GetSalesOrdes </t>
+    <t>24-AC_pro_GetListOFCycleCounts.sql</t>
+  </si>
+  <si>
+    <t>29-AC_pro_GetSalesOrders.sql</t>
   </si>
 </sst>
 </file>
@@ -1977,6 +1977,99 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="75" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="76" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="77" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="54" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="78" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="79" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2079,90 +2172,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="54" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2261,15 +2270,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="75" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="76" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="77" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="78" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="79" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -10572,7 +10572,7 @@
                   <a14:compatExt spid="_x0000_s1236"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D2230B8-CC77-582B-CBB5-F7A67E8158B6}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D4040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -11217,42 +11217,42 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:15" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="126" t="s">
         <v>103</v>
       </c>
-      <c r="B3" s="94"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="94"/>
-      <c r="I3" s="94"/>
-      <c r="J3" s="94"/>
-      <c r="K3" s="94"/>
-      <c r="L3" s="95"/>
-      <c r="N3" s="87" t="s">
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="127"/>
+      <c r="K3" s="127"/>
+      <c r="L3" s="128"/>
+      <c r="N3" s="120" t="s">
         <v>0</v>
       </c>
-      <c r="O3" s="88"/>
+      <c r="O3" s="121"/>
     </row>
     <row r="4" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="100" t="s">
+      <c r="B4" s="133" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="101"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="101"/>
-      <c r="H4" s="101"/>
-      <c r="I4" s="101"/>
-      <c r="J4" s="102"/>
-      <c r="K4" s="102"/>
-      <c r="L4" s="103"/>
+      <c r="C4" s="134"/>
+      <c r="D4" s="134"/>
+      <c r="E4" s="134"/>
+      <c r="F4" s="134"/>
+      <c r="G4" s="134"/>
+      <c r="H4" s="134"/>
+      <c r="I4" s="134"/>
+      <c r="J4" s="135"/>
+      <c r="K4" s="135"/>
+      <c r="L4" s="136"/>
       <c r="N4" s="21" t="s">
         <v>2</v>
       </c>
@@ -11262,19 +11262,19 @@
       <c r="A5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="104" t="s">
+      <c r="B5" s="137" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="104"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="104"/>
-      <c r="F5" s="104"/>
-      <c r="G5" s="104"/>
-      <c r="H5" s="104"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="105"/>
-      <c r="K5" s="105"/>
-      <c r="L5" s="106"/>
+      <c r="C5" s="137"/>
+      <c r="D5" s="137"/>
+      <c r="E5" s="137"/>
+      <c r="F5" s="137"/>
+      <c r="G5" s="137"/>
+      <c r="H5" s="137"/>
+      <c r="I5" s="137"/>
+      <c r="J5" s="138"/>
+      <c r="K5" s="138"/>
+      <c r="L5" s="139"/>
       <c r="N5" s="15" t="s">
         <v>4</v>
       </c>
@@ -11284,19 +11284,19 @@
       <c r="A6" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="90">
+      <c r="B6" s="123">
         <v>46073</v>
       </c>
-      <c r="C6" s="91"/>
-      <c r="D6" s="91"/>
-      <c r="E6" s="91"/>
-      <c r="F6" s="91"/>
-      <c r="G6" s="91"/>
-      <c r="H6" s="91"/>
-      <c r="I6" s="91"/>
-      <c r="J6" s="91"/>
-      <c r="K6" s="91"/>
-      <c r="L6" s="92"/>
+      <c r="C6" s="124"/>
+      <c r="D6" s="124"/>
+      <c r="E6" s="124"/>
+      <c r="F6" s="124"/>
+      <c r="G6" s="124"/>
+      <c r="H6" s="124"/>
+      <c r="I6" s="124"/>
+      <c r="J6" s="124"/>
+      <c r="K6" s="124"/>
+      <c r="L6" s="125"/>
       <c r="N6" s="14"/>
       <c r="O6" s="14"/>
     </row>
@@ -11304,17 +11304,17 @@
       <c r="A7" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="107"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="108"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="108"/>
-      <c r="G7" s="108"/>
-      <c r="H7" s="108"/>
-      <c r="I7" s="108"/>
-      <c r="J7" s="109"/>
-      <c r="K7" s="109"/>
-      <c r="L7" s="110"/>
+      <c r="B7" s="140"/>
+      <c r="C7" s="141"/>
+      <c r="D7" s="141"/>
+      <c r="E7" s="141"/>
+      <c r="F7" s="141"/>
+      <c r="G7" s="141"/>
+      <c r="H7" s="141"/>
+      <c r="I7" s="141"/>
+      <c r="J7" s="142"/>
+      <c r="K7" s="142"/>
+      <c r="L7" s="143"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
@@ -11331,20 +11331,20 @@
       <c r="L8" s="13"/>
     </row>
     <row r="9" spans="1:15" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="96" t="s">
+      <c r="A9" s="129" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="97"/>
-      <c r="C9" s="97"/>
-      <c r="D9" s="97"/>
-      <c r="E9" s="97"/>
-      <c r="F9" s="97"/>
-      <c r="G9" s="97"/>
-      <c r="H9" s="97"/>
-      <c r="I9" s="97"/>
-      <c r="J9" s="98"/>
-      <c r="K9" s="98"/>
-      <c r="L9" s="99"/>
+      <c r="B9" s="130"/>
+      <c r="C9" s="130"/>
+      <c r="D9" s="130"/>
+      <c r="E9" s="130"/>
+      <c r="F9" s="130"/>
+      <c r="G9" s="130"/>
+      <c r="H9" s="130"/>
+      <c r="I9" s="130"/>
+      <c r="J9" s="131"/>
+      <c r="K9" s="131"/>
+      <c r="L9" s="132"/>
     </row>
     <row r="10" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -11444,63 +11444,63 @@
       <c r="A14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="89"/>
-      <c r="C14" s="85"/>
-      <c r="D14" s="85"/>
-      <c r="E14" s="85"/>
-      <c r="F14" s="85"/>
-      <c r="G14" s="85"/>
-      <c r="H14" s="85"/>
-      <c r="I14" s="85"/>
-      <c r="J14" s="85"/>
-      <c r="K14" s="85"/>
-      <c r="L14" s="86"/>
+      <c r="B14" s="122"/>
+      <c r="C14" s="118"/>
+      <c r="D14" s="118"/>
+      <c r="E14" s="118"/>
+      <c r="F14" s="118"/>
+      <c r="G14" s="118"/>
+      <c r="H14" s="118"/>
+      <c r="I14" s="118"/>
+      <c r="J14" s="118"/>
+      <c r="K14" s="118"/>
+      <c r="L14" s="119"/>
     </row>
     <row r="15" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="84"/>
-      <c r="C15" s="85"/>
-      <c r="D15" s="85"/>
-      <c r="E15" s="85"/>
-      <c r="F15" s="85"/>
-      <c r="G15" s="85"/>
-      <c r="H15" s="85"/>
-      <c r="I15" s="85"/>
-      <c r="J15" s="85"/>
-      <c r="K15" s="85"/>
-      <c r="L15" s="86"/>
+      <c r="B15" s="117"/>
+      <c r="C15" s="118"/>
+      <c r="D15" s="118"/>
+      <c r="E15" s="118"/>
+      <c r="F15" s="118"/>
+      <c r="G15" s="118"/>
+      <c r="H15" s="118"/>
+      <c r="I15" s="118"/>
+      <c r="J15" s="118"/>
+      <c r="K15" s="118"/>
+      <c r="L15" s="119"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="77"/>
-      <c r="B16" s="78"/>
-      <c r="C16" s="78"/>
-      <c r="D16" s="78"/>
-      <c r="E16" s="78"/>
-      <c r="F16" s="78"/>
-      <c r="G16" s="78"/>
-      <c r="H16" s="78"/>
-      <c r="I16" s="78"/>
-      <c r="J16" s="78"/>
-      <c r="K16" s="78"/>
-      <c r="L16" s="79"/>
+      <c r="A16" s="110"/>
+      <c r="B16" s="111"/>
+      <c r="C16" s="111"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="111"/>
+      <c r="F16" s="111"/>
+      <c r="G16" s="111"/>
+      <c r="H16" s="111"/>
+      <c r="I16" s="111"/>
+      <c r="J16" s="111"/>
+      <c r="K16" s="111"/>
+      <c r="L16" s="112"/>
     </row>
     <row r="17" spans="1:12" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="80" t="s">
+      <c r="A17" s="113" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="81"/>
-      <c r="C17" s="81"/>
-      <c r="D17" s="81"/>
-      <c r="E17" s="81"/>
-      <c r="F17" s="81"/>
-      <c r="G17" s="81"/>
-      <c r="H17" s="81"/>
-      <c r="I17" s="81"/>
-      <c r="J17" s="82"/>
-      <c r="K17" s="82"/>
-      <c r="L17" s="83"/>
+      <c r="B17" s="114"/>
+      <c r="C17" s="114"/>
+      <c r="D17" s="114"/>
+      <c r="E17" s="114"/>
+      <c r="F17" s="114"/>
+      <c r="G17" s="114"/>
+      <c r="H17" s="114"/>
+      <c r="I17" s="114"/>
+      <c r="J17" s="115"/>
+      <c r="K17" s="115"/>
+      <c r="L17" s="116"/>
     </row>
     <row r="18" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
@@ -11510,19 +11510,19 @@
       <c r="C18" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="111" t="s">
+      <c r="D18" s="86" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="113" t="s">
+      <c r="E18" s="88" t="s">
         <v>137</v>
       </c>
-      <c r="F18" s="113"/>
-      <c r="G18" s="113"/>
-      <c r="H18" s="113"/>
-      <c r="I18" s="113"/>
-      <c r="J18" s="114"/>
-      <c r="K18" s="114"/>
-      <c r="L18" s="115"/>
+      <c r="F18" s="88"/>
+      <c r="G18" s="88"/>
+      <c r="H18" s="88"/>
+      <c r="I18" s="88"/>
+      <c r="J18" s="89"/>
+      <c r="K18" s="89"/>
+      <c r="L18" s="90"/>
     </row>
     <row r="19" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
@@ -11532,15 +11532,15 @@
         <v>30</v>
       </c>
       <c r="C19" s="44"/>
-      <c r="D19" s="112"/>
-      <c r="E19" s="116"/>
-      <c r="F19" s="116"/>
-      <c r="G19" s="116"/>
-      <c r="H19" s="116"/>
-      <c r="I19" s="116"/>
-      <c r="J19" s="117"/>
-      <c r="K19" s="117"/>
-      <c r="L19" s="118"/>
+      <c r="D19" s="87"/>
+      <c r="E19" s="91"/>
+      <c r="F19" s="91"/>
+      <c r="G19" s="91"/>
+      <c r="H19" s="91"/>
+      <c r="I19" s="91"/>
+      <c r="J19" s="92"/>
+      <c r="K19" s="92"/>
+      <c r="L19" s="93"/>
     </row>
     <row r="20" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
@@ -11550,15 +11550,15 @@
       <c r="C20" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="112"/>
-      <c r="E20" s="116"/>
-      <c r="F20" s="116"/>
-      <c r="G20" s="116"/>
-      <c r="H20" s="116"/>
-      <c r="I20" s="116"/>
-      <c r="J20" s="117"/>
-      <c r="K20" s="117"/>
-      <c r="L20" s="118"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="91"/>
+      <c r="F20" s="91"/>
+      <c r="G20" s="91"/>
+      <c r="H20" s="91"/>
+      <c r="I20" s="91"/>
+      <c r="J20" s="92"/>
+      <c r="K20" s="92"/>
+      <c r="L20" s="93"/>
     </row>
     <row r="21" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
@@ -11568,19 +11568,19 @@
       <c r="C21" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="127" t="s">
+      <c r="D21" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="129" t="s">
+      <c r="E21" s="104" t="s">
         <v>107</v>
       </c>
-      <c r="F21" s="130"/>
-      <c r="G21" s="130"/>
-      <c r="H21" s="130"/>
-      <c r="I21" s="130"/>
-      <c r="J21" s="130"/>
-      <c r="K21" s="130"/>
-      <c r="L21" s="131"/>
+      <c r="F21" s="105"/>
+      <c r="G21" s="105"/>
+      <c r="H21" s="105"/>
+      <c r="I21" s="105"/>
+      <c r="J21" s="105"/>
+      <c r="K21" s="105"/>
+      <c r="L21" s="106"/>
     </row>
     <row r="22" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
@@ -11590,45 +11590,45 @@
       <c r="C22" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="128"/>
-      <c r="E22" s="132"/>
-      <c r="F22" s="133"/>
-      <c r="G22" s="133"/>
-      <c r="H22" s="133"/>
-      <c r="I22" s="133"/>
-      <c r="J22" s="133"/>
-      <c r="K22" s="133"/>
-      <c r="L22" s="134"/>
+      <c r="D22" s="103"/>
+      <c r="E22" s="107"/>
+      <c r="F22" s="108"/>
+      <c r="G22" s="108"/>
+      <c r="H22" s="108"/>
+      <c r="I22" s="108"/>
+      <c r="J22" s="108"/>
+      <c r="K22" s="108"/>
+      <c r="L22" s="109"/>
     </row>
     <row r="23" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="120"/>
-      <c r="B23" s="121"/>
-      <c r="C23" s="121"/>
-      <c r="D23" s="122"/>
-      <c r="E23" s="122"/>
-      <c r="F23" s="122"/>
-      <c r="G23" s="122"/>
-      <c r="H23" s="122"/>
-      <c r="I23" s="122"/>
-      <c r="J23" s="122"/>
-      <c r="K23" s="122"/>
-      <c r="L23" s="123"/>
+      <c r="A23" s="95"/>
+      <c r="B23" s="96"/>
+      <c r="C23" s="96"/>
+      <c r="D23" s="97"/>
+      <c r="E23" s="97"/>
+      <c r="F23" s="97"/>
+      <c r="G23" s="97"/>
+      <c r="H23" s="97"/>
+      <c r="I23" s="97"/>
+      <c r="J23" s="97"/>
+      <c r="K23" s="97"/>
+      <c r="L23" s="98"/>
     </row>
     <row r="24" spans="1:12" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="124" t="s">
+      <c r="A24" s="99" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="125"/>
-      <c r="C24" s="125"/>
-      <c r="D24" s="125"/>
-      <c r="E24" s="125"/>
-      <c r="F24" s="125"/>
-      <c r="G24" s="125"/>
-      <c r="H24" s="125"/>
-      <c r="I24" s="125"/>
-      <c r="J24" s="125"/>
-      <c r="K24" s="125"/>
-      <c r="L24" s="126"/>
+      <c r="B24" s="100"/>
+      <c r="C24" s="100"/>
+      <c r="D24" s="100"/>
+      <c r="E24" s="100"/>
+      <c r="F24" s="100"/>
+      <c r="G24" s="100"/>
+      <c r="H24" s="100"/>
+      <c r="I24" s="100"/>
+      <c r="J24" s="100"/>
+      <c r="K24" s="100"/>
+      <c r="L24" s="101"/>
     </row>
     <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
@@ -11640,17 +11640,17 @@
       <c r="C25" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="119" t="s">
+      <c r="D25" s="94" t="s">
         <v>38</v>
       </c>
-      <c r="E25" s="119"/>
-      <c r="F25" s="119"/>
-      <c r="G25" s="119"/>
-      <c r="H25" s="119"/>
-      <c r="I25" s="119"/>
-      <c r="J25" s="119"/>
-      <c r="K25" s="119"/>
-      <c r="L25" s="119"/>
+      <c r="E25" s="94"/>
+      <c r="F25" s="94"/>
+      <c r="G25" s="94"/>
+      <c r="H25" s="94"/>
+      <c r="I25" s="94"/>
+      <c r="J25" s="94"/>
+      <c r="K25" s="94"/>
+      <c r="L25" s="94"/>
     </row>
     <row r="26" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="33">
@@ -11660,17 +11660,17 @@
         <v>115</v>
       </c>
       <c r="C26" s="34"/>
-      <c r="D26" s="135" t="s">
+      <c r="D26" s="80" t="s">
         <v>108</v>
       </c>
-      <c r="E26" s="136"/>
-      <c r="F26" s="136"/>
-      <c r="G26" s="136"/>
-      <c r="H26" s="136"/>
-      <c r="I26" s="136"/>
-      <c r="J26" s="136"/>
-      <c r="K26" s="136"/>
-      <c r="L26" s="136"/>
+      <c r="E26" s="81"/>
+      <c r="F26" s="81"/>
+      <c r="G26" s="81"/>
+      <c r="H26" s="81"/>
+      <c r="I26" s="81"/>
+      <c r="J26" s="81"/>
+      <c r="K26" s="81"/>
+      <c r="L26" s="81"/>
     </row>
     <row r="27" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
@@ -11680,15 +11680,15 @@
         <v>116</v>
       </c>
       <c r="C27" s="34"/>
-      <c r="D27" s="137"/>
-      <c r="E27" s="138"/>
-      <c r="F27" s="138"/>
-      <c r="G27" s="138"/>
-      <c r="H27" s="138"/>
-      <c r="I27" s="138"/>
-      <c r="J27" s="138"/>
-      <c r="K27" s="138"/>
-      <c r="L27" s="138"/>
+      <c r="D27" s="82"/>
+      <c r="E27" s="83"/>
+      <c r="F27" s="83"/>
+      <c r="G27" s="83"/>
+      <c r="H27" s="83"/>
+      <c r="I27" s="83"/>
+      <c r="J27" s="83"/>
+      <c r="K27" s="83"/>
+      <c r="L27" s="83"/>
     </row>
     <row r="28" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="33">
@@ -11698,15 +11698,15 @@
         <v>117</v>
       </c>
       <c r="C28" s="34"/>
-      <c r="D28" s="137"/>
-      <c r="E28" s="138"/>
-      <c r="F28" s="138"/>
-      <c r="G28" s="138"/>
-      <c r="H28" s="138"/>
-      <c r="I28" s="138"/>
-      <c r="J28" s="138"/>
-      <c r="K28" s="138"/>
-      <c r="L28" s="138"/>
+      <c r="D28" s="82"/>
+      <c r="E28" s="83"/>
+      <c r="F28" s="83"/>
+      <c r="G28" s="83"/>
+      <c r="H28" s="83"/>
+      <c r="I28" s="83"/>
+      <c r="J28" s="83"/>
+      <c r="K28" s="83"/>
+      <c r="L28" s="83"/>
     </row>
     <row r="29" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
@@ -11716,15 +11716,15 @@
         <v>138</v>
       </c>
       <c r="C29" s="34"/>
-      <c r="D29" s="137"/>
-      <c r="E29" s="138"/>
-      <c r="F29" s="138"/>
-      <c r="G29" s="138"/>
-      <c r="H29" s="138"/>
-      <c r="I29" s="138"/>
-      <c r="J29" s="138"/>
-      <c r="K29" s="138"/>
-      <c r="L29" s="138"/>
+      <c r="D29" s="82"/>
+      <c r="E29" s="83"/>
+      <c r="F29" s="83"/>
+      <c r="G29" s="83"/>
+      <c r="H29" s="83"/>
+      <c r="I29" s="83"/>
+      <c r="J29" s="83"/>
+      <c r="K29" s="83"/>
+      <c r="L29" s="83"/>
     </row>
     <row r="30" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="33">
@@ -11734,15 +11734,15 @@
         <v>118</v>
       </c>
       <c r="C30" s="34"/>
-      <c r="D30" s="137"/>
-      <c r="E30" s="138"/>
-      <c r="F30" s="138"/>
-      <c r="G30" s="138"/>
-      <c r="H30" s="138"/>
-      <c r="I30" s="138"/>
-      <c r="J30" s="138"/>
-      <c r="K30" s="138"/>
-      <c r="L30" s="138"/>
+      <c r="D30" s="82"/>
+      <c r="E30" s="83"/>
+      <c r="F30" s="83"/>
+      <c r="G30" s="83"/>
+      <c r="H30" s="83"/>
+      <c r="I30" s="83"/>
+      <c r="J30" s="83"/>
+      <c r="K30" s="83"/>
+      <c r="L30" s="83"/>
     </row>
     <row r="31" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="33">
@@ -11752,15 +11752,15 @@
         <v>119</v>
       </c>
       <c r="C31" s="34"/>
-      <c r="D31" s="137"/>
-      <c r="E31" s="138"/>
-      <c r="F31" s="138"/>
-      <c r="G31" s="138"/>
-      <c r="H31" s="138"/>
-      <c r="I31" s="138"/>
-      <c r="J31" s="138"/>
-      <c r="K31" s="138"/>
-      <c r="L31" s="138"/>
+      <c r="D31" s="82"/>
+      <c r="E31" s="83"/>
+      <c r="F31" s="83"/>
+      <c r="G31" s="83"/>
+      <c r="H31" s="83"/>
+      <c r="I31" s="83"/>
+      <c r="J31" s="83"/>
+      <c r="K31" s="83"/>
+      <c r="L31" s="83"/>
     </row>
     <row r="32" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="33">
@@ -11770,15 +11770,15 @@
         <v>120</v>
       </c>
       <c r="C32" s="34"/>
-      <c r="D32" s="137"/>
-      <c r="E32" s="138"/>
-      <c r="F32" s="138"/>
-      <c r="G32" s="138"/>
-      <c r="H32" s="138"/>
-      <c r="I32" s="138"/>
-      <c r="J32" s="138"/>
-      <c r="K32" s="138"/>
-      <c r="L32" s="138"/>
+      <c r="D32" s="82"/>
+      <c r="E32" s="83"/>
+      <c r="F32" s="83"/>
+      <c r="G32" s="83"/>
+      <c r="H32" s="83"/>
+      <c r="I32" s="83"/>
+      <c r="J32" s="83"/>
+      <c r="K32" s="83"/>
+      <c r="L32" s="83"/>
     </row>
     <row r="33" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="33">
@@ -11788,15 +11788,15 @@
         <v>121</v>
       </c>
       <c r="C33" s="34"/>
-      <c r="D33" s="137"/>
-      <c r="E33" s="138"/>
-      <c r="F33" s="138"/>
-      <c r="G33" s="138"/>
-      <c r="H33" s="138"/>
-      <c r="I33" s="138"/>
-      <c r="J33" s="138"/>
-      <c r="K33" s="138"/>
-      <c r="L33" s="138"/>
+      <c r="D33" s="82"/>
+      <c r="E33" s="83"/>
+      <c r="F33" s="83"/>
+      <c r="G33" s="83"/>
+      <c r="H33" s="83"/>
+      <c r="I33" s="83"/>
+      <c r="J33" s="83"/>
+      <c r="K33" s="83"/>
+      <c r="L33" s="83"/>
     </row>
     <row r="34" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="33">
@@ -11806,15 +11806,15 @@
         <v>122</v>
       </c>
       <c r="C34" s="34"/>
-      <c r="D34" s="137"/>
-      <c r="E34" s="138"/>
-      <c r="F34" s="138"/>
-      <c r="G34" s="138"/>
-      <c r="H34" s="138"/>
-      <c r="I34" s="138"/>
-      <c r="J34" s="138"/>
-      <c r="K34" s="138"/>
-      <c r="L34" s="138"/>
+      <c r="D34" s="82"/>
+      <c r="E34" s="83"/>
+      <c r="F34" s="83"/>
+      <c r="G34" s="83"/>
+      <c r="H34" s="83"/>
+      <c r="I34" s="83"/>
+      <c r="J34" s="83"/>
+      <c r="K34" s="83"/>
+      <c r="L34" s="83"/>
     </row>
     <row r="35" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="33">
@@ -11824,15 +11824,15 @@
         <v>123</v>
       </c>
       <c r="C35" s="34"/>
-      <c r="D35" s="137"/>
-      <c r="E35" s="138"/>
-      <c r="F35" s="138"/>
-      <c r="G35" s="138"/>
-      <c r="H35" s="138"/>
-      <c r="I35" s="138"/>
-      <c r="J35" s="138"/>
-      <c r="K35" s="138"/>
-      <c r="L35" s="138"/>
+      <c r="D35" s="82"/>
+      <c r="E35" s="83"/>
+      <c r="F35" s="83"/>
+      <c r="G35" s="83"/>
+      <c r="H35" s="83"/>
+      <c r="I35" s="83"/>
+      <c r="J35" s="83"/>
+      <c r="K35" s="83"/>
+      <c r="L35" s="83"/>
     </row>
     <row r="36" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="33">
@@ -11842,15 +11842,15 @@
         <v>124</v>
       </c>
       <c r="C36" s="34"/>
-      <c r="D36" s="137"/>
-      <c r="E36" s="138"/>
-      <c r="F36" s="138"/>
-      <c r="G36" s="138"/>
-      <c r="H36" s="138"/>
-      <c r="I36" s="138"/>
-      <c r="J36" s="138"/>
-      <c r="K36" s="138"/>
-      <c r="L36" s="138"/>
+      <c r="D36" s="82"/>
+      <c r="E36" s="83"/>
+      <c r="F36" s="83"/>
+      <c r="G36" s="83"/>
+      <c r="H36" s="83"/>
+      <c r="I36" s="83"/>
+      <c r="J36" s="83"/>
+      <c r="K36" s="83"/>
+      <c r="L36" s="83"/>
     </row>
     <row r="37" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="33">
@@ -11860,15 +11860,15 @@
         <v>139</v>
       </c>
       <c r="C37" s="34"/>
-      <c r="D37" s="137"/>
-      <c r="E37" s="138"/>
-      <c r="F37" s="138"/>
-      <c r="G37" s="138"/>
-      <c r="H37" s="138"/>
-      <c r="I37" s="138"/>
-      <c r="J37" s="138"/>
-      <c r="K37" s="138"/>
-      <c r="L37" s="138"/>
+      <c r="D37" s="82"/>
+      <c r="E37" s="83"/>
+      <c r="F37" s="83"/>
+      <c r="G37" s="83"/>
+      <c r="H37" s="83"/>
+      <c r="I37" s="83"/>
+      <c r="J37" s="83"/>
+      <c r="K37" s="83"/>
+      <c r="L37" s="83"/>
     </row>
     <row r="38" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="33">
@@ -11878,15 +11878,15 @@
         <v>125</v>
       </c>
       <c r="C38" s="34"/>
-      <c r="D38" s="137"/>
-      <c r="E38" s="138"/>
-      <c r="F38" s="138"/>
-      <c r="G38" s="138"/>
-      <c r="H38" s="138"/>
-      <c r="I38" s="138"/>
-      <c r="J38" s="138"/>
-      <c r="K38" s="138"/>
-      <c r="L38" s="138"/>
+      <c r="D38" s="82"/>
+      <c r="E38" s="83"/>
+      <c r="F38" s="83"/>
+      <c r="G38" s="83"/>
+      <c r="H38" s="83"/>
+      <c r="I38" s="83"/>
+      <c r="J38" s="83"/>
+      <c r="K38" s="83"/>
+      <c r="L38" s="83"/>
     </row>
     <row r="39" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="33">
@@ -11896,15 +11896,15 @@
         <v>126</v>
       </c>
       <c r="C39" s="34"/>
-      <c r="D39" s="137"/>
-      <c r="E39" s="138"/>
-      <c r="F39" s="138"/>
-      <c r="G39" s="138"/>
-      <c r="H39" s="138"/>
-      <c r="I39" s="138"/>
-      <c r="J39" s="138"/>
-      <c r="K39" s="138"/>
-      <c r="L39" s="138"/>
+      <c r="D39" s="82"/>
+      <c r="E39" s="83"/>
+      <c r="F39" s="83"/>
+      <c r="G39" s="83"/>
+      <c r="H39" s="83"/>
+      <c r="I39" s="83"/>
+      <c r="J39" s="83"/>
+      <c r="K39" s="83"/>
+      <c r="L39" s="83"/>
     </row>
     <row r="40" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="33">
@@ -11914,15 +11914,15 @@
         <v>127</v>
       </c>
       <c r="C40" s="34"/>
-      <c r="D40" s="137"/>
-      <c r="E40" s="138"/>
-      <c r="F40" s="138"/>
-      <c r="G40" s="138"/>
-      <c r="H40" s="138"/>
-      <c r="I40" s="138"/>
-      <c r="J40" s="138"/>
-      <c r="K40" s="138"/>
-      <c r="L40" s="138"/>
+      <c r="D40" s="82"/>
+      <c r="E40" s="83"/>
+      <c r="F40" s="83"/>
+      <c r="G40" s="83"/>
+      <c r="H40" s="83"/>
+      <c r="I40" s="83"/>
+      <c r="J40" s="83"/>
+      <c r="K40" s="83"/>
+      <c r="L40" s="83"/>
     </row>
     <row r="41" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="33">
@@ -11932,15 +11932,15 @@
         <v>128</v>
       </c>
       <c r="C41" s="34"/>
-      <c r="D41" s="137"/>
-      <c r="E41" s="138"/>
-      <c r="F41" s="138"/>
-      <c r="G41" s="138"/>
-      <c r="H41" s="138"/>
-      <c r="I41" s="138"/>
-      <c r="J41" s="138"/>
-      <c r="K41" s="138"/>
-      <c r="L41" s="138"/>
+      <c r="D41" s="82"/>
+      <c r="E41" s="83"/>
+      <c r="F41" s="83"/>
+      <c r="G41" s="83"/>
+      <c r="H41" s="83"/>
+      <c r="I41" s="83"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="83"/>
+      <c r="L41" s="83"/>
     </row>
     <row r="42" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="33">
@@ -11950,15 +11950,15 @@
         <v>140</v>
       </c>
       <c r="C42" s="34"/>
-      <c r="D42" s="137"/>
-      <c r="E42" s="138"/>
-      <c r="F42" s="138"/>
-      <c r="G42" s="138"/>
-      <c r="H42" s="138"/>
-      <c r="I42" s="138"/>
-      <c r="J42" s="138"/>
-      <c r="K42" s="138"/>
-      <c r="L42" s="138"/>
+      <c r="D42" s="82"/>
+      <c r="E42" s="83"/>
+      <c r="F42" s="83"/>
+      <c r="G42" s="83"/>
+      <c r="H42" s="83"/>
+      <c r="I42" s="83"/>
+      <c r="J42" s="83"/>
+      <c r="K42" s="83"/>
+      <c r="L42" s="83"/>
     </row>
     <row r="43" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="33">
@@ -11968,15 +11968,15 @@
         <v>141</v>
       </c>
       <c r="C43" s="34"/>
-      <c r="D43" s="137"/>
-      <c r="E43" s="138"/>
-      <c r="F43" s="138"/>
-      <c r="G43" s="138"/>
-      <c r="H43" s="138"/>
-      <c r="I43" s="138"/>
-      <c r="J43" s="138"/>
-      <c r="K43" s="138"/>
-      <c r="L43" s="138"/>
+      <c r="D43" s="82"/>
+      <c r="E43" s="83"/>
+      <c r="F43" s="83"/>
+      <c r="G43" s="83"/>
+      <c r="H43" s="83"/>
+      <c r="I43" s="83"/>
+      <c r="J43" s="83"/>
+      <c r="K43" s="83"/>
+      <c r="L43" s="83"/>
     </row>
     <row r="44" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="33">
@@ -11986,15 +11986,15 @@
         <v>129</v>
       </c>
       <c r="C44" s="34"/>
-      <c r="D44" s="137"/>
-      <c r="E44" s="138"/>
-      <c r="F44" s="138"/>
-      <c r="G44" s="138"/>
-      <c r="H44" s="138"/>
-      <c r="I44" s="138"/>
-      <c r="J44" s="138"/>
-      <c r="K44" s="138"/>
-      <c r="L44" s="138"/>
+      <c r="D44" s="82"/>
+      <c r="E44" s="83"/>
+      <c r="F44" s="83"/>
+      <c r="G44" s="83"/>
+      <c r="H44" s="83"/>
+      <c r="I44" s="83"/>
+      <c r="J44" s="83"/>
+      <c r="K44" s="83"/>
+      <c r="L44" s="83"/>
     </row>
     <row r="45" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="33">
@@ -12004,15 +12004,15 @@
         <v>130</v>
       </c>
       <c r="C45" s="34"/>
-      <c r="D45" s="137"/>
-      <c r="E45" s="138"/>
-      <c r="F45" s="138"/>
-      <c r="G45" s="138"/>
-      <c r="H45" s="138"/>
-      <c r="I45" s="138"/>
-      <c r="J45" s="138"/>
-      <c r="K45" s="138"/>
-      <c r="L45" s="138"/>
+      <c r="D45" s="82"/>
+      <c r="E45" s="83"/>
+      <c r="F45" s="83"/>
+      <c r="G45" s="83"/>
+      <c r="H45" s="83"/>
+      <c r="I45" s="83"/>
+      <c r="J45" s="83"/>
+      <c r="K45" s="83"/>
+      <c r="L45" s="83"/>
     </row>
     <row r="46" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="33">
@@ -12022,15 +12022,15 @@
         <v>131</v>
       </c>
       <c r="C46" s="34"/>
-      <c r="D46" s="137"/>
-      <c r="E46" s="138"/>
-      <c r="F46" s="138"/>
-      <c r="G46" s="138"/>
-      <c r="H46" s="138"/>
-      <c r="I46" s="138"/>
-      <c r="J46" s="138"/>
-      <c r="K46" s="138"/>
-      <c r="L46" s="138"/>
+      <c r="D46" s="82"/>
+      <c r="E46" s="83"/>
+      <c r="F46" s="83"/>
+      <c r="G46" s="83"/>
+      <c r="H46" s="83"/>
+      <c r="I46" s="83"/>
+      <c r="J46" s="83"/>
+      <c r="K46" s="83"/>
+      <c r="L46" s="83"/>
     </row>
     <row r="47" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="33">
@@ -12040,15 +12040,15 @@
         <v>132</v>
       </c>
       <c r="C47" s="34"/>
-      <c r="D47" s="137"/>
-      <c r="E47" s="138"/>
-      <c r="F47" s="138"/>
-      <c r="G47" s="138"/>
-      <c r="H47" s="138"/>
-      <c r="I47" s="138"/>
-      <c r="J47" s="138"/>
-      <c r="K47" s="138"/>
-      <c r="L47" s="138"/>
+      <c r="D47" s="82"/>
+      <c r="E47" s="83"/>
+      <c r="F47" s="83"/>
+      <c r="G47" s="83"/>
+      <c r="H47" s="83"/>
+      <c r="I47" s="83"/>
+      <c r="J47" s="83"/>
+      <c r="K47" s="83"/>
+      <c r="L47" s="83"/>
     </row>
     <row r="48" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="33">
@@ -12058,134 +12058,126 @@
         <v>133</v>
       </c>
       <c r="C48" s="34"/>
-      <c r="D48" s="137"/>
-      <c r="E48" s="138"/>
-      <c r="F48" s="138"/>
-      <c r="G48" s="138"/>
-      <c r="H48" s="138"/>
-      <c r="I48" s="138"/>
-      <c r="J48" s="138"/>
-      <c r="K48" s="138"/>
-      <c r="L48" s="138"/>
+      <c r="D48" s="82"/>
+      <c r="E48" s="83"/>
+      <c r="F48" s="83"/>
+      <c r="G48" s="83"/>
+      <c r="H48" s="83"/>
+      <c r="I48" s="83"/>
+      <c r="J48" s="83"/>
+      <c r="K48" s="83"/>
+      <c r="L48" s="83"/>
     </row>
     <row r="49" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="33">
         <v>24</v>
       </c>
       <c r="B49" s="34" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C49" s="34"/>
-      <c r="D49" s="137"/>
-      <c r="E49" s="138"/>
-      <c r="F49" s="138"/>
-      <c r="G49" s="138"/>
-      <c r="H49" s="138"/>
-      <c r="I49" s="138"/>
-      <c r="J49" s="138"/>
-      <c r="K49" s="138"/>
-      <c r="L49" s="138"/>
+      <c r="D49" s="82"/>
+      <c r="E49" s="83"/>
+      <c r="F49" s="83"/>
+      <c r="G49" s="83"/>
+      <c r="H49" s="83"/>
+      <c r="I49" s="83"/>
+      <c r="J49" s="83"/>
+      <c r="K49" s="83"/>
+      <c r="L49" s="83"/>
     </row>
     <row r="50" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="72">
         <v>25</v>
       </c>
-      <c r="B50" s="172" t="s">
+      <c r="B50" s="77" t="s">
         <v>134</v>
       </c>
       <c r="C50" s="34"/>
-      <c r="D50" s="137"/>
-      <c r="E50" s="138"/>
-      <c r="F50" s="138"/>
-      <c r="G50" s="138"/>
-      <c r="H50" s="138"/>
-      <c r="I50" s="138"/>
-      <c r="J50" s="138"/>
-      <c r="K50" s="138"/>
-      <c r="L50" s="138"/>
+      <c r="D50" s="82"/>
+      <c r="E50" s="83"/>
+      <c r="F50" s="83"/>
+      <c r="G50" s="83"/>
+      <c r="H50" s="83"/>
+      <c r="I50" s="83"/>
+      <c r="J50" s="83"/>
+      <c r="K50" s="83"/>
+      <c r="L50" s="83"/>
     </row>
     <row r="51" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="72">
         <v>26</v>
       </c>
-      <c r="B51" s="172" t="s">
+      <c r="B51" s="77" t="s">
         <v>135</v>
       </c>
       <c r="C51" s="34"/>
-      <c r="D51" s="137"/>
-      <c r="E51" s="138"/>
-      <c r="F51" s="138"/>
-      <c r="G51" s="138"/>
-      <c r="H51" s="138"/>
-      <c r="I51" s="138"/>
-      <c r="J51" s="138"/>
-      <c r="K51" s="138"/>
-      <c r="L51" s="138"/>
+      <c r="D51" s="82"/>
+      <c r="E51" s="83"/>
+      <c r="F51" s="83"/>
+      <c r="G51" s="83"/>
+      <c r="H51" s="83"/>
+      <c r="I51" s="83"/>
+      <c r="J51" s="83"/>
+      <c r="K51" s="83"/>
+      <c r="L51" s="83"/>
     </row>
     <row r="52" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="72">
         <v>27</v>
       </c>
-      <c r="B52" s="172" t="s">
+      <c r="B52" s="77" t="s">
         <v>136</v>
       </c>
       <c r="C52" s="34"/>
-      <c r="D52" s="137"/>
-      <c r="E52" s="138"/>
-      <c r="F52" s="138"/>
-      <c r="G52" s="138"/>
-      <c r="H52" s="138"/>
-      <c r="I52" s="138"/>
-      <c r="J52" s="138"/>
-      <c r="K52" s="138"/>
-      <c r="L52" s="138"/>
+      <c r="D52" s="82"/>
+      <c r="E52" s="83"/>
+      <c r="F52" s="83"/>
+      <c r="G52" s="83"/>
+      <c r="H52" s="83"/>
+      <c r="I52" s="83"/>
+      <c r="J52" s="83"/>
+      <c r="K52" s="83"/>
+      <c r="L52" s="83"/>
     </row>
     <row r="53" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="72">
         <v>28</v>
       </c>
-      <c r="B53" s="173" t="s">
-        <v>143</v>
-      </c>
-      <c r="C53" s="174"/>
-      <c r="D53" s="137"/>
-      <c r="E53" s="138"/>
-      <c r="F53" s="138"/>
-      <c r="G53" s="138"/>
-      <c r="H53" s="138"/>
-      <c r="I53" s="138"/>
-      <c r="J53" s="138"/>
-      <c r="K53" s="138"/>
-      <c r="L53" s="138"/>
+      <c r="B53" s="78" t="s">
+        <v>142</v>
+      </c>
+      <c r="C53" s="79"/>
+      <c r="D53" s="82"/>
+      <c r="E53" s="83"/>
+      <c r="F53" s="83"/>
+      <c r="G53" s="83"/>
+      <c r="H53" s="83"/>
+      <c r="I53" s="83"/>
+      <c r="J53" s="83"/>
+      <c r="K53" s="83"/>
+      <c r="L53" s="83"/>
     </row>
     <row r="54" spans="1:12" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="72">
         <v>29</v>
       </c>
-      <c r="B54" s="173" t="s">
+      <c r="B54" s="78" t="s">
         <v>144</v>
       </c>
       <c r="C54" s="72"/>
-      <c r="D54" s="175"/>
-      <c r="E54" s="176"/>
-      <c r="F54" s="176"/>
-      <c r="G54" s="176"/>
-      <c r="H54" s="176"/>
-      <c r="I54" s="176"/>
-      <c r="J54" s="176"/>
-      <c r="K54" s="176"/>
-      <c r="L54" s="176"/>
+      <c r="D54" s="84"/>
+      <c r="E54" s="85"/>
+      <c r="F54" s="85"/>
+      <c r="G54" s="85"/>
+      <c r="H54" s="85"/>
+      <c r="I54" s="85"/>
+      <c r="J54" s="85"/>
+      <c r="K54" s="85"/>
+      <c r="L54" s="85"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="D26:L54"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:L20"/>
-    <mergeCell ref="D25:L25"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:L22"/>
     <mergeCell ref="A16:L16"/>
     <mergeCell ref="A17:L17"/>
     <mergeCell ref="B15:L15"/>
@@ -12197,6 +12189,14 @@
     <mergeCell ref="B4:L4"/>
     <mergeCell ref="B5:L5"/>
     <mergeCell ref="B7:L7"/>
+    <mergeCell ref="D26:L54"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:L20"/>
+    <mergeCell ref="D25:L25"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:L22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D26" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -15179,50 +15179,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="153" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="149"/>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
-      <c r="F1" s="149"/>
-      <c r="G1" s="149"/>
-      <c r="H1" s="149"/>
-      <c r="I1" s="149"/>
-      <c r="J1" s="149"/>
-      <c r="K1" s="149"/>
-      <c r="L1" s="150"/>
+      <c r="B1" s="154"/>
+      <c r="C1" s="154"/>
+      <c r="D1" s="154"/>
+      <c r="E1" s="154"/>
+      <c r="F1" s="154"/>
+      <c r="G1" s="154"/>
+      <c r="H1" s="154"/>
+      <c r="I1" s="154"/>
+      <c r="J1" s="154"/>
+      <c r="K1" s="154"/>
+      <c r="L1" s="155"/>
     </row>
     <row r="2" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="151" t="s">
+      <c r="A2" s="156" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="152"/>
-      <c r="C2" s="152"/>
-      <c r="D2" s="152"/>
-      <c r="E2" s="152"/>
-      <c r="F2" s="152"/>
-      <c r="G2" s="152"/>
-      <c r="H2" s="152"/>
-      <c r="I2" s="152"/>
-      <c r="J2" s="152"/>
-      <c r="K2" s="152"/>
-      <c r="L2" s="153"/>
+      <c r="B2" s="157"/>
+      <c r="C2" s="157"/>
+      <c r="D2" s="157"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="157"/>
+      <c r="G2" s="157"/>
+      <c r="H2" s="157"/>
+      <c r="I2" s="157"/>
+      <c r="J2" s="157"/>
+      <c r="K2" s="157"/>
+      <c r="L2" s="158"/>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="154"/>
-      <c r="B3" s="155"/>
-      <c r="C3" s="155"/>
-      <c r="D3" s="155"/>
-      <c r="E3" s="155"/>
-      <c r="F3" s="155"/>
-      <c r="G3" s="155"/>
-      <c r="H3" s="155"/>
-      <c r="I3" s="155"/>
-      <c r="J3" s="155"/>
-      <c r="K3" s="155"/>
-      <c r="L3" s="156"/>
+      <c r="A3" s="159"/>
+      <c r="B3" s="160"/>
+      <c r="C3" s="160"/>
+      <c r="D3" s="160"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="160"/>
+      <c r="H3" s="160"/>
+      <c r="I3" s="160"/>
+      <c r="J3" s="160"/>
+      <c r="K3" s="160"/>
+      <c r="L3" s="161"/>
     </row>
     <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
@@ -15312,65 +15312,65 @@
       <c r="A8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="159"/>
-      <c r="C8" s="160"/>
-      <c r="D8" s="160"/>
-      <c r="E8" s="160"/>
-      <c r="F8" s="160"/>
-      <c r="G8" s="160"/>
-      <c r="H8" s="160"/>
-      <c r="I8" s="160"/>
-      <c r="J8" s="160"/>
-      <c r="K8" s="160"/>
-      <c r="L8" s="161"/>
+      <c r="B8" s="164"/>
+      <c r="C8" s="165"/>
+      <c r="D8" s="165"/>
+      <c r="E8" s="165"/>
+      <c r="F8" s="165"/>
+      <c r="G8" s="165"/>
+      <c r="H8" s="165"/>
+      <c r="I8" s="165"/>
+      <c r="J8" s="165"/>
+      <c r="K8" s="165"/>
+      <c r="L8" s="166"/>
     </row>
     <row r="9" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="162"/>
-      <c r="C9" s="160"/>
-      <c r="D9" s="160"/>
-      <c r="E9" s="160"/>
-      <c r="F9" s="160"/>
-      <c r="G9" s="160"/>
-      <c r="H9" s="160"/>
-      <c r="I9" s="160"/>
-      <c r="J9" s="160"/>
-      <c r="K9" s="160"/>
-      <c r="L9" s="161"/>
+      <c r="B9" s="167"/>
+      <c r="C9" s="165"/>
+      <c r="D9" s="165"/>
+      <c r="E9" s="165"/>
+      <c r="F9" s="165"/>
+      <c r="G9" s="165"/>
+      <c r="H9" s="165"/>
+      <c r="I9" s="165"/>
+      <c r="J9" s="165"/>
+      <c r="K9" s="165"/>
+      <c r="L9" s="166"/>
     </row>
     <row r="10" spans="1:12" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="157" t="s">
+      <c r="A10" s="162" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="158"/>
-      <c r="C10" s="158"/>
-      <c r="D10" s="158"/>
-      <c r="E10" s="158"/>
-      <c r="F10" s="158"/>
-      <c r="G10" s="158"/>
-      <c r="H10" s="158"/>
-      <c r="I10" s="158"/>
-      <c r="J10" s="158"/>
-      <c r="K10" s="158"/>
-      <c r="L10" s="158"/>
+      <c r="B10" s="163"/>
+      <c r="C10" s="163"/>
+      <c r="D10" s="163"/>
+      <c r="E10" s="163"/>
+      <c r="F10" s="163"/>
+      <c r="G10" s="163"/>
+      <c r="H10" s="163"/>
+      <c r="I10" s="163"/>
+      <c r="J10" s="163"/>
+      <c r="K10" s="163"/>
+      <c r="L10" s="163"/>
     </row>
     <row r="11" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="139" t="s">
+      <c r="A11" s="144" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="140"/>
-      <c r="C11" s="140"/>
-      <c r="D11" s="140"/>
-      <c r="E11" s="140"/>
-      <c r="F11" s="140"/>
-      <c r="G11" s="140"/>
-      <c r="H11" s="140"/>
-      <c r="I11" s="140"/>
-      <c r="J11" s="140"/>
-      <c r="K11" s="140"/>
-      <c r="L11" s="141"/>
+      <c r="B11" s="145"/>
+      <c r="C11" s="145"/>
+      <c r="D11" s="145"/>
+      <c r="E11" s="145"/>
+      <c r="F11" s="145"/>
+      <c r="G11" s="145"/>
+      <c r="H11" s="145"/>
+      <c r="I11" s="145"/>
+      <c r="J11" s="145"/>
+      <c r="K11" s="145"/>
+      <c r="L11" s="146"/>
     </row>
     <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
@@ -15382,101 +15382,101 @@
       <c r="C12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="119" t="s">
+      <c r="D12" s="94" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="119"/>
-      <c r="F12" s="119"/>
-      <c r="G12" s="119"/>
-      <c r="H12" s="119"/>
-      <c r="I12" s="119"/>
-      <c r="J12" s="119"/>
-      <c r="K12" s="119"/>
-      <c r="L12" s="119"/>
+      <c r="E12" s="94"/>
+      <c r="F12" s="94"/>
+      <c r="G12" s="94"/>
+      <c r="H12" s="94"/>
+      <c r="I12" s="94"/>
+      <c r="J12" s="94"/>
+      <c r="K12" s="94"/>
+      <c r="L12" s="94"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="49"/>
       <c r="B13" s="50"/>
       <c r="C13" s="50"/>
-      <c r="D13" s="142"/>
-      <c r="E13" s="143"/>
-      <c r="F13" s="143"/>
-      <c r="G13" s="143"/>
-      <c r="H13" s="143"/>
-      <c r="I13" s="143"/>
-      <c r="J13" s="143"/>
-      <c r="K13" s="143"/>
-      <c r="L13" s="144"/>
+      <c r="D13" s="147"/>
+      <c r="E13" s="148"/>
+      <c r="F13" s="148"/>
+      <c r="G13" s="148"/>
+      <c r="H13" s="148"/>
+      <c r="I13" s="148"/>
+      <c r="J13" s="148"/>
+      <c r="K13" s="148"/>
+      <c r="L13" s="149"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="49"/>
       <c r="B14" s="50"/>
       <c r="C14" s="50"/>
-      <c r="D14" s="145"/>
-      <c r="E14" s="146"/>
-      <c r="F14" s="146"/>
-      <c r="G14" s="146"/>
-      <c r="H14" s="146"/>
-      <c r="I14" s="146"/>
-      <c r="J14" s="146"/>
-      <c r="K14" s="146"/>
-      <c r="L14" s="147"/>
+      <c r="D14" s="150"/>
+      <c r="E14" s="151"/>
+      <c r="F14" s="151"/>
+      <c r="G14" s="151"/>
+      <c r="H14" s="151"/>
+      <c r="I14" s="151"/>
+      <c r="J14" s="151"/>
+      <c r="K14" s="151"/>
+      <c r="L14" s="152"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="49"/>
       <c r="B15" s="50"/>
       <c r="C15" s="50"/>
-      <c r="D15" s="145"/>
-      <c r="E15" s="146"/>
-      <c r="F15" s="146"/>
-      <c r="G15" s="146"/>
-      <c r="H15" s="146"/>
-      <c r="I15" s="146"/>
-      <c r="J15" s="146"/>
-      <c r="K15" s="146"/>
-      <c r="L15" s="147"/>
+      <c r="D15" s="150"/>
+      <c r="E15" s="151"/>
+      <c r="F15" s="151"/>
+      <c r="G15" s="151"/>
+      <c r="H15" s="151"/>
+      <c r="I15" s="151"/>
+      <c r="J15" s="151"/>
+      <c r="K15" s="151"/>
+      <c r="L15" s="152"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="49"/>
       <c r="B16" s="50"/>
       <c r="C16" s="50"/>
-      <c r="D16" s="145"/>
-      <c r="E16" s="146"/>
-      <c r="F16" s="146"/>
-      <c r="G16" s="146"/>
-      <c r="H16" s="146"/>
-      <c r="I16" s="146"/>
-      <c r="J16" s="146"/>
-      <c r="K16" s="146"/>
-      <c r="L16" s="147"/>
+      <c r="D16" s="150"/>
+      <c r="E16" s="151"/>
+      <c r="F16" s="151"/>
+      <c r="G16" s="151"/>
+      <c r="H16" s="151"/>
+      <c r="I16" s="151"/>
+      <c r="J16" s="151"/>
+      <c r="K16" s="151"/>
+      <c r="L16" s="152"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="49"/>
       <c r="B17" s="50"/>
       <c r="C17" s="50"/>
-      <c r="D17" s="145"/>
-      <c r="E17" s="146"/>
-      <c r="F17" s="146"/>
-      <c r="G17" s="146"/>
-      <c r="H17" s="146"/>
-      <c r="I17" s="146"/>
-      <c r="J17" s="146"/>
-      <c r="K17" s="146"/>
-      <c r="L17" s="147"/>
+      <c r="D17" s="150"/>
+      <c r="E17" s="151"/>
+      <c r="F17" s="151"/>
+      <c r="G17" s="151"/>
+      <c r="H17" s="151"/>
+      <c r="I17" s="151"/>
+      <c r="J17" s="151"/>
+      <c r="K17" s="151"/>
+      <c r="L17" s="152"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="49"/>
       <c r="B18" s="50"/>
       <c r="C18" s="50"/>
-      <c r="D18" s="145"/>
-      <c r="E18" s="146"/>
-      <c r="F18" s="146"/>
-      <c r="G18" s="146"/>
-      <c r="H18" s="146"/>
-      <c r="I18" s="146"/>
-      <c r="J18" s="146"/>
-      <c r="K18" s="146"/>
-      <c r="L18" s="147"/>
+      <c r="D18" s="150"/>
+      <c r="E18" s="151"/>
+      <c r="F18" s="151"/>
+      <c r="G18" s="151"/>
+      <c r="H18" s="151"/>
+      <c r="I18" s="151"/>
+      <c r="J18" s="151"/>
+      <c r="K18" s="151"/>
+      <c r="L18" s="152"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -15565,10 +15565,10 @@
       <c r="B4" s="63"/>
     </row>
     <row r="6" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="A6" s="163" t="s">
+      <c r="A6" s="168" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="163"/>
+      <c r="B6" s="168"/>
     </row>
     <row r="8" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="66" t="s">
@@ -15721,55 +15721,55 @@
   <sheetData>
     <row r="1" spans="2:6" ht="5.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B2" s="165"/>
-      <c r="C2" s="165"/>
-      <c r="D2" s="166" t="s">
+      <c r="B2" s="170"/>
+      <c r="C2" s="170"/>
+      <c r="D2" s="171" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="167" t="s">
+      <c r="E2" s="172" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="167"/>
+      <c r="F2" s="172"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B3" s="165"/>
-      <c r="C3" s="165"/>
-      <c r="D3" s="166"/>
-      <c r="E3" s="167"/>
-      <c r="F3" s="167"/>
+      <c r="B3" s="170"/>
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="172"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="165"/>
-      <c r="C4" s="165"/>
-      <c r="D4" s="166"/>
-      <c r="E4" s="167" t="s">
+      <c r="B4" s="170"/>
+      <c r="C4" s="170"/>
+      <c r="D4" s="171"/>
+      <c r="E4" s="172" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="167"/>
+      <c r="F4" s="172"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="168" t="s">
+      <c r="B5" s="173" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="168"/>
+      <c r="C5" s="173"/>
       <c r="D5" s="70" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="169" t="s">
+      <c r="E5" s="174" t="s">
         <v>54</v>
       </c>
-      <c r="F5" s="169"/>
+      <c r="F5" s="174"/>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="164" t="s">
+      <c r="C6" s="169" t="s">
         <v>114</v>
       </c>
-      <c r="D6" s="164"/>
-      <c r="E6" s="164"/>
-      <c r="F6" s="164"/>
+      <c r="D6" s="169"/>
+      <c r="E6" s="169"/>
+      <c r="F6" s="169"/>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="71" t="s">
@@ -16026,10 +16026,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="27" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="175" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="171"/>
+      <c r="B1" s="176"/>
     </row>
     <row r="2" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="28" t="s">
@@ -16300,6 +16300,68 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50">
+      <UserInfo>
+        <DisplayName>Luis Campos / Logiztik Alliance</DisplayName>
+        <AccountId>265</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Jairo Gonzalez / Logiztik Alliance</DisplayName>
+        <AccountId>322</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>José Ganchozo / Logiztik Alliance</DisplayName>
+        <AccountId>304</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Edwin Casa / Logiztik Alliance</DisplayName>
+        <AccountId>299</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Cristhian Cuichan / Logiztik Alliance</DisplayName>
+        <AccountId>369</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Oscar Yunda /  Logiztik Alliance</DisplayName>
+        <AccountId>355</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Fernando Ordoñez / Logiztik Alliance</DisplayName>
+        <AccountId>321</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Alex Rivera / Logiztik Alliance</DisplayName>
+        <AccountId>370</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <TaxCatchAll xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="87481c51-c14c-4071-bf64-faa2b5708bb6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101005DA7AC6E4F4FAE42B9D9FCD9C82CAAE1" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="553e0bb76796fbad2df2b84fb95dc83d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="87481c51-c14c-4071-bf64-faa2b5708bb6" xmlns:ns3="8029d101-3d2a-47c4-b15f-619642bf5e50" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d87cd7f238c73dc12c577d08dde48736" ns2:_="" ns3:_="">
     <xsd:import namespace="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
@@ -16548,69 +16610,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD069904-634F-48DA-AA92-BAE250498BEE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8029d101-3d2a-47c4-b15f-619642bf5e50"/>
+    <ds:schemaRef ds:uri="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50">
-      <UserInfo>
-        <DisplayName>Luis Campos / Logiztik Alliance</DisplayName>
-        <AccountId>265</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Jairo Gonzalez / Logiztik Alliance</DisplayName>
-        <AccountId>322</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>José Ganchozo / Logiztik Alliance</DisplayName>
-        <AccountId>304</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Edwin Casa / Logiztik Alliance</DisplayName>
-        <AccountId>299</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Cristhian Cuichan / Logiztik Alliance</DisplayName>
-        <AccountId>369</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Oscar Yunda /  Logiztik Alliance</DisplayName>
-        <AccountId>355</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Fernando Ordoñez / Logiztik Alliance</DisplayName>
-        <AccountId>321</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Alex Rivera / Logiztik Alliance</DisplayName>
-        <AccountId>370</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <TaxCatchAll xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="87481c51-c14c-4071-bf64-faa2b5708bb6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371D8832-41B3-447B-B13D-2663C267E34F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F7F06D0-41B3-4EAF-B418-88FC726117CC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -16627,23 +16646,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371D8832-41B3-447B-B13D-2663C267E34F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD069904-634F-48DA-AA92-BAE250498BEE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8029d101-3d2a-47c4-b15f-619642bf5e50"/>
-    <ds:schemaRef ds:uri="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Guias Produccion/HU-57723.xlsx
+++ b/Guias Produccion/HU-57723.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Alliance\ScriptsEntidades\Guias Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B69ABD94-2576-45C3-B8BE-8F3AF5470FE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5745683B-F80A-4243-BD5C-5903C45993AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guia de implementación" sheetId="1" r:id="rId1"/>
@@ -1980,95 +1980,8 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="75" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="76" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="77" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="54" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="78" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="79" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2172,6 +2085,96 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="54" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="78" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="79" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2243,9 +2246,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -11217,42 +11217,42 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:15" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="126" t="s">
+      <c r="A3" s="97" t="s">
         <v>103</v>
       </c>
-      <c r="B3" s="127"/>
-      <c r="C3" s="127"/>
-      <c r="D3" s="127"/>
-      <c r="E3" s="127"/>
-      <c r="F3" s="127"/>
-      <c r="G3" s="127"/>
-      <c r="H3" s="127"/>
-      <c r="I3" s="127"/>
-      <c r="J3" s="127"/>
-      <c r="K3" s="127"/>
-      <c r="L3" s="128"/>
-      <c r="N3" s="120" t="s">
+      <c r="B3" s="98"/>
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="98"/>
+      <c r="J3" s="98"/>
+      <c r="K3" s="98"/>
+      <c r="L3" s="99"/>
+      <c r="N3" s="91" t="s">
         <v>0</v>
       </c>
-      <c r="O3" s="121"/>
+      <c r="O3" s="92"/>
     </row>
     <row r="4" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="133" t="s">
+      <c r="B4" s="104" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="134"/>
-      <c r="D4" s="134"/>
-      <c r="E4" s="134"/>
-      <c r="F4" s="134"/>
-      <c r="G4" s="134"/>
-      <c r="H4" s="134"/>
-      <c r="I4" s="134"/>
-      <c r="J4" s="135"/>
-      <c r="K4" s="135"/>
-      <c r="L4" s="136"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="105"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="105"/>
+      <c r="I4" s="105"/>
+      <c r="J4" s="106"/>
+      <c r="K4" s="106"/>
+      <c r="L4" s="107"/>
       <c r="N4" s="21" t="s">
         <v>2</v>
       </c>
@@ -11262,19 +11262,19 @@
       <c r="A5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="137" t="s">
+      <c r="B5" s="108" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="137"/>
-      <c r="D5" s="137"/>
-      <c r="E5" s="137"/>
-      <c r="F5" s="137"/>
-      <c r="G5" s="137"/>
-      <c r="H5" s="137"/>
-      <c r="I5" s="137"/>
-      <c r="J5" s="138"/>
-      <c r="K5" s="138"/>
-      <c r="L5" s="139"/>
+      <c r="C5" s="108"/>
+      <c r="D5" s="108"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="108"/>
+      <c r="G5" s="108"/>
+      <c r="H5" s="108"/>
+      <c r="I5" s="108"/>
+      <c r="J5" s="109"/>
+      <c r="K5" s="109"/>
+      <c r="L5" s="110"/>
       <c r="N5" s="15" t="s">
         <v>4</v>
       </c>
@@ -11284,19 +11284,19 @@
       <c r="A6" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="123">
+      <c r="B6" s="94">
         <v>46073</v>
       </c>
-      <c r="C6" s="124"/>
-      <c r="D6" s="124"/>
-      <c r="E6" s="124"/>
-      <c r="F6" s="124"/>
-      <c r="G6" s="124"/>
-      <c r="H6" s="124"/>
-      <c r="I6" s="124"/>
-      <c r="J6" s="124"/>
-      <c r="K6" s="124"/>
-      <c r="L6" s="125"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="95"/>
+      <c r="K6" s="95"/>
+      <c r="L6" s="96"/>
       <c r="N6" s="14"/>
       <c r="O6" s="14"/>
     </row>
@@ -11304,17 +11304,17 @@
       <c r="A7" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="140"/>
-      <c r="C7" s="141"/>
-      <c r="D7" s="141"/>
-      <c r="E7" s="141"/>
-      <c r="F7" s="141"/>
-      <c r="G7" s="141"/>
-      <c r="H7" s="141"/>
-      <c r="I7" s="141"/>
-      <c r="J7" s="142"/>
-      <c r="K7" s="142"/>
-      <c r="L7" s="143"/>
+      <c r="B7" s="111"/>
+      <c r="C7" s="112"/>
+      <c r="D7" s="112"/>
+      <c r="E7" s="112"/>
+      <c r="F7" s="112"/>
+      <c r="G7" s="112"/>
+      <c r="H7" s="112"/>
+      <c r="I7" s="112"/>
+      <c r="J7" s="113"/>
+      <c r="K7" s="113"/>
+      <c r="L7" s="114"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
@@ -11331,20 +11331,20 @@
       <c r="L8" s="13"/>
     </row>
     <row r="9" spans="1:15" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="129" t="s">
+      <c r="A9" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="130"/>
-      <c r="C9" s="130"/>
-      <c r="D9" s="130"/>
-      <c r="E9" s="130"/>
-      <c r="F9" s="130"/>
-      <c r="G9" s="130"/>
-      <c r="H9" s="130"/>
-      <c r="I9" s="130"/>
-      <c r="J9" s="131"/>
-      <c r="K9" s="131"/>
-      <c r="L9" s="132"/>
+      <c r="B9" s="101"/>
+      <c r="C9" s="101"/>
+      <c r="D9" s="101"/>
+      <c r="E9" s="101"/>
+      <c r="F9" s="101"/>
+      <c r="G9" s="101"/>
+      <c r="H9" s="101"/>
+      <c r="I9" s="101"/>
+      <c r="J9" s="102"/>
+      <c r="K9" s="102"/>
+      <c r="L9" s="103"/>
     </row>
     <row r="10" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -11444,63 +11444,63 @@
       <c r="A14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="122"/>
-      <c r="C14" s="118"/>
-      <c r="D14" s="118"/>
-      <c r="E14" s="118"/>
-      <c r="F14" s="118"/>
-      <c r="G14" s="118"/>
-      <c r="H14" s="118"/>
-      <c r="I14" s="118"/>
-      <c r="J14" s="118"/>
-      <c r="K14" s="118"/>
-      <c r="L14" s="119"/>
+      <c r="B14" s="93"/>
+      <c r="C14" s="89"/>
+      <c r="D14" s="89"/>
+      <c r="E14" s="89"/>
+      <c r="F14" s="89"/>
+      <c r="G14" s="89"/>
+      <c r="H14" s="89"/>
+      <c r="I14" s="89"/>
+      <c r="J14" s="89"/>
+      <c r="K14" s="89"/>
+      <c r="L14" s="90"/>
     </row>
     <row r="15" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="117"/>
-      <c r="C15" s="118"/>
-      <c r="D15" s="118"/>
-      <c r="E15" s="118"/>
-      <c r="F15" s="118"/>
-      <c r="G15" s="118"/>
-      <c r="H15" s="118"/>
-      <c r="I15" s="118"/>
-      <c r="J15" s="118"/>
-      <c r="K15" s="118"/>
-      <c r="L15" s="119"/>
+      <c r="B15" s="88"/>
+      <c r="C15" s="89"/>
+      <c r="D15" s="89"/>
+      <c r="E15" s="89"/>
+      <c r="F15" s="89"/>
+      <c r="G15" s="89"/>
+      <c r="H15" s="89"/>
+      <c r="I15" s="89"/>
+      <c r="J15" s="89"/>
+      <c r="K15" s="89"/>
+      <c r="L15" s="90"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="110"/>
-      <c r="B16" s="111"/>
-      <c r="C16" s="111"/>
-      <c r="D16" s="111"/>
-      <c r="E16" s="111"/>
-      <c r="F16" s="111"/>
-      <c r="G16" s="111"/>
-      <c r="H16" s="111"/>
-      <c r="I16" s="111"/>
-      <c r="J16" s="111"/>
-      <c r="K16" s="111"/>
-      <c r="L16" s="112"/>
+      <c r="A16" s="81"/>
+      <c r="B16" s="82"/>
+      <c r="C16" s="82"/>
+      <c r="D16" s="82"/>
+      <c r="E16" s="82"/>
+      <c r="F16" s="82"/>
+      <c r="G16" s="82"/>
+      <c r="H16" s="82"/>
+      <c r="I16" s="82"/>
+      <c r="J16" s="82"/>
+      <c r="K16" s="82"/>
+      <c r="L16" s="83"/>
     </row>
     <row r="17" spans="1:12" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="113" t="s">
+      <c r="A17" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="114"/>
-      <c r="C17" s="114"/>
-      <c r="D17" s="114"/>
-      <c r="E17" s="114"/>
-      <c r="F17" s="114"/>
-      <c r="G17" s="114"/>
-      <c r="H17" s="114"/>
-      <c r="I17" s="114"/>
-      <c r="J17" s="115"/>
-      <c r="K17" s="115"/>
-      <c r="L17" s="116"/>
+      <c r="B17" s="85"/>
+      <c r="C17" s="85"/>
+      <c r="D17" s="85"/>
+      <c r="E17" s="85"/>
+      <c r="F17" s="85"/>
+      <c r="G17" s="85"/>
+      <c r="H17" s="85"/>
+      <c r="I17" s="85"/>
+      <c r="J17" s="86"/>
+      <c r="K17" s="86"/>
+      <c r="L17" s="87"/>
     </row>
     <row r="18" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
@@ -11510,19 +11510,19 @@
       <c r="C18" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="86" t="s">
+      <c r="D18" s="121" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="88" t="s">
+      <c r="E18" s="123" t="s">
         <v>137</v>
       </c>
-      <c r="F18" s="88"/>
-      <c r="G18" s="88"/>
-      <c r="H18" s="88"/>
-      <c r="I18" s="88"/>
-      <c r="J18" s="89"/>
-      <c r="K18" s="89"/>
-      <c r="L18" s="90"/>
+      <c r="F18" s="123"/>
+      <c r="G18" s="123"/>
+      <c r="H18" s="123"/>
+      <c r="I18" s="123"/>
+      <c r="J18" s="124"/>
+      <c r="K18" s="124"/>
+      <c r="L18" s="125"/>
     </row>
     <row r="19" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
@@ -11532,15 +11532,15 @@
         <v>30</v>
       </c>
       <c r="C19" s="44"/>
-      <c r="D19" s="87"/>
-      <c r="E19" s="91"/>
-      <c r="F19" s="91"/>
-      <c r="G19" s="91"/>
-      <c r="H19" s="91"/>
-      <c r="I19" s="91"/>
-      <c r="J19" s="92"/>
-      <c r="K19" s="92"/>
-      <c r="L19" s="93"/>
+      <c r="D19" s="122"/>
+      <c r="E19" s="126"/>
+      <c r="F19" s="126"/>
+      <c r="G19" s="126"/>
+      <c r="H19" s="126"/>
+      <c r="I19" s="126"/>
+      <c r="J19" s="127"/>
+      <c r="K19" s="127"/>
+      <c r="L19" s="128"/>
     </row>
     <row r="20" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
@@ -11550,15 +11550,15 @@
       <c r="C20" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="87"/>
-      <c r="E20" s="91"/>
-      <c r="F20" s="91"/>
-      <c r="G20" s="91"/>
-      <c r="H20" s="91"/>
-      <c r="I20" s="91"/>
-      <c r="J20" s="92"/>
-      <c r="K20" s="92"/>
-      <c r="L20" s="93"/>
+      <c r="D20" s="122"/>
+      <c r="E20" s="126"/>
+      <c r="F20" s="126"/>
+      <c r="G20" s="126"/>
+      <c r="H20" s="126"/>
+      <c r="I20" s="126"/>
+      <c r="J20" s="127"/>
+      <c r="K20" s="127"/>
+      <c r="L20" s="128"/>
     </row>
     <row r="21" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
@@ -11568,19 +11568,19 @@
       <c r="C21" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="102" t="s">
+      <c r="D21" s="137" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="104" t="s">
+      <c r="E21" s="139" t="s">
         <v>107</v>
       </c>
-      <c r="F21" s="105"/>
-      <c r="G21" s="105"/>
-      <c r="H21" s="105"/>
-      <c r="I21" s="105"/>
-      <c r="J21" s="105"/>
-      <c r="K21" s="105"/>
-      <c r="L21" s="106"/>
+      <c r="F21" s="140"/>
+      <c r="G21" s="140"/>
+      <c r="H21" s="140"/>
+      <c r="I21" s="140"/>
+      <c r="J21" s="140"/>
+      <c r="K21" s="140"/>
+      <c r="L21" s="141"/>
     </row>
     <row r="22" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
@@ -11590,45 +11590,45 @@
       <c r="C22" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="103"/>
-      <c r="E22" s="107"/>
-      <c r="F22" s="108"/>
-      <c r="G22" s="108"/>
-      <c r="H22" s="108"/>
-      <c r="I22" s="108"/>
-      <c r="J22" s="108"/>
-      <c r="K22" s="108"/>
-      <c r="L22" s="109"/>
+      <c r="D22" s="138"/>
+      <c r="E22" s="142"/>
+      <c r="F22" s="143"/>
+      <c r="G22" s="143"/>
+      <c r="H22" s="143"/>
+      <c r="I22" s="143"/>
+      <c r="J22" s="143"/>
+      <c r="K22" s="143"/>
+      <c r="L22" s="144"/>
     </row>
     <row r="23" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="95"/>
-      <c r="B23" s="96"/>
-      <c r="C23" s="96"/>
-      <c r="D23" s="97"/>
-      <c r="E23" s="97"/>
-      <c r="F23" s="97"/>
-      <c r="G23" s="97"/>
-      <c r="H23" s="97"/>
-      <c r="I23" s="97"/>
-      <c r="J23" s="97"/>
-      <c r="K23" s="97"/>
-      <c r="L23" s="98"/>
+      <c r="A23" s="130"/>
+      <c r="B23" s="131"/>
+      <c r="C23" s="131"/>
+      <c r="D23" s="132"/>
+      <c r="E23" s="132"/>
+      <c r="F23" s="132"/>
+      <c r="G23" s="132"/>
+      <c r="H23" s="132"/>
+      <c r="I23" s="132"/>
+      <c r="J23" s="132"/>
+      <c r="K23" s="132"/>
+      <c r="L23" s="133"/>
     </row>
     <row r="24" spans="1:12" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="99" t="s">
+      <c r="A24" s="134" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="100"/>
-      <c r="C24" s="100"/>
-      <c r="D24" s="100"/>
-      <c r="E24" s="100"/>
-      <c r="F24" s="100"/>
-      <c r="G24" s="100"/>
-      <c r="H24" s="100"/>
-      <c r="I24" s="100"/>
-      <c r="J24" s="100"/>
-      <c r="K24" s="100"/>
-      <c r="L24" s="101"/>
+      <c r="B24" s="135"/>
+      <c r="C24" s="135"/>
+      <c r="D24" s="135"/>
+      <c r="E24" s="135"/>
+      <c r="F24" s="135"/>
+      <c r="G24" s="135"/>
+      <c r="H24" s="135"/>
+      <c r="I24" s="135"/>
+      <c r="J24" s="135"/>
+      <c r="K24" s="135"/>
+      <c r="L24" s="136"/>
     </row>
     <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
@@ -11640,17 +11640,17 @@
       <c r="C25" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="94" t="s">
+      <c r="D25" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="E25" s="94"/>
-      <c r="F25" s="94"/>
-      <c r="G25" s="94"/>
-      <c r="H25" s="94"/>
-      <c r="I25" s="94"/>
-      <c r="J25" s="94"/>
-      <c r="K25" s="94"/>
-      <c r="L25" s="94"/>
+      <c r="E25" s="129"/>
+      <c r="F25" s="129"/>
+      <c r="G25" s="129"/>
+      <c r="H25" s="129"/>
+      <c r="I25" s="129"/>
+      <c r="J25" s="129"/>
+      <c r="K25" s="129"/>
+      <c r="L25" s="129"/>
     </row>
     <row r="26" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="33">
@@ -11660,17 +11660,17 @@
         <v>115</v>
       </c>
       <c r="C26" s="34"/>
-      <c r="D26" s="80" t="s">
+      <c r="D26" s="115" t="s">
         <v>108</v>
       </c>
-      <c r="E26" s="81"/>
-      <c r="F26" s="81"/>
-      <c r="G26" s="81"/>
-      <c r="H26" s="81"/>
-      <c r="I26" s="81"/>
-      <c r="J26" s="81"/>
-      <c r="K26" s="81"/>
-      <c r="L26" s="81"/>
+      <c r="E26" s="116"/>
+      <c r="F26" s="116"/>
+      <c r="G26" s="116"/>
+      <c r="H26" s="116"/>
+      <c r="I26" s="116"/>
+      <c r="J26" s="116"/>
+      <c r="K26" s="116"/>
+      <c r="L26" s="116"/>
     </row>
     <row r="27" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
@@ -11680,15 +11680,15 @@
         <v>116</v>
       </c>
       <c r="C27" s="34"/>
-      <c r="D27" s="82"/>
-      <c r="E27" s="83"/>
-      <c r="F27" s="83"/>
-      <c r="G27" s="83"/>
-      <c r="H27" s="83"/>
-      <c r="I27" s="83"/>
-      <c r="J27" s="83"/>
-      <c r="K27" s="83"/>
-      <c r="L27" s="83"/>
+      <c r="D27" s="117"/>
+      <c r="E27" s="118"/>
+      <c r="F27" s="118"/>
+      <c r="G27" s="118"/>
+      <c r="H27" s="118"/>
+      <c r="I27" s="118"/>
+      <c r="J27" s="118"/>
+      <c r="K27" s="118"/>
+      <c r="L27" s="118"/>
     </row>
     <row r="28" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="33">
@@ -11698,15 +11698,15 @@
         <v>117</v>
       </c>
       <c r="C28" s="34"/>
-      <c r="D28" s="82"/>
-      <c r="E28" s="83"/>
-      <c r="F28" s="83"/>
-      <c r="G28" s="83"/>
-      <c r="H28" s="83"/>
-      <c r="I28" s="83"/>
-      <c r="J28" s="83"/>
-      <c r="K28" s="83"/>
-      <c r="L28" s="83"/>
+      <c r="D28" s="117"/>
+      <c r="E28" s="118"/>
+      <c r="F28" s="118"/>
+      <c r="G28" s="118"/>
+      <c r="H28" s="118"/>
+      <c r="I28" s="118"/>
+      <c r="J28" s="118"/>
+      <c r="K28" s="118"/>
+      <c r="L28" s="118"/>
     </row>
     <row r="29" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
@@ -11716,15 +11716,15 @@
         <v>138</v>
       </c>
       <c r="C29" s="34"/>
-      <c r="D29" s="82"/>
-      <c r="E29" s="83"/>
-      <c r="F29" s="83"/>
-      <c r="G29" s="83"/>
-      <c r="H29" s="83"/>
-      <c r="I29" s="83"/>
-      <c r="J29" s="83"/>
-      <c r="K29" s="83"/>
-      <c r="L29" s="83"/>
+      <c r="D29" s="117"/>
+      <c r="E29" s="118"/>
+      <c r="F29" s="118"/>
+      <c r="G29" s="118"/>
+      <c r="H29" s="118"/>
+      <c r="I29" s="118"/>
+      <c r="J29" s="118"/>
+      <c r="K29" s="118"/>
+      <c r="L29" s="118"/>
     </row>
     <row r="30" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="33">
@@ -11734,15 +11734,15 @@
         <v>118</v>
       </c>
       <c r="C30" s="34"/>
-      <c r="D30" s="82"/>
-      <c r="E30" s="83"/>
-      <c r="F30" s="83"/>
-      <c r="G30" s="83"/>
-      <c r="H30" s="83"/>
-      <c r="I30" s="83"/>
-      <c r="J30" s="83"/>
-      <c r="K30" s="83"/>
-      <c r="L30" s="83"/>
+      <c r="D30" s="117"/>
+      <c r="E30" s="118"/>
+      <c r="F30" s="118"/>
+      <c r="G30" s="118"/>
+      <c r="H30" s="118"/>
+      <c r="I30" s="118"/>
+      <c r="J30" s="118"/>
+      <c r="K30" s="118"/>
+      <c r="L30" s="118"/>
     </row>
     <row r="31" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="33">
@@ -11752,15 +11752,15 @@
         <v>119</v>
       </c>
       <c r="C31" s="34"/>
-      <c r="D31" s="82"/>
-      <c r="E31" s="83"/>
-      <c r="F31" s="83"/>
-      <c r="G31" s="83"/>
-      <c r="H31" s="83"/>
-      <c r="I31" s="83"/>
-      <c r="J31" s="83"/>
-      <c r="K31" s="83"/>
-      <c r="L31" s="83"/>
+      <c r="D31" s="117"/>
+      <c r="E31" s="118"/>
+      <c r="F31" s="118"/>
+      <c r="G31" s="118"/>
+      <c r="H31" s="118"/>
+      <c r="I31" s="118"/>
+      <c r="J31" s="118"/>
+      <c r="K31" s="118"/>
+      <c r="L31" s="118"/>
     </row>
     <row r="32" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="33">
@@ -11770,15 +11770,15 @@
         <v>120</v>
       </c>
       <c r="C32" s="34"/>
-      <c r="D32" s="82"/>
-      <c r="E32" s="83"/>
-      <c r="F32" s="83"/>
-      <c r="G32" s="83"/>
-      <c r="H32" s="83"/>
-      <c r="I32" s="83"/>
-      <c r="J32" s="83"/>
-      <c r="K32" s="83"/>
-      <c r="L32" s="83"/>
+      <c r="D32" s="117"/>
+      <c r="E32" s="118"/>
+      <c r="F32" s="118"/>
+      <c r="G32" s="118"/>
+      <c r="H32" s="118"/>
+      <c r="I32" s="118"/>
+      <c r="J32" s="118"/>
+      <c r="K32" s="118"/>
+      <c r="L32" s="118"/>
     </row>
     <row r="33" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="33">
@@ -11788,15 +11788,15 @@
         <v>121</v>
       </c>
       <c r="C33" s="34"/>
-      <c r="D33" s="82"/>
-      <c r="E33" s="83"/>
-      <c r="F33" s="83"/>
-      <c r="G33" s="83"/>
-      <c r="H33" s="83"/>
-      <c r="I33" s="83"/>
-      <c r="J33" s="83"/>
-      <c r="K33" s="83"/>
-      <c r="L33" s="83"/>
+      <c r="D33" s="117"/>
+      <c r="E33" s="118"/>
+      <c r="F33" s="118"/>
+      <c r="G33" s="118"/>
+      <c r="H33" s="118"/>
+      <c r="I33" s="118"/>
+      <c r="J33" s="118"/>
+      <c r="K33" s="118"/>
+      <c r="L33" s="118"/>
     </row>
     <row r="34" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="33">
@@ -11806,15 +11806,15 @@
         <v>122</v>
       </c>
       <c r="C34" s="34"/>
-      <c r="D34" s="82"/>
-      <c r="E34" s="83"/>
-      <c r="F34" s="83"/>
-      <c r="G34" s="83"/>
-      <c r="H34" s="83"/>
-      <c r="I34" s="83"/>
-      <c r="J34" s="83"/>
-      <c r="K34" s="83"/>
-      <c r="L34" s="83"/>
+      <c r="D34" s="117"/>
+      <c r="E34" s="118"/>
+      <c r="F34" s="118"/>
+      <c r="G34" s="118"/>
+      <c r="H34" s="118"/>
+      <c r="I34" s="118"/>
+      <c r="J34" s="118"/>
+      <c r="K34" s="118"/>
+      <c r="L34" s="118"/>
     </row>
     <row r="35" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="33">
@@ -11824,15 +11824,15 @@
         <v>123</v>
       </c>
       <c r="C35" s="34"/>
-      <c r="D35" s="82"/>
-      <c r="E35" s="83"/>
-      <c r="F35" s="83"/>
-      <c r="G35" s="83"/>
-      <c r="H35" s="83"/>
-      <c r="I35" s="83"/>
-      <c r="J35" s="83"/>
-      <c r="K35" s="83"/>
-      <c r="L35" s="83"/>
+      <c r="D35" s="117"/>
+      <c r="E35" s="118"/>
+      <c r="F35" s="118"/>
+      <c r="G35" s="118"/>
+      <c r="H35" s="118"/>
+      <c r="I35" s="118"/>
+      <c r="J35" s="118"/>
+      <c r="K35" s="118"/>
+      <c r="L35" s="118"/>
     </row>
     <row r="36" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="33">
@@ -11842,15 +11842,15 @@
         <v>124</v>
       </c>
       <c r="C36" s="34"/>
-      <c r="D36" s="82"/>
-      <c r="E36" s="83"/>
-      <c r="F36" s="83"/>
-      <c r="G36" s="83"/>
-      <c r="H36" s="83"/>
-      <c r="I36" s="83"/>
-      <c r="J36" s="83"/>
-      <c r="K36" s="83"/>
-      <c r="L36" s="83"/>
+      <c r="D36" s="117"/>
+      <c r="E36" s="118"/>
+      <c r="F36" s="118"/>
+      <c r="G36" s="118"/>
+      <c r="H36" s="118"/>
+      <c r="I36" s="118"/>
+      <c r="J36" s="118"/>
+      <c r="K36" s="118"/>
+      <c r="L36" s="118"/>
     </row>
     <row r="37" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="33">
@@ -11860,15 +11860,15 @@
         <v>139</v>
       </c>
       <c r="C37" s="34"/>
-      <c r="D37" s="82"/>
-      <c r="E37" s="83"/>
-      <c r="F37" s="83"/>
-      <c r="G37" s="83"/>
-      <c r="H37" s="83"/>
-      <c r="I37" s="83"/>
-      <c r="J37" s="83"/>
-      <c r="K37" s="83"/>
-      <c r="L37" s="83"/>
+      <c r="D37" s="117"/>
+      <c r="E37" s="118"/>
+      <c r="F37" s="118"/>
+      <c r="G37" s="118"/>
+      <c r="H37" s="118"/>
+      <c r="I37" s="118"/>
+      <c r="J37" s="118"/>
+      <c r="K37" s="118"/>
+      <c r="L37" s="118"/>
     </row>
     <row r="38" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="33">
@@ -11878,15 +11878,15 @@
         <v>125</v>
       </c>
       <c r="C38" s="34"/>
-      <c r="D38" s="82"/>
-      <c r="E38" s="83"/>
-      <c r="F38" s="83"/>
-      <c r="G38" s="83"/>
-      <c r="H38" s="83"/>
-      <c r="I38" s="83"/>
-      <c r="J38" s="83"/>
-      <c r="K38" s="83"/>
-      <c r="L38" s="83"/>
+      <c r="D38" s="117"/>
+      <c r="E38" s="118"/>
+      <c r="F38" s="118"/>
+      <c r="G38" s="118"/>
+      <c r="H38" s="118"/>
+      <c r="I38" s="118"/>
+      <c r="J38" s="118"/>
+      <c r="K38" s="118"/>
+      <c r="L38" s="118"/>
     </row>
     <row r="39" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="33">
@@ -11896,15 +11896,15 @@
         <v>126</v>
       </c>
       <c r="C39" s="34"/>
-      <c r="D39" s="82"/>
-      <c r="E39" s="83"/>
-      <c r="F39" s="83"/>
-      <c r="G39" s="83"/>
-      <c r="H39" s="83"/>
-      <c r="I39" s="83"/>
-      <c r="J39" s="83"/>
-      <c r="K39" s="83"/>
-      <c r="L39" s="83"/>
+      <c r="D39" s="117"/>
+      <c r="E39" s="118"/>
+      <c r="F39" s="118"/>
+      <c r="G39" s="118"/>
+      <c r="H39" s="118"/>
+      <c r="I39" s="118"/>
+      <c r="J39" s="118"/>
+      <c r="K39" s="118"/>
+      <c r="L39" s="118"/>
     </row>
     <row r="40" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="33">
@@ -11914,15 +11914,15 @@
         <v>127</v>
       </c>
       <c r="C40" s="34"/>
-      <c r="D40" s="82"/>
-      <c r="E40" s="83"/>
-      <c r="F40" s="83"/>
-      <c r="G40" s="83"/>
-      <c r="H40" s="83"/>
-      <c r="I40" s="83"/>
-      <c r="J40" s="83"/>
-      <c r="K40" s="83"/>
-      <c r="L40" s="83"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="118"/>
+      <c r="H40" s="118"/>
+      <c r="I40" s="118"/>
+      <c r="J40" s="118"/>
+      <c r="K40" s="118"/>
+      <c r="L40" s="118"/>
     </row>
     <row r="41" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="33">
@@ -11932,15 +11932,15 @@
         <v>128</v>
       </c>
       <c r="C41" s="34"/>
-      <c r="D41" s="82"/>
-      <c r="E41" s="83"/>
-      <c r="F41" s="83"/>
-      <c r="G41" s="83"/>
-      <c r="H41" s="83"/>
-      <c r="I41" s="83"/>
-      <c r="J41" s="83"/>
-      <c r="K41" s="83"/>
-      <c r="L41" s="83"/>
+      <c r="D41" s="117"/>
+      <c r="E41" s="118"/>
+      <c r="F41" s="118"/>
+      <c r="G41" s="118"/>
+      <c r="H41" s="118"/>
+      <c r="I41" s="118"/>
+      <c r="J41" s="118"/>
+      <c r="K41" s="118"/>
+      <c r="L41" s="118"/>
     </row>
     <row r="42" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="33">
@@ -11950,15 +11950,15 @@
         <v>140</v>
       </c>
       <c r="C42" s="34"/>
-      <c r="D42" s="82"/>
-      <c r="E42" s="83"/>
-      <c r="F42" s="83"/>
-      <c r="G42" s="83"/>
-      <c r="H42" s="83"/>
-      <c r="I42" s="83"/>
-      <c r="J42" s="83"/>
-      <c r="K42" s="83"/>
-      <c r="L42" s="83"/>
+      <c r="D42" s="117"/>
+      <c r="E42" s="118"/>
+      <c r="F42" s="118"/>
+      <c r="G42" s="118"/>
+      <c r="H42" s="118"/>
+      <c r="I42" s="118"/>
+      <c r="J42" s="118"/>
+      <c r="K42" s="118"/>
+      <c r="L42" s="118"/>
     </row>
     <row r="43" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="33">
@@ -11968,15 +11968,15 @@
         <v>141</v>
       </c>
       <c r="C43" s="34"/>
-      <c r="D43" s="82"/>
-      <c r="E43" s="83"/>
-      <c r="F43" s="83"/>
-      <c r="G43" s="83"/>
-      <c r="H43" s="83"/>
-      <c r="I43" s="83"/>
-      <c r="J43" s="83"/>
-      <c r="K43" s="83"/>
-      <c r="L43" s="83"/>
+      <c r="D43" s="117"/>
+      <c r="E43" s="118"/>
+      <c r="F43" s="118"/>
+      <c r="G43" s="118"/>
+      <c r="H43" s="118"/>
+      <c r="I43" s="118"/>
+      <c r="J43" s="118"/>
+      <c r="K43" s="118"/>
+      <c r="L43" s="118"/>
     </row>
     <row r="44" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="33">
@@ -11986,15 +11986,15 @@
         <v>129</v>
       </c>
       <c r="C44" s="34"/>
-      <c r="D44" s="82"/>
-      <c r="E44" s="83"/>
-      <c r="F44" s="83"/>
-      <c r="G44" s="83"/>
-      <c r="H44" s="83"/>
-      <c r="I44" s="83"/>
-      <c r="J44" s="83"/>
-      <c r="K44" s="83"/>
-      <c r="L44" s="83"/>
+      <c r="D44" s="117"/>
+      <c r="E44" s="118"/>
+      <c r="F44" s="118"/>
+      <c r="G44" s="118"/>
+      <c r="H44" s="118"/>
+      <c r="I44" s="118"/>
+      <c r="J44" s="118"/>
+      <c r="K44" s="118"/>
+      <c r="L44" s="118"/>
     </row>
     <row r="45" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="33">
@@ -12004,15 +12004,15 @@
         <v>130</v>
       </c>
       <c r="C45" s="34"/>
-      <c r="D45" s="82"/>
-      <c r="E45" s="83"/>
-      <c r="F45" s="83"/>
-      <c r="G45" s="83"/>
-      <c r="H45" s="83"/>
-      <c r="I45" s="83"/>
-      <c r="J45" s="83"/>
-      <c r="K45" s="83"/>
-      <c r="L45" s="83"/>
+      <c r="D45" s="117"/>
+      <c r="E45" s="118"/>
+      <c r="F45" s="118"/>
+      <c r="G45" s="118"/>
+      <c r="H45" s="118"/>
+      <c r="I45" s="118"/>
+      <c r="J45" s="118"/>
+      <c r="K45" s="118"/>
+      <c r="L45" s="118"/>
     </row>
     <row r="46" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="33">
@@ -12022,15 +12022,15 @@
         <v>131</v>
       </c>
       <c r="C46" s="34"/>
-      <c r="D46" s="82"/>
-      <c r="E46" s="83"/>
-      <c r="F46" s="83"/>
-      <c r="G46" s="83"/>
-      <c r="H46" s="83"/>
-      <c r="I46" s="83"/>
-      <c r="J46" s="83"/>
-      <c r="K46" s="83"/>
-      <c r="L46" s="83"/>
+      <c r="D46" s="117"/>
+      <c r="E46" s="118"/>
+      <c r="F46" s="118"/>
+      <c r="G46" s="118"/>
+      <c r="H46" s="118"/>
+      <c r="I46" s="118"/>
+      <c r="J46" s="118"/>
+      <c r="K46" s="118"/>
+      <c r="L46" s="118"/>
     </row>
     <row r="47" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="33">
@@ -12040,15 +12040,15 @@
         <v>132</v>
       </c>
       <c r="C47" s="34"/>
-      <c r="D47" s="82"/>
-      <c r="E47" s="83"/>
-      <c r="F47" s="83"/>
-      <c r="G47" s="83"/>
-      <c r="H47" s="83"/>
-      <c r="I47" s="83"/>
-      <c r="J47" s="83"/>
-      <c r="K47" s="83"/>
-      <c r="L47" s="83"/>
+      <c r="D47" s="117"/>
+      <c r="E47" s="118"/>
+      <c r="F47" s="118"/>
+      <c r="G47" s="118"/>
+      <c r="H47" s="118"/>
+      <c r="I47" s="118"/>
+      <c r="J47" s="118"/>
+      <c r="K47" s="118"/>
+      <c r="L47" s="118"/>
     </row>
     <row r="48" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="33">
@@ -12058,15 +12058,15 @@
         <v>133</v>
       </c>
       <c r="C48" s="34"/>
-      <c r="D48" s="82"/>
-      <c r="E48" s="83"/>
-      <c r="F48" s="83"/>
-      <c r="G48" s="83"/>
-      <c r="H48" s="83"/>
-      <c r="I48" s="83"/>
-      <c r="J48" s="83"/>
-      <c r="K48" s="83"/>
-      <c r="L48" s="83"/>
+      <c r="D48" s="117"/>
+      <c r="E48" s="118"/>
+      <c r="F48" s="118"/>
+      <c r="G48" s="118"/>
+      <c r="H48" s="118"/>
+      <c r="I48" s="118"/>
+      <c r="J48" s="118"/>
+      <c r="K48" s="118"/>
+      <c r="L48" s="118"/>
     </row>
     <row r="49" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="33">
@@ -12076,15 +12076,15 @@
         <v>143</v>
       </c>
       <c r="C49" s="34"/>
-      <c r="D49" s="82"/>
-      <c r="E49" s="83"/>
-      <c r="F49" s="83"/>
-      <c r="G49" s="83"/>
-      <c r="H49" s="83"/>
-      <c r="I49" s="83"/>
-      <c r="J49" s="83"/>
-      <c r="K49" s="83"/>
-      <c r="L49" s="83"/>
+      <c r="D49" s="117"/>
+      <c r="E49" s="118"/>
+      <c r="F49" s="118"/>
+      <c r="G49" s="118"/>
+      <c r="H49" s="118"/>
+      <c r="I49" s="118"/>
+      <c r="J49" s="118"/>
+      <c r="K49" s="118"/>
+      <c r="L49" s="118"/>
     </row>
     <row r="50" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="72">
@@ -12094,15 +12094,15 @@
         <v>134</v>
       </c>
       <c r="C50" s="34"/>
-      <c r="D50" s="82"/>
-      <c r="E50" s="83"/>
-      <c r="F50" s="83"/>
-      <c r="G50" s="83"/>
-      <c r="H50" s="83"/>
-      <c r="I50" s="83"/>
-      <c r="J50" s="83"/>
-      <c r="K50" s="83"/>
-      <c r="L50" s="83"/>
+      <c r="D50" s="117"/>
+      <c r="E50" s="118"/>
+      <c r="F50" s="118"/>
+      <c r="G50" s="118"/>
+      <c r="H50" s="118"/>
+      <c r="I50" s="118"/>
+      <c r="J50" s="118"/>
+      <c r="K50" s="118"/>
+      <c r="L50" s="118"/>
     </row>
     <row r="51" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="72">
@@ -12112,15 +12112,15 @@
         <v>135</v>
       </c>
       <c r="C51" s="34"/>
-      <c r="D51" s="82"/>
-      <c r="E51" s="83"/>
-      <c r="F51" s="83"/>
-      <c r="G51" s="83"/>
-      <c r="H51" s="83"/>
-      <c r="I51" s="83"/>
-      <c r="J51" s="83"/>
-      <c r="K51" s="83"/>
-      <c r="L51" s="83"/>
+      <c r="D51" s="117"/>
+      <c r="E51" s="118"/>
+      <c r="F51" s="118"/>
+      <c r="G51" s="118"/>
+      <c r="H51" s="118"/>
+      <c r="I51" s="118"/>
+      <c r="J51" s="118"/>
+      <c r="K51" s="118"/>
+      <c r="L51" s="118"/>
     </row>
     <row r="52" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="72">
@@ -12130,15 +12130,15 @@
         <v>136</v>
       </c>
       <c r="C52" s="34"/>
-      <c r="D52" s="82"/>
-      <c r="E52" s="83"/>
-      <c r="F52" s="83"/>
-      <c r="G52" s="83"/>
-      <c r="H52" s="83"/>
-      <c r="I52" s="83"/>
-      <c r="J52" s="83"/>
-      <c r="K52" s="83"/>
-      <c r="L52" s="83"/>
+      <c r="D52" s="117"/>
+      <c r="E52" s="118"/>
+      <c r="F52" s="118"/>
+      <c r="G52" s="118"/>
+      <c r="H52" s="118"/>
+      <c r="I52" s="118"/>
+      <c r="J52" s="118"/>
+      <c r="K52" s="118"/>
+      <c r="L52" s="118"/>
     </row>
     <row r="53" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="72">
@@ -12148,15 +12148,15 @@
         <v>142</v>
       </c>
       <c r="C53" s="79"/>
-      <c r="D53" s="82"/>
-      <c r="E53" s="83"/>
-      <c r="F53" s="83"/>
-      <c r="G53" s="83"/>
-      <c r="H53" s="83"/>
-      <c r="I53" s="83"/>
-      <c r="J53" s="83"/>
-      <c r="K53" s="83"/>
-      <c r="L53" s="83"/>
+      <c r="D53" s="117"/>
+      <c r="E53" s="118"/>
+      <c r="F53" s="118"/>
+      <c r="G53" s="118"/>
+      <c r="H53" s="118"/>
+      <c r="I53" s="118"/>
+      <c r="J53" s="118"/>
+      <c r="K53" s="118"/>
+      <c r="L53" s="118"/>
     </row>
     <row r="54" spans="1:12" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="72">
@@ -12166,18 +12166,26 @@
         <v>144</v>
       </c>
       <c r="C54" s="72"/>
-      <c r="D54" s="84"/>
-      <c r="E54" s="85"/>
-      <c r="F54" s="85"/>
-      <c r="G54" s="85"/>
-      <c r="H54" s="85"/>
-      <c r="I54" s="85"/>
-      <c r="J54" s="85"/>
-      <c r="K54" s="85"/>
-      <c r="L54" s="85"/>
+      <c r="D54" s="119"/>
+      <c r="E54" s="120"/>
+      <c r="F54" s="120"/>
+      <c r="G54" s="120"/>
+      <c r="H54" s="120"/>
+      <c r="I54" s="120"/>
+      <c r="J54" s="120"/>
+      <c r="K54" s="120"/>
+      <c r="L54" s="120"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="D26:L54"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:L20"/>
+    <mergeCell ref="D25:L25"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:L22"/>
     <mergeCell ref="A16:L16"/>
     <mergeCell ref="A17:L17"/>
     <mergeCell ref="B15:L15"/>
@@ -12189,14 +12197,6 @@
     <mergeCell ref="B4:L4"/>
     <mergeCell ref="B5:L5"/>
     <mergeCell ref="B7:L7"/>
-    <mergeCell ref="D26:L54"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:L20"/>
-    <mergeCell ref="D25:L25"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:L22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D26" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -15179,50 +15179,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="153" t="s">
+      <c r="A1" s="154" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="154"/>
-      <c r="C1" s="154"/>
-      <c r="D1" s="154"/>
-      <c r="E1" s="154"/>
-      <c r="F1" s="154"/>
-      <c r="G1" s="154"/>
-      <c r="H1" s="154"/>
-      <c r="I1" s="154"/>
-      <c r="J1" s="154"/>
-      <c r="K1" s="154"/>
-      <c r="L1" s="155"/>
+      <c r="B1" s="155"/>
+      <c r="C1" s="155"/>
+      <c r="D1" s="155"/>
+      <c r="E1" s="155"/>
+      <c r="F1" s="155"/>
+      <c r="G1" s="155"/>
+      <c r="H1" s="155"/>
+      <c r="I1" s="155"/>
+      <c r="J1" s="155"/>
+      <c r="K1" s="155"/>
+      <c r="L1" s="156"/>
     </row>
     <row r="2" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="156" t="s">
+      <c r="A2" s="157" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="157"/>
-      <c r="C2" s="157"/>
-      <c r="D2" s="157"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157"/>
-      <c r="J2" s="157"/>
-      <c r="K2" s="157"/>
-      <c r="L2" s="158"/>
+      <c r="B2" s="158"/>
+      <c r="C2" s="158"/>
+      <c r="D2" s="158"/>
+      <c r="E2" s="158"/>
+      <c r="F2" s="158"/>
+      <c r="G2" s="158"/>
+      <c r="H2" s="158"/>
+      <c r="I2" s="158"/>
+      <c r="J2" s="158"/>
+      <c r="K2" s="158"/>
+      <c r="L2" s="159"/>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="159"/>
-      <c r="B3" s="160"/>
-      <c r="C3" s="160"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="160"/>
-      <c r="H3" s="160"/>
-      <c r="I3" s="160"/>
-      <c r="J3" s="160"/>
-      <c r="K3" s="160"/>
-      <c r="L3" s="161"/>
+      <c r="A3" s="160"/>
+      <c r="B3" s="161"/>
+      <c r="C3" s="161"/>
+      <c r="D3" s="161"/>
+      <c r="E3" s="161"/>
+      <c r="F3" s="161"/>
+      <c r="G3" s="161"/>
+      <c r="H3" s="161"/>
+      <c r="I3" s="161"/>
+      <c r="J3" s="161"/>
+      <c r="K3" s="161"/>
+      <c r="L3" s="162"/>
     </row>
     <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
@@ -15312,65 +15312,65 @@
       <c r="A8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="164"/>
-      <c r="C8" s="165"/>
-      <c r="D8" s="165"/>
-      <c r="E8" s="165"/>
-      <c r="F8" s="165"/>
-      <c r="G8" s="165"/>
-      <c r="H8" s="165"/>
-      <c r="I8" s="165"/>
-      <c r="J8" s="165"/>
-      <c r="K8" s="165"/>
-      <c r="L8" s="166"/>
+      <c r="B8" s="165"/>
+      <c r="C8" s="166"/>
+      <c r="D8" s="166"/>
+      <c r="E8" s="166"/>
+      <c r="F8" s="166"/>
+      <c r="G8" s="166"/>
+      <c r="H8" s="166"/>
+      <c r="I8" s="166"/>
+      <c r="J8" s="166"/>
+      <c r="K8" s="166"/>
+      <c r="L8" s="167"/>
     </row>
     <row r="9" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="167"/>
-      <c r="C9" s="165"/>
-      <c r="D9" s="165"/>
-      <c r="E9" s="165"/>
-      <c r="F9" s="165"/>
-      <c r="G9" s="165"/>
-      <c r="H9" s="165"/>
-      <c r="I9" s="165"/>
-      <c r="J9" s="165"/>
-      <c r="K9" s="165"/>
-      <c r="L9" s="166"/>
+      <c r="B9" s="168"/>
+      <c r="C9" s="166"/>
+      <c r="D9" s="166"/>
+      <c r="E9" s="166"/>
+      <c r="F9" s="166"/>
+      <c r="G9" s="166"/>
+      <c r="H9" s="166"/>
+      <c r="I9" s="166"/>
+      <c r="J9" s="166"/>
+      <c r="K9" s="166"/>
+      <c r="L9" s="167"/>
     </row>
     <row r="10" spans="1:12" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="162" t="s">
+      <c r="A10" s="163" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="163"/>
-      <c r="C10" s="163"/>
-      <c r="D10" s="163"/>
-      <c r="E10" s="163"/>
-      <c r="F10" s="163"/>
-      <c r="G10" s="163"/>
-      <c r="H10" s="163"/>
-      <c r="I10" s="163"/>
-      <c r="J10" s="163"/>
-      <c r="K10" s="163"/>
-      <c r="L10" s="163"/>
+      <c r="B10" s="164"/>
+      <c r="C10" s="164"/>
+      <c r="D10" s="164"/>
+      <c r="E10" s="164"/>
+      <c r="F10" s="164"/>
+      <c r="G10" s="164"/>
+      <c r="H10" s="164"/>
+      <c r="I10" s="164"/>
+      <c r="J10" s="164"/>
+      <c r="K10" s="164"/>
+      <c r="L10" s="164"/>
     </row>
     <row r="11" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="144" t="s">
+      <c r="A11" s="145" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="145"/>
-      <c r="C11" s="145"/>
-      <c r="D11" s="145"/>
-      <c r="E11" s="145"/>
-      <c r="F11" s="145"/>
-      <c r="G11" s="145"/>
-      <c r="H11" s="145"/>
-      <c r="I11" s="145"/>
-      <c r="J11" s="145"/>
-      <c r="K11" s="145"/>
-      <c r="L11" s="146"/>
+      <c r="B11" s="146"/>
+      <c r="C11" s="146"/>
+      <c r="D11" s="146"/>
+      <c r="E11" s="146"/>
+      <c r="F11" s="146"/>
+      <c r="G11" s="146"/>
+      <c r="H11" s="146"/>
+      <c r="I11" s="146"/>
+      <c r="J11" s="146"/>
+      <c r="K11" s="146"/>
+      <c r="L11" s="147"/>
     </row>
     <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
@@ -15382,101 +15382,101 @@
       <c r="C12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="94" t="s">
+      <c r="D12" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="94"/>
-      <c r="F12" s="94"/>
-      <c r="G12" s="94"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="94"/>
-      <c r="J12" s="94"/>
-      <c r="K12" s="94"/>
-      <c r="L12" s="94"/>
+      <c r="E12" s="129"/>
+      <c r="F12" s="129"/>
+      <c r="G12" s="129"/>
+      <c r="H12" s="129"/>
+      <c r="I12" s="129"/>
+      <c r="J12" s="129"/>
+      <c r="K12" s="129"/>
+      <c r="L12" s="129"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="49"/>
       <c r="B13" s="50"/>
       <c r="C13" s="50"/>
-      <c r="D13" s="147"/>
-      <c r="E13" s="148"/>
-      <c r="F13" s="148"/>
-      <c r="G13" s="148"/>
-      <c r="H13" s="148"/>
-      <c r="I13" s="148"/>
-      <c r="J13" s="148"/>
-      <c r="K13" s="148"/>
-      <c r="L13" s="149"/>
+      <c r="D13" s="148"/>
+      <c r="E13" s="149"/>
+      <c r="F13" s="149"/>
+      <c r="G13" s="149"/>
+      <c r="H13" s="149"/>
+      <c r="I13" s="149"/>
+      <c r="J13" s="149"/>
+      <c r="K13" s="149"/>
+      <c r="L13" s="150"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="49"/>
       <c r="B14" s="50"/>
       <c r="C14" s="50"/>
-      <c r="D14" s="150"/>
-      <c r="E14" s="151"/>
-      <c r="F14" s="151"/>
-      <c r="G14" s="151"/>
-      <c r="H14" s="151"/>
-      <c r="I14" s="151"/>
-      <c r="J14" s="151"/>
-      <c r="K14" s="151"/>
-      <c r="L14" s="152"/>
+      <c r="D14" s="151"/>
+      <c r="E14" s="152"/>
+      <c r="F14" s="152"/>
+      <c r="G14" s="152"/>
+      <c r="H14" s="152"/>
+      <c r="I14" s="152"/>
+      <c r="J14" s="152"/>
+      <c r="K14" s="152"/>
+      <c r="L14" s="153"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="49"/>
       <c r="B15" s="50"/>
       <c r="C15" s="50"/>
-      <c r="D15" s="150"/>
-      <c r="E15" s="151"/>
-      <c r="F15" s="151"/>
-      <c r="G15" s="151"/>
-      <c r="H15" s="151"/>
-      <c r="I15" s="151"/>
-      <c r="J15" s="151"/>
-      <c r="K15" s="151"/>
-      <c r="L15" s="152"/>
+      <c r="D15" s="151"/>
+      <c r="E15" s="152"/>
+      <c r="F15" s="152"/>
+      <c r="G15" s="152"/>
+      <c r="H15" s="152"/>
+      <c r="I15" s="152"/>
+      <c r="J15" s="152"/>
+      <c r="K15" s="152"/>
+      <c r="L15" s="153"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="49"/>
       <c r="B16" s="50"/>
       <c r="C16" s="50"/>
-      <c r="D16" s="150"/>
-      <c r="E16" s="151"/>
-      <c r="F16" s="151"/>
-      <c r="G16" s="151"/>
-      <c r="H16" s="151"/>
-      <c r="I16" s="151"/>
-      <c r="J16" s="151"/>
-      <c r="K16" s="151"/>
-      <c r="L16" s="152"/>
+      <c r="D16" s="151"/>
+      <c r="E16" s="152"/>
+      <c r="F16" s="152"/>
+      <c r="G16" s="152"/>
+      <c r="H16" s="152"/>
+      <c r="I16" s="152"/>
+      <c r="J16" s="152"/>
+      <c r="K16" s="152"/>
+      <c r="L16" s="153"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="49"/>
       <c r="B17" s="50"/>
       <c r="C17" s="50"/>
-      <c r="D17" s="150"/>
-      <c r="E17" s="151"/>
-      <c r="F17" s="151"/>
-      <c r="G17" s="151"/>
-      <c r="H17" s="151"/>
-      <c r="I17" s="151"/>
-      <c r="J17" s="151"/>
-      <c r="K17" s="151"/>
-      <c r="L17" s="152"/>
+      <c r="D17" s="151"/>
+      <c r="E17" s="152"/>
+      <c r="F17" s="152"/>
+      <c r="G17" s="152"/>
+      <c r="H17" s="152"/>
+      <c r="I17" s="152"/>
+      <c r="J17" s="152"/>
+      <c r="K17" s="152"/>
+      <c r="L17" s="153"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="49"/>
       <c r="B18" s="50"/>
       <c r="C18" s="50"/>
-      <c r="D18" s="150"/>
-      <c r="E18" s="151"/>
-      <c r="F18" s="151"/>
-      <c r="G18" s="151"/>
-      <c r="H18" s="151"/>
-      <c r="I18" s="151"/>
-      <c r="J18" s="151"/>
-      <c r="K18" s="151"/>
-      <c r="L18" s="152"/>
+      <c r="D18" s="151"/>
+      <c r="E18" s="152"/>
+      <c r="F18" s="152"/>
+      <c r="G18" s="152"/>
+      <c r="H18" s="152"/>
+      <c r="I18" s="152"/>
+      <c r="J18" s="152"/>
+      <c r="K18" s="152"/>
+      <c r="L18" s="153"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -15565,10 +15565,10 @@
       <c r="B4" s="63"/>
     </row>
     <row r="6" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="A6" s="168" t="s">
+      <c r="A6" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="168"/>
+      <c r="B6" s="80"/>
     </row>
     <row r="8" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="66" t="s">
@@ -16300,68 +16300,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50">
-      <UserInfo>
-        <DisplayName>Luis Campos / Logiztik Alliance</DisplayName>
-        <AccountId>265</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Jairo Gonzalez / Logiztik Alliance</DisplayName>
-        <AccountId>322</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>José Ganchozo / Logiztik Alliance</DisplayName>
-        <AccountId>304</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Edwin Casa / Logiztik Alliance</DisplayName>
-        <AccountId>299</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Cristhian Cuichan / Logiztik Alliance</DisplayName>
-        <AccountId>369</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Oscar Yunda /  Logiztik Alliance</DisplayName>
-        <AccountId>355</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Fernando Ordoñez / Logiztik Alliance</DisplayName>
-        <AccountId>321</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Alex Rivera / Logiztik Alliance</DisplayName>
-        <AccountId>370</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <TaxCatchAll xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="87481c51-c14c-4071-bf64-faa2b5708bb6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101005DA7AC6E4F4FAE42B9D9FCD9C82CAAE1" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="553e0bb76796fbad2df2b84fb95dc83d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="87481c51-c14c-4071-bf64-faa2b5708bb6" xmlns:ns3="8029d101-3d2a-47c4-b15f-619642bf5e50" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d87cd7f238c73dc12c577d08dde48736" ns2:_="" ns3:_="">
     <xsd:import namespace="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
@@ -16610,26 +16548,69 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD069904-634F-48DA-AA92-BAE250498BEE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8029d101-3d2a-47c4-b15f-619642bf5e50"/>
-    <ds:schemaRef ds:uri="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371D8832-41B3-447B-B13D-2663C267E34F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50">
+      <UserInfo>
+        <DisplayName>Luis Campos / Logiztik Alliance</DisplayName>
+        <AccountId>265</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Jairo Gonzalez / Logiztik Alliance</DisplayName>
+        <AccountId>322</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>José Ganchozo / Logiztik Alliance</DisplayName>
+        <AccountId>304</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Edwin Casa / Logiztik Alliance</DisplayName>
+        <AccountId>299</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Cristhian Cuichan / Logiztik Alliance</DisplayName>
+        <AccountId>369</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Oscar Yunda /  Logiztik Alliance</DisplayName>
+        <AccountId>355</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Fernando Ordoñez / Logiztik Alliance</DisplayName>
+        <AccountId>321</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Alex Rivera / Logiztik Alliance</DisplayName>
+        <AccountId>370</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <TaxCatchAll xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="87481c51-c14c-4071-bf64-faa2b5708bb6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F7F06D0-41B3-4EAF-B418-88FC726117CC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -16646,4 +16627,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371D8832-41B3-447B-B13D-2663C267E34F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD069904-634F-48DA-AA92-BAE250498BEE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8029d101-3d2a-47c4-b15f-619642bf5e50"/>
+    <ds:schemaRef ds:uri="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Guias Produccion/HU-57723.xlsx
+++ b/Guias Produccion/HU-57723.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Alliance\ScriptsEntidades\Guias Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5745683B-F80A-4243-BD5C-5903C45993AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FCEDC94-5C0C-4DBC-909E-C27EDFC18D3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="148">
   <si>
     <t>Guia documentación</t>
   </si>
@@ -599,6 +599,15 @@
   <si>
     <t>29-AC_pro_GetSalesOrders.sql</t>
   </si>
+  <si>
+    <t>31-AC_pro_GetCompletedScheduledPickupShipTo.sql</t>
+  </si>
+  <si>
+    <t>30-AC_pro_GetDispatchReports.sql</t>
+  </si>
+  <si>
+    <t>32-AC_pro_GetCompletedDeliveredPickupShipTo.sql</t>
+  </si>
 </sst>
 </file>
 
@@ -817,7 +826,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="80">
+  <borders count="78">
     <border>
       <left/>
       <right/>
@@ -1802,32 +1811,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="177">
+  <cellXfs count="173">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2085,24 +2074,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="54" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="78" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="79" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2174,6 +2145,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2450,10 +2427,22 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp135.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$18" noThreeD="1" sel="8" val="3"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp136.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$18" noThreeD="1" sel="8" val="3"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp137.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$18" noThreeD="1" sel="8" val="3"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp138.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$17" noThreeD="1" sel="17" val="9"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp136.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp139.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$17" noThreeD="1" sel="17" val="9"/>
 </file>
 
@@ -10573,6 +10562,180 @@
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D4040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>54</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>1409700</xdr:colOff>
+          <xdr:row>55</xdr:row>
+          <xdr:rowOff>2241</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1237" name="Drop Down 213" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1237"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D5040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>55</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>1409700</xdr:colOff>
+          <xdr:row>56</xdr:row>
+          <xdr:rowOff>2241</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1238" name="Drop Down 214" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1238"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D6040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>56</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>1409700</xdr:colOff>
+          <xdr:row>57</xdr:row>
+          <xdr:rowOff>2241</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1239" name="Drop Down 215" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1239"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5306AB2-C689-6E6B-B36B-1B34C0356C8E}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -11198,7 +11361,7 @@
   <sheetPr codeName="Hoja1">
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A3:O54"/>
+  <dimension ref="A3:O57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.44140625" bestFit="1" customWidth="1"/>
@@ -11510,19 +11673,19 @@
       <c r="C18" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="121" t="s">
+      <c r="D18" s="115" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="123" t="s">
+      <c r="E18" s="117" t="s">
         <v>137</v>
       </c>
-      <c r="F18" s="123"/>
-      <c r="G18" s="123"/>
-      <c r="H18" s="123"/>
-      <c r="I18" s="123"/>
-      <c r="J18" s="124"/>
-      <c r="K18" s="124"/>
-      <c r="L18" s="125"/>
+      <c r="F18" s="117"/>
+      <c r="G18" s="117"/>
+      <c r="H18" s="117"/>
+      <c r="I18" s="117"/>
+      <c r="J18" s="118"/>
+      <c r="K18" s="118"/>
+      <c r="L18" s="119"/>
     </row>
     <row r="19" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
@@ -11532,15 +11695,15 @@
         <v>30</v>
       </c>
       <c r="C19" s="44"/>
-      <c r="D19" s="122"/>
-      <c r="E19" s="126"/>
-      <c r="F19" s="126"/>
-      <c r="G19" s="126"/>
-      <c r="H19" s="126"/>
-      <c r="I19" s="126"/>
-      <c r="J19" s="127"/>
-      <c r="K19" s="127"/>
-      <c r="L19" s="128"/>
+      <c r="D19" s="116"/>
+      <c r="E19" s="120"/>
+      <c r="F19" s="120"/>
+      <c r="G19" s="120"/>
+      <c r="H19" s="120"/>
+      <c r="I19" s="120"/>
+      <c r="J19" s="121"/>
+      <c r="K19" s="121"/>
+      <c r="L19" s="122"/>
     </row>
     <row r="20" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
@@ -11550,15 +11713,15 @@
       <c r="C20" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="122"/>
-      <c r="E20" s="126"/>
-      <c r="F20" s="126"/>
-      <c r="G20" s="126"/>
-      <c r="H20" s="126"/>
-      <c r="I20" s="126"/>
-      <c r="J20" s="127"/>
-      <c r="K20" s="127"/>
-      <c r="L20" s="128"/>
+      <c r="D20" s="116"/>
+      <c r="E20" s="120"/>
+      <c r="F20" s="120"/>
+      <c r="G20" s="120"/>
+      <c r="H20" s="120"/>
+      <c r="I20" s="120"/>
+      <c r="J20" s="121"/>
+      <c r="K20" s="121"/>
+      <c r="L20" s="122"/>
     </row>
     <row r="21" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
@@ -11568,19 +11731,19 @@
       <c r="C21" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="137" t="s">
+      <c r="D21" s="131" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="139" t="s">
+      <c r="E21" s="133" t="s">
         <v>107</v>
       </c>
-      <c r="F21" s="140"/>
-      <c r="G21" s="140"/>
-      <c r="H21" s="140"/>
-      <c r="I21" s="140"/>
-      <c r="J21" s="140"/>
-      <c r="K21" s="140"/>
-      <c r="L21" s="141"/>
+      <c r="F21" s="134"/>
+      <c r="G21" s="134"/>
+      <c r="H21" s="134"/>
+      <c r="I21" s="134"/>
+      <c r="J21" s="134"/>
+      <c r="K21" s="134"/>
+      <c r="L21" s="135"/>
     </row>
     <row r="22" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
@@ -11590,45 +11753,45 @@
       <c r="C22" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="138"/>
-      <c r="E22" s="142"/>
-      <c r="F22" s="143"/>
-      <c r="G22" s="143"/>
-      <c r="H22" s="143"/>
-      <c r="I22" s="143"/>
-      <c r="J22" s="143"/>
-      <c r="K22" s="143"/>
-      <c r="L22" s="144"/>
+      <c r="D22" s="132"/>
+      <c r="E22" s="136"/>
+      <c r="F22" s="137"/>
+      <c r="G22" s="137"/>
+      <c r="H22" s="137"/>
+      <c r="I22" s="137"/>
+      <c r="J22" s="137"/>
+      <c r="K22" s="137"/>
+      <c r="L22" s="138"/>
     </row>
     <row r="23" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="130"/>
-      <c r="B23" s="131"/>
-      <c r="C23" s="131"/>
-      <c r="D23" s="132"/>
-      <c r="E23" s="132"/>
-      <c r="F23" s="132"/>
-      <c r="G23" s="132"/>
-      <c r="H23" s="132"/>
-      <c r="I23" s="132"/>
-      <c r="J23" s="132"/>
-      <c r="K23" s="132"/>
-      <c r="L23" s="133"/>
+      <c r="A23" s="124"/>
+      <c r="B23" s="125"/>
+      <c r="C23" s="125"/>
+      <c r="D23" s="126"/>
+      <c r="E23" s="126"/>
+      <c r="F23" s="126"/>
+      <c r="G23" s="126"/>
+      <c r="H23" s="126"/>
+      <c r="I23" s="126"/>
+      <c r="J23" s="126"/>
+      <c r="K23" s="126"/>
+      <c r="L23" s="127"/>
     </row>
     <row r="24" spans="1:12" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="134" t="s">
+      <c r="A24" s="128" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="135"/>
-      <c r="C24" s="135"/>
-      <c r="D24" s="135"/>
-      <c r="E24" s="135"/>
-      <c r="F24" s="135"/>
-      <c r="G24" s="135"/>
-      <c r="H24" s="135"/>
-      <c r="I24" s="135"/>
-      <c r="J24" s="135"/>
-      <c r="K24" s="135"/>
-      <c r="L24" s="136"/>
+      <c r="B24" s="129"/>
+      <c r="C24" s="129"/>
+      <c r="D24" s="129"/>
+      <c r="E24" s="129"/>
+      <c r="F24" s="129"/>
+      <c r="G24" s="129"/>
+      <c r="H24" s="129"/>
+      <c r="I24" s="129"/>
+      <c r="J24" s="129"/>
+      <c r="K24" s="129"/>
+      <c r="L24" s="130"/>
     </row>
     <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
@@ -11640,17 +11803,17 @@
       <c r="C25" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="129" t="s">
+      <c r="D25" s="123" t="s">
         <v>38</v>
       </c>
-      <c r="E25" s="129"/>
-      <c r="F25" s="129"/>
-      <c r="G25" s="129"/>
-      <c r="H25" s="129"/>
-      <c r="I25" s="129"/>
-      <c r="J25" s="129"/>
-      <c r="K25" s="129"/>
-      <c r="L25" s="129"/>
+      <c r="E25" s="123"/>
+      <c r="F25" s="123"/>
+      <c r="G25" s="123"/>
+      <c r="H25" s="123"/>
+      <c r="I25" s="123"/>
+      <c r="J25" s="123"/>
+      <c r="K25" s="123"/>
+      <c r="L25" s="123"/>
     </row>
     <row r="26" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="33">
@@ -11660,17 +11823,17 @@
         <v>115</v>
       </c>
       <c r="C26" s="34"/>
-      <c r="D26" s="115" t="s">
+      <c r="D26" s="139" t="s">
         <v>108</v>
       </c>
-      <c r="E26" s="116"/>
-      <c r="F26" s="116"/>
-      <c r="G26" s="116"/>
-      <c r="H26" s="116"/>
-      <c r="I26" s="116"/>
-      <c r="J26" s="116"/>
-      <c r="K26" s="116"/>
-      <c r="L26" s="116"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="139"/>
+      <c r="H26" s="139"/>
+      <c r="I26" s="139"/>
+      <c r="J26" s="139"/>
+      <c r="K26" s="139"/>
+      <c r="L26" s="139"/>
     </row>
     <row r="27" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
@@ -11680,15 +11843,15 @@
         <v>116</v>
       </c>
       <c r="C27" s="34"/>
-      <c r="D27" s="117"/>
-      <c r="E27" s="118"/>
-      <c r="F27" s="118"/>
-      <c r="G27" s="118"/>
-      <c r="H27" s="118"/>
-      <c r="I27" s="118"/>
-      <c r="J27" s="118"/>
-      <c r="K27" s="118"/>
-      <c r="L27" s="118"/>
+      <c r="D27" s="140"/>
+      <c r="E27" s="140"/>
+      <c r="F27" s="140"/>
+      <c r="G27" s="140"/>
+      <c r="H27" s="140"/>
+      <c r="I27" s="140"/>
+      <c r="J27" s="140"/>
+      <c r="K27" s="140"/>
+      <c r="L27" s="140"/>
     </row>
     <row r="28" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="33">
@@ -11698,15 +11861,15 @@
         <v>117</v>
       </c>
       <c r="C28" s="34"/>
-      <c r="D28" s="117"/>
-      <c r="E28" s="118"/>
-      <c r="F28" s="118"/>
-      <c r="G28" s="118"/>
-      <c r="H28" s="118"/>
-      <c r="I28" s="118"/>
-      <c r="J28" s="118"/>
-      <c r="K28" s="118"/>
-      <c r="L28" s="118"/>
+      <c r="D28" s="140"/>
+      <c r="E28" s="140"/>
+      <c r="F28" s="140"/>
+      <c r="G28" s="140"/>
+      <c r="H28" s="140"/>
+      <c r="I28" s="140"/>
+      <c r="J28" s="140"/>
+      <c r="K28" s="140"/>
+      <c r="L28" s="140"/>
     </row>
     <row r="29" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
@@ -11716,15 +11879,15 @@
         <v>138</v>
       </c>
       <c r="C29" s="34"/>
-      <c r="D29" s="117"/>
-      <c r="E29" s="118"/>
-      <c r="F29" s="118"/>
-      <c r="G29" s="118"/>
-      <c r="H29" s="118"/>
-      <c r="I29" s="118"/>
-      <c r="J29" s="118"/>
-      <c r="K29" s="118"/>
-      <c r="L29" s="118"/>
+      <c r="D29" s="140"/>
+      <c r="E29" s="140"/>
+      <c r="F29" s="140"/>
+      <c r="G29" s="140"/>
+      <c r="H29" s="140"/>
+      <c r="I29" s="140"/>
+      <c r="J29" s="140"/>
+      <c r="K29" s="140"/>
+      <c r="L29" s="140"/>
     </row>
     <row r="30" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="33">
@@ -11734,15 +11897,15 @@
         <v>118</v>
       </c>
       <c r="C30" s="34"/>
-      <c r="D30" s="117"/>
-      <c r="E30" s="118"/>
-      <c r="F30" s="118"/>
-      <c r="G30" s="118"/>
-      <c r="H30" s="118"/>
-      <c r="I30" s="118"/>
-      <c r="J30" s="118"/>
-      <c r="K30" s="118"/>
-      <c r="L30" s="118"/>
+      <c r="D30" s="140"/>
+      <c r="E30" s="140"/>
+      <c r="F30" s="140"/>
+      <c r="G30" s="140"/>
+      <c r="H30" s="140"/>
+      <c r="I30" s="140"/>
+      <c r="J30" s="140"/>
+      <c r="K30" s="140"/>
+      <c r="L30" s="140"/>
     </row>
     <row r="31" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="33">
@@ -11752,15 +11915,15 @@
         <v>119</v>
       </c>
       <c r="C31" s="34"/>
-      <c r="D31" s="117"/>
-      <c r="E31" s="118"/>
-      <c r="F31" s="118"/>
-      <c r="G31" s="118"/>
-      <c r="H31" s="118"/>
-      <c r="I31" s="118"/>
-      <c r="J31" s="118"/>
-      <c r="K31" s="118"/>
-      <c r="L31" s="118"/>
+      <c r="D31" s="140"/>
+      <c r="E31" s="140"/>
+      <c r="F31" s="140"/>
+      <c r="G31" s="140"/>
+      <c r="H31" s="140"/>
+      <c r="I31" s="140"/>
+      <c r="J31" s="140"/>
+      <c r="K31" s="140"/>
+      <c r="L31" s="140"/>
     </row>
     <row r="32" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="33">
@@ -11770,15 +11933,15 @@
         <v>120</v>
       </c>
       <c r="C32" s="34"/>
-      <c r="D32" s="117"/>
-      <c r="E32" s="118"/>
-      <c r="F32" s="118"/>
-      <c r="G32" s="118"/>
-      <c r="H32" s="118"/>
-      <c r="I32" s="118"/>
-      <c r="J32" s="118"/>
-      <c r="K32" s="118"/>
-      <c r="L32" s="118"/>
+      <c r="D32" s="140"/>
+      <c r="E32" s="140"/>
+      <c r="F32" s="140"/>
+      <c r="G32" s="140"/>
+      <c r="H32" s="140"/>
+      <c r="I32" s="140"/>
+      <c r="J32" s="140"/>
+      <c r="K32" s="140"/>
+      <c r="L32" s="140"/>
     </row>
     <row r="33" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="33">
@@ -11788,15 +11951,15 @@
         <v>121</v>
       </c>
       <c r="C33" s="34"/>
-      <c r="D33" s="117"/>
-      <c r="E33" s="118"/>
-      <c r="F33" s="118"/>
-      <c r="G33" s="118"/>
-      <c r="H33" s="118"/>
-      <c r="I33" s="118"/>
-      <c r="J33" s="118"/>
-      <c r="K33" s="118"/>
-      <c r="L33" s="118"/>
+      <c r="D33" s="140"/>
+      <c r="E33" s="140"/>
+      <c r="F33" s="140"/>
+      <c r="G33" s="140"/>
+      <c r="H33" s="140"/>
+      <c r="I33" s="140"/>
+      <c r="J33" s="140"/>
+      <c r="K33" s="140"/>
+      <c r="L33" s="140"/>
     </row>
     <row r="34" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="33">
@@ -11806,15 +11969,15 @@
         <v>122</v>
       </c>
       <c r="C34" s="34"/>
-      <c r="D34" s="117"/>
-      <c r="E34" s="118"/>
-      <c r="F34" s="118"/>
-      <c r="G34" s="118"/>
-      <c r="H34" s="118"/>
-      <c r="I34" s="118"/>
-      <c r="J34" s="118"/>
-      <c r="K34" s="118"/>
-      <c r="L34" s="118"/>
+      <c r="D34" s="140"/>
+      <c r="E34" s="140"/>
+      <c r="F34" s="140"/>
+      <c r="G34" s="140"/>
+      <c r="H34" s="140"/>
+      <c r="I34" s="140"/>
+      <c r="J34" s="140"/>
+      <c r="K34" s="140"/>
+      <c r="L34" s="140"/>
     </row>
     <row r="35" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="33">
@@ -11824,15 +11987,15 @@
         <v>123</v>
       </c>
       <c r="C35" s="34"/>
-      <c r="D35" s="117"/>
-      <c r="E35" s="118"/>
-      <c r="F35" s="118"/>
-      <c r="G35" s="118"/>
-      <c r="H35" s="118"/>
-      <c r="I35" s="118"/>
-      <c r="J35" s="118"/>
-      <c r="K35" s="118"/>
-      <c r="L35" s="118"/>
+      <c r="D35" s="140"/>
+      <c r="E35" s="140"/>
+      <c r="F35" s="140"/>
+      <c r="G35" s="140"/>
+      <c r="H35" s="140"/>
+      <c r="I35" s="140"/>
+      <c r="J35" s="140"/>
+      <c r="K35" s="140"/>
+      <c r="L35" s="140"/>
     </row>
     <row r="36" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="33">
@@ -11842,15 +12005,15 @@
         <v>124</v>
       </c>
       <c r="C36" s="34"/>
-      <c r="D36" s="117"/>
-      <c r="E36" s="118"/>
-      <c r="F36" s="118"/>
-      <c r="G36" s="118"/>
-      <c r="H36" s="118"/>
-      <c r="I36" s="118"/>
-      <c r="J36" s="118"/>
-      <c r="K36" s="118"/>
-      <c r="L36" s="118"/>
+      <c r="D36" s="140"/>
+      <c r="E36" s="140"/>
+      <c r="F36" s="140"/>
+      <c r="G36" s="140"/>
+      <c r="H36" s="140"/>
+      <c r="I36" s="140"/>
+      <c r="J36" s="140"/>
+      <c r="K36" s="140"/>
+      <c r="L36" s="140"/>
     </row>
     <row r="37" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="33">
@@ -11860,15 +12023,15 @@
         <v>139</v>
       </c>
       <c r="C37" s="34"/>
-      <c r="D37" s="117"/>
-      <c r="E37" s="118"/>
-      <c r="F37" s="118"/>
-      <c r="G37" s="118"/>
-      <c r="H37" s="118"/>
-      <c r="I37" s="118"/>
-      <c r="J37" s="118"/>
-      <c r="K37" s="118"/>
-      <c r="L37" s="118"/>
+      <c r="D37" s="140"/>
+      <c r="E37" s="140"/>
+      <c r="F37" s="140"/>
+      <c r="G37" s="140"/>
+      <c r="H37" s="140"/>
+      <c r="I37" s="140"/>
+      <c r="J37" s="140"/>
+      <c r="K37" s="140"/>
+      <c r="L37" s="140"/>
     </row>
     <row r="38" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="33">
@@ -11878,15 +12041,15 @@
         <v>125</v>
       </c>
       <c r="C38" s="34"/>
-      <c r="D38" s="117"/>
-      <c r="E38" s="118"/>
-      <c r="F38" s="118"/>
-      <c r="G38" s="118"/>
-      <c r="H38" s="118"/>
-      <c r="I38" s="118"/>
-      <c r="J38" s="118"/>
-      <c r="K38" s="118"/>
-      <c r="L38" s="118"/>
+      <c r="D38" s="140"/>
+      <c r="E38" s="140"/>
+      <c r="F38" s="140"/>
+      <c r="G38" s="140"/>
+      <c r="H38" s="140"/>
+      <c r="I38" s="140"/>
+      <c r="J38" s="140"/>
+      <c r="K38" s="140"/>
+      <c r="L38" s="140"/>
     </row>
     <row r="39" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="33">
@@ -11896,15 +12059,15 @@
         <v>126</v>
       </c>
       <c r="C39" s="34"/>
-      <c r="D39" s="117"/>
-      <c r="E39" s="118"/>
-      <c r="F39" s="118"/>
-      <c r="G39" s="118"/>
-      <c r="H39" s="118"/>
-      <c r="I39" s="118"/>
-      <c r="J39" s="118"/>
-      <c r="K39" s="118"/>
-      <c r="L39" s="118"/>
+      <c r="D39" s="140"/>
+      <c r="E39" s="140"/>
+      <c r="F39" s="140"/>
+      <c r="G39" s="140"/>
+      <c r="H39" s="140"/>
+      <c r="I39" s="140"/>
+      <c r="J39" s="140"/>
+      <c r="K39" s="140"/>
+      <c r="L39" s="140"/>
     </row>
     <row r="40" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="33">
@@ -11914,15 +12077,15 @@
         <v>127</v>
       </c>
       <c r="C40" s="34"/>
-      <c r="D40" s="117"/>
-      <c r="E40" s="118"/>
-      <c r="F40" s="118"/>
-      <c r="G40" s="118"/>
-      <c r="H40" s="118"/>
-      <c r="I40" s="118"/>
-      <c r="J40" s="118"/>
-      <c r="K40" s="118"/>
-      <c r="L40" s="118"/>
+      <c r="D40" s="140"/>
+      <c r="E40" s="140"/>
+      <c r="F40" s="140"/>
+      <c r="G40" s="140"/>
+      <c r="H40" s="140"/>
+      <c r="I40" s="140"/>
+      <c r="J40" s="140"/>
+      <c r="K40" s="140"/>
+      <c r="L40" s="140"/>
     </row>
     <row r="41" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="33">
@@ -11932,15 +12095,15 @@
         <v>128</v>
       </c>
       <c r="C41" s="34"/>
-      <c r="D41" s="117"/>
-      <c r="E41" s="118"/>
-      <c r="F41" s="118"/>
-      <c r="G41" s="118"/>
-      <c r="H41" s="118"/>
-      <c r="I41" s="118"/>
-      <c r="J41" s="118"/>
-      <c r="K41" s="118"/>
-      <c r="L41" s="118"/>
+      <c r="D41" s="140"/>
+      <c r="E41" s="140"/>
+      <c r="F41" s="140"/>
+      <c r="G41" s="140"/>
+      <c r="H41" s="140"/>
+      <c r="I41" s="140"/>
+      <c r="J41" s="140"/>
+      <c r="K41" s="140"/>
+      <c r="L41" s="140"/>
     </row>
     <row r="42" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="33">
@@ -11950,15 +12113,15 @@
         <v>140</v>
       </c>
       <c r="C42" s="34"/>
-      <c r="D42" s="117"/>
-      <c r="E42" s="118"/>
-      <c r="F42" s="118"/>
-      <c r="G42" s="118"/>
-      <c r="H42" s="118"/>
-      <c r="I42" s="118"/>
-      <c r="J42" s="118"/>
-      <c r="K42" s="118"/>
-      <c r="L42" s="118"/>
+      <c r="D42" s="140"/>
+      <c r="E42" s="140"/>
+      <c r="F42" s="140"/>
+      <c r="G42" s="140"/>
+      <c r="H42" s="140"/>
+      <c r="I42" s="140"/>
+      <c r="J42" s="140"/>
+      <c r="K42" s="140"/>
+      <c r="L42" s="140"/>
     </row>
     <row r="43" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="33">
@@ -11968,15 +12131,15 @@
         <v>141</v>
       </c>
       <c r="C43" s="34"/>
-      <c r="D43" s="117"/>
-      <c r="E43" s="118"/>
-      <c r="F43" s="118"/>
-      <c r="G43" s="118"/>
-      <c r="H43" s="118"/>
-      <c r="I43" s="118"/>
-      <c r="J43" s="118"/>
-      <c r="K43" s="118"/>
-      <c r="L43" s="118"/>
+      <c r="D43" s="140"/>
+      <c r="E43" s="140"/>
+      <c r="F43" s="140"/>
+      <c r="G43" s="140"/>
+      <c r="H43" s="140"/>
+      <c r="I43" s="140"/>
+      <c r="J43" s="140"/>
+      <c r="K43" s="140"/>
+      <c r="L43" s="140"/>
     </row>
     <row r="44" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="33">
@@ -11986,15 +12149,15 @@
         <v>129</v>
       </c>
       <c r="C44" s="34"/>
-      <c r="D44" s="117"/>
-      <c r="E44" s="118"/>
-      <c r="F44" s="118"/>
-      <c r="G44" s="118"/>
-      <c r="H44" s="118"/>
-      <c r="I44" s="118"/>
-      <c r="J44" s="118"/>
-      <c r="K44" s="118"/>
-      <c r="L44" s="118"/>
+      <c r="D44" s="140"/>
+      <c r="E44" s="140"/>
+      <c r="F44" s="140"/>
+      <c r="G44" s="140"/>
+      <c r="H44" s="140"/>
+      <c r="I44" s="140"/>
+      <c r="J44" s="140"/>
+      <c r="K44" s="140"/>
+      <c r="L44" s="140"/>
     </row>
     <row r="45" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="33">
@@ -12004,15 +12167,15 @@
         <v>130</v>
       </c>
       <c r="C45" s="34"/>
-      <c r="D45" s="117"/>
-      <c r="E45" s="118"/>
-      <c r="F45" s="118"/>
-      <c r="G45" s="118"/>
-      <c r="H45" s="118"/>
-      <c r="I45" s="118"/>
-      <c r="J45" s="118"/>
-      <c r="K45" s="118"/>
-      <c r="L45" s="118"/>
+      <c r="D45" s="140"/>
+      <c r="E45" s="140"/>
+      <c r="F45" s="140"/>
+      <c r="G45" s="140"/>
+      <c r="H45" s="140"/>
+      <c r="I45" s="140"/>
+      <c r="J45" s="140"/>
+      <c r="K45" s="140"/>
+      <c r="L45" s="140"/>
     </row>
     <row r="46" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="33">
@@ -12022,15 +12185,15 @@
         <v>131</v>
       </c>
       <c r="C46" s="34"/>
-      <c r="D46" s="117"/>
-      <c r="E46" s="118"/>
-      <c r="F46" s="118"/>
-      <c r="G46" s="118"/>
-      <c r="H46" s="118"/>
-      <c r="I46" s="118"/>
-      <c r="J46" s="118"/>
-      <c r="K46" s="118"/>
-      <c r="L46" s="118"/>
+      <c r="D46" s="140"/>
+      <c r="E46" s="140"/>
+      <c r="F46" s="140"/>
+      <c r="G46" s="140"/>
+      <c r="H46" s="140"/>
+      <c r="I46" s="140"/>
+      <c r="J46" s="140"/>
+      <c r="K46" s="140"/>
+      <c r="L46" s="140"/>
     </row>
     <row r="47" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="33">
@@ -12040,15 +12203,15 @@
         <v>132</v>
       </c>
       <c r="C47" s="34"/>
-      <c r="D47" s="117"/>
-      <c r="E47" s="118"/>
-      <c r="F47" s="118"/>
-      <c r="G47" s="118"/>
-      <c r="H47" s="118"/>
-      <c r="I47" s="118"/>
-      <c r="J47" s="118"/>
-      <c r="K47" s="118"/>
-      <c r="L47" s="118"/>
+      <c r="D47" s="140"/>
+      <c r="E47" s="140"/>
+      <c r="F47" s="140"/>
+      <c r="G47" s="140"/>
+      <c r="H47" s="140"/>
+      <c r="I47" s="140"/>
+      <c r="J47" s="140"/>
+      <c r="K47" s="140"/>
+      <c r="L47" s="140"/>
     </row>
     <row r="48" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="33">
@@ -12058,15 +12221,15 @@
         <v>133</v>
       </c>
       <c r="C48" s="34"/>
-      <c r="D48" s="117"/>
-      <c r="E48" s="118"/>
-      <c r="F48" s="118"/>
-      <c r="G48" s="118"/>
-      <c r="H48" s="118"/>
-      <c r="I48" s="118"/>
-      <c r="J48" s="118"/>
-      <c r="K48" s="118"/>
-      <c r="L48" s="118"/>
+      <c r="D48" s="140"/>
+      <c r="E48" s="140"/>
+      <c r="F48" s="140"/>
+      <c r="G48" s="140"/>
+      <c r="H48" s="140"/>
+      <c r="I48" s="140"/>
+      <c r="J48" s="140"/>
+      <c r="K48" s="140"/>
+      <c r="L48" s="140"/>
     </row>
     <row r="49" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="33">
@@ -12076,15 +12239,15 @@
         <v>143</v>
       </c>
       <c r="C49" s="34"/>
-      <c r="D49" s="117"/>
-      <c r="E49" s="118"/>
-      <c r="F49" s="118"/>
-      <c r="G49" s="118"/>
-      <c r="H49" s="118"/>
-      <c r="I49" s="118"/>
-      <c r="J49" s="118"/>
-      <c r="K49" s="118"/>
-      <c r="L49" s="118"/>
+      <c r="D49" s="140"/>
+      <c r="E49" s="140"/>
+      <c r="F49" s="140"/>
+      <c r="G49" s="140"/>
+      <c r="H49" s="140"/>
+      <c r="I49" s="140"/>
+      <c r="J49" s="140"/>
+      <c r="K49" s="140"/>
+      <c r="L49" s="140"/>
     </row>
     <row r="50" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="72">
@@ -12094,15 +12257,15 @@
         <v>134</v>
       </c>
       <c r="C50" s="34"/>
-      <c r="D50" s="117"/>
-      <c r="E50" s="118"/>
-      <c r="F50" s="118"/>
-      <c r="G50" s="118"/>
-      <c r="H50" s="118"/>
-      <c r="I50" s="118"/>
-      <c r="J50" s="118"/>
-      <c r="K50" s="118"/>
-      <c r="L50" s="118"/>
+      <c r="D50" s="140"/>
+      <c r="E50" s="140"/>
+      <c r="F50" s="140"/>
+      <c r="G50" s="140"/>
+      <c r="H50" s="140"/>
+      <c r="I50" s="140"/>
+      <c r="J50" s="140"/>
+      <c r="K50" s="140"/>
+      <c r="L50" s="140"/>
     </row>
     <row r="51" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="72">
@@ -12112,15 +12275,15 @@
         <v>135</v>
       </c>
       <c r="C51" s="34"/>
-      <c r="D51" s="117"/>
-      <c r="E51" s="118"/>
-      <c r="F51" s="118"/>
-      <c r="G51" s="118"/>
-      <c r="H51" s="118"/>
-      <c r="I51" s="118"/>
-      <c r="J51" s="118"/>
-      <c r="K51" s="118"/>
-      <c r="L51" s="118"/>
+      <c r="D51" s="140"/>
+      <c r="E51" s="140"/>
+      <c r="F51" s="140"/>
+      <c r="G51" s="140"/>
+      <c r="H51" s="140"/>
+      <c r="I51" s="140"/>
+      <c r="J51" s="140"/>
+      <c r="K51" s="140"/>
+      <c r="L51" s="140"/>
     </row>
     <row r="52" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="72">
@@ -12130,15 +12293,15 @@
         <v>136</v>
       </c>
       <c r="C52" s="34"/>
-      <c r="D52" s="117"/>
-      <c r="E52" s="118"/>
-      <c r="F52" s="118"/>
-      <c r="G52" s="118"/>
-      <c r="H52" s="118"/>
-      <c r="I52" s="118"/>
-      <c r="J52" s="118"/>
-      <c r="K52" s="118"/>
-      <c r="L52" s="118"/>
+      <c r="D52" s="140"/>
+      <c r="E52" s="140"/>
+      <c r="F52" s="140"/>
+      <c r="G52" s="140"/>
+      <c r="H52" s="140"/>
+      <c r="I52" s="140"/>
+      <c r="J52" s="140"/>
+      <c r="K52" s="140"/>
+      <c r="L52" s="140"/>
     </row>
     <row r="53" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="72">
@@ -12148,15 +12311,15 @@
         <v>142</v>
       </c>
       <c r="C53" s="79"/>
-      <c r="D53" s="117"/>
-      <c r="E53" s="118"/>
-      <c r="F53" s="118"/>
-      <c r="G53" s="118"/>
-      <c r="H53" s="118"/>
-      <c r="I53" s="118"/>
-      <c r="J53" s="118"/>
-      <c r="K53" s="118"/>
-      <c r="L53" s="118"/>
+      <c r="D53" s="140"/>
+      <c r="E53" s="140"/>
+      <c r="F53" s="140"/>
+      <c r="G53" s="140"/>
+      <c r="H53" s="140"/>
+      <c r="I53" s="140"/>
+      <c r="J53" s="140"/>
+      <c r="K53" s="140"/>
+      <c r="L53" s="140"/>
     </row>
     <row r="54" spans="1:12" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="72">
@@ -12166,19 +12329,73 @@
         <v>144</v>
       </c>
       <c r="C54" s="72"/>
-      <c r="D54" s="119"/>
-      <c r="E54" s="120"/>
-      <c r="F54" s="120"/>
-      <c r="G54" s="120"/>
-      <c r="H54" s="120"/>
-      <c r="I54" s="120"/>
-      <c r="J54" s="120"/>
-      <c r="K54" s="120"/>
-      <c r="L54" s="120"/>
+      <c r="D54" s="140"/>
+      <c r="E54" s="140"/>
+      <c r="F54" s="140"/>
+      <c r="G54" s="140"/>
+      <c r="H54" s="140"/>
+      <c r="I54" s="140"/>
+      <c r="J54" s="140"/>
+      <c r="K54" s="140"/>
+      <c r="L54" s="140"/>
+    </row>
+    <row r="55" spans="1:12" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="72">
+        <v>30</v>
+      </c>
+      <c r="B55" s="78" t="s">
+        <v>146</v>
+      </c>
+      <c r="C55" s="78"/>
+      <c r="D55" s="140"/>
+      <c r="E55" s="140"/>
+      <c r="F55" s="140"/>
+      <c r="G55" s="140"/>
+      <c r="H55" s="140"/>
+      <c r="I55" s="140"/>
+      <c r="J55" s="140"/>
+      <c r="K55" s="140"/>
+      <c r="L55" s="140"/>
+    </row>
+    <row r="56" spans="1:12" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="72">
+        <v>31</v>
+      </c>
+      <c r="B56" s="78" t="s">
+        <v>145</v>
+      </c>
+      <c r="C56" s="78"/>
+      <c r="D56" s="140"/>
+      <c r="E56" s="140"/>
+      <c r="F56" s="140"/>
+      <c r="G56" s="140"/>
+      <c r="H56" s="140"/>
+      <c r="I56" s="140"/>
+      <c r="J56" s="140"/>
+      <c r="K56" s="140"/>
+      <c r="L56" s="140"/>
+    </row>
+    <row r="57" spans="1:12" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="72">
+        <v>32</v>
+      </c>
+      <c r="B57" s="78" t="s">
+        <v>147</v>
+      </c>
+      <c r="C57" s="78"/>
+      <c r="D57" s="140"/>
+      <c r="E57" s="140"/>
+      <c r="F57" s="140"/>
+      <c r="G57" s="140"/>
+      <c r="H57" s="140"/>
+      <c r="I57" s="140"/>
+      <c r="J57" s="140"/>
+      <c r="K57" s="140"/>
+      <c r="L57" s="140"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="D26:L54"/>
+    <mergeCell ref="D26:L57"/>
     <mergeCell ref="D18:D20"/>
     <mergeCell ref="E18:L20"/>
     <mergeCell ref="D25:L25"/>
@@ -15156,6 +15373,72 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1237" r:id="rId139" name="Drop Down 213">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>54</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>1409700</xdr:colOff>
+                    <xdr:row>55</xdr:row>
+                    <xdr:rowOff>7620</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1238" r:id="rId140" name="Drop Down 214">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>55</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>1409700</xdr:colOff>
+                    <xdr:row>56</xdr:row>
+                    <xdr:rowOff>7620</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1239" r:id="rId141" name="Drop Down 215">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>56</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>1409700</xdr:colOff>
+                    <xdr:row>57</xdr:row>
+                    <xdr:rowOff>7620</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </mc:Choice>
   </mc:AlternateContent>
@@ -15179,50 +15462,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="154" t="s">
+      <c r="A1" s="150" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="155"/>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="155"/>
-      <c r="F1" s="155"/>
-      <c r="G1" s="155"/>
-      <c r="H1" s="155"/>
-      <c r="I1" s="155"/>
-      <c r="J1" s="155"/>
-      <c r="K1" s="155"/>
-      <c r="L1" s="156"/>
+      <c r="B1" s="151"/>
+      <c r="C1" s="151"/>
+      <c r="D1" s="151"/>
+      <c r="E1" s="151"/>
+      <c r="F1" s="151"/>
+      <c r="G1" s="151"/>
+      <c r="H1" s="151"/>
+      <c r="I1" s="151"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="152"/>
     </row>
     <row r="2" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="157" t="s">
+      <c r="A2" s="153" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="159"/>
+      <c r="B2" s="154"/>
+      <c r="C2" s="154"/>
+      <c r="D2" s="154"/>
+      <c r="E2" s="154"/>
+      <c r="F2" s="154"/>
+      <c r="G2" s="154"/>
+      <c r="H2" s="154"/>
+      <c r="I2" s="154"/>
+      <c r="J2" s="154"/>
+      <c r="K2" s="154"/>
+      <c r="L2" s="155"/>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="160"/>
-      <c r="B3" s="161"/>
-      <c r="C3" s="161"/>
-      <c r="D3" s="161"/>
-      <c r="E3" s="161"/>
-      <c r="F3" s="161"/>
-      <c r="G3" s="161"/>
-      <c r="H3" s="161"/>
-      <c r="I3" s="161"/>
-      <c r="J3" s="161"/>
-      <c r="K3" s="161"/>
-      <c r="L3" s="162"/>
+      <c r="A3" s="156"/>
+      <c r="B3" s="157"/>
+      <c r="C3" s="157"/>
+      <c r="D3" s="157"/>
+      <c r="E3" s="157"/>
+      <c r="F3" s="157"/>
+      <c r="G3" s="157"/>
+      <c r="H3" s="157"/>
+      <c r="I3" s="157"/>
+      <c r="J3" s="157"/>
+      <c r="K3" s="157"/>
+      <c r="L3" s="158"/>
     </row>
     <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
@@ -15312,65 +15595,65 @@
       <c r="A8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="165"/>
-      <c r="C8" s="166"/>
-      <c r="D8" s="166"/>
-      <c r="E8" s="166"/>
-      <c r="F8" s="166"/>
-      <c r="G8" s="166"/>
-      <c r="H8" s="166"/>
-      <c r="I8" s="166"/>
-      <c r="J8" s="166"/>
-      <c r="K8" s="166"/>
-      <c r="L8" s="167"/>
+      <c r="B8" s="161"/>
+      <c r="C8" s="162"/>
+      <c r="D8" s="162"/>
+      <c r="E8" s="162"/>
+      <c r="F8" s="162"/>
+      <c r="G8" s="162"/>
+      <c r="H8" s="162"/>
+      <c r="I8" s="162"/>
+      <c r="J8" s="162"/>
+      <c r="K8" s="162"/>
+      <c r="L8" s="163"/>
     </row>
     <row r="9" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="168"/>
-      <c r="C9" s="166"/>
-      <c r="D9" s="166"/>
-      <c r="E9" s="166"/>
-      <c r="F9" s="166"/>
-      <c r="G9" s="166"/>
-      <c r="H9" s="166"/>
-      <c r="I9" s="166"/>
-      <c r="J9" s="166"/>
-      <c r="K9" s="166"/>
-      <c r="L9" s="167"/>
+      <c r="B9" s="164"/>
+      <c r="C9" s="162"/>
+      <c r="D9" s="162"/>
+      <c r="E9" s="162"/>
+      <c r="F9" s="162"/>
+      <c r="G9" s="162"/>
+      <c r="H9" s="162"/>
+      <c r="I9" s="162"/>
+      <c r="J9" s="162"/>
+      <c r="K9" s="162"/>
+      <c r="L9" s="163"/>
     </row>
     <row r="10" spans="1:12" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="163" t="s">
+      <c r="A10" s="159" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="164"/>
-      <c r="C10" s="164"/>
-      <c r="D10" s="164"/>
-      <c r="E10" s="164"/>
-      <c r="F10" s="164"/>
-      <c r="G10" s="164"/>
-      <c r="H10" s="164"/>
-      <c r="I10" s="164"/>
-      <c r="J10" s="164"/>
-      <c r="K10" s="164"/>
-      <c r="L10" s="164"/>
+      <c r="B10" s="160"/>
+      <c r="C10" s="160"/>
+      <c r="D10" s="160"/>
+      <c r="E10" s="160"/>
+      <c r="F10" s="160"/>
+      <c r="G10" s="160"/>
+      <c r="H10" s="160"/>
+      <c r="I10" s="160"/>
+      <c r="J10" s="160"/>
+      <c r="K10" s="160"/>
+      <c r="L10" s="160"/>
     </row>
     <row r="11" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="145" t="s">
+      <c r="A11" s="141" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="146"/>
-      <c r="C11" s="146"/>
-      <c r="D11" s="146"/>
-      <c r="E11" s="146"/>
-      <c r="F11" s="146"/>
-      <c r="G11" s="146"/>
-      <c r="H11" s="146"/>
-      <c r="I11" s="146"/>
-      <c r="J11" s="146"/>
-      <c r="K11" s="146"/>
-      <c r="L11" s="147"/>
+      <c r="B11" s="142"/>
+      <c r="C11" s="142"/>
+      <c r="D11" s="142"/>
+      <c r="E11" s="142"/>
+      <c r="F11" s="142"/>
+      <c r="G11" s="142"/>
+      <c r="H11" s="142"/>
+      <c r="I11" s="142"/>
+      <c r="J11" s="142"/>
+      <c r="K11" s="142"/>
+      <c r="L11" s="143"/>
     </row>
     <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
@@ -15382,101 +15665,101 @@
       <c r="C12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="129" t="s">
+      <c r="D12" s="123" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="129"/>
-      <c r="F12" s="129"/>
-      <c r="G12" s="129"/>
-      <c r="H12" s="129"/>
-      <c r="I12" s="129"/>
-      <c r="J12" s="129"/>
-      <c r="K12" s="129"/>
-      <c r="L12" s="129"/>
+      <c r="E12" s="123"/>
+      <c r="F12" s="123"/>
+      <c r="G12" s="123"/>
+      <c r="H12" s="123"/>
+      <c r="I12" s="123"/>
+      <c r="J12" s="123"/>
+      <c r="K12" s="123"/>
+      <c r="L12" s="123"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="49"/>
       <c r="B13" s="50"/>
       <c r="C13" s="50"/>
-      <c r="D13" s="148"/>
-      <c r="E13" s="149"/>
-      <c r="F13" s="149"/>
-      <c r="G13" s="149"/>
-      <c r="H13" s="149"/>
-      <c r="I13" s="149"/>
-      <c r="J13" s="149"/>
-      <c r="K13" s="149"/>
-      <c r="L13" s="150"/>
+      <c r="D13" s="144"/>
+      <c r="E13" s="145"/>
+      <c r="F13" s="145"/>
+      <c r="G13" s="145"/>
+      <c r="H13" s="145"/>
+      <c r="I13" s="145"/>
+      <c r="J13" s="145"/>
+      <c r="K13" s="145"/>
+      <c r="L13" s="146"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="49"/>
       <c r="B14" s="50"/>
       <c r="C14" s="50"/>
-      <c r="D14" s="151"/>
-      <c r="E14" s="152"/>
-      <c r="F14" s="152"/>
-      <c r="G14" s="152"/>
-      <c r="H14" s="152"/>
-      <c r="I14" s="152"/>
-      <c r="J14" s="152"/>
-      <c r="K14" s="152"/>
-      <c r="L14" s="153"/>
+      <c r="D14" s="147"/>
+      <c r="E14" s="148"/>
+      <c r="F14" s="148"/>
+      <c r="G14" s="148"/>
+      <c r="H14" s="148"/>
+      <c r="I14" s="148"/>
+      <c r="J14" s="148"/>
+      <c r="K14" s="148"/>
+      <c r="L14" s="149"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="49"/>
       <c r="B15" s="50"/>
       <c r="C15" s="50"/>
-      <c r="D15" s="151"/>
-      <c r="E15" s="152"/>
-      <c r="F15" s="152"/>
-      <c r="G15" s="152"/>
-      <c r="H15" s="152"/>
-      <c r="I15" s="152"/>
-      <c r="J15" s="152"/>
-      <c r="K15" s="152"/>
-      <c r="L15" s="153"/>
+      <c r="D15" s="147"/>
+      <c r="E15" s="148"/>
+      <c r="F15" s="148"/>
+      <c r="G15" s="148"/>
+      <c r="H15" s="148"/>
+      <c r="I15" s="148"/>
+      <c r="J15" s="148"/>
+      <c r="K15" s="148"/>
+      <c r="L15" s="149"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="49"/>
       <c r="B16" s="50"/>
       <c r="C16" s="50"/>
-      <c r="D16" s="151"/>
-      <c r="E16" s="152"/>
-      <c r="F16" s="152"/>
-      <c r="G16" s="152"/>
-      <c r="H16" s="152"/>
-      <c r="I16" s="152"/>
-      <c r="J16" s="152"/>
-      <c r="K16" s="152"/>
-      <c r="L16" s="153"/>
+      <c r="D16" s="147"/>
+      <c r="E16" s="148"/>
+      <c r="F16" s="148"/>
+      <c r="G16" s="148"/>
+      <c r="H16" s="148"/>
+      <c r="I16" s="148"/>
+      <c r="J16" s="148"/>
+      <c r="K16" s="148"/>
+      <c r="L16" s="149"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="49"/>
       <c r="B17" s="50"/>
       <c r="C17" s="50"/>
-      <c r="D17" s="151"/>
-      <c r="E17" s="152"/>
-      <c r="F17" s="152"/>
-      <c r="G17" s="152"/>
-      <c r="H17" s="152"/>
-      <c r="I17" s="152"/>
-      <c r="J17" s="152"/>
-      <c r="K17" s="152"/>
-      <c r="L17" s="153"/>
+      <c r="D17" s="147"/>
+      <c r="E17" s="148"/>
+      <c r="F17" s="148"/>
+      <c r="G17" s="148"/>
+      <c r="H17" s="148"/>
+      <c r="I17" s="148"/>
+      <c r="J17" s="148"/>
+      <c r="K17" s="148"/>
+      <c r="L17" s="149"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="49"/>
       <c r="B18" s="50"/>
       <c r="C18" s="50"/>
-      <c r="D18" s="151"/>
-      <c r="E18" s="152"/>
-      <c r="F18" s="152"/>
-      <c r="G18" s="152"/>
-      <c r="H18" s="152"/>
-      <c r="I18" s="152"/>
-      <c r="J18" s="152"/>
-      <c r="K18" s="152"/>
-      <c r="L18" s="153"/>
+      <c r="D18" s="147"/>
+      <c r="E18" s="148"/>
+      <c r="F18" s="148"/>
+      <c r="G18" s="148"/>
+      <c r="H18" s="148"/>
+      <c r="I18" s="148"/>
+      <c r="J18" s="148"/>
+      <c r="K18" s="148"/>
+      <c r="L18" s="149"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -15721,55 +16004,55 @@
   <sheetData>
     <row r="1" spans="2:6" ht="5.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B2" s="170"/>
-      <c r="C2" s="170"/>
-      <c r="D2" s="171" t="s">
+      <c r="B2" s="166"/>
+      <c r="C2" s="166"/>
+      <c r="D2" s="167" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="172" t="s">
+      <c r="E2" s="168" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="172"/>
+      <c r="F2" s="168"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B3" s="170"/>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="172"/>
+      <c r="B3" s="166"/>
+      <c r="C3" s="166"/>
+      <c r="D3" s="167"/>
+      <c r="E3" s="168"/>
+      <c r="F3" s="168"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="170"/>
-      <c r="C4" s="170"/>
-      <c r="D4" s="171"/>
-      <c r="E4" s="172" t="s">
+      <c r="B4" s="166"/>
+      <c r="C4" s="166"/>
+      <c r="D4" s="167"/>
+      <c r="E4" s="168" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="172"/>
+      <c r="F4" s="168"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="173" t="s">
+      <c r="B5" s="169" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="173"/>
+      <c r="C5" s="169"/>
       <c r="D5" s="70" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="174" t="s">
+      <c r="E5" s="170" t="s">
         <v>54</v>
       </c>
-      <c r="F5" s="174"/>
+      <c r="F5" s="170"/>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="169" t="s">
+      <c r="C6" s="165" t="s">
         <v>114</v>
       </c>
-      <c r="D6" s="169"/>
-      <c r="E6" s="169"/>
-      <c r="F6" s="169"/>
+      <c r="D6" s="165"/>
+      <c r="E6" s="165"/>
+      <c r="F6" s="165"/>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="71" t="s">
@@ -16026,10 +16309,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="27" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="175" t="s">
+      <c r="A1" s="171" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="176"/>
+      <c r="B1" s="172"/>
     </row>
     <row r="2" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="28" t="s">

--- a/Guias Produccion/HU-57723.xlsx
+++ b/Guias Produccion/HU-57723.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Alliance\ScriptsEntidades\Guias Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FCEDC94-5C0C-4DBC-909E-C27EDFC18D3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0C0A8B-CDE1-4CBF-902C-EB20E9B41D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="149">
   <si>
     <t>Guia documentación</t>
   </si>
@@ -510,103 +510,106 @@
     <t>Patricia Chicaiza</t>
   </si>
   <si>
-    <t>01-trgUpdateEntityTypes.sql</t>
-  </si>
-  <si>
-    <t>02-trgUpdateEntities.sql</t>
-  </si>
-  <si>
-    <t>03-f_SearchEntities.sql</t>
-  </si>
-  <si>
-    <t>05-AC_pro_GetMachineShipments.sql</t>
-  </si>
-  <si>
-    <t>06-AC_pro_GetClientsPiecesDetails.sql</t>
-  </si>
-  <si>
-    <t>07-AC_pro_GetDispatchesByCarrier.sql</t>
-  </si>
-  <si>
-    <t>08-AC_pro_GetClientsEntities.sql</t>
-  </si>
-  <si>
-    <t>09-AC_pro_GetClientsPiecesBySubCarrier.sql</t>
-  </si>
-  <si>
-    <t>10-AC_pro_GetDispatchesByClient.sql</t>
-  </si>
-  <si>
-    <t>11-AC_pro_GetLocalOrdersByEmployee.sql</t>
-  </si>
-  <si>
-    <t>13-AC_pro_ListCarrierProgramming.sql</t>
-  </si>
-  <si>
-    <t>14-AC_pro_ConfirmLocalOrderCoordination.sql</t>
-  </si>
-  <si>
-    <t>15-AC_pro_ConfirmLocalOrder.sql</t>
-  </si>
-  <si>
-    <t>16-AC_pro_ShippingDocumentsPODClient360.sql</t>
-  </si>
-  <si>
-    <t>19-AC_pro_ListPiecesInventory.sql</t>
-  </si>
-  <si>
-    <t>20-AC_pro_GetBarCodeLinks.sql</t>
-  </si>
-  <si>
-    <t>21-AC_pro_LargeLabelTempDefault.sql</t>
-  </si>
-  <si>
-    <t>22-AC_pro_GetDispatchReports.sql</t>
-  </si>
-  <si>
-    <t>23-AC_pro_GetShipmentAnalyticsReports.sql</t>
-  </si>
-  <si>
-    <t>25-AC_pro_GetCycleCountDiscrepancies.sql</t>
-  </si>
-  <si>
-    <t>26-AC_pro_CycleCountDiscrepanciesReport.sql</t>
-  </si>
-  <si>
-    <t>27-AC_pro_GetConsolidatedDispatchAnalytics.sql</t>
-  </si>
-  <si>
     <t>Es necesario que se ejecuten primero los scripts de la Hu 55188, ya que existe dependencia de algunos campos</t>
   </si>
   <si>
-    <t>04-AC_pro_General_GenerateBulkInt.sql</t>
+    <t>01-trgEntityRelations_SyncClientes.sql</t>
   </si>
   <si>
-    <t>12-AC_pro_ManageGuiasHouseDetallesEditedOrder.sql</t>
+    <t>02-trgUpdateEntityTypes.sql</t>
   </si>
   <si>
-    <t>17-AC_pro_ModuleEdiDetail.sql</t>
+    <t>03-trgUpdateEntities.sql</t>
   </si>
   <si>
-    <t>18-AC_pro_Module_Edi.sql</t>
+    <t>04-f_SearchEntities.sql</t>
   </si>
   <si>
-    <t>28-AC_pro_GetAccountingAnalyticsReports.sql</t>
+    <t>05-AC_pro_General_GenerateBulkInt.sql</t>
   </si>
   <si>
-    <t>24-AC_pro_GetListOFCycleCounts.sql</t>
+    <t>06-AC_pro_GetMachineShipments.sql</t>
   </si>
   <si>
-    <t>29-AC_pro_GetSalesOrders.sql</t>
+    <t>07-AC_pro_GetClientsPiecesDetails.sql</t>
   </si>
   <si>
-    <t>31-AC_pro_GetCompletedScheduledPickupShipTo.sql</t>
+    <t>08-AC_pro_GetDispatchesByCarrier.sql</t>
   </si>
   <si>
-    <t>30-AC_pro_GetDispatchReports.sql</t>
+    <t>09-AC_pro_GetClientsEntities.sql</t>
   </si>
   <si>
-    <t>32-AC_pro_GetCompletedDeliveredPickupShipTo.sql</t>
+    <t>10-AC_pro_GetClientsPiecesBySubCarrier.sql</t>
+  </si>
+  <si>
+    <t>11-AC_pro_GetDispatchesByClient.sql</t>
+  </si>
+  <si>
+    <t>12-AC_pro_GetLocalOrdersByEmployee.sql</t>
+  </si>
+  <si>
+    <t>13-AC_pro_ManageGuiasHouseDetallesEditedOrder.sql</t>
+  </si>
+  <si>
+    <t>14-AC_pro_ListCarrierProgramming.sql</t>
+  </si>
+  <si>
+    <t>15-AC_pro_ConfirmLocalOrderCoordination.sql</t>
+  </si>
+  <si>
+    <t>16-AC_pro_ConfirmLocalOrder.sql</t>
+  </si>
+  <si>
+    <t>17-AC_pro_ShippingDocumentsPODClient360.sql</t>
+  </si>
+  <si>
+    <t>18-AC_pro_ModuleEdiDetail.sql</t>
+  </si>
+  <si>
+    <t>19-AC_pro_Module_Edi.sql</t>
+  </si>
+  <si>
+    <t>20-AC_pro_ListPiecesInventory.sql</t>
+  </si>
+  <si>
+    <t>21-AC_pro_GetBarCodeLinks.sql</t>
+  </si>
+  <si>
+    <t>22-AC_pro_LargeLabelTempDefault.sql</t>
+  </si>
+  <si>
+    <t>23-AC_pro_GetDispatchReports.sql</t>
+  </si>
+  <si>
+    <t>24-AC_pro_GetShipmentAnalyticsReports.sql</t>
+  </si>
+  <si>
+    <t>25-AC_pro_GetListOFCycleCounts.sql</t>
+  </si>
+  <si>
+    <t>26-AC_pro_GetCycleCountDiscrepancies.sql</t>
+  </si>
+  <si>
+    <t>27-AC_pro_CycleCountDiscrepanciesReport.sql</t>
+  </si>
+  <si>
+    <t>28-AC_pro_GetConsolidatedDispatchAnalytics.sql</t>
+  </si>
+  <si>
+    <t>29-AC_pro_GetAccountingAnalyticsReports.sql</t>
+  </si>
+  <si>
+    <t>30-AC_pro_GetSalesOrders.sql</t>
+  </si>
+  <si>
+    <t>31-AC_pro_GetDispatchReports.sql</t>
+  </si>
+  <si>
+    <t>32-AC_pro_GetCompletedScheduledPickupShipTo.sql</t>
+  </si>
+  <si>
+    <t>33-AC_pro_GetCompletedDeliveredPickupShipTo.sql</t>
   </si>
 </sst>
 </file>
@@ -826,7 +829,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="78">
+  <borders count="79">
     <border>
       <left/>
       <right/>
@@ -1811,12 +1814,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="173">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1969,8 +1983,83 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="75" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="76" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="77" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2074,84 +2163,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2224,6 +2235,9 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2247,6 +2261,15 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="54" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2311,7 +2334,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp109.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$25" noThreeD="1" sel="17" val="14"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$25" noThreeD="1" sel="23" val="16"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp11.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2319,7 +2342,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp110.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$25" noThreeD="1" sel="8" val="7"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$25" noThreeD="1" sel="17" val="12"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp111.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2439,7 +2462,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp138.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$17" noThreeD="1" sel="17" val="9"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$18" noThreeD="1" sel="8" val="3"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp139.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2448,6 +2471,10 @@
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="[1]Hoja4!$A$1:$A$13" noThreeD="1" sel="0" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp140.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$17" noThreeD="1" sel="17" val="9"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10609,7 +10636,7 @@
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
           <xdr:row>55</xdr:row>
-          <xdr:rowOff>2241</xdr:rowOff>
+          <xdr:rowOff>7620</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10667,7 +10694,7 @@
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
           <xdr:row>56</xdr:row>
-          <xdr:rowOff>2241</xdr:rowOff>
+          <xdr:rowOff>7620</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10725,7 +10752,7 @@
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
           <xdr:row>57</xdr:row>
-          <xdr:rowOff>2241</xdr:rowOff>
+          <xdr:rowOff>7620</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10735,7 +10762,65 @@
                   <a14:compatExt spid="_x0000_s1239"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5306AB2-C689-6E6B-B36B-1B34C0356C8E}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D7040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>57</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>1409700</xdr:colOff>
+          <xdr:row>58</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1240" name="Drop Down 216" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1240"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF2454DC-C779-3BA6-DA50-36A79288A231}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -11361,7 +11446,7 @@
   <sheetPr codeName="Hoja1">
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A3:O57"/>
+  <dimension ref="A3:O58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.44140625" bestFit="1" customWidth="1"/>
@@ -11380,42 +11465,42 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:15" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="97" t="s">
+      <c r="A3" s="122" t="s">
         <v>103</v>
       </c>
-      <c r="B3" s="98"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="98"/>
-      <c r="K3" s="98"/>
-      <c r="L3" s="99"/>
-      <c r="N3" s="91" t="s">
+      <c r="B3" s="123"/>
+      <c r="C3" s="123"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="123"/>
+      <c r="F3" s="123"/>
+      <c r="G3" s="123"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="123"/>
+      <c r="J3" s="123"/>
+      <c r="K3" s="123"/>
+      <c r="L3" s="124"/>
+      <c r="N3" s="116" t="s">
         <v>0</v>
       </c>
-      <c r="O3" s="92"/>
+      <c r="O3" s="117"/>
     </row>
     <row r="4" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="104" t="s">
+      <c r="B4" s="129" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="105"/>
-      <c r="D4" s="105"/>
-      <c r="E4" s="105"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="105"/>
-      <c r="I4" s="105"/>
-      <c r="J4" s="106"/>
-      <c r="K4" s="106"/>
-      <c r="L4" s="107"/>
+      <c r="C4" s="130"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="130"/>
+      <c r="F4" s="130"/>
+      <c r="G4" s="130"/>
+      <c r="H4" s="130"/>
+      <c r="I4" s="130"/>
+      <c r="J4" s="131"/>
+      <c r="K4" s="131"/>
+      <c r="L4" s="132"/>
       <c r="N4" s="21" t="s">
         <v>2</v>
       </c>
@@ -11425,19 +11510,19 @@
       <c r="A5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="108" t="s">
+      <c r="B5" s="133" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="108"/>
-      <c r="D5" s="108"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="108"/>
-      <c r="G5" s="108"/>
-      <c r="H5" s="108"/>
-      <c r="I5" s="108"/>
-      <c r="J5" s="109"/>
-      <c r="K5" s="109"/>
-      <c r="L5" s="110"/>
+      <c r="C5" s="133"/>
+      <c r="D5" s="133"/>
+      <c r="E5" s="133"/>
+      <c r="F5" s="133"/>
+      <c r="G5" s="133"/>
+      <c r="H5" s="133"/>
+      <c r="I5" s="133"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="135"/>
       <c r="N5" s="15" t="s">
         <v>4</v>
       </c>
@@ -11447,19 +11532,19 @@
       <c r="A6" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="94">
+      <c r="B6" s="119">
         <v>46073</v>
       </c>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="95"/>
-      <c r="K6" s="95"/>
-      <c r="L6" s="96"/>
+      <c r="C6" s="120"/>
+      <c r="D6" s="120"/>
+      <c r="E6" s="120"/>
+      <c r="F6" s="120"/>
+      <c r="G6" s="120"/>
+      <c r="H6" s="120"/>
+      <c r="I6" s="120"/>
+      <c r="J6" s="120"/>
+      <c r="K6" s="120"/>
+      <c r="L6" s="121"/>
       <c r="N6" s="14"/>
       <c r="O6" s="14"/>
     </row>
@@ -11467,17 +11552,17 @@
       <c r="A7" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="111"/>
-      <c r="C7" s="112"/>
-      <c r="D7" s="112"/>
-      <c r="E7" s="112"/>
-      <c r="F7" s="112"/>
-      <c r="G7" s="112"/>
-      <c r="H7" s="112"/>
-      <c r="I7" s="112"/>
-      <c r="J7" s="113"/>
-      <c r="K7" s="113"/>
-      <c r="L7" s="114"/>
+      <c r="B7" s="136"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="137"/>
+      <c r="E7" s="137"/>
+      <c r="F7" s="137"/>
+      <c r="G7" s="137"/>
+      <c r="H7" s="137"/>
+      <c r="I7" s="137"/>
+      <c r="J7" s="138"/>
+      <c r="K7" s="138"/>
+      <c r="L7" s="139"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
@@ -11494,20 +11579,20 @@
       <c r="L8" s="13"/>
     </row>
     <row r="9" spans="1:15" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="100" t="s">
+      <c r="A9" s="125" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="101"/>
-      <c r="C9" s="101"/>
-      <c r="D9" s="101"/>
-      <c r="E9" s="101"/>
-      <c r="F9" s="101"/>
-      <c r="G9" s="101"/>
-      <c r="H9" s="101"/>
-      <c r="I9" s="101"/>
-      <c r="J9" s="102"/>
-      <c r="K9" s="102"/>
-      <c r="L9" s="103"/>
+      <c r="B9" s="126"/>
+      <c r="C9" s="126"/>
+      <c r="D9" s="126"/>
+      <c r="E9" s="126"/>
+      <c r="F9" s="126"/>
+      <c r="G9" s="126"/>
+      <c r="H9" s="126"/>
+      <c r="I9" s="126"/>
+      <c r="J9" s="127"/>
+      <c r="K9" s="127"/>
+      <c r="L9" s="128"/>
     </row>
     <row r="10" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -11607,63 +11692,63 @@
       <c r="A14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="93"/>
-      <c r="C14" s="89"/>
-      <c r="D14" s="89"/>
-      <c r="E14" s="89"/>
-      <c r="F14" s="89"/>
-      <c r="G14" s="89"/>
-      <c r="H14" s="89"/>
-      <c r="I14" s="89"/>
-      <c r="J14" s="89"/>
-      <c r="K14" s="89"/>
-      <c r="L14" s="90"/>
+      <c r="B14" s="118"/>
+      <c r="C14" s="114"/>
+      <c r="D14" s="114"/>
+      <c r="E14" s="114"/>
+      <c r="F14" s="114"/>
+      <c r="G14" s="114"/>
+      <c r="H14" s="114"/>
+      <c r="I14" s="114"/>
+      <c r="J14" s="114"/>
+      <c r="K14" s="114"/>
+      <c r="L14" s="115"/>
     </row>
     <row r="15" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="88"/>
-      <c r="C15" s="89"/>
-      <c r="D15" s="89"/>
-      <c r="E15" s="89"/>
-      <c r="F15" s="89"/>
-      <c r="G15" s="89"/>
-      <c r="H15" s="89"/>
-      <c r="I15" s="89"/>
-      <c r="J15" s="89"/>
-      <c r="K15" s="89"/>
-      <c r="L15" s="90"/>
+      <c r="B15" s="113"/>
+      <c r="C15" s="114"/>
+      <c r="D15" s="114"/>
+      <c r="E15" s="114"/>
+      <c r="F15" s="114"/>
+      <c r="G15" s="114"/>
+      <c r="H15" s="114"/>
+      <c r="I15" s="114"/>
+      <c r="J15" s="114"/>
+      <c r="K15" s="114"/>
+      <c r="L15" s="115"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="81"/>
-      <c r="B16" s="82"/>
-      <c r="C16" s="82"/>
-      <c r="D16" s="82"/>
-      <c r="E16" s="82"/>
-      <c r="F16" s="82"/>
-      <c r="G16" s="82"/>
-      <c r="H16" s="82"/>
-      <c r="I16" s="82"/>
-      <c r="J16" s="82"/>
-      <c r="K16" s="82"/>
-      <c r="L16" s="83"/>
+      <c r="A16" s="106"/>
+      <c r="B16" s="107"/>
+      <c r="C16" s="107"/>
+      <c r="D16" s="107"/>
+      <c r="E16" s="107"/>
+      <c r="F16" s="107"/>
+      <c r="G16" s="107"/>
+      <c r="H16" s="107"/>
+      <c r="I16" s="107"/>
+      <c r="J16" s="107"/>
+      <c r="K16" s="107"/>
+      <c r="L16" s="108"/>
     </row>
     <row r="17" spans="1:12" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="84" t="s">
+      <c r="A17" s="109" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="85"/>
-      <c r="C17" s="85"/>
-      <c r="D17" s="85"/>
-      <c r="E17" s="85"/>
-      <c r="F17" s="85"/>
-      <c r="G17" s="85"/>
-      <c r="H17" s="85"/>
-      <c r="I17" s="85"/>
-      <c r="J17" s="86"/>
-      <c r="K17" s="86"/>
-      <c r="L17" s="87"/>
+      <c r="B17" s="110"/>
+      <c r="C17" s="110"/>
+      <c r="D17" s="110"/>
+      <c r="E17" s="110"/>
+      <c r="F17" s="110"/>
+      <c r="G17" s="110"/>
+      <c r="H17" s="110"/>
+      <c r="I17" s="110"/>
+      <c r="J17" s="111"/>
+      <c r="K17" s="111"/>
+      <c r="L17" s="112"/>
     </row>
     <row r="18" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
@@ -11673,19 +11758,19 @@
       <c r="C18" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="115" t="s">
+      <c r="D18" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="117" t="s">
-        <v>137</v>
-      </c>
-      <c r="F18" s="117"/>
-      <c r="G18" s="117"/>
-      <c r="H18" s="117"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="118"/>
-      <c r="K18" s="118"/>
-      <c r="L18" s="119"/>
+      <c r="E18" s="84" t="s">
+        <v>115</v>
+      </c>
+      <c r="F18" s="84"/>
+      <c r="G18" s="84"/>
+      <c r="H18" s="84"/>
+      <c r="I18" s="84"/>
+      <c r="J18" s="85"/>
+      <c r="K18" s="85"/>
+      <c r="L18" s="86"/>
     </row>
     <row r="19" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
@@ -11695,15 +11780,15 @@
         <v>30</v>
       </c>
       <c r="C19" s="44"/>
-      <c r="D19" s="116"/>
-      <c r="E19" s="120"/>
-      <c r="F19" s="120"/>
-      <c r="G19" s="120"/>
-      <c r="H19" s="120"/>
-      <c r="I19" s="120"/>
-      <c r="J19" s="121"/>
-      <c r="K19" s="121"/>
-      <c r="L19" s="122"/>
+      <c r="D19" s="83"/>
+      <c r="E19" s="87"/>
+      <c r="F19" s="87"/>
+      <c r="G19" s="87"/>
+      <c r="H19" s="87"/>
+      <c r="I19" s="87"/>
+      <c r="J19" s="88"/>
+      <c r="K19" s="88"/>
+      <c r="L19" s="89"/>
     </row>
     <row r="20" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
@@ -11713,15 +11798,15 @@
       <c r="C20" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="116"/>
-      <c r="E20" s="120"/>
-      <c r="F20" s="120"/>
-      <c r="G20" s="120"/>
-      <c r="H20" s="120"/>
-      <c r="I20" s="120"/>
-      <c r="J20" s="121"/>
-      <c r="K20" s="121"/>
-      <c r="L20" s="122"/>
+      <c r="D20" s="83"/>
+      <c r="E20" s="87"/>
+      <c r="F20" s="87"/>
+      <c r="G20" s="87"/>
+      <c r="H20" s="87"/>
+      <c r="I20" s="87"/>
+      <c r="J20" s="88"/>
+      <c r="K20" s="88"/>
+      <c r="L20" s="89"/>
     </row>
     <row r="21" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
@@ -11731,19 +11816,19 @@
       <c r="C21" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="131" t="s">
+      <c r="D21" s="98" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="133" t="s">
+      <c r="E21" s="100" t="s">
         <v>107</v>
       </c>
-      <c r="F21" s="134"/>
-      <c r="G21" s="134"/>
-      <c r="H21" s="134"/>
-      <c r="I21" s="134"/>
-      <c r="J21" s="134"/>
-      <c r="K21" s="134"/>
-      <c r="L21" s="135"/>
+      <c r="F21" s="101"/>
+      <c r="G21" s="101"/>
+      <c r="H21" s="101"/>
+      <c r="I21" s="101"/>
+      <c r="J21" s="101"/>
+      <c r="K21" s="101"/>
+      <c r="L21" s="102"/>
     </row>
     <row r="22" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
@@ -11753,45 +11838,45 @@
       <c r="C22" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="132"/>
-      <c r="E22" s="136"/>
-      <c r="F22" s="137"/>
-      <c r="G22" s="137"/>
-      <c r="H22" s="137"/>
-      <c r="I22" s="137"/>
-      <c r="J22" s="137"/>
-      <c r="K22" s="137"/>
-      <c r="L22" s="138"/>
+      <c r="D22" s="99"/>
+      <c r="E22" s="103"/>
+      <c r="F22" s="104"/>
+      <c r="G22" s="104"/>
+      <c r="H22" s="104"/>
+      <c r="I22" s="104"/>
+      <c r="J22" s="104"/>
+      <c r="K22" s="104"/>
+      <c r="L22" s="105"/>
     </row>
     <row r="23" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="124"/>
-      <c r="B23" s="125"/>
-      <c r="C23" s="125"/>
-      <c r="D23" s="126"/>
-      <c r="E23" s="126"/>
-      <c r="F23" s="126"/>
-      <c r="G23" s="126"/>
-      <c r="H23" s="126"/>
-      <c r="I23" s="126"/>
-      <c r="J23" s="126"/>
-      <c r="K23" s="126"/>
-      <c r="L23" s="127"/>
+      <c r="A23" s="91"/>
+      <c r="B23" s="92"/>
+      <c r="C23" s="92"/>
+      <c r="D23" s="93"/>
+      <c r="E23" s="93"/>
+      <c r="F23" s="93"/>
+      <c r="G23" s="93"/>
+      <c r="H23" s="93"/>
+      <c r="I23" s="93"/>
+      <c r="J23" s="93"/>
+      <c r="K23" s="93"/>
+      <c r="L23" s="94"/>
     </row>
     <row r="24" spans="1:12" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="128" t="s">
+      <c r="A24" s="95" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="129"/>
-      <c r="C24" s="129"/>
-      <c r="D24" s="129"/>
-      <c r="E24" s="129"/>
-      <c r="F24" s="129"/>
-      <c r="G24" s="129"/>
-      <c r="H24" s="129"/>
-      <c r="I24" s="129"/>
-      <c r="J24" s="129"/>
-      <c r="K24" s="129"/>
-      <c r="L24" s="130"/>
+      <c r="B24" s="96"/>
+      <c r="C24" s="96"/>
+      <c r="D24" s="96"/>
+      <c r="E24" s="96"/>
+      <c r="F24" s="96"/>
+      <c r="G24" s="96"/>
+      <c r="H24" s="96"/>
+      <c r="I24" s="96"/>
+      <c r="J24" s="96"/>
+      <c r="K24" s="96"/>
+      <c r="L24" s="97"/>
     </row>
     <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
@@ -11803,523 +11888,523 @@
       <c r="C25" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="123" t="s">
+      <c r="D25" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="E25" s="123"/>
-      <c r="F25" s="123"/>
-      <c r="G25" s="123"/>
-      <c r="H25" s="123"/>
-      <c r="I25" s="123"/>
-      <c r="J25" s="123"/>
-      <c r="K25" s="123"/>
-      <c r="L25" s="123"/>
+      <c r="E25" s="90"/>
+      <c r="F25" s="90"/>
+      <c r="G25" s="90"/>
+      <c r="H25" s="90"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="90"/>
+      <c r="K25" s="90"/>
+      <c r="L25" s="90"/>
     </row>
     <row r="26" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="33">
         <v>1</v>
       </c>
       <c r="B26" s="34" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C26" s="34"/>
-      <c r="D26" s="139" t="s">
+      <c r="D26" s="174" t="s">
         <v>108</v>
       </c>
-      <c r="E26" s="139"/>
-      <c r="F26" s="139"/>
-      <c r="G26" s="139"/>
-      <c r="H26" s="139"/>
-      <c r="I26" s="139"/>
-      <c r="J26" s="139"/>
-      <c r="K26" s="139"/>
-      <c r="L26" s="139"/>
+      <c r="E26" s="80"/>
+      <c r="F26" s="80"/>
+      <c r="G26" s="80"/>
+      <c r="H26" s="80"/>
+      <c r="I26" s="80"/>
+      <c r="J26" s="80"/>
+      <c r="K26" s="80"/>
+      <c r="L26" s="80"/>
     </row>
     <row r="27" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
         <v>2</v>
       </c>
       <c r="B27" s="34" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C27" s="34"/>
-      <c r="D27" s="140"/>
-      <c r="E27" s="140"/>
-      <c r="F27" s="140"/>
-      <c r="G27" s="140"/>
-      <c r="H27" s="140"/>
-      <c r="I27" s="140"/>
-      <c r="J27" s="140"/>
-      <c r="K27" s="140"/>
-      <c r="L27" s="140"/>
+      <c r="D27" s="175"/>
+      <c r="E27" s="81"/>
+      <c r="F27" s="81"/>
+      <c r="G27" s="81"/>
+      <c r="H27" s="81"/>
+      <c r="I27" s="81"/>
+      <c r="J27" s="81"/>
+      <c r="K27" s="81"/>
+      <c r="L27" s="81"/>
     </row>
     <row r="28" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="33">
         <v>3</v>
       </c>
       <c r="B28" s="34" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C28" s="34"/>
-      <c r="D28" s="140"/>
-      <c r="E28" s="140"/>
-      <c r="F28" s="140"/>
-      <c r="G28" s="140"/>
-      <c r="H28" s="140"/>
-      <c r="I28" s="140"/>
-      <c r="J28" s="140"/>
-      <c r="K28" s="140"/>
-      <c r="L28" s="140"/>
+      <c r="D28" s="175"/>
+      <c r="E28" s="81"/>
+      <c r="F28" s="81"/>
+      <c r="G28" s="81"/>
+      <c r="H28" s="81"/>
+      <c r="I28" s="81"/>
+      <c r="J28" s="81"/>
+      <c r="K28" s="81"/>
+      <c r="L28" s="81"/>
     </row>
     <row r="29" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
         <v>4</v>
       </c>
       <c r="B29" s="34" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="C29" s="34"/>
-      <c r="D29" s="140"/>
-      <c r="E29" s="140"/>
-      <c r="F29" s="140"/>
-      <c r="G29" s="140"/>
-      <c r="H29" s="140"/>
-      <c r="I29" s="140"/>
-      <c r="J29" s="140"/>
-      <c r="K29" s="140"/>
-      <c r="L29" s="140"/>
+      <c r="D29" s="175"/>
+      <c r="E29" s="81"/>
+      <c r="F29" s="81"/>
+      <c r="G29" s="81"/>
+      <c r="H29" s="81"/>
+      <c r="I29" s="81"/>
+      <c r="J29" s="81"/>
+      <c r="K29" s="81"/>
+      <c r="L29" s="81"/>
     </row>
     <row r="30" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="33">
         <v>5</v>
       </c>
       <c r="B30" s="34" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C30" s="34"/>
-      <c r="D30" s="140"/>
-      <c r="E30" s="140"/>
-      <c r="F30" s="140"/>
-      <c r="G30" s="140"/>
-      <c r="H30" s="140"/>
-      <c r="I30" s="140"/>
-      <c r="J30" s="140"/>
-      <c r="K30" s="140"/>
-      <c r="L30" s="140"/>
+      <c r="D30" s="175"/>
+      <c r="E30" s="81"/>
+      <c r="F30" s="81"/>
+      <c r="G30" s="81"/>
+      <c r="H30" s="81"/>
+      <c r="I30" s="81"/>
+      <c r="J30" s="81"/>
+      <c r="K30" s="81"/>
+      <c r="L30" s="81"/>
     </row>
     <row r="31" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="33">
         <v>6</v>
       </c>
       <c r="B31" s="34" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C31" s="34"/>
-      <c r="D31" s="140"/>
-      <c r="E31" s="140"/>
-      <c r="F31" s="140"/>
-      <c r="G31" s="140"/>
-      <c r="H31" s="140"/>
-      <c r="I31" s="140"/>
-      <c r="J31" s="140"/>
-      <c r="K31" s="140"/>
-      <c r="L31" s="140"/>
+      <c r="D31" s="175"/>
+      <c r="E31" s="81"/>
+      <c r="F31" s="81"/>
+      <c r="G31" s="81"/>
+      <c r="H31" s="81"/>
+      <c r="I31" s="81"/>
+      <c r="J31" s="81"/>
+      <c r="K31" s="81"/>
+      <c r="L31" s="81"/>
     </row>
     <row r="32" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="33">
         <v>7</v>
       </c>
       <c r="B32" s="34" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C32" s="34"/>
-      <c r="D32" s="140"/>
-      <c r="E32" s="140"/>
-      <c r="F32" s="140"/>
-      <c r="G32" s="140"/>
-      <c r="H32" s="140"/>
-      <c r="I32" s="140"/>
-      <c r="J32" s="140"/>
-      <c r="K32" s="140"/>
-      <c r="L32" s="140"/>
+      <c r="D32" s="175"/>
+      <c r="E32" s="81"/>
+      <c r="F32" s="81"/>
+      <c r="G32" s="81"/>
+      <c r="H32" s="81"/>
+      <c r="I32" s="81"/>
+      <c r="J32" s="81"/>
+      <c r="K32" s="81"/>
+      <c r="L32" s="81"/>
     </row>
     <row r="33" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="33">
         <v>8</v>
       </c>
       <c r="B33" s="34" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C33" s="34"/>
-      <c r="D33" s="140"/>
-      <c r="E33" s="140"/>
-      <c r="F33" s="140"/>
-      <c r="G33" s="140"/>
-      <c r="H33" s="140"/>
-      <c r="I33" s="140"/>
-      <c r="J33" s="140"/>
-      <c r="K33" s="140"/>
-      <c r="L33" s="140"/>
+      <c r="D33" s="175"/>
+      <c r="E33" s="81"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="81"/>
+      <c r="H33" s="81"/>
+      <c r="I33" s="81"/>
+      <c r="J33" s="81"/>
+      <c r="K33" s="81"/>
+      <c r="L33" s="81"/>
     </row>
     <row r="34" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="33">
         <v>9</v>
       </c>
       <c r="B34" s="34" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C34" s="34"/>
-      <c r="D34" s="140"/>
-      <c r="E34" s="140"/>
-      <c r="F34" s="140"/>
-      <c r="G34" s="140"/>
-      <c r="H34" s="140"/>
-      <c r="I34" s="140"/>
-      <c r="J34" s="140"/>
-      <c r="K34" s="140"/>
-      <c r="L34" s="140"/>
+      <c r="D34" s="175"/>
+      <c r="E34" s="81"/>
+      <c r="F34" s="81"/>
+      <c r="G34" s="81"/>
+      <c r="H34" s="81"/>
+      <c r="I34" s="81"/>
+      <c r="J34" s="81"/>
+      <c r="K34" s="81"/>
+      <c r="L34" s="81"/>
     </row>
     <row r="35" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="33">
         <v>10</v>
       </c>
       <c r="B35" s="34" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C35" s="34"/>
-      <c r="D35" s="140"/>
-      <c r="E35" s="140"/>
-      <c r="F35" s="140"/>
-      <c r="G35" s="140"/>
-      <c r="H35" s="140"/>
-      <c r="I35" s="140"/>
-      <c r="J35" s="140"/>
-      <c r="K35" s="140"/>
-      <c r="L35" s="140"/>
+      <c r="D35" s="175"/>
+      <c r="E35" s="81"/>
+      <c r="F35" s="81"/>
+      <c r="G35" s="81"/>
+      <c r="H35" s="81"/>
+      <c r="I35" s="81"/>
+      <c r="J35" s="81"/>
+      <c r="K35" s="81"/>
+      <c r="L35" s="81"/>
     </row>
     <row r="36" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="33">
         <v>11</v>
       </c>
       <c r="B36" s="34" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C36" s="34"/>
-      <c r="D36" s="140"/>
-      <c r="E36" s="140"/>
-      <c r="F36" s="140"/>
-      <c r="G36" s="140"/>
-      <c r="H36" s="140"/>
-      <c r="I36" s="140"/>
-      <c r="J36" s="140"/>
-      <c r="K36" s="140"/>
-      <c r="L36" s="140"/>
+      <c r="D36" s="175"/>
+      <c r="E36" s="81"/>
+      <c r="F36" s="81"/>
+      <c r="G36" s="81"/>
+      <c r="H36" s="81"/>
+      <c r="I36" s="81"/>
+      <c r="J36" s="81"/>
+      <c r="K36" s="81"/>
+      <c r="L36" s="81"/>
     </row>
     <row r="37" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="33">
         <v>12</v>
       </c>
       <c r="B37" s="34" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C37" s="34"/>
-      <c r="D37" s="140"/>
-      <c r="E37" s="140"/>
-      <c r="F37" s="140"/>
-      <c r="G37" s="140"/>
-      <c r="H37" s="140"/>
-      <c r="I37" s="140"/>
-      <c r="J37" s="140"/>
-      <c r="K37" s="140"/>
-      <c r="L37" s="140"/>
+      <c r="D37" s="175"/>
+      <c r="E37" s="81"/>
+      <c r="F37" s="81"/>
+      <c r="G37" s="81"/>
+      <c r="H37" s="81"/>
+      <c r="I37" s="81"/>
+      <c r="J37" s="81"/>
+      <c r="K37" s="81"/>
+      <c r="L37" s="81"/>
     </row>
     <row r="38" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="33">
         <v>13</v>
       </c>
       <c r="B38" s="34" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C38" s="34"/>
-      <c r="D38" s="140"/>
-      <c r="E38" s="140"/>
-      <c r="F38" s="140"/>
-      <c r="G38" s="140"/>
-      <c r="H38" s="140"/>
-      <c r="I38" s="140"/>
-      <c r="J38" s="140"/>
-      <c r="K38" s="140"/>
-      <c r="L38" s="140"/>
+      <c r="D38" s="175"/>
+      <c r="E38" s="81"/>
+      <c r="F38" s="81"/>
+      <c r="G38" s="81"/>
+      <c r="H38" s="81"/>
+      <c r="I38" s="81"/>
+      <c r="J38" s="81"/>
+      <c r="K38" s="81"/>
+      <c r="L38" s="81"/>
     </row>
     <row r="39" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="33">
         <v>14</v>
       </c>
       <c r="B39" s="34" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C39" s="34"/>
-      <c r="D39" s="140"/>
-      <c r="E39" s="140"/>
-      <c r="F39" s="140"/>
-      <c r="G39" s="140"/>
-      <c r="H39" s="140"/>
-      <c r="I39" s="140"/>
-      <c r="J39" s="140"/>
-      <c r="K39" s="140"/>
-      <c r="L39" s="140"/>
+      <c r="D39" s="175"/>
+      <c r="E39" s="81"/>
+      <c r="F39" s="81"/>
+      <c r="G39" s="81"/>
+      <c r="H39" s="81"/>
+      <c r="I39" s="81"/>
+      <c r="J39" s="81"/>
+      <c r="K39" s="81"/>
+      <c r="L39" s="81"/>
     </row>
     <row r="40" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="33">
         <v>15</v>
       </c>
       <c r="B40" s="34" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C40" s="34"/>
-      <c r="D40" s="140"/>
-      <c r="E40" s="140"/>
-      <c r="F40" s="140"/>
-      <c r="G40" s="140"/>
-      <c r="H40" s="140"/>
-      <c r="I40" s="140"/>
-      <c r="J40" s="140"/>
-      <c r="K40" s="140"/>
-      <c r="L40" s="140"/>
+      <c r="D40" s="175"/>
+      <c r="E40" s="81"/>
+      <c r="F40" s="81"/>
+      <c r="G40" s="81"/>
+      <c r="H40" s="81"/>
+      <c r="I40" s="81"/>
+      <c r="J40" s="81"/>
+      <c r="K40" s="81"/>
+      <c r="L40" s="81"/>
     </row>
     <row r="41" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="33">
         <v>16</v>
       </c>
       <c r="B41" s="34" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C41" s="34"/>
-      <c r="D41" s="140"/>
-      <c r="E41" s="140"/>
-      <c r="F41" s="140"/>
-      <c r="G41" s="140"/>
-      <c r="H41" s="140"/>
-      <c r="I41" s="140"/>
-      <c r="J41" s="140"/>
-      <c r="K41" s="140"/>
-      <c r="L41" s="140"/>
+      <c r="D41" s="175"/>
+      <c r="E41" s="81"/>
+      <c r="F41" s="81"/>
+      <c r="G41" s="81"/>
+      <c r="H41" s="81"/>
+      <c r="I41" s="81"/>
+      <c r="J41" s="81"/>
+      <c r="K41" s="81"/>
+      <c r="L41" s="81"/>
     </row>
     <row r="42" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="33">
         <v>17</v>
       </c>
       <c r="B42" s="34" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C42" s="34"/>
-      <c r="D42" s="140"/>
-      <c r="E42" s="140"/>
-      <c r="F42" s="140"/>
-      <c r="G42" s="140"/>
-      <c r="H42" s="140"/>
-      <c r="I42" s="140"/>
-      <c r="J42" s="140"/>
-      <c r="K42" s="140"/>
-      <c r="L42" s="140"/>
+      <c r="D42" s="175"/>
+      <c r="E42" s="81"/>
+      <c r="F42" s="81"/>
+      <c r="G42" s="81"/>
+      <c r="H42" s="81"/>
+      <c r="I42" s="81"/>
+      <c r="J42" s="81"/>
+      <c r="K42" s="81"/>
+      <c r="L42" s="81"/>
     </row>
     <row r="43" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="33">
         <v>18</v>
       </c>
       <c r="B43" s="34" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C43" s="34"/>
-      <c r="D43" s="140"/>
-      <c r="E43" s="140"/>
-      <c r="F43" s="140"/>
-      <c r="G43" s="140"/>
-      <c r="H43" s="140"/>
-      <c r="I43" s="140"/>
-      <c r="J43" s="140"/>
-      <c r="K43" s="140"/>
-      <c r="L43" s="140"/>
+      <c r="D43" s="175"/>
+      <c r="E43" s="81"/>
+      <c r="F43" s="81"/>
+      <c r="G43" s="81"/>
+      <c r="H43" s="81"/>
+      <c r="I43" s="81"/>
+      <c r="J43" s="81"/>
+      <c r="K43" s="81"/>
+      <c r="L43" s="81"/>
     </row>
     <row r="44" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="33">
         <v>19</v>
       </c>
       <c r="B44" s="34" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C44" s="34"/>
-      <c r="D44" s="140"/>
-      <c r="E44" s="140"/>
-      <c r="F44" s="140"/>
-      <c r="G44" s="140"/>
-      <c r="H44" s="140"/>
-      <c r="I44" s="140"/>
-      <c r="J44" s="140"/>
-      <c r="K44" s="140"/>
-      <c r="L44" s="140"/>
+      <c r="D44" s="175"/>
+      <c r="E44" s="81"/>
+      <c r="F44" s="81"/>
+      <c r="G44" s="81"/>
+      <c r="H44" s="81"/>
+      <c r="I44" s="81"/>
+      <c r="J44" s="81"/>
+      <c r="K44" s="81"/>
+      <c r="L44" s="81"/>
     </row>
     <row r="45" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="33">
         <v>20</v>
       </c>
       <c r="B45" s="34" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C45" s="34"/>
-      <c r="D45" s="140"/>
-      <c r="E45" s="140"/>
-      <c r="F45" s="140"/>
-      <c r="G45" s="140"/>
-      <c r="H45" s="140"/>
-      <c r="I45" s="140"/>
-      <c r="J45" s="140"/>
-      <c r="K45" s="140"/>
-      <c r="L45" s="140"/>
+      <c r="D45" s="175"/>
+      <c r="E45" s="81"/>
+      <c r="F45" s="81"/>
+      <c r="G45" s="81"/>
+      <c r="H45" s="81"/>
+      <c r="I45" s="81"/>
+      <c r="J45" s="81"/>
+      <c r="K45" s="81"/>
+      <c r="L45" s="81"/>
     </row>
     <row r="46" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="33">
         <v>21</v>
       </c>
       <c r="B46" s="34" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C46" s="34"/>
-      <c r="D46" s="140"/>
-      <c r="E46" s="140"/>
-      <c r="F46" s="140"/>
-      <c r="G46" s="140"/>
-      <c r="H46" s="140"/>
-      <c r="I46" s="140"/>
-      <c r="J46" s="140"/>
-      <c r="K46" s="140"/>
-      <c r="L46" s="140"/>
+      <c r="D46" s="175"/>
+      <c r="E46" s="81"/>
+      <c r="F46" s="81"/>
+      <c r="G46" s="81"/>
+      <c r="H46" s="81"/>
+      <c r="I46" s="81"/>
+      <c r="J46" s="81"/>
+      <c r="K46" s="81"/>
+      <c r="L46" s="81"/>
     </row>
     <row r="47" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="33">
         <v>22</v>
       </c>
       <c r="B47" s="34" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C47" s="34"/>
-      <c r="D47" s="140"/>
-      <c r="E47" s="140"/>
-      <c r="F47" s="140"/>
-      <c r="G47" s="140"/>
-      <c r="H47" s="140"/>
-      <c r="I47" s="140"/>
-      <c r="J47" s="140"/>
-      <c r="K47" s="140"/>
-      <c r="L47" s="140"/>
+      <c r="D47" s="175"/>
+      <c r="E47" s="81"/>
+      <c r="F47" s="81"/>
+      <c r="G47" s="81"/>
+      <c r="H47" s="81"/>
+      <c r="I47" s="81"/>
+      <c r="J47" s="81"/>
+      <c r="K47" s="81"/>
+      <c r="L47" s="81"/>
     </row>
     <row r="48" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="33">
         <v>23</v>
       </c>
       <c r="B48" s="34" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C48" s="34"/>
-      <c r="D48" s="140"/>
-      <c r="E48" s="140"/>
-      <c r="F48" s="140"/>
-      <c r="G48" s="140"/>
-      <c r="H48" s="140"/>
-      <c r="I48" s="140"/>
-      <c r="J48" s="140"/>
-      <c r="K48" s="140"/>
-      <c r="L48" s="140"/>
+      <c r="D48" s="175"/>
+      <c r="E48" s="81"/>
+      <c r="F48" s="81"/>
+      <c r="G48" s="81"/>
+      <c r="H48" s="81"/>
+      <c r="I48" s="81"/>
+      <c r="J48" s="81"/>
+      <c r="K48" s="81"/>
+      <c r="L48" s="81"/>
     </row>
     <row r="49" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="33">
         <v>24</v>
       </c>
       <c r="B49" s="34" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C49" s="34"/>
-      <c r="D49" s="140"/>
-      <c r="E49" s="140"/>
-      <c r="F49" s="140"/>
-      <c r="G49" s="140"/>
-      <c r="H49" s="140"/>
-      <c r="I49" s="140"/>
-      <c r="J49" s="140"/>
-      <c r="K49" s="140"/>
-      <c r="L49" s="140"/>
+      <c r="D49" s="175"/>
+      <c r="E49" s="81"/>
+      <c r="F49" s="81"/>
+      <c r="G49" s="81"/>
+      <c r="H49" s="81"/>
+      <c r="I49" s="81"/>
+      <c r="J49" s="81"/>
+      <c r="K49" s="81"/>
+      <c r="L49" s="81"/>
     </row>
     <row r="50" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="72">
         <v>25</v>
       </c>
       <c r="B50" s="77" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C50" s="34"/>
-      <c r="D50" s="140"/>
-      <c r="E50" s="140"/>
-      <c r="F50" s="140"/>
-      <c r="G50" s="140"/>
-      <c r="H50" s="140"/>
-      <c r="I50" s="140"/>
-      <c r="J50" s="140"/>
-      <c r="K50" s="140"/>
-      <c r="L50" s="140"/>
+      <c r="D50" s="175"/>
+      <c r="E50" s="81"/>
+      <c r="F50" s="81"/>
+      <c r="G50" s="81"/>
+      <c r="H50" s="81"/>
+      <c r="I50" s="81"/>
+      <c r="J50" s="81"/>
+      <c r="K50" s="81"/>
+      <c r="L50" s="81"/>
     </row>
     <row r="51" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="72">
         <v>26</v>
       </c>
       <c r="B51" s="77" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C51" s="34"/>
-      <c r="D51" s="140"/>
-      <c r="E51" s="140"/>
-      <c r="F51" s="140"/>
-      <c r="G51" s="140"/>
-      <c r="H51" s="140"/>
-      <c r="I51" s="140"/>
-      <c r="J51" s="140"/>
-      <c r="K51" s="140"/>
-      <c r="L51" s="140"/>
+      <c r="D51" s="175"/>
+      <c r="E51" s="81"/>
+      <c r="F51" s="81"/>
+      <c r="G51" s="81"/>
+      <c r="H51" s="81"/>
+      <c r="I51" s="81"/>
+      <c r="J51" s="81"/>
+      <c r="K51" s="81"/>
+      <c r="L51" s="81"/>
     </row>
     <row r="52" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="72">
         <v>27</v>
       </c>
       <c r="B52" s="77" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C52" s="34"/>
-      <c r="D52" s="140"/>
-      <c r="E52" s="140"/>
-      <c r="F52" s="140"/>
-      <c r="G52" s="140"/>
-      <c r="H52" s="140"/>
-      <c r="I52" s="140"/>
-      <c r="J52" s="140"/>
-      <c r="K52" s="140"/>
-      <c r="L52" s="140"/>
+      <c r="D52" s="175"/>
+      <c r="E52" s="81"/>
+      <c r="F52" s="81"/>
+      <c r="G52" s="81"/>
+      <c r="H52" s="81"/>
+      <c r="I52" s="81"/>
+      <c r="J52" s="81"/>
+      <c r="K52" s="81"/>
+      <c r="L52" s="81"/>
     </row>
     <row r="53" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="72">
         <v>28</v>
       </c>
       <c r="B53" s="78" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C53" s="79"/>
-      <c r="D53" s="140"/>
-      <c r="E53" s="140"/>
-      <c r="F53" s="140"/>
-      <c r="G53" s="140"/>
-      <c r="H53" s="140"/>
-      <c r="I53" s="140"/>
-      <c r="J53" s="140"/>
-      <c r="K53" s="140"/>
-      <c r="L53" s="140"/>
+      <c r="D53" s="175"/>
+      <c r="E53" s="81"/>
+      <c r="F53" s="81"/>
+      <c r="G53" s="81"/>
+      <c r="H53" s="81"/>
+      <c r="I53" s="81"/>
+      <c r="J53" s="81"/>
+      <c r="K53" s="81"/>
+      <c r="L53" s="81"/>
     </row>
     <row r="54" spans="1:12" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="72">
@@ -12329,51 +12414,51 @@
         <v>144</v>
       </c>
       <c r="C54" s="72"/>
-      <c r="D54" s="140"/>
-      <c r="E54" s="140"/>
-      <c r="F54" s="140"/>
-      <c r="G54" s="140"/>
-      <c r="H54" s="140"/>
-      <c r="I54" s="140"/>
-      <c r="J54" s="140"/>
-      <c r="K54" s="140"/>
-      <c r="L54" s="140"/>
+      <c r="D54" s="175"/>
+      <c r="E54" s="81"/>
+      <c r="F54" s="81"/>
+      <c r="G54" s="81"/>
+      <c r="H54" s="81"/>
+      <c r="I54" s="81"/>
+      <c r="J54" s="81"/>
+      <c r="K54" s="81"/>
+      <c r="L54" s="81"/>
     </row>
     <row r="55" spans="1:12" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="72">
         <v>30</v>
       </c>
       <c r="B55" s="78" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C55" s="78"/>
-      <c r="D55" s="140"/>
-      <c r="E55" s="140"/>
-      <c r="F55" s="140"/>
-      <c r="G55" s="140"/>
-      <c r="H55" s="140"/>
-      <c r="I55" s="140"/>
-      <c r="J55" s="140"/>
-      <c r="K55" s="140"/>
-      <c r="L55" s="140"/>
+      <c r="D55" s="175"/>
+      <c r="E55" s="81"/>
+      <c r="F55" s="81"/>
+      <c r="G55" s="81"/>
+      <c r="H55" s="81"/>
+      <c r="I55" s="81"/>
+      <c r="J55" s="81"/>
+      <c r="K55" s="81"/>
+      <c r="L55" s="81"/>
     </row>
     <row r="56" spans="1:12" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="72">
         <v>31</v>
       </c>
       <c r="B56" s="78" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C56" s="78"/>
-      <c r="D56" s="140"/>
-      <c r="E56" s="140"/>
-      <c r="F56" s="140"/>
-      <c r="G56" s="140"/>
-      <c r="H56" s="140"/>
-      <c r="I56" s="140"/>
-      <c r="J56" s="140"/>
-      <c r="K56" s="140"/>
-      <c r="L56" s="140"/>
+      <c r="D56" s="175"/>
+      <c r="E56" s="81"/>
+      <c r="F56" s="81"/>
+      <c r="G56" s="81"/>
+      <c r="H56" s="81"/>
+      <c r="I56" s="81"/>
+      <c r="J56" s="81"/>
+      <c r="K56" s="81"/>
+      <c r="L56" s="81"/>
     </row>
     <row r="57" spans="1:12" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="72">
@@ -12383,26 +12468,36 @@
         <v>147</v>
       </c>
       <c r="C57" s="78"/>
-      <c r="D57" s="140"/>
-      <c r="E57" s="140"/>
-      <c r="F57" s="140"/>
-      <c r="G57" s="140"/>
-      <c r="H57" s="140"/>
-      <c r="I57" s="140"/>
-      <c r="J57" s="140"/>
-      <c r="K57" s="140"/>
-      <c r="L57" s="140"/>
+      <c r="D57" s="175"/>
+      <c r="E57" s="81"/>
+      <c r="F57" s="81"/>
+      <c r="G57" s="81"/>
+      <c r="H57" s="81"/>
+      <c r="I57" s="81"/>
+      <c r="J57" s="81"/>
+      <c r="K57" s="81"/>
+      <c r="L57" s="81"/>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A58" s="173">
+        <v>33</v>
+      </c>
+      <c r="B58" s="78" t="s">
+        <v>148</v>
+      </c>
+      <c r="C58" s="78"/>
+      <c r="D58" s="175"/>
+      <c r="E58" s="81"/>
+      <c r="F58" s="81"/>
+      <c r="G58" s="81"/>
+      <c r="H58" s="81"/>
+      <c r="I58" s="81"/>
+      <c r="J58" s="81"/>
+      <c r="K58" s="81"/>
+      <c r="L58" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="D26:L57"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:L20"/>
-    <mergeCell ref="D25:L25"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:L22"/>
     <mergeCell ref="A16:L16"/>
     <mergeCell ref="A17:L17"/>
     <mergeCell ref="B15:L15"/>
@@ -12414,6 +12509,14 @@
     <mergeCell ref="B4:L4"/>
     <mergeCell ref="B5:L5"/>
     <mergeCell ref="B7:L7"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:L20"/>
+    <mergeCell ref="D25:L25"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:L22"/>
+    <mergeCell ref="D26:L58"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D26" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -15433,6 +15536,28 @@
                     <xdr:colOff>1409700</xdr:colOff>
                     <xdr:row>57</xdr:row>
                     <xdr:rowOff>7620</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1240" r:id="rId142" name="Drop Down 216">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>57</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>1409700</xdr:colOff>
+                    <xdr:row>58</xdr:row>
+                    <xdr:rowOff>38100</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15462,50 +15587,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="149" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="151"/>
-      <c r="C1" s="151"/>
-      <c r="D1" s="151"/>
-      <c r="E1" s="151"/>
-      <c r="F1" s="151"/>
-      <c r="G1" s="151"/>
-      <c r="H1" s="151"/>
-      <c r="I1" s="151"/>
-      <c r="J1" s="151"/>
-      <c r="K1" s="151"/>
-      <c r="L1" s="152"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
+      <c r="G1" s="150"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="150"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="151"/>
     </row>
     <row r="2" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="153" t="s">
+      <c r="A2" s="152" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="154"/>
-      <c r="C2" s="154"/>
-      <c r="D2" s="154"/>
-      <c r="E2" s="154"/>
-      <c r="F2" s="154"/>
-      <c r="G2" s="154"/>
-      <c r="H2" s="154"/>
-      <c r="I2" s="154"/>
-      <c r="J2" s="154"/>
-      <c r="K2" s="154"/>
-      <c r="L2" s="155"/>
+      <c r="B2" s="153"/>
+      <c r="C2" s="153"/>
+      <c r="D2" s="153"/>
+      <c r="E2" s="153"/>
+      <c r="F2" s="153"/>
+      <c r="G2" s="153"/>
+      <c r="H2" s="153"/>
+      <c r="I2" s="153"/>
+      <c r="J2" s="153"/>
+      <c r="K2" s="153"/>
+      <c r="L2" s="154"/>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="156"/>
-      <c r="B3" s="157"/>
-      <c r="C3" s="157"/>
-      <c r="D3" s="157"/>
-      <c r="E3" s="157"/>
-      <c r="F3" s="157"/>
-      <c r="G3" s="157"/>
-      <c r="H3" s="157"/>
-      <c r="I3" s="157"/>
-      <c r="J3" s="157"/>
-      <c r="K3" s="157"/>
-      <c r="L3" s="158"/>
+      <c r="A3" s="155"/>
+      <c r="B3" s="156"/>
+      <c r="C3" s="156"/>
+      <c r="D3" s="156"/>
+      <c r="E3" s="156"/>
+      <c r="F3" s="156"/>
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="156"/>
+      <c r="K3" s="156"/>
+      <c r="L3" s="157"/>
     </row>
     <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
@@ -15595,65 +15720,65 @@
       <c r="A8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="161"/>
-      <c r="C8" s="162"/>
-      <c r="D8" s="162"/>
-      <c r="E8" s="162"/>
-      <c r="F8" s="162"/>
-      <c r="G8" s="162"/>
-      <c r="H8" s="162"/>
-      <c r="I8" s="162"/>
-      <c r="J8" s="162"/>
-      <c r="K8" s="162"/>
-      <c r="L8" s="163"/>
+      <c r="B8" s="160"/>
+      <c r="C8" s="161"/>
+      <c r="D8" s="161"/>
+      <c r="E8" s="161"/>
+      <c r="F8" s="161"/>
+      <c r="G8" s="161"/>
+      <c r="H8" s="161"/>
+      <c r="I8" s="161"/>
+      <c r="J8" s="161"/>
+      <c r="K8" s="161"/>
+      <c r="L8" s="162"/>
     </row>
     <row r="9" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="164"/>
-      <c r="C9" s="162"/>
-      <c r="D9" s="162"/>
-      <c r="E9" s="162"/>
-      <c r="F9" s="162"/>
-      <c r="G9" s="162"/>
-      <c r="H9" s="162"/>
-      <c r="I9" s="162"/>
-      <c r="J9" s="162"/>
-      <c r="K9" s="162"/>
-      <c r="L9" s="163"/>
+      <c r="B9" s="163"/>
+      <c r="C9" s="161"/>
+      <c r="D9" s="161"/>
+      <c r="E9" s="161"/>
+      <c r="F9" s="161"/>
+      <c r="G9" s="161"/>
+      <c r="H9" s="161"/>
+      <c r="I9" s="161"/>
+      <c r="J9" s="161"/>
+      <c r="K9" s="161"/>
+      <c r="L9" s="162"/>
     </row>
     <row r="10" spans="1:12" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="159" t="s">
+      <c r="A10" s="158" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="160"/>
-      <c r="C10" s="160"/>
-      <c r="D10" s="160"/>
-      <c r="E10" s="160"/>
-      <c r="F10" s="160"/>
-      <c r="G10" s="160"/>
-      <c r="H10" s="160"/>
-      <c r="I10" s="160"/>
-      <c r="J10" s="160"/>
-      <c r="K10" s="160"/>
-      <c r="L10" s="160"/>
+      <c r="B10" s="159"/>
+      <c r="C10" s="159"/>
+      <c r="D10" s="159"/>
+      <c r="E10" s="159"/>
+      <c r="F10" s="159"/>
+      <c r="G10" s="159"/>
+      <c r="H10" s="159"/>
+      <c r="I10" s="159"/>
+      <c r="J10" s="159"/>
+      <c r="K10" s="159"/>
+      <c r="L10" s="159"/>
     </row>
     <row r="11" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="141" t="s">
+      <c r="A11" s="140" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="142"/>
-      <c r="C11" s="142"/>
-      <c r="D11" s="142"/>
-      <c r="E11" s="142"/>
-      <c r="F11" s="142"/>
-      <c r="G11" s="142"/>
-      <c r="H11" s="142"/>
-      <c r="I11" s="142"/>
-      <c r="J11" s="142"/>
-      <c r="K11" s="142"/>
-      <c r="L11" s="143"/>
+      <c r="B11" s="141"/>
+      <c r="C11" s="141"/>
+      <c r="D11" s="141"/>
+      <c r="E11" s="141"/>
+      <c r="F11" s="141"/>
+      <c r="G11" s="141"/>
+      <c r="H11" s="141"/>
+      <c r="I11" s="141"/>
+      <c r="J11" s="141"/>
+      <c r="K11" s="141"/>
+      <c r="L11" s="142"/>
     </row>
     <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
@@ -15665,101 +15790,101 @@
       <c r="C12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="123" t="s">
+      <c r="D12" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="123"/>
-      <c r="F12" s="123"/>
-      <c r="G12" s="123"/>
-      <c r="H12" s="123"/>
-      <c r="I12" s="123"/>
-      <c r="J12" s="123"/>
-      <c r="K12" s="123"/>
-      <c r="L12" s="123"/>
+      <c r="E12" s="90"/>
+      <c r="F12" s="90"/>
+      <c r="G12" s="90"/>
+      <c r="H12" s="90"/>
+      <c r="I12" s="90"/>
+      <c r="J12" s="90"/>
+      <c r="K12" s="90"/>
+      <c r="L12" s="90"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="49"/>
       <c r="B13" s="50"/>
       <c r="C13" s="50"/>
-      <c r="D13" s="144"/>
-      <c r="E13" s="145"/>
-      <c r="F13" s="145"/>
-      <c r="G13" s="145"/>
-      <c r="H13" s="145"/>
-      <c r="I13" s="145"/>
-      <c r="J13" s="145"/>
-      <c r="K13" s="145"/>
-      <c r="L13" s="146"/>
+      <c r="D13" s="143"/>
+      <c r="E13" s="144"/>
+      <c r="F13" s="144"/>
+      <c r="G13" s="144"/>
+      <c r="H13" s="144"/>
+      <c r="I13" s="144"/>
+      <c r="J13" s="144"/>
+      <c r="K13" s="144"/>
+      <c r="L13" s="145"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="49"/>
       <c r="B14" s="50"/>
       <c r="C14" s="50"/>
-      <c r="D14" s="147"/>
-      <c r="E14" s="148"/>
-      <c r="F14" s="148"/>
-      <c r="G14" s="148"/>
-      <c r="H14" s="148"/>
-      <c r="I14" s="148"/>
-      <c r="J14" s="148"/>
-      <c r="K14" s="148"/>
-      <c r="L14" s="149"/>
+      <c r="D14" s="146"/>
+      <c r="E14" s="147"/>
+      <c r="F14" s="147"/>
+      <c r="G14" s="147"/>
+      <c r="H14" s="147"/>
+      <c r="I14" s="147"/>
+      <c r="J14" s="147"/>
+      <c r="K14" s="147"/>
+      <c r="L14" s="148"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="49"/>
       <c r="B15" s="50"/>
       <c r="C15" s="50"/>
-      <c r="D15" s="147"/>
-      <c r="E15" s="148"/>
-      <c r="F15" s="148"/>
-      <c r="G15" s="148"/>
-      <c r="H15" s="148"/>
-      <c r="I15" s="148"/>
-      <c r="J15" s="148"/>
-      <c r="K15" s="148"/>
-      <c r="L15" s="149"/>
+      <c r="D15" s="146"/>
+      <c r="E15" s="147"/>
+      <c r="F15" s="147"/>
+      <c r="G15" s="147"/>
+      <c r="H15" s="147"/>
+      <c r="I15" s="147"/>
+      <c r="J15" s="147"/>
+      <c r="K15" s="147"/>
+      <c r="L15" s="148"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="49"/>
       <c r="B16" s="50"/>
       <c r="C16" s="50"/>
-      <c r="D16" s="147"/>
-      <c r="E16" s="148"/>
-      <c r="F16" s="148"/>
-      <c r="G16" s="148"/>
-      <c r="H16" s="148"/>
-      <c r="I16" s="148"/>
-      <c r="J16" s="148"/>
-      <c r="K16" s="148"/>
-      <c r="L16" s="149"/>
+      <c r="D16" s="146"/>
+      <c r="E16" s="147"/>
+      <c r="F16" s="147"/>
+      <c r="G16" s="147"/>
+      <c r="H16" s="147"/>
+      <c r="I16" s="147"/>
+      <c r="J16" s="147"/>
+      <c r="K16" s="147"/>
+      <c r="L16" s="148"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="49"/>
       <c r="B17" s="50"/>
       <c r="C17" s="50"/>
-      <c r="D17" s="147"/>
-      <c r="E17" s="148"/>
-      <c r="F17" s="148"/>
-      <c r="G17" s="148"/>
-      <c r="H17" s="148"/>
-      <c r="I17" s="148"/>
-      <c r="J17" s="148"/>
-      <c r="K17" s="148"/>
-      <c r="L17" s="149"/>
+      <c r="D17" s="146"/>
+      <c r="E17" s="147"/>
+      <c r="F17" s="147"/>
+      <c r="G17" s="147"/>
+      <c r="H17" s="147"/>
+      <c r="I17" s="147"/>
+      <c r="J17" s="147"/>
+      <c r="K17" s="147"/>
+      <c r="L17" s="148"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="49"/>
       <c r="B18" s="50"/>
       <c r="C18" s="50"/>
-      <c r="D18" s="147"/>
-      <c r="E18" s="148"/>
-      <c r="F18" s="148"/>
-      <c r="G18" s="148"/>
-      <c r="H18" s="148"/>
-      <c r="I18" s="148"/>
-      <c r="J18" s="148"/>
-      <c r="K18" s="148"/>
-      <c r="L18" s="149"/>
+      <c r="D18" s="146"/>
+      <c r="E18" s="147"/>
+      <c r="F18" s="147"/>
+      <c r="G18" s="147"/>
+      <c r="H18" s="147"/>
+      <c r="I18" s="147"/>
+      <c r="J18" s="147"/>
+      <c r="K18" s="147"/>
+      <c r="L18" s="148"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -15848,10 +15973,10 @@
       <c r="B4" s="63"/>
     </row>
     <row r="6" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="164" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="80"/>
+      <c r="B6" s="164"/>
     </row>
     <row r="8" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="66" t="s">
@@ -16583,6 +16708,68 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50">
+      <UserInfo>
+        <DisplayName>Luis Campos / Logiztik Alliance</DisplayName>
+        <AccountId>265</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Jairo Gonzalez / Logiztik Alliance</DisplayName>
+        <AccountId>322</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>José Ganchozo / Logiztik Alliance</DisplayName>
+        <AccountId>304</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Edwin Casa / Logiztik Alliance</DisplayName>
+        <AccountId>299</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Cristhian Cuichan / Logiztik Alliance</DisplayName>
+        <AccountId>369</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Oscar Yunda /  Logiztik Alliance</DisplayName>
+        <AccountId>355</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Fernando Ordoñez / Logiztik Alliance</DisplayName>
+        <AccountId>321</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Alex Rivera / Logiztik Alliance</DisplayName>
+        <AccountId>370</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <TaxCatchAll xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="87481c51-c14c-4071-bf64-faa2b5708bb6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101005DA7AC6E4F4FAE42B9D9FCD9C82CAAE1" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="553e0bb76796fbad2df2b84fb95dc83d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="87481c51-c14c-4071-bf64-faa2b5708bb6" xmlns:ns3="8029d101-3d2a-47c4-b15f-619642bf5e50" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d87cd7f238c73dc12c577d08dde48736" ns2:_="" ns3:_="">
     <xsd:import namespace="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
@@ -16831,69 +17018,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD069904-634F-48DA-AA92-BAE250498BEE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8029d101-3d2a-47c4-b15f-619642bf5e50"/>
+    <ds:schemaRef ds:uri="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50">
-      <UserInfo>
-        <DisplayName>Luis Campos / Logiztik Alliance</DisplayName>
-        <AccountId>265</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Jairo Gonzalez / Logiztik Alliance</DisplayName>
-        <AccountId>322</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>José Ganchozo / Logiztik Alliance</DisplayName>
-        <AccountId>304</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Edwin Casa / Logiztik Alliance</DisplayName>
-        <AccountId>299</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Cristhian Cuichan / Logiztik Alliance</DisplayName>
-        <AccountId>369</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Oscar Yunda /  Logiztik Alliance</DisplayName>
-        <AccountId>355</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Fernando Ordoñez / Logiztik Alliance</DisplayName>
-        <AccountId>321</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Alex Rivera / Logiztik Alliance</DisplayName>
-        <AccountId>370</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <TaxCatchAll xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="87481c51-c14c-4071-bf64-faa2b5708bb6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371D8832-41B3-447B-B13D-2663C267E34F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F7F06D0-41B3-4EAF-B418-88FC726117CC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -16910,23 +17054,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371D8832-41B3-447B-B13D-2663C267E34F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD069904-634F-48DA-AA92-BAE250498BEE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8029d101-3d2a-47c4-b15f-619642bf5e50"/>
-    <ds:schemaRef ds:uri="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Guias Produccion/HU-57723.xlsx
+++ b/Guias Produccion/HU-57723.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Alliance\ScriptsEntidades\Guias Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0C0A8B-CDE1-4CBF-902C-EB20E9B41D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54365CC9-637D-49ED-8D68-74E0504C7C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="155">
   <si>
     <t>Guia documentación</t>
   </si>
@@ -611,6 +611,24 @@
   <si>
     <t>33-AC_pro_GetCompletedDeliveredPickupShipTo.sql</t>
   </si>
+  <si>
+    <t>34-AC_pro_GetPendingPickup.sql</t>
+  </si>
+  <si>
+    <t>35-AC_pro_GetPendingPickupDetails.sql</t>
+  </si>
+  <si>
+    <t>38-AC_pro_GetCompletedDeliveredPickupDetail.sql</t>
+  </si>
+  <si>
+    <t>39-AC_pro_GetCompletedScheduledPickupDetail.sql</t>
+  </si>
+  <si>
+    <t>36-AC_pro_GetCompletedDeliveredPickupShipTo.sql</t>
+  </si>
+  <si>
+    <t>37-AC_pro_GetCompletedScheduledPickupShipTo.sql</t>
+  </si>
 </sst>
 </file>
 
@@ -829,7 +847,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="79">
+  <borders count="78">
     <border>
       <left/>
       <right/>
@@ -1814,23 +1832,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="173">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1983,84 +1990,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="75" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="76" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="77" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2163,6 +2092,84 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2261,15 +2268,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="54" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2466,7 +2464,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp139.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$17" noThreeD="1" sel="17" val="9"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$18" noThreeD="1" sel="8" val="3"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2474,6 +2472,30 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp140.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$18" noThreeD="1" sel="8" val="3"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp141.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$18" noThreeD="1" sel="8" val="3"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp142.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$18" noThreeD="1" sel="8" val="3"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp143.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$18" noThreeD="1" sel="8" val="3"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp144.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$18" noThreeD="1" sel="8" val="3"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp145.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$17" noThreeD="1" sel="17" val="9"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp146.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$17" noThreeD="1" sel="17" val="9"/>
 </file>
 
@@ -10635,8 +10657,8 @@
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>55</xdr:row>
-          <xdr:rowOff>7620</xdr:rowOff>
+          <xdr:row>54</xdr:row>
+          <xdr:rowOff>222773</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10693,8 +10715,8 @@
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>56</xdr:row>
-          <xdr:rowOff>7620</xdr:rowOff>
+          <xdr:row>55</xdr:row>
+          <xdr:rowOff>222773</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10751,8 +10773,8 @@
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>57</xdr:row>
-          <xdr:rowOff>7620</xdr:rowOff>
+          <xdr:row>56</xdr:row>
+          <xdr:rowOff>222773</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10809,8 +10831,8 @@
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>58</xdr:row>
-          <xdr:rowOff>38100</xdr:rowOff>
+          <xdr:row>57</xdr:row>
+          <xdr:rowOff>217394</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10820,7 +10842,355 @@
                   <a14:compatExt spid="_x0000_s1240"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF2454DC-C779-3BA6-DA50-36A79288A231}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D8040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>58</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>1409700</xdr:colOff>
+          <xdr:row>58</xdr:row>
+          <xdr:rowOff>220980</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1241" name="Drop Down 217" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1241"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98B1A0C3-498D-B973-63A0-459F704F1CE6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>59</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>1409700</xdr:colOff>
+          <xdr:row>59</xdr:row>
+          <xdr:rowOff>220980</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1242" name="Drop Down 218" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1242"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8BB485B9-BD9C-436C-B9E9-ECD38173C272}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>60</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>1409700</xdr:colOff>
+          <xdr:row>60</xdr:row>
+          <xdr:rowOff>220980</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1243" name="Drop Down 219" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1243"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D400A784-471F-9085-FFE7-4A994C91E86C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>61</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>1409700</xdr:colOff>
+          <xdr:row>61</xdr:row>
+          <xdr:rowOff>220980</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1244" name="Drop Down 220" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1244"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{527A9FB2-3393-0AD8-7091-4DEB3A6FF31A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>62</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>1409700</xdr:colOff>
+          <xdr:row>62</xdr:row>
+          <xdr:rowOff>220980</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1245" name="Drop Down 221" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1245"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{359D7B14-F917-8BCB-0339-BFCEEB1C7B3A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>63</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>1409700</xdr:colOff>
+          <xdr:row>63</xdr:row>
+          <xdr:rowOff>220980</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1246" name="Drop Down 222" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1246"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AB1582C-D455-F1D6-6827-27C1E6BBBC80}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -11446,7 +11816,7 @@
   <sheetPr codeName="Hoja1">
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A3:O58"/>
+  <dimension ref="A3:O64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.44140625" bestFit="1" customWidth="1"/>
@@ -11465,42 +11835,42 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:15" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="122" t="s">
+      <c r="A3" s="96" t="s">
         <v>103</v>
       </c>
-      <c r="B3" s="123"/>
-      <c r="C3" s="123"/>
-      <c r="D3" s="123"/>
-      <c r="E3" s="123"/>
-      <c r="F3" s="123"/>
-      <c r="G3" s="123"/>
-      <c r="H3" s="123"/>
-      <c r="I3" s="123"/>
-      <c r="J3" s="123"/>
-      <c r="K3" s="123"/>
-      <c r="L3" s="124"/>
-      <c r="N3" s="116" t="s">
+      <c r="B3" s="97"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="97"/>
+      <c r="K3" s="97"/>
+      <c r="L3" s="98"/>
+      <c r="N3" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="O3" s="117"/>
+      <c r="O3" s="91"/>
     </row>
     <row r="4" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="129" t="s">
+      <c r="B4" s="103" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="130"/>
-      <c r="D4" s="130"/>
-      <c r="E4" s="130"/>
-      <c r="F4" s="130"/>
-      <c r="G4" s="130"/>
-      <c r="H4" s="130"/>
-      <c r="I4" s="130"/>
-      <c r="J4" s="131"/>
-      <c r="K4" s="131"/>
-      <c r="L4" s="132"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="105"/>
+      <c r="L4" s="106"/>
       <c r="N4" s="21" t="s">
         <v>2</v>
       </c>
@@ -11510,19 +11880,19 @@
       <c r="A5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="133" t="s">
+      <c r="B5" s="107" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="133"/>
-      <c r="D5" s="133"/>
-      <c r="E5" s="133"/>
-      <c r="F5" s="133"/>
-      <c r="G5" s="133"/>
-      <c r="H5" s="133"/>
-      <c r="I5" s="133"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="135"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="107"/>
+      <c r="G5" s="107"/>
+      <c r="H5" s="107"/>
+      <c r="I5" s="107"/>
+      <c r="J5" s="108"/>
+      <c r="K5" s="108"/>
+      <c r="L5" s="109"/>
       <c r="N5" s="15" t="s">
         <v>4</v>
       </c>
@@ -11532,19 +11902,19 @@
       <c r="A6" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="119">
+      <c r="B6" s="93">
         <v>46073</v>
       </c>
-      <c r="C6" s="120"/>
-      <c r="D6" s="120"/>
-      <c r="E6" s="120"/>
-      <c r="F6" s="120"/>
-      <c r="G6" s="120"/>
-      <c r="H6" s="120"/>
-      <c r="I6" s="120"/>
-      <c r="J6" s="120"/>
-      <c r="K6" s="120"/>
-      <c r="L6" s="121"/>
+      <c r="C6" s="94"/>
+      <c r="D6" s="94"/>
+      <c r="E6" s="94"/>
+      <c r="F6" s="94"/>
+      <c r="G6" s="94"/>
+      <c r="H6" s="94"/>
+      <c r="I6" s="94"/>
+      <c r="J6" s="94"/>
+      <c r="K6" s="94"/>
+      <c r="L6" s="95"/>
       <c r="N6" s="14"/>
       <c r="O6" s="14"/>
     </row>
@@ -11552,17 +11922,17 @@
       <c r="A7" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="136"/>
-      <c r="C7" s="137"/>
-      <c r="D7" s="137"/>
-      <c r="E7" s="137"/>
-      <c r="F7" s="137"/>
-      <c r="G7" s="137"/>
-      <c r="H7" s="137"/>
-      <c r="I7" s="137"/>
-      <c r="J7" s="138"/>
-      <c r="K7" s="138"/>
-      <c r="L7" s="139"/>
+      <c r="B7" s="110"/>
+      <c r="C7" s="111"/>
+      <c r="D7" s="111"/>
+      <c r="E7" s="111"/>
+      <c r="F7" s="111"/>
+      <c r="G7" s="111"/>
+      <c r="H7" s="111"/>
+      <c r="I7" s="111"/>
+      <c r="J7" s="112"/>
+      <c r="K7" s="112"/>
+      <c r="L7" s="113"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
@@ -11579,20 +11949,20 @@
       <c r="L8" s="13"/>
     </row>
     <row r="9" spans="1:15" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="125" t="s">
+      <c r="A9" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="126"/>
-      <c r="C9" s="126"/>
-      <c r="D9" s="126"/>
-      <c r="E9" s="126"/>
-      <c r="F9" s="126"/>
-      <c r="G9" s="126"/>
-      <c r="H9" s="126"/>
-      <c r="I9" s="126"/>
-      <c r="J9" s="127"/>
-      <c r="K9" s="127"/>
-      <c r="L9" s="128"/>
+      <c r="B9" s="100"/>
+      <c r="C9" s="100"/>
+      <c r="D9" s="100"/>
+      <c r="E9" s="100"/>
+      <c r="F9" s="100"/>
+      <c r="G9" s="100"/>
+      <c r="H9" s="100"/>
+      <c r="I9" s="100"/>
+      <c r="J9" s="101"/>
+      <c r="K9" s="101"/>
+      <c r="L9" s="102"/>
     </row>
     <row r="10" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -11692,63 +12062,63 @@
       <c r="A14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="118"/>
-      <c r="C14" s="114"/>
-      <c r="D14" s="114"/>
-      <c r="E14" s="114"/>
-      <c r="F14" s="114"/>
-      <c r="G14" s="114"/>
-      <c r="H14" s="114"/>
-      <c r="I14" s="114"/>
-      <c r="J14" s="114"/>
-      <c r="K14" s="114"/>
-      <c r="L14" s="115"/>
+      <c r="B14" s="92"/>
+      <c r="C14" s="88"/>
+      <c r="D14" s="88"/>
+      <c r="E14" s="88"/>
+      <c r="F14" s="88"/>
+      <c r="G14" s="88"/>
+      <c r="H14" s="88"/>
+      <c r="I14" s="88"/>
+      <c r="J14" s="88"/>
+      <c r="K14" s="88"/>
+      <c r="L14" s="89"/>
     </row>
     <row r="15" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="113"/>
-      <c r="C15" s="114"/>
-      <c r="D15" s="114"/>
-      <c r="E15" s="114"/>
-      <c r="F15" s="114"/>
-      <c r="G15" s="114"/>
-      <c r="H15" s="114"/>
-      <c r="I15" s="114"/>
-      <c r="J15" s="114"/>
-      <c r="K15" s="114"/>
-      <c r="L15" s="115"/>
+      <c r="B15" s="87"/>
+      <c r="C15" s="88"/>
+      <c r="D15" s="88"/>
+      <c r="E15" s="88"/>
+      <c r="F15" s="88"/>
+      <c r="G15" s="88"/>
+      <c r="H15" s="88"/>
+      <c r="I15" s="88"/>
+      <c r="J15" s="88"/>
+      <c r="K15" s="88"/>
+      <c r="L15" s="89"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="106"/>
-      <c r="B16" s="107"/>
-      <c r="C16" s="107"/>
-      <c r="D16" s="107"/>
-      <c r="E16" s="107"/>
-      <c r="F16" s="107"/>
-      <c r="G16" s="107"/>
-      <c r="H16" s="107"/>
-      <c r="I16" s="107"/>
-      <c r="J16" s="107"/>
-      <c r="K16" s="107"/>
-      <c r="L16" s="108"/>
+      <c r="A16" s="80"/>
+      <c r="B16" s="81"/>
+      <c r="C16" s="81"/>
+      <c r="D16" s="81"/>
+      <c r="E16" s="81"/>
+      <c r="F16" s="81"/>
+      <c r="G16" s="81"/>
+      <c r="H16" s="81"/>
+      <c r="I16" s="81"/>
+      <c r="J16" s="81"/>
+      <c r="K16" s="81"/>
+      <c r="L16" s="82"/>
     </row>
     <row r="17" spans="1:12" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="109" t="s">
+      <c r="A17" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="110"/>
-      <c r="C17" s="110"/>
-      <c r="D17" s="110"/>
-      <c r="E17" s="110"/>
-      <c r="F17" s="110"/>
-      <c r="G17" s="110"/>
-      <c r="H17" s="110"/>
-      <c r="I17" s="110"/>
-      <c r="J17" s="111"/>
-      <c r="K17" s="111"/>
-      <c r="L17" s="112"/>
+      <c r="B17" s="84"/>
+      <c r="C17" s="84"/>
+      <c r="D17" s="84"/>
+      <c r="E17" s="84"/>
+      <c r="F17" s="84"/>
+      <c r="G17" s="84"/>
+      <c r="H17" s="84"/>
+      <c r="I17" s="84"/>
+      <c r="J17" s="85"/>
+      <c r="K17" s="85"/>
+      <c r="L17" s="86"/>
     </row>
     <row r="18" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
@@ -11758,19 +12128,19 @@
       <c r="C18" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="82" t="s">
+      <c r="D18" s="114" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="84" t="s">
+      <c r="E18" s="116" t="s">
         <v>115</v>
       </c>
-      <c r="F18" s="84"/>
-      <c r="G18" s="84"/>
-      <c r="H18" s="84"/>
-      <c r="I18" s="84"/>
-      <c r="J18" s="85"/>
-      <c r="K18" s="85"/>
-      <c r="L18" s="86"/>
+      <c r="F18" s="116"/>
+      <c r="G18" s="116"/>
+      <c r="H18" s="116"/>
+      <c r="I18" s="116"/>
+      <c r="J18" s="117"/>
+      <c r="K18" s="117"/>
+      <c r="L18" s="118"/>
     </row>
     <row r="19" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
@@ -11780,15 +12150,15 @@
         <v>30</v>
       </c>
       <c r="C19" s="44"/>
-      <c r="D19" s="83"/>
-      <c r="E19" s="87"/>
-      <c r="F19" s="87"/>
-      <c r="G19" s="87"/>
-      <c r="H19" s="87"/>
-      <c r="I19" s="87"/>
-      <c r="J19" s="88"/>
-      <c r="K19" s="88"/>
-      <c r="L19" s="89"/>
+      <c r="D19" s="115"/>
+      <c r="E19" s="119"/>
+      <c r="F19" s="119"/>
+      <c r="G19" s="119"/>
+      <c r="H19" s="119"/>
+      <c r="I19" s="119"/>
+      <c r="J19" s="120"/>
+      <c r="K19" s="120"/>
+      <c r="L19" s="121"/>
     </row>
     <row r="20" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
@@ -11798,15 +12168,15 @@
       <c r="C20" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="83"/>
-      <c r="E20" s="87"/>
-      <c r="F20" s="87"/>
-      <c r="G20" s="87"/>
-      <c r="H20" s="87"/>
-      <c r="I20" s="87"/>
-      <c r="J20" s="88"/>
-      <c r="K20" s="88"/>
-      <c r="L20" s="89"/>
+      <c r="D20" s="115"/>
+      <c r="E20" s="119"/>
+      <c r="F20" s="119"/>
+      <c r="G20" s="119"/>
+      <c r="H20" s="119"/>
+      <c r="I20" s="119"/>
+      <c r="J20" s="120"/>
+      <c r="K20" s="120"/>
+      <c r="L20" s="121"/>
     </row>
     <row r="21" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
@@ -11816,19 +12186,19 @@
       <c r="C21" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="98" t="s">
+      <c r="D21" s="130" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="100" t="s">
+      <c r="E21" s="132" t="s">
         <v>107</v>
       </c>
-      <c r="F21" s="101"/>
-      <c r="G21" s="101"/>
-      <c r="H21" s="101"/>
-      <c r="I21" s="101"/>
-      <c r="J21" s="101"/>
-      <c r="K21" s="101"/>
-      <c r="L21" s="102"/>
+      <c r="F21" s="133"/>
+      <c r="G21" s="133"/>
+      <c r="H21" s="133"/>
+      <c r="I21" s="133"/>
+      <c r="J21" s="133"/>
+      <c r="K21" s="133"/>
+      <c r="L21" s="134"/>
     </row>
     <row r="22" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
@@ -11838,45 +12208,45 @@
       <c r="C22" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="99"/>
-      <c r="E22" s="103"/>
-      <c r="F22" s="104"/>
-      <c r="G22" s="104"/>
-      <c r="H22" s="104"/>
-      <c r="I22" s="104"/>
-      <c r="J22" s="104"/>
-      <c r="K22" s="104"/>
-      <c r="L22" s="105"/>
+      <c r="D22" s="131"/>
+      <c r="E22" s="135"/>
+      <c r="F22" s="136"/>
+      <c r="G22" s="136"/>
+      <c r="H22" s="136"/>
+      <c r="I22" s="136"/>
+      <c r="J22" s="136"/>
+      <c r="K22" s="136"/>
+      <c r="L22" s="137"/>
     </row>
     <row r="23" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="91"/>
-      <c r="B23" s="92"/>
-      <c r="C23" s="92"/>
-      <c r="D23" s="93"/>
-      <c r="E23" s="93"/>
-      <c r="F23" s="93"/>
-      <c r="G23" s="93"/>
-      <c r="H23" s="93"/>
-      <c r="I23" s="93"/>
-      <c r="J23" s="93"/>
-      <c r="K23" s="93"/>
-      <c r="L23" s="94"/>
+      <c r="A23" s="123"/>
+      <c r="B23" s="124"/>
+      <c r="C23" s="124"/>
+      <c r="D23" s="125"/>
+      <c r="E23" s="125"/>
+      <c r="F23" s="125"/>
+      <c r="G23" s="125"/>
+      <c r="H23" s="125"/>
+      <c r="I23" s="125"/>
+      <c r="J23" s="125"/>
+      <c r="K23" s="125"/>
+      <c r="L23" s="126"/>
     </row>
     <row r="24" spans="1:12" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="95" t="s">
+      <c r="A24" s="127" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="96"/>
-      <c r="C24" s="96"/>
-      <c r="D24" s="96"/>
-      <c r="E24" s="96"/>
-      <c r="F24" s="96"/>
-      <c r="G24" s="96"/>
-      <c r="H24" s="96"/>
-      <c r="I24" s="96"/>
-      <c r="J24" s="96"/>
-      <c r="K24" s="96"/>
-      <c r="L24" s="97"/>
+      <c r="B24" s="128"/>
+      <c r="C24" s="128"/>
+      <c r="D24" s="128"/>
+      <c r="E24" s="128"/>
+      <c r="F24" s="128"/>
+      <c r="G24" s="128"/>
+      <c r="H24" s="128"/>
+      <c r="I24" s="128"/>
+      <c r="J24" s="128"/>
+      <c r="K24" s="128"/>
+      <c r="L24" s="129"/>
     </row>
     <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
@@ -11888,17 +12258,17 @@
       <c r="C25" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="90" t="s">
+      <c r="D25" s="122" t="s">
         <v>38</v>
       </c>
-      <c r="E25" s="90"/>
-      <c r="F25" s="90"/>
-      <c r="G25" s="90"/>
-      <c r="H25" s="90"/>
-      <c r="I25" s="90"/>
-      <c r="J25" s="90"/>
-      <c r="K25" s="90"/>
-      <c r="L25" s="90"/>
+      <c r="E25" s="122"/>
+      <c r="F25" s="122"/>
+      <c r="G25" s="122"/>
+      <c r="H25" s="122"/>
+      <c r="I25" s="122"/>
+      <c r="J25" s="122"/>
+      <c r="K25" s="122"/>
+      <c r="L25" s="122"/>
     </row>
     <row r="26" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="33">
@@ -11908,17 +12278,17 @@
         <v>116</v>
       </c>
       <c r="C26" s="34"/>
-      <c r="D26" s="174" t="s">
+      <c r="D26" s="138" t="s">
         <v>108</v>
       </c>
-      <c r="E26" s="80"/>
-      <c r="F26" s="80"/>
-      <c r="G26" s="80"/>
-      <c r="H26" s="80"/>
-      <c r="I26" s="80"/>
-      <c r="J26" s="80"/>
-      <c r="K26" s="80"/>
-      <c r="L26" s="80"/>
+      <c r="E26" s="138"/>
+      <c r="F26" s="138"/>
+      <c r="G26" s="138"/>
+      <c r="H26" s="138"/>
+      <c r="I26" s="138"/>
+      <c r="J26" s="138"/>
+      <c r="K26" s="138"/>
+      <c r="L26" s="138"/>
     </row>
     <row r="27" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
@@ -11928,15 +12298,15 @@
         <v>117</v>
       </c>
       <c r="C27" s="34"/>
-      <c r="D27" s="175"/>
-      <c r="E27" s="81"/>
-      <c r="F27" s="81"/>
-      <c r="G27" s="81"/>
-      <c r="H27" s="81"/>
-      <c r="I27" s="81"/>
-      <c r="J27" s="81"/>
-      <c r="K27" s="81"/>
-      <c r="L27" s="81"/>
+      <c r="D27" s="139"/>
+      <c r="E27" s="139"/>
+      <c r="F27" s="139"/>
+      <c r="G27" s="139"/>
+      <c r="H27" s="139"/>
+      <c r="I27" s="139"/>
+      <c r="J27" s="139"/>
+      <c r="K27" s="139"/>
+      <c r="L27" s="139"/>
     </row>
     <row r="28" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="33">
@@ -11946,15 +12316,15 @@
         <v>118</v>
       </c>
       <c r="C28" s="34"/>
-      <c r="D28" s="175"/>
-      <c r="E28" s="81"/>
-      <c r="F28" s="81"/>
-      <c r="G28" s="81"/>
-      <c r="H28" s="81"/>
-      <c r="I28" s="81"/>
-      <c r="J28" s="81"/>
-      <c r="K28" s="81"/>
-      <c r="L28" s="81"/>
+      <c r="D28" s="139"/>
+      <c r="E28" s="139"/>
+      <c r="F28" s="139"/>
+      <c r="G28" s="139"/>
+      <c r="H28" s="139"/>
+      <c r="I28" s="139"/>
+      <c r="J28" s="139"/>
+      <c r="K28" s="139"/>
+      <c r="L28" s="139"/>
     </row>
     <row r="29" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
@@ -11964,15 +12334,15 @@
         <v>119</v>
       </c>
       <c r="C29" s="34"/>
-      <c r="D29" s="175"/>
-      <c r="E29" s="81"/>
-      <c r="F29" s="81"/>
-      <c r="G29" s="81"/>
-      <c r="H29" s="81"/>
-      <c r="I29" s="81"/>
-      <c r="J29" s="81"/>
-      <c r="K29" s="81"/>
-      <c r="L29" s="81"/>
+      <c r="D29" s="139"/>
+      <c r="E29" s="139"/>
+      <c r="F29" s="139"/>
+      <c r="G29" s="139"/>
+      <c r="H29" s="139"/>
+      <c r="I29" s="139"/>
+      <c r="J29" s="139"/>
+      <c r="K29" s="139"/>
+      <c r="L29" s="139"/>
     </row>
     <row r="30" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="33">
@@ -11982,15 +12352,15 @@
         <v>120</v>
       </c>
       <c r="C30" s="34"/>
-      <c r="D30" s="175"/>
-      <c r="E30" s="81"/>
-      <c r="F30" s="81"/>
-      <c r="G30" s="81"/>
-      <c r="H30" s="81"/>
-      <c r="I30" s="81"/>
-      <c r="J30" s="81"/>
-      <c r="K30" s="81"/>
-      <c r="L30" s="81"/>
+      <c r="D30" s="139"/>
+      <c r="E30" s="139"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="139"/>
+      <c r="H30" s="139"/>
+      <c r="I30" s="139"/>
+      <c r="J30" s="139"/>
+      <c r="K30" s="139"/>
+      <c r="L30" s="139"/>
     </row>
     <row r="31" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="33">
@@ -12000,15 +12370,15 @@
         <v>121</v>
       </c>
       <c r="C31" s="34"/>
-      <c r="D31" s="175"/>
-      <c r="E31" s="81"/>
-      <c r="F31" s="81"/>
-      <c r="G31" s="81"/>
-      <c r="H31" s="81"/>
-      <c r="I31" s="81"/>
-      <c r="J31" s="81"/>
-      <c r="K31" s="81"/>
-      <c r="L31" s="81"/>
+      <c r="D31" s="139"/>
+      <c r="E31" s="139"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="139"/>
+      <c r="H31" s="139"/>
+      <c r="I31" s="139"/>
+      <c r="J31" s="139"/>
+      <c r="K31" s="139"/>
+      <c r="L31" s="139"/>
     </row>
     <row r="32" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="33">
@@ -12018,15 +12388,15 @@
         <v>122</v>
       </c>
       <c r="C32" s="34"/>
-      <c r="D32" s="175"/>
-      <c r="E32" s="81"/>
-      <c r="F32" s="81"/>
-      <c r="G32" s="81"/>
-      <c r="H32" s="81"/>
-      <c r="I32" s="81"/>
-      <c r="J32" s="81"/>
-      <c r="K32" s="81"/>
-      <c r="L32" s="81"/>
+      <c r="D32" s="139"/>
+      <c r="E32" s="139"/>
+      <c r="F32" s="139"/>
+      <c r="G32" s="139"/>
+      <c r="H32" s="139"/>
+      <c r="I32" s="139"/>
+      <c r="J32" s="139"/>
+      <c r="K32" s="139"/>
+      <c r="L32" s="139"/>
     </row>
     <row r="33" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="33">
@@ -12036,15 +12406,15 @@
         <v>123</v>
       </c>
       <c r="C33" s="34"/>
-      <c r="D33" s="175"/>
-      <c r="E33" s="81"/>
-      <c r="F33" s="81"/>
-      <c r="G33" s="81"/>
-      <c r="H33" s="81"/>
-      <c r="I33" s="81"/>
-      <c r="J33" s="81"/>
-      <c r="K33" s="81"/>
-      <c r="L33" s="81"/>
+      <c r="D33" s="139"/>
+      <c r="E33" s="139"/>
+      <c r="F33" s="139"/>
+      <c r="G33" s="139"/>
+      <c r="H33" s="139"/>
+      <c r="I33" s="139"/>
+      <c r="J33" s="139"/>
+      <c r="K33" s="139"/>
+      <c r="L33" s="139"/>
     </row>
     <row r="34" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="33">
@@ -12054,15 +12424,15 @@
         <v>124</v>
       </c>
       <c r="C34" s="34"/>
-      <c r="D34" s="175"/>
-      <c r="E34" s="81"/>
-      <c r="F34" s="81"/>
-      <c r="G34" s="81"/>
-      <c r="H34" s="81"/>
-      <c r="I34" s="81"/>
-      <c r="J34" s="81"/>
-      <c r="K34" s="81"/>
-      <c r="L34" s="81"/>
+      <c r="D34" s="139"/>
+      <c r="E34" s="139"/>
+      <c r="F34" s="139"/>
+      <c r="G34" s="139"/>
+      <c r="H34" s="139"/>
+      <c r="I34" s="139"/>
+      <c r="J34" s="139"/>
+      <c r="K34" s="139"/>
+      <c r="L34" s="139"/>
     </row>
     <row r="35" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="33">
@@ -12072,15 +12442,15 @@
         <v>125</v>
       </c>
       <c r="C35" s="34"/>
-      <c r="D35" s="175"/>
-      <c r="E35" s="81"/>
-      <c r="F35" s="81"/>
-      <c r="G35" s="81"/>
-      <c r="H35" s="81"/>
-      <c r="I35" s="81"/>
-      <c r="J35" s="81"/>
-      <c r="K35" s="81"/>
-      <c r="L35" s="81"/>
+      <c r="D35" s="139"/>
+      <c r="E35" s="139"/>
+      <c r="F35" s="139"/>
+      <c r="G35" s="139"/>
+      <c r="H35" s="139"/>
+      <c r="I35" s="139"/>
+      <c r="J35" s="139"/>
+      <c r="K35" s="139"/>
+      <c r="L35" s="139"/>
     </row>
     <row r="36" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="33">
@@ -12090,15 +12460,15 @@
         <v>126</v>
       </c>
       <c r="C36" s="34"/>
-      <c r="D36" s="175"/>
-      <c r="E36" s="81"/>
-      <c r="F36" s="81"/>
-      <c r="G36" s="81"/>
-      <c r="H36" s="81"/>
-      <c r="I36" s="81"/>
-      <c r="J36" s="81"/>
-      <c r="K36" s="81"/>
-      <c r="L36" s="81"/>
+      <c r="D36" s="139"/>
+      <c r="E36" s="139"/>
+      <c r="F36" s="139"/>
+      <c r="G36" s="139"/>
+      <c r="H36" s="139"/>
+      <c r="I36" s="139"/>
+      <c r="J36" s="139"/>
+      <c r="K36" s="139"/>
+      <c r="L36" s="139"/>
     </row>
     <row r="37" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="33">
@@ -12108,15 +12478,15 @@
         <v>127</v>
       </c>
       <c r="C37" s="34"/>
-      <c r="D37" s="175"/>
-      <c r="E37" s="81"/>
-      <c r="F37" s="81"/>
-      <c r="G37" s="81"/>
-      <c r="H37" s="81"/>
-      <c r="I37" s="81"/>
-      <c r="J37" s="81"/>
-      <c r="K37" s="81"/>
-      <c r="L37" s="81"/>
+      <c r="D37" s="139"/>
+      <c r="E37" s="139"/>
+      <c r="F37" s="139"/>
+      <c r="G37" s="139"/>
+      <c r="H37" s="139"/>
+      <c r="I37" s="139"/>
+      <c r="J37" s="139"/>
+      <c r="K37" s="139"/>
+      <c r="L37" s="139"/>
     </row>
     <row r="38" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="33">
@@ -12126,15 +12496,15 @@
         <v>128</v>
       </c>
       <c r="C38" s="34"/>
-      <c r="D38" s="175"/>
-      <c r="E38" s="81"/>
-      <c r="F38" s="81"/>
-      <c r="G38" s="81"/>
-      <c r="H38" s="81"/>
-      <c r="I38" s="81"/>
-      <c r="J38" s="81"/>
-      <c r="K38" s="81"/>
-      <c r="L38" s="81"/>
+      <c r="D38" s="139"/>
+      <c r="E38" s="139"/>
+      <c r="F38" s="139"/>
+      <c r="G38" s="139"/>
+      <c r="H38" s="139"/>
+      <c r="I38" s="139"/>
+      <c r="J38" s="139"/>
+      <c r="K38" s="139"/>
+      <c r="L38" s="139"/>
     </row>
     <row r="39" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="33">
@@ -12144,15 +12514,15 @@
         <v>129</v>
       </c>
       <c r="C39" s="34"/>
-      <c r="D39" s="175"/>
-      <c r="E39" s="81"/>
-      <c r="F39" s="81"/>
-      <c r="G39" s="81"/>
-      <c r="H39" s="81"/>
-      <c r="I39" s="81"/>
-      <c r="J39" s="81"/>
-      <c r="K39" s="81"/>
-      <c r="L39" s="81"/>
+      <c r="D39" s="139"/>
+      <c r="E39" s="139"/>
+      <c r="F39" s="139"/>
+      <c r="G39" s="139"/>
+      <c r="H39" s="139"/>
+      <c r="I39" s="139"/>
+      <c r="J39" s="139"/>
+      <c r="K39" s="139"/>
+      <c r="L39" s="139"/>
     </row>
     <row r="40" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="33">
@@ -12162,15 +12532,15 @@
         <v>130</v>
       </c>
       <c r="C40" s="34"/>
-      <c r="D40" s="175"/>
-      <c r="E40" s="81"/>
-      <c r="F40" s="81"/>
-      <c r="G40" s="81"/>
-      <c r="H40" s="81"/>
-      <c r="I40" s="81"/>
-      <c r="J40" s="81"/>
-      <c r="K40" s="81"/>
-      <c r="L40" s="81"/>
+      <c r="D40" s="139"/>
+      <c r="E40" s="139"/>
+      <c r="F40" s="139"/>
+      <c r="G40" s="139"/>
+      <c r="H40" s="139"/>
+      <c r="I40" s="139"/>
+      <c r="J40" s="139"/>
+      <c r="K40" s="139"/>
+      <c r="L40" s="139"/>
     </row>
     <row r="41" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="33">
@@ -12180,15 +12550,15 @@
         <v>131</v>
       </c>
       <c r="C41" s="34"/>
-      <c r="D41" s="175"/>
-      <c r="E41" s="81"/>
-      <c r="F41" s="81"/>
-      <c r="G41" s="81"/>
-      <c r="H41" s="81"/>
-      <c r="I41" s="81"/>
-      <c r="J41" s="81"/>
-      <c r="K41" s="81"/>
-      <c r="L41" s="81"/>
+      <c r="D41" s="139"/>
+      <c r="E41" s="139"/>
+      <c r="F41" s="139"/>
+      <c r="G41" s="139"/>
+      <c r="H41" s="139"/>
+      <c r="I41" s="139"/>
+      <c r="J41" s="139"/>
+      <c r="K41" s="139"/>
+      <c r="L41" s="139"/>
     </row>
     <row r="42" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="33">
@@ -12198,15 +12568,15 @@
         <v>132</v>
       </c>
       <c r="C42" s="34"/>
-      <c r="D42" s="175"/>
-      <c r="E42" s="81"/>
-      <c r="F42" s="81"/>
-      <c r="G42" s="81"/>
-      <c r="H42" s="81"/>
-      <c r="I42" s="81"/>
-      <c r="J42" s="81"/>
-      <c r="K42" s="81"/>
-      <c r="L42" s="81"/>
+      <c r="D42" s="139"/>
+      <c r="E42" s="139"/>
+      <c r="F42" s="139"/>
+      <c r="G42" s="139"/>
+      <c r="H42" s="139"/>
+      <c r="I42" s="139"/>
+      <c r="J42" s="139"/>
+      <c r="K42" s="139"/>
+      <c r="L42" s="139"/>
     </row>
     <row r="43" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="33">
@@ -12216,15 +12586,15 @@
         <v>133</v>
       </c>
       <c r="C43" s="34"/>
-      <c r="D43" s="175"/>
-      <c r="E43" s="81"/>
-      <c r="F43" s="81"/>
-      <c r="G43" s="81"/>
-      <c r="H43" s="81"/>
-      <c r="I43" s="81"/>
-      <c r="J43" s="81"/>
-      <c r="K43" s="81"/>
-      <c r="L43" s="81"/>
+      <c r="D43" s="139"/>
+      <c r="E43" s="139"/>
+      <c r="F43" s="139"/>
+      <c r="G43" s="139"/>
+      <c r="H43" s="139"/>
+      <c r="I43" s="139"/>
+      <c r="J43" s="139"/>
+      <c r="K43" s="139"/>
+      <c r="L43" s="139"/>
     </row>
     <row r="44" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="33">
@@ -12234,15 +12604,15 @@
         <v>134</v>
       </c>
       <c r="C44" s="34"/>
-      <c r="D44" s="175"/>
-      <c r="E44" s="81"/>
-      <c r="F44" s="81"/>
-      <c r="G44" s="81"/>
-      <c r="H44" s="81"/>
-      <c r="I44" s="81"/>
-      <c r="J44" s="81"/>
-      <c r="K44" s="81"/>
-      <c r="L44" s="81"/>
+      <c r="D44" s="139"/>
+      <c r="E44" s="139"/>
+      <c r="F44" s="139"/>
+      <c r="G44" s="139"/>
+      <c r="H44" s="139"/>
+      <c r="I44" s="139"/>
+      <c r="J44" s="139"/>
+      <c r="K44" s="139"/>
+      <c r="L44" s="139"/>
     </row>
     <row r="45" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="33">
@@ -12252,15 +12622,15 @@
         <v>135</v>
       </c>
       <c r="C45" s="34"/>
-      <c r="D45" s="175"/>
-      <c r="E45" s="81"/>
-      <c r="F45" s="81"/>
-      <c r="G45" s="81"/>
-      <c r="H45" s="81"/>
-      <c r="I45" s="81"/>
-      <c r="J45" s="81"/>
-      <c r="K45" s="81"/>
-      <c r="L45" s="81"/>
+      <c r="D45" s="139"/>
+      <c r="E45" s="139"/>
+      <c r="F45" s="139"/>
+      <c r="G45" s="139"/>
+      <c r="H45" s="139"/>
+      <c r="I45" s="139"/>
+      <c r="J45" s="139"/>
+      <c r="K45" s="139"/>
+      <c r="L45" s="139"/>
     </row>
     <row r="46" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="33">
@@ -12270,15 +12640,15 @@
         <v>136</v>
       </c>
       <c r="C46" s="34"/>
-      <c r="D46" s="175"/>
-      <c r="E46" s="81"/>
-      <c r="F46" s="81"/>
-      <c r="G46" s="81"/>
-      <c r="H46" s="81"/>
-      <c r="I46" s="81"/>
-      <c r="J46" s="81"/>
-      <c r="K46" s="81"/>
-      <c r="L46" s="81"/>
+      <c r="D46" s="139"/>
+      <c r="E46" s="139"/>
+      <c r="F46" s="139"/>
+      <c r="G46" s="139"/>
+      <c r="H46" s="139"/>
+      <c r="I46" s="139"/>
+      <c r="J46" s="139"/>
+      <c r="K46" s="139"/>
+      <c r="L46" s="139"/>
     </row>
     <row r="47" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="33">
@@ -12288,15 +12658,15 @@
         <v>137</v>
       </c>
       <c r="C47" s="34"/>
-      <c r="D47" s="175"/>
-      <c r="E47" s="81"/>
-      <c r="F47" s="81"/>
-      <c r="G47" s="81"/>
-      <c r="H47" s="81"/>
-      <c r="I47" s="81"/>
-      <c r="J47" s="81"/>
-      <c r="K47" s="81"/>
-      <c r="L47" s="81"/>
+      <c r="D47" s="139"/>
+      <c r="E47" s="139"/>
+      <c r="F47" s="139"/>
+      <c r="G47" s="139"/>
+      <c r="H47" s="139"/>
+      <c r="I47" s="139"/>
+      <c r="J47" s="139"/>
+      <c r="K47" s="139"/>
+      <c r="L47" s="139"/>
     </row>
     <row r="48" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="33">
@@ -12306,15 +12676,15 @@
         <v>138</v>
       </c>
       <c r="C48" s="34"/>
-      <c r="D48" s="175"/>
-      <c r="E48" s="81"/>
-      <c r="F48" s="81"/>
-      <c r="G48" s="81"/>
-      <c r="H48" s="81"/>
-      <c r="I48" s="81"/>
-      <c r="J48" s="81"/>
-      <c r="K48" s="81"/>
-      <c r="L48" s="81"/>
+      <c r="D48" s="139"/>
+      <c r="E48" s="139"/>
+      <c r="F48" s="139"/>
+      <c r="G48" s="139"/>
+      <c r="H48" s="139"/>
+      <c r="I48" s="139"/>
+      <c r="J48" s="139"/>
+      <c r="K48" s="139"/>
+      <c r="L48" s="139"/>
     </row>
     <row r="49" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="33">
@@ -12324,15 +12694,15 @@
         <v>139</v>
       </c>
       <c r="C49" s="34"/>
-      <c r="D49" s="175"/>
-      <c r="E49" s="81"/>
-      <c r="F49" s="81"/>
-      <c r="G49" s="81"/>
-      <c r="H49" s="81"/>
-      <c r="I49" s="81"/>
-      <c r="J49" s="81"/>
-      <c r="K49" s="81"/>
-      <c r="L49" s="81"/>
+      <c r="D49" s="139"/>
+      <c r="E49" s="139"/>
+      <c r="F49" s="139"/>
+      <c r="G49" s="139"/>
+      <c r="H49" s="139"/>
+      <c r="I49" s="139"/>
+      <c r="J49" s="139"/>
+      <c r="K49" s="139"/>
+      <c r="L49" s="139"/>
     </row>
     <row r="50" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="72">
@@ -12342,15 +12712,15 @@
         <v>140</v>
       </c>
       <c r="C50" s="34"/>
-      <c r="D50" s="175"/>
-      <c r="E50" s="81"/>
-      <c r="F50" s="81"/>
-      <c r="G50" s="81"/>
-      <c r="H50" s="81"/>
-      <c r="I50" s="81"/>
-      <c r="J50" s="81"/>
-      <c r="K50" s="81"/>
-      <c r="L50" s="81"/>
+      <c r="D50" s="139"/>
+      <c r="E50" s="139"/>
+      <c r="F50" s="139"/>
+      <c r="G50" s="139"/>
+      <c r="H50" s="139"/>
+      <c r="I50" s="139"/>
+      <c r="J50" s="139"/>
+      <c r="K50" s="139"/>
+      <c r="L50" s="139"/>
     </row>
     <row r="51" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="72">
@@ -12360,15 +12730,15 @@
         <v>141</v>
       </c>
       <c r="C51" s="34"/>
-      <c r="D51" s="175"/>
-      <c r="E51" s="81"/>
-      <c r="F51" s="81"/>
-      <c r="G51" s="81"/>
-      <c r="H51" s="81"/>
-      <c r="I51" s="81"/>
-      <c r="J51" s="81"/>
-      <c r="K51" s="81"/>
-      <c r="L51" s="81"/>
+      <c r="D51" s="139"/>
+      <c r="E51" s="139"/>
+      <c r="F51" s="139"/>
+      <c r="G51" s="139"/>
+      <c r="H51" s="139"/>
+      <c r="I51" s="139"/>
+      <c r="J51" s="139"/>
+      <c r="K51" s="139"/>
+      <c r="L51" s="139"/>
     </row>
     <row r="52" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="72">
@@ -12378,17 +12748,17 @@
         <v>142</v>
       </c>
       <c r="C52" s="34"/>
-      <c r="D52" s="175"/>
-      <c r="E52" s="81"/>
-      <c r="F52" s="81"/>
-      <c r="G52" s="81"/>
-      <c r="H52" s="81"/>
-      <c r="I52" s="81"/>
-      <c r="J52" s="81"/>
-      <c r="K52" s="81"/>
-      <c r="L52" s="81"/>
+      <c r="D52" s="139"/>
+      <c r="E52" s="139"/>
+      <c r="F52" s="139"/>
+      <c r="G52" s="139"/>
+      <c r="H52" s="139"/>
+      <c r="I52" s="139"/>
+      <c r="J52" s="139"/>
+      <c r="K52" s="139"/>
+      <c r="L52" s="139"/>
     </row>
-    <row r="53" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="72">
         <v>28</v>
       </c>
@@ -12396,17 +12766,17 @@
         <v>143</v>
       </c>
       <c r="C53" s="79"/>
-      <c r="D53" s="175"/>
-      <c r="E53" s="81"/>
-      <c r="F53" s="81"/>
-      <c r="G53" s="81"/>
-      <c r="H53" s="81"/>
-      <c r="I53" s="81"/>
-      <c r="J53" s="81"/>
-      <c r="K53" s="81"/>
-      <c r="L53" s="81"/>
+      <c r="D53" s="139"/>
+      <c r="E53" s="139"/>
+      <c r="F53" s="139"/>
+      <c r="G53" s="139"/>
+      <c r="H53" s="139"/>
+      <c r="I53" s="139"/>
+      <c r="J53" s="139"/>
+      <c r="K53" s="139"/>
+      <c r="L53" s="139"/>
     </row>
-    <row r="54" spans="1:12" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="72">
         <v>29</v>
       </c>
@@ -12414,17 +12784,17 @@
         <v>144</v>
       </c>
       <c r="C54" s="72"/>
-      <c r="D54" s="175"/>
-      <c r="E54" s="81"/>
-      <c r="F54" s="81"/>
-      <c r="G54" s="81"/>
-      <c r="H54" s="81"/>
-      <c r="I54" s="81"/>
-      <c r="J54" s="81"/>
-      <c r="K54" s="81"/>
-      <c r="L54" s="81"/>
+      <c r="D54" s="139"/>
+      <c r="E54" s="139"/>
+      <c r="F54" s="139"/>
+      <c r="G54" s="139"/>
+      <c r="H54" s="139"/>
+      <c r="I54" s="139"/>
+      <c r="J54" s="139"/>
+      <c r="K54" s="139"/>
+      <c r="L54" s="139"/>
     </row>
-    <row r="55" spans="1:12" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="72">
         <v>30</v>
       </c>
@@ -12432,17 +12802,17 @@
         <v>145</v>
       </c>
       <c r="C55" s="78"/>
-      <c r="D55" s="175"/>
-      <c r="E55" s="81"/>
-      <c r="F55" s="81"/>
-      <c r="G55" s="81"/>
-      <c r="H55" s="81"/>
-      <c r="I55" s="81"/>
-      <c r="J55" s="81"/>
-      <c r="K55" s="81"/>
-      <c r="L55" s="81"/>
+      <c r="D55" s="139"/>
+      <c r="E55" s="139"/>
+      <c r="F55" s="139"/>
+      <c r="G55" s="139"/>
+      <c r="H55" s="139"/>
+      <c r="I55" s="139"/>
+      <c r="J55" s="139"/>
+      <c r="K55" s="139"/>
+      <c r="L55" s="139"/>
     </row>
-    <row r="56" spans="1:12" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="72">
         <v>31</v>
       </c>
@@ -12450,17 +12820,17 @@
         <v>146</v>
       </c>
       <c r="C56" s="78"/>
-      <c r="D56" s="175"/>
-      <c r="E56" s="81"/>
-      <c r="F56" s="81"/>
-      <c r="G56" s="81"/>
-      <c r="H56" s="81"/>
-      <c r="I56" s="81"/>
-      <c r="J56" s="81"/>
-      <c r="K56" s="81"/>
-      <c r="L56" s="81"/>
+      <c r="D56" s="139"/>
+      <c r="E56" s="139"/>
+      <c r="F56" s="139"/>
+      <c r="G56" s="139"/>
+      <c r="H56" s="139"/>
+      <c r="I56" s="139"/>
+      <c r="J56" s="139"/>
+      <c r="K56" s="139"/>
+      <c r="L56" s="139"/>
     </row>
-    <row r="57" spans="1:12" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="72">
         <v>32</v>
       </c>
@@ -12468,36 +12838,152 @@
         <v>147</v>
       </c>
       <c r="C57" s="78"/>
-      <c r="D57" s="175"/>
-      <c r="E57" s="81"/>
-      <c r="F57" s="81"/>
-      <c r="G57" s="81"/>
-      <c r="H57" s="81"/>
-      <c r="I57" s="81"/>
-      <c r="J57" s="81"/>
-      <c r="K57" s="81"/>
-      <c r="L57" s="81"/>
+      <c r="D57" s="139"/>
+      <c r="E57" s="139"/>
+      <c r="F57" s="139"/>
+      <c r="G57" s="139"/>
+      <c r="H57" s="139"/>
+      <c r="I57" s="139"/>
+      <c r="J57" s="139"/>
+      <c r="K57" s="139"/>
+      <c r="L57" s="139"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A58" s="173">
+    <row r="58" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="72">
         <v>33</v>
       </c>
       <c r="B58" s="78" t="s">
         <v>148</v>
       </c>
       <c r="C58" s="78"/>
-      <c r="D58" s="175"/>
-      <c r="E58" s="81"/>
-      <c r="F58" s="81"/>
-      <c r="G58" s="81"/>
-      <c r="H58" s="81"/>
-      <c r="I58" s="81"/>
-      <c r="J58" s="81"/>
-      <c r="K58" s="81"/>
-      <c r="L58" s="81"/>
+      <c r="D58" s="139"/>
+      <c r="E58" s="139"/>
+      <c r="F58" s="139"/>
+      <c r="G58" s="139"/>
+      <c r="H58" s="139"/>
+      <c r="I58" s="139"/>
+      <c r="J58" s="139"/>
+      <c r="K58" s="139"/>
+      <c r="L58" s="139"/>
+    </row>
+    <row r="59" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="72">
+        <v>34</v>
+      </c>
+      <c r="B59" s="78" t="s">
+        <v>149</v>
+      </c>
+      <c r="C59" s="78"/>
+      <c r="D59" s="139"/>
+      <c r="E59" s="139"/>
+      <c r="F59" s="139"/>
+      <c r="G59" s="139"/>
+      <c r="H59" s="139"/>
+      <c r="I59" s="139"/>
+      <c r="J59" s="139"/>
+      <c r="K59" s="139"/>
+      <c r="L59" s="139"/>
+    </row>
+    <row r="60" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="72">
+        <v>35</v>
+      </c>
+      <c r="B60" s="78" t="s">
+        <v>150</v>
+      </c>
+      <c r="C60" s="78"/>
+      <c r="D60" s="139"/>
+      <c r="E60" s="139"/>
+      <c r="F60" s="139"/>
+      <c r="G60" s="139"/>
+      <c r="H60" s="139"/>
+      <c r="I60" s="139"/>
+      <c r="J60" s="139"/>
+      <c r="K60" s="139"/>
+      <c r="L60" s="139"/>
+    </row>
+    <row r="61" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="72">
+        <v>36</v>
+      </c>
+      <c r="B61" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="C61" s="78"/>
+      <c r="D61" s="139"/>
+      <c r="E61" s="139"/>
+      <c r="F61" s="139"/>
+      <c r="G61" s="139"/>
+      <c r="H61" s="139"/>
+      <c r="I61" s="139"/>
+      <c r="J61" s="139"/>
+      <c r="K61" s="139"/>
+      <c r="L61" s="139"/>
+    </row>
+    <row r="62" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="72">
+        <v>37</v>
+      </c>
+      <c r="B62" s="78" t="s">
+        <v>154</v>
+      </c>
+      <c r="C62" s="78"/>
+      <c r="D62" s="139"/>
+      <c r="E62" s="139"/>
+      <c r="F62" s="139"/>
+      <c r="G62" s="139"/>
+      <c r="H62" s="139"/>
+      <c r="I62" s="139"/>
+      <c r="J62" s="139"/>
+      <c r="K62" s="139"/>
+      <c r="L62" s="139"/>
+    </row>
+    <row r="63" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="72">
+        <v>38</v>
+      </c>
+      <c r="B63" s="78" t="s">
+        <v>151</v>
+      </c>
+      <c r="C63" s="78"/>
+      <c r="D63" s="139"/>
+      <c r="E63" s="139"/>
+      <c r="F63" s="139"/>
+      <c r="G63" s="139"/>
+      <c r="H63" s="139"/>
+      <c r="I63" s="139"/>
+      <c r="J63" s="139"/>
+      <c r="K63" s="139"/>
+      <c r="L63" s="139"/>
+    </row>
+    <row r="64" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="72">
+        <v>39</v>
+      </c>
+      <c r="B64" s="78" t="s">
+        <v>152</v>
+      </c>
+      <c r="C64" s="78"/>
+      <c r="D64" s="139"/>
+      <c r="E64" s="139"/>
+      <c r="F64" s="139"/>
+      <c r="G64" s="139"/>
+      <c r="H64" s="139"/>
+      <c r="I64" s="139"/>
+      <c r="J64" s="139"/>
+      <c r="K64" s="139"/>
+      <c r="L64" s="139"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="D26:L64"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:L20"/>
+    <mergeCell ref="D25:L25"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:L22"/>
     <mergeCell ref="A16:L16"/>
     <mergeCell ref="A17:L17"/>
     <mergeCell ref="B15:L15"/>
@@ -12509,14 +12995,6 @@
     <mergeCell ref="B4:L4"/>
     <mergeCell ref="B5:L5"/>
     <mergeCell ref="B7:L7"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:L20"/>
-    <mergeCell ref="D25:L25"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:L22"/>
-    <mergeCell ref="D26:L58"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D26" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -15490,8 +15968,8 @@
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>55</xdr:row>
-                    <xdr:rowOff>7620</xdr:rowOff>
+                    <xdr:row>54</xdr:row>
+                    <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15512,8 +15990,8 @@
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>56</xdr:row>
-                    <xdr:rowOff>7620</xdr:rowOff>
+                    <xdr:row>55</xdr:row>
+                    <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15534,8 +16012,8 @@
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>57</xdr:row>
-                    <xdr:rowOff>7620</xdr:rowOff>
+                    <xdr:row>56</xdr:row>
+                    <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15556,8 +16034,140 @@
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
+                    <xdr:row>57</xdr:row>
+                    <xdr:rowOff>220980</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1241" r:id="rId143" name="Drop Down 217">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
                     <xdr:row>58</xdr:row>
-                    <xdr:rowOff>38100</xdr:rowOff>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>1409700</xdr:colOff>
+                    <xdr:row>58</xdr:row>
+                    <xdr:rowOff>220980</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1242" r:id="rId144" name="Drop Down 218">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>59</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>1409700</xdr:colOff>
+                    <xdr:row>59</xdr:row>
+                    <xdr:rowOff>220980</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1243" r:id="rId145" name="Drop Down 219">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>60</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>1409700</xdr:colOff>
+                    <xdr:row>60</xdr:row>
+                    <xdr:rowOff>220980</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1244" r:id="rId146" name="Drop Down 220">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>61</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>1409700</xdr:colOff>
+                    <xdr:row>61</xdr:row>
+                    <xdr:rowOff>220980</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1245" r:id="rId147" name="Drop Down 221">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>62</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>1409700</xdr:colOff>
+                    <xdr:row>62</xdr:row>
+                    <xdr:rowOff>220980</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1246" r:id="rId148" name="Drop Down 222">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>63</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>1409700</xdr:colOff>
+                    <xdr:row>63</xdr:row>
+                    <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -15790,17 +16400,17 @@
       <c r="C12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="90" t="s">
+      <c r="D12" s="122" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="90"/>
-      <c r="F12" s="90"/>
-      <c r="G12" s="90"/>
-      <c r="H12" s="90"/>
-      <c r="I12" s="90"/>
-      <c r="J12" s="90"/>
-      <c r="K12" s="90"/>
-      <c r="L12" s="90"/>
+      <c r="E12" s="122"/>
+      <c r="F12" s="122"/>
+      <c r="G12" s="122"/>
+      <c r="H12" s="122"/>
+      <c r="I12" s="122"/>
+      <c r="J12" s="122"/>
+      <c r="K12" s="122"/>
+      <c r="L12" s="122"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="49"/>
@@ -16708,6 +17318,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <SharedWithUsers xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50">
@@ -16758,15 +17377,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17019,20 +17629,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371D8832-41B3-447B-B13D-2663C267E34F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD069904-634F-48DA-AA92-BAE250498BEE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="8029d101-3d2a-47c4-b15f-619642bf5e50"/>
     <ds:schemaRef ds:uri="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371D8832-41B3-447B-B13D-2663C267E34F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Guias Produccion/HU-57723.xlsx
+++ b/Guias Produccion/HU-57723.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Alliance\ScriptsEntidades\Guias Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54365CC9-637D-49ED-8D68-74E0504C7C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{731E405A-CE5E-415D-AE23-E5CD0DBDA9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="156">
   <si>
     <t>Guia documentación</t>
   </si>
@@ -629,6 +629,9 @@
   <si>
     <t>37-AC_pro_GetCompletedScheduledPickupShipTo.sql</t>
   </si>
+  <si>
+    <t>40-AC_pro_InsertAccountingClient.sql</t>
+  </si>
 </sst>
 </file>
 
@@ -847,7 +850,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="78">
+  <borders count="79">
     <border>
       <left/>
       <right/>
@@ -1832,12 +1835,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="173">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1990,6 +2004,84 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="75" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="76" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="77" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2092,84 +2184,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2268,6 +2282,15 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="54" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2492,10 +2515,14 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp145.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$18" noThreeD="1" sel="8" val="3"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp146.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$17" noThreeD="1" sel="17" val="9"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp146.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp147.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$17" noThreeD="1" sel="17" val="9"/>
 </file>
 
@@ -10658,7 +10685,7 @@
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
           <xdr:row>54</xdr:row>
-          <xdr:rowOff>222773</xdr:rowOff>
+          <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10716,7 +10743,7 @@
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
           <xdr:row>55</xdr:row>
-          <xdr:rowOff>222773</xdr:rowOff>
+          <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10774,7 +10801,7 @@
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
           <xdr:row>56</xdr:row>
-          <xdr:rowOff>222773</xdr:rowOff>
+          <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10832,7 +10859,7 @@
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
           <xdr:row>57</xdr:row>
-          <xdr:rowOff>217394</xdr:rowOff>
+          <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10900,7 +10927,7 @@
                   <a14:compatExt spid="_x0000_s1241"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98B1A0C3-498D-B973-63A0-459F704F1CE6}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D9040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -10958,7 +10985,7 @@
                   <a14:compatExt spid="_x0000_s1242"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8BB485B9-BD9C-436C-B9E9-ECD38173C272}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000DA040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -11016,7 +11043,7 @@
                   <a14:compatExt spid="_x0000_s1243"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D400A784-471F-9085-FFE7-4A994C91E86C}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000DB040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -11074,7 +11101,7 @@
                   <a14:compatExt spid="_x0000_s1244"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{527A9FB2-3393-0AD8-7091-4DEB3A6FF31A}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000DC040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -11132,7 +11159,7 @@
                   <a14:compatExt spid="_x0000_s1245"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{359D7B14-F917-8BCB-0339-BFCEEB1C7B3A}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000DD040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -11190,7 +11217,65 @@
                   <a14:compatExt spid="_x0000_s1246"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AB1582C-D455-F1D6-6827-27C1E6BBBC80}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000DE040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>64</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>1409700</xdr:colOff>
+          <xdr:row>65</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1247" name="Drop Down 223" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1247"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{267A547B-07F1-0730-BD33-E8E5A53B68A8}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -11816,7 +11901,7 @@
   <sheetPr codeName="Hoja1">
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A3:O64"/>
+  <dimension ref="A3:O65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.44140625" bestFit="1" customWidth="1"/>
@@ -11835,42 +11920,42 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:15" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="96" t="s">
+      <c r="A3" s="122" t="s">
         <v>103</v>
       </c>
-      <c r="B3" s="97"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="97"/>
-      <c r="E3" s="97"/>
-      <c r="F3" s="97"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="97"/>
-      <c r="I3" s="97"/>
-      <c r="J3" s="97"/>
-      <c r="K3" s="97"/>
-      <c r="L3" s="98"/>
-      <c r="N3" s="90" t="s">
+      <c r="B3" s="123"/>
+      <c r="C3" s="123"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="123"/>
+      <c r="F3" s="123"/>
+      <c r="G3" s="123"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="123"/>
+      <c r="J3" s="123"/>
+      <c r="K3" s="123"/>
+      <c r="L3" s="124"/>
+      <c r="N3" s="116" t="s">
         <v>0</v>
       </c>
-      <c r="O3" s="91"/>
+      <c r="O3" s="117"/>
     </row>
     <row r="4" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="103" t="s">
+      <c r="B4" s="129" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="104"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="104"/>
-      <c r="I4" s="104"/>
-      <c r="J4" s="105"/>
-      <c r="K4" s="105"/>
-      <c r="L4" s="106"/>
+      <c r="C4" s="130"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="130"/>
+      <c r="F4" s="130"/>
+      <c r="G4" s="130"/>
+      <c r="H4" s="130"/>
+      <c r="I4" s="130"/>
+      <c r="J4" s="131"/>
+      <c r="K4" s="131"/>
+      <c r="L4" s="132"/>
       <c r="N4" s="21" t="s">
         <v>2</v>
       </c>
@@ -11880,19 +11965,19 @@
       <c r="A5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="107" t="s">
+      <c r="B5" s="133" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="107"/>
-      <c r="D5" s="107"/>
-      <c r="E5" s="107"/>
-      <c r="F5" s="107"/>
-      <c r="G5" s="107"/>
-      <c r="H5" s="107"/>
-      <c r="I5" s="107"/>
-      <c r="J5" s="108"/>
-      <c r="K5" s="108"/>
-      <c r="L5" s="109"/>
+      <c r="C5" s="133"/>
+      <c r="D5" s="133"/>
+      <c r="E5" s="133"/>
+      <c r="F5" s="133"/>
+      <c r="G5" s="133"/>
+      <c r="H5" s="133"/>
+      <c r="I5" s="133"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="135"/>
       <c r="N5" s="15" t="s">
         <v>4</v>
       </c>
@@ -11902,19 +11987,19 @@
       <c r="A6" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="93">
+      <c r="B6" s="119">
         <v>46073</v>
       </c>
-      <c r="C6" s="94"/>
-      <c r="D6" s="94"/>
-      <c r="E6" s="94"/>
-      <c r="F6" s="94"/>
-      <c r="G6" s="94"/>
-      <c r="H6" s="94"/>
-      <c r="I6" s="94"/>
-      <c r="J6" s="94"/>
-      <c r="K6" s="94"/>
-      <c r="L6" s="95"/>
+      <c r="C6" s="120"/>
+      <c r="D6" s="120"/>
+      <c r="E6" s="120"/>
+      <c r="F6" s="120"/>
+      <c r="G6" s="120"/>
+      <c r="H6" s="120"/>
+      <c r="I6" s="120"/>
+      <c r="J6" s="120"/>
+      <c r="K6" s="120"/>
+      <c r="L6" s="121"/>
       <c r="N6" s="14"/>
       <c r="O6" s="14"/>
     </row>
@@ -11922,17 +12007,17 @@
       <c r="A7" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="110"/>
-      <c r="C7" s="111"/>
-      <c r="D7" s="111"/>
-      <c r="E7" s="111"/>
-      <c r="F7" s="111"/>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="112"/>
-      <c r="K7" s="112"/>
-      <c r="L7" s="113"/>
+      <c r="B7" s="136"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="137"/>
+      <c r="E7" s="137"/>
+      <c r="F7" s="137"/>
+      <c r="G7" s="137"/>
+      <c r="H7" s="137"/>
+      <c r="I7" s="137"/>
+      <c r="J7" s="138"/>
+      <c r="K7" s="138"/>
+      <c r="L7" s="139"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
@@ -11949,20 +12034,20 @@
       <c r="L8" s="13"/>
     </row>
     <row r="9" spans="1:15" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="99" t="s">
+      <c r="A9" s="125" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="100"/>
-      <c r="C9" s="100"/>
-      <c r="D9" s="100"/>
-      <c r="E9" s="100"/>
-      <c r="F9" s="100"/>
-      <c r="G9" s="100"/>
-      <c r="H9" s="100"/>
-      <c r="I9" s="100"/>
-      <c r="J9" s="101"/>
-      <c r="K9" s="101"/>
-      <c r="L9" s="102"/>
+      <c r="B9" s="126"/>
+      <c r="C9" s="126"/>
+      <c r="D9" s="126"/>
+      <c r="E9" s="126"/>
+      <c r="F9" s="126"/>
+      <c r="G9" s="126"/>
+      <c r="H9" s="126"/>
+      <c r="I9" s="126"/>
+      <c r="J9" s="127"/>
+      <c r="K9" s="127"/>
+      <c r="L9" s="128"/>
     </row>
     <row r="10" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -12062,63 +12147,63 @@
       <c r="A14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="92"/>
-      <c r="C14" s="88"/>
-      <c r="D14" s="88"/>
-      <c r="E14" s="88"/>
-      <c r="F14" s="88"/>
-      <c r="G14" s="88"/>
-      <c r="H14" s="88"/>
-      <c r="I14" s="88"/>
-      <c r="J14" s="88"/>
-      <c r="K14" s="88"/>
-      <c r="L14" s="89"/>
+      <c r="B14" s="118"/>
+      <c r="C14" s="114"/>
+      <c r="D14" s="114"/>
+      <c r="E14" s="114"/>
+      <c r="F14" s="114"/>
+      <c r="G14" s="114"/>
+      <c r="H14" s="114"/>
+      <c r="I14" s="114"/>
+      <c r="J14" s="114"/>
+      <c r="K14" s="114"/>
+      <c r="L14" s="115"/>
     </row>
     <row r="15" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="87"/>
-      <c r="C15" s="88"/>
-      <c r="D15" s="88"/>
-      <c r="E15" s="88"/>
-      <c r="F15" s="88"/>
-      <c r="G15" s="88"/>
-      <c r="H15" s="88"/>
-      <c r="I15" s="88"/>
-      <c r="J15" s="88"/>
-      <c r="K15" s="88"/>
-      <c r="L15" s="89"/>
+      <c r="B15" s="113"/>
+      <c r="C15" s="114"/>
+      <c r="D15" s="114"/>
+      <c r="E15" s="114"/>
+      <c r="F15" s="114"/>
+      <c r="G15" s="114"/>
+      <c r="H15" s="114"/>
+      <c r="I15" s="114"/>
+      <c r="J15" s="114"/>
+      <c r="K15" s="114"/>
+      <c r="L15" s="115"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="80"/>
-      <c r="B16" s="81"/>
-      <c r="C16" s="81"/>
-      <c r="D16" s="81"/>
-      <c r="E16" s="81"/>
-      <c r="F16" s="81"/>
-      <c r="G16" s="81"/>
-      <c r="H16" s="81"/>
-      <c r="I16" s="81"/>
-      <c r="J16" s="81"/>
-      <c r="K16" s="81"/>
-      <c r="L16" s="82"/>
+      <c r="A16" s="106"/>
+      <c r="B16" s="107"/>
+      <c r="C16" s="107"/>
+      <c r="D16" s="107"/>
+      <c r="E16" s="107"/>
+      <c r="F16" s="107"/>
+      <c r="G16" s="107"/>
+      <c r="H16" s="107"/>
+      <c r="I16" s="107"/>
+      <c r="J16" s="107"/>
+      <c r="K16" s="107"/>
+      <c r="L16" s="108"/>
     </row>
     <row r="17" spans="1:12" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="83" t="s">
+      <c r="A17" s="109" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="84"/>
-      <c r="C17" s="84"/>
-      <c r="D17" s="84"/>
-      <c r="E17" s="84"/>
-      <c r="F17" s="84"/>
-      <c r="G17" s="84"/>
-      <c r="H17" s="84"/>
-      <c r="I17" s="84"/>
-      <c r="J17" s="85"/>
-      <c r="K17" s="85"/>
-      <c r="L17" s="86"/>
+      <c r="B17" s="110"/>
+      <c r="C17" s="110"/>
+      <c r="D17" s="110"/>
+      <c r="E17" s="110"/>
+      <c r="F17" s="110"/>
+      <c r="G17" s="110"/>
+      <c r="H17" s="110"/>
+      <c r="I17" s="110"/>
+      <c r="J17" s="111"/>
+      <c r="K17" s="111"/>
+      <c r="L17" s="112"/>
     </row>
     <row r="18" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
@@ -12128,19 +12213,19 @@
       <c r="C18" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="114" t="s">
+      <c r="D18" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="116" t="s">
+      <c r="E18" s="84" t="s">
         <v>115</v>
       </c>
-      <c r="F18" s="116"/>
-      <c r="G18" s="116"/>
-      <c r="H18" s="116"/>
-      <c r="I18" s="116"/>
-      <c r="J18" s="117"/>
-      <c r="K18" s="117"/>
-      <c r="L18" s="118"/>
+      <c r="F18" s="84"/>
+      <c r="G18" s="84"/>
+      <c r="H18" s="84"/>
+      <c r="I18" s="84"/>
+      <c r="J18" s="85"/>
+      <c r="K18" s="85"/>
+      <c r="L18" s="86"/>
     </row>
     <row r="19" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
@@ -12150,15 +12235,15 @@
         <v>30</v>
       </c>
       <c r="C19" s="44"/>
-      <c r="D19" s="115"/>
-      <c r="E19" s="119"/>
-      <c r="F19" s="119"/>
-      <c r="G19" s="119"/>
-      <c r="H19" s="119"/>
-      <c r="I19" s="119"/>
-      <c r="J19" s="120"/>
-      <c r="K19" s="120"/>
-      <c r="L19" s="121"/>
+      <c r="D19" s="83"/>
+      <c r="E19" s="87"/>
+      <c r="F19" s="87"/>
+      <c r="G19" s="87"/>
+      <c r="H19" s="87"/>
+      <c r="I19" s="87"/>
+      <c r="J19" s="88"/>
+      <c r="K19" s="88"/>
+      <c r="L19" s="89"/>
     </row>
     <row r="20" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
@@ -12168,15 +12253,15 @@
       <c r="C20" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="115"/>
-      <c r="E20" s="119"/>
-      <c r="F20" s="119"/>
-      <c r="G20" s="119"/>
-      <c r="H20" s="119"/>
-      <c r="I20" s="119"/>
-      <c r="J20" s="120"/>
-      <c r="K20" s="120"/>
-      <c r="L20" s="121"/>
+      <c r="D20" s="83"/>
+      <c r="E20" s="87"/>
+      <c r="F20" s="87"/>
+      <c r="G20" s="87"/>
+      <c r="H20" s="87"/>
+      <c r="I20" s="87"/>
+      <c r="J20" s="88"/>
+      <c r="K20" s="88"/>
+      <c r="L20" s="89"/>
     </row>
     <row r="21" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
@@ -12186,19 +12271,19 @@
       <c r="C21" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="130" t="s">
+      <c r="D21" s="98" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="132" t="s">
+      <c r="E21" s="100" t="s">
         <v>107</v>
       </c>
-      <c r="F21" s="133"/>
-      <c r="G21" s="133"/>
-      <c r="H21" s="133"/>
-      <c r="I21" s="133"/>
-      <c r="J21" s="133"/>
-      <c r="K21" s="133"/>
-      <c r="L21" s="134"/>
+      <c r="F21" s="101"/>
+      <c r="G21" s="101"/>
+      <c r="H21" s="101"/>
+      <c r="I21" s="101"/>
+      <c r="J21" s="101"/>
+      <c r="K21" s="101"/>
+      <c r="L21" s="102"/>
     </row>
     <row r="22" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
@@ -12208,45 +12293,45 @@
       <c r="C22" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="131"/>
-      <c r="E22" s="135"/>
-      <c r="F22" s="136"/>
-      <c r="G22" s="136"/>
-      <c r="H22" s="136"/>
-      <c r="I22" s="136"/>
-      <c r="J22" s="136"/>
-      <c r="K22" s="136"/>
-      <c r="L22" s="137"/>
+      <c r="D22" s="99"/>
+      <c r="E22" s="103"/>
+      <c r="F22" s="104"/>
+      <c r="G22" s="104"/>
+      <c r="H22" s="104"/>
+      <c r="I22" s="104"/>
+      <c r="J22" s="104"/>
+      <c r="K22" s="104"/>
+      <c r="L22" s="105"/>
     </row>
     <row r="23" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="123"/>
-      <c r="B23" s="124"/>
-      <c r="C23" s="124"/>
-      <c r="D23" s="125"/>
-      <c r="E23" s="125"/>
-      <c r="F23" s="125"/>
-      <c r="G23" s="125"/>
-      <c r="H23" s="125"/>
-      <c r="I23" s="125"/>
-      <c r="J23" s="125"/>
-      <c r="K23" s="125"/>
-      <c r="L23" s="126"/>
+      <c r="A23" s="91"/>
+      <c r="B23" s="92"/>
+      <c r="C23" s="92"/>
+      <c r="D23" s="93"/>
+      <c r="E23" s="93"/>
+      <c r="F23" s="93"/>
+      <c r="G23" s="93"/>
+      <c r="H23" s="93"/>
+      <c r="I23" s="93"/>
+      <c r="J23" s="93"/>
+      <c r="K23" s="93"/>
+      <c r="L23" s="94"/>
     </row>
     <row r="24" spans="1:12" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="127" t="s">
+      <c r="A24" s="95" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="128"/>
-      <c r="C24" s="128"/>
-      <c r="D24" s="128"/>
-      <c r="E24" s="128"/>
-      <c r="F24" s="128"/>
-      <c r="G24" s="128"/>
-      <c r="H24" s="128"/>
-      <c r="I24" s="128"/>
-      <c r="J24" s="128"/>
-      <c r="K24" s="128"/>
-      <c r="L24" s="129"/>
+      <c r="B24" s="96"/>
+      <c r="C24" s="96"/>
+      <c r="D24" s="96"/>
+      <c r="E24" s="96"/>
+      <c r="F24" s="96"/>
+      <c r="G24" s="96"/>
+      <c r="H24" s="96"/>
+      <c r="I24" s="96"/>
+      <c r="J24" s="96"/>
+      <c r="K24" s="96"/>
+      <c r="L24" s="97"/>
     </row>
     <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
@@ -12258,17 +12343,17 @@
       <c r="C25" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="122" t="s">
+      <c r="D25" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="E25" s="122"/>
-      <c r="F25" s="122"/>
-      <c r="G25" s="122"/>
-      <c r="H25" s="122"/>
-      <c r="I25" s="122"/>
-      <c r="J25" s="122"/>
-      <c r="K25" s="122"/>
-      <c r="L25" s="122"/>
+      <c r="E25" s="90"/>
+      <c r="F25" s="90"/>
+      <c r="G25" s="90"/>
+      <c r="H25" s="90"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="90"/>
+      <c r="K25" s="90"/>
+      <c r="L25" s="90"/>
     </row>
     <row r="26" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="33">
@@ -12278,17 +12363,17 @@
         <v>116</v>
       </c>
       <c r="C26" s="34"/>
-      <c r="D26" s="138" t="s">
+      <c r="D26" s="174" t="s">
         <v>108</v>
       </c>
-      <c r="E26" s="138"/>
-      <c r="F26" s="138"/>
-      <c r="G26" s="138"/>
-      <c r="H26" s="138"/>
-      <c r="I26" s="138"/>
-      <c r="J26" s="138"/>
-      <c r="K26" s="138"/>
-      <c r="L26" s="138"/>
+      <c r="E26" s="80"/>
+      <c r="F26" s="80"/>
+      <c r="G26" s="80"/>
+      <c r="H26" s="80"/>
+      <c r="I26" s="80"/>
+      <c r="J26" s="80"/>
+      <c r="K26" s="80"/>
+      <c r="L26" s="80"/>
     </row>
     <row r="27" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
@@ -12298,15 +12383,15 @@
         <v>117</v>
       </c>
       <c r="C27" s="34"/>
-      <c r="D27" s="139"/>
-      <c r="E27" s="139"/>
-      <c r="F27" s="139"/>
-      <c r="G27" s="139"/>
-      <c r="H27" s="139"/>
-      <c r="I27" s="139"/>
-      <c r="J27" s="139"/>
-      <c r="K27" s="139"/>
-      <c r="L27" s="139"/>
+      <c r="D27" s="175"/>
+      <c r="E27" s="81"/>
+      <c r="F27" s="81"/>
+      <c r="G27" s="81"/>
+      <c r="H27" s="81"/>
+      <c r="I27" s="81"/>
+      <c r="J27" s="81"/>
+      <c r="K27" s="81"/>
+      <c r="L27" s="81"/>
     </row>
     <row r="28" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="33">
@@ -12316,15 +12401,15 @@
         <v>118</v>
       </c>
       <c r="C28" s="34"/>
-      <c r="D28" s="139"/>
-      <c r="E28" s="139"/>
-      <c r="F28" s="139"/>
-      <c r="G28" s="139"/>
-      <c r="H28" s="139"/>
-      <c r="I28" s="139"/>
-      <c r="J28" s="139"/>
-      <c r="K28" s="139"/>
-      <c r="L28" s="139"/>
+      <c r="D28" s="175"/>
+      <c r="E28" s="81"/>
+      <c r="F28" s="81"/>
+      <c r="G28" s="81"/>
+      <c r="H28" s="81"/>
+      <c r="I28" s="81"/>
+      <c r="J28" s="81"/>
+      <c r="K28" s="81"/>
+      <c r="L28" s="81"/>
     </row>
     <row r="29" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
@@ -12334,15 +12419,15 @@
         <v>119</v>
       </c>
       <c r="C29" s="34"/>
-      <c r="D29" s="139"/>
-      <c r="E29" s="139"/>
-      <c r="F29" s="139"/>
-      <c r="G29" s="139"/>
-      <c r="H29" s="139"/>
-      <c r="I29" s="139"/>
-      <c r="J29" s="139"/>
-      <c r="K29" s="139"/>
-      <c r="L29" s="139"/>
+      <c r="D29" s="175"/>
+      <c r="E29" s="81"/>
+      <c r="F29" s="81"/>
+      <c r="G29" s="81"/>
+      <c r="H29" s="81"/>
+      <c r="I29" s="81"/>
+      <c r="J29" s="81"/>
+      <c r="K29" s="81"/>
+      <c r="L29" s="81"/>
     </row>
     <row r="30" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="33">
@@ -12352,15 +12437,15 @@
         <v>120</v>
       </c>
       <c r="C30" s="34"/>
-      <c r="D30" s="139"/>
-      <c r="E30" s="139"/>
-      <c r="F30" s="139"/>
-      <c r="G30" s="139"/>
-      <c r="H30" s="139"/>
-      <c r="I30" s="139"/>
-      <c r="J30" s="139"/>
-      <c r="K30" s="139"/>
-      <c r="L30" s="139"/>
+      <c r="D30" s="175"/>
+      <c r="E30" s="81"/>
+      <c r="F30" s="81"/>
+      <c r="G30" s="81"/>
+      <c r="H30" s="81"/>
+      <c r="I30" s="81"/>
+      <c r="J30" s="81"/>
+      <c r="K30" s="81"/>
+      <c r="L30" s="81"/>
     </row>
     <row r="31" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="33">
@@ -12370,15 +12455,15 @@
         <v>121</v>
       </c>
       <c r="C31" s="34"/>
-      <c r="D31" s="139"/>
-      <c r="E31" s="139"/>
-      <c r="F31" s="139"/>
-      <c r="G31" s="139"/>
-      <c r="H31" s="139"/>
-      <c r="I31" s="139"/>
-      <c r="J31" s="139"/>
-      <c r="K31" s="139"/>
-      <c r="L31" s="139"/>
+      <c r="D31" s="175"/>
+      <c r="E31" s="81"/>
+      <c r="F31" s="81"/>
+      <c r="G31" s="81"/>
+      <c r="H31" s="81"/>
+      <c r="I31" s="81"/>
+      <c r="J31" s="81"/>
+      <c r="K31" s="81"/>
+      <c r="L31" s="81"/>
     </row>
     <row r="32" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="33">
@@ -12388,15 +12473,15 @@
         <v>122</v>
       </c>
       <c r="C32" s="34"/>
-      <c r="D32" s="139"/>
-      <c r="E32" s="139"/>
-      <c r="F32" s="139"/>
-      <c r="G32" s="139"/>
-      <c r="H32" s="139"/>
-      <c r="I32" s="139"/>
-      <c r="J32" s="139"/>
-      <c r="K32" s="139"/>
-      <c r="L32" s="139"/>
+      <c r="D32" s="175"/>
+      <c r="E32" s="81"/>
+      <c r="F32" s="81"/>
+      <c r="G32" s="81"/>
+      <c r="H32" s="81"/>
+      <c r="I32" s="81"/>
+      <c r="J32" s="81"/>
+      <c r="K32" s="81"/>
+      <c r="L32" s="81"/>
     </row>
     <row r="33" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="33">
@@ -12406,15 +12491,15 @@
         <v>123</v>
       </c>
       <c r="C33" s="34"/>
-      <c r="D33" s="139"/>
-      <c r="E33" s="139"/>
-      <c r="F33" s="139"/>
-      <c r="G33" s="139"/>
-      <c r="H33" s="139"/>
-      <c r="I33" s="139"/>
-      <c r="J33" s="139"/>
-      <c r="K33" s="139"/>
-      <c r="L33" s="139"/>
+      <c r="D33" s="175"/>
+      <c r="E33" s="81"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="81"/>
+      <c r="H33" s="81"/>
+      <c r="I33" s="81"/>
+      <c r="J33" s="81"/>
+      <c r="K33" s="81"/>
+      <c r="L33" s="81"/>
     </row>
     <row r="34" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="33">
@@ -12424,15 +12509,15 @@
         <v>124</v>
       </c>
       <c r="C34" s="34"/>
-      <c r="D34" s="139"/>
-      <c r="E34" s="139"/>
-      <c r="F34" s="139"/>
-      <c r="G34" s="139"/>
-      <c r="H34" s="139"/>
-      <c r="I34" s="139"/>
-      <c r="J34" s="139"/>
-      <c r="K34" s="139"/>
-      <c r="L34" s="139"/>
+      <c r="D34" s="175"/>
+      <c r="E34" s="81"/>
+      <c r="F34" s="81"/>
+      <c r="G34" s="81"/>
+      <c r="H34" s="81"/>
+      <c r="I34" s="81"/>
+      <c r="J34" s="81"/>
+      <c r="K34" s="81"/>
+      <c r="L34" s="81"/>
     </row>
     <row r="35" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="33">
@@ -12442,15 +12527,15 @@
         <v>125</v>
       </c>
       <c r="C35" s="34"/>
-      <c r="D35" s="139"/>
-      <c r="E35" s="139"/>
-      <c r="F35" s="139"/>
-      <c r="G35" s="139"/>
-      <c r="H35" s="139"/>
-      <c r="I35" s="139"/>
-      <c r="J35" s="139"/>
-      <c r="K35" s="139"/>
-      <c r="L35" s="139"/>
+      <c r="D35" s="175"/>
+      <c r="E35" s="81"/>
+      <c r="F35" s="81"/>
+      <c r="G35" s="81"/>
+      <c r="H35" s="81"/>
+      <c r="I35" s="81"/>
+      <c r="J35" s="81"/>
+      <c r="K35" s="81"/>
+      <c r="L35" s="81"/>
     </row>
     <row r="36" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="33">
@@ -12460,15 +12545,15 @@
         <v>126</v>
       </c>
       <c r="C36" s="34"/>
-      <c r="D36" s="139"/>
-      <c r="E36" s="139"/>
-      <c r="F36" s="139"/>
-      <c r="G36" s="139"/>
-      <c r="H36" s="139"/>
-      <c r="I36" s="139"/>
-      <c r="J36" s="139"/>
-      <c r="K36" s="139"/>
-      <c r="L36" s="139"/>
+      <c r="D36" s="175"/>
+      <c r="E36" s="81"/>
+      <c r="F36" s="81"/>
+      <c r="G36" s="81"/>
+      <c r="H36" s="81"/>
+      <c r="I36" s="81"/>
+      <c r="J36" s="81"/>
+      <c r="K36" s="81"/>
+      <c r="L36" s="81"/>
     </row>
     <row r="37" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="33">
@@ -12478,15 +12563,15 @@
         <v>127</v>
       </c>
       <c r="C37" s="34"/>
-      <c r="D37" s="139"/>
-      <c r="E37" s="139"/>
-      <c r="F37" s="139"/>
-      <c r="G37" s="139"/>
-      <c r="H37" s="139"/>
-      <c r="I37" s="139"/>
-      <c r="J37" s="139"/>
-      <c r="K37" s="139"/>
-      <c r="L37" s="139"/>
+      <c r="D37" s="175"/>
+      <c r="E37" s="81"/>
+      <c r="F37" s="81"/>
+      <c r="G37" s="81"/>
+      <c r="H37" s="81"/>
+      <c r="I37" s="81"/>
+      <c r="J37" s="81"/>
+      <c r="K37" s="81"/>
+      <c r="L37" s="81"/>
     </row>
     <row r="38" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="33">
@@ -12496,15 +12581,15 @@
         <v>128</v>
       </c>
       <c r="C38" s="34"/>
-      <c r="D38" s="139"/>
-      <c r="E38" s="139"/>
-      <c r="F38" s="139"/>
-      <c r="G38" s="139"/>
-      <c r="H38" s="139"/>
-      <c r="I38" s="139"/>
-      <c r="J38" s="139"/>
-      <c r="K38" s="139"/>
-      <c r="L38" s="139"/>
+      <c r="D38" s="175"/>
+      <c r="E38" s="81"/>
+      <c r="F38" s="81"/>
+      <c r="G38" s="81"/>
+      <c r="H38" s="81"/>
+      <c r="I38" s="81"/>
+      <c r="J38" s="81"/>
+      <c r="K38" s="81"/>
+      <c r="L38" s="81"/>
     </row>
     <row r="39" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="33">
@@ -12514,15 +12599,15 @@
         <v>129</v>
       </c>
       <c r="C39" s="34"/>
-      <c r="D39" s="139"/>
-      <c r="E39" s="139"/>
-      <c r="F39" s="139"/>
-      <c r="G39" s="139"/>
-      <c r="H39" s="139"/>
-      <c r="I39" s="139"/>
-      <c r="J39" s="139"/>
-      <c r="K39" s="139"/>
-      <c r="L39" s="139"/>
+      <c r="D39" s="175"/>
+      <c r="E39" s="81"/>
+      <c r="F39" s="81"/>
+      <c r="G39" s="81"/>
+      <c r="H39" s="81"/>
+      <c r="I39" s="81"/>
+      <c r="J39" s="81"/>
+      <c r="K39" s="81"/>
+      <c r="L39" s="81"/>
     </row>
     <row r="40" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="33">
@@ -12532,15 +12617,15 @@
         <v>130</v>
       </c>
       <c r="C40" s="34"/>
-      <c r="D40" s="139"/>
-      <c r="E40" s="139"/>
-      <c r="F40" s="139"/>
-      <c r="G40" s="139"/>
-      <c r="H40" s="139"/>
-      <c r="I40" s="139"/>
-      <c r="J40" s="139"/>
-      <c r="K40" s="139"/>
-      <c r="L40" s="139"/>
+      <c r="D40" s="175"/>
+      <c r="E40" s="81"/>
+      <c r="F40" s="81"/>
+      <c r="G40" s="81"/>
+      <c r="H40" s="81"/>
+      <c r="I40" s="81"/>
+      <c r="J40" s="81"/>
+      <c r="K40" s="81"/>
+      <c r="L40" s="81"/>
     </row>
     <row r="41" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="33">
@@ -12550,15 +12635,15 @@
         <v>131</v>
       </c>
       <c r="C41" s="34"/>
-      <c r="D41" s="139"/>
-      <c r="E41" s="139"/>
-      <c r="F41" s="139"/>
-      <c r="G41" s="139"/>
-      <c r="H41" s="139"/>
-      <c r="I41" s="139"/>
-      <c r="J41" s="139"/>
-      <c r="K41" s="139"/>
-      <c r="L41" s="139"/>
+      <c r="D41" s="175"/>
+      <c r="E41" s="81"/>
+      <c r="F41" s="81"/>
+      <c r="G41" s="81"/>
+      <c r="H41" s="81"/>
+      <c r="I41" s="81"/>
+      <c r="J41" s="81"/>
+      <c r="K41" s="81"/>
+      <c r="L41" s="81"/>
     </row>
     <row r="42" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="33">
@@ -12568,15 +12653,15 @@
         <v>132</v>
       </c>
       <c r="C42" s="34"/>
-      <c r="D42" s="139"/>
-      <c r="E42" s="139"/>
-      <c r="F42" s="139"/>
-      <c r="G42" s="139"/>
-      <c r="H42" s="139"/>
-      <c r="I42" s="139"/>
-      <c r="J42" s="139"/>
-      <c r="K42" s="139"/>
-      <c r="L42" s="139"/>
+      <c r="D42" s="175"/>
+      <c r="E42" s="81"/>
+      <c r="F42" s="81"/>
+      <c r="G42" s="81"/>
+      <c r="H42" s="81"/>
+      <c r="I42" s="81"/>
+      <c r="J42" s="81"/>
+      <c r="K42" s="81"/>
+      <c r="L42" s="81"/>
     </row>
     <row r="43" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="33">
@@ -12586,15 +12671,15 @@
         <v>133</v>
       </c>
       <c r="C43" s="34"/>
-      <c r="D43" s="139"/>
-      <c r="E43" s="139"/>
-      <c r="F43" s="139"/>
-      <c r="G43" s="139"/>
-      <c r="H43" s="139"/>
-      <c r="I43" s="139"/>
-      <c r="J43" s="139"/>
-      <c r="K43" s="139"/>
-      <c r="L43" s="139"/>
+      <c r="D43" s="175"/>
+      <c r="E43" s="81"/>
+      <c r="F43" s="81"/>
+      <c r="G43" s="81"/>
+      <c r="H43" s="81"/>
+      <c r="I43" s="81"/>
+      <c r="J43" s="81"/>
+      <c r="K43" s="81"/>
+      <c r="L43" s="81"/>
     </row>
     <row r="44" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="33">
@@ -12604,15 +12689,15 @@
         <v>134</v>
       </c>
       <c r="C44" s="34"/>
-      <c r="D44" s="139"/>
-      <c r="E44" s="139"/>
-      <c r="F44" s="139"/>
-      <c r="G44" s="139"/>
-      <c r="H44" s="139"/>
-      <c r="I44" s="139"/>
-      <c r="J44" s="139"/>
-      <c r="K44" s="139"/>
-      <c r="L44" s="139"/>
+      <c r="D44" s="175"/>
+      <c r="E44" s="81"/>
+      <c r="F44" s="81"/>
+      <c r="G44" s="81"/>
+      <c r="H44" s="81"/>
+      <c r="I44" s="81"/>
+      <c r="J44" s="81"/>
+      <c r="K44" s="81"/>
+      <c r="L44" s="81"/>
     </row>
     <row r="45" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="33">
@@ -12622,15 +12707,15 @@
         <v>135</v>
       </c>
       <c r="C45" s="34"/>
-      <c r="D45" s="139"/>
-      <c r="E45" s="139"/>
-      <c r="F45" s="139"/>
-      <c r="G45" s="139"/>
-      <c r="H45" s="139"/>
-      <c r="I45" s="139"/>
-      <c r="J45" s="139"/>
-      <c r="K45" s="139"/>
-      <c r="L45" s="139"/>
+      <c r="D45" s="175"/>
+      <c r="E45" s="81"/>
+      <c r="F45" s="81"/>
+      <c r="G45" s="81"/>
+      <c r="H45" s="81"/>
+      <c r="I45" s="81"/>
+      <c r="J45" s="81"/>
+      <c r="K45" s="81"/>
+      <c r="L45" s="81"/>
     </row>
     <row r="46" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="33">
@@ -12640,15 +12725,15 @@
         <v>136</v>
       </c>
       <c r="C46" s="34"/>
-      <c r="D46" s="139"/>
-      <c r="E46" s="139"/>
-      <c r="F46" s="139"/>
-      <c r="G46" s="139"/>
-      <c r="H46" s="139"/>
-      <c r="I46" s="139"/>
-      <c r="J46" s="139"/>
-      <c r="K46" s="139"/>
-      <c r="L46" s="139"/>
+      <c r="D46" s="175"/>
+      <c r="E46" s="81"/>
+      <c r="F46" s="81"/>
+      <c r="G46" s="81"/>
+      <c r="H46" s="81"/>
+      <c r="I46" s="81"/>
+      <c r="J46" s="81"/>
+      <c r="K46" s="81"/>
+      <c r="L46" s="81"/>
     </row>
     <row r="47" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="33">
@@ -12658,15 +12743,15 @@
         <v>137</v>
       </c>
       <c r="C47" s="34"/>
-      <c r="D47" s="139"/>
-      <c r="E47" s="139"/>
-      <c r="F47" s="139"/>
-      <c r="G47" s="139"/>
-      <c r="H47" s="139"/>
-      <c r="I47" s="139"/>
-      <c r="J47" s="139"/>
-      <c r="K47" s="139"/>
-      <c r="L47" s="139"/>
+      <c r="D47" s="175"/>
+      <c r="E47" s="81"/>
+      <c r="F47" s="81"/>
+      <c r="G47" s="81"/>
+      <c r="H47" s="81"/>
+      <c r="I47" s="81"/>
+      <c r="J47" s="81"/>
+      <c r="K47" s="81"/>
+      <c r="L47" s="81"/>
     </row>
     <row r="48" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="33">
@@ -12676,15 +12761,15 @@
         <v>138</v>
       </c>
       <c r="C48" s="34"/>
-      <c r="D48" s="139"/>
-      <c r="E48" s="139"/>
-      <c r="F48" s="139"/>
-      <c r="G48" s="139"/>
-      <c r="H48" s="139"/>
-      <c r="I48" s="139"/>
-      <c r="J48" s="139"/>
-      <c r="K48" s="139"/>
-      <c r="L48" s="139"/>
+      <c r="D48" s="175"/>
+      <c r="E48" s="81"/>
+      <c r="F48" s="81"/>
+      <c r="G48" s="81"/>
+      <c r="H48" s="81"/>
+      <c r="I48" s="81"/>
+      <c r="J48" s="81"/>
+      <c r="K48" s="81"/>
+      <c r="L48" s="81"/>
     </row>
     <row r="49" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="33">
@@ -12694,15 +12779,15 @@
         <v>139</v>
       </c>
       <c r="C49" s="34"/>
-      <c r="D49" s="139"/>
-      <c r="E49" s="139"/>
-      <c r="F49" s="139"/>
-      <c r="G49" s="139"/>
-      <c r="H49" s="139"/>
-      <c r="I49" s="139"/>
-      <c r="J49" s="139"/>
-      <c r="K49" s="139"/>
-      <c r="L49" s="139"/>
+      <c r="D49" s="175"/>
+      <c r="E49" s="81"/>
+      <c r="F49" s="81"/>
+      <c r="G49" s="81"/>
+      <c r="H49" s="81"/>
+      <c r="I49" s="81"/>
+      <c r="J49" s="81"/>
+      <c r="K49" s="81"/>
+      <c r="L49" s="81"/>
     </row>
     <row r="50" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="72">
@@ -12712,15 +12797,15 @@
         <v>140</v>
       </c>
       <c r="C50" s="34"/>
-      <c r="D50" s="139"/>
-      <c r="E50" s="139"/>
-      <c r="F50" s="139"/>
-      <c r="G50" s="139"/>
-      <c r="H50" s="139"/>
-      <c r="I50" s="139"/>
-      <c r="J50" s="139"/>
-      <c r="K50" s="139"/>
-      <c r="L50" s="139"/>
+      <c r="D50" s="175"/>
+      <c r="E50" s="81"/>
+      <c r="F50" s="81"/>
+      <c r="G50" s="81"/>
+      <c r="H50" s="81"/>
+      <c r="I50" s="81"/>
+      <c r="J50" s="81"/>
+      <c r="K50" s="81"/>
+      <c r="L50" s="81"/>
     </row>
     <row r="51" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="72">
@@ -12730,15 +12815,15 @@
         <v>141</v>
       </c>
       <c r="C51" s="34"/>
-      <c r="D51" s="139"/>
-      <c r="E51" s="139"/>
-      <c r="F51" s="139"/>
-      <c r="G51" s="139"/>
-      <c r="H51" s="139"/>
-      <c r="I51" s="139"/>
-      <c r="J51" s="139"/>
-      <c r="K51" s="139"/>
-      <c r="L51" s="139"/>
+      <c r="D51" s="175"/>
+      <c r="E51" s="81"/>
+      <c r="F51" s="81"/>
+      <c r="G51" s="81"/>
+      <c r="H51" s="81"/>
+      <c r="I51" s="81"/>
+      <c r="J51" s="81"/>
+      <c r="K51" s="81"/>
+      <c r="L51" s="81"/>
     </row>
     <row r="52" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="72">
@@ -12748,15 +12833,15 @@
         <v>142</v>
       </c>
       <c r="C52" s="34"/>
-      <c r="D52" s="139"/>
-      <c r="E52" s="139"/>
-      <c r="F52" s="139"/>
-      <c r="G52" s="139"/>
-      <c r="H52" s="139"/>
-      <c r="I52" s="139"/>
-      <c r="J52" s="139"/>
-      <c r="K52" s="139"/>
-      <c r="L52" s="139"/>
+      <c r="D52" s="175"/>
+      <c r="E52" s="81"/>
+      <c r="F52" s="81"/>
+      <c r="G52" s="81"/>
+      <c r="H52" s="81"/>
+      <c r="I52" s="81"/>
+      <c r="J52" s="81"/>
+      <c r="K52" s="81"/>
+      <c r="L52" s="81"/>
     </row>
     <row r="53" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="72">
@@ -12766,15 +12851,15 @@
         <v>143</v>
       </c>
       <c r="C53" s="79"/>
-      <c r="D53" s="139"/>
-      <c r="E53" s="139"/>
-      <c r="F53" s="139"/>
-      <c r="G53" s="139"/>
-      <c r="H53" s="139"/>
-      <c r="I53" s="139"/>
-      <c r="J53" s="139"/>
-      <c r="K53" s="139"/>
-      <c r="L53" s="139"/>
+      <c r="D53" s="175"/>
+      <c r="E53" s="81"/>
+      <c r="F53" s="81"/>
+      <c r="G53" s="81"/>
+      <c r="H53" s="81"/>
+      <c r="I53" s="81"/>
+      <c r="J53" s="81"/>
+      <c r="K53" s="81"/>
+      <c r="L53" s="81"/>
     </row>
     <row r="54" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="72">
@@ -12784,15 +12869,15 @@
         <v>144</v>
       </c>
       <c r="C54" s="72"/>
-      <c r="D54" s="139"/>
-      <c r="E54" s="139"/>
-      <c r="F54" s="139"/>
-      <c r="G54" s="139"/>
-      <c r="H54" s="139"/>
-      <c r="I54" s="139"/>
-      <c r="J54" s="139"/>
-      <c r="K54" s="139"/>
-      <c r="L54" s="139"/>
+      <c r="D54" s="175"/>
+      <c r="E54" s="81"/>
+      <c r="F54" s="81"/>
+      <c r="G54" s="81"/>
+      <c r="H54" s="81"/>
+      <c r="I54" s="81"/>
+      <c r="J54" s="81"/>
+      <c r="K54" s="81"/>
+      <c r="L54" s="81"/>
     </row>
     <row r="55" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="72">
@@ -12802,15 +12887,15 @@
         <v>145</v>
       </c>
       <c r="C55" s="78"/>
-      <c r="D55" s="139"/>
-      <c r="E55" s="139"/>
-      <c r="F55" s="139"/>
-      <c r="G55" s="139"/>
-      <c r="H55" s="139"/>
-      <c r="I55" s="139"/>
-      <c r="J55" s="139"/>
-      <c r="K55" s="139"/>
-      <c r="L55" s="139"/>
+      <c r="D55" s="175"/>
+      <c r="E55" s="81"/>
+      <c r="F55" s="81"/>
+      <c r="G55" s="81"/>
+      <c r="H55" s="81"/>
+      <c r="I55" s="81"/>
+      <c r="J55" s="81"/>
+      <c r="K55" s="81"/>
+      <c r="L55" s="81"/>
     </row>
     <row r="56" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="72">
@@ -12820,15 +12905,15 @@
         <v>146</v>
       </c>
       <c r="C56" s="78"/>
-      <c r="D56" s="139"/>
-      <c r="E56" s="139"/>
-      <c r="F56" s="139"/>
-      <c r="G56" s="139"/>
-      <c r="H56" s="139"/>
-      <c r="I56" s="139"/>
-      <c r="J56" s="139"/>
-      <c r="K56" s="139"/>
-      <c r="L56" s="139"/>
+      <c r="D56" s="175"/>
+      <c r="E56" s="81"/>
+      <c r="F56" s="81"/>
+      <c r="G56" s="81"/>
+      <c r="H56" s="81"/>
+      <c r="I56" s="81"/>
+      <c r="J56" s="81"/>
+      <c r="K56" s="81"/>
+      <c r="L56" s="81"/>
     </row>
     <row r="57" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="72">
@@ -12838,15 +12923,15 @@
         <v>147</v>
       </c>
       <c r="C57" s="78"/>
-      <c r="D57" s="139"/>
-      <c r="E57" s="139"/>
-      <c r="F57" s="139"/>
-      <c r="G57" s="139"/>
-      <c r="H57" s="139"/>
-      <c r="I57" s="139"/>
-      <c r="J57" s="139"/>
-      <c r="K57" s="139"/>
-      <c r="L57" s="139"/>
+      <c r="D57" s="175"/>
+      <c r="E57" s="81"/>
+      <c r="F57" s="81"/>
+      <c r="G57" s="81"/>
+      <c r="H57" s="81"/>
+      <c r="I57" s="81"/>
+      <c r="J57" s="81"/>
+      <c r="K57" s="81"/>
+      <c r="L57" s="81"/>
     </row>
     <row r="58" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="72">
@@ -12856,15 +12941,15 @@
         <v>148</v>
       </c>
       <c r="C58" s="78"/>
-      <c r="D58" s="139"/>
-      <c r="E58" s="139"/>
-      <c r="F58" s="139"/>
-      <c r="G58" s="139"/>
-      <c r="H58" s="139"/>
-      <c r="I58" s="139"/>
-      <c r="J58" s="139"/>
-      <c r="K58" s="139"/>
-      <c r="L58" s="139"/>
+      <c r="D58" s="175"/>
+      <c r="E58" s="81"/>
+      <c r="F58" s="81"/>
+      <c r="G58" s="81"/>
+      <c r="H58" s="81"/>
+      <c r="I58" s="81"/>
+      <c r="J58" s="81"/>
+      <c r="K58" s="81"/>
+      <c r="L58" s="81"/>
     </row>
     <row r="59" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="72">
@@ -12874,15 +12959,15 @@
         <v>149</v>
       </c>
       <c r="C59" s="78"/>
-      <c r="D59" s="139"/>
-      <c r="E59" s="139"/>
-      <c r="F59" s="139"/>
-      <c r="G59" s="139"/>
-      <c r="H59" s="139"/>
-      <c r="I59" s="139"/>
-      <c r="J59" s="139"/>
-      <c r="K59" s="139"/>
-      <c r="L59" s="139"/>
+      <c r="D59" s="175"/>
+      <c r="E59" s="81"/>
+      <c r="F59" s="81"/>
+      <c r="G59" s="81"/>
+      <c r="H59" s="81"/>
+      <c r="I59" s="81"/>
+      <c r="J59" s="81"/>
+      <c r="K59" s="81"/>
+      <c r="L59" s="81"/>
     </row>
     <row r="60" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="72">
@@ -12892,15 +12977,15 @@
         <v>150</v>
       </c>
       <c r="C60" s="78"/>
-      <c r="D60" s="139"/>
-      <c r="E60" s="139"/>
-      <c r="F60" s="139"/>
-      <c r="G60" s="139"/>
-      <c r="H60" s="139"/>
-      <c r="I60" s="139"/>
-      <c r="J60" s="139"/>
-      <c r="K60" s="139"/>
-      <c r="L60" s="139"/>
+      <c r="D60" s="175"/>
+      <c r="E60" s="81"/>
+      <c r="F60" s="81"/>
+      <c r="G60" s="81"/>
+      <c r="H60" s="81"/>
+      <c r="I60" s="81"/>
+      <c r="J60" s="81"/>
+      <c r="K60" s="81"/>
+      <c r="L60" s="81"/>
     </row>
     <row r="61" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="72">
@@ -12910,15 +12995,15 @@
         <v>153</v>
       </c>
       <c r="C61" s="78"/>
-      <c r="D61" s="139"/>
-      <c r="E61" s="139"/>
-      <c r="F61" s="139"/>
-      <c r="G61" s="139"/>
-      <c r="H61" s="139"/>
-      <c r="I61" s="139"/>
-      <c r="J61" s="139"/>
-      <c r="K61" s="139"/>
-      <c r="L61" s="139"/>
+      <c r="D61" s="175"/>
+      <c r="E61" s="81"/>
+      <c r="F61" s="81"/>
+      <c r="G61" s="81"/>
+      <c r="H61" s="81"/>
+      <c r="I61" s="81"/>
+      <c r="J61" s="81"/>
+      <c r="K61" s="81"/>
+      <c r="L61" s="81"/>
     </row>
     <row r="62" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="72">
@@ -12928,15 +13013,15 @@
         <v>154</v>
       </c>
       <c r="C62" s="78"/>
-      <c r="D62" s="139"/>
-      <c r="E62" s="139"/>
-      <c r="F62" s="139"/>
-      <c r="G62" s="139"/>
-      <c r="H62" s="139"/>
-      <c r="I62" s="139"/>
-      <c r="J62" s="139"/>
-      <c r="K62" s="139"/>
-      <c r="L62" s="139"/>
+      <c r="D62" s="175"/>
+      <c r="E62" s="81"/>
+      <c r="F62" s="81"/>
+      <c r="G62" s="81"/>
+      <c r="H62" s="81"/>
+      <c r="I62" s="81"/>
+      <c r="J62" s="81"/>
+      <c r="K62" s="81"/>
+      <c r="L62" s="81"/>
     </row>
     <row r="63" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="72">
@@ -12946,15 +13031,15 @@
         <v>151</v>
       </c>
       <c r="C63" s="78"/>
-      <c r="D63" s="139"/>
-      <c r="E63" s="139"/>
-      <c r="F63" s="139"/>
-      <c r="G63" s="139"/>
-      <c r="H63" s="139"/>
-      <c r="I63" s="139"/>
-      <c r="J63" s="139"/>
-      <c r="K63" s="139"/>
-      <c r="L63" s="139"/>
+      <c r="D63" s="175"/>
+      <c r="E63" s="81"/>
+      <c r="F63" s="81"/>
+      <c r="G63" s="81"/>
+      <c r="H63" s="81"/>
+      <c r="I63" s="81"/>
+      <c r="J63" s="81"/>
+      <c r="K63" s="81"/>
+      <c r="L63" s="81"/>
     </row>
     <row r="64" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="72">
@@ -12964,26 +13049,36 @@
         <v>152</v>
       </c>
       <c r="C64" s="78"/>
-      <c r="D64" s="139"/>
-      <c r="E64" s="139"/>
-      <c r="F64" s="139"/>
-      <c r="G64" s="139"/>
-      <c r="H64" s="139"/>
-      <c r="I64" s="139"/>
-      <c r="J64" s="139"/>
-      <c r="K64" s="139"/>
-      <c r="L64" s="139"/>
+      <c r="D64" s="175"/>
+      <c r="E64" s="81"/>
+      <c r="F64" s="81"/>
+      <c r="G64" s="81"/>
+      <c r="H64" s="81"/>
+      <c r="I64" s="81"/>
+      <c r="J64" s="81"/>
+      <c r="K64" s="81"/>
+      <c r="L64" s="81"/>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A65" s="173">
+        <v>40</v>
+      </c>
+      <c r="B65" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="C65" s="78"/>
+      <c r="D65" s="175"/>
+      <c r="E65" s="81"/>
+      <c r="F65" s="81"/>
+      <c r="G65" s="81"/>
+      <c r="H65" s="81"/>
+      <c r="I65" s="81"/>
+      <c r="J65" s="81"/>
+      <c r="K65" s="81"/>
+      <c r="L65" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="D26:L64"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:L20"/>
-    <mergeCell ref="D25:L25"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:L22"/>
     <mergeCell ref="A16:L16"/>
     <mergeCell ref="A17:L17"/>
     <mergeCell ref="B15:L15"/>
@@ -12995,6 +13090,14 @@
     <mergeCell ref="B4:L4"/>
     <mergeCell ref="B5:L5"/>
     <mergeCell ref="B7:L7"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:L20"/>
+    <mergeCell ref="D25:L25"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:L22"/>
+    <mergeCell ref="D26:L65"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D26" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -16168,6 +16271,28 @@
                     <xdr:colOff>1409700</xdr:colOff>
                     <xdr:row>63</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1247" r:id="rId149" name="Drop Down 223">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>64</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>1409700</xdr:colOff>
+                    <xdr:row>65</xdr:row>
+                    <xdr:rowOff>38100</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -16400,17 +16525,17 @@
       <c r="C12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="122" t="s">
+      <c r="D12" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="122"/>
-      <c r="F12" s="122"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="122"/>
-      <c r="J12" s="122"/>
-      <c r="K12" s="122"/>
-      <c r="L12" s="122"/>
+      <c r="E12" s="90"/>
+      <c r="F12" s="90"/>
+      <c r="G12" s="90"/>
+      <c r="H12" s="90"/>
+      <c r="I12" s="90"/>
+      <c r="J12" s="90"/>
+      <c r="K12" s="90"/>
+      <c r="L12" s="90"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="49"/>
@@ -17327,59 +17452,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50">
-      <UserInfo>
-        <DisplayName>Luis Campos / Logiztik Alliance</DisplayName>
-        <AccountId>265</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Jairo Gonzalez / Logiztik Alliance</DisplayName>
-        <AccountId>322</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>José Ganchozo / Logiztik Alliance</DisplayName>
-        <AccountId>304</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Edwin Casa / Logiztik Alliance</DisplayName>
-        <AccountId>299</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Cristhian Cuichan / Logiztik Alliance</DisplayName>
-        <AccountId>369</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Oscar Yunda /  Logiztik Alliance</DisplayName>
-        <AccountId>355</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Fernando Ordoñez / Logiztik Alliance</DisplayName>
-        <AccountId>321</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Alex Rivera / Logiztik Alliance</DisplayName>
-        <AccountId>370</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <TaxCatchAll xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="87481c51-c14c-4071-bf64-faa2b5708bb6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101005DA7AC6E4F4FAE42B9D9FCD9C82CAAE1" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="553e0bb76796fbad2df2b84fb95dc83d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="87481c51-c14c-4071-bf64-faa2b5708bb6" xmlns:ns3="8029d101-3d2a-47c4-b15f-619642bf5e50" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d87cd7f238c73dc12c577d08dde48736" ns2:_="" ns3:_="">
     <xsd:import namespace="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
@@ -17628,6 +17700,59 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50">
+      <UserInfo>
+        <DisplayName>Luis Campos / Logiztik Alliance</DisplayName>
+        <AccountId>265</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Jairo Gonzalez / Logiztik Alliance</DisplayName>
+        <AccountId>322</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>José Ganchozo / Logiztik Alliance</DisplayName>
+        <AccountId>304</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Edwin Casa / Logiztik Alliance</DisplayName>
+        <AccountId>299</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Cristhian Cuichan / Logiztik Alliance</DisplayName>
+        <AccountId>369</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Oscar Yunda /  Logiztik Alliance</DisplayName>
+        <AccountId>355</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Fernando Ordoñez / Logiztik Alliance</DisplayName>
+        <AccountId>321</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Alex Rivera / Logiztik Alliance</DisplayName>
+        <AccountId>370</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <TaxCatchAll xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="87481c51-c14c-4071-bf64-faa2b5708bb6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371D8832-41B3-447B-B13D-2663C267E34F}">
   <ds:schemaRefs>
@@ -17637,17 +17762,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD069904-634F-48DA-AA92-BAE250498BEE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8029d101-3d2a-47c4-b15f-619642bf5e50"/>
-    <ds:schemaRef ds:uri="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F7F06D0-41B3-4EAF-B418-88FC726117CC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17664,4 +17778,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD069904-634F-48DA-AA92-BAE250498BEE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8029d101-3d2a-47c4-b15f-619642bf5e50"/>
+    <ds:schemaRef ds:uri="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Guias Produccion/HU-57723.xlsx
+++ b/Guias Produccion/HU-57723.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Alliance\ScriptsEntidades\Guias Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{731E405A-CE5E-415D-AE23-E5CD0DBDA9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2562A79-56CB-479F-A8EE-E024C97D8DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2004,83 +2004,8 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="75" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="76" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="77" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2184,6 +2109,90 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="54" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2282,15 +2291,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="54" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -11275,7 +11275,7 @@
                   <a14:compatExt spid="_x0000_s1247"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{267A547B-07F1-0730-BD33-E8E5A53B68A8}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000DF040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -11920,42 +11920,42 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:15" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="122" t="s">
+      <c r="A3" s="97" t="s">
         <v>103</v>
       </c>
-      <c r="B3" s="123"/>
-      <c r="C3" s="123"/>
-      <c r="D3" s="123"/>
-      <c r="E3" s="123"/>
-      <c r="F3" s="123"/>
-      <c r="G3" s="123"/>
-      <c r="H3" s="123"/>
-      <c r="I3" s="123"/>
-      <c r="J3" s="123"/>
-      <c r="K3" s="123"/>
-      <c r="L3" s="124"/>
-      <c r="N3" s="116" t="s">
+      <c r="B3" s="98"/>
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="98"/>
+      <c r="J3" s="98"/>
+      <c r="K3" s="98"/>
+      <c r="L3" s="99"/>
+      <c r="N3" s="91" t="s">
         <v>0</v>
       </c>
-      <c r="O3" s="117"/>
+      <c r="O3" s="92"/>
     </row>
     <row r="4" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="129" t="s">
+      <c r="B4" s="104" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="130"/>
-      <c r="D4" s="130"/>
-      <c r="E4" s="130"/>
-      <c r="F4" s="130"/>
-      <c r="G4" s="130"/>
-      <c r="H4" s="130"/>
-      <c r="I4" s="130"/>
-      <c r="J4" s="131"/>
-      <c r="K4" s="131"/>
-      <c r="L4" s="132"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="105"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="105"/>
+      <c r="I4" s="105"/>
+      <c r="J4" s="106"/>
+      <c r="K4" s="106"/>
+      <c r="L4" s="107"/>
       <c r="N4" s="21" t="s">
         <v>2</v>
       </c>
@@ -11965,19 +11965,19 @@
       <c r="A5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="133" t="s">
+      <c r="B5" s="108" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="133"/>
-      <c r="D5" s="133"/>
-      <c r="E5" s="133"/>
-      <c r="F5" s="133"/>
-      <c r="G5" s="133"/>
-      <c r="H5" s="133"/>
-      <c r="I5" s="133"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="135"/>
+      <c r="C5" s="108"/>
+      <c r="D5" s="108"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="108"/>
+      <c r="G5" s="108"/>
+      <c r="H5" s="108"/>
+      <c r="I5" s="108"/>
+      <c r="J5" s="109"/>
+      <c r="K5" s="109"/>
+      <c r="L5" s="110"/>
       <c r="N5" s="15" t="s">
         <v>4</v>
       </c>
@@ -11987,19 +11987,19 @@
       <c r="A6" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="119">
+      <c r="B6" s="94">
         <v>46073</v>
       </c>
-      <c r="C6" s="120"/>
-      <c r="D6" s="120"/>
-      <c r="E6" s="120"/>
-      <c r="F6" s="120"/>
-      <c r="G6" s="120"/>
-      <c r="H6" s="120"/>
-      <c r="I6" s="120"/>
-      <c r="J6" s="120"/>
-      <c r="K6" s="120"/>
-      <c r="L6" s="121"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="95"/>
+      <c r="K6" s="95"/>
+      <c r="L6" s="96"/>
       <c r="N6" s="14"/>
       <c r="O6" s="14"/>
     </row>
@@ -12007,17 +12007,17 @@
       <c r="A7" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="136"/>
-      <c r="C7" s="137"/>
-      <c r="D7" s="137"/>
-      <c r="E7" s="137"/>
-      <c r="F7" s="137"/>
-      <c r="G7" s="137"/>
-      <c r="H7" s="137"/>
-      <c r="I7" s="137"/>
-      <c r="J7" s="138"/>
-      <c r="K7" s="138"/>
-      <c r="L7" s="139"/>
+      <c r="B7" s="111"/>
+      <c r="C7" s="112"/>
+      <c r="D7" s="112"/>
+      <c r="E7" s="112"/>
+      <c r="F7" s="112"/>
+      <c r="G7" s="112"/>
+      <c r="H7" s="112"/>
+      <c r="I7" s="112"/>
+      <c r="J7" s="113"/>
+      <c r="K7" s="113"/>
+      <c r="L7" s="114"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
@@ -12034,20 +12034,20 @@
       <c r="L8" s="13"/>
     </row>
     <row r="9" spans="1:15" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="125" t="s">
+      <c r="A9" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="126"/>
-      <c r="C9" s="126"/>
-      <c r="D9" s="126"/>
-      <c r="E9" s="126"/>
-      <c r="F9" s="126"/>
-      <c r="G9" s="126"/>
-      <c r="H9" s="126"/>
-      <c r="I9" s="126"/>
-      <c r="J9" s="127"/>
-      <c r="K9" s="127"/>
-      <c r="L9" s="128"/>
+      <c r="B9" s="101"/>
+      <c r="C9" s="101"/>
+      <c r="D9" s="101"/>
+      <c r="E9" s="101"/>
+      <c r="F9" s="101"/>
+      <c r="G9" s="101"/>
+      <c r="H9" s="101"/>
+      <c r="I9" s="101"/>
+      <c r="J9" s="102"/>
+      <c r="K9" s="102"/>
+      <c r="L9" s="103"/>
     </row>
     <row r="10" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -12147,63 +12147,63 @@
       <c r="A14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="118"/>
-      <c r="C14" s="114"/>
-      <c r="D14" s="114"/>
-      <c r="E14" s="114"/>
-      <c r="F14" s="114"/>
-      <c r="G14" s="114"/>
-      <c r="H14" s="114"/>
-      <c r="I14" s="114"/>
-      <c r="J14" s="114"/>
-      <c r="K14" s="114"/>
-      <c r="L14" s="115"/>
+      <c r="B14" s="93"/>
+      <c r="C14" s="89"/>
+      <c r="D14" s="89"/>
+      <c r="E14" s="89"/>
+      <c r="F14" s="89"/>
+      <c r="G14" s="89"/>
+      <c r="H14" s="89"/>
+      <c r="I14" s="89"/>
+      <c r="J14" s="89"/>
+      <c r="K14" s="89"/>
+      <c r="L14" s="90"/>
     </row>
     <row r="15" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="113"/>
-      <c r="C15" s="114"/>
-      <c r="D15" s="114"/>
-      <c r="E15" s="114"/>
-      <c r="F15" s="114"/>
-      <c r="G15" s="114"/>
-      <c r="H15" s="114"/>
-      <c r="I15" s="114"/>
-      <c r="J15" s="114"/>
-      <c r="K15" s="114"/>
-      <c r="L15" s="115"/>
+      <c r="B15" s="88"/>
+      <c r="C15" s="89"/>
+      <c r="D15" s="89"/>
+      <c r="E15" s="89"/>
+      <c r="F15" s="89"/>
+      <c r="G15" s="89"/>
+      <c r="H15" s="89"/>
+      <c r="I15" s="89"/>
+      <c r="J15" s="89"/>
+      <c r="K15" s="89"/>
+      <c r="L15" s="90"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="106"/>
-      <c r="B16" s="107"/>
-      <c r="C16" s="107"/>
-      <c r="D16" s="107"/>
-      <c r="E16" s="107"/>
-      <c r="F16" s="107"/>
-      <c r="G16" s="107"/>
-      <c r="H16" s="107"/>
-      <c r="I16" s="107"/>
-      <c r="J16" s="107"/>
-      <c r="K16" s="107"/>
-      <c r="L16" s="108"/>
+      <c r="A16" s="81"/>
+      <c r="B16" s="82"/>
+      <c r="C16" s="82"/>
+      <c r="D16" s="82"/>
+      <c r="E16" s="82"/>
+      <c r="F16" s="82"/>
+      <c r="G16" s="82"/>
+      <c r="H16" s="82"/>
+      <c r="I16" s="82"/>
+      <c r="J16" s="82"/>
+      <c r="K16" s="82"/>
+      <c r="L16" s="83"/>
     </row>
     <row r="17" spans="1:12" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="109" t="s">
+      <c r="A17" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="110"/>
-      <c r="C17" s="110"/>
-      <c r="D17" s="110"/>
-      <c r="E17" s="110"/>
-      <c r="F17" s="110"/>
-      <c r="G17" s="110"/>
-      <c r="H17" s="110"/>
-      <c r="I17" s="110"/>
-      <c r="J17" s="111"/>
-      <c r="K17" s="111"/>
-      <c r="L17" s="112"/>
+      <c r="B17" s="85"/>
+      <c r="C17" s="85"/>
+      <c r="D17" s="85"/>
+      <c r="E17" s="85"/>
+      <c r="F17" s="85"/>
+      <c r="G17" s="85"/>
+      <c r="H17" s="85"/>
+      <c r="I17" s="85"/>
+      <c r="J17" s="86"/>
+      <c r="K17" s="86"/>
+      <c r="L17" s="87"/>
     </row>
     <row r="18" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
@@ -12213,19 +12213,19 @@
       <c r="C18" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="82" t="s">
+      <c r="D18" s="115" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="84" t="s">
+      <c r="E18" s="117" t="s">
         <v>115</v>
       </c>
-      <c r="F18" s="84"/>
-      <c r="G18" s="84"/>
-      <c r="H18" s="84"/>
-      <c r="I18" s="84"/>
-      <c r="J18" s="85"/>
-      <c r="K18" s="85"/>
-      <c r="L18" s="86"/>
+      <c r="F18" s="117"/>
+      <c r="G18" s="117"/>
+      <c r="H18" s="117"/>
+      <c r="I18" s="117"/>
+      <c r="J18" s="118"/>
+      <c r="K18" s="118"/>
+      <c r="L18" s="119"/>
     </row>
     <row r="19" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
@@ -12235,15 +12235,15 @@
         <v>30</v>
       </c>
       <c r="C19" s="44"/>
-      <c r="D19" s="83"/>
-      <c r="E19" s="87"/>
-      <c r="F19" s="87"/>
-      <c r="G19" s="87"/>
-      <c r="H19" s="87"/>
-      <c r="I19" s="87"/>
-      <c r="J19" s="88"/>
-      <c r="K19" s="88"/>
-      <c r="L19" s="89"/>
+      <c r="D19" s="116"/>
+      <c r="E19" s="120"/>
+      <c r="F19" s="120"/>
+      <c r="G19" s="120"/>
+      <c r="H19" s="120"/>
+      <c r="I19" s="120"/>
+      <c r="J19" s="121"/>
+      <c r="K19" s="121"/>
+      <c r="L19" s="122"/>
     </row>
     <row r="20" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
@@ -12253,15 +12253,15 @@
       <c r="C20" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="83"/>
-      <c r="E20" s="87"/>
-      <c r="F20" s="87"/>
-      <c r="G20" s="87"/>
-      <c r="H20" s="87"/>
-      <c r="I20" s="87"/>
-      <c r="J20" s="88"/>
-      <c r="K20" s="88"/>
-      <c r="L20" s="89"/>
+      <c r="D20" s="116"/>
+      <c r="E20" s="120"/>
+      <c r="F20" s="120"/>
+      <c r="G20" s="120"/>
+      <c r="H20" s="120"/>
+      <c r="I20" s="120"/>
+      <c r="J20" s="121"/>
+      <c r="K20" s="121"/>
+      <c r="L20" s="122"/>
     </row>
     <row r="21" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
@@ -12271,19 +12271,19 @@
       <c r="C21" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="98" t="s">
+      <c r="D21" s="131" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="100" t="s">
+      <c r="E21" s="133" t="s">
         <v>107</v>
       </c>
-      <c r="F21" s="101"/>
-      <c r="G21" s="101"/>
-      <c r="H21" s="101"/>
-      <c r="I21" s="101"/>
-      <c r="J21" s="101"/>
-      <c r="K21" s="101"/>
-      <c r="L21" s="102"/>
+      <c r="F21" s="134"/>
+      <c r="G21" s="134"/>
+      <c r="H21" s="134"/>
+      <c r="I21" s="134"/>
+      <c r="J21" s="134"/>
+      <c r="K21" s="134"/>
+      <c r="L21" s="135"/>
     </row>
     <row r="22" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
@@ -12293,45 +12293,45 @@
       <c r="C22" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="99"/>
-      <c r="E22" s="103"/>
-      <c r="F22" s="104"/>
-      <c r="G22" s="104"/>
-      <c r="H22" s="104"/>
-      <c r="I22" s="104"/>
-      <c r="J22" s="104"/>
-      <c r="K22" s="104"/>
-      <c r="L22" s="105"/>
+      <c r="D22" s="132"/>
+      <c r="E22" s="136"/>
+      <c r="F22" s="137"/>
+      <c r="G22" s="137"/>
+      <c r="H22" s="137"/>
+      <c r="I22" s="137"/>
+      <c r="J22" s="137"/>
+      <c r="K22" s="137"/>
+      <c r="L22" s="138"/>
     </row>
     <row r="23" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="91"/>
-      <c r="B23" s="92"/>
-      <c r="C23" s="92"/>
-      <c r="D23" s="93"/>
-      <c r="E23" s="93"/>
-      <c r="F23" s="93"/>
-      <c r="G23" s="93"/>
-      <c r="H23" s="93"/>
-      <c r="I23" s="93"/>
-      <c r="J23" s="93"/>
-      <c r="K23" s="93"/>
-      <c r="L23" s="94"/>
+      <c r="A23" s="124"/>
+      <c r="B23" s="125"/>
+      <c r="C23" s="125"/>
+      <c r="D23" s="126"/>
+      <c r="E23" s="126"/>
+      <c r="F23" s="126"/>
+      <c r="G23" s="126"/>
+      <c r="H23" s="126"/>
+      <c r="I23" s="126"/>
+      <c r="J23" s="126"/>
+      <c r="K23" s="126"/>
+      <c r="L23" s="127"/>
     </row>
     <row r="24" spans="1:12" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="95" t="s">
+      <c r="A24" s="128" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="96"/>
-      <c r="C24" s="96"/>
-      <c r="D24" s="96"/>
-      <c r="E24" s="96"/>
-      <c r="F24" s="96"/>
-      <c r="G24" s="96"/>
-      <c r="H24" s="96"/>
-      <c r="I24" s="96"/>
-      <c r="J24" s="96"/>
-      <c r="K24" s="96"/>
-      <c r="L24" s="97"/>
+      <c r="B24" s="129"/>
+      <c r="C24" s="129"/>
+      <c r="D24" s="129"/>
+      <c r="E24" s="129"/>
+      <c r="F24" s="129"/>
+      <c r="G24" s="129"/>
+      <c r="H24" s="129"/>
+      <c r="I24" s="129"/>
+      <c r="J24" s="129"/>
+      <c r="K24" s="129"/>
+      <c r="L24" s="130"/>
     </row>
     <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
@@ -12343,17 +12343,17 @@
       <c r="C25" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="90" t="s">
+      <c r="D25" s="123" t="s">
         <v>38</v>
       </c>
-      <c r="E25" s="90"/>
-      <c r="F25" s="90"/>
-      <c r="G25" s="90"/>
-      <c r="H25" s="90"/>
-      <c r="I25" s="90"/>
-      <c r="J25" s="90"/>
-      <c r="K25" s="90"/>
-      <c r="L25" s="90"/>
+      <c r="E25" s="123"/>
+      <c r="F25" s="123"/>
+      <c r="G25" s="123"/>
+      <c r="H25" s="123"/>
+      <c r="I25" s="123"/>
+      <c r="J25" s="123"/>
+      <c r="K25" s="123"/>
+      <c r="L25" s="123"/>
     </row>
     <row r="26" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="33">
@@ -12363,17 +12363,17 @@
         <v>116</v>
       </c>
       <c r="C26" s="34"/>
-      <c r="D26" s="174" t="s">
+      <c r="D26" s="139" t="s">
         <v>108</v>
       </c>
-      <c r="E26" s="80"/>
-      <c r="F26" s="80"/>
-      <c r="G26" s="80"/>
-      <c r="H26" s="80"/>
-      <c r="I26" s="80"/>
-      <c r="J26" s="80"/>
-      <c r="K26" s="80"/>
-      <c r="L26" s="80"/>
+      <c r="E26" s="140"/>
+      <c r="F26" s="140"/>
+      <c r="G26" s="140"/>
+      <c r="H26" s="140"/>
+      <c r="I26" s="140"/>
+      <c r="J26" s="140"/>
+      <c r="K26" s="140"/>
+      <c r="L26" s="140"/>
     </row>
     <row r="27" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
@@ -12383,15 +12383,15 @@
         <v>117</v>
       </c>
       <c r="C27" s="34"/>
-      <c r="D27" s="175"/>
-      <c r="E27" s="81"/>
-      <c r="F27" s="81"/>
-      <c r="G27" s="81"/>
-      <c r="H27" s="81"/>
-      <c r="I27" s="81"/>
-      <c r="J27" s="81"/>
-      <c r="K27" s="81"/>
-      <c r="L27" s="81"/>
+      <c r="D27" s="141"/>
+      <c r="E27" s="142"/>
+      <c r="F27" s="142"/>
+      <c r="G27" s="142"/>
+      <c r="H27" s="142"/>
+      <c r="I27" s="142"/>
+      <c r="J27" s="142"/>
+      <c r="K27" s="142"/>
+      <c r="L27" s="142"/>
     </row>
     <row r="28" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="33">
@@ -12401,15 +12401,15 @@
         <v>118</v>
       </c>
       <c r="C28" s="34"/>
-      <c r="D28" s="175"/>
-      <c r="E28" s="81"/>
-      <c r="F28" s="81"/>
-      <c r="G28" s="81"/>
-      <c r="H28" s="81"/>
-      <c r="I28" s="81"/>
-      <c r="J28" s="81"/>
-      <c r="K28" s="81"/>
-      <c r="L28" s="81"/>
+      <c r="D28" s="141"/>
+      <c r="E28" s="142"/>
+      <c r="F28" s="142"/>
+      <c r="G28" s="142"/>
+      <c r="H28" s="142"/>
+      <c r="I28" s="142"/>
+      <c r="J28" s="142"/>
+      <c r="K28" s="142"/>
+      <c r="L28" s="142"/>
     </row>
     <row r="29" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
@@ -12419,15 +12419,15 @@
         <v>119</v>
       </c>
       <c r="C29" s="34"/>
-      <c r="D29" s="175"/>
-      <c r="E29" s="81"/>
-      <c r="F29" s="81"/>
-      <c r="G29" s="81"/>
-      <c r="H29" s="81"/>
-      <c r="I29" s="81"/>
-      <c r="J29" s="81"/>
-      <c r="K29" s="81"/>
-      <c r="L29" s="81"/>
+      <c r="D29" s="141"/>
+      <c r="E29" s="142"/>
+      <c r="F29" s="142"/>
+      <c r="G29" s="142"/>
+      <c r="H29" s="142"/>
+      <c r="I29" s="142"/>
+      <c r="J29" s="142"/>
+      <c r="K29" s="142"/>
+      <c r="L29" s="142"/>
     </row>
     <row r="30" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="33">
@@ -12437,15 +12437,15 @@
         <v>120</v>
       </c>
       <c r="C30" s="34"/>
-      <c r="D30" s="175"/>
-      <c r="E30" s="81"/>
-      <c r="F30" s="81"/>
-      <c r="G30" s="81"/>
-      <c r="H30" s="81"/>
-      <c r="I30" s="81"/>
-      <c r="J30" s="81"/>
-      <c r="K30" s="81"/>
-      <c r="L30" s="81"/>
+      <c r="D30" s="141"/>
+      <c r="E30" s="142"/>
+      <c r="F30" s="142"/>
+      <c r="G30" s="142"/>
+      <c r="H30" s="142"/>
+      <c r="I30" s="142"/>
+      <c r="J30" s="142"/>
+      <c r="K30" s="142"/>
+      <c r="L30" s="142"/>
     </row>
     <row r="31" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="33">
@@ -12455,15 +12455,15 @@
         <v>121</v>
       </c>
       <c r="C31" s="34"/>
-      <c r="D31" s="175"/>
-      <c r="E31" s="81"/>
-      <c r="F31" s="81"/>
-      <c r="G31" s="81"/>
-      <c r="H31" s="81"/>
-      <c r="I31" s="81"/>
-      <c r="J31" s="81"/>
-      <c r="K31" s="81"/>
-      <c r="L31" s="81"/>
+      <c r="D31" s="141"/>
+      <c r="E31" s="142"/>
+      <c r="F31" s="142"/>
+      <c r="G31" s="142"/>
+      <c r="H31" s="142"/>
+      <c r="I31" s="142"/>
+      <c r="J31" s="142"/>
+      <c r="K31" s="142"/>
+      <c r="L31" s="142"/>
     </row>
     <row r="32" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="33">
@@ -12473,15 +12473,15 @@
         <v>122</v>
       </c>
       <c r="C32" s="34"/>
-      <c r="D32" s="175"/>
-      <c r="E32" s="81"/>
-      <c r="F32" s="81"/>
-      <c r="G32" s="81"/>
-      <c r="H32" s="81"/>
-      <c r="I32" s="81"/>
-      <c r="J32" s="81"/>
-      <c r="K32" s="81"/>
-      <c r="L32" s="81"/>
+      <c r="D32" s="141"/>
+      <c r="E32" s="142"/>
+      <c r="F32" s="142"/>
+      <c r="G32" s="142"/>
+      <c r="H32" s="142"/>
+      <c r="I32" s="142"/>
+      <c r="J32" s="142"/>
+      <c r="K32" s="142"/>
+      <c r="L32" s="142"/>
     </row>
     <row r="33" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="33">
@@ -12491,15 +12491,15 @@
         <v>123</v>
       </c>
       <c r="C33" s="34"/>
-      <c r="D33" s="175"/>
-      <c r="E33" s="81"/>
-      <c r="F33" s="81"/>
-      <c r="G33" s="81"/>
-      <c r="H33" s="81"/>
-      <c r="I33" s="81"/>
-      <c r="J33" s="81"/>
-      <c r="K33" s="81"/>
-      <c r="L33" s="81"/>
+      <c r="D33" s="141"/>
+      <c r="E33" s="142"/>
+      <c r="F33" s="142"/>
+      <c r="G33" s="142"/>
+      <c r="H33" s="142"/>
+      <c r="I33" s="142"/>
+      <c r="J33" s="142"/>
+      <c r="K33" s="142"/>
+      <c r="L33" s="142"/>
     </row>
     <row r="34" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="33">
@@ -12509,15 +12509,15 @@
         <v>124</v>
       </c>
       <c r="C34" s="34"/>
-      <c r="D34" s="175"/>
-      <c r="E34" s="81"/>
-      <c r="F34" s="81"/>
-      <c r="G34" s="81"/>
-      <c r="H34" s="81"/>
-      <c r="I34" s="81"/>
-      <c r="J34" s="81"/>
-      <c r="K34" s="81"/>
-      <c r="L34" s="81"/>
+      <c r="D34" s="141"/>
+      <c r="E34" s="142"/>
+      <c r="F34" s="142"/>
+      <c r="G34" s="142"/>
+      <c r="H34" s="142"/>
+      <c r="I34" s="142"/>
+      <c r="J34" s="142"/>
+      <c r="K34" s="142"/>
+      <c r="L34" s="142"/>
     </row>
     <row r="35" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="33">
@@ -12527,15 +12527,15 @@
         <v>125</v>
       </c>
       <c r="C35" s="34"/>
-      <c r="D35" s="175"/>
-      <c r="E35" s="81"/>
-      <c r="F35" s="81"/>
-      <c r="G35" s="81"/>
-      <c r="H35" s="81"/>
-      <c r="I35" s="81"/>
-      <c r="J35" s="81"/>
-      <c r="K35" s="81"/>
-      <c r="L35" s="81"/>
+      <c r="D35" s="141"/>
+      <c r="E35" s="142"/>
+      <c r="F35" s="142"/>
+      <c r="G35" s="142"/>
+      <c r="H35" s="142"/>
+      <c r="I35" s="142"/>
+      <c r="J35" s="142"/>
+      <c r="K35" s="142"/>
+      <c r="L35" s="142"/>
     </row>
     <row r="36" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="33">
@@ -12545,15 +12545,15 @@
         <v>126</v>
       </c>
       <c r="C36" s="34"/>
-      <c r="D36" s="175"/>
-      <c r="E36" s="81"/>
-      <c r="F36" s="81"/>
-      <c r="G36" s="81"/>
-      <c r="H36" s="81"/>
-      <c r="I36" s="81"/>
-      <c r="J36" s="81"/>
-      <c r="K36" s="81"/>
-      <c r="L36" s="81"/>
+      <c r="D36" s="141"/>
+      <c r="E36" s="142"/>
+      <c r="F36" s="142"/>
+      <c r="G36" s="142"/>
+      <c r="H36" s="142"/>
+      <c r="I36" s="142"/>
+      <c r="J36" s="142"/>
+      <c r="K36" s="142"/>
+      <c r="L36" s="142"/>
     </row>
     <row r="37" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="33">
@@ -12563,15 +12563,15 @@
         <v>127</v>
       </c>
       <c r="C37" s="34"/>
-      <c r="D37" s="175"/>
-      <c r="E37" s="81"/>
-      <c r="F37" s="81"/>
-      <c r="G37" s="81"/>
-      <c r="H37" s="81"/>
-      <c r="I37" s="81"/>
-      <c r="J37" s="81"/>
-      <c r="K37" s="81"/>
-      <c r="L37" s="81"/>
+      <c r="D37" s="141"/>
+      <c r="E37" s="142"/>
+      <c r="F37" s="142"/>
+      <c r="G37" s="142"/>
+      <c r="H37" s="142"/>
+      <c r="I37" s="142"/>
+      <c r="J37" s="142"/>
+      <c r="K37" s="142"/>
+      <c r="L37" s="142"/>
     </row>
     <row r="38" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="33">
@@ -12581,15 +12581,15 @@
         <v>128</v>
       </c>
       <c r="C38" s="34"/>
-      <c r="D38" s="175"/>
-      <c r="E38" s="81"/>
-      <c r="F38" s="81"/>
-      <c r="G38" s="81"/>
-      <c r="H38" s="81"/>
-      <c r="I38" s="81"/>
-      <c r="J38" s="81"/>
-      <c r="K38" s="81"/>
-      <c r="L38" s="81"/>
+      <c r="D38" s="141"/>
+      <c r="E38" s="142"/>
+      <c r="F38" s="142"/>
+      <c r="G38" s="142"/>
+      <c r="H38" s="142"/>
+      <c r="I38" s="142"/>
+      <c r="J38" s="142"/>
+      <c r="K38" s="142"/>
+      <c r="L38" s="142"/>
     </row>
     <row r="39" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="33">
@@ -12599,15 +12599,15 @@
         <v>129</v>
       </c>
       <c r="C39" s="34"/>
-      <c r="D39" s="175"/>
-      <c r="E39" s="81"/>
-      <c r="F39" s="81"/>
-      <c r="G39" s="81"/>
-      <c r="H39" s="81"/>
-      <c r="I39" s="81"/>
-      <c r="J39" s="81"/>
-      <c r="K39" s="81"/>
-      <c r="L39" s="81"/>
+      <c r="D39" s="141"/>
+      <c r="E39" s="142"/>
+      <c r="F39" s="142"/>
+      <c r="G39" s="142"/>
+      <c r="H39" s="142"/>
+      <c r="I39" s="142"/>
+      <c r="J39" s="142"/>
+      <c r="K39" s="142"/>
+      <c r="L39" s="142"/>
     </row>
     <row r="40" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="33">
@@ -12617,15 +12617,15 @@
         <v>130</v>
       </c>
       <c r="C40" s="34"/>
-      <c r="D40" s="175"/>
-      <c r="E40" s="81"/>
-      <c r="F40" s="81"/>
-      <c r="G40" s="81"/>
-      <c r="H40" s="81"/>
-      <c r="I40" s="81"/>
-      <c r="J40" s="81"/>
-      <c r="K40" s="81"/>
-      <c r="L40" s="81"/>
+      <c r="D40" s="141"/>
+      <c r="E40" s="142"/>
+      <c r="F40" s="142"/>
+      <c r="G40" s="142"/>
+      <c r="H40" s="142"/>
+      <c r="I40" s="142"/>
+      <c r="J40" s="142"/>
+      <c r="K40" s="142"/>
+      <c r="L40" s="142"/>
     </row>
     <row r="41" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="33">
@@ -12635,15 +12635,15 @@
         <v>131</v>
       </c>
       <c r="C41" s="34"/>
-      <c r="D41" s="175"/>
-      <c r="E41" s="81"/>
-      <c r="F41" s="81"/>
-      <c r="G41" s="81"/>
-      <c r="H41" s="81"/>
-      <c r="I41" s="81"/>
-      <c r="J41" s="81"/>
-      <c r="K41" s="81"/>
-      <c r="L41" s="81"/>
+      <c r="D41" s="141"/>
+      <c r="E41" s="142"/>
+      <c r="F41" s="142"/>
+      <c r="G41" s="142"/>
+      <c r="H41" s="142"/>
+      <c r="I41" s="142"/>
+      <c r="J41" s="142"/>
+      <c r="K41" s="142"/>
+      <c r="L41" s="142"/>
     </row>
     <row r="42" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="33">
@@ -12653,15 +12653,15 @@
         <v>132</v>
       </c>
       <c r="C42" s="34"/>
-      <c r="D42" s="175"/>
-      <c r="E42" s="81"/>
-      <c r="F42" s="81"/>
-      <c r="G42" s="81"/>
-      <c r="H42" s="81"/>
-      <c r="I42" s="81"/>
-      <c r="J42" s="81"/>
-      <c r="K42" s="81"/>
-      <c r="L42" s="81"/>
+      <c r="D42" s="141"/>
+      <c r="E42" s="142"/>
+      <c r="F42" s="142"/>
+      <c r="G42" s="142"/>
+      <c r="H42" s="142"/>
+      <c r="I42" s="142"/>
+      <c r="J42" s="142"/>
+      <c r="K42" s="142"/>
+      <c r="L42" s="142"/>
     </row>
     <row r="43" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="33">
@@ -12671,15 +12671,15 @@
         <v>133</v>
       </c>
       <c r="C43" s="34"/>
-      <c r="D43" s="175"/>
-      <c r="E43" s="81"/>
-      <c r="F43" s="81"/>
-      <c r="G43" s="81"/>
-      <c r="H43" s="81"/>
-      <c r="I43" s="81"/>
-      <c r="J43" s="81"/>
-      <c r="K43" s="81"/>
-      <c r="L43" s="81"/>
+      <c r="D43" s="141"/>
+      <c r="E43" s="142"/>
+      <c r="F43" s="142"/>
+      <c r="G43" s="142"/>
+      <c r="H43" s="142"/>
+      <c r="I43" s="142"/>
+      <c r="J43" s="142"/>
+      <c r="K43" s="142"/>
+      <c r="L43" s="142"/>
     </row>
     <row r="44" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="33">
@@ -12689,15 +12689,15 @@
         <v>134</v>
       </c>
       <c r="C44" s="34"/>
-      <c r="D44" s="175"/>
-      <c r="E44" s="81"/>
-      <c r="F44" s="81"/>
-      <c r="G44" s="81"/>
-      <c r="H44" s="81"/>
-      <c r="I44" s="81"/>
-      <c r="J44" s="81"/>
-      <c r="K44" s="81"/>
-      <c r="L44" s="81"/>
+      <c r="D44" s="141"/>
+      <c r="E44" s="142"/>
+      <c r="F44" s="142"/>
+      <c r="G44" s="142"/>
+      <c r="H44" s="142"/>
+      <c r="I44" s="142"/>
+      <c r="J44" s="142"/>
+      <c r="K44" s="142"/>
+      <c r="L44" s="142"/>
     </row>
     <row r="45" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="33">
@@ -12707,15 +12707,15 @@
         <v>135</v>
       </c>
       <c r="C45" s="34"/>
-      <c r="D45" s="175"/>
-      <c r="E45" s="81"/>
-      <c r="F45" s="81"/>
-      <c r="G45" s="81"/>
-      <c r="H45" s="81"/>
-      <c r="I45" s="81"/>
-      <c r="J45" s="81"/>
-      <c r="K45" s="81"/>
-      <c r="L45" s="81"/>
+      <c r="D45" s="141"/>
+      <c r="E45" s="142"/>
+      <c r="F45" s="142"/>
+      <c r="G45" s="142"/>
+      <c r="H45" s="142"/>
+      <c r="I45" s="142"/>
+      <c r="J45" s="142"/>
+      <c r="K45" s="142"/>
+      <c r="L45" s="142"/>
     </row>
     <row r="46" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="33">
@@ -12725,15 +12725,15 @@
         <v>136</v>
       </c>
       <c r="C46" s="34"/>
-      <c r="D46" s="175"/>
-      <c r="E46" s="81"/>
-      <c r="F46" s="81"/>
-      <c r="G46" s="81"/>
-      <c r="H46" s="81"/>
-      <c r="I46" s="81"/>
-      <c r="J46" s="81"/>
-      <c r="K46" s="81"/>
-      <c r="L46" s="81"/>
+      <c r="D46" s="141"/>
+      <c r="E46" s="142"/>
+      <c r="F46" s="142"/>
+      <c r="G46" s="142"/>
+      <c r="H46" s="142"/>
+      <c r="I46" s="142"/>
+      <c r="J46" s="142"/>
+      <c r="K46" s="142"/>
+      <c r="L46" s="142"/>
     </row>
     <row r="47" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="33">
@@ -12743,15 +12743,15 @@
         <v>137</v>
       </c>
       <c r="C47" s="34"/>
-      <c r="D47" s="175"/>
-      <c r="E47" s="81"/>
-      <c r="F47" s="81"/>
-      <c r="G47" s="81"/>
-      <c r="H47" s="81"/>
-      <c r="I47" s="81"/>
-      <c r="J47" s="81"/>
-      <c r="K47" s="81"/>
-      <c r="L47" s="81"/>
+      <c r="D47" s="141"/>
+      <c r="E47" s="142"/>
+      <c r="F47" s="142"/>
+      <c r="G47" s="142"/>
+      <c r="H47" s="142"/>
+      <c r="I47" s="142"/>
+      <c r="J47" s="142"/>
+      <c r="K47" s="142"/>
+      <c r="L47" s="142"/>
     </row>
     <row r="48" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="33">
@@ -12761,15 +12761,15 @@
         <v>138</v>
       </c>
       <c r="C48" s="34"/>
-      <c r="D48" s="175"/>
-      <c r="E48" s="81"/>
-      <c r="F48" s="81"/>
-      <c r="G48" s="81"/>
-      <c r="H48" s="81"/>
-      <c r="I48" s="81"/>
-      <c r="J48" s="81"/>
-      <c r="K48" s="81"/>
-      <c r="L48" s="81"/>
+      <c r="D48" s="141"/>
+      <c r="E48" s="142"/>
+      <c r="F48" s="142"/>
+      <c r="G48" s="142"/>
+      <c r="H48" s="142"/>
+      <c r="I48" s="142"/>
+      <c r="J48" s="142"/>
+      <c r="K48" s="142"/>
+      <c r="L48" s="142"/>
     </row>
     <row r="49" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="33">
@@ -12779,15 +12779,15 @@
         <v>139</v>
       </c>
       <c r="C49" s="34"/>
-      <c r="D49" s="175"/>
-      <c r="E49" s="81"/>
-      <c r="F49" s="81"/>
-      <c r="G49" s="81"/>
-      <c r="H49" s="81"/>
-      <c r="I49" s="81"/>
-      <c r="J49" s="81"/>
-      <c r="K49" s="81"/>
-      <c r="L49" s="81"/>
+      <c r="D49" s="141"/>
+      <c r="E49" s="142"/>
+      <c r="F49" s="142"/>
+      <c r="G49" s="142"/>
+      <c r="H49" s="142"/>
+      <c r="I49" s="142"/>
+      <c r="J49" s="142"/>
+      <c r="K49" s="142"/>
+      <c r="L49" s="142"/>
     </row>
     <row r="50" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="72">
@@ -12797,15 +12797,15 @@
         <v>140</v>
       </c>
       <c r="C50" s="34"/>
-      <c r="D50" s="175"/>
-      <c r="E50" s="81"/>
-      <c r="F50" s="81"/>
-      <c r="G50" s="81"/>
-      <c r="H50" s="81"/>
-      <c r="I50" s="81"/>
-      <c r="J50" s="81"/>
-      <c r="K50" s="81"/>
-      <c r="L50" s="81"/>
+      <c r="D50" s="141"/>
+      <c r="E50" s="142"/>
+      <c r="F50" s="142"/>
+      <c r="G50" s="142"/>
+      <c r="H50" s="142"/>
+      <c r="I50" s="142"/>
+      <c r="J50" s="142"/>
+      <c r="K50" s="142"/>
+      <c r="L50" s="142"/>
     </row>
     <row r="51" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="72">
@@ -12815,15 +12815,15 @@
         <v>141</v>
       </c>
       <c r="C51" s="34"/>
-      <c r="D51" s="175"/>
-      <c r="E51" s="81"/>
-      <c r="F51" s="81"/>
-      <c r="G51" s="81"/>
-      <c r="H51" s="81"/>
-      <c r="I51" s="81"/>
-      <c r="J51" s="81"/>
-      <c r="K51" s="81"/>
-      <c r="L51" s="81"/>
+      <c r="D51" s="141"/>
+      <c r="E51" s="142"/>
+      <c r="F51" s="142"/>
+      <c r="G51" s="142"/>
+      <c r="H51" s="142"/>
+      <c r="I51" s="142"/>
+      <c r="J51" s="142"/>
+      <c r="K51" s="142"/>
+      <c r="L51" s="142"/>
     </row>
     <row r="52" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="72">
@@ -12833,15 +12833,15 @@
         <v>142</v>
       </c>
       <c r="C52" s="34"/>
-      <c r="D52" s="175"/>
-      <c r="E52" s="81"/>
-      <c r="F52" s="81"/>
-      <c r="G52" s="81"/>
-      <c r="H52" s="81"/>
-      <c r="I52" s="81"/>
-      <c r="J52" s="81"/>
-      <c r="K52" s="81"/>
-      <c r="L52" s="81"/>
+      <c r="D52" s="141"/>
+      <c r="E52" s="142"/>
+      <c r="F52" s="142"/>
+      <c r="G52" s="142"/>
+      <c r="H52" s="142"/>
+      <c r="I52" s="142"/>
+      <c r="J52" s="142"/>
+      <c r="K52" s="142"/>
+      <c r="L52" s="142"/>
     </row>
     <row r="53" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="72">
@@ -12851,15 +12851,15 @@
         <v>143</v>
       </c>
       <c r="C53" s="79"/>
-      <c r="D53" s="175"/>
-      <c r="E53" s="81"/>
-      <c r="F53" s="81"/>
-      <c r="G53" s="81"/>
-      <c r="H53" s="81"/>
-      <c r="I53" s="81"/>
-      <c r="J53" s="81"/>
-      <c r="K53" s="81"/>
-      <c r="L53" s="81"/>
+      <c r="D53" s="141"/>
+      <c r="E53" s="142"/>
+      <c r="F53" s="142"/>
+      <c r="G53" s="142"/>
+      <c r="H53" s="142"/>
+      <c r="I53" s="142"/>
+      <c r="J53" s="142"/>
+      <c r="K53" s="142"/>
+      <c r="L53" s="142"/>
     </row>
     <row r="54" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="72">
@@ -12869,15 +12869,15 @@
         <v>144</v>
       </c>
       <c r="C54" s="72"/>
-      <c r="D54" s="175"/>
-      <c r="E54" s="81"/>
-      <c r="F54" s="81"/>
-      <c r="G54" s="81"/>
-      <c r="H54" s="81"/>
-      <c r="I54" s="81"/>
-      <c r="J54" s="81"/>
-      <c r="K54" s="81"/>
-      <c r="L54" s="81"/>
+      <c r="D54" s="141"/>
+      <c r="E54" s="142"/>
+      <c r="F54" s="142"/>
+      <c r="G54" s="142"/>
+      <c r="H54" s="142"/>
+      <c r="I54" s="142"/>
+      <c r="J54" s="142"/>
+      <c r="K54" s="142"/>
+      <c r="L54" s="142"/>
     </row>
     <row r="55" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="72">
@@ -12887,15 +12887,15 @@
         <v>145</v>
       </c>
       <c r="C55" s="78"/>
-      <c r="D55" s="175"/>
-      <c r="E55" s="81"/>
-      <c r="F55" s="81"/>
-      <c r="G55" s="81"/>
-      <c r="H55" s="81"/>
-      <c r="I55" s="81"/>
-      <c r="J55" s="81"/>
-      <c r="K55" s="81"/>
-      <c r="L55" s="81"/>
+      <c r="D55" s="141"/>
+      <c r="E55" s="142"/>
+      <c r="F55" s="142"/>
+      <c r="G55" s="142"/>
+      <c r="H55" s="142"/>
+      <c r="I55" s="142"/>
+      <c r="J55" s="142"/>
+      <c r="K55" s="142"/>
+      <c r="L55" s="142"/>
     </row>
     <row r="56" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="72">
@@ -12905,15 +12905,15 @@
         <v>146</v>
       </c>
       <c r="C56" s="78"/>
-      <c r="D56" s="175"/>
-      <c r="E56" s="81"/>
-      <c r="F56" s="81"/>
-      <c r="G56" s="81"/>
-      <c r="H56" s="81"/>
-      <c r="I56" s="81"/>
-      <c r="J56" s="81"/>
-      <c r="K56" s="81"/>
-      <c r="L56" s="81"/>
+      <c r="D56" s="141"/>
+      <c r="E56" s="142"/>
+      <c r="F56" s="142"/>
+      <c r="G56" s="142"/>
+      <c r="H56" s="142"/>
+      <c r="I56" s="142"/>
+      <c r="J56" s="142"/>
+      <c r="K56" s="142"/>
+      <c r="L56" s="142"/>
     </row>
     <row r="57" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="72">
@@ -12923,15 +12923,15 @@
         <v>147</v>
       </c>
       <c r="C57" s="78"/>
-      <c r="D57" s="175"/>
-      <c r="E57" s="81"/>
-      <c r="F57" s="81"/>
-      <c r="G57" s="81"/>
-      <c r="H57" s="81"/>
-      <c r="I57" s="81"/>
-      <c r="J57" s="81"/>
-      <c r="K57" s="81"/>
-      <c r="L57" s="81"/>
+      <c r="D57" s="141"/>
+      <c r="E57" s="142"/>
+      <c r="F57" s="142"/>
+      <c r="G57" s="142"/>
+      <c r="H57" s="142"/>
+      <c r="I57" s="142"/>
+      <c r="J57" s="142"/>
+      <c r="K57" s="142"/>
+      <c r="L57" s="142"/>
     </row>
     <row r="58" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="72">
@@ -12941,15 +12941,15 @@
         <v>148</v>
       </c>
       <c r="C58" s="78"/>
-      <c r="D58" s="175"/>
-      <c r="E58" s="81"/>
-      <c r="F58" s="81"/>
-      <c r="G58" s="81"/>
-      <c r="H58" s="81"/>
-      <c r="I58" s="81"/>
-      <c r="J58" s="81"/>
-      <c r="K58" s="81"/>
-      <c r="L58" s="81"/>
+      <c r="D58" s="141"/>
+      <c r="E58" s="142"/>
+      <c r="F58" s="142"/>
+      <c r="G58" s="142"/>
+      <c r="H58" s="142"/>
+      <c r="I58" s="142"/>
+      <c r="J58" s="142"/>
+      <c r="K58" s="142"/>
+      <c r="L58" s="142"/>
     </row>
     <row r="59" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="72">
@@ -12959,15 +12959,15 @@
         <v>149</v>
       </c>
       <c r="C59" s="78"/>
-      <c r="D59" s="175"/>
-      <c r="E59" s="81"/>
-      <c r="F59" s="81"/>
-      <c r="G59" s="81"/>
-      <c r="H59" s="81"/>
-      <c r="I59" s="81"/>
-      <c r="J59" s="81"/>
-      <c r="K59" s="81"/>
-      <c r="L59" s="81"/>
+      <c r="D59" s="141"/>
+      <c r="E59" s="142"/>
+      <c r="F59" s="142"/>
+      <c r="G59" s="142"/>
+      <c r="H59" s="142"/>
+      <c r="I59" s="142"/>
+      <c r="J59" s="142"/>
+      <c r="K59" s="142"/>
+      <c r="L59" s="142"/>
     </row>
     <row r="60" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="72">
@@ -12977,15 +12977,15 @@
         <v>150</v>
       </c>
       <c r="C60" s="78"/>
-      <c r="D60" s="175"/>
-      <c r="E60" s="81"/>
-      <c r="F60" s="81"/>
-      <c r="G60" s="81"/>
-      <c r="H60" s="81"/>
-      <c r="I60" s="81"/>
-      <c r="J60" s="81"/>
-      <c r="K60" s="81"/>
-      <c r="L60" s="81"/>
+      <c r="D60" s="141"/>
+      <c r="E60" s="142"/>
+      <c r="F60" s="142"/>
+      <c r="G60" s="142"/>
+      <c r="H60" s="142"/>
+      <c r="I60" s="142"/>
+      <c r="J60" s="142"/>
+      <c r="K60" s="142"/>
+      <c r="L60" s="142"/>
     </row>
     <row r="61" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="72">
@@ -12995,15 +12995,15 @@
         <v>153</v>
       </c>
       <c r="C61" s="78"/>
-      <c r="D61" s="175"/>
-      <c r="E61" s="81"/>
-      <c r="F61" s="81"/>
-      <c r="G61" s="81"/>
-      <c r="H61" s="81"/>
-      <c r="I61" s="81"/>
-      <c r="J61" s="81"/>
-      <c r="K61" s="81"/>
-      <c r="L61" s="81"/>
+      <c r="D61" s="141"/>
+      <c r="E61" s="142"/>
+      <c r="F61" s="142"/>
+      <c r="G61" s="142"/>
+      <c r="H61" s="142"/>
+      <c r="I61" s="142"/>
+      <c r="J61" s="142"/>
+      <c r="K61" s="142"/>
+      <c r="L61" s="142"/>
     </row>
     <row r="62" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="72">
@@ -13013,15 +13013,15 @@
         <v>154</v>
       </c>
       <c r="C62" s="78"/>
-      <c r="D62" s="175"/>
-      <c r="E62" s="81"/>
-      <c r="F62" s="81"/>
-      <c r="G62" s="81"/>
-      <c r="H62" s="81"/>
-      <c r="I62" s="81"/>
-      <c r="J62" s="81"/>
-      <c r="K62" s="81"/>
-      <c r="L62" s="81"/>
+      <c r="D62" s="141"/>
+      <c r="E62" s="142"/>
+      <c r="F62" s="142"/>
+      <c r="G62" s="142"/>
+      <c r="H62" s="142"/>
+      <c r="I62" s="142"/>
+      <c r="J62" s="142"/>
+      <c r="K62" s="142"/>
+      <c r="L62" s="142"/>
     </row>
     <row r="63" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="72">
@@ -13031,15 +13031,15 @@
         <v>151</v>
       </c>
       <c r="C63" s="78"/>
-      <c r="D63" s="175"/>
-      <c r="E63" s="81"/>
-      <c r="F63" s="81"/>
-      <c r="G63" s="81"/>
-      <c r="H63" s="81"/>
-      <c r="I63" s="81"/>
-      <c r="J63" s="81"/>
-      <c r="K63" s="81"/>
-      <c r="L63" s="81"/>
+      <c r="D63" s="141"/>
+      <c r="E63" s="142"/>
+      <c r="F63" s="142"/>
+      <c r="G63" s="142"/>
+      <c r="H63" s="142"/>
+      <c r="I63" s="142"/>
+      <c r="J63" s="142"/>
+      <c r="K63" s="142"/>
+      <c r="L63" s="142"/>
     </row>
     <row r="64" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="72">
@@ -13049,36 +13049,44 @@
         <v>152</v>
       </c>
       <c r="C64" s="78"/>
-      <c r="D64" s="175"/>
-      <c r="E64" s="81"/>
-      <c r="F64" s="81"/>
-      <c r="G64" s="81"/>
-      <c r="H64" s="81"/>
-      <c r="I64" s="81"/>
-      <c r="J64" s="81"/>
-      <c r="K64" s="81"/>
-      <c r="L64" s="81"/>
+      <c r="D64" s="141"/>
+      <c r="E64" s="142"/>
+      <c r="F64" s="142"/>
+      <c r="G64" s="142"/>
+      <c r="H64" s="142"/>
+      <c r="I64" s="142"/>
+      <c r="J64" s="142"/>
+      <c r="K64" s="142"/>
+      <c r="L64" s="142"/>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A65" s="173">
+      <c r="A65" s="80">
         <v>40</v>
       </c>
       <c r="B65" s="34" t="s">
         <v>155</v>
       </c>
       <c r="C65" s="78"/>
-      <c r="D65" s="175"/>
-      <c r="E65" s="81"/>
-      <c r="F65" s="81"/>
-      <c r="G65" s="81"/>
-      <c r="H65" s="81"/>
-      <c r="I65" s="81"/>
-      <c r="J65" s="81"/>
-      <c r="K65" s="81"/>
-      <c r="L65" s="81"/>
+      <c r="D65" s="141"/>
+      <c r="E65" s="142"/>
+      <c r="F65" s="142"/>
+      <c r="G65" s="142"/>
+      <c r="H65" s="142"/>
+      <c r="I65" s="142"/>
+      <c r="J65" s="142"/>
+      <c r="K65" s="142"/>
+      <c r="L65" s="142"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="D26:L65"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:L20"/>
+    <mergeCell ref="D25:L25"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:L22"/>
     <mergeCell ref="A16:L16"/>
     <mergeCell ref="A17:L17"/>
     <mergeCell ref="B15:L15"/>
@@ -13090,14 +13098,6 @@
     <mergeCell ref="B4:L4"/>
     <mergeCell ref="B5:L5"/>
     <mergeCell ref="B7:L7"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:L20"/>
-    <mergeCell ref="D25:L25"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:L22"/>
-    <mergeCell ref="D26:L65"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D26" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -16322,50 +16322,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="149" t="s">
+      <c r="A1" s="152" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="150"/>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="151"/>
+      <c r="B1" s="153"/>
+      <c r="C1" s="153"/>
+      <c r="D1" s="153"/>
+      <c r="E1" s="153"/>
+      <c r="F1" s="153"/>
+      <c r="G1" s="153"/>
+      <c r="H1" s="153"/>
+      <c r="I1" s="153"/>
+      <c r="J1" s="153"/>
+      <c r="K1" s="153"/>
+      <c r="L1" s="154"/>
     </row>
     <row r="2" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="155" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="153"/>
-      <c r="D2" s="153"/>
-      <c r="E2" s="153"/>
-      <c r="F2" s="153"/>
-      <c r="G2" s="153"/>
-      <c r="H2" s="153"/>
-      <c r="I2" s="153"/>
-      <c r="J2" s="153"/>
-      <c r="K2" s="153"/>
-      <c r="L2" s="154"/>
+      <c r="B2" s="156"/>
+      <c r="C2" s="156"/>
+      <c r="D2" s="156"/>
+      <c r="E2" s="156"/>
+      <c r="F2" s="156"/>
+      <c r="G2" s="156"/>
+      <c r="H2" s="156"/>
+      <c r="I2" s="156"/>
+      <c r="J2" s="156"/>
+      <c r="K2" s="156"/>
+      <c r="L2" s="157"/>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="155"/>
-      <c r="B3" s="156"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="156"/>
-      <c r="F3" s="156"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="156"/>
-      <c r="K3" s="156"/>
-      <c r="L3" s="157"/>
+      <c r="A3" s="158"/>
+      <c r="B3" s="159"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="159"/>
+      <c r="G3" s="159"/>
+      <c r="H3" s="159"/>
+      <c r="I3" s="159"/>
+      <c r="J3" s="159"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="160"/>
     </row>
     <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
@@ -16455,65 +16455,65 @@
       <c r="A8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="160"/>
-      <c r="C8" s="161"/>
-      <c r="D8" s="161"/>
-      <c r="E8" s="161"/>
-      <c r="F8" s="161"/>
-      <c r="G8" s="161"/>
-      <c r="H8" s="161"/>
-      <c r="I8" s="161"/>
-      <c r="J8" s="161"/>
-      <c r="K8" s="161"/>
-      <c r="L8" s="162"/>
+      <c r="B8" s="163"/>
+      <c r="C8" s="164"/>
+      <c r="D8" s="164"/>
+      <c r="E8" s="164"/>
+      <c r="F8" s="164"/>
+      <c r="G8" s="164"/>
+      <c r="H8" s="164"/>
+      <c r="I8" s="164"/>
+      <c r="J8" s="164"/>
+      <c r="K8" s="164"/>
+      <c r="L8" s="165"/>
     </row>
     <row r="9" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="163"/>
-      <c r="C9" s="161"/>
-      <c r="D9" s="161"/>
-      <c r="E9" s="161"/>
-      <c r="F9" s="161"/>
-      <c r="G9" s="161"/>
-      <c r="H9" s="161"/>
-      <c r="I9" s="161"/>
-      <c r="J9" s="161"/>
-      <c r="K9" s="161"/>
-      <c r="L9" s="162"/>
+      <c r="B9" s="166"/>
+      <c r="C9" s="164"/>
+      <c r="D9" s="164"/>
+      <c r="E9" s="164"/>
+      <c r="F9" s="164"/>
+      <c r="G9" s="164"/>
+      <c r="H9" s="164"/>
+      <c r="I9" s="164"/>
+      <c r="J9" s="164"/>
+      <c r="K9" s="164"/>
+      <c r="L9" s="165"/>
     </row>
     <row r="10" spans="1:12" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="158" t="s">
+      <c r="A10" s="161" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="159"/>
-      <c r="C10" s="159"/>
-      <c r="D10" s="159"/>
-      <c r="E10" s="159"/>
-      <c r="F10" s="159"/>
-      <c r="G10" s="159"/>
-      <c r="H10" s="159"/>
-      <c r="I10" s="159"/>
-      <c r="J10" s="159"/>
-      <c r="K10" s="159"/>
-      <c r="L10" s="159"/>
+      <c r="B10" s="162"/>
+      <c r="C10" s="162"/>
+      <c r="D10" s="162"/>
+      <c r="E10" s="162"/>
+      <c r="F10" s="162"/>
+      <c r="G10" s="162"/>
+      <c r="H10" s="162"/>
+      <c r="I10" s="162"/>
+      <c r="J10" s="162"/>
+      <c r="K10" s="162"/>
+      <c r="L10" s="162"/>
     </row>
     <row r="11" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="140" t="s">
+      <c r="A11" s="143" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="141"/>
-      <c r="C11" s="141"/>
-      <c r="D11" s="141"/>
-      <c r="E11" s="141"/>
-      <c r="F11" s="141"/>
-      <c r="G11" s="141"/>
-      <c r="H11" s="141"/>
-      <c r="I11" s="141"/>
-      <c r="J11" s="141"/>
-      <c r="K11" s="141"/>
-      <c r="L11" s="142"/>
+      <c r="B11" s="144"/>
+      <c r="C11" s="144"/>
+      <c r="D11" s="144"/>
+      <c r="E11" s="144"/>
+      <c r="F11" s="144"/>
+      <c r="G11" s="144"/>
+      <c r="H11" s="144"/>
+      <c r="I11" s="144"/>
+      <c r="J11" s="144"/>
+      <c r="K11" s="144"/>
+      <c r="L11" s="145"/>
     </row>
     <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
@@ -16525,101 +16525,101 @@
       <c r="C12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="90" t="s">
+      <c r="D12" s="123" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="90"/>
-      <c r="F12" s="90"/>
-      <c r="G12" s="90"/>
-      <c r="H12" s="90"/>
-      <c r="I12" s="90"/>
-      <c r="J12" s="90"/>
-      <c r="K12" s="90"/>
-      <c r="L12" s="90"/>
+      <c r="E12" s="123"/>
+      <c r="F12" s="123"/>
+      <c r="G12" s="123"/>
+      <c r="H12" s="123"/>
+      <c r="I12" s="123"/>
+      <c r="J12" s="123"/>
+      <c r="K12" s="123"/>
+      <c r="L12" s="123"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="49"/>
       <c r="B13" s="50"/>
       <c r="C13" s="50"/>
-      <c r="D13" s="143"/>
-      <c r="E13" s="144"/>
-      <c r="F13" s="144"/>
-      <c r="G13" s="144"/>
-      <c r="H13" s="144"/>
-      <c r="I13" s="144"/>
-      <c r="J13" s="144"/>
-      <c r="K13" s="144"/>
-      <c r="L13" s="145"/>
+      <c r="D13" s="146"/>
+      <c r="E13" s="147"/>
+      <c r="F13" s="147"/>
+      <c r="G13" s="147"/>
+      <c r="H13" s="147"/>
+      <c r="I13" s="147"/>
+      <c r="J13" s="147"/>
+      <c r="K13" s="147"/>
+      <c r="L13" s="148"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="49"/>
       <c r="B14" s="50"/>
       <c r="C14" s="50"/>
-      <c r="D14" s="146"/>
-      <c r="E14" s="147"/>
-      <c r="F14" s="147"/>
-      <c r="G14" s="147"/>
-      <c r="H14" s="147"/>
-      <c r="I14" s="147"/>
-      <c r="J14" s="147"/>
-      <c r="K14" s="147"/>
-      <c r="L14" s="148"/>
+      <c r="D14" s="149"/>
+      <c r="E14" s="150"/>
+      <c r="F14" s="150"/>
+      <c r="G14" s="150"/>
+      <c r="H14" s="150"/>
+      <c r="I14" s="150"/>
+      <c r="J14" s="150"/>
+      <c r="K14" s="150"/>
+      <c r="L14" s="151"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="49"/>
       <c r="B15" s="50"/>
       <c r="C15" s="50"/>
-      <c r="D15" s="146"/>
-      <c r="E15" s="147"/>
-      <c r="F15" s="147"/>
-      <c r="G15" s="147"/>
-      <c r="H15" s="147"/>
-      <c r="I15" s="147"/>
-      <c r="J15" s="147"/>
-      <c r="K15" s="147"/>
-      <c r="L15" s="148"/>
+      <c r="D15" s="149"/>
+      <c r="E15" s="150"/>
+      <c r="F15" s="150"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="150"/>
+      <c r="I15" s="150"/>
+      <c r="J15" s="150"/>
+      <c r="K15" s="150"/>
+      <c r="L15" s="151"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="49"/>
       <c r="B16" s="50"/>
       <c r="C16" s="50"/>
-      <c r="D16" s="146"/>
-      <c r="E16" s="147"/>
-      <c r="F16" s="147"/>
-      <c r="G16" s="147"/>
-      <c r="H16" s="147"/>
-      <c r="I16" s="147"/>
-      <c r="J16" s="147"/>
-      <c r="K16" s="147"/>
-      <c r="L16" s="148"/>
+      <c r="D16" s="149"/>
+      <c r="E16" s="150"/>
+      <c r="F16" s="150"/>
+      <c r="G16" s="150"/>
+      <c r="H16" s="150"/>
+      <c r="I16" s="150"/>
+      <c r="J16" s="150"/>
+      <c r="K16" s="150"/>
+      <c r="L16" s="151"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="49"/>
       <c r="B17" s="50"/>
       <c r="C17" s="50"/>
-      <c r="D17" s="146"/>
-      <c r="E17" s="147"/>
-      <c r="F17" s="147"/>
-      <c r="G17" s="147"/>
-      <c r="H17" s="147"/>
-      <c r="I17" s="147"/>
-      <c r="J17" s="147"/>
-      <c r="K17" s="147"/>
-      <c r="L17" s="148"/>
+      <c r="D17" s="149"/>
+      <c r="E17" s="150"/>
+      <c r="F17" s="150"/>
+      <c r="G17" s="150"/>
+      <c r="H17" s="150"/>
+      <c r="I17" s="150"/>
+      <c r="J17" s="150"/>
+      <c r="K17" s="150"/>
+      <c r="L17" s="151"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="49"/>
       <c r="B18" s="50"/>
       <c r="C18" s="50"/>
-      <c r="D18" s="146"/>
-      <c r="E18" s="147"/>
-      <c r="F18" s="147"/>
-      <c r="G18" s="147"/>
-      <c r="H18" s="147"/>
-      <c r="I18" s="147"/>
-      <c r="J18" s="147"/>
-      <c r="K18" s="147"/>
-      <c r="L18" s="148"/>
+      <c r="D18" s="149"/>
+      <c r="E18" s="150"/>
+      <c r="F18" s="150"/>
+      <c r="G18" s="150"/>
+      <c r="H18" s="150"/>
+      <c r="I18" s="150"/>
+      <c r="J18" s="150"/>
+      <c r="K18" s="150"/>
+      <c r="L18" s="151"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -16708,10 +16708,10 @@
       <c r="B4" s="63"/>
     </row>
     <row r="6" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="A6" s="164" t="s">
+      <c r="A6" s="167" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="164"/>
+      <c r="B6" s="167"/>
     </row>
     <row r="8" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="66" t="s">
@@ -16864,55 +16864,55 @@
   <sheetData>
     <row r="1" spans="2:6" ht="5.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B2" s="166"/>
-      <c r="C2" s="166"/>
-      <c r="D2" s="167" t="s">
+      <c r="B2" s="169"/>
+      <c r="C2" s="169"/>
+      <c r="D2" s="170" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="168" t="s">
+      <c r="E2" s="171" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="168"/>
+      <c r="F2" s="171"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B3" s="166"/>
-      <c r="C3" s="166"/>
-      <c r="D3" s="167"/>
-      <c r="E3" s="168"/>
-      <c r="F3" s="168"/>
+      <c r="B3" s="169"/>
+      <c r="C3" s="169"/>
+      <c r="D3" s="170"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="171"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="166"/>
-      <c r="C4" s="166"/>
-      <c r="D4" s="167"/>
-      <c r="E4" s="168" t="s">
+      <c r="B4" s="169"/>
+      <c r="C4" s="169"/>
+      <c r="D4" s="170"/>
+      <c r="E4" s="171" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="168"/>
+      <c r="F4" s="171"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="169" t="s">
+      <c r="B5" s="172" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="169"/>
+      <c r="C5" s="172"/>
       <c r="D5" s="70" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="170" t="s">
+      <c r="E5" s="173" t="s">
         <v>54</v>
       </c>
-      <c r="F5" s="170"/>
+      <c r="F5" s="173"/>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="165" t="s">
+      <c r="C6" s="168" t="s">
         <v>114</v>
       </c>
-      <c r="D6" s="165"/>
-      <c r="E6" s="165"/>
-      <c r="F6" s="165"/>
+      <c r="D6" s="168"/>
+      <c r="E6" s="168"/>
+      <c r="F6" s="168"/>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="71" t="s">
@@ -17169,10 +17169,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="27" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="171" t="s">
+      <c r="A1" s="174" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="172"/>
+      <c r="B1" s="175"/>
     </row>
     <row r="2" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="28" t="s">
@@ -17443,12 +17443,56 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50">
+      <UserInfo>
+        <DisplayName>Luis Campos / Logiztik Alliance</DisplayName>
+        <AccountId>265</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Jairo Gonzalez / Logiztik Alliance</DisplayName>
+        <AccountId>322</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>José Ganchozo / Logiztik Alliance</DisplayName>
+        <AccountId>304</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Edwin Casa / Logiztik Alliance</DisplayName>
+        <AccountId>299</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Cristhian Cuichan / Logiztik Alliance</DisplayName>
+        <AccountId>369</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Oscar Yunda /  Logiztik Alliance</DisplayName>
+        <AccountId>355</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Fernando Ordoñez / Logiztik Alliance</DisplayName>
+        <AccountId>321</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Alex Rivera / Logiztik Alliance</DisplayName>
+        <AccountId>370</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <TaxCatchAll xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="87481c51-c14c-4071-bf64-faa2b5708bb6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17701,62 +17745,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50">
-      <UserInfo>
-        <DisplayName>Luis Campos / Logiztik Alliance</DisplayName>
-        <AccountId>265</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Jairo Gonzalez / Logiztik Alliance</DisplayName>
-        <AccountId>322</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>José Ganchozo / Logiztik Alliance</DisplayName>
-        <AccountId>304</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Edwin Casa / Logiztik Alliance</DisplayName>
-        <AccountId>299</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Cristhian Cuichan / Logiztik Alliance</DisplayName>
-        <AccountId>369</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Oscar Yunda /  Logiztik Alliance</DisplayName>
-        <AccountId>355</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Fernando Ordoñez / Logiztik Alliance</DisplayName>
-        <AccountId>321</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Alex Rivera / Logiztik Alliance</DisplayName>
-        <AccountId>370</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <TaxCatchAll xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="87481c51-c14c-4071-bf64-faa2b5708bb6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371D8832-41B3-447B-B13D-2663C267E34F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD069904-634F-48DA-AA92-BAE250498BEE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8029d101-3d2a-47c4-b15f-619642bf5e50"/>
+    <ds:schemaRef ds:uri="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -17781,12 +17784,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD069904-634F-48DA-AA92-BAE250498BEE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371D8832-41B3-447B-B13D-2663C267E34F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8029d101-3d2a-47c4-b15f-619642bf5e50"/>
-    <ds:schemaRef ds:uri="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Guias Produccion/HU-57723.xlsx
+++ b/Guias Produccion/HU-57723.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Alliance\ScriptsEntidades\Guias Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2562A79-56CB-479F-A8EE-E024C97D8DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDAF6402-1753-4DB9-B79D-DB6F146EC683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2007,6 +2007,90 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="54" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2108,90 +2192,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="54" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -11920,42 +11920,42 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:15" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="97" t="s">
+      <c r="A3" s="125" t="s">
         <v>103</v>
       </c>
-      <c r="B3" s="98"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="98"/>
-      <c r="K3" s="98"/>
-      <c r="L3" s="99"/>
-      <c r="N3" s="91" t="s">
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="126"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="126"/>
+      <c r="H3" s="126"/>
+      <c r="I3" s="126"/>
+      <c r="J3" s="126"/>
+      <c r="K3" s="126"/>
+      <c r="L3" s="127"/>
+      <c r="N3" s="119" t="s">
         <v>0</v>
       </c>
-      <c r="O3" s="92"/>
+      <c r="O3" s="120"/>
     </row>
     <row r="4" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="104" t="s">
+      <c r="B4" s="132" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="105"/>
-      <c r="D4" s="105"/>
-      <c r="E4" s="105"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="105"/>
-      <c r="I4" s="105"/>
-      <c r="J4" s="106"/>
-      <c r="K4" s="106"/>
-      <c r="L4" s="107"/>
+      <c r="C4" s="133"/>
+      <c r="D4" s="133"/>
+      <c r="E4" s="133"/>
+      <c r="F4" s="133"/>
+      <c r="G4" s="133"/>
+      <c r="H4" s="133"/>
+      <c r="I4" s="133"/>
+      <c r="J4" s="134"/>
+      <c r="K4" s="134"/>
+      <c r="L4" s="135"/>
       <c r="N4" s="21" t="s">
         <v>2</v>
       </c>
@@ -11965,19 +11965,19 @@
       <c r="A5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="108" t="s">
+      <c r="B5" s="136" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="108"/>
-      <c r="D5" s="108"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="108"/>
-      <c r="G5" s="108"/>
-      <c r="H5" s="108"/>
-      <c r="I5" s="108"/>
-      <c r="J5" s="109"/>
-      <c r="K5" s="109"/>
-      <c r="L5" s="110"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="136"/>
+      <c r="F5" s="136"/>
+      <c r="G5" s="136"/>
+      <c r="H5" s="136"/>
+      <c r="I5" s="136"/>
+      <c r="J5" s="137"/>
+      <c r="K5" s="137"/>
+      <c r="L5" s="138"/>
       <c r="N5" s="15" t="s">
         <v>4</v>
       </c>
@@ -11987,19 +11987,19 @@
       <c r="A6" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="94">
+      <c r="B6" s="122">
         <v>46073</v>
       </c>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="95"/>
-      <c r="K6" s="95"/>
-      <c r="L6" s="96"/>
+      <c r="C6" s="123"/>
+      <c r="D6" s="123"/>
+      <c r="E6" s="123"/>
+      <c r="F6" s="123"/>
+      <c r="G6" s="123"/>
+      <c r="H6" s="123"/>
+      <c r="I6" s="123"/>
+      <c r="J6" s="123"/>
+      <c r="K6" s="123"/>
+      <c r="L6" s="124"/>
       <c r="N6" s="14"/>
       <c r="O6" s="14"/>
     </row>
@@ -12007,17 +12007,17 @@
       <c r="A7" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="111"/>
-      <c r="C7" s="112"/>
-      <c r="D7" s="112"/>
-      <c r="E7" s="112"/>
-      <c r="F7" s="112"/>
-      <c r="G7" s="112"/>
-      <c r="H7" s="112"/>
-      <c r="I7" s="112"/>
-      <c r="J7" s="113"/>
-      <c r="K7" s="113"/>
-      <c r="L7" s="114"/>
+      <c r="B7" s="139"/>
+      <c r="C7" s="140"/>
+      <c r="D7" s="140"/>
+      <c r="E7" s="140"/>
+      <c r="F7" s="140"/>
+      <c r="G7" s="140"/>
+      <c r="H7" s="140"/>
+      <c r="I7" s="140"/>
+      <c r="J7" s="141"/>
+      <c r="K7" s="141"/>
+      <c r="L7" s="142"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
@@ -12034,20 +12034,20 @@
       <c r="L8" s="13"/>
     </row>
     <row r="9" spans="1:15" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="100" t="s">
+      <c r="A9" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="101"/>
-      <c r="C9" s="101"/>
-      <c r="D9" s="101"/>
-      <c r="E9" s="101"/>
-      <c r="F9" s="101"/>
-      <c r="G9" s="101"/>
-      <c r="H9" s="101"/>
-      <c r="I9" s="101"/>
-      <c r="J9" s="102"/>
-      <c r="K9" s="102"/>
-      <c r="L9" s="103"/>
+      <c r="B9" s="129"/>
+      <c r="C9" s="129"/>
+      <c r="D9" s="129"/>
+      <c r="E9" s="129"/>
+      <c r="F9" s="129"/>
+      <c r="G9" s="129"/>
+      <c r="H9" s="129"/>
+      <c r="I9" s="129"/>
+      <c r="J9" s="130"/>
+      <c r="K9" s="130"/>
+      <c r="L9" s="131"/>
     </row>
     <row r="10" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -12147,63 +12147,63 @@
       <c r="A14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="93"/>
-      <c r="C14" s="89"/>
-      <c r="D14" s="89"/>
-      <c r="E14" s="89"/>
-      <c r="F14" s="89"/>
-      <c r="G14" s="89"/>
-      <c r="H14" s="89"/>
-      <c r="I14" s="89"/>
-      <c r="J14" s="89"/>
-      <c r="K14" s="89"/>
-      <c r="L14" s="90"/>
+      <c r="B14" s="121"/>
+      <c r="C14" s="117"/>
+      <c r="D14" s="117"/>
+      <c r="E14" s="117"/>
+      <c r="F14" s="117"/>
+      <c r="G14" s="117"/>
+      <c r="H14" s="117"/>
+      <c r="I14" s="117"/>
+      <c r="J14" s="117"/>
+      <c r="K14" s="117"/>
+      <c r="L14" s="118"/>
     </row>
     <row r="15" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="88"/>
-      <c r="C15" s="89"/>
-      <c r="D15" s="89"/>
-      <c r="E15" s="89"/>
-      <c r="F15" s="89"/>
-      <c r="G15" s="89"/>
-      <c r="H15" s="89"/>
-      <c r="I15" s="89"/>
-      <c r="J15" s="89"/>
-      <c r="K15" s="89"/>
-      <c r="L15" s="90"/>
+      <c r="B15" s="116"/>
+      <c r="C15" s="117"/>
+      <c r="D15" s="117"/>
+      <c r="E15" s="117"/>
+      <c r="F15" s="117"/>
+      <c r="G15" s="117"/>
+      <c r="H15" s="117"/>
+      <c r="I15" s="117"/>
+      <c r="J15" s="117"/>
+      <c r="K15" s="117"/>
+      <c r="L15" s="118"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="81"/>
-      <c r="B16" s="82"/>
-      <c r="C16" s="82"/>
-      <c r="D16" s="82"/>
-      <c r="E16" s="82"/>
-      <c r="F16" s="82"/>
-      <c r="G16" s="82"/>
-      <c r="H16" s="82"/>
-      <c r="I16" s="82"/>
-      <c r="J16" s="82"/>
-      <c r="K16" s="82"/>
-      <c r="L16" s="83"/>
+      <c r="A16" s="109"/>
+      <c r="B16" s="110"/>
+      <c r="C16" s="110"/>
+      <c r="D16" s="110"/>
+      <c r="E16" s="110"/>
+      <c r="F16" s="110"/>
+      <c r="G16" s="110"/>
+      <c r="H16" s="110"/>
+      <c r="I16" s="110"/>
+      <c r="J16" s="110"/>
+      <c r="K16" s="110"/>
+      <c r="L16" s="111"/>
     </row>
     <row r="17" spans="1:12" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="84" t="s">
+      <c r="A17" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="85"/>
-      <c r="C17" s="85"/>
-      <c r="D17" s="85"/>
-      <c r="E17" s="85"/>
-      <c r="F17" s="85"/>
-      <c r="G17" s="85"/>
-      <c r="H17" s="85"/>
-      <c r="I17" s="85"/>
-      <c r="J17" s="86"/>
-      <c r="K17" s="86"/>
-      <c r="L17" s="87"/>
+      <c r="B17" s="113"/>
+      <c r="C17" s="113"/>
+      <c r="D17" s="113"/>
+      <c r="E17" s="113"/>
+      <c r="F17" s="113"/>
+      <c r="G17" s="113"/>
+      <c r="H17" s="113"/>
+      <c r="I17" s="113"/>
+      <c r="J17" s="114"/>
+      <c r="K17" s="114"/>
+      <c r="L17" s="115"/>
     </row>
     <row r="18" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
@@ -12213,19 +12213,19 @@
       <c r="C18" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="115" t="s">
+      <c r="D18" s="85" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="117" t="s">
+      <c r="E18" s="87" t="s">
         <v>115</v>
       </c>
-      <c r="F18" s="117"/>
-      <c r="G18" s="117"/>
-      <c r="H18" s="117"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="118"/>
-      <c r="K18" s="118"/>
-      <c r="L18" s="119"/>
+      <c r="F18" s="87"/>
+      <c r="G18" s="87"/>
+      <c r="H18" s="87"/>
+      <c r="I18" s="87"/>
+      <c r="J18" s="88"/>
+      <c r="K18" s="88"/>
+      <c r="L18" s="89"/>
     </row>
     <row r="19" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
@@ -12235,15 +12235,15 @@
         <v>30</v>
       </c>
       <c r="C19" s="44"/>
-      <c r="D19" s="116"/>
-      <c r="E19" s="120"/>
-      <c r="F19" s="120"/>
-      <c r="G19" s="120"/>
-      <c r="H19" s="120"/>
-      <c r="I19" s="120"/>
-      <c r="J19" s="121"/>
-      <c r="K19" s="121"/>
-      <c r="L19" s="122"/>
+      <c r="D19" s="86"/>
+      <c r="E19" s="90"/>
+      <c r="F19" s="90"/>
+      <c r="G19" s="90"/>
+      <c r="H19" s="90"/>
+      <c r="I19" s="90"/>
+      <c r="J19" s="91"/>
+      <c r="K19" s="91"/>
+      <c r="L19" s="92"/>
     </row>
     <row r="20" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
@@ -12253,15 +12253,15 @@
       <c r="C20" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="116"/>
-      <c r="E20" s="120"/>
-      <c r="F20" s="120"/>
-      <c r="G20" s="120"/>
-      <c r="H20" s="120"/>
-      <c r="I20" s="120"/>
-      <c r="J20" s="121"/>
-      <c r="K20" s="121"/>
-      <c r="L20" s="122"/>
+      <c r="D20" s="86"/>
+      <c r="E20" s="90"/>
+      <c r="F20" s="90"/>
+      <c r="G20" s="90"/>
+      <c r="H20" s="90"/>
+      <c r="I20" s="90"/>
+      <c r="J20" s="91"/>
+      <c r="K20" s="91"/>
+      <c r="L20" s="92"/>
     </row>
     <row r="21" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
@@ -12271,19 +12271,19 @@
       <c r="C21" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="131" t="s">
+      <c r="D21" s="101" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="133" t="s">
+      <c r="E21" s="103" t="s">
         <v>107</v>
       </c>
-      <c r="F21" s="134"/>
-      <c r="G21" s="134"/>
-      <c r="H21" s="134"/>
-      <c r="I21" s="134"/>
-      <c r="J21" s="134"/>
-      <c r="K21" s="134"/>
-      <c r="L21" s="135"/>
+      <c r="F21" s="104"/>
+      <c r="G21" s="104"/>
+      <c r="H21" s="104"/>
+      <c r="I21" s="104"/>
+      <c r="J21" s="104"/>
+      <c r="K21" s="104"/>
+      <c r="L21" s="105"/>
     </row>
     <row r="22" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
@@ -12293,45 +12293,45 @@
       <c r="C22" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="132"/>
-      <c r="E22" s="136"/>
-      <c r="F22" s="137"/>
-      <c r="G22" s="137"/>
-      <c r="H22" s="137"/>
-      <c r="I22" s="137"/>
-      <c r="J22" s="137"/>
-      <c r="K22" s="137"/>
-      <c r="L22" s="138"/>
+      <c r="D22" s="102"/>
+      <c r="E22" s="106"/>
+      <c r="F22" s="107"/>
+      <c r="G22" s="107"/>
+      <c r="H22" s="107"/>
+      <c r="I22" s="107"/>
+      <c r="J22" s="107"/>
+      <c r="K22" s="107"/>
+      <c r="L22" s="108"/>
     </row>
     <row r="23" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="124"/>
-      <c r="B23" s="125"/>
-      <c r="C23" s="125"/>
-      <c r="D23" s="126"/>
-      <c r="E23" s="126"/>
-      <c r="F23" s="126"/>
-      <c r="G23" s="126"/>
-      <c r="H23" s="126"/>
-      <c r="I23" s="126"/>
-      <c r="J23" s="126"/>
-      <c r="K23" s="126"/>
-      <c r="L23" s="127"/>
+      <c r="A23" s="94"/>
+      <c r="B23" s="95"/>
+      <c r="C23" s="95"/>
+      <c r="D23" s="96"/>
+      <c r="E23" s="96"/>
+      <c r="F23" s="96"/>
+      <c r="G23" s="96"/>
+      <c r="H23" s="96"/>
+      <c r="I23" s="96"/>
+      <c r="J23" s="96"/>
+      <c r="K23" s="96"/>
+      <c r="L23" s="97"/>
     </row>
     <row r="24" spans="1:12" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="128" t="s">
+      <c r="A24" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="129"/>
-      <c r="C24" s="129"/>
-      <c r="D24" s="129"/>
-      <c r="E24" s="129"/>
-      <c r="F24" s="129"/>
-      <c r="G24" s="129"/>
-      <c r="H24" s="129"/>
-      <c r="I24" s="129"/>
-      <c r="J24" s="129"/>
-      <c r="K24" s="129"/>
-      <c r="L24" s="130"/>
+      <c r="B24" s="99"/>
+      <c r="C24" s="99"/>
+      <c r="D24" s="99"/>
+      <c r="E24" s="99"/>
+      <c r="F24" s="99"/>
+      <c r="G24" s="99"/>
+      <c r="H24" s="99"/>
+      <c r="I24" s="99"/>
+      <c r="J24" s="99"/>
+      <c r="K24" s="99"/>
+      <c r="L24" s="100"/>
     </row>
     <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
@@ -12343,17 +12343,17 @@
       <c r="C25" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="123" t="s">
+      <c r="D25" s="93" t="s">
         <v>38</v>
       </c>
-      <c r="E25" s="123"/>
-      <c r="F25" s="123"/>
-      <c r="G25" s="123"/>
-      <c r="H25" s="123"/>
-      <c r="I25" s="123"/>
-      <c r="J25" s="123"/>
-      <c r="K25" s="123"/>
-      <c r="L25" s="123"/>
+      <c r="E25" s="93"/>
+      <c r="F25" s="93"/>
+      <c r="G25" s="93"/>
+      <c r="H25" s="93"/>
+      <c r="I25" s="93"/>
+      <c r="J25" s="93"/>
+      <c r="K25" s="93"/>
+      <c r="L25" s="93"/>
     </row>
     <row r="26" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="33">
@@ -12363,17 +12363,17 @@
         <v>116</v>
       </c>
       <c r="C26" s="34"/>
-      <c r="D26" s="139" t="s">
+      <c r="D26" s="81" t="s">
         <v>108</v>
       </c>
-      <c r="E26" s="140"/>
-      <c r="F26" s="140"/>
-      <c r="G26" s="140"/>
-      <c r="H26" s="140"/>
-      <c r="I26" s="140"/>
-      <c r="J26" s="140"/>
-      <c r="K26" s="140"/>
-      <c r="L26" s="140"/>
+      <c r="E26" s="82"/>
+      <c r="F26" s="82"/>
+      <c r="G26" s="82"/>
+      <c r="H26" s="82"/>
+      <c r="I26" s="82"/>
+      <c r="J26" s="82"/>
+      <c r="K26" s="82"/>
+      <c r="L26" s="82"/>
     </row>
     <row r="27" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
@@ -12383,15 +12383,15 @@
         <v>117</v>
       </c>
       <c r="C27" s="34"/>
-      <c r="D27" s="141"/>
-      <c r="E27" s="142"/>
-      <c r="F27" s="142"/>
-      <c r="G27" s="142"/>
-      <c r="H27" s="142"/>
-      <c r="I27" s="142"/>
-      <c r="J27" s="142"/>
-      <c r="K27" s="142"/>
-      <c r="L27" s="142"/>
+      <c r="D27" s="83"/>
+      <c r="E27" s="84"/>
+      <c r="F27" s="84"/>
+      <c r="G27" s="84"/>
+      <c r="H27" s="84"/>
+      <c r="I27" s="84"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="84"/>
+      <c r="L27" s="84"/>
     </row>
     <row r="28" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="33">
@@ -12401,15 +12401,15 @@
         <v>118</v>
       </c>
       <c r="C28" s="34"/>
-      <c r="D28" s="141"/>
-      <c r="E28" s="142"/>
-      <c r="F28" s="142"/>
-      <c r="G28" s="142"/>
-      <c r="H28" s="142"/>
-      <c r="I28" s="142"/>
-      <c r="J28" s="142"/>
-      <c r="K28" s="142"/>
-      <c r="L28" s="142"/>
+      <c r="D28" s="83"/>
+      <c r="E28" s="84"/>
+      <c r="F28" s="84"/>
+      <c r="G28" s="84"/>
+      <c r="H28" s="84"/>
+      <c r="I28" s="84"/>
+      <c r="J28" s="84"/>
+      <c r="K28" s="84"/>
+      <c r="L28" s="84"/>
     </row>
     <row r="29" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
@@ -12419,15 +12419,15 @@
         <v>119</v>
       </c>
       <c r="C29" s="34"/>
-      <c r="D29" s="141"/>
-      <c r="E29" s="142"/>
-      <c r="F29" s="142"/>
-      <c r="G29" s="142"/>
-      <c r="H29" s="142"/>
-      <c r="I29" s="142"/>
-      <c r="J29" s="142"/>
-      <c r="K29" s="142"/>
-      <c r="L29" s="142"/>
+      <c r="D29" s="83"/>
+      <c r="E29" s="84"/>
+      <c r="F29" s="84"/>
+      <c r="G29" s="84"/>
+      <c r="H29" s="84"/>
+      <c r="I29" s="84"/>
+      <c r="J29" s="84"/>
+      <c r="K29" s="84"/>
+      <c r="L29" s="84"/>
     </row>
     <row r="30" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="33">
@@ -12437,15 +12437,15 @@
         <v>120</v>
       </c>
       <c r="C30" s="34"/>
-      <c r="D30" s="141"/>
-      <c r="E30" s="142"/>
-      <c r="F30" s="142"/>
-      <c r="G30" s="142"/>
-      <c r="H30" s="142"/>
-      <c r="I30" s="142"/>
-      <c r="J30" s="142"/>
-      <c r="K30" s="142"/>
-      <c r="L30" s="142"/>
+      <c r="D30" s="83"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="84"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="84"/>
     </row>
     <row r="31" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="33">
@@ -12455,15 +12455,15 @@
         <v>121</v>
       </c>
       <c r="C31" s="34"/>
-      <c r="D31" s="141"/>
-      <c r="E31" s="142"/>
-      <c r="F31" s="142"/>
-      <c r="G31" s="142"/>
-      <c r="H31" s="142"/>
-      <c r="I31" s="142"/>
-      <c r="J31" s="142"/>
-      <c r="K31" s="142"/>
-      <c r="L31" s="142"/>
+      <c r="D31" s="83"/>
+      <c r="E31" s="84"/>
+      <c r="F31" s="84"/>
+      <c r="G31" s="84"/>
+      <c r="H31" s="84"/>
+      <c r="I31" s="84"/>
+      <c r="J31" s="84"/>
+      <c r="K31" s="84"/>
+      <c r="L31" s="84"/>
     </row>
     <row r="32" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="33">
@@ -12473,15 +12473,15 @@
         <v>122</v>
       </c>
       <c r="C32" s="34"/>
-      <c r="D32" s="141"/>
-      <c r="E32" s="142"/>
-      <c r="F32" s="142"/>
-      <c r="G32" s="142"/>
-      <c r="H32" s="142"/>
-      <c r="I32" s="142"/>
-      <c r="J32" s="142"/>
-      <c r="K32" s="142"/>
-      <c r="L32" s="142"/>
+      <c r="D32" s="83"/>
+      <c r="E32" s="84"/>
+      <c r="F32" s="84"/>
+      <c r="G32" s="84"/>
+      <c r="H32" s="84"/>
+      <c r="I32" s="84"/>
+      <c r="J32" s="84"/>
+      <c r="K32" s="84"/>
+      <c r="L32" s="84"/>
     </row>
     <row r="33" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="33">
@@ -12491,15 +12491,15 @@
         <v>123</v>
       </c>
       <c r="C33" s="34"/>
-      <c r="D33" s="141"/>
-      <c r="E33" s="142"/>
-      <c r="F33" s="142"/>
-      <c r="G33" s="142"/>
-      <c r="H33" s="142"/>
-      <c r="I33" s="142"/>
-      <c r="J33" s="142"/>
-      <c r="K33" s="142"/>
-      <c r="L33" s="142"/>
+      <c r="D33" s="83"/>
+      <c r="E33" s="84"/>
+      <c r="F33" s="84"/>
+      <c r="G33" s="84"/>
+      <c r="H33" s="84"/>
+      <c r="I33" s="84"/>
+      <c r="J33" s="84"/>
+      <c r="K33" s="84"/>
+      <c r="L33" s="84"/>
     </row>
     <row r="34" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="33">
@@ -12509,15 +12509,15 @@
         <v>124</v>
       </c>
       <c r="C34" s="34"/>
-      <c r="D34" s="141"/>
-      <c r="E34" s="142"/>
-      <c r="F34" s="142"/>
-      <c r="G34" s="142"/>
-      <c r="H34" s="142"/>
-      <c r="I34" s="142"/>
-      <c r="J34" s="142"/>
-      <c r="K34" s="142"/>
-      <c r="L34" s="142"/>
+      <c r="D34" s="83"/>
+      <c r="E34" s="84"/>
+      <c r="F34" s="84"/>
+      <c r="G34" s="84"/>
+      <c r="H34" s="84"/>
+      <c r="I34" s="84"/>
+      <c r="J34" s="84"/>
+      <c r="K34" s="84"/>
+      <c r="L34" s="84"/>
     </row>
     <row r="35" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="33">
@@ -12527,15 +12527,15 @@
         <v>125</v>
       </c>
       <c r="C35" s="34"/>
-      <c r="D35" s="141"/>
-      <c r="E35" s="142"/>
-      <c r="F35" s="142"/>
-      <c r="G35" s="142"/>
-      <c r="H35" s="142"/>
-      <c r="I35" s="142"/>
-      <c r="J35" s="142"/>
-      <c r="K35" s="142"/>
-      <c r="L35" s="142"/>
+      <c r="D35" s="83"/>
+      <c r="E35" s="84"/>
+      <c r="F35" s="84"/>
+      <c r="G35" s="84"/>
+      <c r="H35" s="84"/>
+      <c r="I35" s="84"/>
+      <c r="J35" s="84"/>
+      <c r="K35" s="84"/>
+      <c r="L35" s="84"/>
     </row>
     <row r="36" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="33">
@@ -12545,15 +12545,15 @@
         <v>126</v>
       </c>
       <c r="C36" s="34"/>
-      <c r="D36" s="141"/>
-      <c r="E36" s="142"/>
-      <c r="F36" s="142"/>
-      <c r="G36" s="142"/>
-      <c r="H36" s="142"/>
-      <c r="I36" s="142"/>
-      <c r="J36" s="142"/>
-      <c r="K36" s="142"/>
-      <c r="L36" s="142"/>
+      <c r="D36" s="83"/>
+      <c r="E36" s="84"/>
+      <c r="F36" s="84"/>
+      <c r="G36" s="84"/>
+      <c r="H36" s="84"/>
+      <c r="I36" s="84"/>
+      <c r="J36" s="84"/>
+      <c r="K36" s="84"/>
+      <c r="L36" s="84"/>
     </row>
     <row r="37" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="33">
@@ -12563,15 +12563,15 @@
         <v>127</v>
       </c>
       <c r="C37" s="34"/>
-      <c r="D37" s="141"/>
-      <c r="E37" s="142"/>
-      <c r="F37" s="142"/>
-      <c r="G37" s="142"/>
-      <c r="H37" s="142"/>
-      <c r="I37" s="142"/>
-      <c r="J37" s="142"/>
-      <c r="K37" s="142"/>
-      <c r="L37" s="142"/>
+      <c r="D37" s="83"/>
+      <c r="E37" s="84"/>
+      <c r="F37" s="84"/>
+      <c r="G37" s="84"/>
+      <c r="H37" s="84"/>
+      <c r="I37" s="84"/>
+      <c r="J37" s="84"/>
+      <c r="K37" s="84"/>
+      <c r="L37" s="84"/>
     </row>
     <row r="38" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="33">
@@ -12581,15 +12581,15 @@
         <v>128</v>
       </c>
       <c r="C38" s="34"/>
-      <c r="D38" s="141"/>
-      <c r="E38" s="142"/>
-      <c r="F38" s="142"/>
-      <c r="G38" s="142"/>
-      <c r="H38" s="142"/>
-      <c r="I38" s="142"/>
-      <c r="J38" s="142"/>
-      <c r="K38" s="142"/>
-      <c r="L38" s="142"/>
+      <c r="D38" s="83"/>
+      <c r="E38" s="84"/>
+      <c r="F38" s="84"/>
+      <c r="G38" s="84"/>
+      <c r="H38" s="84"/>
+      <c r="I38" s="84"/>
+      <c r="J38" s="84"/>
+      <c r="K38" s="84"/>
+      <c r="L38" s="84"/>
     </row>
     <row r="39" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="33">
@@ -12599,15 +12599,15 @@
         <v>129</v>
       </c>
       <c r="C39" s="34"/>
-      <c r="D39" s="141"/>
-      <c r="E39" s="142"/>
-      <c r="F39" s="142"/>
-      <c r="G39" s="142"/>
-      <c r="H39" s="142"/>
-      <c r="I39" s="142"/>
-      <c r="J39" s="142"/>
-      <c r="K39" s="142"/>
-      <c r="L39" s="142"/>
+      <c r="D39" s="83"/>
+      <c r="E39" s="84"/>
+      <c r="F39" s="84"/>
+      <c r="G39" s="84"/>
+      <c r="H39" s="84"/>
+      <c r="I39" s="84"/>
+      <c r="J39" s="84"/>
+      <c r="K39" s="84"/>
+      <c r="L39" s="84"/>
     </row>
     <row r="40" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="33">
@@ -12617,15 +12617,15 @@
         <v>130</v>
       </c>
       <c r="C40" s="34"/>
-      <c r="D40" s="141"/>
-      <c r="E40" s="142"/>
-      <c r="F40" s="142"/>
-      <c r="G40" s="142"/>
-      <c r="H40" s="142"/>
-      <c r="I40" s="142"/>
-      <c r="J40" s="142"/>
-      <c r="K40" s="142"/>
-      <c r="L40" s="142"/>
+      <c r="D40" s="83"/>
+      <c r="E40" s="84"/>
+      <c r="F40" s="84"/>
+      <c r="G40" s="84"/>
+      <c r="H40" s="84"/>
+      <c r="I40" s="84"/>
+      <c r="J40" s="84"/>
+      <c r="K40" s="84"/>
+      <c r="L40" s="84"/>
     </row>
     <row r="41" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="33">
@@ -12635,15 +12635,15 @@
         <v>131</v>
       </c>
       <c r="C41" s="34"/>
-      <c r="D41" s="141"/>
-      <c r="E41" s="142"/>
-      <c r="F41" s="142"/>
-      <c r="G41" s="142"/>
-      <c r="H41" s="142"/>
-      <c r="I41" s="142"/>
-      <c r="J41" s="142"/>
-      <c r="K41" s="142"/>
-      <c r="L41" s="142"/>
+      <c r="D41" s="83"/>
+      <c r="E41" s="84"/>
+      <c r="F41" s="84"/>
+      <c r="G41" s="84"/>
+      <c r="H41" s="84"/>
+      <c r="I41" s="84"/>
+      <c r="J41" s="84"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="84"/>
     </row>
     <row r="42" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="33">
@@ -12653,15 +12653,15 @@
         <v>132</v>
       </c>
       <c r="C42" s="34"/>
-      <c r="D42" s="141"/>
-      <c r="E42" s="142"/>
-      <c r="F42" s="142"/>
-      <c r="G42" s="142"/>
-      <c r="H42" s="142"/>
-      <c r="I42" s="142"/>
-      <c r="J42" s="142"/>
-      <c r="K42" s="142"/>
-      <c r="L42" s="142"/>
+      <c r="D42" s="83"/>
+      <c r="E42" s="84"/>
+      <c r="F42" s="84"/>
+      <c r="G42" s="84"/>
+      <c r="H42" s="84"/>
+      <c r="I42" s="84"/>
+      <c r="J42" s="84"/>
+      <c r="K42" s="84"/>
+      <c r="L42" s="84"/>
     </row>
     <row r="43" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="33">
@@ -12671,15 +12671,15 @@
         <v>133</v>
       </c>
       <c r="C43" s="34"/>
-      <c r="D43" s="141"/>
-      <c r="E43" s="142"/>
-      <c r="F43" s="142"/>
-      <c r="G43" s="142"/>
-      <c r="H43" s="142"/>
-      <c r="I43" s="142"/>
-      <c r="J43" s="142"/>
-      <c r="K43" s="142"/>
-      <c r="L43" s="142"/>
+      <c r="D43" s="83"/>
+      <c r="E43" s="84"/>
+      <c r="F43" s="84"/>
+      <c r="G43" s="84"/>
+      <c r="H43" s="84"/>
+      <c r="I43" s="84"/>
+      <c r="J43" s="84"/>
+      <c r="K43" s="84"/>
+      <c r="L43" s="84"/>
     </row>
     <row r="44" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="33">
@@ -12689,15 +12689,15 @@
         <v>134</v>
       </c>
       <c r="C44" s="34"/>
-      <c r="D44" s="141"/>
-      <c r="E44" s="142"/>
-      <c r="F44" s="142"/>
-      <c r="G44" s="142"/>
-      <c r="H44" s="142"/>
-      <c r="I44" s="142"/>
-      <c r="J44" s="142"/>
-      <c r="K44" s="142"/>
-      <c r="L44" s="142"/>
+      <c r="D44" s="83"/>
+      <c r="E44" s="84"/>
+      <c r="F44" s="84"/>
+      <c r="G44" s="84"/>
+      <c r="H44" s="84"/>
+      <c r="I44" s="84"/>
+      <c r="J44" s="84"/>
+      <c r="K44" s="84"/>
+      <c r="L44" s="84"/>
     </row>
     <row r="45" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="33">
@@ -12707,15 +12707,15 @@
         <v>135</v>
       </c>
       <c r="C45" s="34"/>
-      <c r="D45" s="141"/>
-      <c r="E45" s="142"/>
-      <c r="F45" s="142"/>
-      <c r="G45" s="142"/>
-      <c r="H45" s="142"/>
-      <c r="I45" s="142"/>
-      <c r="J45" s="142"/>
-      <c r="K45" s="142"/>
-      <c r="L45" s="142"/>
+      <c r="D45" s="83"/>
+      <c r="E45" s="84"/>
+      <c r="F45" s="84"/>
+      <c r="G45" s="84"/>
+      <c r="H45" s="84"/>
+      <c r="I45" s="84"/>
+      <c r="J45" s="84"/>
+      <c r="K45" s="84"/>
+      <c r="L45" s="84"/>
     </row>
     <row r="46" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="33">
@@ -12725,15 +12725,15 @@
         <v>136</v>
       </c>
       <c r="C46" s="34"/>
-      <c r="D46" s="141"/>
-      <c r="E46" s="142"/>
-      <c r="F46" s="142"/>
-      <c r="G46" s="142"/>
-      <c r="H46" s="142"/>
-      <c r="I46" s="142"/>
-      <c r="J46" s="142"/>
-      <c r="K46" s="142"/>
-      <c r="L46" s="142"/>
+      <c r="D46" s="83"/>
+      <c r="E46" s="84"/>
+      <c r="F46" s="84"/>
+      <c r="G46" s="84"/>
+      <c r="H46" s="84"/>
+      <c r="I46" s="84"/>
+      <c r="J46" s="84"/>
+      <c r="K46" s="84"/>
+      <c r="L46" s="84"/>
     </row>
     <row r="47" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="33">
@@ -12743,15 +12743,15 @@
         <v>137</v>
       </c>
       <c r="C47" s="34"/>
-      <c r="D47" s="141"/>
-      <c r="E47" s="142"/>
-      <c r="F47" s="142"/>
-      <c r="G47" s="142"/>
-      <c r="H47" s="142"/>
-      <c r="I47" s="142"/>
-      <c r="J47" s="142"/>
-      <c r="K47" s="142"/>
-      <c r="L47" s="142"/>
+      <c r="D47" s="83"/>
+      <c r="E47" s="84"/>
+      <c r="F47" s="84"/>
+      <c r="G47" s="84"/>
+      <c r="H47" s="84"/>
+      <c r="I47" s="84"/>
+      <c r="J47" s="84"/>
+      <c r="K47" s="84"/>
+      <c r="L47" s="84"/>
     </row>
     <row r="48" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="33">
@@ -12761,15 +12761,15 @@
         <v>138</v>
       </c>
       <c r="C48" s="34"/>
-      <c r="D48" s="141"/>
-      <c r="E48" s="142"/>
-      <c r="F48" s="142"/>
-      <c r="G48" s="142"/>
-      <c r="H48" s="142"/>
-      <c r="I48" s="142"/>
-      <c r="J48" s="142"/>
-      <c r="K48" s="142"/>
-      <c r="L48" s="142"/>
+      <c r="D48" s="83"/>
+      <c r="E48" s="84"/>
+      <c r="F48" s="84"/>
+      <c r="G48" s="84"/>
+      <c r="H48" s="84"/>
+      <c r="I48" s="84"/>
+      <c r="J48" s="84"/>
+      <c r="K48" s="84"/>
+      <c r="L48" s="84"/>
     </row>
     <row r="49" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="33">
@@ -12779,15 +12779,15 @@
         <v>139</v>
       </c>
       <c r="C49" s="34"/>
-      <c r="D49" s="141"/>
-      <c r="E49" s="142"/>
-      <c r="F49" s="142"/>
-      <c r="G49" s="142"/>
-      <c r="H49" s="142"/>
-      <c r="I49" s="142"/>
-      <c r="J49" s="142"/>
-      <c r="K49" s="142"/>
-      <c r="L49" s="142"/>
+      <c r="D49" s="83"/>
+      <c r="E49" s="84"/>
+      <c r="F49" s="84"/>
+      <c r="G49" s="84"/>
+      <c r="H49" s="84"/>
+      <c r="I49" s="84"/>
+      <c r="J49" s="84"/>
+      <c r="K49" s="84"/>
+      <c r="L49" s="84"/>
     </row>
     <row r="50" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="72">
@@ -12797,15 +12797,15 @@
         <v>140</v>
       </c>
       <c r="C50" s="34"/>
-      <c r="D50" s="141"/>
-      <c r="E50" s="142"/>
-      <c r="F50" s="142"/>
-      <c r="G50" s="142"/>
-      <c r="H50" s="142"/>
-      <c r="I50" s="142"/>
-      <c r="J50" s="142"/>
-      <c r="K50" s="142"/>
-      <c r="L50" s="142"/>
+      <c r="D50" s="83"/>
+      <c r="E50" s="84"/>
+      <c r="F50" s="84"/>
+      <c r="G50" s="84"/>
+      <c r="H50" s="84"/>
+      <c r="I50" s="84"/>
+      <c r="J50" s="84"/>
+      <c r="K50" s="84"/>
+      <c r="L50" s="84"/>
     </row>
     <row r="51" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="72">
@@ -12815,15 +12815,15 @@
         <v>141</v>
       </c>
       <c r="C51" s="34"/>
-      <c r="D51" s="141"/>
-      <c r="E51" s="142"/>
-      <c r="F51" s="142"/>
-      <c r="G51" s="142"/>
-      <c r="H51" s="142"/>
-      <c r="I51" s="142"/>
-      <c r="J51" s="142"/>
-      <c r="K51" s="142"/>
-      <c r="L51" s="142"/>
+      <c r="D51" s="83"/>
+      <c r="E51" s="84"/>
+      <c r="F51" s="84"/>
+      <c r="G51" s="84"/>
+      <c r="H51" s="84"/>
+      <c r="I51" s="84"/>
+      <c r="J51" s="84"/>
+      <c r="K51" s="84"/>
+      <c r="L51" s="84"/>
     </row>
     <row r="52" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="72">
@@ -12833,15 +12833,15 @@
         <v>142</v>
       </c>
       <c r="C52" s="34"/>
-      <c r="D52" s="141"/>
-      <c r="E52" s="142"/>
-      <c r="F52" s="142"/>
-      <c r="G52" s="142"/>
-      <c r="H52" s="142"/>
-      <c r="I52" s="142"/>
-      <c r="J52" s="142"/>
-      <c r="K52" s="142"/>
-      <c r="L52" s="142"/>
+      <c r="D52" s="83"/>
+      <c r="E52" s="84"/>
+      <c r="F52" s="84"/>
+      <c r="G52" s="84"/>
+      <c r="H52" s="84"/>
+      <c r="I52" s="84"/>
+      <c r="J52" s="84"/>
+      <c r="K52" s="84"/>
+      <c r="L52" s="84"/>
     </row>
     <row r="53" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="72">
@@ -12851,15 +12851,15 @@
         <v>143</v>
       </c>
       <c r="C53" s="79"/>
-      <c r="D53" s="141"/>
-      <c r="E53" s="142"/>
-      <c r="F53" s="142"/>
-      <c r="G53" s="142"/>
-      <c r="H53" s="142"/>
-      <c r="I53" s="142"/>
-      <c r="J53" s="142"/>
-      <c r="K53" s="142"/>
-      <c r="L53" s="142"/>
+      <c r="D53" s="83"/>
+      <c r="E53" s="84"/>
+      <c r="F53" s="84"/>
+      <c r="G53" s="84"/>
+      <c r="H53" s="84"/>
+      <c r="I53" s="84"/>
+      <c r="J53" s="84"/>
+      <c r="K53" s="84"/>
+      <c r="L53" s="84"/>
     </row>
     <row r="54" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="72">
@@ -12869,15 +12869,15 @@
         <v>144</v>
       </c>
       <c r="C54" s="72"/>
-      <c r="D54" s="141"/>
-      <c r="E54" s="142"/>
-      <c r="F54" s="142"/>
-      <c r="G54" s="142"/>
-      <c r="H54" s="142"/>
-      <c r="I54" s="142"/>
-      <c r="J54" s="142"/>
-      <c r="K54" s="142"/>
-      <c r="L54" s="142"/>
+      <c r="D54" s="83"/>
+      <c r="E54" s="84"/>
+      <c r="F54" s="84"/>
+      <c r="G54" s="84"/>
+      <c r="H54" s="84"/>
+      <c r="I54" s="84"/>
+      <c r="J54" s="84"/>
+      <c r="K54" s="84"/>
+      <c r="L54" s="84"/>
     </row>
     <row r="55" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="72">
@@ -12887,15 +12887,15 @@
         <v>145</v>
       </c>
       <c r="C55" s="78"/>
-      <c r="D55" s="141"/>
-      <c r="E55" s="142"/>
-      <c r="F55" s="142"/>
-      <c r="G55" s="142"/>
-      <c r="H55" s="142"/>
-      <c r="I55" s="142"/>
-      <c r="J55" s="142"/>
-      <c r="K55" s="142"/>
-      <c r="L55" s="142"/>
+      <c r="D55" s="83"/>
+      <c r="E55" s="84"/>
+      <c r="F55" s="84"/>
+      <c r="G55" s="84"/>
+      <c r="H55" s="84"/>
+      <c r="I55" s="84"/>
+      <c r="J55" s="84"/>
+      <c r="K55" s="84"/>
+      <c r="L55" s="84"/>
     </row>
     <row r="56" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="72">
@@ -12905,15 +12905,15 @@
         <v>146</v>
       </c>
       <c r="C56" s="78"/>
-      <c r="D56" s="141"/>
-      <c r="E56" s="142"/>
-      <c r="F56" s="142"/>
-      <c r="G56" s="142"/>
-      <c r="H56" s="142"/>
-      <c r="I56" s="142"/>
-      <c r="J56" s="142"/>
-      <c r="K56" s="142"/>
-      <c r="L56" s="142"/>
+      <c r="D56" s="83"/>
+      <c r="E56" s="84"/>
+      <c r="F56" s="84"/>
+      <c r="G56" s="84"/>
+      <c r="H56" s="84"/>
+      <c r="I56" s="84"/>
+      <c r="J56" s="84"/>
+      <c r="K56" s="84"/>
+      <c r="L56" s="84"/>
     </row>
     <row r="57" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="72">
@@ -12923,15 +12923,15 @@
         <v>147</v>
       </c>
       <c r="C57" s="78"/>
-      <c r="D57" s="141"/>
-      <c r="E57" s="142"/>
-      <c r="F57" s="142"/>
-      <c r="G57" s="142"/>
-      <c r="H57" s="142"/>
-      <c r="I57" s="142"/>
-      <c r="J57" s="142"/>
-      <c r="K57" s="142"/>
-      <c r="L57" s="142"/>
+      <c r="D57" s="83"/>
+      <c r="E57" s="84"/>
+      <c r="F57" s="84"/>
+      <c r="G57" s="84"/>
+      <c r="H57" s="84"/>
+      <c r="I57" s="84"/>
+      <c r="J57" s="84"/>
+      <c r="K57" s="84"/>
+      <c r="L57" s="84"/>
     </row>
     <row r="58" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="72">
@@ -12941,15 +12941,15 @@
         <v>148</v>
       </c>
       <c r="C58" s="78"/>
-      <c r="D58" s="141"/>
-      <c r="E58" s="142"/>
-      <c r="F58" s="142"/>
-      <c r="G58" s="142"/>
-      <c r="H58" s="142"/>
-      <c r="I58" s="142"/>
-      <c r="J58" s="142"/>
-      <c r="K58" s="142"/>
-      <c r="L58" s="142"/>
+      <c r="D58" s="83"/>
+      <c r="E58" s="84"/>
+      <c r="F58" s="84"/>
+      <c r="G58" s="84"/>
+      <c r="H58" s="84"/>
+      <c r="I58" s="84"/>
+      <c r="J58" s="84"/>
+      <c r="K58" s="84"/>
+      <c r="L58" s="84"/>
     </row>
     <row r="59" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="72">
@@ -12959,15 +12959,15 @@
         <v>149</v>
       </c>
       <c r="C59" s="78"/>
-      <c r="D59" s="141"/>
-      <c r="E59" s="142"/>
-      <c r="F59" s="142"/>
-      <c r="G59" s="142"/>
-      <c r="H59" s="142"/>
-      <c r="I59" s="142"/>
-      <c r="J59" s="142"/>
-      <c r="K59" s="142"/>
-      <c r="L59" s="142"/>
+      <c r="D59" s="83"/>
+      <c r="E59" s="84"/>
+      <c r="F59" s="84"/>
+      <c r="G59" s="84"/>
+      <c r="H59" s="84"/>
+      <c r="I59" s="84"/>
+      <c r="J59" s="84"/>
+      <c r="K59" s="84"/>
+      <c r="L59" s="84"/>
     </row>
     <row r="60" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="72">
@@ -12977,15 +12977,15 @@
         <v>150</v>
       </c>
       <c r="C60" s="78"/>
-      <c r="D60" s="141"/>
-      <c r="E60" s="142"/>
-      <c r="F60" s="142"/>
-      <c r="G60" s="142"/>
-      <c r="H60" s="142"/>
-      <c r="I60" s="142"/>
-      <c r="J60" s="142"/>
-      <c r="K60" s="142"/>
-      <c r="L60" s="142"/>
+      <c r="D60" s="83"/>
+      <c r="E60" s="84"/>
+      <c r="F60" s="84"/>
+      <c r="G60" s="84"/>
+      <c r="H60" s="84"/>
+      <c r="I60" s="84"/>
+      <c r="J60" s="84"/>
+      <c r="K60" s="84"/>
+      <c r="L60" s="84"/>
     </row>
     <row r="61" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="72">
@@ -12995,15 +12995,15 @@
         <v>153</v>
       </c>
       <c r="C61" s="78"/>
-      <c r="D61" s="141"/>
-      <c r="E61" s="142"/>
-      <c r="F61" s="142"/>
-      <c r="G61" s="142"/>
-      <c r="H61" s="142"/>
-      <c r="I61" s="142"/>
-      <c r="J61" s="142"/>
-      <c r="K61" s="142"/>
-      <c r="L61" s="142"/>
+      <c r="D61" s="83"/>
+      <c r="E61" s="84"/>
+      <c r="F61" s="84"/>
+      <c r="G61" s="84"/>
+      <c r="H61" s="84"/>
+      <c r="I61" s="84"/>
+      <c r="J61" s="84"/>
+      <c r="K61" s="84"/>
+      <c r="L61" s="84"/>
     </row>
     <row r="62" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="72">
@@ -13013,15 +13013,15 @@
         <v>154</v>
       </c>
       <c r="C62" s="78"/>
-      <c r="D62" s="141"/>
-      <c r="E62" s="142"/>
-      <c r="F62" s="142"/>
-      <c r="G62" s="142"/>
-      <c r="H62" s="142"/>
-      <c r="I62" s="142"/>
-      <c r="J62" s="142"/>
-      <c r="K62" s="142"/>
-      <c r="L62" s="142"/>
+      <c r="D62" s="83"/>
+      <c r="E62" s="84"/>
+      <c r="F62" s="84"/>
+      <c r="G62" s="84"/>
+      <c r="H62" s="84"/>
+      <c r="I62" s="84"/>
+      <c r="J62" s="84"/>
+      <c r="K62" s="84"/>
+      <c r="L62" s="84"/>
     </row>
     <row r="63" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="72">
@@ -13031,15 +13031,15 @@
         <v>151</v>
       </c>
       <c r="C63" s="78"/>
-      <c r="D63" s="141"/>
-      <c r="E63" s="142"/>
-      <c r="F63" s="142"/>
-      <c r="G63" s="142"/>
-      <c r="H63" s="142"/>
-      <c r="I63" s="142"/>
-      <c r="J63" s="142"/>
-      <c r="K63" s="142"/>
-      <c r="L63" s="142"/>
+      <c r="D63" s="83"/>
+      <c r="E63" s="84"/>
+      <c r="F63" s="84"/>
+      <c r="G63" s="84"/>
+      <c r="H63" s="84"/>
+      <c r="I63" s="84"/>
+      <c r="J63" s="84"/>
+      <c r="K63" s="84"/>
+      <c r="L63" s="84"/>
     </row>
     <row r="64" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="72">
@@ -13049,15 +13049,15 @@
         <v>152</v>
       </c>
       <c r="C64" s="78"/>
-      <c r="D64" s="141"/>
-      <c r="E64" s="142"/>
-      <c r="F64" s="142"/>
-      <c r="G64" s="142"/>
-      <c r="H64" s="142"/>
-      <c r="I64" s="142"/>
-      <c r="J64" s="142"/>
-      <c r="K64" s="142"/>
-      <c r="L64" s="142"/>
+      <c r="D64" s="83"/>
+      <c r="E64" s="84"/>
+      <c r="F64" s="84"/>
+      <c r="G64" s="84"/>
+      <c r="H64" s="84"/>
+      <c r="I64" s="84"/>
+      <c r="J64" s="84"/>
+      <c r="K64" s="84"/>
+      <c r="L64" s="84"/>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="80">
@@ -13067,26 +13067,18 @@
         <v>155</v>
       </c>
       <c r="C65" s="78"/>
-      <c r="D65" s="141"/>
-      <c r="E65" s="142"/>
-      <c r="F65" s="142"/>
-      <c r="G65" s="142"/>
-      <c r="H65" s="142"/>
-      <c r="I65" s="142"/>
-      <c r="J65" s="142"/>
-      <c r="K65" s="142"/>
-      <c r="L65" s="142"/>
+      <c r="D65" s="83"/>
+      <c r="E65" s="84"/>
+      <c r="F65" s="84"/>
+      <c r="G65" s="84"/>
+      <c r="H65" s="84"/>
+      <c r="I65" s="84"/>
+      <c r="J65" s="84"/>
+      <c r="K65" s="84"/>
+      <c r="L65" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="D26:L65"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:L20"/>
-    <mergeCell ref="D25:L25"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:L22"/>
     <mergeCell ref="A16:L16"/>
     <mergeCell ref="A17:L17"/>
     <mergeCell ref="B15:L15"/>
@@ -13098,6 +13090,14 @@
     <mergeCell ref="B4:L4"/>
     <mergeCell ref="B5:L5"/>
     <mergeCell ref="B7:L7"/>
+    <mergeCell ref="D26:L65"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:L20"/>
+    <mergeCell ref="D25:L25"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:L22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D26" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -16525,17 +16525,17 @@
       <c r="C12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="123" t="s">
+      <c r="D12" s="93" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="123"/>
-      <c r="F12" s="123"/>
-      <c r="G12" s="123"/>
-      <c r="H12" s="123"/>
-      <c r="I12" s="123"/>
-      <c r="J12" s="123"/>
-      <c r="K12" s="123"/>
-      <c r="L12" s="123"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="93"/>
+      <c r="K12" s="93"/>
+      <c r="L12" s="93"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="49"/>
@@ -17443,56 +17443,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50">
-      <UserInfo>
-        <DisplayName>Luis Campos / Logiztik Alliance</DisplayName>
-        <AccountId>265</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Jairo Gonzalez / Logiztik Alliance</DisplayName>
-        <AccountId>322</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>José Ganchozo / Logiztik Alliance</DisplayName>
-        <AccountId>304</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Edwin Casa / Logiztik Alliance</DisplayName>
-        <AccountId>299</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Cristhian Cuichan / Logiztik Alliance</DisplayName>
-        <AccountId>369</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Oscar Yunda /  Logiztik Alliance</DisplayName>
-        <AccountId>355</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Fernando Ordoñez / Logiztik Alliance</DisplayName>
-        <AccountId>321</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Alex Rivera / Logiztik Alliance</DisplayName>
-        <AccountId>370</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <TaxCatchAll xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="87481c51-c14c-4071-bf64-faa2b5708bb6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17745,21 +17701,62 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50">
+      <UserInfo>
+        <DisplayName>Luis Campos / Logiztik Alliance</DisplayName>
+        <AccountId>265</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Jairo Gonzalez / Logiztik Alliance</DisplayName>
+        <AccountId>322</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>José Ganchozo / Logiztik Alliance</DisplayName>
+        <AccountId>304</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Edwin Casa / Logiztik Alliance</DisplayName>
+        <AccountId>299</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Cristhian Cuichan / Logiztik Alliance</DisplayName>
+        <AccountId>369</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Oscar Yunda /  Logiztik Alliance</DisplayName>
+        <AccountId>355</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Fernando Ordoñez / Logiztik Alliance</DisplayName>
+        <AccountId>321</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Alex Rivera / Logiztik Alliance</DisplayName>
+        <AccountId>370</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <TaxCatchAll xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="87481c51-c14c-4071-bf64-faa2b5708bb6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD069904-634F-48DA-AA92-BAE250498BEE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371D8832-41B3-447B-B13D-2663C267E34F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8029d101-3d2a-47c4-b15f-619642bf5e50"/>
-    <ds:schemaRef ds:uri="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -17784,9 +17781,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371D8832-41B3-447B-B13D-2663C267E34F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD069904-634F-48DA-AA92-BAE250498BEE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8029d101-3d2a-47c4-b15f-619642bf5e50"/>
+    <ds:schemaRef ds:uri="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Guias Produccion/HU-57723.xlsx
+++ b/Guias Produccion/HU-57723.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Alliance\ScriptsEntidades\Guias Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDAF6402-1753-4DB9-B79D-DB6F146EC683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA7E2A6E-9941-4833-A1A4-8BCD32696C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="157">
   <si>
     <t>Guia documentación</t>
   </si>
@@ -525,112 +525,115 @@
     <t>04-f_SearchEntities.sql</t>
   </si>
   <si>
-    <t>05-AC_pro_General_GenerateBulkInt.sql</t>
+    <t>05-f_GetClientsEntities.sql</t>
   </si>
   <si>
-    <t>06-AC_pro_GetMachineShipments.sql</t>
+    <t>06-AC_pro_General_GenerateBulkInt.sql</t>
   </si>
   <si>
-    <t>07-AC_pro_GetClientsPiecesDetails.sql</t>
+    <t>07-AC_pro_GetMachineShipments.sql</t>
   </si>
   <si>
-    <t>08-AC_pro_GetDispatchesByCarrier.sql</t>
+    <t>08-AC_pro_GetClientsPiecesDetails.sql</t>
   </si>
   <si>
-    <t>09-AC_pro_GetClientsEntities.sql</t>
+    <t>09-AC_pro_GetDispatchesByCarrier.sql</t>
   </si>
   <si>
-    <t>10-AC_pro_GetClientsPiecesBySubCarrier.sql</t>
+    <t>10-AC_pro_GetClientsEntities.sql</t>
   </si>
   <si>
-    <t>11-AC_pro_GetDispatchesByClient.sql</t>
+    <t>11-AC_pro_GetClientsPiecesBySubCarrier.sql</t>
   </si>
   <si>
-    <t>12-AC_pro_GetLocalOrdersByEmployee.sql</t>
+    <t>12-AC_pro_GetDispatchesByClient.sql</t>
   </si>
   <si>
-    <t>13-AC_pro_ManageGuiasHouseDetallesEditedOrder.sql</t>
+    <t>13-AC_pro_GetLocalOrdersByEmployee.sql</t>
   </si>
   <si>
-    <t>14-AC_pro_ListCarrierProgramming.sql</t>
+    <t>14-AC_pro_ManageGuiasHouseDetallesEditedOrder.sql</t>
   </si>
   <si>
-    <t>15-AC_pro_ConfirmLocalOrderCoordination.sql</t>
+    <t>15-AC_pro_ListCarrierProgramming.sql</t>
   </si>
   <si>
-    <t>16-AC_pro_ConfirmLocalOrder.sql</t>
+    <t>16-AC_pro_ConfirmLocalOrderCoordination.sql</t>
   </si>
   <si>
-    <t>17-AC_pro_ShippingDocumentsPODClient360.sql</t>
+    <t>17-AC_pro_ConfirmLocalOrder.sql</t>
   </si>
   <si>
-    <t>18-AC_pro_ModuleEdiDetail.sql</t>
+    <t>18-AC_pro_ShippingDocumentsPODClient360.sql</t>
   </si>
   <si>
-    <t>19-AC_pro_Module_Edi.sql</t>
+    <t>19-AC_pro_ModuleEdiDetail.sql</t>
   </si>
   <si>
-    <t>20-AC_pro_ListPiecesInventory.sql</t>
+    <t>20-AC_pro_Module_Edi.sql</t>
   </si>
   <si>
-    <t>21-AC_pro_GetBarCodeLinks.sql</t>
+    <t>21-AC_pro_ListPiecesInventory.sql</t>
   </si>
   <si>
-    <t>22-AC_pro_LargeLabelTempDefault.sql</t>
+    <t>22-AC_pro_GetBarCodeLinks.sql</t>
   </si>
   <si>
-    <t>23-AC_pro_GetDispatchReports.sql</t>
+    <t>23-AC_pro_LargeLabelTempDefault.sql</t>
   </si>
   <si>
-    <t>24-AC_pro_GetShipmentAnalyticsReports.sql</t>
+    <t>24-AC_pro_GetDispatchReports.sql</t>
   </si>
   <si>
-    <t>25-AC_pro_GetListOFCycleCounts.sql</t>
+    <t>25-AC_pro_GetShipmentAnalyticsReports.sql</t>
   </si>
   <si>
-    <t>26-AC_pro_GetCycleCountDiscrepancies.sql</t>
+    <t>26-AC_pro_GetListOFCycleCounts.sql</t>
   </si>
   <si>
-    <t>27-AC_pro_CycleCountDiscrepanciesReport.sql</t>
+    <t>27-AC_pro_GetCycleCountDiscrepancies.sql</t>
   </si>
   <si>
-    <t>28-AC_pro_GetConsolidatedDispatchAnalytics.sql</t>
+    <t>28-AC_pro_CycleCountDiscrepanciesReport.sql</t>
   </si>
   <si>
-    <t>29-AC_pro_GetAccountingAnalyticsReports.sql</t>
+    <t>29-AC_pro_GetConsolidatedDispatchAnalytics.sql</t>
   </si>
   <si>
-    <t>30-AC_pro_GetSalesOrders.sql</t>
+    <t>30-AC_pro_GetAccountingAnalyticsReports.sql</t>
   </si>
   <si>
-    <t>31-AC_pro_GetDispatchReports.sql</t>
+    <t>31-AC_pro_GetSalesOrders.sql</t>
   </si>
   <si>
-    <t>32-AC_pro_GetCompletedScheduledPickupShipTo.sql</t>
+    <t>32-AC_pro_GetDispatchReports.sql</t>
   </si>
   <si>
-    <t>33-AC_pro_GetCompletedDeliveredPickupShipTo.sql</t>
+    <t>33-AC_pro_GetCompletedScheduledPickupShipTo.sql</t>
   </si>
   <si>
-    <t>34-AC_pro_GetPendingPickup.sql</t>
+    <t>34-AC_pro_GetCompletedDeliveredPickupShipTo.sql</t>
   </si>
   <si>
-    <t>35-AC_pro_GetPendingPickupDetails.sql</t>
+    <t>35-AC_pro_GetPendingPickup.sql</t>
   </si>
   <si>
-    <t>38-AC_pro_GetCompletedDeliveredPickupDetail.sql</t>
+    <t>36-AC_pro_GetPendingPickupDetails.sql</t>
   </si>
   <si>
-    <t>39-AC_pro_GetCompletedScheduledPickupDetail.sql</t>
+    <t>37-AC_pro_GetCompletedDeliveredPickupShipTo.sql</t>
   </si>
   <si>
-    <t>36-AC_pro_GetCompletedDeliveredPickupShipTo.sql</t>
+    <t>38-AC_pro_GetCompletedScheduledPickupShipTo.sql</t>
   </si>
   <si>
-    <t>37-AC_pro_GetCompletedScheduledPickupShipTo.sql</t>
+    <t>39-AC_pro_GetCompletedDeliveredPickupDetail.sql</t>
   </si>
   <si>
-    <t>40-AC_pro_InsertAccountingClient.sql</t>
+    <t>40-AC_pro_GetCompletedScheduledPickupDetail.sql</t>
+  </si>
+  <si>
+    <t>41-AC_pro_InsertAccountingClient.sql</t>
   </si>
 </sst>
 </file>
@@ -850,7 +853,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="79">
+  <borders count="78">
     <border>
       <left/>
       <right/>
@@ -1835,23 +1838,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2004,9 +1996,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="75" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="76" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="77" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2519,10 +2508,14 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp146.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$25" noThreeD="1" sel="17" val="12"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp147.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$17" noThreeD="1" sel="17" val="9"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp147.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp148.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$17" noThreeD="1" sel="17" val="9"/>
 </file>
 
@@ -2964,13 +2957,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -3022,13 +3015,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -3080,13 +3073,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -3138,13 +3131,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -3196,13 +3189,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -3254,13 +3247,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -3312,13 +3305,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -3370,13 +3363,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -3428,13 +3421,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -3486,13 +3479,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -3544,13 +3537,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -3602,13 +3595,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -3660,13 +3653,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -3718,13 +3711,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -3776,13 +3769,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -3834,13 +3827,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -3892,13 +3885,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -3950,13 +3943,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -4008,13 +4001,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -4066,13 +4059,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -4124,13 +4117,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -4182,13 +4175,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -4240,13 +4233,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -4298,13 +4291,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -4356,13 +4349,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -4414,13 +4407,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -4472,13 +4465,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -4530,13 +4523,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -4588,13 +4581,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -4646,13 +4639,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -4704,13 +4697,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -4762,13 +4755,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -4820,13 +4813,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -4878,13 +4871,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -4936,13 +4929,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -4994,13 +4987,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -5052,13 +5045,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -5110,13 +5103,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -5168,13 +5161,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -5226,13 +5219,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -5284,13 +5277,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -5342,13 +5335,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -5400,13 +5393,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -5458,13 +5451,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -5516,13 +5509,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -5574,13 +5567,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -5632,13 +5625,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -5690,13 +5683,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -5748,13 +5741,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -5806,13 +5799,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -5864,13 +5857,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -5922,13 +5915,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -5980,13 +5973,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -6038,13 +6031,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -6096,13 +6089,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -6154,13 +6147,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -6212,13 +6205,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -6270,13 +6263,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -6328,13 +6321,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -6386,13 +6379,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -6444,13 +6437,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -6502,13 +6495,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -6560,13 +6553,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -6618,13 +6611,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -6676,13 +6669,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -6734,13 +6727,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -6792,13 +6785,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -6850,13 +6843,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -6908,13 +6901,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -6966,13 +6959,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -7024,13 +7017,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -7082,13 +7075,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -7140,13 +7133,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -7198,13 +7191,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -7256,13 +7249,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -7314,13 +7307,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -7372,13 +7365,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -7430,13 +7423,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -7488,13 +7481,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -7546,13 +7539,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -7604,13 +7597,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -7662,13 +7655,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -7720,13 +7713,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -7778,13 +7771,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -7836,13 +7829,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -7894,13 +7887,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -7952,13 +7945,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -8010,13 +8003,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -8068,13 +8061,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -8126,13 +8119,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -8184,13 +8177,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -8242,13 +8235,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -8300,13 +8293,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -8358,13 +8351,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -8416,13 +8409,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -8474,13 +8467,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -8532,13 +8525,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -8590,13 +8583,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -8648,13 +8641,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -8706,13 +8699,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -8764,13 +8757,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -8822,13 +8815,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -8880,13 +8873,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -8938,13 +8931,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -8996,13 +8989,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -9054,13 +9047,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -9286,13 +9279,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>228600</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -9344,13 +9337,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>228600</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -9402,13 +9395,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>228600</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -9460,13 +9453,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>228600</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -9518,13 +9511,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>228600</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -9576,13 +9569,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>228600</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -9634,13 +9627,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -9692,13 +9685,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -9750,13 +9743,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -9808,13 +9801,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -9866,13 +9859,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -9924,13 +9917,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -9982,13 +9975,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -10040,13 +10033,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>44</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>44</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -10098,13 +10091,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>45</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>45</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -10156,13 +10149,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>46</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>46</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -10214,13 +10207,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>47</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>47</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -10272,13 +10265,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>47</xdr:row>
+          <xdr:row>48</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>47</xdr:row>
+          <xdr:row>48</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -10330,13 +10323,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>48</xdr:row>
+          <xdr:row>49</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>48</xdr:row>
+          <xdr:row>49</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -10388,13 +10381,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>49</xdr:row>
+          <xdr:row>50</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>49</xdr:row>
+          <xdr:row>50</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -10446,13 +10439,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>50</xdr:row>
+          <xdr:row>51</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>50</xdr:row>
+          <xdr:row>51</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -10504,13 +10497,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>51</xdr:row>
+          <xdr:row>52</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>51</xdr:row>
+          <xdr:row>52</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -10562,13 +10555,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>52</xdr:row>
+          <xdr:row>53</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>52</xdr:row>
+          <xdr:row>53</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -10620,13 +10613,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>53</xdr:row>
+          <xdr:row>54</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>53</xdr:row>
+          <xdr:row>54</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -10678,13 +10671,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>54</xdr:row>
+          <xdr:row>55</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>54</xdr:row>
+          <xdr:row>55</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -10736,13 +10729,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>55</xdr:row>
+          <xdr:row>56</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>55</xdr:row>
+          <xdr:row>56</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -10794,13 +10787,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>56</xdr:row>
+          <xdr:row>57</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>56</xdr:row>
+          <xdr:row>57</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -10852,13 +10845,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>57</xdr:row>
+          <xdr:row>58</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>57</xdr:row>
+          <xdr:row>58</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -10910,13 +10903,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>58</xdr:row>
+          <xdr:row>59</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>58</xdr:row>
+          <xdr:row>59</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -10968,13 +10961,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>59</xdr:row>
+          <xdr:row>60</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>59</xdr:row>
+          <xdr:row>60</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -11026,13 +11019,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>60</xdr:row>
+          <xdr:row>61</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>60</xdr:row>
+          <xdr:row>61</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -11084,13 +11077,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>61</xdr:row>
+          <xdr:row>62</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>61</xdr:row>
+          <xdr:row>62</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -11142,13 +11135,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>62</xdr:row>
+          <xdr:row>63</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>62</xdr:row>
+          <xdr:row>63</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -11200,13 +11193,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>63</xdr:row>
+          <xdr:row>64</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>63</xdr:row>
+          <xdr:row>64</xdr:row>
           <xdr:rowOff>220980</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -11258,13 +11251,13 @@
         <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>64</xdr:row>
+          <xdr:row>65</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>65</xdr:row>
+          <xdr:row>66</xdr:row>
           <xdr:rowOff>38100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -11276,6 +11269,64 @@
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000DF040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>1409700</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>228600</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1248" name="Drop Down 224" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1248"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000E0040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -11901,7 +11952,7 @@
   <sheetPr codeName="Hoja1">
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A3:O65"/>
+  <dimension ref="A3:O66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.44140625" bestFit="1" customWidth="1"/>
@@ -11920,42 +11971,42 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:15" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="125" t="s">
+      <c r="A3" s="124" t="s">
         <v>103</v>
       </c>
-      <c r="B3" s="126"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="126"/>
-      <c r="E3" s="126"/>
-      <c r="F3" s="126"/>
-      <c r="G3" s="126"/>
-      <c r="H3" s="126"/>
-      <c r="I3" s="126"/>
-      <c r="J3" s="126"/>
-      <c r="K3" s="126"/>
-      <c r="L3" s="127"/>
-      <c r="N3" s="119" t="s">
+      <c r="B3" s="125"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="125"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="126"/>
+      <c r="N3" s="118" t="s">
         <v>0</v>
       </c>
-      <c r="O3" s="120"/>
+      <c r="O3" s="119"/>
     </row>
     <row r="4" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="132" t="s">
+      <c r="B4" s="131" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="133"/>
-      <c r="D4" s="133"/>
-      <c r="E4" s="133"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="133"/>
-      <c r="H4" s="133"/>
-      <c r="I4" s="133"/>
-      <c r="J4" s="134"/>
-      <c r="K4" s="134"/>
-      <c r="L4" s="135"/>
+      <c r="C4" s="132"/>
+      <c r="D4" s="132"/>
+      <c r="E4" s="132"/>
+      <c r="F4" s="132"/>
+      <c r="G4" s="132"/>
+      <c r="H4" s="132"/>
+      <c r="I4" s="132"/>
+      <c r="J4" s="133"/>
+      <c r="K4" s="133"/>
+      <c r="L4" s="134"/>
       <c r="N4" s="21" t="s">
         <v>2</v>
       </c>
@@ -11965,19 +12016,19 @@
       <c r="A5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="136" t="s">
+      <c r="B5" s="135" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="136"/>
-      <c r="D5" s="136"/>
-      <c r="E5" s="136"/>
-      <c r="F5" s="136"/>
-      <c r="G5" s="136"/>
-      <c r="H5" s="136"/>
-      <c r="I5" s="136"/>
-      <c r="J5" s="137"/>
-      <c r="K5" s="137"/>
-      <c r="L5" s="138"/>
+      <c r="C5" s="135"/>
+      <c r="D5" s="135"/>
+      <c r="E5" s="135"/>
+      <c r="F5" s="135"/>
+      <c r="G5" s="135"/>
+      <c r="H5" s="135"/>
+      <c r="I5" s="135"/>
+      <c r="J5" s="136"/>
+      <c r="K5" s="136"/>
+      <c r="L5" s="137"/>
       <c r="N5" s="15" t="s">
         <v>4</v>
       </c>
@@ -11987,19 +12038,19 @@
       <c r="A6" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="122">
+      <c r="B6" s="121">
         <v>46073</v>
       </c>
-      <c r="C6" s="123"/>
-      <c r="D6" s="123"/>
-      <c r="E6" s="123"/>
-      <c r="F6" s="123"/>
-      <c r="G6" s="123"/>
-      <c r="H6" s="123"/>
-      <c r="I6" s="123"/>
-      <c r="J6" s="123"/>
-      <c r="K6" s="123"/>
-      <c r="L6" s="124"/>
+      <c r="C6" s="122"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="122"/>
+      <c r="F6" s="122"/>
+      <c r="G6" s="122"/>
+      <c r="H6" s="122"/>
+      <c r="I6" s="122"/>
+      <c r="J6" s="122"/>
+      <c r="K6" s="122"/>
+      <c r="L6" s="123"/>
       <c r="N6" s="14"/>
       <c r="O6" s="14"/>
     </row>
@@ -12007,17 +12058,17 @@
       <c r="A7" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="139"/>
-      <c r="C7" s="140"/>
-      <c r="D7" s="140"/>
-      <c r="E7" s="140"/>
-      <c r="F7" s="140"/>
-      <c r="G7" s="140"/>
-      <c r="H7" s="140"/>
-      <c r="I7" s="140"/>
-      <c r="J7" s="141"/>
-      <c r="K7" s="141"/>
-      <c r="L7" s="142"/>
+      <c r="B7" s="138"/>
+      <c r="C7" s="139"/>
+      <c r="D7" s="139"/>
+      <c r="E7" s="139"/>
+      <c r="F7" s="139"/>
+      <c r="G7" s="139"/>
+      <c r="H7" s="139"/>
+      <c r="I7" s="139"/>
+      <c r="J7" s="140"/>
+      <c r="K7" s="140"/>
+      <c r="L7" s="141"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
@@ -12034,20 +12085,20 @@
       <c r="L8" s="13"/>
     </row>
     <row r="9" spans="1:15" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="128" t="s">
+      <c r="A9" s="127" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="129"/>
-      <c r="C9" s="129"/>
-      <c r="D9" s="129"/>
-      <c r="E9" s="129"/>
-      <c r="F9" s="129"/>
-      <c r="G9" s="129"/>
-      <c r="H9" s="129"/>
-      <c r="I9" s="129"/>
-      <c r="J9" s="130"/>
-      <c r="K9" s="130"/>
-      <c r="L9" s="131"/>
+      <c r="B9" s="128"/>
+      <c r="C9" s="128"/>
+      <c r="D9" s="128"/>
+      <c r="E9" s="128"/>
+      <c r="F9" s="128"/>
+      <c r="G9" s="128"/>
+      <c r="H9" s="128"/>
+      <c r="I9" s="128"/>
+      <c r="J9" s="129"/>
+      <c r="K9" s="129"/>
+      <c r="L9" s="130"/>
     </row>
     <row r="10" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -12147,63 +12198,63 @@
       <c r="A14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="121"/>
-      <c r="C14" s="117"/>
-      <c r="D14" s="117"/>
-      <c r="E14" s="117"/>
-      <c r="F14" s="117"/>
-      <c r="G14" s="117"/>
-      <c r="H14" s="117"/>
-      <c r="I14" s="117"/>
-      <c r="J14" s="117"/>
-      <c r="K14" s="117"/>
-      <c r="L14" s="118"/>
+      <c r="B14" s="120"/>
+      <c r="C14" s="116"/>
+      <c r="D14" s="116"/>
+      <c r="E14" s="116"/>
+      <c r="F14" s="116"/>
+      <c r="G14" s="116"/>
+      <c r="H14" s="116"/>
+      <c r="I14" s="116"/>
+      <c r="J14" s="116"/>
+      <c r="K14" s="116"/>
+      <c r="L14" s="117"/>
     </row>
     <row r="15" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="116"/>
-      <c r="C15" s="117"/>
-      <c r="D15" s="117"/>
-      <c r="E15" s="117"/>
-      <c r="F15" s="117"/>
-      <c r="G15" s="117"/>
-      <c r="H15" s="117"/>
-      <c r="I15" s="117"/>
-      <c r="J15" s="117"/>
-      <c r="K15" s="117"/>
-      <c r="L15" s="118"/>
+      <c r="B15" s="115"/>
+      <c r="C15" s="116"/>
+      <c r="D15" s="116"/>
+      <c r="E15" s="116"/>
+      <c r="F15" s="116"/>
+      <c r="G15" s="116"/>
+      <c r="H15" s="116"/>
+      <c r="I15" s="116"/>
+      <c r="J15" s="116"/>
+      <c r="K15" s="116"/>
+      <c r="L15" s="117"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="109"/>
-      <c r="B16" s="110"/>
-      <c r="C16" s="110"/>
-      <c r="D16" s="110"/>
-      <c r="E16" s="110"/>
-      <c r="F16" s="110"/>
-      <c r="G16" s="110"/>
-      <c r="H16" s="110"/>
-      <c r="I16" s="110"/>
-      <c r="J16" s="110"/>
-      <c r="K16" s="110"/>
-      <c r="L16" s="111"/>
+      <c r="A16" s="108"/>
+      <c r="B16" s="109"/>
+      <c r="C16" s="109"/>
+      <c r="D16" s="109"/>
+      <c r="E16" s="109"/>
+      <c r="F16" s="109"/>
+      <c r="G16" s="109"/>
+      <c r="H16" s="109"/>
+      <c r="I16" s="109"/>
+      <c r="J16" s="109"/>
+      <c r="K16" s="109"/>
+      <c r="L16" s="110"/>
     </row>
     <row r="17" spans="1:12" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="112" t="s">
+      <c r="A17" s="111" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="113"/>
-      <c r="C17" s="113"/>
-      <c r="D17" s="113"/>
-      <c r="E17" s="113"/>
-      <c r="F17" s="113"/>
-      <c r="G17" s="113"/>
-      <c r="H17" s="113"/>
-      <c r="I17" s="113"/>
-      <c r="J17" s="114"/>
-      <c r="K17" s="114"/>
-      <c r="L17" s="115"/>
+      <c r="B17" s="112"/>
+      <c r="C17" s="112"/>
+      <c r="D17" s="112"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="112"/>
+      <c r="H17" s="112"/>
+      <c r="I17" s="112"/>
+      <c r="J17" s="113"/>
+      <c r="K17" s="113"/>
+      <c r="L17" s="114"/>
     </row>
     <row r="18" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
@@ -12213,19 +12264,19 @@
       <c r="C18" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="85" t="s">
+      <c r="D18" s="84" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="87" t="s">
+      <c r="E18" s="86" t="s">
         <v>115</v>
       </c>
-      <c r="F18" s="87"/>
-      <c r="G18" s="87"/>
-      <c r="H18" s="87"/>
-      <c r="I18" s="87"/>
-      <c r="J18" s="88"/>
-      <c r="K18" s="88"/>
-      <c r="L18" s="89"/>
+      <c r="F18" s="86"/>
+      <c r="G18" s="86"/>
+      <c r="H18" s="86"/>
+      <c r="I18" s="86"/>
+      <c r="J18" s="87"/>
+      <c r="K18" s="87"/>
+      <c r="L18" s="88"/>
     </row>
     <row r="19" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
@@ -12235,15 +12286,15 @@
         <v>30</v>
       </c>
       <c r="C19" s="44"/>
-      <c r="D19" s="86"/>
-      <c r="E19" s="90"/>
-      <c r="F19" s="90"/>
-      <c r="G19" s="90"/>
-      <c r="H19" s="90"/>
-      <c r="I19" s="90"/>
-      <c r="J19" s="91"/>
-      <c r="K19" s="91"/>
-      <c r="L19" s="92"/>
+      <c r="D19" s="85"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="89"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="90"/>
+      <c r="K19" s="90"/>
+      <c r="L19" s="91"/>
     </row>
     <row r="20" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
@@ -12253,15 +12304,15 @@
       <c r="C20" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="86"/>
-      <c r="E20" s="90"/>
-      <c r="F20" s="90"/>
-      <c r="G20" s="90"/>
-      <c r="H20" s="90"/>
-      <c r="I20" s="90"/>
-      <c r="J20" s="91"/>
-      <c r="K20" s="91"/>
-      <c r="L20" s="92"/>
+      <c r="D20" s="85"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="89"/>
+      <c r="I20" s="89"/>
+      <c r="J20" s="90"/>
+      <c r="K20" s="90"/>
+      <c r="L20" s="91"/>
     </row>
     <row r="21" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
@@ -12271,19 +12322,19 @@
       <c r="C21" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="101" t="s">
+      <c r="D21" s="100" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="103" t="s">
+      <c r="E21" s="102" t="s">
         <v>107</v>
       </c>
-      <c r="F21" s="104"/>
-      <c r="G21" s="104"/>
-      <c r="H21" s="104"/>
-      <c r="I21" s="104"/>
-      <c r="J21" s="104"/>
-      <c r="K21" s="104"/>
-      <c r="L21" s="105"/>
+      <c r="F21" s="103"/>
+      <c r="G21" s="103"/>
+      <c r="H21" s="103"/>
+      <c r="I21" s="103"/>
+      <c r="J21" s="103"/>
+      <c r="K21" s="103"/>
+      <c r="L21" s="104"/>
     </row>
     <row r="22" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
@@ -12293,45 +12344,45 @@
       <c r="C22" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="102"/>
-      <c r="E22" s="106"/>
-      <c r="F22" s="107"/>
-      <c r="G22" s="107"/>
-      <c r="H22" s="107"/>
-      <c r="I22" s="107"/>
-      <c r="J22" s="107"/>
-      <c r="K22" s="107"/>
-      <c r="L22" s="108"/>
+      <c r="D22" s="101"/>
+      <c r="E22" s="105"/>
+      <c r="F22" s="106"/>
+      <c r="G22" s="106"/>
+      <c r="H22" s="106"/>
+      <c r="I22" s="106"/>
+      <c r="J22" s="106"/>
+      <c r="K22" s="106"/>
+      <c r="L22" s="107"/>
     </row>
     <row r="23" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="94"/>
-      <c r="B23" s="95"/>
-      <c r="C23" s="95"/>
-      <c r="D23" s="96"/>
-      <c r="E23" s="96"/>
-      <c r="F23" s="96"/>
-      <c r="G23" s="96"/>
-      <c r="H23" s="96"/>
-      <c r="I23" s="96"/>
-      <c r="J23" s="96"/>
-      <c r="K23" s="96"/>
-      <c r="L23" s="97"/>
+      <c r="A23" s="93"/>
+      <c r="B23" s="94"/>
+      <c r="C23" s="94"/>
+      <c r="D23" s="95"/>
+      <c r="E23" s="95"/>
+      <c r="F23" s="95"/>
+      <c r="G23" s="95"/>
+      <c r="H23" s="95"/>
+      <c r="I23" s="95"/>
+      <c r="J23" s="95"/>
+      <c r="K23" s="95"/>
+      <c r="L23" s="96"/>
     </row>
     <row r="24" spans="1:12" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="98" t="s">
+      <c r="A24" s="97" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="99"/>
-      <c r="C24" s="99"/>
-      <c r="D24" s="99"/>
-      <c r="E24" s="99"/>
-      <c r="F24" s="99"/>
-      <c r="G24" s="99"/>
-      <c r="H24" s="99"/>
-      <c r="I24" s="99"/>
-      <c r="J24" s="99"/>
-      <c r="K24" s="99"/>
-      <c r="L24" s="100"/>
+      <c r="B24" s="98"/>
+      <c r="C24" s="98"/>
+      <c r="D24" s="98"/>
+      <c r="E24" s="98"/>
+      <c r="F24" s="98"/>
+      <c r="G24" s="98"/>
+      <c r="H24" s="98"/>
+      <c r="I24" s="98"/>
+      <c r="J24" s="98"/>
+      <c r="K24" s="98"/>
+      <c r="L24" s="99"/>
     </row>
     <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
@@ -12343,17 +12394,17 @@
       <c r="C25" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="93" t="s">
+      <c r="D25" s="92" t="s">
         <v>38</v>
       </c>
-      <c r="E25" s="93"/>
-      <c r="F25" s="93"/>
-      <c r="G25" s="93"/>
-      <c r="H25" s="93"/>
-      <c r="I25" s="93"/>
-      <c r="J25" s="93"/>
-      <c r="K25" s="93"/>
-      <c r="L25" s="93"/>
+      <c r="E25" s="92"/>
+      <c r="F25" s="92"/>
+      <c r="G25" s="92"/>
+      <c r="H25" s="92"/>
+      <c r="I25" s="92"/>
+      <c r="J25" s="92"/>
+      <c r="K25" s="92"/>
+      <c r="L25" s="92"/>
     </row>
     <row r="26" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="33">
@@ -12363,17 +12414,17 @@
         <v>116</v>
       </c>
       <c r="C26" s="34"/>
-      <c r="D26" s="81" t="s">
+      <c r="D26" s="80" t="s">
         <v>108</v>
       </c>
-      <c r="E26" s="82"/>
-      <c r="F26" s="82"/>
-      <c r="G26" s="82"/>
-      <c r="H26" s="82"/>
-      <c r="I26" s="82"/>
-      <c r="J26" s="82"/>
-      <c r="K26" s="82"/>
-      <c r="L26" s="82"/>
+      <c r="E26" s="81"/>
+      <c r="F26" s="81"/>
+      <c r="G26" s="81"/>
+      <c r="H26" s="81"/>
+      <c r="I26" s="81"/>
+      <c r="J26" s="81"/>
+      <c r="K26" s="81"/>
+      <c r="L26" s="81"/>
     </row>
     <row r="27" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
@@ -12383,15 +12434,15 @@
         <v>117</v>
       </c>
       <c r="C27" s="34"/>
-      <c r="D27" s="83"/>
-      <c r="E27" s="84"/>
-      <c r="F27" s="84"/>
-      <c r="G27" s="84"/>
-      <c r="H27" s="84"/>
-      <c r="I27" s="84"/>
-      <c r="J27" s="84"/>
-      <c r="K27" s="84"/>
-      <c r="L27" s="84"/>
+      <c r="D27" s="82"/>
+      <c r="E27" s="83"/>
+      <c r="F27" s="83"/>
+      <c r="G27" s="83"/>
+      <c r="H27" s="83"/>
+      <c r="I27" s="83"/>
+      <c r="J27" s="83"/>
+      <c r="K27" s="83"/>
+      <c r="L27" s="83"/>
     </row>
     <row r="28" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="33">
@@ -12401,15 +12452,15 @@
         <v>118</v>
       </c>
       <c r="C28" s="34"/>
-      <c r="D28" s="83"/>
-      <c r="E28" s="84"/>
-      <c r="F28" s="84"/>
-      <c r="G28" s="84"/>
-      <c r="H28" s="84"/>
-      <c r="I28" s="84"/>
-      <c r="J28" s="84"/>
-      <c r="K28" s="84"/>
-      <c r="L28" s="84"/>
+      <c r="D28" s="82"/>
+      <c r="E28" s="83"/>
+      <c r="F28" s="83"/>
+      <c r="G28" s="83"/>
+      <c r="H28" s="83"/>
+      <c r="I28" s="83"/>
+      <c r="J28" s="83"/>
+      <c r="K28" s="83"/>
+      <c r="L28" s="83"/>
     </row>
     <row r="29" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
@@ -12419,15 +12470,15 @@
         <v>119</v>
       </c>
       <c r="C29" s="34"/>
-      <c r="D29" s="83"/>
-      <c r="E29" s="84"/>
-      <c r="F29" s="84"/>
-      <c r="G29" s="84"/>
-      <c r="H29" s="84"/>
-      <c r="I29" s="84"/>
-      <c r="J29" s="84"/>
-      <c r="K29" s="84"/>
-      <c r="L29" s="84"/>
+      <c r="D29" s="82"/>
+      <c r="E29" s="83"/>
+      <c r="F29" s="83"/>
+      <c r="G29" s="83"/>
+      <c r="H29" s="83"/>
+      <c r="I29" s="83"/>
+      <c r="J29" s="83"/>
+      <c r="K29" s="83"/>
+      <c r="L29" s="83"/>
     </row>
     <row r="30" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="33">
@@ -12437,15 +12488,15 @@
         <v>120</v>
       </c>
       <c r="C30" s="34"/>
-      <c r="D30" s="83"/>
-      <c r="E30" s="84"/>
-      <c r="F30" s="84"/>
-      <c r="G30" s="84"/>
-      <c r="H30" s="84"/>
-      <c r="I30" s="84"/>
-      <c r="J30" s="84"/>
-      <c r="K30" s="84"/>
-      <c r="L30" s="84"/>
+      <c r="D30" s="82"/>
+      <c r="E30" s="83"/>
+      <c r="F30" s="83"/>
+      <c r="G30" s="83"/>
+      <c r="H30" s="83"/>
+      <c r="I30" s="83"/>
+      <c r="J30" s="83"/>
+      <c r="K30" s="83"/>
+      <c r="L30" s="83"/>
     </row>
     <row r="31" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="33">
@@ -12455,15 +12506,15 @@
         <v>121</v>
       </c>
       <c r="C31" s="34"/>
-      <c r="D31" s="83"/>
-      <c r="E31" s="84"/>
-      <c r="F31" s="84"/>
-      <c r="G31" s="84"/>
-      <c r="H31" s="84"/>
-      <c r="I31" s="84"/>
-      <c r="J31" s="84"/>
-      <c r="K31" s="84"/>
-      <c r="L31" s="84"/>
+      <c r="D31" s="82"/>
+      <c r="E31" s="83"/>
+      <c r="F31" s="83"/>
+      <c r="G31" s="83"/>
+      <c r="H31" s="83"/>
+      <c r="I31" s="83"/>
+      <c r="J31" s="83"/>
+      <c r="K31" s="83"/>
+      <c r="L31" s="83"/>
     </row>
     <row r="32" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="33">
@@ -12473,15 +12524,15 @@
         <v>122</v>
       </c>
       <c r="C32" s="34"/>
-      <c r="D32" s="83"/>
-      <c r="E32" s="84"/>
-      <c r="F32" s="84"/>
-      <c r="G32" s="84"/>
-      <c r="H32" s="84"/>
-      <c r="I32" s="84"/>
-      <c r="J32" s="84"/>
-      <c r="K32" s="84"/>
-      <c r="L32" s="84"/>
+      <c r="D32" s="82"/>
+      <c r="E32" s="83"/>
+      <c r="F32" s="83"/>
+      <c r="G32" s="83"/>
+      <c r="H32" s="83"/>
+      <c r="I32" s="83"/>
+      <c r="J32" s="83"/>
+      <c r="K32" s="83"/>
+      <c r="L32" s="83"/>
     </row>
     <row r="33" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="33">
@@ -12491,15 +12542,15 @@
         <v>123</v>
       </c>
       <c r="C33" s="34"/>
-      <c r="D33" s="83"/>
-      <c r="E33" s="84"/>
-      <c r="F33" s="84"/>
-      <c r="G33" s="84"/>
-      <c r="H33" s="84"/>
-      <c r="I33" s="84"/>
-      <c r="J33" s="84"/>
-      <c r="K33" s="84"/>
-      <c r="L33" s="84"/>
+      <c r="D33" s="82"/>
+      <c r="E33" s="83"/>
+      <c r="F33" s="83"/>
+      <c r="G33" s="83"/>
+      <c r="H33" s="83"/>
+      <c r="I33" s="83"/>
+      <c r="J33" s="83"/>
+      <c r="K33" s="83"/>
+      <c r="L33" s="83"/>
     </row>
     <row r="34" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="33">
@@ -12509,15 +12560,15 @@
         <v>124</v>
       </c>
       <c r="C34" s="34"/>
-      <c r="D34" s="83"/>
-      <c r="E34" s="84"/>
-      <c r="F34" s="84"/>
-      <c r="G34" s="84"/>
-      <c r="H34" s="84"/>
-      <c r="I34" s="84"/>
-      <c r="J34" s="84"/>
-      <c r="K34" s="84"/>
-      <c r="L34" s="84"/>
+      <c r="D34" s="82"/>
+      <c r="E34" s="83"/>
+      <c r="F34" s="83"/>
+      <c r="G34" s="83"/>
+      <c r="H34" s="83"/>
+      <c r="I34" s="83"/>
+      <c r="J34" s="83"/>
+      <c r="K34" s="83"/>
+      <c r="L34" s="83"/>
     </row>
     <row r="35" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="33">
@@ -12527,15 +12578,15 @@
         <v>125</v>
       </c>
       <c r="C35" s="34"/>
-      <c r="D35" s="83"/>
-      <c r="E35" s="84"/>
-      <c r="F35" s="84"/>
-      <c r="G35" s="84"/>
-      <c r="H35" s="84"/>
-      <c r="I35" s="84"/>
-      <c r="J35" s="84"/>
-      <c r="K35" s="84"/>
-      <c r="L35" s="84"/>
+      <c r="D35" s="82"/>
+      <c r="E35" s="83"/>
+      <c r="F35" s="83"/>
+      <c r="G35" s="83"/>
+      <c r="H35" s="83"/>
+      <c r="I35" s="83"/>
+      <c r="J35" s="83"/>
+      <c r="K35" s="83"/>
+      <c r="L35" s="83"/>
     </row>
     <row r="36" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="33">
@@ -12545,15 +12596,15 @@
         <v>126</v>
       </c>
       <c r="C36" s="34"/>
-      <c r="D36" s="83"/>
-      <c r="E36" s="84"/>
-      <c r="F36" s="84"/>
-      <c r="G36" s="84"/>
-      <c r="H36" s="84"/>
-      <c r="I36" s="84"/>
-      <c r="J36" s="84"/>
-      <c r="K36" s="84"/>
-      <c r="L36" s="84"/>
+      <c r="D36" s="82"/>
+      <c r="E36" s="83"/>
+      <c r="F36" s="83"/>
+      <c r="G36" s="83"/>
+      <c r="H36" s="83"/>
+      <c r="I36" s="83"/>
+      <c r="J36" s="83"/>
+      <c r="K36" s="83"/>
+      <c r="L36" s="83"/>
     </row>
     <row r="37" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="33">
@@ -12563,15 +12614,15 @@
         <v>127</v>
       </c>
       <c r="C37" s="34"/>
-      <c r="D37" s="83"/>
-      <c r="E37" s="84"/>
-      <c r="F37" s="84"/>
-      <c r="G37" s="84"/>
-      <c r="H37" s="84"/>
-      <c r="I37" s="84"/>
-      <c r="J37" s="84"/>
-      <c r="K37" s="84"/>
-      <c r="L37" s="84"/>
+      <c r="D37" s="82"/>
+      <c r="E37" s="83"/>
+      <c r="F37" s="83"/>
+      <c r="G37" s="83"/>
+      <c r="H37" s="83"/>
+      <c r="I37" s="83"/>
+      <c r="J37" s="83"/>
+      <c r="K37" s="83"/>
+      <c r="L37" s="83"/>
     </row>
     <row r="38" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="33">
@@ -12581,15 +12632,15 @@
         <v>128</v>
       </c>
       <c r="C38" s="34"/>
-      <c r="D38" s="83"/>
-      <c r="E38" s="84"/>
-      <c r="F38" s="84"/>
-      <c r="G38" s="84"/>
-      <c r="H38" s="84"/>
-      <c r="I38" s="84"/>
-      <c r="J38" s="84"/>
-      <c r="K38" s="84"/>
-      <c r="L38" s="84"/>
+      <c r="D38" s="82"/>
+      <c r="E38" s="83"/>
+      <c r="F38" s="83"/>
+      <c r="G38" s="83"/>
+      <c r="H38" s="83"/>
+      <c r="I38" s="83"/>
+      <c r="J38" s="83"/>
+      <c r="K38" s="83"/>
+      <c r="L38" s="83"/>
     </row>
     <row r="39" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="33">
@@ -12599,15 +12650,15 @@
         <v>129</v>
       </c>
       <c r="C39" s="34"/>
-      <c r="D39" s="83"/>
-      <c r="E39" s="84"/>
-      <c r="F39" s="84"/>
-      <c r="G39" s="84"/>
-      <c r="H39" s="84"/>
-      <c r="I39" s="84"/>
-      <c r="J39" s="84"/>
-      <c r="K39" s="84"/>
-      <c r="L39" s="84"/>
+      <c r="D39" s="82"/>
+      <c r="E39" s="83"/>
+      <c r="F39" s="83"/>
+      <c r="G39" s="83"/>
+      <c r="H39" s="83"/>
+      <c r="I39" s="83"/>
+      <c r="J39" s="83"/>
+      <c r="K39" s="83"/>
+      <c r="L39" s="83"/>
     </row>
     <row r="40" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="33">
@@ -12617,15 +12668,15 @@
         <v>130</v>
       </c>
       <c r="C40" s="34"/>
-      <c r="D40" s="83"/>
-      <c r="E40" s="84"/>
-      <c r="F40" s="84"/>
-      <c r="G40" s="84"/>
-      <c r="H40" s="84"/>
-      <c r="I40" s="84"/>
-      <c r="J40" s="84"/>
-      <c r="K40" s="84"/>
-      <c r="L40" s="84"/>
+      <c r="D40" s="82"/>
+      <c r="E40" s="83"/>
+      <c r="F40" s="83"/>
+      <c r="G40" s="83"/>
+      <c r="H40" s="83"/>
+      <c r="I40" s="83"/>
+      <c r="J40" s="83"/>
+      <c r="K40" s="83"/>
+      <c r="L40" s="83"/>
     </row>
     <row r="41" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="33">
@@ -12635,15 +12686,15 @@
         <v>131</v>
       </c>
       <c r="C41" s="34"/>
-      <c r="D41" s="83"/>
-      <c r="E41" s="84"/>
-      <c r="F41" s="84"/>
-      <c r="G41" s="84"/>
-      <c r="H41" s="84"/>
-      <c r="I41" s="84"/>
-      <c r="J41" s="84"/>
-      <c r="K41" s="84"/>
-      <c r="L41" s="84"/>
+      <c r="D41" s="82"/>
+      <c r="E41" s="83"/>
+      <c r="F41" s="83"/>
+      <c r="G41" s="83"/>
+      <c r="H41" s="83"/>
+      <c r="I41" s="83"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="83"/>
+      <c r="L41" s="83"/>
     </row>
     <row r="42" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="33">
@@ -12653,15 +12704,15 @@
         <v>132</v>
       </c>
       <c r="C42" s="34"/>
-      <c r="D42" s="83"/>
-      <c r="E42" s="84"/>
-      <c r="F42" s="84"/>
-      <c r="G42" s="84"/>
-      <c r="H42" s="84"/>
-      <c r="I42" s="84"/>
-      <c r="J42" s="84"/>
-      <c r="K42" s="84"/>
-      <c r="L42" s="84"/>
+      <c r="D42" s="82"/>
+      <c r="E42" s="83"/>
+      <c r="F42" s="83"/>
+      <c r="G42" s="83"/>
+      <c r="H42" s="83"/>
+      <c r="I42" s="83"/>
+      <c r="J42" s="83"/>
+      <c r="K42" s="83"/>
+      <c r="L42" s="83"/>
     </row>
     <row r="43" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="33">
@@ -12671,15 +12722,15 @@
         <v>133</v>
       </c>
       <c r="C43" s="34"/>
-      <c r="D43" s="83"/>
-      <c r="E43" s="84"/>
-      <c r="F43" s="84"/>
-      <c r="G43" s="84"/>
-      <c r="H43" s="84"/>
-      <c r="I43" s="84"/>
-      <c r="J43" s="84"/>
-      <c r="K43" s="84"/>
-      <c r="L43" s="84"/>
+      <c r="D43" s="82"/>
+      <c r="E43" s="83"/>
+      <c r="F43" s="83"/>
+      <c r="G43" s="83"/>
+      <c r="H43" s="83"/>
+      <c r="I43" s="83"/>
+      <c r="J43" s="83"/>
+      <c r="K43" s="83"/>
+      <c r="L43" s="83"/>
     </row>
     <row r="44" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="33">
@@ -12689,15 +12740,15 @@
         <v>134</v>
       </c>
       <c r="C44" s="34"/>
-      <c r="D44" s="83"/>
-      <c r="E44" s="84"/>
-      <c r="F44" s="84"/>
-      <c r="G44" s="84"/>
-      <c r="H44" s="84"/>
-      <c r="I44" s="84"/>
-      <c r="J44" s="84"/>
-      <c r="K44" s="84"/>
-      <c r="L44" s="84"/>
+      <c r="D44" s="82"/>
+      <c r="E44" s="83"/>
+      <c r="F44" s="83"/>
+      <c r="G44" s="83"/>
+      <c r="H44" s="83"/>
+      <c r="I44" s="83"/>
+      <c r="J44" s="83"/>
+      <c r="K44" s="83"/>
+      <c r="L44" s="83"/>
     </row>
     <row r="45" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="33">
@@ -12707,15 +12758,15 @@
         <v>135</v>
       </c>
       <c r="C45" s="34"/>
-      <c r="D45" s="83"/>
-      <c r="E45" s="84"/>
-      <c r="F45" s="84"/>
-      <c r="G45" s="84"/>
-      <c r="H45" s="84"/>
-      <c r="I45" s="84"/>
-      <c r="J45" s="84"/>
-      <c r="K45" s="84"/>
-      <c r="L45" s="84"/>
+      <c r="D45" s="82"/>
+      <c r="E45" s="83"/>
+      <c r="F45" s="83"/>
+      <c r="G45" s="83"/>
+      <c r="H45" s="83"/>
+      <c r="I45" s="83"/>
+      <c r="J45" s="83"/>
+      <c r="K45" s="83"/>
+      <c r="L45" s="83"/>
     </row>
     <row r="46" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="33">
@@ -12725,15 +12776,15 @@
         <v>136</v>
       </c>
       <c r="C46" s="34"/>
-      <c r="D46" s="83"/>
-      <c r="E46" s="84"/>
-      <c r="F46" s="84"/>
-      <c r="G46" s="84"/>
-      <c r="H46" s="84"/>
-      <c r="I46" s="84"/>
-      <c r="J46" s="84"/>
-      <c r="K46" s="84"/>
-      <c r="L46" s="84"/>
+      <c r="D46" s="82"/>
+      <c r="E46" s="83"/>
+      <c r="F46" s="83"/>
+      <c r="G46" s="83"/>
+      <c r="H46" s="83"/>
+      <c r="I46" s="83"/>
+      <c r="J46" s="83"/>
+      <c r="K46" s="83"/>
+      <c r="L46" s="83"/>
     </row>
     <row r="47" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="33">
@@ -12743,15 +12794,15 @@
         <v>137</v>
       </c>
       <c r="C47" s="34"/>
-      <c r="D47" s="83"/>
-      <c r="E47" s="84"/>
-      <c r="F47" s="84"/>
-      <c r="G47" s="84"/>
-      <c r="H47" s="84"/>
-      <c r="I47" s="84"/>
-      <c r="J47" s="84"/>
-      <c r="K47" s="84"/>
-      <c r="L47" s="84"/>
+      <c r="D47" s="82"/>
+      <c r="E47" s="83"/>
+      <c r="F47" s="83"/>
+      <c r="G47" s="83"/>
+      <c r="H47" s="83"/>
+      <c r="I47" s="83"/>
+      <c r="J47" s="83"/>
+      <c r="K47" s="83"/>
+      <c r="L47" s="83"/>
     </row>
     <row r="48" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="33">
@@ -12761,15 +12812,15 @@
         <v>138</v>
       </c>
       <c r="C48" s="34"/>
-      <c r="D48" s="83"/>
-      <c r="E48" s="84"/>
-      <c r="F48" s="84"/>
-      <c r="G48" s="84"/>
-      <c r="H48" s="84"/>
-      <c r="I48" s="84"/>
-      <c r="J48" s="84"/>
-      <c r="K48" s="84"/>
-      <c r="L48" s="84"/>
+      <c r="D48" s="82"/>
+      <c r="E48" s="83"/>
+      <c r="F48" s="83"/>
+      <c r="G48" s="83"/>
+      <c r="H48" s="83"/>
+      <c r="I48" s="83"/>
+      <c r="J48" s="83"/>
+      <c r="K48" s="83"/>
+      <c r="L48" s="83"/>
     </row>
     <row r="49" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="33">
@@ -12779,303 +12830,321 @@
         <v>139</v>
       </c>
       <c r="C49" s="34"/>
-      <c r="D49" s="83"/>
-      <c r="E49" s="84"/>
-      <c r="F49" s="84"/>
-      <c r="G49" s="84"/>
-      <c r="H49" s="84"/>
-      <c r="I49" s="84"/>
-      <c r="J49" s="84"/>
-      <c r="K49" s="84"/>
-      <c r="L49" s="84"/>
+      <c r="D49" s="82"/>
+      <c r="E49" s="83"/>
+      <c r="F49" s="83"/>
+      <c r="G49" s="83"/>
+      <c r="H49" s="83"/>
+      <c r="I49" s="83"/>
+      <c r="J49" s="83"/>
+      <c r="K49" s="83"/>
+      <c r="L49" s="83"/>
     </row>
     <row r="50" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="72">
+      <c r="A50" s="33">
         <v>25</v>
       </c>
-      <c r="B50" s="77" t="s">
+      <c r="B50" s="34" t="s">
         <v>140</v>
       </c>
       <c r="C50" s="34"/>
-      <c r="D50" s="83"/>
-      <c r="E50" s="84"/>
-      <c r="F50" s="84"/>
-      <c r="G50" s="84"/>
-      <c r="H50" s="84"/>
-      <c r="I50" s="84"/>
-      <c r="J50" s="84"/>
-      <c r="K50" s="84"/>
-      <c r="L50" s="84"/>
+      <c r="D50" s="82"/>
+      <c r="E50" s="83"/>
+      <c r="F50" s="83"/>
+      <c r="G50" s="83"/>
+      <c r="H50" s="83"/>
+      <c r="I50" s="83"/>
+      <c r="J50" s="83"/>
+      <c r="K50" s="83"/>
+      <c r="L50" s="83"/>
     </row>
     <row r="51" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="72">
+      <c r="A51" s="33">
         <v>26</v>
       </c>
       <c r="B51" s="77" t="s">
         <v>141</v>
       </c>
       <c r="C51" s="34"/>
-      <c r="D51" s="83"/>
-      <c r="E51" s="84"/>
-      <c r="F51" s="84"/>
-      <c r="G51" s="84"/>
-      <c r="H51" s="84"/>
-      <c r="I51" s="84"/>
-      <c r="J51" s="84"/>
-      <c r="K51" s="84"/>
-      <c r="L51" s="84"/>
+      <c r="D51" s="82"/>
+      <c r="E51" s="83"/>
+      <c r="F51" s="83"/>
+      <c r="G51" s="83"/>
+      <c r="H51" s="83"/>
+      <c r="I51" s="83"/>
+      <c r="J51" s="83"/>
+      <c r="K51" s="83"/>
+      <c r="L51" s="83"/>
     </row>
     <row r="52" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="72">
+      <c r="A52" s="33">
         <v>27</v>
       </c>
       <c r="B52" s="77" t="s">
         <v>142</v>
       </c>
       <c r="C52" s="34"/>
-      <c r="D52" s="83"/>
-      <c r="E52" s="84"/>
-      <c r="F52" s="84"/>
-      <c r="G52" s="84"/>
-      <c r="H52" s="84"/>
-      <c r="I52" s="84"/>
-      <c r="J52" s="84"/>
-      <c r="K52" s="84"/>
-      <c r="L52" s="84"/>
+      <c r="D52" s="82"/>
+      <c r="E52" s="83"/>
+      <c r="F52" s="83"/>
+      <c r="G52" s="83"/>
+      <c r="H52" s="83"/>
+      <c r="I52" s="83"/>
+      <c r="J52" s="83"/>
+      <c r="K52" s="83"/>
+      <c r="L52" s="83"/>
     </row>
     <row r="53" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="72">
+      <c r="A53" s="33">
         <v>28</v>
       </c>
-      <c r="B53" s="78" t="s">
+      <c r="B53" s="77" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="79"/>
-      <c r="D53" s="83"/>
-      <c r="E53" s="84"/>
-      <c r="F53" s="84"/>
-      <c r="G53" s="84"/>
-      <c r="H53" s="84"/>
-      <c r="I53" s="84"/>
-      <c r="J53" s="84"/>
-      <c r="K53" s="84"/>
-      <c r="L53" s="84"/>
+      <c r="C53" s="34"/>
+      <c r="D53" s="82"/>
+      <c r="E53" s="83"/>
+      <c r="F53" s="83"/>
+      <c r="G53" s="83"/>
+      <c r="H53" s="83"/>
+      <c r="I53" s="83"/>
+      <c r="J53" s="83"/>
+      <c r="K53" s="83"/>
+      <c r="L53" s="83"/>
     </row>
     <row r="54" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="72">
+      <c r="A54" s="33">
         <v>29</v>
       </c>
       <c r="B54" s="78" t="s">
         <v>144</v>
       </c>
-      <c r="C54" s="72"/>
-      <c r="D54" s="83"/>
-      <c r="E54" s="84"/>
-      <c r="F54" s="84"/>
-      <c r="G54" s="84"/>
-      <c r="H54" s="84"/>
-      <c r="I54" s="84"/>
-      <c r="J54" s="84"/>
-      <c r="K54" s="84"/>
-      <c r="L54" s="84"/>
+      <c r="C54" s="79"/>
+      <c r="D54" s="82"/>
+      <c r="E54" s="83"/>
+      <c r="F54" s="83"/>
+      <c r="G54" s="83"/>
+      <c r="H54" s="83"/>
+      <c r="I54" s="83"/>
+      <c r="J54" s="83"/>
+      <c r="K54" s="83"/>
+      <c r="L54" s="83"/>
     </row>
     <row r="55" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="72">
+      <c r="A55" s="33">
         <v>30</v>
       </c>
       <c r="B55" s="78" t="s">
         <v>145</v>
       </c>
-      <c r="C55" s="78"/>
-      <c r="D55" s="83"/>
-      <c r="E55" s="84"/>
-      <c r="F55" s="84"/>
-      <c r="G55" s="84"/>
-      <c r="H55" s="84"/>
-      <c r="I55" s="84"/>
-      <c r="J55" s="84"/>
-      <c r="K55" s="84"/>
-      <c r="L55" s="84"/>
+      <c r="C55" s="72"/>
+      <c r="D55" s="82"/>
+      <c r="E55" s="83"/>
+      <c r="F55" s="83"/>
+      <c r="G55" s="83"/>
+      <c r="H55" s="83"/>
+      <c r="I55" s="83"/>
+      <c r="J55" s="83"/>
+      <c r="K55" s="83"/>
+      <c r="L55" s="83"/>
     </row>
     <row r="56" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="72">
+      <c r="A56" s="33">
         <v>31</v>
       </c>
       <c r="B56" s="78" t="s">
         <v>146</v>
       </c>
       <c r="C56" s="78"/>
-      <c r="D56" s="83"/>
-      <c r="E56" s="84"/>
-      <c r="F56" s="84"/>
-      <c r="G56" s="84"/>
-      <c r="H56" s="84"/>
-      <c r="I56" s="84"/>
-      <c r="J56" s="84"/>
-      <c r="K56" s="84"/>
-      <c r="L56" s="84"/>
+      <c r="D56" s="82"/>
+      <c r="E56" s="83"/>
+      <c r="F56" s="83"/>
+      <c r="G56" s="83"/>
+      <c r="H56" s="83"/>
+      <c r="I56" s="83"/>
+      <c r="J56" s="83"/>
+      <c r="K56" s="83"/>
+      <c r="L56" s="83"/>
     </row>
     <row r="57" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="72">
+      <c r="A57" s="33">
         <v>32</v>
       </c>
       <c r="B57" s="78" t="s">
         <v>147</v>
       </c>
       <c r="C57" s="78"/>
-      <c r="D57" s="83"/>
-      <c r="E57" s="84"/>
-      <c r="F57" s="84"/>
-      <c r="G57" s="84"/>
-      <c r="H57" s="84"/>
-      <c r="I57" s="84"/>
-      <c r="J57" s="84"/>
-      <c r="K57" s="84"/>
-      <c r="L57" s="84"/>
+      <c r="D57" s="82"/>
+      <c r="E57" s="83"/>
+      <c r="F57" s="83"/>
+      <c r="G57" s="83"/>
+      <c r="H57" s="83"/>
+      <c r="I57" s="83"/>
+      <c r="J57" s="83"/>
+      <c r="K57" s="83"/>
+      <c r="L57" s="83"/>
     </row>
     <row r="58" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="72">
+      <c r="A58" s="33">
         <v>33</v>
       </c>
       <c r="B58" s="78" t="s">
         <v>148</v>
       </c>
       <c r="C58" s="78"/>
-      <c r="D58" s="83"/>
-      <c r="E58" s="84"/>
-      <c r="F58" s="84"/>
-      <c r="G58" s="84"/>
-      <c r="H58" s="84"/>
-      <c r="I58" s="84"/>
-      <c r="J58" s="84"/>
-      <c r="K58" s="84"/>
-      <c r="L58" s="84"/>
+      <c r="D58" s="82"/>
+      <c r="E58" s="83"/>
+      <c r="F58" s="83"/>
+      <c r="G58" s="83"/>
+      <c r="H58" s="83"/>
+      <c r="I58" s="83"/>
+      <c r="J58" s="83"/>
+      <c r="K58" s="83"/>
+      <c r="L58" s="83"/>
     </row>
     <row r="59" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="72">
+      <c r="A59" s="33">
         <v>34</v>
       </c>
       <c r="B59" s="78" t="s">
         <v>149</v>
       </c>
       <c r="C59" s="78"/>
-      <c r="D59" s="83"/>
-      <c r="E59" s="84"/>
-      <c r="F59" s="84"/>
-      <c r="G59" s="84"/>
-      <c r="H59" s="84"/>
-      <c r="I59" s="84"/>
-      <c r="J59" s="84"/>
-      <c r="K59" s="84"/>
-      <c r="L59" s="84"/>
+      <c r="D59" s="82"/>
+      <c r="E59" s="83"/>
+      <c r="F59" s="83"/>
+      <c r="G59" s="83"/>
+      <c r="H59" s="83"/>
+      <c r="I59" s="83"/>
+      <c r="J59" s="83"/>
+      <c r="K59" s="83"/>
+      <c r="L59" s="83"/>
     </row>
     <row r="60" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="72">
+      <c r="A60" s="33">
         <v>35</v>
       </c>
       <c r="B60" s="78" t="s">
         <v>150</v>
       </c>
       <c r="C60" s="78"/>
-      <c r="D60" s="83"/>
-      <c r="E60" s="84"/>
-      <c r="F60" s="84"/>
-      <c r="G60" s="84"/>
-      <c r="H60" s="84"/>
-      <c r="I60" s="84"/>
-      <c r="J60" s="84"/>
-      <c r="K60" s="84"/>
-      <c r="L60" s="84"/>
+      <c r="D60" s="82"/>
+      <c r="E60" s="83"/>
+      <c r="F60" s="83"/>
+      <c r="G60" s="83"/>
+      <c r="H60" s="83"/>
+      <c r="I60" s="83"/>
+      <c r="J60" s="83"/>
+      <c r="K60" s="83"/>
+      <c r="L60" s="83"/>
     </row>
     <row r="61" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="72">
+      <c r="A61" s="33">
         <v>36</v>
       </c>
       <c r="B61" s="78" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C61" s="78"/>
-      <c r="D61" s="83"/>
-      <c r="E61" s="84"/>
-      <c r="F61" s="84"/>
-      <c r="G61" s="84"/>
-      <c r="H61" s="84"/>
-      <c r="I61" s="84"/>
-      <c r="J61" s="84"/>
-      <c r="K61" s="84"/>
-      <c r="L61" s="84"/>
+      <c r="D61" s="82"/>
+      <c r="E61" s="83"/>
+      <c r="F61" s="83"/>
+      <c r="G61" s="83"/>
+      <c r="H61" s="83"/>
+      <c r="I61" s="83"/>
+      <c r="J61" s="83"/>
+      <c r="K61" s="83"/>
+      <c r="L61" s="83"/>
     </row>
     <row r="62" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="72">
+      <c r="A62" s="33">
         <v>37</v>
       </c>
       <c r="B62" s="78" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C62" s="78"/>
-      <c r="D62" s="83"/>
-      <c r="E62" s="84"/>
-      <c r="F62" s="84"/>
-      <c r="G62" s="84"/>
-      <c r="H62" s="84"/>
-      <c r="I62" s="84"/>
-      <c r="J62" s="84"/>
-      <c r="K62" s="84"/>
-      <c r="L62" s="84"/>
+      <c r="D62" s="82"/>
+      <c r="E62" s="83"/>
+      <c r="F62" s="83"/>
+      <c r="G62" s="83"/>
+      <c r="H62" s="83"/>
+      <c r="I62" s="83"/>
+      <c r="J62" s="83"/>
+      <c r="K62" s="83"/>
+      <c r="L62" s="83"/>
     </row>
     <row r="63" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="72">
+      <c r="A63" s="33">
         <v>38</v>
       </c>
       <c r="B63" s="78" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C63" s="78"/>
-      <c r="D63" s="83"/>
-      <c r="E63" s="84"/>
-      <c r="F63" s="84"/>
-      <c r="G63" s="84"/>
-      <c r="H63" s="84"/>
-      <c r="I63" s="84"/>
-      <c r="J63" s="84"/>
-      <c r="K63" s="84"/>
-      <c r="L63" s="84"/>
+      <c r="D63" s="82"/>
+      <c r="E63" s="83"/>
+      <c r="F63" s="83"/>
+      <c r="G63" s="83"/>
+      <c r="H63" s="83"/>
+      <c r="I63" s="83"/>
+      <c r="J63" s="83"/>
+      <c r="K63" s="83"/>
+      <c r="L63" s="83"/>
     </row>
     <row r="64" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="72">
+      <c r="A64" s="33">
         <v>39</v>
       </c>
       <c r="B64" s="78" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C64" s="78"/>
-      <c r="D64" s="83"/>
-      <c r="E64" s="84"/>
-      <c r="F64" s="84"/>
-      <c r="G64" s="84"/>
-      <c r="H64" s="84"/>
-      <c r="I64" s="84"/>
-      <c r="J64" s="84"/>
-      <c r="K64" s="84"/>
-      <c r="L64" s="84"/>
+      <c r="D64" s="82"/>
+      <c r="E64" s="83"/>
+      <c r="F64" s="83"/>
+      <c r="G64" s="83"/>
+      <c r="H64" s="83"/>
+      <c r="I64" s="83"/>
+      <c r="J64" s="83"/>
+      <c r="K64" s="83"/>
+      <c r="L64" s="83"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A65" s="80">
+    <row r="65" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="33">
         <v>40</v>
       </c>
-      <c r="B65" s="34" t="s">
+      <c r="B65" s="78" t="s">
         <v>155</v>
       </c>
       <c r="C65" s="78"/>
-      <c r="D65" s="83"/>
-      <c r="E65" s="84"/>
-      <c r="F65" s="84"/>
-      <c r="G65" s="84"/>
-      <c r="H65" s="84"/>
-      <c r="I65" s="84"/>
-      <c r="J65" s="84"/>
-      <c r="K65" s="84"/>
-      <c r="L65" s="84"/>
+      <c r="D65" s="82"/>
+      <c r="E65" s="83"/>
+      <c r="F65" s="83"/>
+      <c r="G65" s="83"/>
+      <c r="H65" s="83"/>
+      <c r="I65" s="83"/>
+      <c r="J65" s="83"/>
+      <c r="K65" s="83"/>
+      <c r="L65" s="83"/>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A66" s="33">
+        <v>41</v>
+      </c>
+      <c r="B66" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="C66" s="78"/>
+      <c r="D66" s="82"/>
+      <c r="E66" s="83"/>
+      <c r="F66" s="83"/>
+      <c r="G66" s="83"/>
+      <c r="H66" s="83"/>
+      <c r="I66" s="83"/>
+      <c r="J66" s="83"/>
+      <c r="K66" s="83"/>
+      <c r="L66" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -13090,7 +13159,7 @@
     <mergeCell ref="B4:L4"/>
     <mergeCell ref="B5:L5"/>
     <mergeCell ref="B7:L7"/>
-    <mergeCell ref="D26:L65"/>
+    <mergeCell ref="D26:L66"/>
     <mergeCell ref="D18:D20"/>
     <mergeCell ref="E18:L20"/>
     <mergeCell ref="D25:L25"/>
@@ -13139,13 +13208,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13161,13 +13230,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13183,13 +13252,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13205,13 +13274,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13227,13 +13296,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13249,13 +13318,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13271,13 +13340,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13293,13 +13362,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13315,13 +13384,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13337,13 +13406,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13359,13 +13428,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13381,13 +13450,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13403,13 +13472,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13425,13 +13494,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13447,13 +13516,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13469,13 +13538,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13491,13 +13560,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13513,13 +13582,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13535,13 +13604,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13557,13 +13626,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13579,13 +13648,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13601,13 +13670,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13623,13 +13692,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13645,13 +13714,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13667,13 +13736,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13689,13 +13758,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13711,13 +13780,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13733,13 +13802,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13755,13 +13824,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13777,13 +13846,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13799,13 +13868,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13821,13 +13890,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13843,13 +13912,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13865,13 +13934,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13887,13 +13956,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13909,13 +13978,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13931,13 +14000,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13953,13 +14022,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13975,13 +14044,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -13997,13 +14066,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14019,13 +14088,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14041,13 +14110,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14063,13 +14132,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14085,13 +14154,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14107,13 +14176,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14129,13 +14198,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14151,13 +14220,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14173,13 +14242,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14195,13 +14264,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14217,13 +14286,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14239,13 +14308,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14261,13 +14330,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14283,13 +14352,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14305,13 +14374,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14327,13 +14396,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14349,13 +14418,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14371,13 +14440,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14393,13 +14462,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14415,13 +14484,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14437,13 +14506,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14459,13 +14528,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14481,13 +14550,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14503,13 +14572,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14525,13 +14594,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14547,13 +14616,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14569,13 +14638,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14591,13 +14660,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14613,13 +14682,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14635,13 +14704,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14657,13 +14726,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14679,13 +14748,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14701,13 +14770,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14723,13 +14792,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14745,13 +14814,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14767,13 +14836,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14789,13 +14858,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14811,13 +14880,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14833,13 +14902,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14855,13 +14924,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14877,13 +14946,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14899,13 +14968,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14921,13 +14990,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14943,13 +15012,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14965,13 +15034,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -14987,13 +15056,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15009,13 +15078,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15031,13 +15100,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15053,13 +15122,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15075,13 +15144,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15097,13 +15166,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15119,13 +15188,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15141,13 +15210,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15163,13 +15232,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15185,13 +15254,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15207,13 +15276,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15229,13 +15298,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15251,13 +15320,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15273,13 +15342,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15295,13 +15364,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15317,13 +15386,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15339,13 +15408,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15361,13 +15430,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15383,13 +15452,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15405,13 +15474,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15427,13 +15496,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15449,13 +15518,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>35</xdr:row>
+                    <xdr:row>36</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15537,13 +15606,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>29</xdr:row>
+                    <xdr:row>30</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>29</xdr:row>
+                    <xdr:row>30</xdr:row>
                     <xdr:rowOff>228600</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15559,13 +15628,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>30</xdr:row>
+                    <xdr:row>31</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>30</xdr:row>
+                    <xdr:row>31</xdr:row>
                     <xdr:rowOff>228600</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15581,13 +15650,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>31</xdr:row>
+                    <xdr:row>32</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>31</xdr:row>
+                    <xdr:row>32</xdr:row>
                     <xdr:rowOff>228600</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15603,13 +15672,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>32</xdr:row>
+                    <xdr:row>33</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>32</xdr:row>
+                    <xdr:row>33</xdr:row>
                     <xdr:rowOff>228600</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15625,13 +15694,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>33</xdr:row>
+                    <xdr:row>34</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>33</xdr:row>
+                    <xdr:row>34</xdr:row>
                     <xdr:rowOff>228600</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15647,13 +15716,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>34</xdr:row>
+                    <xdr:row>35</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>34</xdr:row>
+                    <xdr:row>35</xdr:row>
                     <xdr:rowOff>228600</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15669,13 +15738,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>36</xdr:row>
+                    <xdr:row>37</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>36</xdr:row>
+                    <xdr:row>37</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15691,13 +15760,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>37</xdr:row>
+                    <xdr:row>38</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>37</xdr:row>
+                    <xdr:row>38</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15713,13 +15782,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>38</xdr:row>
+                    <xdr:row>39</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>38</xdr:row>
+                    <xdr:row>39</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15735,13 +15804,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>39</xdr:row>
+                    <xdr:row>40</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>39</xdr:row>
+                    <xdr:row>40</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15757,13 +15826,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>40</xdr:row>
+                    <xdr:row>41</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>40</xdr:row>
+                    <xdr:row>41</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15779,13 +15848,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>41</xdr:row>
+                    <xdr:row>42</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>41</xdr:row>
+                    <xdr:row>42</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15801,13 +15870,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>42</xdr:row>
+                    <xdr:row>43</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>42</xdr:row>
+                    <xdr:row>43</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15823,13 +15892,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>43</xdr:row>
+                    <xdr:row>44</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>43</xdr:row>
+                    <xdr:row>44</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15845,13 +15914,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>44</xdr:row>
+                    <xdr:row>45</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>44</xdr:row>
+                    <xdr:row>45</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15867,13 +15936,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>45</xdr:row>
+                    <xdr:row>46</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>45</xdr:row>
+                    <xdr:row>46</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15889,13 +15958,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>46</xdr:row>
+                    <xdr:row>47</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>46</xdr:row>
+                    <xdr:row>47</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15911,13 +15980,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>47</xdr:row>
+                    <xdr:row>48</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>47</xdr:row>
+                    <xdr:row>48</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15933,13 +16002,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>48</xdr:row>
+                    <xdr:row>49</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>48</xdr:row>
+                    <xdr:row>49</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15955,13 +16024,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>49</xdr:row>
+                    <xdr:row>50</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>49</xdr:row>
+                    <xdr:row>50</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15977,13 +16046,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>50</xdr:row>
+                    <xdr:row>51</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>50</xdr:row>
+                    <xdr:row>51</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -15999,13 +16068,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>51</xdr:row>
+                    <xdr:row>52</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>51</xdr:row>
+                    <xdr:row>52</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -16021,13 +16090,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>52</xdr:row>
+                    <xdr:row>53</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>52</xdr:row>
+                    <xdr:row>53</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -16043,13 +16112,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>53</xdr:row>
+                    <xdr:row>54</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>53</xdr:row>
+                    <xdr:row>54</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -16065,13 +16134,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>54</xdr:row>
+                    <xdr:row>55</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>54</xdr:row>
+                    <xdr:row>55</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -16087,13 +16156,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>55</xdr:row>
+                    <xdr:row>56</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>55</xdr:row>
+                    <xdr:row>56</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -16109,13 +16178,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>56</xdr:row>
+                    <xdr:row>57</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>56</xdr:row>
+                    <xdr:row>57</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -16131,13 +16200,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>57</xdr:row>
+                    <xdr:row>58</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>57</xdr:row>
+                    <xdr:row>58</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -16153,13 +16222,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>58</xdr:row>
+                    <xdr:row>59</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>58</xdr:row>
+                    <xdr:row>59</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -16175,13 +16244,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>59</xdr:row>
+                    <xdr:row>60</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>59</xdr:row>
+                    <xdr:row>60</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -16197,13 +16266,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>60</xdr:row>
+                    <xdr:row>61</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>60</xdr:row>
+                    <xdr:row>61</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -16219,13 +16288,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>61</xdr:row>
+                    <xdr:row>62</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>61</xdr:row>
+                    <xdr:row>62</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -16241,13 +16310,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>62</xdr:row>
+                    <xdr:row>63</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>62</xdr:row>
+                    <xdr:row>63</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -16263,13 +16332,13 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>63</xdr:row>
+                    <xdr:row>64</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>63</xdr:row>
+                    <xdr:row>64</xdr:row>
                     <xdr:rowOff>220980</xdr:rowOff>
                   </to>
                 </anchor>
@@ -16285,14 +16354,36 @@
                   <from>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>64</xdr:row>
+                    <xdr:row>65</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>65</xdr:row>
+                    <xdr:row>66</xdr:row>
                     <xdr:rowOff>38100</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1248" r:id="rId150" name="Drop Down 224">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>29</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>1409700</xdr:colOff>
+                    <xdr:row>29</xdr:row>
+                    <xdr:rowOff>228600</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -16322,50 +16413,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="151" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="153"/>
-      <c r="C1" s="153"/>
-      <c r="D1" s="153"/>
-      <c r="E1" s="153"/>
-      <c r="F1" s="153"/>
-      <c r="G1" s="153"/>
-      <c r="H1" s="153"/>
-      <c r="I1" s="153"/>
-      <c r="J1" s="153"/>
-      <c r="K1" s="153"/>
-      <c r="L1" s="154"/>
+      <c r="B1" s="152"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="152"/>
+      <c r="F1" s="152"/>
+      <c r="G1" s="152"/>
+      <c r="H1" s="152"/>
+      <c r="I1" s="152"/>
+      <c r="J1" s="152"/>
+      <c r="K1" s="152"/>
+      <c r="L1" s="153"/>
     </row>
     <row r="2" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="154" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="156"/>
-      <c r="C2" s="156"/>
-      <c r="D2" s="156"/>
-      <c r="E2" s="156"/>
-      <c r="F2" s="156"/>
-      <c r="G2" s="156"/>
-      <c r="H2" s="156"/>
-      <c r="I2" s="156"/>
-      <c r="J2" s="156"/>
-      <c r="K2" s="156"/>
-      <c r="L2" s="157"/>
+      <c r="B2" s="155"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="155"/>
+      <c r="F2" s="155"/>
+      <c r="G2" s="155"/>
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="155"/>
+      <c r="K2" s="155"/>
+      <c r="L2" s="156"/>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="158"/>
-      <c r="B3" s="159"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="159"/>
-      <c r="G3" s="159"/>
-      <c r="H3" s="159"/>
-      <c r="I3" s="159"/>
-      <c r="J3" s="159"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="160"/>
+      <c r="A3" s="157"/>
+      <c r="B3" s="158"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="158"/>
+      <c r="F3" s="158"/>
+      <c r="G3" s="158"/>
+      <c r="H3" s="158"/>
+      <c r="I3" s="158"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="159"/>
     </row>
     <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
@@ -16455,65 +16546,65 @@
       <c r="A8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="163"/>
-      <c r="C8" s="164"/>
-      <c r="D8" s="164"/>
-      <c r="E8" s="164"/>
-      <c r="F8" s="164"/>
-      <c r="G8" s="164"/>
-      <c r="H8" s="164"/>
-      <c r="I8" s="164"/>
-      <c r="J8" s="164"/>
-      <c r="K8" s="164"/>
-      <c r="L8" s="165"/>
+      <c r="B8" s="162"/>
+      <c r="C8" s="163"/>
+      <c r="D8" s="163"/>
+      <c r="E8" s="163"/>
+      <c r="F8" s="163"/>
+      <c r="G8" s="163"/>
+      <c r="H8" s="163"/>
+      <c r="I8" s="163"/>
+      <c r="J8" s="163"/>
+      <c r="K8" s="163"/>
+      <c r="L8" s="164"/>
     </row>
     <row r="9" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="166"/>
-      <c r="C9" s="164"/>
-      <c r="D9" s="164"/>
-      <c r="E9" s="164"/>
-      <c r="F9" s="164"/>
-      <c r="G9" s="164"/>
-      <c r="H9" s="164"/>
-      <c r="I9" s="164"/>
-      <c r="J9" s="164"/>
-      <c r="K9" s="164"/>
-      <c r="L9" s="165"/>
+      <c r="B9" s="165"/>
+      <c r="C9" s="163"/>
+      <c r="D9" s="163"/>
+      <c r="E9" s="163"/>
+      <c r="F9" s="163"/>
+      <c r="G9" s="163"/>
+      <c r="H9" s="163"/>
+      <c r="I9" s="163"/>
+      <c r="J9" s="163"/>
+      <c r="K9" s="163"/>
+      <c r="L9" s="164"/>
     </row>
     <row r="10" spans="1:12" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="161" t="s">
+      <c r="A10" s="160" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="162"/>
-      <c r="C10" s="162"/>
-      <c r="D10" s="162"/>
-      <c r="E10" s="162"/>
-      <c r="F10" s="162"/>
-      <c r="G10" s="162"/>
-      <c r="H10" s="162"/>
-      <c r="I10" s="162"/>
-      <c r="J10" s="162"/>
-      <c r="K10" s="162"/>
-      <c r="L10" s="162"/>
+      <c r="B10" s="161"/>
+      <c r="C10" s="161"/>
+      <c r="D10" s="161"/>
+      <c r="E10" s="161"/>
+      <c r="F10" s="161"/>
+      <c r="G10" s="161"/>
+      <c r="H10" s="161"/>
+      <c r="I10" s="161"/>
+      <c r="J10" s="161"/>
+      <c r="K10" s="161"/>
+      <c r="L10" s="161"/>
     </row>
     <row r="11" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="143" t="s">
+      <c r="A11" s="142" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="144"/>
-      <c r="C11" s="144"/>
-      <c r="D11" s="144"/>
-      <c r="E11" s="144"/>
-      <c r="F11" s="144"/>
-      <c r="G11" s="144"/>
-      <c r="H11" s="144"/>
-      <c r="I11" s="144"/>
-      <c r="J11" s="144"/>
-      <c r="K11" s="144"/>
-      <c r="L11" s="145"/>
+      <c r="B11" s="143"/>
+      <c r="C11" s="143"/>
+      <c r="D11" s="143"/>
+      <c r="E11" s="143"/>
+      <c r="F11" s="143"/>
+      <c r="G11" s="143"/>
+      <c r="H11" s="143"/>
+      <c r="I11" s="143"/>
+      <c r="J11" s="143"/>
+      <c r="K11" s="143"/>
+      <c r="L11" s="144"/>
     </row>
     <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
@@ -16525,101 +16616,101 @@
       <c r="C12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="93" t="s">
+      <c r="D12" s="92" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="93"/>
-      <c r="F12" s="93"/>
-      <c r="G12" s="93"/>
-      <c r="H12" s="93"/>
-      <c r="I12" s="93"/>
-      <c r="J12" s="93"/>
-      <c r="K12" s="93"/>
-      <c r="L12" s="93"/>
+      <c r="E12" s="92"/>
+      <c r="F12" s="92"/>
+      <c r="G12" s="92"/>
+      <c r="H12" s="92"/>
+      <c r="I12" s="92"/>
+      <c r="J12" s="92"/>
+      <c r="K12" s="92"/>
+      <c r="L12" s="92"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="49"/>
       <c r="B13" s="50"/>
       <c r="C13" s="50"/>
-      <c r="D13" s="146"/>
-      <c r="E13" s="147"/>
-      <c r="F13" s="147"/>
-      <c r="G13" s="147"/>
-      <c r="H13" s="147"/>
-      <c r="I13" s="147"/>
-      <c r="J13" s="147"/>
-      <c r="K13" s="147"/>
-      <c r="L13" s="148"/>
+      <c r="D13" s="145"/>
+      <c r="E13" s="146"/>
+      <c r="F13" s="146"/>
+      <c r="G13" s="146"/>
+      <c r="H13" s="146"/>
+      <c r="I13" s="146"/>
+      <c r="J13" s="146"/>
+      <c r="K13" s="146"/>
+      <c r="L13" s="147"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="49"/>
       <c r="B14" s="50"/>
       <c r="C14" s="50"/>
-      <c r="D14" s="149"/>
-      <c r="E14" s="150"/>
-      <c r="F14" s="150"/>
-      <c r="G14" s="150"/>
-      <c r="H14" s="150"/>
-      <c r="I14" s="150"/>
-      <c r="J14" s="150"/>
-      <c r="K14" s="150"/>
-      <c r="L14" s="151"/>
+      <c r="D14" s="148"/>
+      <c r="E14" s="149"/>
+      <c r="F14" s="149"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="149"/>
+      <c r="J14" s="149"/>
+      <c r="K14" s="149"/>
+      <c r="L14" s="150"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="49"/>
       <c r="B15" s="50"/>
       <c r="C15" s="50"/>
-      <c r="D15" s="149"/>
-      <c r="E15" s="150"/>
-      <c r="F15" s="150"/>
-      <c r="G15" s="150"/>
-      <c r="H15" s="150"/>
-      <c r="I15" s="150"/>
-      <c r="J15" s="150"/>
-      <c r="K15" s="150"/>
-      <c r="L15" s="151"/>
+      <c r="D15" s="148"/>
+      <c r="E15" s="149"/>
+      <c r="F15" s="149"/>
+      <c r="G15" s="149"/>
+      <c r="H15" s="149"/>
+      <c r="I15" s="149"/>
+      <c r="J15" s="149"/>
+      <c r="K15" s="149"/>
+      <c r="L15" s="150"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="49"/>
       <c r="B16" s="50"/>
       <c r="C16" s="50"/>
-      <c r="D16" s="149"/>
-      <c r="E16" s="150"/>
-      <c r="F16" s="150"/>
-      <c r="G16" s="150"/>
-      <c r="H16" s="150"/>
-      <c r="I16" s="150"/>
-      <c r="J16" s="150"/>
-      <c r="K16" s="150"/>
-      <c r="L16" s="151"/>
+      <c r="D16" s="148"/>
+      <c r="E16" s="149"/>
+      <c r="F16" s="149"/>
+      <c r="G16" s="149"/>
+      <c r="H16" s="149"/>
+      <c r="I16" s="149"/>
+      <c r="J16" s="149"/>
+      <c r="K16" s="149"/>
+      <c r="L16" s="150"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="49"/>
       <c r="B17" s="50"/>
       <c r="C17" s="50"/>
-      <c r="D17" s="149"/>
-      <c r="E17" s="150"/>
-      <c r="F17" s="150"/>
-      <c r="G17" s="150"/>
-      <c r="H17" s="150"/>
-      <c r="I17" s="150"/>
-      <c r="J17" s="150"/>
-      <c r="K17" s="150"/>
-      <c r="L17" s="151"/>
+      <c r="D17" s="148"/>
+      <c r="E17" s="149"/>
+      <c r="F17" s="149"/>
+      <c r="G17" s="149"/>
+      <c r="H17" s="149"/>
+      <c r="I17" s="149"/>
+      <c r="J17" s="149"/>
+      <c r="K17" s="149"/>
+      <c r="L17" s="150"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="49"/>
       <c r="B18" s="50"/>
       <c r="C18" s="50"/>
-      <c r="D18" s="149"/>
-      <c r="E18" s="150"/>
-      <c r="F18" s="150"/>
-      <c r="G18" s="150"/>
-      <c r="H18" s="150"/>
-      <c r="I18" s="150"/>
-      <c r="J18" s="150"/>
-      <c r="K18" s="150"/>
-      <c r="L18" s="151"/>
+      <c r="D18" s="148"/>
+      <c r="E18" s="149"/>
+      <c r="F18" s="149"/>
+      <c r="G18" s="149"/>
+      <c r="H18" s="149"/>
+      <c r="I18" s="149"/>
+      <c r="J18" s="149"/>
+      <c r="K18" s="149"/>
+      <c r="L18" s="150"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -16708,10 +16799,10 @@
       <c r="B4" s="63"/>
     </row>
     <row r="6" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="A6" s="167" t="s">
+      <c r="A6" s="166" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="167"/>
+      <c r="B6" s="166"/>
     </row>
     <row r="8" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="66" t="s">
@@ -16864,55 +16955,55 @@
   <sheetData>
     <row r="1" spans="2:6" ht="5.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B2" s="169"/>
-      <c r="C2" s="169"/>
-      <c r="D2" s="170" t="s">
+      <c r="B2" s="168"/>
+      <c r="C2" s="168"/>
+      <c r="D2" s="169" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="171" t="s">
+      <c r="E2" s="170" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="171"/>
+      <c r="F2" s="170"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B3" s="169"/>
-      <c r="C3" s="169"/>
-      <c r="D3" s="170"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="171"/>
+      <c r="B3" s="168"/>
+      <c r="C3" s="168"/>
+      <c r="D3" s="169"/>
+      <c r="E3" s="170"/>
+      <c r="F3" s="170"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="169"/>
-      <c r="C4" s="169"/>
-      <c r="D4" s="170"/>
-      <c r="E4" s="171" t="s">
+      <c r="B4" s="168"/>
+      <c r="C4" s="168"/>
+      <c r="D4" s="169"/>
+      <c r="E4" s="170" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="171"/>
+      <c r="F4" s="170"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="172" t="s">
+      <c r="B5" s="171" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="172"/>
+      <c r="C5" s="171"/>
       <c r="D5" s="70" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="173" t="s">
+      <c r="E5" s="172" t="s">
         <v>54</v>
       </c>
-      <c r="F5" s="173"/>
+      <c r="F5" s="172"/>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="168" t="s">
+      <c r="C6" s="167" t="s">
         <v>114</v>
       </c>
-      <c r="D6" s="168"/>
-      <c r="E6" s="168"/>
-      <c r="F6" s="168"/>
+      <c r="D6" s="167"/>
+      <c r="E6" s="167"/>
+      <c r="F6" s="167"/>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="71" t="s">
@@ -17169,10 +17260,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="27" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="173" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="175"/>
+      <c r="B1" s="174"/>
     </row>
     <row r="2" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="28" t="s">

--- a/Guias Produccion/HU-57723.xlsx
+++ b/Guias Produccion/HU-57723.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Alliance\ScriptsEntidades\Guias Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA7E2A6E-9941-4833-A1A4-8BCD32696C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A4498C8-1B0D-4B1D-AEF8-07A1BC630030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guia de implementación" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="156">
   <si>
     <t>Guia documentación</t>
   </si>
@@ -513,21 +513,6 @@
     <t>Es necesario que se ejecuten primero los scripts de la Hu 55188, ya que existe dependencia de algunos campos</t>
   </si>
   <si>
-    <t>01-trgEntityRelations_SyncClientes.sql</t>
-  </si>
-  <si>
-    <t>02-trgUpdateEntityTypes.sql</t>
-  </si>
-  <si>
-    <t>03-trgUpdateEntities.sql</t>
-  </si>
-  <si>
-    <t>04-f_SearchEntities.sql</t>
-  </si>
-  <si>
-    <t>05-f_GetClientsEntities.sql</t>
-  </si>
-  <si>
     <t>06-AC_pro_General_GenerateBulkInt.sql</t>
   </si>
   <si>
@@ -540,100 +525,112 @@
     <t>09-AC_pro_GetDispatchesByCarrier.sql</t>
   </si>
   <si>
-    <t>10-AC_pro_GetClientsEntities.sql</t>
+    <t>01-f_SearchEntities.sql</t>
   </si>
   <si>
-    <t>11-AC_pro_GetClientsPiecesBySubCarrier.sql</t>
+    <t>02-f_GetClientsEntities.sql</t>
   </si>
   <si>
-    <t>12-AC_pro_GetDispatchesByClient.sql</t>
+    <t>03-f_GetAllGuiasHouse.sql</t>
   </si>
   <si>
-    <t>13-AC_pro_GetLocalOrdersByEmployee.sql</t>
+    <t>04-f_SearchGuiasHouseByType.sql</t>
   </si>
   <si>
-    <t>14-AC_pro_ManageGuiasHouseDetallesEditedOrder.sql</t>
+    <t>05-f_SearchGuiasHouseDetallesByType.sql</t>
   </si>
   <si>
-    <t>15-AC_pro_ListCarrierProgramming.sql</t>
+    <t>10-AC_pro_GetClientsPiecesBySubCarrier.sql</t>
   </si>
   <si>
-    <t>16-AC_pro_ConfirmLocalOrderCoordination.sql</t>
+    <t>11-AC_pro_GetDispatchesByClient.sql</t>
   </si>
   <si>
-    <t>17-AC_pro_ConfirmLocalOrder.sql</t>
+    <t>12-AC_pro_GetLocalOrdersByEmployee.sql</t>
   </si>
   <si>
-    <t>18-AC_pro_ShippingDocumentsPODClient360.sql</t>
+    <t>13-AC_pro_ManageGuiasHouseDetallesEditedOrder.sql</t>
   </si>
   <si>
-    <t>19-AC_pro_ModuleEdiDetail.sql</t>
+    <t>14-AC_pro_ListCarrierProgramming.sql</t>
   </si>
   <si>
-    <t>20-AC_pro_Module_Edi.sql</t>
+    <t>15-AC_pro_ConfirmLocalOrderCoordination.sql</t>
   </si>
   <si>
-    <t>21-AC_pro_ListPiecesInventory.sql</t>
+    <t>16-AC_pro_ConfirmLocalOrder.sql</t>
   </si>
   <si>
-    <t>22-AC_pro_GetBarCodeLinks.sql</t>
+    <t>17-AC_pro_ShippingDocumentsPODClient360.sql</t>
   </si>
   <si>
-    <t>23-AC_pro_LargeLabelTempDefault.sql</t>
+    <t>18-AC_pro_ModuleEdiDetail.sql</t>
   </si>
   <si>
-    <t>24-AC_pro_GetDispatchReports.sql</t>
+    <t>19-AC_pro_Module_Edi.sql</t>
   </si>
   <si>
-    <t>25-AC_pro_GetShipmentAnalyticsReports.sql</t>
+    <t>20-AC_pro_ListPiecesInventory.sql</t>
   </si>
   <si>
-    <t>26-AC_pro_GetListOFCycleCounts.sql</t>
+    <t>21-AC_pro_GetBarCodeLinks.sql</t>
   </si>
   <si>
-    <t>27-AC_pro_GetCycleCountDiscrepancies.sql</t>
+    <t>22-AC_pro_LargeLabelTempDefault.sql</t>
   </si>
   <si>
-    <t>28-AC_pro_CycleCountDiscrepanciesReport.sql</t>
+    <t>23-AC_pro_GetDispatchReports.sql</t>
   </si>
   <si>
-    <t>29-AC_pro_GetConsolidatedDispatchAnalytics.sql</t>
+    <t>24-AC_pro_GetShipmentAnalyticsReports.sql</t>
   </si>
   <si>
-    <t>30-AC_pro_GetAccountingAnalyticsReports.sql</t>
+    <t>25-AC_pro_GetListOFCycleCounts.sql</t>
   </si>
   <si>
-    <t>31-AC_pro_GetSalesOrders.sql</t>
+    <t>26-AC_pro_GetCycleCountDiscrepancies.sql</t>
   </si>
   <si>
-    <t>32-AC_pro_GetDispatchReports.sql</t>
+    <t>27-AC_pro_CycleCountDiscrepanciesReport.sql</t>
   </si>
   <si>
-    <t>33-AC_pro_GetCompletedScheduledPickupShipTo.sql</t>
+    <t>28-AC_pro_GetConsolidatedDispatchAnalytics.sql</t>
   </si>
   <si>
-    <t>34-AC_pro_GetCompletedDeliveredPickupShipTo.sql</t>
+    <t>29-AC_pro_GetAccountingAnalyticsReports.sql</t>
   </si>
   <si>
-    <t>35-AC_pro_GetPendingPickup.sql</t>
+    <t>30-AC_pro_GetSalesOrders.sql</t>
   </si>
   <si>
-    <t>36-AC_pro_GetPendingPickupDetails.sql</t>
+    <t>31-AC_pro_GetDispatchReports.sql</t>
   </si>
   <si>
-    <t>37-AC_pro_GetCompletedDeliveredPickupShipTo.sql</t>
+    <t>32-AC_pro_GetCompletedScheduledPickupShipTo.sql</t>
   </si>
   <si>
-    <t>38-AC_pro_GetCompletedScheduledPickupShipTo.sql</t>
+    <t>33-AC_pro_GetCompletedDeliveredPickupShipTo.sql</t>
   </si>
   <si>
-    <t>39-AC_pro_GetCompletedDeliveredPickupDetail.sql</t>
+    <t>34-AC_pro_GetPendingPickup.sql</t>
   </si>
   <si>
-    <t>40-AC_pro_GetCompletedScheduledPickupDetail.sql</t>
+    <t>35-AC_pro_GetPendingPickupDetails.sql</t>
   </si>
   <si>
-    <t>41-AC_pro_InsertAccountingClient.sql</t>
+    <t>36-AC_pro_GetCompletedDeliveredPickupShipTo.sql</t>
+  </si>
+  <si>
+    <t>37-AC_pro_GetCompletedScheduledPickupShipTo.sql</t>
+  </si>
+  <si>
+    <t>38-AC_pro_GetCompletedDeliveredPickupDetail.sql</t>
+  </si>
+  <si>
+    <t>39-AC_pro_GetCompletedScheduledPickupDetail.sql</t>
+  </si>
+  <si>
+    <t>40-AC_pro_InsertAccountingClient.sql</t>
   </si>
 </sst>
 </file>
@@ -2300,7 +2297,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$25" noThreeD="1" sel="23" val="17"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$25" noThreeD="1" sel="17" val="9"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp10.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2340,7 +2337,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp108.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$25" noThreeD="1" sel="23" val="17"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$25" noThreeD="1" sel="17" val="14"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp109.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2504,18 +2501,14 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp145.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$18" noThreeD="1" sel="8" val="3"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$25" noThreeD="1" sel="17" val="12"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp146.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$25" noThreeD="1" sel="17" val="12"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$17" noThreeD="1" sel="17" val="9"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp147.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$17" noThreeD="1" sel="17" val="9"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp148.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$17" noThreeD="1" sel="17" val="9"/>
 </file>
 
@@ -11211,64 +11204,6 @@
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000DE040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>65</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>66</xdr:row>
-          <xdr:rowOff>38100</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1247" name="Drop Down 223" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1247"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000DF040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -12411,7 +12346,7 @@
         <v>1</v>
       </c>
       <c r="B26" s="34" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C26" s="34"/>
       <c r="D26" s="80" t="s">
@@ -12431,7 +12366,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="34" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C27" s="34"/>
       <c r="D27" s="82"/>
@@ -12449,7 +12384,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="34" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C28" s="34"/>
       <c r="D28" s="82"/>
@@ -12467,7 +12402,7 @@
         <v>4</v>
       </c>
       <c r="B29" s="34" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C29" s="34"/>
       <c r="D29" s="82"/>
@@ -12485,7 +12420,7 @@
         <v>5</v>
       </c>
       <c r="B30" s="34" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C30" s="34"/>
       <c r="D30" s="82"/>
@@ -12503,7 +12438,7 @@
         <v>6</v>
       </c>
       <c r="B31" s="34" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C31" s="34"/>
       <c r="D31" s="82"/>
@@ -12521,7 +12456,7 @@
         <v>7</v>
       </c>
       <c r="B32" s="34" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C32" s="34"/>
       <c r="D32" s="82"/>
@@ -12539,7 +12474,7 @@
         <v>8</v>
       </c>
       <c r="B33" s="34" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C33" s="34"/>
       <c r="D33" s="82"/>
@@ -12557,7 +12492,7 @@
         <v>9</v>
       </c>
       <c r="B34" s="34" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C34" s="34"/>
       <c r="D34" s="82"/>
@@ -13129,12 +13064,8 @@
       <c r="L65" s="83"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A66" s="33">
-        <v>41</v>
-      </c>
-      <c r="B66" s="34" t="s">
-        <v>156</v>
-      </c>
+      <c r="A66" s="33"/>
+      <c r="B66" s="34"/>
       <c r="C66" s="78"/>
       <c r="D66" s="82"/>
       <c r="E66" s="83"/>
@@ -16348,29 +16279,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1247" r:id="rId149" name="Drop Down 223">
-              <controlPr defaultSize="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>2</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>65</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>2</xdr:col>
-                    <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>66</xdr:row>
-                    <xdr:rowOff>38100</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1248" r:id="rId150" name="Drop Down 224">
+            <control shapeId="1248" r:id="rId149" name="Drop Down 224">
               <controlPr defaultSize="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17534,15 +17443,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101005DA7AC6E4F4FAE42B9D9FCD9C82CAAE1" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="553e0bb76796fbad2df2b84fb95dc83d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="87481c51-c14c-4071-bf64-faa2b5708bb6" xmlns:ns3="8029d101-3d2a-47c4-b15f-619642bf5e50" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d87cd7f238c73dc12c577d08dde48736" ns2:_="" ns3:_="">
     <xsd:import namespace="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
@@ -17791,7 +17691,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <SharedWithUsers xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50">
@@ -17844,15 +17744,16 @@
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371D8832-41B3-447B-B13D-2663C267E34F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F7F06D0-41B3-4EAF-B418-88FC726117CC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17871,7 +17772,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD069904-634F-48DA-AA92-BAE250498BEE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -17880,4 +17781,12 @@
     <ds:schemaRef ds:uri="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371D8832-41B3-447B-B13D-2663C267E34F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Guias Produccion/HU-57723.xlsx
+++ b/Guias Produccion/HU-57723.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Alliance\ScriptsEntidades\Guias Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A4498C8-1B0D-4B1D-AEF8-07A1BC630030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F521BE-B7E9-480B-B66D-C49F84F783D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guia de implementación" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="155">
   <si>
     <t>Guia documentación</t>
   </si>
@@ -618,19 +618,16 @@
     <t>35-AC_pro_GetPendingPickupDetails.sql</t>
   </si>
   <si>
-    <t>36-AC_pro_GetCompletedDeliveredPickupShipTo.sql</t>
+    <t>36-AC_pro_GetCompletedScheduledPickupShipTo.sql</t>
   </si>
   <si>
-    <t>37-AC_pro_GetCompletedScheduledPickupShipTo.sql</t>
+    <t>37-AC_pro_GetCompletedDeliveredPickupDetail.sql</t>
   </si>
   <si>
-    <t>38-AC_pro_GetCompletedDeliveredPickupDetail.sql</t>
+    <t>38-AC_pro_GetCompletedScheduledPickupDetail.sql</t>
   </si>
   <si>
-    <t>39-AC_pro_GetCompletedScheduledPickupDetail.sql</t>
-  </si>
-  <si>
-    <t>40-AC_pro_InsertAccountingClient.sql</t>
+    <t>39-AC_pro_InsertAccountingClient.sql</t>
   </si>
 </sst>
 </file>
@@ -1840,7 +1837,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="175">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1993,89 +1990,8 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="75" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="76" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="77" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="54" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2179,6 +2095,90 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="54" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2251,9 +2251,6 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2278,6 +2275,7 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -2497,18 +2495,14 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp144.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$18" noThreeD="1" sel="8" val="3"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$25" noThreeD="1" sel="17" val="12"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp145.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$25" noThreeD="1" sel="17" val="12"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$17" noThreeD="1" sel="17" val="9"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp146.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$17" noThreeD="1" sel="17" val="9"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp147.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$17" noThreeD="1" sel="17" val="9"/>
 </file>
 
@@ -11146,64 +11140,6 @@
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000DD040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>64</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>64</xdr:row>
-          <xdr:rowOff>220980</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1246" name="Drop Down 222" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1246"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000DE040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -11906,42 +11842,42 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:15" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="124" t="s">
+      <c r="A3" s="97" t="s">
         <v>103</v>
       </c>
-      <c r="B3" s="125"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="125"/>
-      <c r="E3" s="125"/>
-      <c r="F3" s="125"/>
-      <c r="G3" s="125"/>
-      <c r="H3" s="125"/>
-      <c r="I3" s="125"/>
-      <c r="J3" s="125"/>
-      <c r="K3" s="125"/>
-      <c r="L3" s="126"/>
-      <c r="N3" s="118" t="s">
+      <c r="B3" s="98"/>
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="98"/>
+      <c r="J3" s="98"/>
+      <c r="K3" s="98"/>
+      <c r="L3" s="99"/>
+      <c r="N3" s="91" t="s">
         <v>0</v>
       </c>
-      <c r="O3" s="119"/>
+      <c r="O3" s="92"/>
     </row>
     <row r="4" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="131" t="s">
+      <c r="B4" s="104" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="132"/>
-      <c r="D4" s="132"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="132"/>
-      <c r="G4" s="132"/>
-      <c r="H4" s="132"/>
-      <c r="I4" s="132"/>
-      <c r="J4" s="133"/>
-      <c r="K4" s="133"/>
-      <c r="L4" s="134"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="105"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="105"/>
+      <c r="I4" s="105"/>
+      <c r="J4" s="106"/>
+      <c r="K4" s="106"/>
+      <c r="L4" s="107"/>
       <c r="N4" s="21" t="s">
         <v>2</v>
       </c>
@@ -11951,19 +11887,19 @@
       <c r="A5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="135" t="s">
+      <c r="B5" s="108" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="135"/>
-      <c r="D5" s="135"/>
-      <c r="E5" s="135"/>
-      <c r="F5" s="135"/>
-      <c r="G5" s="135"/>
-      <c r="H5" s="135"/>
-      <c r="I5" s="135"/>
-      <c r="J5" s="136"/>
-      <c r="K5" s="136"/>
-      <c r="L5" s="137"/>
+      <c r="C5" s="108"/>
+      <c r="D5" s="108"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="108"/>
+      <c r="G5" s="108"/>
+      <c r="H5" s="108"/>
+      <c r="I5" s="108"/>
+      <c r="J5" s="109"/>
+      <c r="K5" s="109"/>
+      <c r="L5" s="110"/>
       <c r="N5" s="15" t="s">
         <v>4</v>
       </c>
@@ -11973,19 +11909,19 @@
       <c r="A6" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="121">
+      <c r="B6" s="94">
         <v>46073</v>
       </c>
-      <c r="C6" s="122"/>
-      <c r="D6" s="122"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="122"/>
-      <c r="J6" s="122"/>
-      <c r="K6" s="122"/>
-      <c r="L6" s="123"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="95"/>
+      <c r="K6" s="95"/>
+      <c r="L6" s="96"/>
       <c r="N6" s="14"/>
       <c r="O6" s="14"/>
     </row>
@@ -11993,17 +11929,17 @@
       <c r="A7" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="138"/>
-      <c r="C7" s="139"/>
-      <c r="D7" s="139"/>
-      <c r="E7" s="139"/>
-      <c r="F7" s="139"/>
-      <c r="G7" s="139"/>
-      <c r="H7" s="139"/>
-      <c r="I7" s="139"/>
-      <c r="J7" s="140"/>
-      <c r="K7" s="140"/>
-      <c r="L7" s="141"/>
+      <c r="B7" s="111"/>
+      <c r="C7" s="112"/>
+      <c r="D7" s="112"/>
+      <c r="E7" s="112"/>
+      <c r="F7" s="112"/>
+      <c r="G7" s="112"/>
+      <c r="H7" s="112"/>
+      <c r="I7" s="112"/>
+      <c r="J7" s="113"/>
+      <c r="K7" s="113"/>
+      <c r="L7" s="114"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
@@ -12020,20 +11956,20 @@
       <c r="L8" s="13"/>
     </row>
     <row r="9" spans="1:15" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="127" t="s">
+      <c r="A9" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="128"/>
-      <c r="C9" s="128"/>
-      <c r="D9" s="128"/>
-      <c r="E9" s="128"/>
-      <c r="F9" s="128"/>
-      <c r="G9" s="128"/>
-      <c r="H9" s="128"/>
-      <c r="I9" s="128"/>
-      <c r="J9" s="129"/>
-      <c r="K9" s="129"/>
-      <c r="L9" s="130"/>
+      <c r="B9" s="101"/>
+      <c r="C9" s="101"/>
+      <c r="D9" s="101"/>
+      <c r="E9" s="101"/>
+      <c r="F9" s="101"/>
+      <c r="G9" s="101"/>
+      <c r="H9" s="101"/>
+      <c r="I9" s="101"/>
+      <c r="J9" s="102"/>
+      <c r="K9" s="102"/>
+      <c r="L9" s="103"/>
     </row>
     <row r="10" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -12133,63 +12069,63 @@
       <c r="A14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="120"/>
-      <c r="C14" s="116"/>
-      <c r="D14" s="116"/>
-      <c r="E14" s="116"/>
-      <c r="F14" s="116"/>
-      <c r="G14" s="116"/>
-      <c r="H14" s="116"/>
-      <c r="I14" s="116"/>
-      <c r="J14" s="116"/>
-      <c r="K14" s="116"/>
-      <c r="L14" s="117"/>
+      <c r="B14" s="93"/>
+      <c r="C14" s="89"/>
+      <c r="D14" s="89"/>
+      <c r="E14" s="89"/>
+      <c r="F14" s="89"/>
+      <c r="G14" s="89"/>
+      <c r="H14" s="89"/>
+      <c r="I14" s="89"/>
+      <c r="J14" s="89"/>
+      <c r="K14" s="89"/>
+      <c r="L14" s="90"/>
     </row>
     <row r="15" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="115"/>
-      <c r="C15" s="116"/>
-      <c r="D15" s="116"/>
-      <c r="E15" s="116"/>
-      <c r="F15" s="116"/>
-      <c r="G15" s="116"/>
-      <c r="H15" s="116"/>
-      <c r="I15" s="116"/>
-      <c r="J15" s="116"/>
-      <c r="K15" s="116"/>
-      <c r="L15" s="117"/>
+      <c r="B15" s="88"/>
+      <c r="C15" s="89"/>
+      <c r="D15" s="89"/>
+      <c r="E15" s="89"/>
+      <c r="F15" s="89"/>
+      <c r="G15" s="89"/>
+      <c r="H15" s="89"/>
+      <c r="I15" s="89"/>
+      <c r="J15" s="89"/>
+      <c r="K15" s="89"/>
+      <c r="L15" s="90"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="108"/>
-      <c r="B16" s="109"/>
-      <c r="C16" s="109"/>
-      <c r="D16" s="109"/>
-      <c r="E16" s="109"/>
-      <c r="F16" s="109"/>
-      <c r="G16" s="109"/>
-      <c r="H16" s="109"/>
-      <c r="I16" s="109"/>
-      <c r="J16" s="109"/>
-      <c r="K16" s="109"/>
-      <c r="L16" s="110"/>
+      <c r="A16" s="81"/>
+      <c r="B16" s="82"/>
+      <c r="C16" s="82"/>
+      <c r="D16" s="82"/>
+      <c r="E16" s="82"/>
+      <c r="F16" s="82"/>
+      <c r="G16" s="82"/>
+      <c r="H16" s="82"/>
+      <c r="I16" s="82"/>
+      <c r="J16" s="82"/>
+      <c r="K16" s="82"/>
+      <c r="L16" s="83"/>
     </row>
     <row r="17" spans="1:12" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="111" t="s">
+      <c r="A17" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="112"/>
-      <c r="C17" s="112"/>
-      <c r="D17" s="112"/>
-      <c r="E17" s="112"/>
-      <c r="F17" s="112"/>
-      <c r="G17" s="112"/>
-      <c r="H17" s="112"/>
-      <c r="I17" s="112"/>
-      <c r="J17" s="113"/>
-      <c r="K17" s="113"/>
-      <c r="L17" s="114"/>
+      <c r="B17" s="85"/>
+      <c r="C17" s="85"/>
+      <c r="D17" s="85"/>
+      <c r="E17" s="85"/>
+      <c r="F17" s="85"/>
+      <c r="G17" s="85"/>
+      <c r="H17" s="85"/>
+      <c r="I17" s="85"/>
+      <c r="J17" s="86"/>
+      <c r="K17" s="86"/>
+      <c r="L17" s="87"/>
     </row>
     <row r="18" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
@@ -12199,19 +12135,19 @@
       <c r="C18" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="84" t="s">
+      <c r="D18" s="119" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="86" t="s">
+      <c r="E18" s="121" t="s">
         <v>115</v>
       </c>
-      <c r="F18" s="86"/>
-      <c r="G18" s="86"/>
-      <c r="H18" s="86"/>
-      <c r="I18" s="86"/>
-      <c r="J18" s="87"/>
-      <c r="K18" s="87"/>
-      <c r="L18" s="88"/>
+      <c r="F18" s="121"/>
+      <c r="G18" s="121"/>
+      <c r="H18" s="121"/>
+      <c r="I18" s="121"/>
+      <c r="J18" s="122"/>
+      <c r="K18" s="122"/>
+      <c r="L18" s="123"/>
     </row>
     <row r="19" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
@@ -12221,15 +12157,15 @@
         <v>30</v>
       </c>
       <c r="C19" s="44"/>
-      <c r="D19" s="85"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="89"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="90"/>
-      <c r="K19" s="90"/>
-      <c r="L19" s="91"/>
+      <c r="D19" s="120"/>
+      <c r="E19" s="124"/>
+      <c r="F19" s="124"/>
+      <c r="G19" s="124"/>
+      <c r="H19" s="124"/>
+      <c r="I19" s="124"/>
+      <c r="J19" s="125"/>
+      <c r="K19" s="125"/>
+      <c r="L19" s="126"/>
     </row>
     <row r="20" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
@@ -12239,15 +12175,15 @@
       <c r="C20" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="85"/>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="89"/>
-      <c r="I20" s="89"/>
-      <c r="J20" s="90"/>
-      <c r="K20" s="90"/>
-      <c r="L20" s="91"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="124"/>
+      <c r="F20" s="124"/>
+      <c r="G20" s="124"/>
+      <c r="H20" s="124"/>
+      <c r="I20" s="124"/>
+      <c r="J20" s="125"/>
+      <c r="K20" s="125"/>
+      <c r="L20" s="126"/>
     </row>
     <row r="21" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
@@ -12257,19 +12193,19 @@
       <c r="C21" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="100" t="s">
+      <c r="D21" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="102" t="s">
+      <c r="E21" s="137" t="s">
         <v>107</v>
       </c>
-      <c r="F21" s="103"/>
-      <c r="G21" s="103"/>
-      <c r="H21" s="103"/>
-      <c r="I21" s="103"/>
-      <c r="J21" s="103"/>
-      <c r="K21" s="103"/>
-      <c r="L21" s="104"/>
+      <c r="F21" s="138"/>
+      <c r="G21" s="138"/>
+      <c r="H21" s="138"/>
+      <c r="I21" s="138"/>
+      <c r="J21" s="138"/>
+      <c r="K21" s="138"/>
+      <c r="L21" s="139"/>
     </row>
     <row r="22" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
@@ -12279,45 +12215,45 @@
       <c r="C22" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="101"/>
-      <c r="E22" s="105"/>
-      <c r="F22" s="106"/>
-      <c r="G22" s="106"/>
-      <c r="H22" s="106"/>
-      <c r="I22" s="106"/>
-      <c r="J22" s="106"/>
-      <c r="K22" s="106"/>
-      <c r="L22" s="107"/>
+      <c r="D22" s="136"/>
+      <c r="E22" s="140"/>
+      <c r="F22" s="141"/>
+      <c r="G22" s="141"/>
+      <c r="H22" s="141"/>
+      <c r="I22" s="141"/>
+      <c r="J22" s="141"/>
+      <c r="K22" s="141"/>
+      <c r="L22" s="142"/>
     </row>
     <row r="23" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="93"/>
-      <c r="B23" s="94"/>
-      <c r="C23" s="94"/>
-      <c r="D23" s="95"/>
-      <c r="E23" s="95"/>
-      <c r="F23" s="95"/>
-      <c r="G23" s="95"/>
-      <c r="H23" s="95"/>
-      <c r="I23" s="95"/>
-      <c r="J23" s="95"/>
-      <c r="K23" s="95"/>
-      <c r="L23" s="96"/>
+      <c r="A23" s="128"/>
+      <c r="B23" s="129"/>
+      <c r="C23" s="129"/>
+      <c r="D23" s="130"/>
+      <c r="E23" s="130"/>
+      <c r="F23" s="130"/>
+      <c r="G23" s="130"/>
+      <c r="H23" s="130"/>
+      <c r="I23" s="130"/>
+      <c r="J23" s="130"/>
+      <c r="K23" s="130"/>
+      <c r="L23" s="131"/>
     </row>
     <row r="24" spans="1:12" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="97" t="s">
+      <c r="A24" s="132" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="98"/>
-      <c r="C24" s="98"/>
-      <c r="D24" s="98"/>
-      <c r="E24" s="98"/>
-      <c r="F24" s="98"/>
-      <c r="G24" s="98"/>
-      <c r="H24" s="98"/>
-      <c r="I24" s="98"/>
-      <c r="J24" s="98"/>
-      <c r="K24" s="98"/>
-      <c r="L24" s="99"/>
+      <c r="B24" s="133"/>
+      <c r="C24" s="133"/>
+      <c r="D24" s="133"/>
+      <c r="E24" s="133"/>
+      <c r="F24" s="133"/>
+      <c r="G24" s="133"/>
+      <c r="H24" s="133"/>
+      <c r="I24" s="133"/>
+      <c r="J24" s="133"/>
+      <c r="K24" s="133"/>
+      <c r="L24" s="134"/>
     </row>
     <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
@@ -12329,17 +12265,17 @@
       <c r="C25" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="92" t="s">
+      <c r="D25" s="127" t="s">
         <v>38</v>
       </c>
-      <c r="E25" s="92"/>
-      <c r="F25" s="92"/>
-      <c r="G25" s="92"/>
-      <c r="H25" s="92"/>
-      <c r="I25" s="92"/>
-      <c r="J25" s="92"/>
-      <c r="K25" s="92"/>
-      <c r="L25" s="92"/>
+      <c r="E25" s="127"/>
+      <c r="F25" s="127"/>
+      <c r="G25" s="127"/>
+      <c r="H25" s="127"/>
+      <c r="I25" s="127"/>
+      <c r="J25" s="127"/>
+      <c r="K25" s="127"/>
+      <c r="L25" s="127"/>
     </row>
     <row r="26" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="33">
@@ -12349,17 +12285,17 @@
         <v>120</v>
       </c>
       <c r="C26" s="34"/>
-      <c r="D26" s="80" t="s">
+      <c r="D26" s="115" t="s">
         <v>108</v>
       </c>
-      <c r="E26" s="81"/>
-      <c r="F26" s="81"/>
-      <c r="G26" s="81"/>
-      <c r="H26" s="81"/>
-      <c r="I26" s="81"/>
-      <c r="J26" s="81"/>
-      <c r="K26" s="81"/>
-      <c r="L26" s="81"/>
+      <c r="E26" s="116"/>
+      <c r="F26" s="116"/>
+      <c r="G26" s="116"/>
+      <c r="H26" s="116"/>
+      <c r="I26" s="116"/>
+      <c r="J26" s="116"/>
+      <c r="K26" s="116"/>
+      <c r="L26" s="116"/>
     </row>
     <row r="27" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
@@ -12369,15 +12305,15 @@
         <v>121</v>
       </c>
       <c r="C27" s="34"/>
-      <c r="D27" s="82"/>
-      <c r="E27" s="83"/>
-      <c r="F27" s="83"/>
-      <c r="G27" s="83"/>
-      <c r="H27" s="83"/>
-      <c r="I27" s="83"/>
-      <c r="J27" s="83"/>
-      <c r="K27" s="83"/>
-      <c r="L27" s="83"/>
+      <c r="D27" s="117"/>
+      <c r="E27" s="118"/>
+      <c r="F27" s="118"/>
+      <c r="G27" s="118"/>
+      <c r="H27" s="118"/>
+      <c r="I27" s="118"/>
+      <c r="J27" s="118"/>
+      <c r="K27" s="118"/>
+      <c r="L27" s="118"/>
     </row>
     <row r="28" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="33">
@@ -12387,15 +12323,15 @@
         <v>122</v>
       </c>
       <c r="C28" s="34"/>
-      <c r="D28" s="82"/>
-      <c r="E28" s="83"/>
-      <c r="F28" s="83"/>
-      <c r="G28" s="83"/>
-      <c r="H28" s="83"/>
-      <c r="I28" s="83"/>
-      <c r="J28" s="83"/>
-      <c r="K28" s="83"/>
-      <c r="L28" s="83"/>
+      <c r="D28" s="117"/>
+      <c r="E28" s="118"/>
+      <c r="F28" s="118"/>
+      <c r="G28" s="118"/>
+      <c r="H28" s="118"/>
+      <c r="I28" s="118"/>
+      <c r="J28" s="118"/>
+      <c r="K28" s="118"/>
+      <c r="L28" s="118"/>
     </row>
     <row r="29" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
@@ -12405,15 +12341,15 @@
         <v>123</v>
       </c>
       <c r="C29" s="34"/>
-      <c r="D29" s="82"/>
-      <c r="E29" s="83"/>
-      <c r="F29" s="83"/>
-      <c r="G29" s="83"/>
-      <c r="H29" s="83"/>
-      <c r="I29" s="83"/>
-      <c r="J29" s="83"/>
-      <c r="K29" s="83"/>
-      <c r="L29" s="83"/>
+      <c r="D29" s="117"/>
+      <c r="E29" s="118"/>
+      <c r="F29" s="118"/>
+      <c r="G29" s="118"/>
+      <c r="H29" s="118"/>
+      <c r="I29" s="118"/>
+      <c r="J29" s="118"/>
+      <c r="K29" s="118"/>
+      <c r="L29" s="118"/>
     </row>
     <row r="30" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="33">
@@ -12423,15 +12359,15 @@
         <v>124</v>
       </c>
       <c r="C30" s="34"/>
-      <c r="D30" s="82"/>
-      <c r="E30" s="83"/>
-      <c r="F30" s="83"/>
-      <c r="G30" s="83"/>
-      <c r="H30" s="83"/>
-      <c r="I30" s="83"/>
-      <c r="J30" s="83"/>
-      <c r="K30" s="83"/>
-      <c r="L30" s="83"/>
+      <c r="D30" s="117"/>
+      <c r="E30" s="118"/>
+      <c r="F30" s="118"/>
+      <c r="G30" s="118"/>
+      <c r="H30" s="118"/>
+      <c r="I30" s="118"/>
+      <c r="J30" s="118"/>
+      <c r="K30" s="118"/>
+      <c r="L30" s="118"/>
     </row>
     <row r="31" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="33">
@@ -12441,15 +12377,15 @@
         <v>116</v>
       </c>
       <c r="C31" s="34"/>
-      <c r="D31" s="82"/>
-      <c r="E31" s="83"/>
-      <c r="F31" s="83"/>
-      <c r="G31" s="83"/>
-      <c r="H31" s="83"/>
-      <c r="I31" s="83"/>
-      <c r="J31" s="83"/>
-      <c r="K31" s="83"/>
-      <c r="L31" s="83"/>
+      <c r="D31" s="117"/>
+      <c r="E31" s="118"/>
+      <c r="F31" s="118"/>
+      <c r="G31" s="118"/>
+      <c r="H31" s="118"/>
+      <c r="I31" s="118"/>
+      <c r="J31" s="118"/>
+      <c r="K31" s="118"/>
+      <c r="L31" s="118"/>
     </row>
     <row r="32" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="33">
@@ -12459,15 +12395,15 @@
         <v>117</v>
       </c>
       <c r="C32" s="34"/>
-      <c r="D32" s="82"/>
-      <c r="E32" s="83"/>
-      <c r="F32" s="83"/>
-      <c r="G32" s="83"/>
-      <c r="H32" s="83"/>
-      <c r="I32" s="83"/>
-      <c r="J32" s="83"/>
-      <c r="K32" s="83"/>
-      <c r="L32" s="83"/>
+      <c r="D32" s="117"/>
+      <c r="E32" s="118"/>
+      <c r="F32" s="118"/>
+      <c r="G32" s="118"/>
+      <c r="H32" s="118"/>
+      <c r="I32" s="118"/>
+      <c r="J32" s="118"/>
+      <c r="K32" s="118"/>
+      <c r="L32" s="118"/>
     </row>
     <row r="33" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="33">
@@ -12477,15 +12413,15 @@
         <v>118</v>
       </c>
       <c r="C33" s="34"/>
-      <c r="D33" s="82"/>
-      <c r="E33" s="83"/>
-      <c r="F33" s="83"/>
-      <c r="G33" s="83"/>
-      <c r="H33" s="83"/>
-      <c r="I33" s="83"/>
-      <c r="J33" s="83"/>
-      <c r="K33" s="83"/>
-      <c r="L33" s="83"/>
+      <c r="D33" s="117"/>
+      <c r="E33" s="118"/>
+      <c r="F33" s="118"/>
+      <c r="G33" s="118"/>
+      <c r="H33" s="118"/>
+      <c r="I33" s="118"/>
+      <c r="J33" s="118"/>
+      <c r="K33" s="118"/>
+      <c r="L33" s="118"/>
     </row>
     <row r="34" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="33">
@@ -12495,15 +12431,15 @@
         <v>119</v>
       </c>
       <c r="C34" s="34"/>
-      <c r="D34" s="82"/>
-      <c r="E34" s="83"/>
-      <c r="F34" s="83"/>
-      <c r="G34" s="83"/>
-      <c r="H34" s="83"/>
-      <c r="I34" s="83"/>
-      <c r="J34" s="83"/>
-      <c r="K34" s="83"/>
-      <c r="L34" s="83"/>
+      <c r="D34" s="117"/>
+      <c r="E34" s="118"/>
+      <c r="F34" s="118"/>
+      <c r="G34" s="118"/>
+      <c r="H34" s="118"/>
+      <c r="I34" s="118"/>
+      <c r="J34" s="118"/>
+      <c r="K34" s="118"/>
+      <c r="L34" s="118"/>
     </row>
     <row r="35" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="33">
@@ -12513,15 +12449,15 @@
         <v>125</v>
       </c>
       <c r="C35" s="34"/>
-      <c r="D35" s="82"/>
-      <c r="E35" s="83"/>
-      <c r="F35" s="83"/>
-      <c r="G35" s="83"/>
-      <c r="H35" s="83"/>
-      <c r="I35" s="83"/>
-      <c r="J35" s="83"/>
-      <c r="K35" s="83"/>
-      <c r="L35" s="83"/>
+      <c r="D35" s="117"/>
+      <c r="E35" s="118"/>
+      <c r="F35" s="118"/>
+      <c r="G35" s="118"/>
+      <c r="H35" s="118"/>
+      <c r="I35" s="118"/>
+      <c r="J35" s="118"/>
+      <c r="K35" s="118"/>
+      <c r="L35" s="118"/>
     </row>
     <row r="36" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="33">
@@ -12531,15 +12467,15 @@
         <v>126</v>
       </c>
       <c r="C36" s="34"/>
-      <c r="D36" s="82"/>
-      <c r="E36" s="83"/>
-      <c r="F36" s="83"/>
-      <c r="G36" s="83"/>
-      <c r="H36" s="83"/>
-      <c r="I36" s="83"/>
-      <c r="J36" s="83"/>
-      <c r="K36" s="83"/>
-      <c r="L36" s="83"/>
+      <c r="D36" s="117"/>
+      <c r="E36" s="118"/>
+      <c r="F36" s="118"/>
+      <c r="G36" s="118"/>
+      <c r="H36" s="118"/>
+      <c r="I36" s="118"/>
+      <c r="J36" s="118"/>
+      <c r="K36" s="118"/>
+      <c r="L36" s="118"/>
     </row>
     <row r="37" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="33">
@@ -12549,15 +12485,15 @@
         <v>127</v>
       </c>
       <c r="C37" s="34"/>
-      <c r="D37" s="82"/>
-      <c r="E37" s="83"/>
-      <c r="F37" s="83"/>
-      <c r="G37" s="83"/>
-      <c r="H37" s="83"/>
-      <c r="I37" s="83"/>
-      <c r="J37" s="83"/>
-      <c r="K37" s="83"/>
-      <c r="L37" s="83"/>
+      <c r="D37" s="117"/>
+      <c r="E37" s="118"/>
+      <c r="F37" s="118"/>
+      <c r="G37" s="118"/>
+      <c r="H37" s="118"/>
+      <c r="I37" s="118"/>
+      <c r="J37" s="118"/>
+      <c r="K37" s="118"/>
+      <c r="L37" s="118"/>
     </row>
     <row r="38" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="33">
@@ -12567,15 +12503,15 @@
         <v>128</v>
       </c>
       <c r="C38" s="34"/>
-      <c r="D38" s="82"/>
-      <c r="E38" s="83"/>
-      <c r="F38" s="83"/>
-      <c r="G38" s="83"/>
-      <c r="H38" s="83"/>
-      <c r="I38" s="83"/>
-      <c r="J38" s="83"/>
-      <c r="K38" s="83"/>
-      <c r="L38" s="83"/>
+      <c r="D38" s="117"/>
+      <c r="E38" s="118"/>
+      <c r="F38" s="118"/>
+      <c r="G38" s="118"/>
+      <c r="H38" s="118"/>
+      <c r="I38" s="118"/>
+      <c r="J38" s="118"/>
+      <c r="K38" s="118"/>
+      <c r="L38" s="118"/>
     </row>
     <row r="39" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="33">
@@ -12585,15 +12521,15 @@
         <v>129</v>
       </c>
       <c r="C39" s="34"/>
-      <c r="D39" s="82"/>
-      <c r="E39" s="83"/>
-      <c r="F39" s="83"/>
-      <c r="G39" s="83"/>
-      <c r="H39" s="83"/>
-      <c r="I39" s="83"/>
-      <c r="J39" s="83"/>
-      <c r="K39" s="83"/>
-      <c r="L39" s="83"/>
+      <c r="D39" s="117"/>
+      <c r="E39" s="118"/>
+      <c r="F39" s="118"/>
+      <c r="G39" s="118"/>
+      <c r="H39" s="118"/>
+      <c r="I39" s="118"/>
+      <c r="J39" s="118"/>
+      <c r="K39" s="118"/>
+      <c r="L39" s="118"/>
     </row>
     <row r="40" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="33">
@@ -12603,15 +12539,15 @@
         <v>130</v>
       </c>
       <c r="C40" s="34"/>
-      <c r="D40" s="82"/>
-      <c r="E40" s="83"/>
-      <c r="F40" s="83"/>
-      <c r="G40" s="83"/>
-      <c r="H40" s="83"/>
-      <c r="I40" s="83"/>
-      <c r="J40" s="83"/>
-      <c r="K40" s="83"/>
-      <c r="L40" s="83"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="118"/>
+      <c r="H40" s="118"/>
+      <c r="I40" s="118"/>
+      <c r="J40" s="118"/>
+      <c r="K40" s="118"/>
+      <c r="L40" s="118"/>
     </row>
     <row r="41" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="33">
@@ -12621,15 +12557,15 @@
         <v>131</v>
       </c>
       <c r="C41" s="34"/>
-      <c r="D41" s="82"/>
-      <c r="E41" s="83"/>
-      <c r="F41" s="83"/>
-      <c r="G41" s="83"/>
-      <c r="H41" s="83"/>
-      <c r="I41" s="83"/>
-      <c r="J41" s="83"/>
-      <c r="K41" s="83"/>
-      <c r="L41" s="83"/>
+      <c r="D41" s="117"/>
+      <c r="E41" s="118"/>
+      <c r="F41" s="118"/>
+      <c r="G41" s="118"/>
+      <c r="H41" s="118"/>
+      <c r="I41" s="118"/>
+      <c r="J41" s="118"/>
+      <c r="K41" s="118"/>
+      <c r="L41" s="118"/>
     </row>
     <row r="42" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="33">
@@ -12639,15 +12575,15 @@
         <v>132</v>
       </c>
       <c r="C42" s="34"/>
-      <c r="D42" s="82"/>
-      <c r="E42" s="83"/>
-      <c r="F42" s="83"/>
-      <c r="G42" s="83"/>
-      <c r="H42" s="83"/>
-      <c r="I42" s="83"/>
-      <c r="J42" s="83"/>
-      <c r="K42" s="83"/>
-      <c r="L42" s="83"/>
+      <c r="D42" s="117"/>
+      <c r="E42" s="118"/>
+      <c r="F42" s="118"/>
+      <c r="G42" s="118"/>
+      <c r="H42" s="118"/>
+      <c r="I42" s="118"/>
+      <c r="J42" s="118"/>
+      <c r="K42" s="118"/>
+      <c r="L42" s="118"/>
     </row>
     <row r="43" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="33">
@@ -12657,15 +12593,15 @@
         <v>133</v>
       </c>
       <c r="C43" s="34"/>
-      <c r="D43" s="82"/>
-      <c r="E43" s="83"/>
-      <c r="F43" s="83"/>
-      <c r="G43" s="83"/>
-      <c r="H43" s="83"/>
-      <c r="I43" s="83"/>
-      <c r="J43" s="83"/>
-      <c r="K43" s="83"/>
-      <c r="L43" s="83"/>
+      <c r="D43" s="117"/>
+      <c r="E43" s="118"/>
+      <c r="F43" s="118"/>
+      <c r="G43" s="118"/>
+      <c r="H43" s="118"/>
+      <c r="I43" s="118"/>
+      <c r="J43" s="118"/>
+      <c r="K43" s="118"/>
+      <c r="L43" s="118"/>
     </row>
     <row r="44" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="33">
@@ -12675,15 +12611,15 @@
         <v>134</v>
       </c>
       <c r="C44" s="34"/>
-      <c r="D44" s="82"/>
-      <c r="E44" s="83"/>
-      <c r="F44" s="83"/>
-      <c r="G44" s="83"/>
-      <c r="H44" s="83"/>
-      <c r="I44" s="83"/>
-      <c r="J44" s="83"/>
-      <c r="K44" s="83"/>
-      <c r="L44" s="83"/>
+      <c r="D44" s="117"/>
+      <c r="E44" s="118"/>
+      <c r="F44" s="118"/>
+      <c r="G44" s="118"/>
+      <c r="H44" s="118"/>
+      <c r="I44" s="118"/>
+      <c r="J44" s="118"/>
+      <c r="K44" s="118"/>
+      <c r="L44" s="118"/>
     </row>
     <row r="45" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="33">
@@ -12693,15 +12629,15 @@
         <v>135</v>
       </c>
       <c r="C45" s="34"/>
-      <c r="D45" s="82"/>
-      <c r="E45" s="83"/>
-      <c r="F45" s="83"/>
-      <c r="G45" s="83"/>
-      <c r="H45" s="83"/>
-      <c r="I45" s="83"/>
-      <c r="J45" s="83"/>
-      <c r="K45" s="83"/>
-      <c r="L45" s="83"/>
+      <c r="D45" s="117"/>
+      <c r="E45" s="118"/>
+      <c r="F45" s="118"/>
+      <c r="G45" s="118"/>
+      <c r="H45" s="118"/>
+      <c r="I45" s="118"/>
+      <c r="J45" s="118"/>
+      <c r="K45" s="118"/>
+      <c r="L45" s="118"/>
     </row>
     <row r="46" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="33">
@@ -12711,15 +12647,15 @@
         <v>136</v>
       </c>
       <c r="C46" s="34"/>
-      <c r="D46" s="82"/>
-      <c r="E46" s="83"/>
-      <c r="F46" s="83"/>
-      <c r="G46" s="83"/>
-      <c r="H46" s="83"/>
-      <c r="I46" s="83"/>
-      <c r="J46" s="83"/>
-      <c r="K46" s="83"/>
-      <c r="L46" s="83"/>
+      <c r="D46" s="117"/>
+      <c r="E46" s="118"/>
+      <c r="F46" s="118"/>
+      <c r="G46" s="118"/>
+      <c r="H46" s="118"/>
+      <c r="I46" s="118"/>
+      <c r="J46" s="118"/>
+      <c r="K46" s="118"/>
+      <c r="L46" s="118"/>
     </row>
     <row r="47" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="33">
@@ -12729,15 +12665,15 @@
         <v>137</v>
       </c>
       <c r="C47" s="34"/>
-      <c r="D47" s="82"/>
-      <c r="E47" s="83"/>
-      <c r="F47" s="83"/>
-      <c r="G47" s="83"/>
-      <c r="H47" s="83"/>
-      <c r="I47" s="83"/>
-      <c r="J47" s="83"/>
-      <c r="K47" s="83"/>
-      <c r="L47" s="83"/>
+      <c r="D47" s="117"/>
+      <c r="E47" s="118"/>
+      <c r="F47" s="118"/>
+      <c r="G47" s="118"/>
+      <c r="H47" s="118"/>
+      <c r="I47" s="118"/>
+      <c r="J47" s="118"/>
+      <c r="K47" s="118"/>
+      <c r="L47" s="118"/>
     </row>
     <row r="48" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="33">
@@ -12747,15 +12683,15 @@
         <v>138</v>
       </c>
       <c r="C48" s="34"/>
-      <c r="D48" s="82"/>
-      <c r="E48" s="83"/>
-      <c r="F48" s="83"/>
-      <c r="G48" s="83"/>
-      <c r="H48" s="83"/>
-      <c r="I48" s="83"/>
-      <c r="J48" s="83"/>
-      <c r="K48" s="83"/>
-      <c r="L48" s="83"/>
+      <c r="D48" s="117"/>
+      <c r="E48" s="118"/>
+      <c r="F48" s="118"/>
+      <c r="G48" s="118"/>
+      <c r="H48" s="118"/>
+      <c r="I48" s="118"/>
+      <c r="J48" s="118"/>
+      <c r="K48" s="118"/>
+      <c r="L48" s="118"/>
     </row>
     <row r="49" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="33">
@@ -12765,15 +12701,15 @@
         <v>139</v>
       </c>
       <c r="C49" s="34"/>
-      <c r="D49" s="82"/>
-      <c r="E49" s="83"/>
-      <c r="F49" s="83"/>
-      <c r="G49" s="83"/>
-      <c r="H49" s="83"/>
-      <c r="I49" s="83"/>
-      <c r="J49" s="83"/>
-      <c r="K49" s="83"/>
-      <c r="L49" s="83"/>
+      <c r="D49" s="117"/>
+      <c r="E49" s="118"/>
+      <c r="F49" s="118"/>
+      <c r="G49" s="118"/>
+      <c r="H49" s="118"/>
+      <c r="I49" s="118"/>
+      <c r="J49" s="118"/>
+      <c r="K49" s="118"/>
+      <c r="L49" s="118"/>
     </row>
     <row r="50" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="33">
@@ -12783,15 +12719,15 @@
         <v>140</v>
       </c>
       <c r="C50" s="34"/>
-      <c r="D50" s="82"/>
-      <c r="E50" s="83"/>
-      <c r="F50" s="83"/>
-      <c r="G50" s="83"/>
-      <c r="H50" s="83"/>
-      <c r="I50" s="83"/>
-      <c r="J50" s="83"/>
-      <c r="K50" s="83"/>
-      <c r="L50" s="83"/>
+      <c r="D50" s="117"/>
+      <c r="E50" s="118"/>
+      <c r="F50" s="118"/>
+      <c r="G50" s="118"/>
+      <c r="H50" s="118"/>
+      <c r="I50" s="118"/>
+      <c r="J50" s="118"/>
+      <c r="K50" s="118"/>
+      <c r="L50" s="118"/>
     </row>
     <row r="51" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="33">
@@ -12801,15 +12737,15 @@
         <v>141</v>
       </c>
       <c r="C51" s="34"/>
-      <c r="D51" s="82"/>
-      <c r="E51" s="83"/>
-      <c r="F51" s="83"/>
-      <c r="G51" s="83"/>
-      <c r="H51" s="83"/>
-      <c r="I51" s="83"/>
-      <c r="J51" s="83"/>
-      <c r="K51" s="83"/>
-      <c r="L51" s="83"/>
+      <c r="D51" s="117"/>
+      <c r="E51" s="118"/>
+      <c r="F51" s="118"/>
+      <c r="G51" s="118"/>
+      <c r="H51" s="118"/>
+      <c r="I51" s="118"/>
+      <c r="J51" s="118"/>
+      <c r="K51" s="118"/>
+      <c r="L51" s="118"/>
     </row>
     <row r="52" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="33">
@@ -12819,15 +12755,15 @@
         <v>142</v>
       </c>
       <c r="C52" s="34"/>
-      <c r="D52" s="82"/>
-      <c r="E52" s="83"/>
-      <c r="F52" s="83"/>
-      <c r="G52" s="83"/>
-      <c r="H52" s="83"/>
-      <c r="I52" s="83"/>
-      <c r="J52" s="83"/>
-      <c r="K52" s="83"/>
-      <c r="L52" s="83"/>
+      <c r="D52" s="117"/>
+      <c r="E52" s="118"/>
+      <c r="F52" s="118"/>
+      <c r="G52" s="118"/>
+      <c r="H52" s="118"/>
+      <c r="I52" s="118"/>
+      <c r="J52" s="118"/>
+      <c r="K52" s="118"/>
+      <c r="L52" s="118"/>
     </row>
     <row r="53" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="33">
@@ -12837,33 +12773,33 @@
         <v>143</v>
       </c>
       <c r="C53" s="34"/>
-      <c r="D53" s="82"/>
-      <c r="E53" s="83"/>
-      <c r="F53" s="83"/>
-      <c r="G53" s="83"/>
-      <c r="H53" s="83"/>
-      <c r="I53" s="83"/>
-      <c r="J53" s="83"/>
-      <c r="K53" s="83"/>
-      <c r="L53" s="83"/>
+      <c r="D53" s="117"/>
+      <c r="E53" s="118"/>
+      <c r="F53" s="118"/>
+      <c r="G53" s="118"/>
+      <c r="H53" s="118"/>
+      <c r="I53" s="118"/>
+      <c r="J53" s="118"/>
+      <c r="K53" s="118"/>
+      <c r="L53" s="118"/>
     </row>
     <row r="54" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="33">
         <v>29</v>
       </c>
-      <c r="B54" s="78" t="s">
+      <c r="B54" s="175" t="s">
         <v>144</v>
       </c>
       <c r="C54" s="79"/>
-      <c r="D54" s="82"/>
-      <c r="E54" s="83"/>
-      <c r="F54" s="83"/>
-      <c r="G54" s="83"/>
-      <c r="H54" s="83"/>
-      <c r="I54" s="83"/>
-      <c r="J54" s="83"/>
-      <c r="K54" s="83"/>
-      <c r="L54" s="83"/>
+      <c r="D54" s="117"/>
+      <c r="E54" s="118"/>
+      <c r="F54" s="118"/>
+      <c r="G54" s="118"/>
+      <c r="H54" s="118"/>
+      <c r="I54" s="118"/>
+      <c r="J54" s="118"/>
+      <c r="K54" s="118"/>
+      <c r="L54" s="118"/>
     </row>
     <row r="55" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="33">
@@ -12873,15 +12809,15 @@
         <v>145</v>
       </c>
       <c r="C55" s="72"/>
-      <c r="D55" s="82"/>
-      <c r="E55" s="83"/>
-      <c r="F55" s="83"/>
-      <c r="G55" s="83"/>
-      <c r="H55" s="83"/>
-      <c r="I55" s="83"/>
-      <c r="J55" s="83"/>
-      <c r="K55" s="83"/>
-      <c r="L55" s="83"/>
+      <c r="D55" s="117"/>
+      <c r="E55" s="118"/>
+      <c r="F55" s="118"/>
+      <c r="G55" s="118"/>
+      <c r="H55" s="118"/>
+      <c r="I55" s="118"/>
+      <c r="J55" s="118"/>
+      <c r="K55" s="118"/>
+      <c r="L55" s="118"/>
     </row>
     <row r="56" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="33">
@@ -12891,15 +12827,15 @@
         <v>146</v>
       </c>
       <c r="C56" s="78"/>
-      <c r="D56" s="82"/>
-      <c r="E56" s="83"/>
-      <c r="F56" s="83"/>
-      <c r="G56" s="83"/>
-      <c r="H56" s="83"/>
-      <c r="I56" s="83"/>
-      <c r="J56" s="83"/>
-      <c r="K56" s="83"/>
-      <c r="L56" s="83"/>
+      <c r="D56" s="117"/>
+      <c r="E56" s="118"/>
+      <c r="F56" s="118"/>
+      <c r="G56" s="118"/>
+      <c r="H56" s="118"/>
+      <c r="I56" s="118"/>
+      <c r="J56" s="118"/>
+      <c r="K56" s="118"/>
+      <c r="L56" s="118"/>
     </row>
     <row r="57" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="33">
@@ -12909,51 +12845,51 @@
         <v>147</v>
       </c>
       <c r="C57" s="78"/>
-      <c r="D57" s="82"/>
-      <c r="E57" s="83"/>
-      <c r="F57" s="83"/>
-      <c r="G57" s="83"/>
-      <c r="H57" s="83"/>
-      <c r="I57" s="83"/>
-      <c r="J57" s="83"/>
-      <c r="K57" s="83"/>
-      <c r="L57" s="83"/>
+      <c r="D57" s="117"/>
+      <c r="E57" s="118"/>
+      <c r="F57" s="118"/>
+      <c r="G57" s="118"/>
+      <c r="H57" s="118"/>
+      <c r="I57" s="118"/>
+      <c r="J57" s="118"/>
+      <c r="K57" s="118"/>
+      <c r="L57" s="118"/>
     </row>
     <row r="58" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="33">
         <v>33</v>
       </c>
-      <c r="B58" s="78" t="s">
+      <c r="B58" s="175" t="s">
         <v>148</v>
       </c>
       <c r="C58" s="78"/>
-      <c r="D58" s="82"/>
-      <c r="E58" s="83"/>
-      <c r="F58" s="83"/>
-      <c r="G58" s="83"/>
-      <c r="H58" s="83"/>
-      <c r="I58" s="83"/>
-      <c r="J58" s="83"/>
-      <c r="K58" s="83"/>
-      <c r="L58" s="83"/>
+      <c r="D58" s="117"/>
+      <c r="E58" s="118"/>
+      <c r="F58" s="118"/>
+      <c r="G58" s="118"/>
+      <c r="H58" s="118"/>
+      <c r="I58" s="118"/>
+      <c r="J58" s="118"/>
+      <c r="K58" s="118"/>
+      <c r="L58" s="118"/>
     </row>
     <row r="59" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="33">
         <v>34</v>
       </c>
-      <c r="B59" s="78" t="s">
+      <c r="B59" s="175" t="s">
         <v>149</v>
       </c>
       <c r="C59" s="78"/>
-      <c r="D59" s="82"/>
-      <c r="E59" s="83"/>
-      <c r="F59" s="83"/>
-      <c r="G59" s="83"/>
-      <c r="H59" s="83"/>
-      <c r="I59" s="83"/>
-      <c r="J59" s="83"/>
-      <c r="K59" s="83"/>
-      <c r="L59" s="83"/>
+      <c r="D59" s="117"/>
+      <c r="E59" s="118"/>
+      <c r="F59" s="118"/>
+      <c r="G59" s="118"/>
+      <c r="H59" s="118"/>
+      <c r="I59" s="118"/>
+      <c r="J59" s="118"/>
+      <c r="K59" s="118"/>
+      <c r="L59" s="118"/>
     </row>
     <row r="60" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="33">
@@ -12963,15 +12899,15 @@
         <v>150</v>
       </c>
       <c r="C60" s="78"/>
-      <c r="D60" s="82"/>
-      <c r="E60" s="83"/>
-      <c r="F60" s="83"/>
-      <c r="G60" s="83"/>
-      <c r="H60" s="83"/>
-      <c r="I60" s="83"/>
-      <c r="J60" s="83"/>
-      <c r="K60" s="83"/>
-      <c r="L60" s="83"/>
+      <c r="D60" s="117"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="118"/>
+      <c r="L60" s="118"/>
     </row>
     <row r="61" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="33">
@@ -12981,15 +12917,15 @@
         <v>151</v>
       </c>
       <c r="C61" s="78"/>
-      <c r="D61" s="82"/>
-      <c r="E61" s="83"/>
-      <c r="F61" s="83"/>
-      <c r="G61" s="83"/>
-      <c r="H61" s="83"/>
-      <c r="I61" s="83"/>
-      <c r="J61" s="83"/>
-      <c r="K61" s="83"/>
-      <c r="L61" s="83"/>
+      <c r="D61" s="117"/>
+      <c r="E61" s="118"/>
+      <c r="F61" s="118"/>
+      <c r="G61" s="118"/>
+      <c r="H61" s="118"/>
+      <c r="I61" s="118"/>
+      <c r="J61" s="118"/>
+      <c r="K61" s="118"/>
+      <c r="L61" s="118"/>
     </row>
     <row r="62" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="33">
@@ -12999,15 +12935,15 @@
         <v>152</v>
       </c>
       <c r="C62" s="78"/>
-      <c r="D62" s="82"/>
-      <c r="E62" s="83"/>
-      <c r="F62" s="83"/>
-      <c r="G62" s="83"/>
-      <c r="H62" s="83"/>
-      <c r="I62" s="83"/>
-      <c r="J62" s="83"/>
-      <c r="K62" s="83"/>
-      <c r="L62" s="83"/>
+      <c r="D62" s="117"/>
+      <c r="E62" s="118"/>
+      <c r="F62" s="118"/>
+      <c r="G62" s="118"/>
+      <c r="H62" s="118"/>
+      <c r="I62" s="118"/>
+      <c r="J62" s="118"/>
+      <c r="K62" s="118"/>
+      <c r="L62" s="118"/>
     </row>
     <row r="63" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="33">
@@ -13017,15 +12953,15 @@
         <v>153</v>
       </c>
       <c r="C63" s="78"/>
-      <c r="D63" s="82"/>
-      <c r="E63" s="83"/>
-      <c r="F63" s="83"/>
-      <c r="G63" s="83"/>
-      <c r="H63" s="83"/>
-      <c r="I63" s="83"/>
-      <c r="J63" s="83"/>
-      <c r="K63" s="83"/>
-      <c r="L63" s="83"/>
+      <c r="D63" s="117"/>
+      <c r="E63" s="118"/>
+      <c r="F63" s="118"/>
+      <c r="G63" s="118"/>
+      <c r="H63" s="118"/>
+      <c r="I63" s="118"/>
+      <c r="J63" s="118"/>
+      <c r="K63" s="118"/>
+      <c r="L63" s="118"/>
     </row>
     <row r="64" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="33">
@@ -13035,50 +12971,54 @@
         <v>154</v>
       </c>
       <c r="C64" s="78"/>
-      <c r="D64" s="82"/>
-      <c r="E64" s="83"/>
-      <c r="F64" s="83"/>
-      <c r="G64" s="83"/>
-      <c r="H64" s="83"/>
-      <c r="I64" s="83"/>
-      <c r="J64" s="83"/>
-      <c r="K64" s="83"/>
-      <c r="L64" s="83"/>
+      <c r="D64" s="117"/>
+      <c r="E64" s="118"/>
+      <c r="F64" s="118"/>
+      <c r="G64" s="118"/>
+      <c r="H64" s="118"/>
+      <c r="I64" s="118"/>
+      <c r="J64" s="118"/>
+      <c r="K64" s="118"/>
+      <c r="L64" s="118"/>
     </row>
     <row r="65" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="33">
-        <v>40</v>
-      </c>
-      <c r="B65" s="78" t="s">
-        <v>155</v>
-      </c>
+      <c r="A65" s="33"/>
+      <c r="B65" s="33"/>
       <c r="C65" s="78"/>
-      <c r="D65" s="82"/>
-      <c r="E65" s="83"/>
-      <c r="F65" s="83"/>
-      <c r="G65" s="83"/>
-      <c r="H65" s="83"/>
-      <c r="I65" s="83"/>
-      <c r="J65" s="83"/>
-      <c r="K65" s="83"/>
-      <c r="L65" s="83"/>
+      <c r="D65" s="117"/>
+      <c r="E65" s="118"/>
+      <c r="F65" s="118"/>
+      <c r="G65" s="118"/>
+      <c r="H65" s="118"/>
+      <c r="I65" s="118"/>
+      <c r="J65" s="118"/>
+      <c r="K65" s="118"/>
+      <c r="L65" s="118"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="33"/>
       <c r="B66" s="34"/>
       <c r="C66" s="78"/>
-      <c r="D66" s="82"/>
-      <c r="E66" s="83"/>
-      <c r="F66" s="83"/>
-      <c r="G66" s="83"/>
-      <c r="H66" s="83"/>
-      <c r="I66" s="83"/>
-      <c r="J66" s="83"/>
-      <c r="K66" s="83"/>
-      <c r="L66" s="83"/>
+      <c r="D66" s="117"/>
+      <c r="E66" s="118"/>
+      <c r="F66" s="118"/>
+      <c r="G66" s="118"/>
+      <c r="H66" s="118"/>
+      <c r="I66" s="118"/>
+      <c r="J66" s="118"/>
+      <c r="K66" s="118"/>
+      <c r="L66" s="118"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="D26:L66"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:L20"/>
+    <mergeCell ref="D25:L25"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:L22"/>
     <mergeCell ref="A16:L16"/>
     <mergeCell ref="A17:L17"/>
     <mergeCell ref="B15:L15"/>
@@ -13090,14 +13030,6 @@
     <mergeCell ref="B4:L4"/>
     <mergeCell ref="B5:L5"/>
     <mergeCell ref="B7:L7"/>
-    <mergeCell ref="D26:L66"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:L20"/>
-    <mergeCell ref="D25:L25"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:L22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D26" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -16257,29 +16189,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1246" r:id="rId148" name="Drop Down 222">
-              <controlPr defaultSize="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>2</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>64</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>2</xdr:col>
-                    <xdr:colOff>1409700</xdr:colOff>
-                    <xdr:row>64</xdr:row>
-                    <xdr:rowOff>220980</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1248" r:id="rId149" name="Drop Down 224">
+            <control shapeId="1248" r:id="rId148" name="Drop Down 224">
               <controlPr defaultSize="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16322,50 +16232,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="152" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="152"/>
-      <c r="G1" s="152"/>
-      <c r="H1" s="152"/>
-      <c r="I1" s="152"/>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
-      <c r="L1" s="153"/>
+      <c r="B1" s="153"/>
+      <c r="C1" s="153"/>
+      <c r="D1" s="153"/>
+      <c r="E1" s="153"/>
+      <c r="F1" s="153"/>
+      <c r="G1" s="153"/>
+      <c r="H1" s="153"/>
+      <c r="I1" s="153"/>
+      <c r="J1" s="153"/>
+      <c r="K1" s="153"/>
+      <c r="L1" s="154"/>
     </row>
     <row r="2" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="154" t="s">
+      <c r="A2" s="155" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="155"/>
-      <c r="C2" s="155"/>
-      <c r="D2" s="155"/>
-      <c r="E2" s="155"/>
-      <c r="F2" s="155"/>
-      <c r="G2" s="155"/>
-      <c r="H2" s="155"/>
-      <c r="I2" s="155"/>
-      <c r="J2" s="155"/>
-      <c r="K2" s="155"/>
-      <c r="L2" s="156"/>
+      <c r="B2" s="156"/>
+      <c r="C2" s="156"/>
+      <c r="D2" s="156"/>
+      <c r="E2" s="156"/>
+      <c r="F2" s="156"/>
+      <c r="G2" s="156"/>
+      <c r="H2" s="156"/>
+      <c r="I2" s="156"/>
+      <c r="J2" s="156"/>
+      <c r="K2" s="156"/>
+      <c r="L2" s="157"/>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="157"/>
-      <c r="B3" s="158"/>
-      <c r="C3" s="158"/>
-      <c r="D3" s="158"/>
-      <c r="E3" s="158"/>
-      <c r="F3" s="158"/>
-      <c r="G3" s="158"/>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="158"/>
-      <c r="K3" s="158"/>
-      <c r="L3" s="159"/>
+      <c r="A3" s="158"/>
+      <c r="B3" s="159"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="159"/>
+      <c r="G3" s="159"/>
+      <c r="H3" s="159"/>
+      <c r="I3" s="159"/>
+      <c r="J3" s="159"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="160"/>
     </row>
     <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
@@ -16455,65 +16365,65 @@
       <c r="A8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="162"/>
-      <c r="C8" s="163"/>
-      <c r="D8" s="163"/>
-      <c r="E8" s="163"/>
-      <c r="F8" s="163"/>
-      <c r="G8" s="163"/>
-      <c r="H8" s="163"/>
-      <c r="I8" s="163"/>
-      <c r="J8" s="163"/>
-      <c r="K8" s="163"/>
-      <c r="L8" s="164"/>
+      <c r="B8" s="163"/>
+      <c r="C8" s="164"/>
+      <c r="D8" s="164"/>
+      <c r="E8" s="164"/>
+      <c r="F8" s="164"/>
+      <c r="G8" s="164"/>
+      <c r="H8" s="164"/>
+      <c r="I8" s="164"/>
+      <c r="J8" s="164"/>
+      <c r="K8" s="164"/>
+      <c r="L8" s="165"/>
     </row>
     <row r="9" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="165"/>
-      <c r="C9" s="163"/>
-      <c r="D9" s="163"/>
-      <c r="E9" s="163"/>
-      <c r="F9" s="163"/>
-      <c r="G9" s="163"/>
-      <c r="H9" s="163"/>
-      <c r="I9" s="163"/>
-      <c r="J9" s="163"/>
-      <c r="K9" s="163"/>
-      <c r="L9" s="164"/>
+      <c r="B9" s="166"/>
+      <c r="C9" s="164"/>
+      <c r="D9" s="164"/>
+      <c r="E9" s="164"/>
+      <c r="F9" s="164"/>
+      <c r="G9" s="164"/>
+      <c r="H9" s="164"/>
+      <c r="I9" s="164"/>
+      <c r="J9" s="164"/>
+      <c r="K9" s="164"/>
+      <c r="L9" s="165"/>
     </row>
     <row r="10" spans="1:12" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="160" t="s">
+      <c r="A10" s="161" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="161"/>
-      <c r="C10" s="161"/>
-      <c r="D10" s="161"/>
-      <c r="E10" s="161"/>
-      <c r="F10" s="161"/>
-      <c r="G10" s="161"/>
-      <c r="H10" s="161"/>
-      <c r="I10" s="161"/>
-      <c r="J10" s="161"/>
-      <c r="K10" s="161"/>
-      <c r="L10" s="161"/>
+      <c r="B10" s="162"/>
+      <c r="C10" s="162"/>
+      <c r="D10" s="162"/>
+      <c r="E10" s="162"/>
+      <c r="F10" s="162"/>
+      <c r="G10" s="162"/>
+      <c r="H10" s="162"/>
+      <c r="I10" s="162"/>
+      <c r="J10" s="162"/>
+      <c r="K10" s="162"/>
+      <c r="L10" s="162"/>
     </row>
     <row r="11" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="142" t="s">
+      <c r="A11" s="143" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="143"/>
-      <c r="C11" s="143"/>
-      <c r="D11" s="143"/>
-      <c r="E11" s="143"/>
-      <c r="F11" s="143"/>
-      <c r="G11" s="143"/>
-      <c r="H11" s="143"/>
-      <c r="I11" s="143"/>
-      <c r="J11" s="143"/>
-      <c r="K11" s="143"/>
-      <c r="L11" s="144"/>
+      <c r="B11" s="144"/>
+      <c r="C11" s="144"/>
+      <c r="D11" s="144"/>
+      <c r="E11" s="144"/>
+      <c r="F11" s="144"/>
+      <c r="G11" s="144"/>
+      <c r="H11" s="144"/>
+      <c r="I11" s="144"/>
+      <c r="J11" s="144"/>
+      <c r="K11" s="144"/>
+      <c r="L11" s="145"/>
     </row>
     <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
@@ -16525,101 +16435,101 @@
       <c r="C12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="92" t="s">
+      <c r="D12" s="127" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="92"/>
-      <c r="F12" s="92"/>
-      <c r="G12" s="92"/>
-      <c r="H12" s="92"/>
-      <c r="I12" s="92"/>
-      <c r="J12" s="92"/>
-      <c r="K12" s="92"/>
-      <c r="L12" s="92"/>
+      <c r="E12" s="127"/>
+      <c r="F12" s="127"/>
+      <c r="G12" s="127"/>
+      <c r="H12" s="127"/>
+      <c r="I12" s="127"/>
+      <c r="J12" s="127"/>
+      <c r="K12" s="127"/>
+      <c r="L12" s="127"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="49"/>
       <c r="B13" s="50"/>
       <c r="C13" s="50"/>
-      <c r="D13" s="145"/>
-      <c r="E13" s="146"/>
-      <c r="F13" s="146"/>
-      <c r="G13" s="146"/>
-      <c r="H13" s="146"/>
-      <c r="I13" s="146"/>
-      <c r="J13" s="146"/>
-      <c r="K13" s="146"/>
-      <c r="L13" s="147"/>
+      <c r="D13" s="146"/>
+      <c r="E13" s="147"/>
+      <c r="F13" s="147"/>
+      <c r="G13" s="147"/>
+      <c r="H13" s="147"/>
+      <c r="I13" s="147"/>
+      <c r="J13" s="147"/>
+      <c r="K13" s="147"/>
+      <c r="L13" s="148"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="49"/>
       <c r="B14" s="50"/>
       <c r="C14" s="50"/>
-      <c r="D14" s="148"/>
-      <c r="E14" s="149"/>
-      <c r="F14" s="149"/>
-      <c r="G14" s="149"/>
-      <c r="H14" s="149"/>
-      <c r="I14" s="149"/>
-      <c r="J14" s="149"/>
-      <c r="K14" s="149"/>
-      <c r="L14" s="150"/>
+      <c r="D14" s="149"/>
+      <c r="E14" s="150"/>
+      <c r="F14" s="150"/>
+      <c r="G14" s="150"/>
+      <c r="H14" s="150"/>
+      <c r="I14" s="150"/>
+      <c r="J14" s="150"/>
+      <c r="K14" s="150"/>
+      <c r="L14" s="151"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="49"/>
       <c r="B15" s="50"/>
       <c r="C15" s="50"/>
-      <c r="D15" s="148"/>
-      <c r="E15" s="149"/>
-      <c r="F15" s="149"/>
-      <c r="G15" s="149"/>
-      <c r="H15" s="149"/>
-      <c r="I15" s="149"/>
-      <c r="J15" s="149"/>
-      <c r="K15" s="149"/>
-      <c r="L15" s="150"/>
+      <c r="D15" s="149"/>
+      <c r="E15" s="150"/>
+      <c r="F15" s="150"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="150"/>
+      <c r="I15" s="150"/>
+      <c r="J15" s="150"/>
+      <c r="K15" s="150"/>
+      <c r="L15" s="151"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="49"/>
       <c r="B16" s="50"/>
       <c r="C16" s="50"/>
-      <c r="D16" s="148"/>
-      <c r="E16" s="149"/>
-      <c r="F16" s="149"/>
-      <c r="G16" s="149"/>
-      <c r="H16" s="149"/>
-      <c r="I16" s="149"/>
-      <c r="J16" s="149"/>
-      <c r="K16" s="149"/>
-      <c r="L16" s="150"/>
+      <c r="D16" s="149"/>
+      <c r="E16" s="150"/>
+      <c r="F16" s="150"/>
+      <c r="G16" s="150"/>
+      <c r="H16" s="150"/>
+      <c r="I16" s="150"/>
+      <c r="J16" s="150"/>
+      <c r="K16" s="150"/>
+      <c r="L16" s="151"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="49"/>
       <c r="B17" s="50"/>
       <c r="C17" s="50"/>
-      <c r="D17" s="148"/>
-      <c r="E17" s="149"/>
-      <c r="F17" s="149"/>
-      <c r="G17" s="149"/>
-      <c r="H17" s="149"/>
-      <c r="I17" s="149"/>
-      <c r="J17" s="149"/>
-      <c r="K17" s="149"/>
-      <c r="L17" s="150"/>
+      <c r="D17" s="149"/>
+      <c r="E17" s="150"/>
+      <c r="F17" s="150"/>
+      <c r="G17" s="150"/>
+      <c r="H17" s="150"/>
+      <c r="I17" s="150"/>
+      <c r="J17" s="150"/>
+      <c r="K17" s="150"/>
+      <c r="L17" s="151"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="49"/>
       <c r="B18" s="50"/>
       <c r="C18" s="50"/>
-      <c r="D18" s="148"/>
-      <c r="E18" s="149"/>
-      <c r="F18" s="149"/>
-      <c r="G18" s="149"/>
-      <c r="H18" s="149"/>
-      <c r="I18" s="149"/>
-      <c r="J18" s="149"/>
-      <c r="K18" s="149"/>
-      <c r="L18" s="150"/>
+      <c r="D18" s="149"/>
+      <c r="E18" s="150"/>
+      <c r="F18" s="150"/>
+      <c r="G18" s="150"/>
+      <c r="H18" s="150"/>
+      <c r="I18" s="150"/>
+      <c r="J18" s="150"/>
+      <c r="K18" s="150"/>
+      <c r="L18" s="151"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -16708,10 +16618,10 @@
       <c r="B4" s="63"/>
     </row>
     <row r="6" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="A6" s="166" t="s">
+      <c r="A6" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="166"/>
+      <c r="B6" s="80"/>
     </row>
     <row r="8" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="66" t="s">
@@ -17692,6 +17602,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <SharedWithUsers xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50">
@@ -17744,15 +17663,6 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F7F06D0-41B3-4EAF-B418-88FC726117CC}">
   <ds:schemaRefs>
@@ -17773,6 +17683,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371D8832-41B3-447B-B13D-2663C267E34F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD069904-634F-48DA-AA92-BAE250498BEE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -17781,12 +17699,4 @@
     <ds:schemaRef ds:uri="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371D8832-41B3-447B-B13D-2663C267E34F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Guias Produccion/HU-57723.xlsx
+++ b/Guias Produccion/HU-57723.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Alliance\ScriptsEntidades\Guias Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F521BE-B7E9-480B-B66D-C49F84F783D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D490284C-DB3F-4D2A-960D-1157D267FCD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="158">
   <si>
     <t>Guia documentación</t>
   </si>
@@ -513,18 +513,6 @@
     <t>Es necesario que se ejecuten primero los scripts de la Hu 55188, ya que existe dependencia de algunos campos</t>
   </si>
   <si>
-    <t>06-AC_pro_General_GenerateBulkInt.sql</t>
-  </si>
-  <si>
-    <t>07-AC_pro_GetMachineShipments.sql</t>
-  </si>
-  <si>
-    <t>08-AC_pro_GetClientsPiecesDetails.sql</t>
-  </si>
-  <si>
-    <t>09-AC_pro_GetDispatchesByCarrier.sql</t>
-  </si>
-  <si>
     <t>01-f_SearchEntities.sql</t>
   </si>
   <si>
@@ -540,87 +528,6 @@
     <t>05-f_SearchGuiasHouseDetallesByType.sql</t>
   </si>
   <si>
-    <t>10-AC_pro_GetClientsPiecesBySubCarrier.sql</t>
-  </si>
-  <si>
-    <t>11-AC_pro_GetDispatchesByClient.sql</t>
-  </si>
-  <si>
-    <t>12-AC_pro_GetLocalOrdersByEmployee.sql</t>
-  </si>
-  <si>
-    <t>13-AC_pro_ManageGuiasHouseDetallesEditedOrder.sql</t>
-  </si>
-  <si>
-    <t>14-AC_pro_ListCarrierProgramming.sql</t>
-  </si>
-  <si>
-    <t>15-AC_pro_ConfirmLocalOrderCoordination.sql</t>
-  </si>
-  <si>
-    <t>16-AC_pro_ConfirmLocalOrder.sql</t>
-  </si>
-  <si>
-    <t>17-AC_pro_ShippingDocumentsPODClient360.sql</t>
-  </si>
-  <si>
-    <t>18-AC_pro_ModuleEdiDetail.sql</t>
-  </si>
-  <si>
-    <t>19-AC_pro_Module_Edi.sql</t>
-  </si>
-  <si>
-    <t>20-AC_pro_ListPiecesInventory.sql</t>
-  </si>
-  <si>
-    <t>21-AC_pro_GetBarCodeLinks.sql</t>
-  </si>
-  <si>
-    <t>22-AC_pro_LargeLabelTempDefault.sql</t>
-  </si>
-  <si>
-    <t>23-AC_pro_GetDispatchReports.sql</t>
-  </si>
-  <si>
-    <t>24-AC_pro_GetShipmentAnalyticsReports.sql</t>
-  </si>
-  <si>
-    <t>25-AC_pro_GetListOFCycleCounts.sql</t>
-  </si>
-  <si>
-    <t>26-AC_pro_GetCycleCountDiscrepancies.sql</t>
-  </si>
-  <si>
-    <t>27-AC_pro_CycleCountDiscrepanciesReport.sql</t>
-  </si>
-  <si>
-    <t>28-AC_pro_GetConsolidatedDispatchAnalytics.sql</t>
-  </si>
-  <si>
-    <t>29-AC_pro_GetAccountingAnalyticsReports.sql</t>
-  </si>
-  <si>
-    <t>30-AC_pro_GetSalesOrders.sql</t>
-  </si>
-  <si>
-    <t>31-AC_pro_GetDispatchReports.sql</t>
-  </si>
-  <si>
-    <t>32-AC_pro_GetCompletedScheduledPickupShipTo.sql</t>
-  </si>
-  <si>
-    <t>33-AC_pro_GetCompletedDeliveredPickupShipTo.sql</t>
-  </si>
-  <si>
-    <t>34-AC_pro_GetPendingPickup.sql</t>
-  </si>
-  <si>
-    <t>35-AC_pro_GetPendingPickupDetails.sql</t>
-  </si>
-  <si>
-    <t>36-AC_pro_GetCompletedScheduledPickupShipTo.sql</t>
-  </si>
-  <si>
     <t>37-AC_pro_GetCompletedDeliveredPickupDetail.sql</t>
   </si>
   <si>
@@ -628,6 +535,108 @@
   </si>
   <si>
     <t>39-AC_pro_InsertAccountingClient.sql</t>
+  </si>
+  <si>
+    <t>06-f_GetHawbEntities.sql</t>
+  </si>
+  <si>
+    <t>07-AC_pro_General_GenerateBulkInt.sql</t>
+  </si>
+  <si>
+    <t>08-AC_pro_GetMachineShipments.sql</t>
+  </si>
+  <si>
+    <t>09-AC_pro_GetClientsPiecesDetails.sql</t>
+  </si>
+  <si>
+    <t>10-AC_pro_GetDispatchesByCarrier.sql</t>
+  </si>
+  <si>
+    <t>11-AC_pro_GetClientsPiecesBySubCarrier.sql</t>
+  </si>
+  <si>
+    <t>12-AC_pro_GetDispatchesByClient.sql</t>
+  </si>
+  <si>
+    <t>13-AC_pro_GetLocalOrdersByEmployee.sql</t>
+  </si>
+  <si>
+    <t>14-AC_pro_ManageGuiasHouseDetallesEditedOrder.sql</t>
+  </si>
+  <si>
+    <t>15-AC_pro_ListCarrierProgramming.sql</t>
+  </si>
+  <si>
+    <t>16-AC_pro_ConfirmLocalOrderCoordination.sql</t>
+  </si>
+  <si>
+    <t>17-AC_pro_ConfirmLocalOrder.sql</t>
+  </si>
+  <si>
+    <t>18-AC_pro_ShippingDocumentsPODClient360.sql</t>
+  </si>
+  <si>
+    <t>19-AC_pro_ModuleEdiDetail.sql</t>
+  </si>
+  <si>
+    <t>20-AC_pro_Module_Edi.sql</t>
+  </si>
+  <si>
+    <t>21-AC_pro_ListPiecesInventory.sql</t>
+  </si>
+  <si>
+    <t>22-AC_pro_GetBarCodeLinks.sql</t>
+  </si>
+  <si>
+    <t>23-AC_pro_LargeLabelTempDefault.sql</t>
+  </si>
+  <si>
+    <t>24-AC_pro_GetDispatchReports.sql</t>
+  </si>
+  <si>
+    <t>25-AC_pro_GetShipmentAnalyticsReports.sql</t>
+  </si>
+  <si>
+    <t>26-AC_pro_GetListOFCycleCounts.sql</t>
+  </si>
+  <si>
+    <t>27-AC_pro_GetCycleCountDiscrepancies.sql</t>
+  </si>
+  <si>
+    <t>28-AC_pro_CycleCountDiscrepanciesReport.sql</t>
+  </si>
+  <si>
+    <t>29-AC_pro_GetConsolidatedDispatchAnalytics.sql</t>
+  </si>
+  <si>
+    <t>30-AC_pro_GetAccountingAnalyticsReports.sql</t>
+  </si>
+  <si>
+    <t>31-AC_pro_GetSalesOrders.sql</t>
+  </si>
+  <si>
+    <t>32-AC_pro_GetDispatchReports.sql</t>
+  </si>
+  <si>
+    <t>33-AC_pro_GetCompletedScheduledPickupShipTo.sql</t>
+  </si>
+  <si>
+    <t>34-AC_pro_GetCompletedDeliveredPickupShipTo.sql</t>
+  </si>
+  <si>
+    <t>35-AC_pro_GetPendingPickup.sql</t>
+  </si>
+  <si>
+    <t>36-AC_pro_GetPendingPickupDetails.sql</t>
+  </si>
+  <si>
+    <t>40-AC_pro_UpdateCustomersInTransmission.sql</t>
+  </si>
+  <si>
+    <t>41-AC_pro_UpdateCustomersHomologateProcess.sql</t>
+  </si>
+  <si>
+    <t>42-AC_pro_GetCustomersToHomologate.sql</t>
   </si>
 </sst>
 </file>
@@ -847,7 +856,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="78">
+  <borders count="79">
     <border>
       <left/>
       <right/>
@@ -1832,12 +1841,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="177">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1987,11 +2005,85 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="75" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="76" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="77" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2095,90 +2187,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="51" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="52" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="54" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="74" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2251,6 +2259,9 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2275,7 +2286,15 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="78" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -2339,7 +2358,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp109.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$25" noThreeD="1" sel="23" val="16"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$25" noThreeD="1" sel="17" val="9"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp11.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2351,7 +2370,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp111.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$25" noThreeD="1" sel="8" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$25" noThreeD="1" sel="17" val="9"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp112.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2499,10 +2518,22 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp145.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$18" noThreeD="1" sel="8" val="3"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp146.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$18" noThreeD="1" sel="8" val="3"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp147.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$18" noThreeD="1" sel="8" val="3"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp148.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$17" noThreeD="1" sel="17" val="9"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp146.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp149.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="26" fmlaRange="Hoja4!$A$1:$A$17" noThreeD="1" sel="17" val="9"/>
 </file>
 
@@ -11198,6 +11229,180 @@
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000E0040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>64</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>1409700</xdr:colOff>
+          <xdr:row>64</xdr:row>
+          <xdr:rowOff>220980</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1249" name="Drop Down 225" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1249"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41759AB5-AA69-B36A-357A-51BEADF993F6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>65</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>1409700</xdr:colOff>
+          <xdr:row>66</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1250" name="Drop Down 226" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1250"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{217ABE21-BF77-DCC5-F479-8233345FC7CE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>66</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>1409700</xdr:colOff>
+          <xdr:row>67</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1251" name="Drop Down 227" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1251"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{801FCA98-1F3E-7B35-614D-E86C829DD9EF}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -11823,7 +12028,7 @@
   <sheetPr codeName="Hoja1">
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A3:O66"/>
+  <dimension ref="A3:O67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.44140625" bestFit="1" customWidth="1"/>
@@ -11842,42 +12047,42 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:15" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="97" t="s">
+      <c r="A3" s="121" t="s">
         <v>103</v>
       </c>
-      <c r="B3" s="98"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="98"/>
-      <c r="K3" s="98"/>
-      <c r="L3" s="99"/>
-      <c r="N3" s="91" t="s">
+      <c r="B3" s="122"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="122"/>
+      <c r="I3" s="122"/>
+      <c r="J3" s="122"/>
+      <c r="K3" s="122"/>
+      <c r="L3" s="123"/>
+      <c r="N3" s="115" t="s">
         <v>0</v>
       </c>
-      <c r="O3" s="92"/>
+      <c r="O3" s="116"/>
     </row>
     <row r="4" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="104" t="s">
+      <c r="B4" s="128" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="105"/>
-      <c r="D4" s="105"/>
-      <c r="E4" s="105"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="105"/>
-      <c r="I4" s="105"/>
-      <c r="J4" s="106"/>
-      <c r="K4" s="106"/>
-      <c r="L4" s="107"/>
+      <c r="C4" s="129"/>
+      <c r="D4" s="129"/>
+      <c r="E4" s="129"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="129"/>
+      <c r="H4" s="129"/>
+      <c r="I4" s="129"/>
+      <c r="J4" s="130"/>
+      <c r="K4" s="130"/>
+      <c r="L4" s="131"/>
       <c r="N4" s="21" t="s">
         <v>2</v>
       </c>
@@ -11887,19 +12092,19 @@
       <c r="A5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="108" t="s">
+      <c r="B5" s="132" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="108"/>
-      <c r="D5" s="108"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="108"/>
-      <c r="G5" s="108"/>
-      <c r="H5" s="108"/>
-      <c r="I5" s="108"/>
-      <c r="J5" s="109"/>
-      <c r="K5" s="109"/>
-      <c r="L5" s="110"/>
+      <c r="C5" s="132"/>
+      <c r="D5" s="132"/>
+      <c r="E5" s="132"/>
+      <c r="F5" s="132"/>
+      <c r="G5" s="132"/>
+      <c r="H5" s="132"/>
+      <c r="I5" s="132"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="133"/>
+      <c r="L5" s="134"/>
       <c r="N5" s="15" t="s">
         <v>4</v>
       </c>
@@ -11909,19 +12114,19 @@
       <c r="A6" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="94">
+      <c r="B6" s="118">
         <v>46073</v>
       </c>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="95"/>
-      <c r="K6" s="95"/>
-      <c r="L6" s="96"/>
+      <c r="C6" s="119"/>
+      <c r="D6" s="119"/>
+      <c r="E6" s="119"/>
+      <c r="F6" s="119"/>
+      <c r="G6" s="119"/>
+      <c r="H6" s="119"/>
+      <c r="I6" s="119"/>
+      <c r="J6" s="119"/>
+      <c r="K6" s="119"/>
+      <c r="L6" s="120"/>
       <c r="N6" s="14"/>
       <c r="O6" s="14"/>
     </row>
@@ -11929,17 +12134,17 @@
       <c r="A7" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="111"/>
-      <c r="C7" s="112"/>
-      <c r="D7" s="112"/>
-      <c r="E7" s="112"/>
-      <c r="F7" s="112"/>
-      <c r="G7" s="112"/>
-      <c r="H7" s="112"/>
-      <c r="I7" s="112"/>
-      <c r="J7" s="113"/>
-      <c r="K7" s="113"/>
-      <c r="L7" s="114"/>
+      <c r="B7" s="135"/>
+      <c r="C7" s="136"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="136"/>
+      <c r="F7" s="136"/>
+      <c r="G7" s="136"/>
+      <c r="H7" s="136"/>
+      <c r="I7" s="136"/>
+      <c r="J7" s="137"/>
+      <c r="K7" s="137"/>
+      <c r="L7" s="138"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
@@ -11956,20 +12161,20 @@
       <c r="L8" s="13"/>
     </row>
     <row r="9" spans="1:15" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="100" t="s">
+      <c r="A9" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="101"/>
-      <c r="C9" s="101"/>
-      <c r="D9" s="101"/>
-      <c r="E9" s="101"/>
-      <c r="F9" s="101"/>
-      <c r="G9" s="101"/>
-      <c r="H9" s="101"/>
-      <c r="I9" s="101"/>
-      <c r="J9" s="102"/>
-      <c r="K9" s="102"/>
-      <c r="L9" s="103"/>
+      <c r="B9" s="125"/>
+      <c r="C9" s="125"/>
+      <c r="D9" s="125"/>
+      <c r="E9" s="125"/>
+      <c r="F9" s="125"/>
+      <c r="G9" s="125"/>
+      <c r="H9" s="125"/>
+      <c r="I9" s="125"/>
+      <c r="J9" s="126"/>
+      <c r="K9" s="126"/>
+      <c r="L9" s="127"/>
     </row>
     <row r="10" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -12069,63 +12274,63 @@
       <c r="A14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="93"/>
-      <c r="C14" s="89"/>
-      <c r="D14" s="89"/>
-      <c r="E14" s="89"/>
-      <c r="F14" s="89"/>
-      <c r="G14" s="89"/>
-      <c r="H14" s="89"/>
-      <c r="I14" s="89"/>
-      <c r="J14" s="89"/>
-      <c r="K14" s="89"/>
-      <c r="L14" s="90"/>
+      <c r="B14" s="117"/>
+      <c r="C14" s="113"/>
+      <c r="D14" s="113"/>
+      <c r="E14" s="113"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="113"/>
+      <c r="H14" s="113"/>
+      <c r="I14" s="113"/>
+      <c r="J14" s="113"/>
+      <c r="K14" s="113"/>
+      <c r="L14" s="114"/>
     </row>
     <row r="15" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="88"/>
-      <c r="C15" s="89"/>
-      <c r="D15" s="89"/>
-      <c r="E15" s="89"/>
-      <c r="F15" s="89"/>
-      <c r="G15" s="89"/>
-      <c r="H15" s="89"/>
-      <c r="I15" s="89"/>
-      <c r="J15" s="89"/>
-      <c r="K15" s="89"/>
-      <c r="L15" s="90"/>
+      <c r="B15" s="112"/>
+      <c r="C15" s="113"/>
+      <c r="D15" s="113"/>
+      <c r="E15" s="113"/>
+      <c r="F15" s="113"/>
+      <c r="G15" s="113"/>
+      <c r="H15" s="113"/>
+      <c r="I15" s="113"/>
+      <c r="J15" s="113"/>
+      <c r="K15" s="113"/>
+      <c r="L15" s="114"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="81"/>
-      <c r="B16" s="82"/>
-      <c r="C16" s="82"/>
-      <c r="D16" s="82"/>
-      <c r="E16" s="82"/>
-      <c r="F16" s="82"/>
-      <c r="G16" s="82"/>
-      <c r="H16" s="82"/>
-      <c r="I16" s="82"/>
-      <c r="J16" s="82"/>
-      <c r="K16" s="82"/>
-      <c r="L16" s="83"/>
+      <c r="A16" s="105"/>
+      <c r="B16" s="106"/>
+      <c r="C16" s="106"/>
+      <c r="D16" s="106"/>
+      <c r="E16" s="106"/>
+      <c r="F16" s="106"/>
+      <c r="G16" s="106"/>
+      <c r="H16" s="106"/>
+      <c r="I16" s="106"/>
+      <c r="J16" s="106"/>
+      <c r="K16" s="106"/>
+      <c r="L16" s="107"/>
     </row>
     <row r="17" spans="1:12" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="84" t="s">
+      <c r="A17" s="108" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="85"/>
-      <c r="C17" s="85"/>
-      <c r="D17" s="85"/>
-      <c r="E17" s="85"/>
-      <c r="F17" s="85"/>
-      <c r="G17" s="85"/>
-      <c r="H17" s="85"/>
-      <c r="I17" s="85"/>
-      <c r="J17" s="86"/>
-      <c r="K17" s="86"/>
-      <c r="L17" s="87"/>
+      <c r="B17" s="109"/>
+      <c r="C17" s="109"/>
+      <c r="D17" s="109"/>
+      <c r="E17" s="109"/>
+      <c r="F17" s="109"/>
+      <c r="G17" s="109"/>
+      <c r="H17" s="109"/>
+      <c r="I17" s="109"/>
+      <c r="J17" s="110"/>
+      <c r="K17" s="110"/>
+      <c r="L17" s="111"/>
     </row>
     <row r="18" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
@@ -12135,19 +12340,19 @@
       <c r="C18" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="119" t="s">
+      <c r="D18" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="121" t="s">
+      <c r="E18" s="83" t="s">
         <v>115</v>
       </c>
-      <c r="F18" s="121"/>
-      <c r="G18" s="121"/>
-      <c r="H18" s="121"/>
-      <c r="I18" s="121"/>
-      <c r="J18" s="122"/>
-      <c r="K18" s="122"/>
-      <c r="L18" s="123"/>
+      <c r="F18" s="83"/>
+      <c r="G18" s="83"/>
+      <c r="H18" s="83"/>
+      <c r="I18" s="83"/>
+      <c r="J18" s="84"/>
+      <c r="K18" s="84"/>
+      <c r="L18" s="85"/>
     </row>
     <row r="19" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
@@ -12157,15 +12362,15 @@
         <v>30</v>
       </c>
       <c r="C19" s="44"/>
-      <c r="D19" s="120"/>
-      <c r="E19" s="124"/>
-      <c r="F19" s="124"/>
-      <c r="G19" s="124"/>
-      <c r="H19" s="124"/>
-      <c r="I19" s="124"/>
-      <c r="J19" s="125"/>
-      <c r="K19" s="125"/>
-      <c r="L19" s="126"/>
+      <c r="D19" s="82"/>
+      <c r="E19" s="86"/>
+      <c r="F19" s="86"/>
+      <c r="G19" s="86"/>
+      <c r="H19" s="86"/>
+      <c r="I19" s="86"/>
+      <c r="J19" s="87"/>
+      <c r="K19" s="87"/>
+      <c r="L19" s="88"/>
     </row>
     <row r="20" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
@@ -12175,15 +12380,15 @@
       <c r="C20" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="120"/>
-      <c r="E20" s="124"/>
-      <c r="F20" s="124"/>
-      <c r="G20" s="124"/>
-      <c r="H20" s="124"/>
-      <c r="I20" s="124"/>
-      <c r="J20" s="125"/>
-      <c r="K20" s="125"/>
-      <c r="L20" s="126"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="86"/>
+      <c r="F20" s="86"/>
+      <c r="G20" s="86"/>
+      <c r="H20" s="86"/>
+      <c r="I20" s="86"/>
+      <c r="J20" s="87"/>
+      <c r="K20" s="87"/>
+      <c r="L20" s="88"/>
     </row>
     <row r="21" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
@@ -12193,19 +12398,19 @@
       <c r="C21" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="135" t="s">
+      <c r="D21" s="97" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="137" t="s">
+      <c r="E21" s="99" t="s">
         <v>107</v>
       </c>
-      <c r="F21" s="138"/>
-      <c r="G21" s="138"/>
-      <c r="H21" s="138"/>
-      <c r="I21" s="138"/>
-      <c r="J21" s="138"/>
-      <c r="K21" s="138"/>
-      <c r="L21" s="139"/>
+      <c r="F21" s="100"/>
+      <c r="G21" s="100"/>
+      <c r="H21" s="100"/>
+      <c r="I21" s="100"/>
+      <c r="J21" s="100"/>
+      <c r="K21" s="100"/>
+      <c r="L21" s="101"/>
     </row>
     <row r="22" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
@@ -12215,45 +12420,45 @@
       <c r="C22" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="136"/>
-      <c r="E22" s="140"/>
-      <c r="F22" s="141"/>
-      <c r="G22" s="141"/>
-      <c r="H22" s="141"/>
-      <c r="I22" s="141"/>
-      <c r="J22" s="141"/>
-      <c r="K22" s="141"/>
-      <c r="L22" s="142"/>
+      <c r="D22" s="98"/>
+      <c r="E22" s="102"/>
+      <c r="F22" s="103"/>
+      <c r="G22" s="103"/>
+      <c r="H22" s="103"/>
+      <c r="I22" s="103"/>
+      <c r="J22" s="103"/>
+      <c r="K22" s="103"/>
+      <c r="L22" s="104"/>
     </row>
     <row r="23" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="128"/>
-      <c r="B23" s="129"/>
-      <c r="C23" s="129"/>
-      <c r="D23" s="130"/>
-      <c r="E23" s="130"/>
-      <c r="F23" s="130"/>
-      <c r="G23" s="130"/>
-      <c r="H23" s="130"/>
-      <c r="I23" s="130"/>
-      <c r="J23" s="130"/>
-      <c r="K23" s="130"/>
-      <c r="L23" s="131"/>
+      <c r="A23" s="90"/>
+      <c r="B23" s="91"/>
+      <c r="C23" s="91"/>
+      <c r="D23" s="92"/>
+      <c r="E23" s="92"/>
+      <c r="F23" s="92"/>
+      <c r="G23" s="92"/>
+      <c r="H23" s="92"/>
+      <c r="I23" s="92"/>
+      <c r="J23" s="92"/>
+      <c r="K23" s="92"/>
+      <c r="L23" s="93"/>
     </row>
     <row r="24" spans="1:12" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="132" t="s">
+      <c r="A24" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="133"/>
-      <c r="C24" s="133"/>
-      <c r="D24" s="133"/>
-      <c r="E24" s="133"/>
-      <c r="F24" s="133"/>
-      <c r="G24" s="133"/>
-      <c r="H24" s="133"/>
-      <c r="I24" s="133"/>
-      <c r="J24" s="133"/>
-      <c r="K24" s="133"/>
-      <c r="L24" s="134"/>
+      <c r="B24" s="95"/>
+      <c r="C24" s="95"/>
+      <c r="D24" s="95"/>
+      <c r="E24" s="95"/>
+      <c r="F24" s="95"/>
+      <c r="G24" s="95"/>
+      <c r="H24" s="95"/>
+      <c r="I24" s="95"/>
+      <c r="J24" s="95"/>
+      <c r="K24" s="95"/>
+      <c r="L24" s="96"/>
     </row>
     <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
@@ -12265,760 +12470,778 @@
       <c r="C25" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="127" t="s">
+      <c r="D25" s="89" t="s">
         <v>38</v>
       </c>
-      <c r="E25" s="127"/>
-      <c r="F25" s="127"/>
-      <c r="G25" s="127"/>
-      <c r="H25" s="127"/>
-      <c r="I25" s="127"/>
-      <c r="J25" s="127"/>
-      <c r="K25" s="127"/>
-      <c r="L25" s="127"/>
+      <c r="E25" s="89"/>
+      <c r="F25" s="89"/>
+      <c r="G25" s="89"/>
+      <c r="H25" s="89"/>
+      <c r="I25" s="89"/>
+      <c r="J25" s="89"/>
+      <c r="K25" s="89"/>
+      <c r="L25" s="89"/>
     </row>
     <row r="26" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="33">
         <v>1</v>
       </c>
-      <c r="B26" s="34" t="s">
-        <v>120</v>
+      <c r="B26" s="172" t="s">
+        <v>116</v>
       </c>
       <c r="C26" s="34"/>
-      <c r="D26" s="115" t="s">
+      <c r="D26" s="79" t="s">
         <v>108</v>
       </c>
-      <c r="E26" s="116"/>
-      <c r="F26" s="116"/>
-      <c r="G26" s="116"/>
-      <c r="H26" s="116"/>
-      <c r="I26" s="116"/>
-      <c r="J26" s="116"/>
-      <c r="K26" s="116"/>
-      <c r="L26" s="116"/>
+      <c r="E26" s="79"/>
+      <c r="F26" s="79"/>
+      <c r="G26" s="79"/>
+      <c r="H26" s="79"/>
+      <c r="I26" s="79"/>
+      <c r="J26" s="79"/>
+      <c r="K26" s="79"/>
+      <c r="L26" s="79"/>
     </row>
     <row r="27" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
         <v>2</v>
       </c>
-      <c r="B27" s="34" t="s">
-        <v>121</v>
+      <c r="B27" s="172" t="s">
+        <v>117</v>
       </c>
       <c r="C27" s="34"/>
-      <c r="D27" s="117"/>
-      <c r="E27" s="118"/>
-      <c r="F27" s="118"/>
-      <c r="G27" s="118"/>
-      <c r="H27" s="118"/>
-      <c r="I27" s="118"/>
-      <c r="J27" s="118"/>
-      <c r="K27" s="118"/>
-      <c r="L27" s="118"/>
+      <c r="D27" s="80"/>
+      <c r="E27" s="80"/>
+      <c r="F27" s="80"/>
+      <c r="G27" s="80"/>
+      <c r="H27" s="80"/>
+      <c r="I27" s="80"/>
+      <c r="J27" s="80"/>
+      <c r="K27" s="80"/>
+      <c r="L27" s="80"/>
     </row>
     <row r="28" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="33">
         <v>3</v>
       </c>
-      <c r="B28" s="34" t="s">
-        <v>122</v>
+      <c r="B28" s="172" t="s">
+        <v>118</v>
       </c>
       <c r="C28" s="34"/>
-      <c r="D28" s="117"/>
-      <c r="E28" s="118"/>
-      <c r="F28" s="118"/>
-      <c r="G28" s="118"/>
-      <c r="H28" s="118"/>
-      <c r="I28" s="118"/>
-      <c r="J28" s="118"/>
-      <c r="K28" s="118"/>
-      <c r="L28" s="118"/>
+      <c r="D28" s="80"/>
+      <c r="E28" s="80"/>
+      <c r="F28" s="80"/>
+      <c r="G28" s="80"/>
+      <c r="H28" s="80"/>
+      <c r="I28" s="80"/>
+      <c r="J28" s="80"/>
+      <c r="K28" s="80"/>
+      <c r="L28" s="80"/>
     </row>
     <row r="29" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
         <v>4</v>
       </c>
-      <c r="B29" s="34" t="s">
-        <v>123</v>
+      <c r="B29" s="172" t="s">
+        <v>119</v>
       </c>
       <c r="C29" s="34"/>
-      <c r="D29" s="117"/>
-      <c r="E29" s="118"/>
-      <c r="F29" s="118"/>
-      <c r="G29" s="118"/>
-      <c r="H29" s="118"/>
-      <c r="I29" s="118"/>
-      <c r="J29" s="118"/>
-      <c r="K29" s="118"/>
-      <c r="L29" s="118"/>
+      <c r="D29" s="80"/>
+      <c r="E29" s="80"/>
+      <c r="F29" s="80"/>
+      <c r="G29" s="80"/>
+      <c r="H29" s="80"/>
+      <c r="I29" s="80"/>
+      <c r="J29" s="80"/>
+      <c r="K29" s="80"/>
+      <c r="L29" s="80"/>
     </row>
     <row r="30" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="33">
         <v>5</v>
       </c>
-      <c r="B30" s="34" t="s">
-        <v>124</v>
+      <c r="B30" s="172" t="s">
+        <v>120</v>
       </c>
       <c r="C30" s="34"/>
-      <c r="D30" s="117"/>
-      <c r="E30" s="118"/>
-      <c r="F30" s="118"/>
-      <c r="G30" s="118"/>
-      <c r="H30" s="118"/>
-      <c r="I30" s="118"/>
-      <c r="J30" s="118"/>
-      <c r="K30" s="118"/>
-      <c r="L30" s="118"/>
+      <c r="D30" s="80"/>
+      <c r="E30" s="80"/>
+      <c r="F30" s="80"/>
+      <c r="G30" s="80"/>
+      <c r="H30" s="80"/>
+      <c r="I30" s="80"/>
+      <c r="J30" s="80"/>
+      <c r="K30" s="80"/>
+      <c r="L30" s="80"/>
     </row>
     <row r="31" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="33">
         <v>6</v>
       </c>
-      <c r="B31" s="34" t="s">
-        <v>116</v>
+      <c r="B31" s="172" t="s">
+        <v>124</v>
       </c>
       <c r="C31" s="34"/>
-      <c r="D31" s="117"/>
-      <c r="E31" s="118"/>
-      <c r="F31" s="118"/>
-      <c r="G31" s="118"/>
-      <c r="H31" s="118"/>
-      <c r="I31" s="118"/>
-      <c r="J31" s="118"/>
-      <c r="K31" s="118"/>
-      <c r="L31" s="118"/>
+      <c r="D31" s="80"/>
+      <c r="E31" s="80"/>
+      <c r="F31" s="80"/>
+      <c r="G31" s="80"/>
+      <c r="H31" s="80"/>
+      <c r="I31" s="80"/>
+      <c r="J31" s="80"/>
+      <c r="K31" s="80"/>
+      <c r="L31" s="80"/>
     </row>
     <row r="32" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="33">
         <v>7</v>
       </c>
-      <c r="B32" s="34" t="s">
-        <v>117</v>
+      <c r="B32" s="172" t="s">
+        <v>125</v>
       </c>
       <c r="C32" s="34"/>
-      <c r="D32" s="117"/>
-      <c r="E32" s="118"/>
-      <c r="F32" s="118"/>
-      <c r="G32" s="118"/>
-      <c r="H32" s="118"/>
-      <c r="I32" s="118"/>
-      <c r="J32" s="118"/>
-      <c r="K32" s="118"/>
-      <c r="L32" s="118"/>
+      <c r="D32" s="80"/>
+      <c r="E32" s="80"/>
+      <c r="F32" s="80"/>
+      <c r="G32" s="80"/>
+      <c r="H32" s="80"/>
+      <c r="I32" s="80"/>
+      <c r="J32" s="80"/>
+      <c r="K32" s="80"/>
+      <c r="L32" s="80"/>
     </row>
     <row r="33" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="33">
         <v>8</v>
       </c>
-      <c r="B33" s="34" t="s">
-        <v>118</v>
+      <c r="B33" s="172" t="s">
+        <v>126</v>
       </c>
       <c r="C33" s="34"/>
-      <c r="D33" s="117"/>
-      <c r="E33" s="118"/>
-      <c r="F33" s="118"/>
-      <c r="G33" s="118"/>
-      <c r="H33" s="118"/>
-      <c r="I33" s="118"/>
-      <c r="J33" s="118"/>
-      <c r="K33" s="118"/>
-      <c r="L33" s="118"/>
+      <c r="D33" s="80"/>
+      <c r="E33" s="80"/>
+      <c r="F33" s="80"/>
+      <c r="G33" s="80"/>
+      <c r="H33" s="80"/>
+      <c r="I33" s="80"/>
+      <c r="J33" s="80"/>
+      <c r="K33" s="80"/>
+      <c r="L33" s="80"/>
     </row>
     <row r="34" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="33">
         <v>9</v>
       </c>
-      <c r="B34" s="34" t="s">
-        <v>119</v>
+      <c r="B34" s="172" t="s">
+        <v>127</v>
       </c>
       <c r="C34" s="34"/>
-      <c r="D34" s="117"/>
-      <c r="E34" s="118"/>
-      <c r="F34" s="118"/>
-      <c r="G34" s="118"/>
-      <c r="H34" s="118"/>
-      <c r="I34" s="118"/>
-      <c r="J34" s="118"/>
-      <c r="K34" s="118"/>
-      <c r="L34" s="118"/>
+      <c r="D34" s="80"/>
+      <c r="E34" s="80"/>
+      <c r="F34" s="80"/>
+      <c r="G34" s="80"/>
+      <c r="H34" s="80"/>
+      <c r="I34" s="80"/>
+      <c r="J34" s="80"/>
+      <c r="K34" s="80"/>
+      <c r="L34" s="80"/>
     </row>
     <row r="35" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="33">
         <v>10</v>
       </c>
-      <c r="B35" s="34" t="s">
-        <v>125</v>
+      <c r="B35" s="172" t="s">
+        <v>128</v>
       </c>
       <c r="C35" s="34"/>
-      <c r="D35" s="117"/>
-      <c r="E35" s="118"/>
-      <c r="F35" s="118"/>
-      <c r="G35" s="118"/>
-      <c r="H35" s="118"/>
-      <c r="I35" s="118"/>
-      <c r="J35" s="118"/>
-      <c r="K35" s="118"/>
-      <c r="L35" s="118"/>
+      <c r="D35" s="80"/>
+      <c r="E35" s="80"/>
+      <c r="F35" s="80"/>
+      <c r="G35" s="80"/>
+      <c r="H35" s="80"/>
+      <c r="I35" s="80"/>
+      <c r="J35" s="80"/>
+      <c r="K35" s="80"/>
+      <c r="L35" s="80"/>
     </row>
     <row r="36" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="33">
         <v>11</v>
       </c>
-      <c r="B36" s="34" t="s">
-        <v>126</v>
+      <c r="B36" s="172" t="s">
+        <v>129</v>
       </c>
       <c r="C36" s="34"/>
-      <c r="D36" s="117"/>
-      <c r="E36" s="118"/>
-      <c r="F36" s="118"/>
-      <c r="G36" s="118"/>
-      <c r="H36" s="118"/>
-      <c r="I36" s="118"/>
-      <c r="J36" s="118"/>
-      <c r="K36" s="118"/>
-      <c r="L36" s="118"/>
+      <c r="D36" s="80"/>
+      <c r="E36" s="80"/>
+      <c r="F36" s="80"/>
+      <c r="G36" s="80"/>
+      <c r="H36" s="80"/>
+      <c r="I36" s="80"/>
+      <c r="J36" s="80"/>
+      <c r="K36" s="80"/>
+      <c r="L36" s="80"/>
     </row>
     <row r="37" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="33">
         <v>12</v>
       </c>
-      <c r="B37" s="34" t="s">
-        <v>127</v>
+      <c r="B37" s="172" t="s">
+        <v>130</v>
       </c>
       <c r="C37" s="34"/>
-      <c r="D37" s="117"/>
-      <c r="E37" s="118"/>
-      <c r="F37" s="118"/>
-      <c r="G37" s="118"/>
-      <c r="H37" s="118"/>
-      <c r="I37" s="118"/>
-      <c r="J37" s="118"/>
-      <c r="K37" s="118"/>
-      <c r="L37" s="118"/>
+      <c r="D37" s="80"/>
+      <c r="E37" s="80"/>
+      <c r="F37" s="80"/>
+      <c r="G37" s="80"/>
+      <c r="H37" s="80"/>
+      <c r="I37" s="80"/>
+      <c r="J37" s="80"/>
+      <c r="K37" s="80"/>
+      <c r="L37" s="80"/>
     </row>
     <row r="38" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="33">
         <v>13</v>
       </c>
-      <c r="B38" s="34" t="s">
-        <v>128</v>
+      <c r="B38" s="172" t="s">
+        <v>131</v>
       </c>
       <c r="C38" s="34"/>
-      <c r="D38" s="117"/>
-      <c r="E38" s="118"/>
-      <c r="F38" s="118"/>
-      <c r="G38" s="118"/>
-      <c r="H38" s="118"/>
-      <c r="I38" s="118"/>
-      <c r="J38" s="118"/>
-      <c r="K38" s="118"/>
-      <c r="L38" s="118"/>
+      <c r="D38" s="80"/>
+      <c r="E38" s="80"/>
+      <c r="F38" s="80"/>
+      <c r="G38" s="80"/>
+      <c r="H38" s="80"/>
+      <c r="I38" s="80"/>
+      <c r="J38" s="80"/>
+      <c r="K38" s="80"/>
+      <c r="L38" s="80"/>
     </row>
     <row r="39" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="33">
         <v>14</v>
       </c>
-      <c r="B39" s="34" t="s">
-        <v>129</v>
+      <c r="B39" s="172" t="s">
+        <v>132</v>
       </c>
       <c r="C39" s="34"/>
-      <c r="D39" s="117"/>
-      <c r="E39" s="118"/>
-      <c r="F39" s="118"/>
-      <c r="G39" s="118"/>
-      <c r="H39" s="118"/>
-      <c r="I39" s="118"/>
-      <c r="J39" s="118"/>
-      <c r="K39" s="118"/>
-      <c r="L39" s="118"/>
+      <c r="D39" s="80"/>
+      <c r="E39" s="80"/>
+      <c r="F39" s="80"/>
+      <c r="G39" s="80"/>
+      <c r="H39" s="80"/>
+      <c r="I39" s="80"/>
+      <c r="J39" s="80"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="80"/>
     </row>
     <row r="40" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="33">
         <v>15</v>
       </c>
-      <c r="B40" s="34" t="s">
-        <v>130</v>
+      <c r="B40" s="172" t="s">
+        <v>133</v>
       </c>
       <c r="C40" s="34"/>
-      <c r="D40" s="117"/>
-      <c r="E40" s="118"/>
-      <c r="F40" s="118"/>
-      <c r="G40" s="118"/>
-      <c r="H40" s="118"/>
-      <c r="I40" s="118"/>
-      <c r="J40" s="118"/>
-      <c r="K40" s="118"/>
-      <c r="L40" s="118"/>
+      <c r="D40" s="80"/>
+      <c r="E40" s="80"/>
+      <c r="F40" s="80"/>
+      <c r="G40" s="80"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="80"/>
+      <c r="J40" s="80"/>
+      <c r="K40" s="80"/>
+      <c r="L40" s="80"/>
     </row>
     <row r="41" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="33">
         <v>16</v>
       </c>
-      <c r="B41" s="34" t="s">
-        <v>131</v>
+      <c r="B41" s="172" t="s">
+        <v>134</v>
       </c>
       <c r="C41" s="34"/>
-      <c r="D41" s="117"/>
-      <c r="E41" s="118"/>
-      <c r="F41" s="118"/>
-      <c r="G41" s="118"/>
-      <c r="H41" s="118"/>
-      <c r="I41" s="118"/>
-      <c r="J41" s="118"/>
-      <c r="K41" s="118"/>
-      <c r="L41" s="118"/>
+      <c r="D41" s="80"/>
+      <c r="E41" s="80"/>
+      <c r="F41" s="80"/>
+      <c r="G41" s="80"/>
+      <c r="H41" s="80"/>
+      <c r="I41" s="80"/>
+      <c r="J41" s="80"/>
+      <c r="K41" s="80"/>
+      <c r="L41" s="80"/>
     </row>
     <row r="42" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="33">
         <v>17</v>
       </c>
-      <c r="B42" s="34" t="s">
-        <v>132</v>
+      <c r="B42" s="172" t="s">
+        <v>135</v>
       </c>
       <c r="C42" s="34"/>
-      <c r="D42" s="117"/>
-      <c r="E42" s="118"/>
-      <c r="F42" s="118"/>
-      <c r="G42" s="118"/>
-      <c r="H42" s="118"/>
-      <c r="I42" s="118"/>
-      <c r="J42" s="118"/>
-      <c r="K42" s="118"/>
-      <c r="L42" s="118"/>
+      <c r="D42" s="80"/>
+      <c r="E42" s="80"/>
+      <c r="F42" s="80"/>
+      <c r="G42" s="80"/>
+      <c r="H42" s="80"/>
+      <c r="I42" s="80"/>
+      <c r="J42" s="80"/>
+      <c r="K42" s="80"/>
+      <c r="L42" s="80"/>
     </row>
     <row r="43" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="33">
         <v>18</v>
       </c>
-      <c r="B43" s="34" t="s">
-        <v>133</v>
+      <c r="B43" s="172" t="s">
+        <v>136</v>
       </c>
       <c r="C43" s="34"/>
-      <c r="D43" s="117"/>
-      <c r="E43" s="118"/>
-      <c r="F43" s="118"/>
-      <c r="G43" s="118"/>
-      <c r="H43" s="118"/>
-      <c r="I43" s="118"/>
-      <c r="J43" s="118"/>
-      <c r="K43" s="118"/>
-      <c r="L43" s="118"/>
+      <c r="D43" s="80"/>
+      <c r="E43" s="80"/>
+      <c r="F43" s="80"/>
+      <c r="G43" s="80"/>
+      <c r="H43" s="80"/>
+      <c r="I43" s="80"/>
+      <c r="J43" s="80"/>
+      <c r="K43" s="80"/>
+      <c r="L43" s="80"/>
     </row>
     <row r="44" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="33">
         <v>19</v>
       </c>
-      <c r="B44" s="34" t="s">
-        <v>134</v>
+      <c r="B44" s="172" t="s">
+        <v>137</v>
       </c>
       <c r="C44" s="34"/>
-      <c r="D44" s="117"/>
-      <c r="E44" s="118"/>
-      <c r="F44" s="118"/>
-      <c r="G44" s="118"/>
-      <c r="H44" s="118"/>
-      <c r="I44" s="118"/>
-      <c r="J44" s="118"/>
-      <c r="K44" s="118"/>
-      <c r="L44" s="118"/>
+      <c r="D44" s="80"/>
+      <c r="E44" s="80"/>
+      <c r="F44" s="80"/>
+      <c r="G44" s="80"/>
+      <c r="H44" s="80"/>
+      <c r="I44" s="80"/>
+      <c r="J44" s="80"/>
+      <c r="K44" s="80"/>
+      <c r="L44" s="80"/>
     </row>
     <row r="45" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="33">
         <v>20</v>
       </c>
-      <c r="B45" s="34" t="s">
-        <v>135</v>
+      <c r="B45" s="172" t="s">
+        <v>138</v>
       </c>
       <c r="C45" s="34"/>
-      <c r="D45" s="117"/>
-      <c r="E45" s="118"/>
-      <c r="F45" s="118"/>
-      <c r="G45" s="118"/>
-      <c r="H45" s="118"/>
-      <c r="I45" s="118"/>
-      <c r="J45" s="118"/>
-      <c r="K45" s="118"/>
-      <c r="L45" s="118"/>
+      <c r="D45" s="80"/>
+      <c r="E45" s="80"/>
+      <c r="F45" s="80"/>
+      <c r="G45" s="80"/>
+      <c r="H45" s="80"/>
+      <c r="I45" s="80"/>
+      <c r="J45" s="80"/>
+      <c r="K45" s="80"/>
+      <c r="L45" s="80"/>
     </row>
     <row r="46" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="33">
         <v>21</v>
       </c>
-      <c r="B46" s="34" t="s">
-        <v>136</v>
+      <c r="B46" s="172" t="s">
+        <v>139</v>
       </c>
       <c r="C46" s="34"/>
-      <c r="D46" s="117"/>
-      <c r="E46" s="118"/>
-      <c r="F46" s="118"/>
-      <c r="G46" s="118"/>
-      <c r="H46" s="118"/>
-      <c r="I46" s="118"/>
-      <c r="J46" s="118"/>
-      <c r="K46" s="118"/>
-      <c r="L46" s="118"/>
+      <c r="D46" s="80"/>
+      <c r="E46" s="80"/>
+      <c r="F46" s="80"/>
+      <c r="G46" s="80"/>
+      <c r="H46" s="80"/>
+      <c r="I46" s="80"/>
+      <c r="J46" s="80"/>
+      <c r="K46" s="80"/>
+      <c r="L46" s="80"/>
     </row>
     <row r="47" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="33">
         <v>22</v>
       </c>
-      <c r="B47" s="34" t="s">
-        <v>137</v>
+      <c r="B47" s="172" t="s">
+        <v>140</v>
       </c>
       <c r="C47" s="34"/>
-      <c r="D47" s="117"/>
-      <c r="E47" s="118"/>
-      <c r="F47" s="118"/>
-      <c r="G47" s="118"/>
-      <c r="H47" s="118"/>
-      <c r="I47" s="118"/>
-      <c r="J47" s="118"/>
-      <c r="K47" s="118"/>
-      <c r="L47" s="118"/>
+      <c r="D47" s="80"/>
+      <c r="E47" s="80"/>
+      <c r="F47" s="80"/>
+      <c r="G47" s="80"/>
+      <c r="H47" s="80"/>
+      <c r="I47" s="80"/>
+      <c r="J47" s="80"/>
+      <c r="K47" s="80"/>
+      <c r="L47" s="80"/>
     </row>
     <row r="48" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="33">
         <v>23</v>
       </c>
-      <c r="B48" s="34" t="s">
-        <v>138</v>
+      <c r="B48" s="172" t="s">
+        <v>141</v>
       </c>
       <c r="C48" s="34"/>
-      <c r="D48" s="117"/>
-      <c r="E48" s="118"/>
-      <c r="F48" s="118"/>
-      <c r="G48" s="118"/>
-      <c r="H48" s="118"/>
-      <c r="I48" s="118"/>
-      <c r="J48" s="118"/>
-      <c r="K48" s="118"/>
-      <c r="L48" s="118"/>
+      <c r="D48" s="80"/>
+      <c r="E48" s="80"/>
+      <c r="F48" s="80"/>
+      <c r="G48" s="80"/>
+      <c r="H48" s="80"/>
+      <c r="I48" s="80"/>
+      <c r="J48" s="80"/>
+      <c r="K48" s="80"/>
+      <c r="L48" s="80"/>
     </row>
     <row r="49" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="33">
         <v>24</v>
       </c>
-      <c r="B49" s="34" t="s">
-        <v>139</v>
+      <c r="B49" s="172" t="s">
+        <v>142</v>
       </c>
       <c r="C49" s="34"/>
-      <c r="D49" s="117"/>
-      <c r="E49" s="118"/>
-      <c r="F49" s="118"/>
-      <c r="G49" s="118"/>
-      <c r="H49" s="118"/>
-      <c r="I49" s="118"/>
-      <c r="J49" s="118"/>
-      <c r="K49" s="118"/>
-      <c r="L49" s="118"/>
+      <c r="D49" s="80"/>
+      <c r="E49" s="80"/>
+      <c r="F49" s="80"/>
+      <c r="G49" s="80"/>
+      <c r="H49" s="80"/>
+      <c r="I49" s="80"/>
+      <c r="J49" s="80"/>
+      <c r="K49" s="80"/>
+      <c r="L49" s="80"/>
     </row>
     <row r="50" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="33">
         <v>25</v>
       </c>
-      <c r="B50" s="34" t="s">
-        <v>140</v>
+      <c r="B50" s="172" t="s">
+        <v>143</v>
       </c>
       <c r="C50" s="34"/>
-      <c r="D50" s="117"/>
-      <c r="E50" s="118"/>
-      <c r="F50" s="118"/>
-      <c r="G50" s="118"/>
-      <c r="H50" s="118"/>
-      <c r="I50" s="118"/>
-      <c r="J50" s="118"/>
-      <c r="K50" s="118"/>
-      <c r="L50" s="118"/>
+      <c r="D50" s="80"/>
+      <c r="E50" s="80"/>
+      <c r="F50" s="80"/>
+      <c r="G50" s="80"/>
+      <c r="H50" s="80"/>
+      <c r="I50" s="80"/>
+      <c r="J50" s="80"/>
+      <c r="K50" s="80"/>
+      <c r="L50" s="80"/>
     </row>
     <row r="51" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="33">
         <v>26</v>
       </c>
-      <c r="B51" s="77" t="s">
-        <v>141</v>
+      <c r="B51" s="173" t="s">
+        <v>144</v>
       </c>
       <c r="C51" s="34"/>
-      <c r="D51" s="117"/>
-      <c r="E51" s="118"/>
-      <c r="F51" s="118"/>
-      <c r="G51" s="118"/>
-      <c r="H51" s="118"/>
-      <c r="I51" s="118"/>
-      <c r="J51" s="118"/>
-      <c r="K51" s="118"/>
-      <c r="L51" s="118"/>
+      <c r="D51" s="80"/>
+      <c r="E51" s="80"/>
+      <c r="F51" s="80"/>
+      <c r="G51" s="80"/>
+      <c r="H51" s="80"/>
+      <c r="I51" s="80"/>
+      <c r="J51" s="80"/>
+      <c r="K51" s="80"/>
+      <c r="L51" s="80"/>
     </row>
     <row r="52" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="33">
         <v>27</v>
       </c>
-      <c r="B52" s="77" t="s">
-        <v>142</v>
+      <c r="B52" s="173" t="s">
+        <v>145</v>
       </c>
       <c r="C52" s="34"/>
-      <c r="D52" s="117"/>
-      <c r="E52" s="118"/>
-      <c r="F52" s="118"/>
-      <c r="G52" s="118"/>
-      <c r="H52" s="118"/>
-      <c r="I52" s="118"/>
-      <c r="J52" s="118"/>
-      <c r="K52" s="118"/>
-      <c r="L52" s="118"/>
+      <c r="D52" s="80"/>
+      <c r="E52" s="80"/>
+      <c r="F52" s="80"/>
+      <c r="G52" s="80"/>
+      <c r="H52" s="80"/>
+      <c r="I52" s="80"/>
+      <c r="J52" s="80"/>
+      <c r="K52" s="80"/>
+      <c r="L52" s="80"/>
     </row>
     <row r="53" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="33">
         <v>28</v>
       </c>
-      <c r="B53" s="77" t="s">
-        <v>143</v>
+      <c r="B53" s="173" t="s">
+        <v>146</v>
       </c>
       <c r="C53" s="34"/>
-      <c r="D53" s="117"/>
-      <c r="E53" s="118"/>
-      <c r="F53" s="118"/>
-      <c r="G53" s="118"/>
-      <c r="H53" s="118"/>
-      <c r="I53" s="118"/>
-      <c r="J53" s="118"/>
-      <c r="K53" s="118"/>
-      <c r="L53" s="118"/>
+      <c r="D53" s="80"/>
+      <c r="E53" s="80"/>
+      <c r="F53" s="80"/>
+      <c r="G53" s="80"/>
+      <c r="H53" s="80"/>
+      <c r="I53" s="80"/>
+      <c r="J53" s="80"/>
+      <c r="K53" s="80"/>
+      <c r="L53" s="80"/>
     </row>
     <row r="54" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="33">
         <v>29</v>
       </c>
-      <c r="B54" s="175" t="s">
-        <v>144</v>
-      </c>
-      <c r="C54" s="79"/>
-      <c r="D54" s="117"/>
-      <c r="E54" s="118"/>
-      <c r="F54" s="118"/>
-      <c r="G54" s="118"/>
-      <c r="H54" s="118"/>
-      <c r="I54" s="118"/>
-      <c r="J54" s="118"/>
-      <c r="K54" s="118"/>
-      <c r="L54" s="118"/>
+      <c r="B54" s="174" t="s">
+        <v>147</v>
+      </c>
+      <c r="C54" s="78"/>
+      <c r="D54" s="80"/>
+      <c r="E54" s="80"/>
+      <c r="F54" s="80"/>
+      <c r="G54" s="80"/>
+      <c r="H54" s="80"/>
+      <c r="I54" s="80"/>
+      <c r="J54" s="80"/>
+      <c r="K54" s="80"/>
+      <c r="L54" s="80"/>
     </row>
     <row r="55" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="33">
         <v>30</v>
       </c>
-      <c r="B55" s="78" t="s">
-        <v>145</v>
+      <c r="B55" s="174" t="s">
+        <v>148</v>
       </c>
       <c r="C55" s="72"/>
-      <c r="D55" s="117"/>
-      <c r="E55" s="118"/>
-      <c r="F55" s="118"/>
-      <c r="G55" s="118"/>
-      <c r="H55" s="118"/>
-      <c r="I55" s="118"/>
-      <c r="J55" s="118"/>
-      <c r="K55" s="118"/>
-      <c r="L55" s="118"/>
+      <c r="D55" s="80"/>
+      <c r="E55" s="80"/>
+      <c r="F55" s="80"/>
+      <c r="G55" s="80"/>
+      <c r="H55" s="80"/>
+      <c r="I55" s="80"/>
+      <c r="J55" s="80"/>
+      <c r="K55" s="80"/>
+      <c r="L55" s="80"/>
     </row>
     <row r="56" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="33">
         <v>31</v>
       </c>
-      <c r="B56" s="78" t="s">
-        <v>146</v>
-      </c>
-      <c r="C56" s="78"/>
-      <c r="D56" s="117"/>
-      <c r="E56" s="118"/>
-      <c r="F56" s="118"/>
-      <c r="G56" s="118"/>
-      <c r="H56" s="118"/>
-      <c r="I56" s="118"/>
-      <c r="J56" s="118"/>
-      <c r="K56" s="118"/>
-      <c r="L56" s="118"/>
+      <c r="B56" s="174" t="s">
+        <v>149</v>
+      </c>
+      <c r="C56" s="77"/>
+      <c r="D56" s="80"/>
+      <c r="E56" s="80"/>
+      <c r="F56" s="80"/>
+      <c r="G56" s="80"/>
+      <c r="H56" s="80"/>
+      <c r="I56" s="80"/>
+      <c r="J56" s="80"/>
+      <c r="K56" s="80"/>
+      <c r="L56" s="80"/>
     </row>
     <row r="57" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="33">
         <v>32</v>
       </c>
-      <c r="B57" s="78" t="s">
-        <v>147</v>
-      </c>
-      <c r="C57" s="78"/>
-      <c r="D57" s="117"/>
-      <c r="E57" s="118"/>
-      <c r="F57" s="118"/>
-      <c r="G57" s="118"/>
-      <c r="H57" s="118"/>
-      <c r="I57" s="118"/>
-      <c r="J57" s="118"/>
-      <c r="K57" s="118"/>
-      <c r="L57" s="118"/>
+      <c r="B57" s="174" t="s">
+        <v>150</v>
+      </c>
+      <c r="C57" s="77"/>
+      <c r="D57" s="80"/>
+      <c r="E57" s="80"/>
+      <c r="F57" s="80"/>
+      <c r="G57" s="80"/>
+      <c r="H57" s="80"/>
+      <c r="I57" s="80"/>
+      <c r="J57" s="80"/>
+      <c r="K57" s="80"/>
+      <c r="L57" s="80"/>
     </row>
     <row r="58" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="33">
         <v>33</v>
       </c>
-      <c r="B58" s="175" t="s">
-        <v>148</v>
-      </c>
-      <c r="C58" s="78"/>
-      <c r="D58" s="117"/>
-      <c r="E58" s="118"/>
-      <c r="F58" s="118"/>
-      <c r="G58" s="118"/>
-      <c r="H58" s="118"/>
-      <c r="I58" s="118"/>
-      <c r="J58" s="118"/>
-      <c r="K58" s="118"/>
-      <c r="L58" s="118"/>
+      <c r="B58" s="174" t="s">
+        <v>151</v>
+      </c>
+      <c r="C58" s="77"/>
+      <c r="D58" s="80"/>
+      <c r="E58" s="80"/>
+      <c r="F58" s="80"/>
+      <c r="G58" s="80"/>
+      <c r="H58" s="80"/>
+      <c r="I58" s="80"/>
+      <c r="J58" s="80"/>
+      <c r="K58" s="80"/>
+      <c r="L58" s="80"/>
     </row>
     <row r="59" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="33">
         <v>34</v>
       </c>
-      <c r="B59" s="175" t="s">
-        <v>149</v>
-      </c>
-      <c r="C59" s="78"/>
-      <c r="D59" s="117"/>
-      <c r="E59" s="118"/>
-      <c r="F59" s="118"/>
-      <c r="G59" s="118"/>
-      <c r="H59" s="118"/>
-      <c r="I59" s="118"/>
-      <c r="J59" s="118"/>
-      <c r="K59" s="118"/>
-      <c r="L59" s="118"/>
+      <c r="B59" s="174" t="s">
+        <v>152</v>
+      </c>
+      <c r="C59" s="77"/>
+      <c r="D59" s="80"/>
+      <c r="E59" s="80"/>
+      <c r="F59" s="80"/>
+      <c r="G59" s="80"/>
+      <c r="H59" s="80"/>
+      <c r="I59" s="80"/>
+      <c r="J59" s="80"/>
+      <c r="K59" s="80"/>
+      <c r="L59" s="80"/>
     </row>
     <row r="60" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="33">
         <v>35</v>
       </c>
-      <c r="B60" s="78" t="s">
-        <v>150</v>
-      </c>
-      <c r="C60" s="78"/>
-      <c r="D60" s="117"/>
-      <c r="E60" s="118"/>
-      <c r="F60" s="118"/>
-      <c r="G60" s="118"/>
-      <c r="H60" s="118"/>
-      <c r="I60" s="118"/>
-      <c r="J60" s="118"/>
-      <c r="K60" s="118"/>
-      <c r="L60" s="118"/>
+      <c r="B60" s="174" t="s">
+        <v>153</v>
+      </c>
+      <c r="C60" s="77"/>
+      <c r="D60" s="80"/>
+      <c r="E60" s="80"/>
+      <c r="F60" s="80"/>
+      <c r="G60" s="80"/>
+      <c r="H60" s="80"/>
+      <c r="I60" s="80"/>
+      <c r="J60" s="80"/>
+      <c r="K60" s="80"/>
+      <c r="L60" s="80"/>
     </row>
     <row r="61" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="33">
         <v>36</v>
       </c>
-      <c r="B61" s="78" t="s">
-        <v>151</v>
-      </c>
-      <c r="C61" s="78"/>
-      <c r="D61" s="117"/>
-      <c r="E61" s="118"/>
-      <c r="F61" s="118"/>
-      <c r="G61" s="118"/>
-      <c r="H61" s="118"/>
-      <c r="I61" s="118"/>
-      <c r="J61" s="118"/>
-      <c r="K61" s="118"/>
-      <c r="L61" s="118"/>
+      <c r="B61" s="174" t="s">
+        <v>154</v>
+      </c>
+      <c r="C61" s="77"/>
+      <c r="D61" s="80"/>
+      <c r="E61" s="80"/>
+      <c r="F61" s="80"/>
+      <c r="G61" s="80"/>
+      <c r="H61" s="80"/>
+      <c r="I61" s="80"/>
+      <c r="J61" s="80"/>
+      <c r="K61" s="80"/>
+      <c r="L61" s="80"/>
     </row>
     <row r="62" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="33">
         <v>37</v>
       </c>
-      <c r="B62" s="78" t="s">
-        <v>152</v>
-      </c>
-      <c r="C62" s="78"/>
-      <c r="D62" s="117"/>
-      <c r="E62" s="118"/>
-      <c r="F62" s="118"/>
-      <c r="G62" s="118"/>
-      <c r="H62" s="118"/>
-      <c r="I62" s="118"/>
-      <c r="J62" s="118"/>
-      <c r="K62" s="118"/>
-      <c r="L62" s="118"/>
+      <c r="B62" s="174" t="s">
+        <v>121</v>
+      </c>
+      <c r="C62" s="77"/>
+      <c r="D62" s="80"/>
+      <c r="E62" s="80"/>
+      <c r="F62" s="80"/>
+      <c r="G62" s="80"/>
+      <c r="H62" s="80"/>
+      <c r="I62" s="80"/>
+      <c r="J62" s="80"/>
+      <c r="K62" s="80"/>
+      <c r="L62" s="80"/>
     </row>
     <row r="63" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="33">
         <v>38</v>
       </c>
-      <c r="B63" s="78" t="s">
-        <v>153</v>
-      </c>
-      <c r="C63" s="78"/>
-      <c r="D63" s="117"/>
-      <c r="E63" s="118"/>
-      <c r="F63" s="118"/>
-      <c r="G63" s="118"/>
-      <c r="H63" s="118"/>
-      <c r="I63" s="118"/>
-      <c r="J63" s="118"/>
-      <c r="K63" s="118"/>
-      <c r="L63" s="118"/>
+      <c r="B63" s="174" t="s">
+        <v>122</v>
+      </c>
+      <c r="C63" s="77"/>
+      <c r="D63" s="80"/>
+      <c r="E63" s="80"/>
+      <c r="F63" s="80"/>
+      <c r="G63" s="80"/>
+      <c r="H63" s="80"/>
+      <c r="I63" s="80"/>
+      <c r="J63" s="80"/>
+      <c r="K63" s="80"/>
+      <c r="L63" s="80"/>
     </row>
     <row r="64" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="33">
         <v>39</v>
       </c>
-      <c r="B64" s="78" t="s">
-        <v>154</v>
-      </c>
-      <c r="C64" s="78"/>
-      <c r="D64" s="117"/>
-      <c r="E64" s="118"/>
-      <c r="F64" s="118"/>
-      <c r="G64" s="118"/>
-      <c r="H64" s="118"/>
-      <c r="I64" s="118"/>
-      <c r="J64" s="118"/>
-      <c r="K64" s="118"/>
-      <c r="L64" s="118"/>
+      <c r="B64" s="174" t="s">
+        <v>123</v>
+      </c>
+      <c r="C64" s="77"/>
+      <c r="D64" s="80"/>
+      <c r="E64" s="80"/>
+      <c r="F64" s="80"/>
+      <c r="G64" s="80"/>
+      <c r="H64" s="80"/>
+      <c r="I64" s="80"/>
+      <c r="J64" s="80"/>
+      <c r="K64" s="80"/>
+      <c r="L64" s="80"/>
     </row>
     <row r="65" spans="1:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="33"/>
-      <c r="B65" s="33"/>
-      <c r="C65" s="78"/>
-      <c r="D65" s="117"/>
-      <c r="E65" s="118"/>
-      <c r="F65" s="118"/>
-      <c r="G65" s="118"/>
-      <c r="H65" s="118"/>
-      <c r="I65" s="118"/>
-      <c r="J65" s="118"/>
-      <c r="K65" s="118"/>
-      <c r="L65" s="118"/>
+      <c r="A65" s="33">
+        <v>40</v>
+      </c>
+      <c r="B65" s="175" t="s">
+        <v>155</v>
+      </c>
+      <c r="C65" s="77"/>
+      <c r="D65" s="80"/>
+      <c r="E65" s="80"/>
+      <c r="F65" s="80"/>
+      <c r="G65" s="80"/>
+      <c r="H65" s="80"/>
+      <c r="I65" s="80"/>
+      <c r="J65" s="80"/>
+      <c r="K65" s="80"/>
+      <c r="L65" s="80"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A66" s="33"/>
-      <c r="B66" s="34"/>
-      <c r="C66" s="78"/>
-      <c r="D66" s="117"/>
-      <c r="E66" s="118"/>
-      <c r="F66" s="118"/>
-      <c r="G66" s="118"/>
-      <c r="H66" s="118"/>
-      <c r="I66" s="118"/>
-      <c r="J66" s="118"/>
-      <c r="K66" s="118"/>
-      <c r="L66" s="118"/>
+      <c r="A66" s="33">
+        <v>41</v>
+      </c>
+      <c r="B66" s="172" t="s">
+        <v>156</v>
+      </c>
+      <c r="C66" s="77"/>
+      <c r="D66" s="80"/>
+      <c r="E66" s="80"/>
+      <c r="F66" s="80"/>
+      <c r="G66" s="80"/>
+      <c r="H66" s="80"/>
+      <c r="I66" s="80"/>
+      <c r="J66" s="80"/>
+      <c r="K66" s="80"/>
+      <c r="L66" s="80"/>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A67" s="33">
+        <v>42</v>
+      </c>
+      <c r="B67" s="175" t="s">
+        <v>157</v>
+      </c>
+      <c r="C67" s="175"/>
+      <c r="D67" s="176"/>
+      <c r="E67" s="176"/>
+      <c r="F67" s="176"/>
+      <c r="G67" s="176"/>
+      <c r="H67" s="176"/>
+      <c r="I67" s="176"/>
+      <c r="J67" s="176"/>
+      <c r="K67" s="176"/>
+      <c r="L67" s="176"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="D26:L66"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:L20"/>
-    <mergeCell ref="D25:L25"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:L22"/>
     <mergeCell ref="A16:L16"/>
     <mergeCell ref="A17:L17"/>
     <mergeCell ref="B15:L15"/>
@@ -13030,6 +13253,14 @@
     <mergeCell ref="B4:L4"/>
     <mergeCell ref="B5:L5"/>
     <mergeCell ref="B7:L7"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:L20"/>
+    <mergeCell ref="D25:L25"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:L22"/>
+    <mergeCell ref="D26:L67"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D26" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -16203,6 +16434,72 @@
                     <xdr:colOff>1409700</xdr:colOff>
                     <xdr:row>29</xdr:row>
                     <xdr:rowOff>228600</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1249" r:id="rId149" name="Drop Down 225">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>64</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>1409700</xdr:colOff>
+                    <xdr:row>64</xdr:row>
+                    <xdr:rowOff>220980</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1250" r:id="rId150" name="Drop Down 226">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>65</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>1409700</xdr:colOff>
+                    <xdr:row>66</xdr:row>
+                    <xdr:rowOff>38100</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1251" r:id="rId151" name="Drop Down 227">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>66</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>1409700</xdr:colOff>
+                    <xdr:row>67</xdr:row>
+                    <xdr:rowOff>38100</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -16232,50 +16529,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="148" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="153"/>
-      <c r="C1" s="153"/>
-      <c r="D1" s="153"/>
-      <c r="E1" s="153"/>
-      <c r="F1" s="153"/>
-      <c r="G1" s="153"/>
-      <c r="H1" s="153"/>
-      <c r="I1" s="153"/>
-      <c r="J1" s="153"/>
-      <c r="K1" s="153"/>
-      <c r="L1" s="154"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="150"/>
     </row>
     <row r="2" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="151" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="156"/>
-      <c r="C2" s="156"/>
-      <c r="D2" s="156"/>
-      <c r="E2" s="156"/>
-      <c r="F2" s="156"/>
-      <c r="G2" s="156"/>
-      <c r="H2" s="156"/>
-      <c r="I2" s="156"/>
-      <c r="J2" s="156"/>
-      <c r="K2" s="156"/>
-      <c r="L2" s="157"/>
+      <c r="B2" s="152"/>
+      <c r="C2" s="152"/>
+      <c r="D2" s="152"/>
+      <c r="E2" s="152"/>
+      <c r="F2" s="152"/>
+      <c r="G2" s="152"/>
+      <c r="H2" s="152"/>
+      <c r="I2" s="152"/>
+      <c r="J2" s="152"/>
+      <c r="K2" s="152"/>
+      <c r="L2" s="153"/>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="158"/>
-      <c r="B3" s="159"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="159"/>
-      <c r="G3" s="159"/>
-      <c r="H3" s="159"/>
-      <c r="I3" s="159"/>
-      <c r="J3" s="159"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="160"/>
+      <c r="A3" s="154"/>
+      <c r="B3" s="155"/>
+      <c r="C3" s="155"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="155"/>
+      <c r="F3" s="155"/>
+      <c r="G3" s="155"/>
+      <c r="H3" s="155"/>
+      <c r="I3" s="155"/>
+      <c r="J3" s="155"/>
+      <c r="K3" s="155"/>
+      <c r="L3" s="156"/>
     </row>
     <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
@@ -16365,65 +16662,65 @@
       <c r="A8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="163"/>
-      <c r="C8" s="164"/>
-      <c r="D8" s="164"/>
-      <c r="E8" s="164"/>
-      <c r="F8" s="164"/>
-      <c r="G8" s="164"/>
-      <c r="H8" s="164"/>
-      <c r="I8" s="164"/>
-      <c r="J8" s="164"/>
-      <c r="K8" s="164"/>
-      <c r="L8" s="165"/>
+      <c r="B8" s="159"/>
+      <c r="C8" s="160"/>
+      <c r="D8" s="160"/>
+      <c r="E8" s="160"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="160"/>
+      <c r="H8" s="160"/>
+      <c r="I8" s="160"/>
+      <c r="J8" s="160"/>
+      <c r="K8" s="160"/>
+      <c r="L8" s="161"/>
     </row>
     <row r="9" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="166"/>
-      <c r="C9" s="164"/>
-      <c r="D9" s="164"/>
-      <c r="E9" s="164"/>
-      <c r="F9" s="164"/>
-      <c r="G9" s="164"/>
-      <c r="H9" s="164"/>
-      <c r="I9" s="164"/>
-      <c r="J9" s="164"/>
-      <c r="K9" s="164"/>
-      <c r="L9" s="165"/>
+      <c r="B9" s="162"/>
+      <c r="C9" s="160"/>
+      <c r="D9" s="160"/>
+      <c r="E9" s="160"/>
+      <c r="F9" s="160"/>
+      <c r="G9" s="160"/>
+      <c r="H9" s="160"/>
+      <c r="I9" s="160"/>
+      <c r="J9" s="160"/>
+      <c r="K9" s="160"/>
+      <c r="L9" s="161"/>
     </row>
     <row r="10" spans="1:12" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="161" t="s">
+      <c r="A10" s="157" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="162"/>
-      <c r="C10" s="162"/>
-      <c r="D10" s="162"/>
-      <c r="E10" s="162"/>
-      <c r="F10" s="162"/>
-      <c r="G10" s="162"/>
-      <c r="H10" s="162"/>
-      <c r="I10" s="162"/>
-      <c r="J10" s="162"/>
-      <c r="K10" s="162"/>
-      <c r="L10" s="162"/>
+      <c r="B10" s="158"/>
+      <c r="C10" s="158"/>
+      <c r="D10" s="158"/>
+      <c r="E10" s="158"/>
+      <c r="F10" s="158"/>
+      <c r="G10" s="158"/>
+      <c r="H10" s="158"/>
+      <c r="I10" s="158"/>
+      <c r="J10" s="158"/>
+      <c r="K10" s="158"/>
+      <c r="L10" s="158"/>
     </row>
     <row r="11" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="143" t="s">
+      <c r="A11" s="139" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="144"/>
-      <c r="C11" s="144"/>
-      <c r="D11" s="144"/>
-      <c r="E11" s="144"/>
-      <c r="F11" s="144"/>
-      <c r="G11" s="144"/>
-      <c r="H11" s="144"/>
-      <c r="I11" s="144"/>
-      <c r="J11" s="144"/>
-      <c r="K11" s="144"/>
-      <c r="L11" s="145"/>
+      <c r="B11" s="140"/>
+      <c r="C11" s="140"/>
+      <c r="D11" s="140"/>
+      <c r="E11" s="140"/>
+      <c r="F11" s="140"/>
+      <c r="G11" s="140"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="140"/>
+      <c r="K11" s="140"/>
+      <c r="L11" s="141"/>
     </row>
     <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
@@ -16435,101 +16732,101 @@
       <c r="C12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="127" t="s">
+      <c r="D12" s="89" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="127"/>
-      <c r="F12" s="127"/>
-      <c r="G12" s="127"/>
-      <c r="H12" s="127"/>
-      <c r="I12" s="127"/>
-      <c r="J12" s="127"/>
-      <c r="K12" s="127"/>
-      <c r="L12" s="127"/>
+      <c r="E12" s="89"/>
+      <c r="F12" s="89"/>
+      <c r="G12" s="89"/>
+      <c r="H12" s="89"/>
+      <c r="I12" s="89"/>
+      <c r="J12" s="89"/>
+      <c r="K12" s="89"/>
+      <c r="L12" s="89"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="49"/>
       <c r="B13" s="50"/>
       <c r="C13" s="50"/>
-      <c r="D13" s="146"/>
-      <c r="E13" s="147"/>
-      <c r="F13" s="147"/>
-      <c r="G13" s="147"/>
-      <c r="H13" s="147"/>
-      <c r="I13" s="147"/>
-      <c r="J13" s="147"/>
-      <c r="K13" s="147"/>
-      <c r="L13" s="148"/>
+      <c r="D13" s="142"/>
+      <c r="E13" s="143"/>
+      <c r="F13" s="143"/>
+      <c r="G13" s="143"/>
+      <c r="H13" s="143"/>
+      <c r="I13" s="143"/>
+      <c r="J13" s="143"/>
+      <c r="K13" s="143"/>
+      <c r="L13" s="144"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="49"/>
       <c r="B14" s="50"/>
       <c r="C14" s="50"/>
-      <c r="D14" s="149"/>
-      <c r="E14" s="150"/>
-      <c r="F14" s="150"/>
-      <c r="G14" s="150"/>
-      <c r="H14" s="150"/>
-      <c r="I14" s="150"/>
-      <c r="J14" s="150"/>
-      <c r="K14" s="150"/>
-      <c r="L14" s="151"/>
+      <c r="D14" s="145"/>
+      <c r="E14" s="146"/>
+      <c r="F14" s="146"/>
+      <c r="G14" s="146"/>
+      <c r="H14" s="146"/>
+      <c r="I14" s="146"/>
+      <c r="J14" s="146"/>
+      <c r="K14" s="146"/>
+      <c r="L14" s="147"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="49"/>
       <c r="B15" s="50"/>
       <c r="C15" s="50"/>
-      <c r="D15" s="149"/>
-      <c r="E15" s="150"/>
-      <c r="F15" s="150"/>
-      <c r="G15" s="150"/>
-      <c r="H15" s="150"/>
-      <c r="I15" s="150"/>
-      <c r="J15" s="150"/>
-      <c r="K15" s="150"/>
-      <c r="L15" s="151"/>
+      <c r="D15" s="145"/>
+      <c r="E15" s="146"/>
+      <c r="F15" s="146"/>
+      <c r="G15" s="146"/>
+      <c r="H15" s="146"/>
+      <c r="I15" s="146"/>
+      <c r="J15" s="146"/>
+      <c r="K15" s="146"/>
+      <c r="L15" s="147"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="49"/>
       <c r="B16" s="50"/>
       <c r="C16" s="50"/>
-      <c r="D16" s="149"/>
-      <c r="E16" s="150"/>
-      <c r="F16" s="150"/>
-      <c r="G16" s="150"/>
-      <c r="H16" s="150"/>
-      <c r="I16" s="150"/>
-      <c r="J16" s="150"/>
-      <c r="K16" s="150"/>
-      <c r="L16" s="151"/>
+      <c r="D16" s="145"/>
+      <c r="E16" s="146"/>
+      <c r="F16" s="146"/>
+      <c r="G16" s="146"/>
+      <c r="H16" s="146"/>
+      <c r="I16" s="146"/>
+      <c r="J16" s="146"/>
+      <c r="K16" s="146"/>
+      <c r="L16" s="147"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="49"/>
       <c r="B17" s="50"/>
       <c r="C17" s="50"/>
-      <c r="D17" s="149"/>
-      <c r="E17" s="150"/>
-      <c r="F17" s="150"/>
-      <c r="G17" s="150"/>
-      <c r="H17" s="150"/>
-      <c r="I17" s="150"/>
-      <c r="J17" s="150"/>
-      <c r="K17" s="150"/>
-      <c r="L17" s="151"/>
+      <c r="D17" s="145"/>
+      <c r="E17" s="146"/>
+      <c r="F17" s="146"/>
+      <c r="G17" s="146"/>
+      <c r="H17" s="146"/>
+      <c r="I17" s="146"/>
+      <c r="J17" s="146"/>
+      <c r="K17" s="146"/>
+      <c r="L17" s="147"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="49"/>
       <c r="B18" s="50"/>
       <c r="C18" s="50"/>
-      <c r="D18" s="149"/>
-      <c r="E18" s="150"/>
-      <c r="F18" s="150"/>
-      <c r="G18" s="150"/>
-      <c r="H18" s="150"/>
-      <c r="I18" s="150"/>
-      <c r="J18" s="150"/>
-      <c r="K18" s="150"/>
-      <c r="L18" s="151"/>
+      <c r="D18" s="145"/>
+      <c r="E18" s="146"/>
+      <c r="F18" s="146"/>
+      <c r="G18" s="146"/>
+      <c r="H18" s="146"/>
+      <c r="I18" s="146"/>
+      <c r="J18" s="146"/>
+      <c r="K18" s="146"/>
+      <c r="L18" s="147"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -16618,10 +16915,10 @@
       <c r="B4" s="63"/>
     </row>
     <row r="6" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="163" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="80"/>
+      <c r="B6" s="163"/>
     </row>
     <row r="8" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="66" t="s">
@@ -16774,55 +17071,55 @@
   <sheetData>
     <row r="1" spans="2:6" ht="5.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B2" s="168"/>
-      <c r="C2" s="168"/>
-      <c r="D2" s="169" t="s">
+      <c r="B2" s="165"/>
+      <c r="C2" s="165"/>
+      <c r="D2" s="166" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="170" t="s">
+      <c r="E2" s="167" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="170"/>
+      <c r="F2" s="167"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B3" s="168"/>
-      <c r="C3" s="168"/>
-      <c r="D3" s="169"/>
-      <c r="E3" s="170"/>
-      <c r="F3" s="170"/>
+      <c r="B3" s="165"/>
+      <c r="C3" s="165"/>
+      <c r="D3" s="166"/>
+      <c r="E3" s="167"/>
+      <c r="F3" s="167"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="168"/>
-      <c r="C4" s="168"/>
-      <c r="D4" s="169"/>
-      <c r="E4" s="170" t="s">
+      <c r="B4" s="165"/>
+      <c r="C4" s="165"/>
+      <c r="D4" s="166"/>
+      <c r="E4" s="167" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="170"/>
+      <c r="F4" s="167"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="171" t="s">
+      <c r="B5" s="168" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="171"/>
+      <c r="C5" s="168"/>
       <c r="D5" s="70" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="172" t="s">
+      <c r="E5" s="169" t="s">
         <v>54</v>
       </c>
-      <c r="F5" s="172"/>
+      <c r="F5" s="169"/>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="167" t="s">
+      <c r="C6" s="164" t="s">
         <v>114</v>
       </c>
-      <c r="D6" s="167"/>
-      <c r="E6" s="167"/>
-      <c r="F6" s="167"/>
+      <c r="D6" s="164"/>
+      <c r="E6" s="164"/>
+      <c r="F6" s="164"/>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="71" t="s">
@@ -17079,10 +17376,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="27" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="173" t="s">
+      <c r="A1" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="174"/>
+      <c r="B1" s="171"/>
     </row>
     <row r="2" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="28" t="s">
@@ -17353,6 +17650,68 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50">
+      <UserInfo>
+        <DisplayName>Luis Campos / Logiztik Alliance</DisplayName>
+        <AccountId>265</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Jairo Gonzalez / Logiztik Alliance</DisplayName>
+        <AccountId>322</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>José Ganchozo / Logiztik Alliance</DisplayName>
+        <AccountId>304</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Edwin Casa / Logiztik Alliance</DisplayName>
+        <AccountId>299</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Cristhian Cuichan / Logiztik Alliance</DisplayName>
+        <AccountId>369</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Oscar Yunda /  Logiztik Alliance</DisplayName>
+        <AccountId>355</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Fernando Ordoñez / Logiztik Alliance</DisplayName>
+        <AccountId>321</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Alex Rivera / Logiztik Alliance</DisplayName>
+        <AccountId>370</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <TaxCatchAll xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="87481c51-c14c-4071-bf64-faa2b5708bb6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101005DA7AC6E4F4FAE42B9D9FCD9C82CAAE1" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="553e0bb76796fbad2df2b84fb95dc83d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="87481c51-c14c-4071-bf64-faa2b5708bb6" xmlns:ns3="8029d101-3d2a-47c4-b15f-619642bf5e50" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d87cd7f238c73dc12c577d08dde48736" ns2:_="" ns3:_="">
     <xsd:import namespace="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
@@ -17601,69 +17960,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD069904-634F-48DA-AA92-BAE250498BEE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8029d101-3d2a-47c4-b15f-619642bf5e50"/>
+    <ds:schemaRef ds:uri="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50">
-      <UserInfo>
-        <DisplayName>Luis Campos / Logiztik Alliance</DisplayName>
-        <AccountId>265</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Jairo Gonzalez / Logiztik Alliance</DisplayName>
-        <AccountId>322</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>José Ganchozo / Logiztik Alliance</DisplayName>
-        <AccountId>304</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Edwin Casa / Logiztik Alliance</DisplayName>
-        <AccountId>299</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Cristhian Cuichan / Logiztik Alliance</DisplayName>
-        <AccountId>369</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Oscar Yunda /  Logiztik Alliance</DisplayName>
-        <AccountId>355</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Fernando Ordoñez / Logiztik Alliance</DisplayName>
-        <AccountId>321</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Alex Rivera / Logiztik Alliance</DisplayName>
-        <AccountId>370</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <TaxCatchAll xmlns="8029d101-3d2a-47c4-b15f-619642bf5e50" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="87481c51-c14c-4071-bf64-faa2b5708bb6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371D8832-41B3-447B-B13D-2663C267E34F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F7F06D0-41B3-4EAF-B418-88FC726117CC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17680,23 +17996,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{371D8832-41B3-447B-B13D-2663C267E34F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD069904-634F-48DA-AA92-BAE250498BEE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8029d101-3d2a-47c4-b15f-619642bf5e50"/>
-    <ds:schemaRef ds:uri="87481c51-c14c-4071-bf64-faa2b5708bb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>